--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="criteria" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$V$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$W$287</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>53 records</t>
+          <t>55 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>75 records</t>
+          <t>79 records</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3696,8 +3696,120 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>'No podcast' is the WRONG filter for Johnnie's leg 1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Nurture; the podcast-target roster</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Redefines the target list</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 16 Jul 2026: 'Nurture is one of the most significant categories... johnnie emphasized that evangelicals are under indexing in podcasting so I think a top goal will be identifying christian zionists with long-form audio-video potential.' The existing filter (podcastStatus = 'No podcast (TARGET)', 61 people) does not survive contact with the facts, for TWO separate reasons. (1) IT IS FACTUALLY WRONG: verified against the Apple Podcasts API on 16 Jul 2026, at least 13 of the 61 ALREADY HOST ACTIVE PODCASTS -- Riley Gaines (The Riley Gaines Show, 196 eps, Fox), Ben Ferguson (2,032 eps), Brandon Tatum (The Officer Tatum Show), Nick Shirley, CJ Pearson, Jentezen Franklin (361), Allen Jackson (796), Larry Huch (553), Joni Lamb (575), Tony Perkins (201), Susan Michael (287), Laurie Cardoza-Moore, Joshua Carr (568). Handing Johnnie a 'move these people into podcasting' list led by a Fox host with 196 episodes would be humiliating. (2) IT IS CONCEPTUALLY WRONG, which matters more. Evangelicals do NOT under-index in SERMON podcasting -- that genre is saturated (Franklin 361, Jackson 796, Huch 553, Lamb 575). They under-index in CONVERSATIONAL long-form: the Rogan / Lex / Shapiro / Theo Von format. A sermon is broadcast; a podcast is conversation. Those are different skills and different products. THE FILTER SHOULD BE: proven long-form delivery + significant audience + NOT YET in conversational long-form + available. Not merely 'has no RSS feed'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Long-form A/V potential: the scoring rubric</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Nurture roster candidates</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Ranks podcast targets</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Rank on these, highest weight first. (1) PROVEN LONG-FORM DELIVERY -- do they already hold an audience for 30+ minutes anywhere? Sermons, lectures, streams, teaching, standup. This is the single strongest signal and the most under-exploited: A PASTOR ALREADY DELIVERS 40 MINUTES TO CAMERA EVERY WEEK, with a built-in audience. The gap is format and distribution, not ability. Johnnie came from exactly that world (Liberty). (2) CONVERSATIONAL RANGE -- can they be INTERVIEWED, not just deliver? Look for guest appearances on other shows. A preacher who cannot do dialogue will not survive the format. Wesley Huff is the proof case: his Rogan appearance was the whole breakout, and it was conversation, not preaching. (3) AUDIENCE ON THE WRONG PLATFORM -- big on TikTok/IG/X (short-form) with no long-form home. That IS the arbitrage. Allie Schnacky (4M+ TikTok) is the archetype. (4) AVAILABILITY -- this disqualifies most of the current list. A sitting Speaker of the House, a sitting Senator, an 83-year-old megachurch founder, or someone running a $700M NGO is NOT going to start a podcast. Screen for career stage: building and hungry, not established and busy. (5) US/ENGLISH AUDIENCE -- per the audience-geography criterion, which outranks nationality. The current list carries Japanese, Hungarian, Kenyan, Congolese and Latin American pastors: real allies, real networks, but not answers to 'evangelicals under-index in AMERICAN podcasting'. Keep them as allies; remove them from THIS list. (6) A 'WHY NOW' -- a book, a controversy, a viral moment, a platform shift. Podcasts launch off momentum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Podcast status must be VERIFIED, never asserted</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Every podcast/roster claim</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>The Apple Podcasts search API is free, needs no key, and returns show name, host, episode count and last-release date: https://itunes.apple.com/search?media=podcast&amp;term=NAME&amp;country=US -- use it before tagging anyone. CAUTION, learned the hard way on 16 Jul 2026: automated name-matching FAILS IN BOTH DIRECTIONS and cannot be trusted unattended. Loose matching produced false positives -- 'Mike Johnson' matched a cybersecurity podcast and a Baptist church, 'Tim Scott' matched a Walt Disney World fan podcast, and 'Manny Pacquiao - Audio Biography' is a show ABOUT him, not BY him. Tightening it to require the person as credited artist then produced false NEGATIVES -- it lost Riley Gaines and Ben Ferguson, because their shows are credited to FOX, not to them. There is no regex that solves this. Verify each candidate by eye. Record the show, episode count, last-release date and the date checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>DORMANT beats ABSENT as a podcast target</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Inclusion Signal</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Nurture roster</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Prioritisation</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>A dormant podcast is a BETTER leg-1 target than no podcast at all, and this inverts the intuition. Someone who ran a show and stopped has already proven they can do it, already has a feed and back catalogue, and already built some audience -- they need a reason and backing to restart, not persuading that they are capable. Someone who never started is an unproven bet on latent ability. Verified example: Allie Schnacky hosted 'Keep It Real' (44 episodes, last 27 Jul 2025) alongside 4M+ TikTok followers. She is not a 'can she do it?' question, she is a 'why did she stop?' question -- and that is a far cheaper thing for BFT to fix. Sweep the full roster for dormant feeds; they are the cheapest wins on the board.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F76"/>
+  <autoFilter ref="A1:F80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3708,7 +3820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V287"/>
+  <dimension ref="A1:W287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3721,18 +3833,19 @@
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3803,45 +3916,50 @@
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
+          <t>podcastCheck</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
           <t>allianceScore</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>researchNotes</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>entSubcategory</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>audienceVerified</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>related</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>nationality</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>addedBy</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>audienceGeography</t>
         </is>
@@ -3910,6 +4028,7 @@
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3986,6 +4105,7 @@
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4050,6 +4170,7 @@
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4114,6 +4235,7 @@
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4190,6 +4312,7 @@
       <c r="T6" s="6" t="inlineStr"/>
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4266,6 +4389,7 @@
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4342,6 +4466,7 @@
       <c r="T8" s="6" t="inlineStr"/>
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4406,6 +4531,7 @@
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4482,6 +4608,7 @@
       <c r="T10" s="6" t="inlineStr"/>
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4558,6 +4685,7 @@
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4622,6 +4750,7 @@
       <c r="T12" s="6" t="inlineStr"/>
       <c r="U12" s="6" t="inlineStr"/>
       <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4686,6 +4815,7 @@
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4750,6 +4880,7 @@
       <c r="T14" s="6" t="inlineStr"/>
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4814,6 +4945,7 @@
       <c r="T15" s="6" t="inlineStr"/>
       <c r="U15" s="6" t="inlineStr"/>
       <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4864,12 +4996,12 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The Officer Tatum Show (100 eps, latest 2026-07-14)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -4877,7 +5009,11 @@
           <t>1.5M+ combined</t>
         </is>
       </c>
-      <c r="N16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The Officer Tatum Show': 100 episodes, latest 2026-07-14. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
@@ -4886,6 +5022,7 @@
       <c r="T16" s="6" t="inlineStr"/>
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4946,6 +5083,7 @@
       <c r="T17" s="6" t="inlineStr"/>
       <c r="U17" s="6" t="inlineStr"/>
       <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5006,6 +5144,7 @@
       <c r="T18" s="6" t="inlineStr"/>
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5078,6 +5217,7 @@
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
       <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5138,6 +5278,7 @@
       <c r="T20" s="6" t="inlineStr"/>
       <c r="U20" s="6" t="inlineStr"/>
       <c r="V20" s="6" t="inlineStr"/>
+      <c r="W20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5198,6 +5339,7 @@
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5258,6 +5400,7 @@
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5318,6 +5461,7 @@
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5390,6 +5534,7 @@
       <c r="T24" s="6" t="inlineStr"/>
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5462,6 +5607,7 @@
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5512,12 +5658,12 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Focus on Israel (OnePlace) (20 eps, latest 2026-07-03)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -5525,7 +5671,11 @@
           <t>National reach</t>
         </is>
       </c>
-      <c r="N26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Focus on Israel (OnePlace)': 20 episodes, latest 2026-07-03. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
@@ -5534,6 +5684,7 @@
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5584,12 +5735,12 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Jentezen Franklin at Free Chapel (361 eps, latest 2026-06-28)</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -5597,7 +5748,11 @@
           <t>Large global reach</t>
         </is>
       </c>
-      <c r="N27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Jentezen Franklin at Free Chapel': 361 episodes, latest 2026-06-28. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
@@ -5606,6 +5761,7 @@
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5678,6 +5834,7 @@
       <c r="T28" s="6" t="inlineStr"/>
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5750,6 +5907,7 @@
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5822,6 +5980,7 @@
       <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5894,6 +6053,7 @@
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -5944,12 +6104,12 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Allen Jackson Ministries: Sermon Podcast (796 eps, latest 2026-07-14)</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -5957,7 +6117,11 @@
           <t>3M+ weekly worldwide</t>
         </is>
       </c>
-      <c r="N32" s="6" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Allen Jackson Ministries: Sermon Podcast': 796 episodes, latest 2026-07-14. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
@@ -5966,6 +6130,7 @@
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6026,6 +6191,7 @@
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -6086,6 +6252,7 @@
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -6136,12 +6303,12 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The Josh Carr Show (568 eps, latest 2026-07-16)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -6149,7 +6316,11 @@
           <t>64K subscribers</t>
         </is>
       </c>
-      <c r="N35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The Josh Carr Show': 568 episodes, latest 2026-07-16. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
@@ -6158,6 +6329,7 @@
       <c r="T35" s="6" t="inlineStr"/>
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6208,12 +6380,12 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The CJ Pearson Show (19 eps, latest 2026-02-19)</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -6221,7 +6393,11 @@
           <t>1M+ followers</t>
         </is>
       </c>
-      <c r="N36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The CJ Pearson Show': 19 episodes, latest 2026-02-19. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
@@ -6230,6 +6406,7 @@
       <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -6290,6 +6467,7 @@
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -6354,6 +6532,7 @@
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -6414,6 +6593,7 @@
       <c r="T39" s="6" t="inlineStr"/>
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -6474,6 +6654,7 @@
       <c r="T40" s="6" t="inlineStr"/>
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -6534,6 +6715,7 @@
       <c r="T41" s="6" t="inlineStr"/>
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -6594,6 +6776,7 @@
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -6654,6 +6837,7 @@
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -6714,6 +6898,7 @@
       <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -6774,6 +6959,7 @@
       <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -6834,6 +7020,7 @@
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -6894,6 +7081,7 @@
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -6954,6 +7142,7 @@
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -7014,6 +7203,7 @@
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7074,6 +7264,7 @@
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -7134,6 +7325,7 @@
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7194,6 +7386,7 @@
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -7254,6 +7447,7 @@
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7314,6 +7508,7 @@
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -7374,6 +7569,7 @@
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7446,6 +7642,7 @@
       <c r="T56" s="6" t="inlineStr"/>
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -7496,7 +7693,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>DORMANT PODCAST -- Keep It Real (44 eps, last 2025-07-27)</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -7509,7 +7706,11 @@
           <t>4M+ TikTok</t>
         </is>
       </c>
-      <c r="N57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026: DORMANT, not absent. Hosted 'Keep It Real' (44 episodes, last 2025-07-27). This is arguably a BETTER leg-1 target than someone who never started -- capability is proven, the feed exists, the audience was built. They need a reason and backing to restart, not persuading that they can.</t>
+        </is>
+      </c>
       <c r="O57" s="6" t="inlineStr"/>
       <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="6" t="inlineStr"/>
@@ -7518,6 +7719,7 @@
       <c r="T57" s="6" t="inlineStr"/>
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -7578,6 +7780,7 @@
       <c r="T58" s="6" t="inlineStr"/>
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -7638,6 +7841,7 @@
       <c r="T59" s="6" t="inlineStr"/>
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -7698,6 +7902,7 @@
       <c r="T60" s="6" t="inlineStr"/>
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -7758,6 +7963,7 @@
       <c r="T61" s="6" t="inlineStr"/>
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -7818,6 +8024,7 @@
       <c r="T62" s="6" t="inlineStr"/>
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -7878,6 +8085,7 @@
       <c r="T63" s="6" t="inlineStr"/>
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -7938,6 +8146,7 @@
       <c r="T64" s="6" t="inlineStr"/>
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -7998,6 +8207,7 @@
       <c r="T65" s="6" t="inlineStr"/>
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -8058,6 +8268,7 @@
       <c r="T66" s="6" t="inlineStr"/>
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -8118,6 +8329,7 @@
       <c r="T67" s="6" t="inlineStr"/>
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -8168,12 +8380,12 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The Ben Ferguson Podcast (2032 eps, latest 2026-07-16)</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -8181,7 +8393,11 @@
           <t>156.8K X followers</t>
         </is>
       </c>
-      <c r="N68" s="6" t="inlineStr"/>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The Ben Ferguson Podcast': 2032 episodes, latest 2026-07-16. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
       <c r="O68" s="6" t="inlineStr"/>
       <c r="P68" s="6" t="inlineStr"/>
       <c r="Q68" s="6" t="inlineStr"/>
@@ -8190,6 +8406,7 @@
       <c r="T68" s="6" t="inlineStr"/>
       <c r="U68" s="6" t="inlineStr"/>
       <c r="V68" s="6" t="inlineStr"/>
+      <c r="W68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -8262,6 +8479,7 @@
       <c r="T69" s="6" t="inlineStr"/>
       <c r="U69" s="6" t="inlineStr"/>
       <c r="V69" s="6" t="inlineStr"/>
+      <c r="W69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -8322,6 +8540,7 @@
       <c r="T70" s="6" t="inlineStr"/>
       <c r="U70" s="6" t="inlineStr"/>
       <c r="V70" s="6" t="inlineStr"/>
+      <c r="W70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -8382,6 +8601,7 @@
       <c r="T71" s="6" t="inlineStr"/>
       <c r="U71" s="6" t="inlineStr"/>
       <c r="V71" s="6" t="inlineStr"/>
+      <c r="W71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8442,6 +8662,7 @@
       <c r="T72" s="6" t="inlineStr"/>
       <c r="U72" s="6" t="inlineStr"/>
       <c r="V72" s="6" t="inlineStr"/>
+      <c r="W72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8514,6 +8735,7 @@
       <c r="T73" s="6" t="inlineStr"/>
       <c r="U73" s="6" t="inlineStr"/>
       <c r="V73" s="6" t="inlineStr"/>
+      <c r="W73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -8574,6 +8796,7 @@
       <c r="T74" s="6" t="inlineStr"/>
       <c r="U74" s="6" t="inlineStr"/>
       <c r="V74" s="6" t="inlineStr"/>
+      <c r="W74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -8634,6 +8857,7 @@
       <c r="T75" s="6" t="inlineStr"/>
       <c r="U75" s="6" t="inlineStr"/>
       <c r="V75" s="6" t="inlineStr"/>
+      <c r="W75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -8694,6 +8918,7 @@
       <c r="T76" s="6" t="inlineStr"/>
       <c r="U76" s="6" t="inlineStr"/>
       <c r="V76" s="6" t="inlineStr"/>
+      <c r="W76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -8766,6 +8991,7 @@
       <c r="T77" s="6" t="inlineStr"/>
       <c r="U77" s="6" t="inlineStr"/>
       <c r="V77" s="6" t="inlineStr"/>
+      <c r="W77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -8826,6 +9052,7 @@
       <c r="T78" s="6" t="inlineStr"/>
       <c r="U78" s="6" t="inlineStr"/>
       <c r="V78" s="6" t="inlineStr"/>
+      <c r="W78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -8898,6 +9125,7 @@
       <c r="T79" s="6" t="inlineStr"/>
       <c r="U79" s="6" t="inlineStr"/>
       <c r="V79" s="6" t="inlineStr"/>
+      <c r="W79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -8958,6 +9186,7 @@
       <c r="T80" s="6" t="inlineStr"/>
       <c r="U80" s="6" t="inlineStr"/>
       <c r="V80" s="6" t="inlineStr"/>
+      <c r="W80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -9018,6 +9247,7 @@
       <c r="T81" s="6" t="inlineStr"/>
       <c r="U81" s="6" t="inlineStr"/>
       <c r="V81" s="6" t="inlineStr"/>
+      <c r="W81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -9078,6 +9308,7 @@
       <c r="T82" s="6" t="inlineStr"/>
       <c r="U82" s="6" t="inlineStr"/>
       <c r="V82" s="6" t="inlineStr"/>
+      <c r="W82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -9138,6 +9369,7 @@
       <c r="T83" s="6" t="inlineStr"/>
       <c r="U83" s="6" t="inlineStr"/>
       <c r="V83" s="6" t="inlineStr"/>
+      <c r="W83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -9210,6 +9442,7 @@
       <c r="T84" s="6" t="inlineStr"/>
       <c r="U84" s="6" t="inlineStr"/>
       <c r="V84" s="6" t="inlineStr"/>
+      <c r="W84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -9270,6 +9503,7 @@
       <c r="T85" s="6" t="inlineStr"/>
       <c r="U85" s="6" t="inlineStr"/>
       <c r="V85" s="6" t="inlineStr"/>
+      <c r="W85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -9342,6 +9576,7 @@
       <c r="T86" s="6" t="inlineStr"/>
       <c r="U86" s="6" t="inlineStr"/>
       <c r="V86" s="6" t="inlineStr"/>
+      <c r="W86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -9402,6 +9637,7 @@
       <c r="T87" s="6" t="inlineStr"/>
       <c r="U87" s="6" t="inlineStr"/>
       <c r="V87" s="6" t="inlineStr"/>
+      <c r="W87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -9462,6 +9698,7 @@
       <c r="T88" s="6" t="inlineStr"/>
       <c r="U88" s="6" t="inlineStr"/>
       <c r="V88" s="6" t="inlineStr"/>
+      <c r="W88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -9522,6 +9759,7 @@
       <c r="T89" s="6" t="inlineStr"/>
       <c r="U89" s="6" t="inlineStr"/>
       <c r="V89" s="6" t="inlineStr"/>
+      <c r="W89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -9582,6 +9820,7 @@
       <c r="T90" s="6" t="inlineStr"/>
       <c r="U90" s="6" t="inlineStr"/>
       <c r="V90" s="6" t="inlineStr"/>
+      <c r="W90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -9642,6 +9881,7 @@
       <c r="T91" s="6" t="inlineStr"/>
       <c r="U91" s="6" t="inlineStr"/>
       <c r="V91" s="6" t="inlineStr"/>
+      <c r="W91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -9702,6 +9942,7 @@
       <c r="T92" s="6" t="inlineStr"/>
       <c r="U92" s="6" t="inlineStr"/>
       <c r="V92" s="6" t="inlineStr"/>
+      <c r="W92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -9762,6 +10003,7 @@
       <c r="T93" s="6" t="inlineStr"/>
       <c r="U93" s="6" t="inlineStr"/>
       <c r="V93" s="6" t="inlineStr"/>
+      <c r="W93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -9822,6 +10064,7 @@
       <c r="T94" s="6" t="inlineStr"/>
       <c r="U94" s="6" t="inlineStr"/>
       <c r="V94" s="6" t="inlineStr"/>
+      <c r="W94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -9882,6 +10125,7 @@
       <c r="T95" s="6" t="inlineStr"/>
       <c r="U95" s="6" t="inlineStr"/>
       <c r="V95" s="6" t="inlineStr"/>
+      <c r="W95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -9942,6 +10186,7 @@
       <c r="T96" s="6" t="inlineStr"/>
       <c r="U96" s="6" t="inlineStr"/>
       <c r="V96" s="6" t="inlineStr"/>
+      <c r="W96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -10002,6 +10247,7 @@
       <c r="T97" s="6" t="inlineStr"/>
       <c r="U97" s="6" t="inlineStr"/>
       <c r="V97" s="6" t="inlineStr"/>
+      <c r="W97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -10062,6 +10308,7 @@
       <c r="T98" s="6" t="inlineStr"/>
       <c r="U98" s="6" t="inlineStr"/>
       <c r="V98" s="6" t="inlineStr"/>
+      <c r="W98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -10122,6 +10369,7 @@
       <c r="T99" s="6" t="inlineStr"/>
       <c r="U99" s="6" t="inlineStr"/>
       <c r="V99" s="6" t="inlineStr"/>
+      <c r="W99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -10182,6 +10430,7 @@
       <c r="T100" s="6" t="inlineStr"/>
       <c r="U100" s="6" t="inlineStr"/>
       <c r="V100" s="6" t="inlineStr"/>
+      <c r="W100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -10242,6 +10491,7 @@
       <c r="T101" s="6" t="inlineStr"/>
       <c r="U101" s="6" t="inlineStr"/>
       <c r="V101" s="6" t="inlineStr"/>
+      <c r="W101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -10302,6 +10552,7 @@
       <c r="T102" s="6" t="inlineStr"/>
       <c r="U102" s="6" t="inlineStr"/>
       <c r="V102" s="6" t="inlineStr"/>
+      <c r="W102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -10362,6 +10613,7 @@
       <c r="T103" s="6" t="inlineStr"/>
       <c r="U103" s="6" t="inlineStr"/>
       <c r="V103" s="6" t="inlineStr"/>
+      <c r="W103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -10422,6 +10674,7 @@
       <c r="T104" s="6" t="inlineStr"/>
       <c r="U104" s="6" t="inlineStr"/>
       <c r="V104" s="6" t="inlineStr"/>
+      <c r="W104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -10482,6 +10735,7 @@
       <c r="T105" s="6" t="inlineStr"/>
       <c r="U105" s="6" t="inlineStr"/>
       <c r="V105" s="6" t="inlineStr"/>
+      <c r="W105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -10542,6 +10796,7 @@
       <c r="T106" s="6" t="inlineStr"/>
       <c r="U106" s="6" t="inlineStr"/>
       <c r="V106" s="6" t="inlineStr"/>
+      <c r="W106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -10602,6 +10857,7 @@
       <c r="T107" s="6" t="inlineStr"/>
       <c r="U107" s="6" t="inlineStr"/>
       <c r="V107" s="6" t="inlineStr"/>
+      <c r="W107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -10662,6 +10918,7 @@
       <c r="T108" s="6" t="inlineStr"/>
       <c r="U108" s="6" t="inlineStr"/>
       <c r="V108" s="6" t="inlineStr"/>
+      <c r="W108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -10722,6 +10979,7 @@
       <c r="T109" s="6" t="inlineStr"/>
       <c r="U109" s="6" t="inlineStr"/>
       <c r="V109" s="6" t="inlineStr"/>
+      <c r="W109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -10782,6 +11040,7 @@
       <c r="T110" s="6" t="inlineStr"/>
       <c r="U110" s="6" t="inlineStr"/>
       <c r="V110" s="6" t="inlineStr"/>
+      <c r="W110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -10842,6 +11101,7 @@
       <c r="T111" s="6" t="inlineStr"/>
       <c r="U111" s="6" t="inlineStr"/>
       <c r="V111" s="6" t="inlineStr"/>
+      <c r="W111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -10902,6 +11162,7 @@
       <c r="T112" s="6" t="inlineStr"/>
       <c r="U112" s="6" t="inlineStr"/>
       <c r="V112" s="6" t="inlineStr"/>
+      <c r="W112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -10962,6 +11223,7 @@
       <c r="T113" s="6" t="inlineStr"/>
       <c r="U113" s="6" t="inlineStr"/>
       <c r="V113" s="6" t="inlineStr"/>
+      <c r="W113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -11034,6 +11296,7 @@
       <c r="T114" s="6" t="inlineStr"/>
       <c r="U114" s="6" t="inlineStr"/>
       <c r="V114" s="6" t="inlineStr"/>
+      <c r="W114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -11094,6 +11357,7 @@
       <c r="T115" s="6" t="inlineStr"/>
       <c r="U115" s="6" t="inlineStr"/>
       <c r="V115" s="6" t="inlineStr"/>
+      <c r="W115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -11154,6 +11418,7 @@
       <c r="T116" s="6" t="inlineStr"/>
       <c r="U116" s="6" t="inlineStr"/>
       <c r="V116" s="6" t="inlineStr"/>
+      <c r="W116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -11214,6 +11479,7 @@
       <c r="T117" s="6" t="inlineStr"/>
       <c r="U117" s="6" t="inlineStr"/>
       <c r="V117" s="6" t="inlineStr"/>
+      <c r="W117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -11274,6 +11540,7 @@
       <c r="T118" s="6" t="inlineStr"/>
       <c r="U118" s="6" t="inlineStr"/>
       <c r="V118" s="6" t="inlineStr"/>
+      <c r="W118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -11334,6 +11601,7 @@
       <c r="T119" s="6" t="inlineStr"/>
       <c r="U119" s="6" t="inlineStr"/>
       <c r="V119" s="6" t="inlineStr"/>
+      <c r="W119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -11394,6 +11662,7 @@
       <c r="T120" s="6" t="inlineStr"/>
       <c r="U120" s="6" t="inlineStr"/>
       <c r="V120" s="6" t="inlineStr"/>
+      <c r="W120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -11454,6 +11723,7 @@
       <c r="T121" s="6" t="inlineStr"/>
       <c r="U121" s="6" t="inlineStr"/>
       <c r="V121" s="6" t="inlineStr"/>
+      <c r="W121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -11514,6 +11784,7 @@
       <c r="T122" s="6" t="inlineStr"/>
       <c r="U122" s="6" t="inlineStr"/>
       <c r="V122" s="6" t="inlineStr"/>
+      <c r="W122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -11574,6 +11845,7 @@
       <c r="T123" s="6" t="inlineStr"/>
       <c r="U123" s="6" t="inlineStr"/>
       <c r="V123" s="6" t="inlineStr"/>
+      <c r="W123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -11634,6 +11906,7 @@
       <c r="T124" s="6" t="inlineStr"/>
       <c r="U124" s="6" t="inlineStr"/>
       <c r="V124" s="6" t="inlineStr"/>
+      <c r="W124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -11694,6 +11967,7 @@
       <c r="T125" s="6" t="inlineStr"/>
       <c r="U125" s="6" t="inlineStr"/>
       <c r="V125" s="6" t="inlineStr"/>
+      <c r="W125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -11754,6 +12028,7 @@
       <c r="T126" s="6" t="inlineStr"/>
       <c r="U126" s="6" t="inlineStr"/>
       <c r="V126" s="6" t="inlineStr"/>
+      <c r="W126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -11814,6 +12089,7 @@
       <c r="T127" s="6" t="inlineStr"/>
       <c r="U127" s="6" t="inlineStr"/>
       <c r="V127" s="6" t="inlineStr"/>
+      <c r="W127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -11874,6 +12150,7 @@
       <c r="T128" s="6" t="inlineStr"/>
       <c r="U128" s="6" t="inlineStr"/>
       <c r="V128" s="6" t="inlineStr"/>
+      <c r="W128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -11934,6 +12211,7 @@
       <c r="T129" s="6" t="inlineStr"/>
       <c r="U129" s="6" t="inlineStr"/>
       <c r="V129" s="6" t="inlineStr"/>
+      <c r="W129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -11994,6 +12272,7 @@
       <c r="T130" s="6" t="inlineStr"/>
       <c r="U130" s="6" t="inlineStr"/>
       <c r="V130" s="6" t="inlineStr"/>
+      <c r="W130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -12054,6 +12333,7 @@
       <c r="T131" s="6" t="inlineStr"/>
       <c r="U131" s="6" t="inlineStr"/>
       <c r="V131" s="6" t="inlineStr"/>
+      <c r="W131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -12114,6 +12394,7 @@
       <c r="T132" s="6" t="inlineStr"/>
       <c r="U132" s="6" t="inlineStr"/>
       <c r="V132" s="6" t="inlineStr"/>
+      <c r="W132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -12174,6 +12455,7 @@
       <c r="T133" s="6" t="inlineStr"/>
       <c r="U133" s="6" t="inlineStr"/>
       <c r="V133" s="6" t="inlineStr"/>
+      <c r="W133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -12234,6 +12516,7 @@
       <c r="T134" s="6" t="inlineStr"/>
       <c r="U134" s="6" t="inlineStr"/>
       <c r="V134" s="6" t="inlineStr"/>
+      <c r="W134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -12294,6 +12577,7 @@
       <c r="T135" s="6" t="inlineStr"/>
       <c r="U135" s="6" t="inlineStr"/>
       <c r="V135" s="6" t="inlineStr"/>
+      <c r="W135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -12354,6 +12638,7 @@
       <c r="T136" s="6" t="inlineStr"/>
       <c r="U136" s="6" t="inlineStr"/>
       <c r="V136" s="6" t="inlineStr"/>
+      <c r="W136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -12405,12 +12690,12 @@
       <c r="K137" s="6" t="inlineStr"/>
       <c r="L137" s="6" t="inlineStr"/>
       <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="N137" s="6" t="inlineStr"/>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O137" s="6" t="inlineStr"/>
       <c r="P137" s="6" t="inlineStr"/>
       <c r="Q137" s="6" t="inlineStr"/>
       <c r="R137" s="6" t="inlineStr"/>
@@ -12418,6 +12703,7 @@
       <c r="T137" s="6" t="inlineStr"/>
       <c r="U137" s="6" t="inlineStr"/>
       <c r="V137" s="6" t="inlineStr"/>
+      <c r="W137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -12469,23 +12755,24 @@
       <c r="K138" s="6" t="inlineStr"/>
       <c r="L138" s="6" t="inlineStr"/>
       <c r="M138" s="6" t="inlineStr"/>
-      <c r="N138" s="6" t="inlineStr">
+      <c r="N138" s="6" t="inlineStr"/>
+      <c r="O138" s="6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="O138" s="6" t="inlineStr">
+      <c r="P138" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P138" s="6" t="inlineStr"/>
       <c r="Q138" s="6" t="inlineStr"/>
       <c r="R138" s="6" t="inlineStr"/>
       <c r="S138" s="6" t="inlineStr"/>
       <c r="T138" s="6" t="inlineStr"/>
       <c r="U138" s="6" t="inlineStr"/>
       <c r="V138" s="6" t="inlineStr"/>
+      <c r="W138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -12537,23 +12824,24 @@
       <c r="K139" s="6" t="inlineStr"/>
       <c r="L139" s="6" t="inlineStr"/>
       <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="N139" s="6" t="inlineStr"/>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="O139" s="6" t="inlineStr">
+      <c r="P139" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P139" s="6" t="inlineStr"/>
       <c r="Q139" s="6" t="inlineStr"/>
       <c r="R139" s="6" t="inlineStr"/>
       <c r="S139" s="6" t="inlineStr"/>
       <c r="T139" s="6" t="inlineStr"/>
       <c r="U139" s="6" t="inlineStr"/>
       <c r="V139" s="6" t="inlineStr"/>
+      <c r="W139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -12605,23 +12893,24 @@
       <c r="K140" s="6" t="inlineStr"/>
       <c r="L140" s="6" t="inlineStr"/>
       <c r="M140" s="6" t="inlineStr"/>
-      <c r="N140" s="6" t="inlineStr">
+      <c r="N140" s="6" t="inlineStr"/>
+      <c r="O140" s="6" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="O140" s="6" t="inlineStr">
+      <c r="P140" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P140" s="6" t="inlineStr"/>
       <c r="Q140" s="6" t="inlineStr"/>
       <c r="R140" s="6" t="inlineStr"/>
       <c r="S140" s="6" t="inlineStr"/>
       <c r="T140" s="6" t="inlineStr"/>
       <c r="U140" s="6" t="inlineStr"/>
       <c r="V140" s="6" t="inlineStr"/>
+      <c r="W140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -12673,23 +12962,24 @@
       <c r="K141" s="6" t="inlineStr"/>
       <c r="L141" s="6" t="inlineStr"/>
       <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="6" t="inlineStr">
+      <c r="N141" s="6" t="inlineStr"/>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O141" s="6" t="inlineStr">
+      <c r="P141" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P141" s="6" t="inlineStr"/>
       <c r="Q141" s="6" t="inlineStr"/>
       <c r="R141" s="6" t="inlineStr"/>
       <c r="S141" s="6" t="inlineStr"/>
       <c r="T141" s="6" t="inlineStr"/>
       <c r="U141" s="6" t="inlineStr"/>
       <c r="V141" s="6" t="inlineStr"/>
+      <c r="W141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -12741,23 +13031,24 @@
       <c r="K142" s="6" t="inlineStr"/>
       <c r="L142" s="6" t="inlineStr"/>
       <c r="M142" s="6" t="inlineStr"/>
-      <c r="N142" s="6" t="inlineStr">
+      <c r="N142" s="6" t="inlineStr"/>
+      <c r="O142" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O142" s="6" t="inlineStr">
+      <c r="P142" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P142" s="6" t="inlineStr"/>
       <c r="Q142" s="6" t="inlineStr"/>
       <c r="R142" s="6" t="inlineStr"/>
       <c r="S142" s="6" t="inlineStr"/>
       <c r="T142" s="6" t="inlineStr"/>
       <c r="U142" s="6" t="inlineStr"/>
       <c r="V142" s="6" t="inlineStr"/>
+      <c r="W142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -12809,23 +13100,24 @@
       <c r="K143" s="6" t="inlineStr"/>
       <c r="L143" s="6" t="inlineStr"/>
       <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="6" t="inlineStr">
+      <c r="N143" s="6" t="inlineStr"/>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O143" s="6" t="inlineStr">
+      <c r="P143" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P143" s="6" t="inlineStr"/>
       <c r="Q143" s="6" t="inlineStr"/>
       <c r="R143" s="6" t="inlineStr"/>
       <c r="S143" s="6" t="inlineStr"/>
       <c r="T143" s="6" t="inlineStr"/>
       <c r="U143" s="6" t="inlineStr"/>
       <c r="V143" s="6" t="inlineStr"/>
+      <c r="W143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -12877,23 +13169,24 @@
       <c r="K144" s="6" t="inlineStr"/>
       <c r="L144" s="6" t="inlineStr"/>
       <c r="M144" s="6" t="inlineStr"/>
-      <c r="N144" s="6" t="inlineStr">
+      <c r="N144" s="6" t="inlineStr"/>
+      <c r="O144" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O144" s="6" t="inlineStr">
+      <c r="P144" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P144" s="6" t="inlineStr"/>
       <c r="Q144" s="6" t="inlineStr"/>
       <c r="R144" s="6" t="inlineStr"/>
       <c r="S144" s="6" t="inlineStr"/>
       <c r="T144" s="6" t="inlineStr"/>
       <c r="U144" s="6" t="inlineStr"/>
       <c r="V144" s="6" t="inlineStr"/>
+      <c r="W144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -12945,23 +13238,24 @@
       <c r="K145" s="6" t="inlineStr"/>
       <c r="L145" s="6" t="inlineStr"/>
       <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="6" t="inlineStr">
+      <c r="N145" s="6" t="inlineStr"/>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O145" s="6" t="inlineStr">
+      <c r="P145" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P145" s="6" t="inlineStr"/>
       <c r="Q145" s="6" t="inlineStr"/>
       <c r="R145" s="6" t="inlineStr"/>
       <c r="S145" s="6" t="inlineStr"/>
       <c r="T145" s="6" t="inlineStr"/>
       <c r="U145" s="6" t="inlineStr"/>
       <c r="V145" s="6" t="inlineStr"/>
+      <c r="W145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -13025,27 +13319,28 @@
           <t>Viral reach post-Rogan appearance</t>
         </is>
       </c>
-      <c r="N146" s="6" t="inlineStr">
+      <c r="N146" s="6" t="inlineStr"/>
+      <c r="O146" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O146" s="6" t="inlineStr">
+      <c r="P146" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P146" s="6" t="inlineStr">
+      <c r="Q146" s="6" t="inlineStr">
         <is>
           <t>Confirm any explicit Israel-specific statements; stance is currently by evangelical/Judeo-Christian alignment, not a documented Israel position.</t>
         </is>
       </c>
-      <c r="Q146" s="6" t="inlineStr"/>
       <c r="R146" s="6" t="inlineStr"/>
       <c r="S146" s="6" t="inlineStr"/>
       <c r="T146" s="6" t="inlineStr"/>
       <c r="U146" s="6" t="inlineStr"/>
       <c r="V146" s="6" t="inlineStr"/>
+      <c r="W146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -13097,27 +13392,28 @@
       <c r="K147" s="6" t="inlineStr"/>
       <c r="L147" s="6" t="inlineStr"/>
       <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="6" t="inlineStr">
+      <c r="N147" s="6" t="inlineStr"/>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O147" s="6" t="inlineStr">
+      <c r="P147" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P147" s="6" t="inlineStr">
+      <c r="Q147" s="6" t="inlineStr">
         <is>
           <t>Direct verification limited -- confirm his own Israel/faith statements and audience size; currently added on association with confirmed allies.</t>
         </is>
       </c>
-      <c r="Q147" s="6" t="inlineStr"/>
       <c r="R147" s="6" t="inlineStr"/>
       <c r="S147" s="6" t="inlineStr"/>
       <c r="T147" s="6" t="inlineStr"/>
       <c r="U147" s="6" t="inlineStr"/>
       <c r="V147" s="6" t="inlineStr"/>
+      <c r="W147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -13169,31 +13465,32 @@
       <c r="K148" s="6" t="inlineStr"/>
       <c r="L148" s="6" t="inlineStr"/>
       <c r="M148" s="6" t="inlineStr"/>
-      <c r="N148" s="6" t="inlineStr">
+      <c r="N148" s="6" t="inlineStr"/>
+      <c r="O148" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O148" s="6" t="inlineStr">
+      <c r="P148" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P148" s="6" t="inlineStr">
+      <c r="Q148" s="6" t="inlineStr">
         <is>
           <t>No explicit Israel statement found; stance is by evangelical alignment + platform value, not a documented Israel position.</t>
         </is>
       </c>
-      <c r="Q148" s="6" t="inlineStr">
+      <c r="R148" s="6" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="R148" s="6" t="inlineStr"/>
       <c r="S148" s="6" t="inlineStr"/>
       <c r="T148" s="6" t="inlineStr"/>
       <c r="U148" s="6" t="inlineStr"/>
       <c r="V148" s="6" t="inlineStr"/>
+      <c r="W148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -13245,27 +13542,28 @@
       <c r="K149" s="6" t="inlineStr"/>
       <c r="L149" s="6" t="inlineStr"/>
       <c r="M149" s="6" t="inlineStr"/>
-      <c r="N149" s="6" t="inlineStr">
+      <c r="N149" s="6" t="inlineStr"/>
+      <c r="O149" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O149" s="6" t="inlineStr">
+      <c r="P149" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P149" s="6" t="inlineStr">
+      <c r="Q149" s="6" t="inlineStr">
         <is>
           <t>Confirm specific Israel statements; currently pro on Tech Right / pro-West coalition alignment and firm orientation.</t>
         </is>
       </c>
-      <c r="Q149" s="6" t="inlineStr"/>
       <c r="R149" s="6" t="inlineStr"/>
       <c r="S149" s="6" t="inlineStr"/>
       <c r="T149" s="6" t="inlineStr"/>
       <c r="U149" s="6" t="inlineStr"/>
       <c r="V149" s="6" t="inlineStr"/>
+      <c r="W149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -13317,27 +13615,28 @@
       <c r="K150" s="6" t="inlineStr"/>
       <c r="L150" s="6" t="inlineStr"/>
       <c r="M150" s="6" t="inlineStr"/>
-      <c r="N150" s="6" t="inlineStr">
+      <c r="N150" s="6" t="inlineStr"/>
+      <c r="O150" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O150" s="6" t="inlineStr">
+      <c r="P150" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P150" s="6" t="inlineStr">
+      <c r="Q150" s="6" t="inlineStr">
         <is>
           <t>Determine his and The Atlantic's editorial posture toward Israel; no documented personal stance yet -- do not assume.</t>
         </is>
       </c>
-      <c r="Q150" s="6" t="inlineStr"/>
       <c r="R150" s="6" t="inlineStr"/>
       <c r="S150" s="6" t="inlineStr"/>
       <c r="T150" s="6" t="inlineStr"/>
       <c r="U150" s="6" t="inlineStr"/>
       <c r="V150" s="6" t="inlineStr"/>
+      <c r="W150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -13389,27 +13688,28 @@
       <c r="K151" s="6" t="inlineStr"/>
       <c r="L151" s="6" t="inlineStr"/>
       <c r="M151" s="6" t="inlineStr"/>
-      <c r="N151" s="6" t="inlineStr">
+      <c r="N151" s="6" t="inlineStr"/>
+      <c r="O151" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O151" s="6" t="inlineStr">
+      <c r="P151" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P151" s="6" t="inlineStr">
+      <c r="Q151" s="6" t="inlineStr">
         <is>
           <t>Identify role, affiliations, and any Israel/faith signal -- entry is a placeholder pending detail from Andy or a reachable public source.</t>
         </is>
       </c>
-      <c r="Q151" s="6" t="inlineStr"/>
       <c r="R151" s="6" t="inlineStr"/>
       <c r="S151" s="6" t="inlineStr"/>
       <c r="T151" s="6" t="inlineStr"/>
       <c r="U151" s="6" t="inlineStr"/>
       <c r="V151" s="6" t="inlineStr"/>
+      <c r="W151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -13465,23 +13765,24 @@
       <c r="K152" s="6" t="inlineStr"/>
       <c r="L152" s="6" t="inlineStr"/>
       <c r="M152" s="6" t="inlineStr"/>
-      <c r="N152" s="6" t="inlineStr">
+      <c r="N152" s="6" t="inlineStr"/>
+      <c r="O152" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O152" s="6" t="inlineStr">
+      <c r="P152" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P152" s="6" t="inlineStr"/>
       <c r="Q152" s="6" t="inlineStr"/>
       <c r="R152" s="6" t="inlineStr"/>
       <c r="S152" s="6" t="inlineStr"/>
       <c r="T152" s="6" t="inlineStr"/>
       <c r="U152" s="6" t="inlineStr"/>
       <c r="V152" s="6" t="inlineStr"/>
+      <c r="W152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -13537,23 +13838,24 @@
       <c r="K153" s="6" t="inlineStr"/>
       <c r="L153" s="6" t="inlineStr"/>
       <c r="M153" s="6" t="inlineStr"/>
-      <c r="N153" s="6" t="inlineStr">
+      <c r="N153" s="6" t="inlineStr"/>
+      <c r="O153" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O153" s="6" t="inlineStr">
+      <c r="P153" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P153" s="6" t="inlineStr"/>
       <c r="Q153" s="6" t="inlineStr"/>
       <c r="R153" s="6" t="inlineStr"/>
       <c r="S153" s="6" t="inlineStr"/>
       <c r="T153" s="6" t="inlineStr"/>
       <c r="U153" s="6" t="inlineStr"/>
       <c r="V153" s="6" t="inlineStr"/>
+      <c r="W153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -13605,27 +13907,28 @@
       <c r="K154" s="6" t="inlineStr"/>
       <c r="L154" s="6" t="inlineStr"/>
       <c r="M154" s="6" t="inlineStr"/>
-      <c r="N154" s="6" t="inlineStr">
+      <c r="N154" s="6" t="inlineStr"/>
+      <c r="O154" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O154" s="6" t="inlineStr">
+      <c r="P154" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P154" s="6" t="inlineStr">
+      <c r="Q154" s="6" t="inlineStr">
         <is>
           <t>Track trajectory; stance is genuinely contested -- document specific statements rather than assuming a fixed position.</t>
         </is>
       </c>
-      <c r="Q154" s="6" t="inlineStr"/>
       <c r="R154" s="6" t="inlineStr"/>
       <c r="S154" s="6" t="inlineStr"/>
       <c r="T154" s="6" t="inlineStr"/>
       <c r="U154" s="6" t="inlineStr"/>
       <c r="V154" s="6" t="inlineStr"/>
+      <c r="W154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -13677,27 +13980,28 @@
       <c r="K155" s="6" t="inlineStr"/>
       <c r="L155" s="6" t="inlineStr"/>
       <c r="M155" s="6" t="inlineStr"/>
-      <c r="N155" s="6" t="inlineStr">
+      <c r="N155" s="6" t="inlineStr"/>
+      <c r="O155" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O155" s="6" t="inlineStr">
+      <c r="P155" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P155" s="6" t="inlineStr">
+      <c r="Q155" s="6" t="inlineStr">
         <is>
           <t>Weigh election-fraud-litigation reputational risk against the CUFI/evangelical alignment before any engagement.</t>
         </is>
       </c>
-      <c r="Q155" s="6" t="inlineStr"/>
       <c r="R155" s="6" t="inlineStr"/>
       <c r="S155" s="6" t="inlineStr"/>
       <c r="T155" s="6" t="inlineStr"/>
       <c r="U155" s="6" t="inlineStr"/>
       <c r="V155" s="6" t="inlineStr"/>
+      <c r="W155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -13749,27 +14053,28 @@
       <c r="K156" s="6" t="inlineStr"/>
       <c r="L156" s="6" t="inlineStr"/>
       <c r="M156" s="6" t="inlineStr"/>
-      <c r="N156" s="6" t="inlineStr">
+      <c r="N156" s="6" t="inlineStr"/>
+      <c r="O156" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O156" s="6" t="inlineStr">
+      <c r="P156" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P156" s="6" t="inlineStr">
+      <c r="Q156" s="6" t="inlineStr">
         <is>
           <t>Confirm her own Israel statements; monitor the Alex Stein / Joel-Webbon-adjacent association -- currently pro on RealLindellTV + Jewish-background + Andy's read.</t>
         </is>
       </c>
-      <c r="Q156" s="6" t="inlineStr"/>
       <c r="R156" s="6" t="inlineStr"/>
       <c r="S156" s="6" t="inlineStr"/>
       <c r="T156" s="6" t="inlineStr"/>
       <c r="U156" s="6" t="inlineStr"/>
       <c r="V156" s="6" t="inlineStr"/>
+      <c r="W156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -13821,27 +14126,28 @@
       <c r="K157" s="6" t="inlineStr"/>
       <c r="L157" s="6" t="inlineStr"/>
       <c r="M157" s="6" t="inlineStr"/>
-      <c r="N157" s="6" t="inlineStr">
+      <c r="N157" s="6" t="inlineStr"/>
+      <c r="O157" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O157" s="6" t="inlineStr">
+      <c r="P157" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P157" s="6" t="inlineStr">
+      <c r="Q157" s="6" t="inlineStr">
         <is>
           <t>No political/Israel stance by design; value is audience reach + LDS network, not a documented position. Engage only if he signals openness.</t>
         </is>
       </c>
-      <c r="Q157" s="6" t="inlineStr"/>
       <c r="R157" s="6" t="inlineStr"/>
       <c r="S157" s="6" t="inlineStr"/>
       <c r="T157" s="6" t="inlineStr"/>
       <c r="U157" s="6" t="inlineStr"/>
       <c r="V157" s="6" t="inlineStr"/>
+      <c r="W157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -13893,31 +14199,32 @@
       <c r="K158" s="6" t="inlineStr"/>
       <c r="L158" s="6" t="inlineStr"/>
       <c r="M158" s="6" t="inlineStr"/>
-      <c r="N158" s="6" t="inlineStr">
+      <c r="N158" s="6" t="inlineStr"/>
+      <c r="O158" s="6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O158" s="6" t="inlineStr">
+      <c r="P158" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P158" s="6" t="inlineStr">
+      <c r="Q158" s="6" t="inlineStr">
         <is>
           <t>Reconsider inclusion -- the pro-Israel signal is thin/indirect and the reputational cost is high. Documented here honestly rather than mislabeled 'pro.'</t>
         </is>
       </c>
-      <c r="Q158" s="6" t="inlineStr">
+      <c r="R158" s="6" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="R158" s="6" t="inlineStr"/>
       <c r="S158" s="6" t="inlineStr"/>
       <c r="T158" s="6" t="inlineStr"/>
       <c r="U158" s="6" t="inlineStr"/>
       <c r="V158" s="6" t="inlineStr"/>
+      <c r="W158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -13969,27 +14276,28 @@
       <c r="K159" s="6" t="inlineStr"/>
       <c r="L159" s="6" t="inlineStr"/>
       <c r="M159" s="6" t="inlineStr"/>
-      <c r="N159" s="6" t="inlineStr">
+      <c r="N159" s="6" t="inlineStr"/>
+      <c r="O159" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O159" s="6" t="inlineStr">
+      <c r="P159" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P159" s="6" t="inlineStr">
+      <c r="Q159" s="6" t="inlineStr">
         <is>
           <t>Enumerate specific still-active connections worth adding; weigh the 2020 scandal reputational risk before any engagement.</t>
         </is>
       </c>
-      <c r="Q159" s="6" t="inlineStr"/>
       <c r="R159" s="6" t="inlineStr"/>
       <c r="S159" s="6" t="inlineStr"/>
       <c r="T159" s="6" t="inlineStr"/>
       <c r="U159" s="6" t="inlineStr"/>
       <c r="V159" s="6" t="inlineStr"/>
+      <c r="W159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
@@ -14045,23 +14353,24 @@
       <c r="K160" s="6" t="inlineStr"/>
       <c r="L160" s="6" t="inlineStr"/>
       <c r="M160" s="6" t="inlineStr"/>
-      <c r="N160" s="6" t="inlineStr">
+      <c r="N160" s="6" t="inlineStr"/>
+      <c r="O160" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O160" s="6" t="inlineStr">
+      <c r="P160" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P160" s="6" t="inlineStr"/>
       <c r="Q160" s="6" t="inlineStr"/>
       <c r="R160" s="6" t="inlineStr"/>
       <c r="S160" s="6" t="inlineStr"/>
       <c r="T160" s="6" t="inlineStr"/>
       <c r="U160" s="6" t="inlineStr"/>
       <c r="V160" s="6" t="inlineStr"/>
+      <c r="W160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -14117,31 +14426,32 @@
       <c r="K161" s="6" t="inlineStr"/>
       <c r="L161" s="6" t="inlineStr"/>
       <c r="M161" s="6" t="inlineStr"/>
-      <c r="N161" s="6" t="inlineStr">
+      <c r="N161" s="6" t="inlineStr"/>
+      <c r="O161" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O161" s="6" t="inlineStr">
+      <c r="P161" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P161" s="6" t="inlineStr">
+      <c r="Q161" s="6" t="inlineStr">
         <is>
           <t>Verify political lean and any Israel/Jewish-community signal; user-submitted lead.</t>
         </is>
       </c>
-      <c r="Q161" s="6" t="inlineStr"/>
-      <c r="R161" s="6" t="inlineStr">
+      <c r="R161" s="6" t="inlineStr"/>
+      <c r="S161" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S161" s="6" t="inlineStr"/>
       <c r="T161" s="6" t="inlineStr"/>
       <c r="U161" s="6" t="inlineStr"/>
       <c r="V161" s="6" t="inlineStr"/>
+      <c r="W161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -14197,31 +14507,32 @@
       <c r="K162" s="6" t="inlineStr"/>
       <c r="L162" s="6" t="inlineStr"/>
       <c r="M162" s="6" t="inlineStr"/>
-      <c r="N162" s="6" t="inlineStr">
+      <c r="N162" s="6" t="inlineStr"/>
+      <c r="O162" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O162" s="6" t="inlineStr">
+      <c r="P162" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P162" s="6" t="inlineStr">
+      <c r="Q162" s="6" t="inlineStr">
         <is>
           <t>Watch for Israel/Jewish-community signals; her religious-persecution advocacy suggests openness to faith-coalition framing.</t>
         </is>
       </c>
-      <c r="Q162" s="6" t="inlineStr">
+      <c r="R162" s="6" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
       </c>
-      <c r="R162" s="6" t="inlineStr"/>
       <c r="S162" s="6" t="inlineStr"/>
       <c r="T162" s="6" t="inlineStr"/>
       <c r="U162" s="6" t="inlineStr"/>
       <c r="V162" s="6" t="inlineStr"/>
+      <c r="W162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -14273,31 +14584,32 @@
       <c r="K163" s="6" t="inlineStr"/>
       <c r="L163" s="6" t="inlineStr"/>
       <c r="M163" s="6" t="inlineStr"/>
-      <c r="N163" s="6" t="inlineStr">
+      <c r="N163" s="6" t="inlineStr"/>
+      <c r="O163" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O163" s="6" t="inlineStr">
+      <c r="P163" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P163" s="6" t="inlineStr">
+      <c r="Q163" s="6" t="inlineStr">
         <is>
           <t>Verify the user-submitted TikTok evidence (tiktok.com/@intothev0rtex/video/7658066785861766414) and any recent Israel-related statements.</t>
         </is>
       </c>
-      <c r="Q163" s="6" t="inlineStr">
+      <c r="R163" s="6" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
       </c>
-      <c r="R163" s="6" t="inlineStr"/>
       <c r="S163" s="6" t="inlineStr"/>
       <c r="T163" s="6" t="inlineStr"/>
       <c r="U163" s="6" t="inlineStr"/>
       <c r="V163" s="6" t="inlineStr"/>
+      <c r="W163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -14349,23 +14661,24 @@
       <c r="K164" s="6" t="inlineStr"/>
       <c r="L164" s="6" t="inlineStr"/>
       <c r="M164" s="6" t="inlineStr"/>
-      <c r="N164" s="6" t="inlineStr">
+      <c r="N164" s="6" t="inlineStr"/>
+      <c r="O164" s="6" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="O164" s="6" t="inlineStr">
+      <c r="P164" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P164" s="6" t="inlineStr"/>
       <c r="Q164" s="6" t="inlineStr"/>
       <c r="R164" s="6" t="inlineStr"/>
       <c r="S164" s="6" t="inlineStr"/>
       <c r="T164" s="6" t="inlineStr"/>
       <c r="U164" s="6" t="inlineStr"/>
       <c r="V164" s="6" t="inlineStr"/>
+      <c r="W164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -14417,27 +14730,28 @@
       <c r="K165" s="6" t="inlineStr"/>
       <c r="L165" s="6" t="inlineStr"/>
       <c r="M165" s="6" t="inlineStr"/>
-      <c r="N165" s="6" t="inlineStr">
+      <c r="N165" s="6" t="inlineStr"/>
+      <c r="O165" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O165" s="6" t="inlineStr">
+      <c r="P165" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P165" s="6" t="inlineStr">
+      <c r="Q165" s="6" t="inlineStr">
         <is>
           <t>Confirm "David Edison" meant David Ellison.</t>
         </is>
       </c>
-      <c r="Q165" s="6" t="inlineStr"/>
       <c r="R165" s="6" t="inlineStr"/>
       <c r="S165" s="6" t="inlineStr"/>
       <c r="T165" s="6" t="inlineStr"/>
       <c r="U165" s="6" t="inlineStr"/>
       <c r="V165" s="6" t="inlineStr"/>
+      <c r="W165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -14493,23 +14807,24 @@
       <c r="K166" s="6" t="inlineStr"/>
       <c r="L166" s="6" t="inlineStr"/>
       <c r="M166" s="6" t="inlineStr"/>
-      <c r="N166" s="6" t="inlineStr">
+      <c r="N166" s="6" t="inlineStr"/>
+      <c r="O166" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O166" s="6" t="inlineStr">
+      <c r="P166" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P166" s="6" t="inlineStr"/>
       <c r="Q166" s="6" t="inlineStr"/>
       <c r="R166" s="6" t="inlineStr"/>
       <c r="S166" s="6" t="inlineStr"/>
       <c r="T166" s="6" t="inlineStr"/>
       <c r="U166" s="6" t="inlineStr"/>
       <c r="V166" s="6" t="inlineStr"/>
+      <c r="W166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -14565,27 +14880,28 @@
       <c r="K167" s="6" t="inlineStr"/>
       <c r="L167" s="6" t="inlineStr"/>
       <c r="M167" s="6" t="inlineStr"/>
-      <c r="N167" s="6" t="inlineStr">
+      <c r="N167" s="6" t="inlineStr"/>
+      <c r="O167" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O167" s="6" t="inlineStr">
+      <c r="P167" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P167" s="6" t="inlineStr">
+      <c r="Q167" s="6" t="inlineStr">
         <is>
           <t>Verify any Israel-specific commentary.</t>
         </is>
       </c>
-      <c r="Q167" s="6" t="inlineStr"/>
       <c r="R167" s="6" t="inlineStr"/>
       <c r="S167" s="6" t="inlineStr"/>
       <c r="T167" s="6" t="inlineStr"/>
       <c r="U167" s="6" t="inlineStr"/>
       <c r="V167" s="6" t="inlineStr"/>
+      <c r="W167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -14641,23 +14957,24 @@
       <c r="K168" s="6" t="inlineStr"/>
       <c r="L168" s="6" t="inlineStr"/>
       <c r="M168" s="6" t="inlineStr"/>
-      <c r="N168" s="6" t="inlineStr">
+      <c r="N168" s="6" t="inlineStr"/>
+      <c r="O168" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O168" s="6" t="inlineStr">
+      <c r="P168" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P168" s="6" t="inlineStr"/>
       <c r="Q168" s="6" t="inlineStr"/>
       <c r="R168" s="6" t="inlineStr"/>
       <c r="S168" s="6" t="inlineStr"/>
       <c r="T168" s="6" t="inlineStr"/>
       <c r="U168" s="6" t="inlineStr"/>
       <c r="V168" s="6" t="inlineStr"/>
+      <c r="W168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -14713,23 +15030,24 @@
       <c r="K169" s="6" t="inlineStr"/>
       <c r="L169" s="6" t="inlineStr"/>
       <c r="M169" s="6" t="inlineStr"/>
-      <c r="N169" s="6" t="inlineStr">
+      <c r="N169" s="6" t="inlineStr"/>
+      <c r="O169" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O169" s="6" t="inlineStr">
+      <c r="P169" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P169" s="6" t="inlineStr"/>
       <c r="Q169" s="6" t="inlineStr"/>
       <c r="R169" s="6" t="inlineStr"/>
       <c r="S169" s="6" t="inlineStr"/>
       <c r="T169" s="6" t="inlineStr"/>
       <c r="U169" s="6" t="inlineStr"/>
       <c r="V169" s="6" t="inlineStr"/>
+      <c r="W169" s="6" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
@@ -14785,23 +15103,24 @@
       <c r="K170" s="6" t="inlineStr"/>
       <c r="L170" s="6" t="inlineStr"/>
       <c r="M170" s="6" t="inlineStr"/>
-      <c r="N170" s="6" t="inlineStr">
+      <c r="N170" s="6" t="inlineStr"/>
+      <c r="O170" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O170" s="6" t="inlineStr">
+      <c r="P170" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P170" s="6" t="inlineStr"/>
       <c r="Q170" s="6" t="inlineStr"/>
       <c r="R170" s="6" t="inlineStr"/>
       <c r="S170" s="6" t="inlineStr"/>
       <c r="T170" s="6" t="inlineStr"/>
       <c r="U170" s="6" t="inlineStr"/>
       <c r="V170" s="6" t="inlineStr"/>
+      <c r="W170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -14853,27 +15172,28 @@
       <c r="K171" s="6" t="inlineStr"/>
       <c r="L171" s="6" t="inlineStr"/>
       <c r="M171" s="6" t="inlineStr"/>
-      <c r="N171" s="6" t="inlineStr">
+      <c r="N171" s="6" t="inlineStr"/>
+      <c r="O171" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O171" s="6" t="inlineStr">
+      <c r="P171" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P171" s="6" t="inlineStr">
+      <c r="Q171" s="6" t="inlineStr">
         <is>
           <t>Track his framing on Israel/antisemitism segments; assess bridge potential to center-left audiences.</t>
         </is>
       </c>
-      <c r="Q171" s="6" t="inlineStr"/>
       <c r="R171" s="6" t="inlineStr"/>
       <c r="S171" s="6" t="inlineStr"/>
       <c r="T171" s="6" t="inlineStr"/>
       <c r="U171" s="6" t="inlineStr"/>
       <c r="V171" s="6" t="inlineStr"/>
+      <c r="W171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
@@ -14925,27 +15245,28 @@
       <c r="K172" s="6" t="inlineStr"/>
       <c r="L172" s="6" t="inlineStr"/>
       <c r="M172" s="6" t="inlineStr"/>
-      <c r="N172" s="6" t="inlineStr">
+      <c r="N172" s="6" t="inlineStr"/>
+      <c r="O172" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O172" s="6" t="inlineStr">
+      <c r="P172" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P172" s="6" t="inlineStr">
+      <c r="Q172" s="6" t="inlineStr">
         <is>
           <t>Confirm "Dana Basch" meant CNN's Dana Bash.</t>
         </is>
       </c>
-      <c r="Q172" s="6" t="inlineStr"/>
       <c r="R172" s="6" t="inlineStr"/>
       <c r="S172" s="6" t="inlineStr"/>
       <c r="T172" s="6" t="inlineStr"/>
       <c r="U172" s="6" t="inlineStr"/>
       <c r="V172" s="6" t="inlineStr"/>
+      <c r="W172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -14997,31 +15318,32 @@
       <c r="K173" s="6" t="inlineStr"/>
       <c r="L173" s="6" t="inlineStr"/>
       <c r="M173" s="6" t="inlineStr"/>
-      <c r="N173" s="6" t="inlineStr">
+      <c r="N173" s="6" t="inlineStr"/>
+      <c r="O173" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O173" s="6" t="inlineStr">
+      <c r="P173" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P173" s="6" t="inlineStr">
+      <c r="Q173" s="6" t="inlineStr">
         <is>
           <t>Verify the user-submitted TikTok evidence and what pro-Israel/philosemitic signal it shows.</t>
         </is>
       </c>
-      <c r="Q173" s="6" t="inlineStr">
+      <c r="R173" s="6" t="inlineStr">
         <is>
           <t>Film</t>
         </is>
       </c>
-      <c r="R173" s="6" t="inlineStr"/>
       <c r="S173" s="6" t="inlineStr"/>
       <c r="T173" s="6" t="inlineStr"/>
       <c r="U173" s="6" t="inlineStr"/>
       <c r="V173" s="6" t="inlineStr"/>
+      <c r="W173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
@@ -15077,31 +15399,32 @@
       <c r="K174" s="6" t="inlineStr"/>
       <c r="L174" s="6" t="inlineStr"/>
       <c r="M174" s="6" t="inlineStr"/>
-      <c r="N174" s="6" t="inlineStr">
+      <c r="N174" s="6" t="inlineStr"/>
+      <c r="O174" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O174" s="6" t="inlineStr">
+      <c r="P174" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P174" s="6" t="inlineStr">
+      <c r="Q174" s="6" t="inlineStr">
         <is>
           <t>Disambiguate @mominthebeleiver vs MilkBarTV; verify Livingstone's Israel-related content directly.</t>
         </is>
       </c>
-      <c r="Q174" s="6" t="inlineStr"/>
-      <c r="R174" s="6" t="inlineStr">
+      <c r="R174" s="6" t="inlineStr"/>
+      <c r="S174" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S174" s="6" t="inlineStr"/>
       <c r="T174" s="6" t="inlineStr"/>
       <c r="U174" s="6" t="inlineStr"/>
       <c r="V174" s="6" t="inlineStr"/>
+      <c r="W174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -15157,23 +15480,24 @@
       <c r="K175" s="6" t="inlineStr"/>
       <c r="L175" s="6" t="inlineStr"/>
       <c r="M175" s="6" t="inlineStr"/>
-      <c r="N175" s="6" t="inlineStr">
+      <c r="N175" s="6" t="inlineStr"/>
+      <c r="O175" s="6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="O175" s="6" t="inlineStr">
+      <c r="P175" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P175" s="6" t="inlineStr"/>
       <c r="Q175" s="6" t="inlineStr"/>
       <c r="R175" s="6" t="inlineStr"/>
       <c r="S175" s="6" t="inlineStr"/>
       <c r="T175" s="6" t="inlineStr"/>
       <c r="U175" s="6" t="inlineStr"/>
       <c r="V175" s="6" t="inlineStr"/>
+      <c r="W175" s="6" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -15225,23 +15549,24 @@
       <c r="K176" s="6" t="inlineStr"/>
       <c r="L176" s="6" t="inlineStr"/>
       <c r="M176" s="6" t="inlineStr"/>
-      <c r="N176" s="6" t="inlineStr">
+      <c r="N176" s="6" t="inlineStr"/>
+      <c r="O176" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O176" s="6" t="inlineStr">
+      <c r="P176" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P176" s="6" t="inlineStr"/>
       <c r="Q176" s="6" t="inlineStr"/>
       <c r="R176" s="6" t="inlineStr"/>
       <c r="S176" s="6" t="inlineStr"/>
       <c r="T176" s="6" t="inlineStr"/>
       <c r="U176" s="6" t="inlineStr"/>
       <c r="V176" s="6" t="inlineStr"/>
+      <c r="W176" s="6" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -15297,27 +15622,28 @@
       <c r="K177" s="6" t="inlineStr"/>
       <c r="L177" s="6" t="inlineStr"/>
       <c r="M177" s="6" t="inlineStr"/>
-      <c r="N177" s="6" t="inlineStr">
+      <c r="N177" s="6" t="inlineStr"/>
+      <c r="O177" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O177" s="6" t="inlineStr">
+      <c r="P177" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P177" s="6" t="inlineStr"/>
       <c r="Q177" s="6" t="inlineStr"/>
-      <c r="R177" s="6" t="inlineStr">
+      <c r="R177" s="6" t="inlineStr"/>
+      <c r="S177" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S177" s="6" t="inlineStr"/>
       <c r="T177" s="6" t="inlineStr"/>
       <c r="U177" s="6" t="inlineStr"/>
       <c r="V177" s="6" t="inlineStr"/>
+      <c r="W177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -15369,23 +15695,24 @@
       <c r="K178" s="6" t="inlineStr"/>
       <c r="L178" s="6" t="inlineStr"/>
       <c r="M178" s="6" t="inlineStr"/>
-      <c r="N178" s="6" t="inlineStr">
+      <c r="N178" s="6" t="inlineStr"/>
+      <c r="O178" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O178" s="6" t="inlineStr">
+      <c r="P178" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P178" s="6" t="inlineStr"/>
       <c r="Q178" s="6" t="inlineStr"/>
       <c r="R178" s="6" t="inlineStr"/>
       <c r="S178" s="6" t="inlineStr"/>
       <c r="T178" s="6" t="inlineStr"/>
       <c r="U178" s="6" t="inlineStr"/>
       <c r="V178" s="6" t="inlineStr"/>
+      <c r="W178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -15437,27 +15764,28 @@
       <c r="K179" s="6" t="inlineStr"/>
       <c r="L179" s="6" t="inlineStr"/>
       <c r="M179" s="6" t="inlineStr"/>
-      <c r="N179" s="6" t="inlineStr">
+      <c r="N179" s="6" t="inlineStr"/>
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O179" s="6" t="inlineStr">
+      <c r="P179" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P179" s="6" t="inlineStr">
+      <c r="Q179" s="6" t="inlineStr">
         <is>
           <t>Assess whether his civil-liberties framing makes him a bridge or a fence-sitter.</t>
         </is>
       </c>
-      <c r="Q179" s="6" t="inlineStr"/>
       <c r="R179" s="6" t="inlineStr"/>
       <c r="S179" s="6" t="inlineStr"/>
       <c r="T179" s="6" t="inlineStr"/>
       <c r="U179" s="6" t="inlineStr"/>
       <c r="V179" s="6" t="inlineStr"/>
+      <c r="W179" s="6" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -15509,27 +15837,28 @@
       <c r="K180" s="6" t="inlineStr"/>
       <c r="L180" s="6" t="inlineStr"/>
       <c r="M180" s="6" t="inlineStr"/>
-      <c r="N180" s="6" t="inlineStr">
+      <c r="N180" s="6" t="inlineStr"/>
+      <c r="O180" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O180" s="6" t="inlineStr">
+      <c r="P180" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P180" s="6" t="inlineStr">
+      <c r="Q180" s="6" t="inlineStr">
         <is>
           <t>Volatility assessment before any engagement; her feuds inside MAGA (incl. with other tracked figures) shift rapidly.</t>
         </is>
       </c>
-      <c r="Q180" s="6" t="inlineStr"/>
       <c r="R180" s="6" t="inlineStr"/>
       <c r="S180" s="6" t="inlineStr"/>
       <c r="T180" s="6" t="inlineStr"/>
       <c r="U180" s="6" t="inlineStr"/>
       <c r="V180" s="6" t="inlineStr"/>
+      <c r="W180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -15581,23 +15910,24 @@
       <c r="K181" s="6" t="inlineStr"/>
       <c r="L181" s="6" t="inlineStr"/>
       <c r="M181" s="6" t="inlineStr"/>
-      <c r="N181" s="6" t="inlineStr">
+      <c r="N181" s="6" t="inlineStr"/>
+      <c r="O181" s="6" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="O181" s="6" t="inlineStr">
+      <c r="P181" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P181" s="6" t="inlineStr"/>
       <c r="Q181" s="6" t="inlineStr"/>
       <c r="R181" s="6" t="inlineStr"/>
       <c r="S181" s="6" t="inlineStr"/>
       <c r="T181" s="6" t="inlineStr"/>
       <c r="U181" s="6" t="inlineStr"/>
       <c r="V181" s="6" t="inlineStr"/>
+      <c r="W181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -15649,23 +15979,24 @@
       <c r="K182" s="6" t="inlineStr"/>
       <c r="L182" s="6" t="inlineStr"/>
       <c r="M182" s="6" t="inlineStr"/>
-      <c r="N182" s="6" t="inlineStr">
+      <c r="N182" s="6" t="inlineStr"/>
+      <c r="O182" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O182" s="6" t="inlineStr">
+      <c r="P182" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P182" s="6" t="inlineStr"/>
       <c r="Q182" s="6" t="inlineStr"/>
       <c r="R182" s="6" t="inlineStr"/>
       <c r="S182" s="6" t="inlineStr"/>
       <c r="T182" s="6" t="inlineStr"/>
       <c r="U182" s="6" t="inlineStr"/>
       <c r="V182" s="6" t="inlineStr"/>
+      <c r="W182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -15717,27 +16048,28 @@
       <c r="K183" s="6" t="inlineStr"/>
       <c r="L183" s="6" t="inlineStr"/>
       <c r="M183" s="6" t="inlineStr"/>
-      <c r="N183" s="6" t="inlineStr">
+      <c r="N183" s="6" t="inlineStr"/>
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O183" s="6" t="inlineStr">
+      <c r="P183" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P183" s="6" t="inlineStr">
+      <c r="Q183" s="6" t="inlineStr">
         <is>
           <t>Verify any explicit Israel/antisemitism statements.</t>
         </is>
       </c>
-      <c r="Q183" s="6" t="inlineStr"/>
       <c r="R183" s="6" t="inlineStr"/>
       <c r="S183" s="6" t="inlineStr"/>
       <c r="T183" s="6" t="inlineStr"/>
       <c r="U183" s="6" t="inlineStr"/>
       <c r="V183" s="6" t="inlineStr"/>
+      <c r="W183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -15788,12 +16120,12 @@
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The Riley Gaines Show (Fox) (196 eps, latest 2026-07-14)</t>
         </is>
       </c>
       <c r="L184" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M184" s="6" t="inlineStr">
@@ -15803,29 +16135,34 @@
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The Riley Gaines Show (Fox)': 196 episodes, latest 2026-07-14. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O184" s="6" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O184" s="6" t="inlineStr">
+      <c r="P184" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P184" s="6" t="inlineStr">
+      <c r="Q184" s="6" t="inlineStr">
         <is>
           <t>Verify Israel-specific commentary.</t>
         </is>
       </c>
-      <c r="Q184" s="6" t="inlineStr">
+      <c r="R184" s="6" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="R184" s="6" t="inlineStr"/>
       <c r="S184" s="6" t="inlineStr"/>
       <c r="T184" s="6" t="inlineStr"/>
       <c r="U184" s="6" t="inlineStr"/>
       <c r="V184" s="6" t="inlineStr"/>
+      <c r="W184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -15877,31 +16214,32 @@
       <c r="K185" s="6" t="inlineStr"/>
       <c r="L185" s="6" t="inlineStr"/>
       <c r="M185" s="6" t="inlineStr"/>
-      <c r="N185" s="6" t="inlineStr">
+      <c r="N185" s="6" t="inlineStr"/>
+      <c r="O185" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O185" s="6" t="inlineStr">
+      <c r="P185" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P185" s="6" t="inlineStr">
+      <c r="Q185" s="6" t="inlineStr">
         <is>
           <t>Watch for any faith/Israel signals; identify possible warm intro paths (faith-athlete networks, Jonathan Isaac-style outreach).</t>
         </is>
       </c>
-      <c r="Q185" s="6" t="inlineStr">
+      <c r="R185" s="6" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="R185" s="6" t="inlineStr"/>
       <c r="S185" s="6" t="inlineStr"/>
       <c r="T185" s="6" t="inlineStr"/>
       <c r="U185" s="6" t="inlineStr"/>
       <c r="V185" s="6" t="inlineStr"/>
+      <c r="W185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
@@ -15957,31 +16295,32 @@
       <c r="K186" s="6" t="inlineStr"/>
       <c r="L186" s="6" t="inlineStr"/>
       <c r="M186" s="6" t="inlineStr"/>
-      <c r="N186" s="6" t="inlineStr">
+      <c r="N186" s="6" t="inlineStr"/>
+      <c r="O186" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O186" s="6" t="inlineStr">
+      <c r="P186" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P186" s="6" t="inlineStr">
+      <c r="Q186" s="6" t="inlineStr">
         <is>
           <t>Anonymous -- identity unknown; monitor for continued alignment. Strong candidate for the ally-expansion rule: map who amplifies her (Cruz +).</t>
         </is>
       </c>
-      <c r="Q186" s="6" t="inlineStr"/>
       <c r="R186" s="6" t="inlineStr"/>
-      <c r="S186" s="6" t="inlineStr">
+      <c r="S186" s="6" t="inlineStr"/>
+      <c r="T186" s="6" t="inlineStr">
         <is>
           <t>Ted Cruz</t>
         </is>
       </c>
-      <c r="T186" s="6" t="inlineStr"/>
       <c r="U186" s="6" t="inlineStr"/>
       <c r="V186" s="6" t="inlineStr"/>
+      <c r="W186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -16037,31 +16376,32 @@
       <c r="K187" s="6" t="inlineStr"/>
       <c r="L187" s="6" t="inlineStr"/>
       <c r="M187" s="6" t="inlineStr"/>
-      <c r="N187" s="6" t="inlineStr">
+      <c r="N187" s="6" t="inlineStr"/>
+      <c r="O187" s="6" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="O187" s="6" t="inlineStr">
+      <c r="P187" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P187" s="6" t="inlineStr">
+      <c r="Q187" s="6" t="inlineStr">
         <is>
           <t>Strong ally-expansion node: map who collaborates with him as a positive-signal graph.</t>
         </is>
       </c>
-      <c r="Q187" s="6" t="inlineStr"/>
       <c r="R187" s="6" t="inlineStr"/>
-      <c r="S187" s="6" t="inlineStr">
+      <c r="S187" s="6" t="inlineStr"/>
+      <c r="T187" s="6" t="inlineStr">
         <is>
           <t>Evan Faunce</t>
         </is>
       </c>
-      <c r="T187" s="6" t="inlineStr"/>
       <c r="U187" s="6" t="inlineStr"/>
       <c r="V187" s="6" t="inlineStr"/>
+      <c r="W187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -16117,35 +16457,36 @@
       <c r="K188" s="6" t="inlineStr"/>
       <c r="L188" s="6" t="inlineStr"/>
       <c r="M188" s="6" t="inlineStr"/>
-      <c r="N188" s="6" t="inlineStr">
+      <c r="N188" s="6" t="inlineStr"/>
+      <c r="O188" s="6" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O188" s="6" t="inlineStr">
+      <c r="P188" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P188" s="6" t="inlineStr">
+      <c r="Q188" s="6" t="inlineStr">
         <is>
           <t>Associational signal, not an explicit stance -- confirm his own views if possible; watch for further pro-Israel/Jewish-creator collaborations.</t>
         </is>
       </c>
-      <c r="Q188" s="6" t="inlineStr"/>
-      <c r="R188" s="6" t="inlineStr">
+      <c r="R188" s="6" t="inlineStr"/>
+      <c r="S188" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S188" s="6" t="inlineStr">
+      <c r="T188" s="6" t="inlineStr">
         <is>
           <t>Ami Kozak</t>
         </is>
       </c>
-      <c r="T188" s="6" t="inlineStr"/>
       <c r="U188" s="6" t="inlineStr"/>
       <c r="V188" s="6" t="inlineStr"/>
+      <c r="W188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -16201,27 +16542,28 @@
       <c r="K189" s="6" t="inlineStr"/>
       <c r="L189" s="6" t="inlineStr"/>
       <c r="M189" s="6" t="inlineStr"/>
-      <c r="N189" s="6" t="inlineStr">
+      <c r="N189" s="6" t="inlineStr"/>
+      <c r="O189" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O189" s="6" t="inlineStr">
+      <c r="P189" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P189" s="6" t="inlineStr">
+      <c r="Q189" s="6" t="inlineStr">
         <is>
           <t>Assess whether the parody targets lean supportive or mocking of pro-Israel figures; verify any direct stance.</t>
         </is>
       </c>
-      <c r="Q189" s="6" t="inlineStr"/>
       <c r="R189" s="6" t="inlineStr"/>
       <c r="S189" s="6" t="inlineStr"/>
       <c r="T189" s="6" t="inlineStr"/>
       <c r="U189" s="6" t="inlineStr"/>
       <c r="V189" s="6" t="inlineStr"/>
+      <c r="W189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -16277,27 +16619,28 @@
       <c r="K190" s="6" t="inlineStr"/>
       <c r="L190" s="6" t="inlineStr"/>
       <c r="M190" s="6" t="inlineStr"/>
-      <c r="N190" s="6" t="inlineStr">
+      <c r="N190" s="6" t="inlineStr"/>
+      <c r="O190" s="6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="O190" s="6" t="inlineStr">
+      <c r="P190" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P190" s="6" t="inlineStr"/>
       <c r="Q190" s="6" t="inlineStr"/>
       <c r="R190" s="6" t="inlineStr"/>
-      <c r="S190" s="6" t="inlineStr">
+      <c r="S190" s="6" t="inlineStr"/>
+      <c r="T190" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation, Knesset Christian Allies Caucus</t>
         </is>
       </c>
-      <c r="T190" s="6" t="inlineStr"/>
       <c r="U190" s="6" t="inlineStr"/>
       <c r="V190" s="6" t="inlineStr"/>
+      <c r="W190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -16349,27 +16692,28 @@
       <c r="K191" s="6" t="inlineStr"/>
       <c r="L191" s="6" t="inlineStr"/>
       <c r="M191" s="6" t="inlineStr"/>
-      <c r="N191" s="6" t="inlineStr">
+      <c r="N191" s="6" t="inlineStr"/>
+      <c r="O191" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O191" s="6" t="inlineStr">
+      <c r="P191" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P191" s="6" t="inlineStr"/>
       <c r="Q191" s="6" t="inlineStr"/>
       <c r="R191" s="6" t="inlineStr"/>
-      <c r="S191" s="6" t="inlineStr">
+      <c r="S191" s="6" t="inlineStr"/>
+      <c r="T191" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation, CrownQuest Operating</t>
         </is>
       </c>
-      <c r="T191" s="6" t="inlineStr"/>
       <c r="U191" s="6" t="inlineStr"/>
       <c r="V191" s="6" t="inlineStr"/>
+      <c r="W191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
@@ -16421,27 +16765,28 @@
       <c r="K192" s="6" t="inlineStr"/>
       <c r="L192" s="6" t="inlineStr"/>
       <c r="M192" s="6" t="inlineStr"/>
-      <c r="N192" s="6" t="inlineStr">
+      <c r="N192" s="6" t="inlineStr"/>
+      <c r="O192" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O192" s="6" t="inlineStr">
+      <c r="P192" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P192" s="6" t="inlineStr"/>
       <c r="Q192" s="6" t="inlineStr"/>
       <c r="R192" s="6" t="inlineStr"/>
-      <c r="S192" s="6" t="inlineStr">
+      <c r="S192" s="6" t="inlineStr"/>
+      <c r="T192" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation, Saulsbury Industries</t>
         </is>
       </c>
-      <c r="T192" s="6" t="inlineStr"/>
       <c r="U192" s="6" t="inlineStr"/>
       <c r="V192" s="6" t="inlineStr"/>
+      <c r="W192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -16505,27 +16850,28 @@
           <t>US + Israel broadcast reach</t>
         </is>
       </c>
-      <c r="N193" s="6" t="inlineStr">
+      <c r="N193" s="6" t="inlineStr"/>
+      <c r="O193" s="6" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="O193" s="6" t="inlineStr">
+      <c r="P193" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P193" s="6" t="inlineStr"/>
       <c r="Q193" s="6" t="inlineStr"/>
       <c r="R193" s="6" t="inlineStr"/>
-      <c r="S193" s="6" t="inlineStr">
+      <c r="S193" s="6" t="inlineStr"/>
+      <c r="T193" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T193" s="6" t="inlineStr"/>
       <c r="U193" s="6" t="inlineStr"/>
       <c r="V193" s="6" t="inlineStr"/>
+      <c r="W193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
@@ -16577,27 +16923,28 @@
       <c r="K194" s="6" t="inlineStr"/>
       <c r="L194" s="6" t="inlineStr"/>
       <c r="M194" s="6" t="inlineStr"/>
-      <c r="N194" s="6" t="inlineStr">
+      <c r="N194" s="6" t="inlineStr"/>
+      <c r="O194" s="6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O194" s="6" t="inlineStr">
+      <c r="P194" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P194" s="6" t="inlineStr"/>
       <c r="Q194" s="6" t="inlineStr"/>
       <c r="R194" s="6" t="inlineStr"/>
-      <c r="S194" s="6" t="inlineStr">
+      <c r="S194" s="6" t="inlineStr"/>
+      <c r="T194" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T194" s="6" t="inlineStr"/>
       <c r="U194" s="6" t="inlineStr"/>
       <c r="V194" s="6" t="inlineStr"/>
+      <c r="W194" s="6" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -16648,12 +16995,12 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Larry Huch Ministries Podcast (553 eps, latest 2026-07-12)</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr">
@@ -16663,25 +17010,30 @@
       </c>
       <c r="N195" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Larry Huch Ministries Podcast': 553 episodes, latest 2026-07-12. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O195" s="6" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O195" s="6" t="inlineStr">
+      <c r="P195" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P195" s="6" t="inlineStr"/>
       <c r="Q195" s="6" t="inlineStr"/>
       <c r="R195" s="6" t="inlineStr"/>
-      <c r="S195" s="6" t="inlineStr">
+      <c r="S195" s="6" t="inlineStr"/>
+      <c r="T195" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation, New Beginnings Church</t>
         </is>
       </c>
-      <c r="T195" s="6" t="inlineStr"/>
       <c r="U195" s="6" t="inlineStr"/>
       <c r="V195" s="6" t="inlineStr"/>
+      <c r="W195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -16733,27 +17085,28 @@
       <c r="K196" s="6" t="inlineStr"/>
       <c r="L196" s="6" t="inlineStr"/>
       <c r="M196" s="6" t="inlineStr"/>
-      <c r="N196" s="6" t="inlineStr">
+      <c r="N196" s="6" t="inlineStr"/>
+      <c r="O196" s="6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O196" s="6" t="inlineStr">
+      <c r="P196" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P196" s="6" t="inlineStr"/>
       <c r="Q196" s="6" t="inlineStr"/>
       <c r="R196" s="6" t="inlineStr"/>
-      <c r="S196" s="6" t="inlineStr">
+      <c r="S196" s="6" t="inlineStr"/>
+      <c r="T196" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation, Bridges for Peace</t>
         </is>
       </c>
-      <c r="T196" s="6" t="inlineStr"/>
       <c r="U196" s="6" t="inlineStr"/>
       <c r="V196" s="6" t="inlineStr"/>
+      <c r="W196" s="6" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -16805,31 +17158,32 @@
       <c r="K197" s="6" t="inlineStr"/>
       <c r="L197" s="6" t="inlineStr"/>
       <c r="M197" s="6" t="inlineStr"/>
-      <c r="N197" s="6" t="inlineStr">
+      <c r="N197" s="6" t="inlineStr"/>
+      <c r="O197" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O197" s="6" t="inlineStr">
+      <c r="P197" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P197" s="6" t="inlineStr">
+      <c r="Q197" s="6" t="inlineStr">
         <is>
           <t>Add contact/social links; map her congressional-affairs relationships (ally-expansion).</t>
         </is>
       </c>
-      <c r="Q197" s="6" t="inlineStr"/>
       <c r="R197" s="6" t="inlineStr"/>
-      <c r="S197" s="6" t="inlineStr">
+      <c r="S197" s="6" t="inlineStr"/>
+      <c r="T197" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T197" s="6" t="inlineStr"/>
       <c r="U197" s="6" t="inlineStr"/>
       <c r="V197" s="6" t="inlineStr"/>
+      <c r="W197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
@@ -16881,27 +17235,28 @@
       <c r="K198" s="6" t="inlineStr"/>
       <c r="L198" s="6" t="inlineStr"/>
       <c r="M198" s="6" t="inlineStr"/>
-      <c r="N198" s="6" t="inlineStr">
+      <c r="N198" s="6" t="inlineStr"/>
+      <c r="O198" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O198" s="6" t="inlineStr">
+      <c r="P198" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P198" s="6" t="inlineStr"/>
       <c r="Q198" s="6" t="inlineStr"/>
       <c r="R198" s="6" t="inlineStr"/>
-      <c r="S198" s="6" t="inlineStr">
+      <c r="S198" s="6" t="inlineStr"/>
+      <c r="T198" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T198" s="6" t="inlineStr"/>
       <c r="U198" s="6" t="inlineStr"/>
       <c r="V198" s="6" t="inlineStr"/>
+      <c r="W198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -16953,27 +17308,28 @@
       <c r="K199" s="6" t="inlineStr"/>
       <c r="L199" s="6" t="inlineStr"/>
       <c r="M199" s="6" t="inlineStr"/>
-      <c r="N199" s="6" t="inlineStr">
+      <c r="N199" s="6" t="inlineStr"/>
+      <c r="O199" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O199" s="6" t="inlineStr">
+      <c r="P199" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P199" s="6" t="inlineStr"/>
       <c r="Q199" s="6" t="inlineStr"/>
       <c r="R199" s="6" t="inlineStr"/>
-      <c r="S199" s="6" t="inlineStr">
+      <c r="S199" s="6" t="inlineStr"/>
+      <c r="T199" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T199" s="6" t="inlineStr"/>
       <c r="U199" s="6" t="inlineStr"/>
       <c r="V199" s="6" t="inlineStr"/>
+      <c r="W199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
@@ -17037,27 +17393,28 @@
           <t>IAF Europe network</t>
         </is>
       </c>
-      <c r="N200" s="6" t="inlineStr">
+      <c r="N200" s="6" t="inlineStr"/>
+      <c r="O200" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O200" s="6" t="inlineStr">
+      <c r="P200" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P200" s="6" t="inlineStr"/>
       <c r="Q200" s="6" t="inlineStr"/>
       <c r="R200" s="6" t="inlineStr"/>
-      <c r="S200" s="6" t="inlineStr">
+      <c r="S200" s="6" t="inlineStr"/>
+      <c r="T200" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T200" s="6" t="inlineStr"/>
       <c r="U200" s="6" t="inlineStr"/>
       <c r="V200" s="6" t="inlineStr"/>
+      <c r="W200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -17121,27 +17478,28 @@
           <t>IAF Africa network</t>
         </is>
       </c>
-      <c r="N201" s="6" t="inlineStr">
+      <c r="N201" s="6" t="inlineStr"/>
+      <c r="O201" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O201" s="6" t="inlineStr">
+      <c r="P201" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P201" s="6" t="inlineStr"/>
       <c r="Q201" s="6" t="inlineStr"/>
       <c r="R201" s="6" t="inlineStr"/>
-      <c r="S201" s="6" t="inlineStr">
+      <c r="S201" s="6" t="inlineStr"/>
+      <c r="T201" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T201" s="6" t="inlineStr"/>
       <c r="U201" s="6" t="inlineStr"/>
       <c r="V201" s="6" t="inlineStr"/>
+      <c r="W201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
@@ -17192,12 +17550,12 @@
       </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Joni Table Talk Podcast (575 eps, latest 2026-07-13)</t>
         </is>
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M202" s="6" t="inlineStr">
@@ -17207,25 +17565,30 @@
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Joni Table Talk Podcast': 575 episodes, latest 2026-07-13. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O202" s="6" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O202" s="6" t="inlineStr">
+      <c r="P202" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P202" s="6" t="inlineStr"/>
       <c r="Q202" s="6" t="inlineStr"/>
       <c r="R202" s="6" t="inlineStr"/>
-      <c r="S202" s="6" t="inlineStr">
+      <c r="S202" s="6" t="inlineStr"/>
+      <c r="T202" s="6" t="inlineStr">
         <is>
           <t>Daystar Television Network</t>
         </is>
       </c>
-      <c r="T202" s="6" t="inlineStr"/>
       <c r="U202" s="6" t="inlineStr"/>
       <c r="V202" s="6" t="inlineStr"/>
+      <c r="W202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -17289,23 +17652,24 @@
           <t>Congregational + broadcast</t>
         </is>
       </c>
-      <c r="N203" s="6" t="inlineStr">
+      <c r="N203" s="6" t="inlineStr"/>
+      <c r="O203" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O203" s="6" t="inlineStr">
+      <c r="P203" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P203" s="6" t="inlineStr"/>
       <c r="Q203" s="6" t="inlineStr"/>
       <c r="R203" s="6" t="inlineStr"/>
       <c r="S203" s="6" t="inlineStr"/>
       <c r="T203" s="6" t="inlineStr"/>
       <c r="U203" s="6" t="inlineStr"/>
       <c r="V203" s="6" t="inlineStr"/>
+      <c r="W203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -17369,27 +17733,28 @@
           <t>CUFI's 10M+ member network</t>
         </is>
       </c>
-      <c r="N204" s="6" t="inlineStr">
+      <c r="N204" s="6" t="inlineStr"/>
+      <c r="O204" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O204" s="6" t="inlineStr">
+      <c r="P204" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P204" s="6" t="inlineStr"/>
       <c r="Q204" s="6" t="inlineStr"/>
       <c r="R204" s="6" t="inlineStr"/>
-      <c r="S204" s="6" t="inlineStr">
+      <c r="S204" s="6" t="inlineStr"/>
+      <c r="T204" s="6" t="inlineStr">
         <is>
           <t>CUFI (Christians United for Israel)</t>
         </is>
       </c>
-      <c r="T204" s="6" t="inlineStr"/>
       <c r="U204" s="6" t="inlineStr"/>
       <c r="V204" s="6" t="inlineStr"/>
+      <c r="W204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -17437,27 +17802,28 @@
       <c r="K205" s="6" t="inlineStr"/>
       <c r="L205" s="6" t="inlineStr"/>
       <c r="M205" s="6" t="inlineStr"/>
-      <c r="N205" s="6" t="inlineStr">
+      <c r="N205" s="6" t="inlineStr"/>
+      <c r="O205" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O205" s="6" t="inlineStr">
+      <c r="P205" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P205" s="6" t="inlineStr">
+      <c r="Q205" s="6" t="inlineStr">
         <is>
           <t>Document the specific pro-Israel actions that earned IAF Top-50 placement; strong center-left bridge candidate if confirmed.</t>
         </is>
       </c>
-      <c r="Q205" s="6" t="inlineStr"/>
       <c r="R205" s="6" t="inlineStr"/>
       <c r="S205" s="6" t="inlineStr"/>
       <c r="T205" s="6" t="inlineStr"/>
       <c r="U205" s="6" t="inlineStr"/>
       <c r="V205" s="6" t="inlineStr"/>
+      <c r="W205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
@@ -17509,27 +17875,28 @@
       <c r="K206" s="6" t="inlineStr"/>
       <c r="L206" s="6" t="inlineStr"/>
       <c r="M206" s="6" t="inlineStr"/>
-      <c r="N206" s="6" t="inlineStr">
+      <c r="N206" s="6" t="inlineStr"/>
+      <c r="O206" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O206" s="6" t="inlineStr">
+      <c r="P206" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P206" s="6" t="inlineStr"/>
       <c r="Q206" s="6" t="inlineStr"/>
       <c r="R206" s="6" t="inlineStr"/>
-      <c r="S206" s="6" t="inlineStr">
+      <c r="S206" s="6" t="inlineStr"/>
+      <c r="T206" s="6" t="inlineStr">
         <is>
           <t>Bridges for Peace</t>
         </is>
       </c>
-      <c r="T206" s="6" t="inlineStr"/>
       <c r="U206" s="6" t="inlineStr"/>
       <c r="V206" s="6" t="inlineStr"/>
+      <c r="W206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -17593,27 +17960,28 @@
           <t>NRB member network (thousands of Christian broadcasters)</t>
         </is>
       </c>
-      <c r="N207" s="6" t="inlineStr">
+      <c r="N207" s="6" t="inlineStr"/>
+      <c r="O207" s="6" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="O207" s="6" t="inlineStr">
+      <c r="P207" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P207" s="6" t="inlineStr"/>
       <c r="Q207" s="6" t="inlineStr"/>
       <c r="R207" s="6" t="inlineStr"/>
-      <c r="S207" s="6" t="inlineStr">
+      <c r="S207" s="6" t="inlineStr"/>
+      <c r="T207" s="6" t="inlineStr">
         <is>
           <t>National Religious Broadcasters</t>
         </is>
       </c>
-      <c r="T207" s="6" t="inlineStr"/>
       <c r="U207" s="6" t="inlineStr"/>
       <c r="V207" s="6" t="inlineStr"/>
+      <c r="W207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
@@ -17677,27 +18045,28 @@
           <t>CPAC national + international reach</t>
         </is>
       </c>
-      <c r="N208" s="6" t="inlineStr">
+      <c r="N208" s="6" t="inlineStr"/>
+      <c r="O208" s="6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O208" s="6" t="inlineStr">
+      <c r="P208" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P208" s="6" t="inlineStr"/>
       <c r="Q208" s="6" t="inlineStr"/>
       <c r="R208" s="6" t="inlineStr"/>
-      <c r="S208" s="6" t="inlineStr">
+      <c r="S208" s="6" t="inlineStr"/>
+      <c r="T208" s="6" t="inlineStr">
         <is>
           <t>American Conservative Union (CPAC)</t>
         </is>
       </c>
-      <c r="T208" s="6" t="inlineStr"/>
       <c r="U208" s="6" t="inlineStr"/>
       <c r="V208" s="6" t="inlineStr"/>
+      <c r="W208" s="6" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -17749,27 +18118,28 @@
       <c r="K209" s="6" t="inlineStr"/>
       <c r="L209" s="6" t="inlineStr"/>
       <c r="M209" s="6" t="inlineStr"/>
-      <c r="N209" s="6" t="inlineStr">
+      <c r="N209" s="6" t="inlineStr"/>
+      <c r="O209" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O209" s="6" t="inlineStr">
+      <c r="P209" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P209" s="6" t="inlineStr"/>
-      <c r="Q209" s="6" t="inlineStr">
+      <c r="Q209" s="6" t="inlineStr"/>
+      <c r="R209" s="6" t="inlineStr">
         <is>
           <t>Film</t>
         </is>
       </c>
-      <c r="R209" s="6" t="inlineStr"/>
       <c r="S209" s="6" t="inlineStr"/>
       <c r="T209" s="6" t="inlineStr"/>
       <c r="U209" s="6" t="inlineStr"/>
       <c r="V209" s="6" t="inlineStr"/>
+      <c r="W209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -17833,23 +18203,24 @@
           <t>Major East African megachurch</t>
         </is>
       </c>
-      <c r="N210" s="6" t="inlineStr">
+      <c r="N210" s="6" t="inlineStr"/>
+      <c r="O210" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O210" s="6" t="inlineStr">
+      <c r="P210" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P210" s="6" t="inlineStr"/>
       <c r="Q210" s="6" t="inlineStr"/>
       <c r="R210" s="6" t="inlineStr"/>
       <c r="S210" s="6" t="inlineStr"/>
       <c r="T210" s="6" t="inlineStr"/>
       <c r="U210" s="6" t="inlineStr"/>
       <c r="V210" s="6" t="inlineStr"/>
+      <c r="W210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -17913,23 +18284,24 @@
           <t>One of the world's largest church networks</t>
         </is>
       </c>
-      <c r="N211" s="6" t="inlineStr">
+      <c r="N211" s="6" t="inlineStr"/>
+      <c r="O211" s="6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O211" s="6" t="inlineStr">
+      <c r="P211" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P211" s="6" t="inlineStr"/>
       <c r="Q211" s="6" t="inlineStr"/>
       <c r="R211" s="6" t="inlineStr"/>
       <c r="S211" s="6" t="inlineStr"/>
       <c r="T211" s="6" t="inlineStr"/>
       <c r="U211" s="6" t="inlineStr"/>
       <c r="V211" s="6" t="inlineStr"/>
+      <c r="W211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
@@ -17993,27 +18365,28 @@
           <t>Major conservative cable/streaming audience</t>
         </is>
       </c>
-      <c r="N212" s="6" t="inlineStr">
+      <c r="N212" s="6" t="inlineStr"/>
+      <c r="O212" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O212" s="6" t="inlineStr">
+      <c r="P212" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P212" s="6" t="inlineStr"/>
       <c r="Q212" s="6" t="inlineStr"/>
       <c r="R212" s="6" t="inlineStr"/>
-      <c r="S212" s="6" t="inlineStr">
+      <c r="S212" s="6" t="inlineStr"/>
+      <c r="T212" s="6" t="inlineStr">
         <is>
           <t>Newsmax</t>
         </is>
       </c>
-      <c r="T212" s="6" t="inlineStr"/>
       <c r="U212" s="6" t="inlineStr"/>
       <c r="V212" s="6" t="inlineStr"/>
+      <c r="W212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -18077,27 +18450,28 @@
           <t>Global C4I network</t>
         </is>
       </c>
-      <c r="N213" s="6" t="inlineStr">
+      <c r="N213" s="6" t="inlineStr"/>
+      <c r="O213" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O213" s="6" t="inlineStr">
+      <c r="P213" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P213" s="6" t="inlineStr"/>
       <c r="Q213" s="6" t="inlineStr"/>
       <c r="R213" s="6" t="inlineStr"/>
-      <c r="S213" s="6" t="inlineStr">
+      <c r="S213" s="6" t="inlineStr"/>
+      <c r="T213" s="6" t="inlineStr">
         <is>
           <t>Christians for Israel (C4I)</t>
         </is>
       </c>
-      <c r="T213" s="6" t="inlineStr"/>
       <c r="U213" s="6" t="inlineStr"/>
       <c r="V213" s="6" t="inlineStr"/>
+      <c r="W213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -18148,12 +18522,12 @@
       </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Out of Zion with Susan Michael (287 eps, latest 2026-07-10)</t>
         </is>
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M214" s="6" t="inlineStr">
@@ -18163,25 +18537,30 @@
       </c>
       <c r="N214" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Out of Zion with Susan Michael': 287 episodes, latest 2026-07-10. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O214" s="6" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="O214" s="6" t="inlineStr">
+      <c r="P214" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P214" s="6" t="inlineStr"/>
       <c r="Q214" s="6" t="inlineStr"/>
       <c r="R214" s="6" t="inlineStr"/>
-      <c r="S214" s="6" t="inlineStr">
+      <c r="S214" s="6" t="inlineStr"/>
+      <c r="T214" s="6" t="inlineStr">
         <is>
           <t>ICEJ</t>
         </is>
       </c>
-      <c r="T214" s="6" t="inlineStr"/>
       <c r="U214" s="6" t="inlineStr"/>
       <c r="V214" s="6" t="inlineStr"/>
+      <c r="W214" s="6" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -18245,27 +18624,28 @@
           <t>Growing pro-settlement volunteer + media network</t>
         </is>
       </c>
-      <c r="N215" s="6" t="inlineStr">
+      <c r="N215" s="6" t="inlineStr"/>
+      <c r="O215" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O215" s="6" t="inlineStr">
+      <c r="P215" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P215" s="6" t="inlineStr"/>
       <c r="Q215" s="6" t="inlineStr"/>
       <c r="R215" s="6" t="inlineStr"/>
-      <c r="S215" s="6" t="inlineStr">
+      <c r="S215" s="6" t="inlineStr"/>
+      <c r="T215" s="6" t="inlineStr">
         <is>
           <t>HaYovel</t>
         </is>
       </c>
-      <c r="T215" s="6" t="inlineStr"/>
       <c r="U215" s="6" t="inlineStr"/>
       <c r="V215" s="6" t="inlineStr"/>
+      <c r="W215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -18317,23 +18697,24 @@
       <c r="K216" s="6" t="inlineStr"/>
       <c r="L216" s="6" t="inlineStr"/>
       <c r="M216" s="6" t="inlineStr"/>
-      <c r="N216" s="6" t="inlineStr">
+      <c r="N216" s="6" t="inlineStr"/>
+      <c r="O216" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O216" s="6" t="inlineStr">
+      <c r="P216" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P216" s="6" t="inlineStr"/>
       <c r="Q216" s="6" t="inlineStr"/>
       <c r="R216" s="6" t="inlineStr"/>
       <c r="S216" s="6" t="inlineStr"/>
       <c r="T216" s="6" t="inlineStr"/>
       <c r="U216" s="6" t="inlineStr"/>
       <c r="V216" s="6" t="inlineStr"/>
+      <c r="W216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -18397,23 +18778,24 @@
           <t>Major Kenyan church network</t>
         </is>
       </c>
-      <c r="N217" s="6" t="inlineStr">
+      <c r="N217" s="6" t="inlineStr"/>
+      <c r="O217" s="6" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O217" s="6" t="inlineStr">
+      <c r="P217" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P217" s="6" t="inlineStr"/>
       <c r="Q217" s="6" t="inlineStr"/>
       <c r="R217" s="6" t="inlineStr"/>
       <c r="S217" s="6" t="inlineStr"/>
       <c r="T217" s="6" t="inlineStr"/>
       <c r="U217" s="6" t="inlineStr"/>
       <c r="V217" s="6" t="inlineStr"/>
+      <c r="W217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -18464,12 +18846,12 @@
       </c>
       <c r="K218" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- Stand on the Word with Tony Perkins (201 eps, latest 2026-07-16)</t>
         </is>
       </c>
       <c r="L218" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M218" s="6" t="inlineStr">
@@ -18479,25 +18861,30 @@
       </c>
       <c r="N218" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'Stand on the Word with Tony Perkins': 201 episodes, latest 2026-07-16. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O218" s="6" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O218" s="6" t="inlineStr">
+      <c r="P218" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P218" s="6" t="inlineStr"/>
       <c r="Q218" s="6" t="inlineStr"/>
       <c r="R218" s="6" t="inlineStr"/>
-      <c r="S218" s="6" t="inlineStr">
+      <c r="S218" s="6" t="inlineStr"/>
+      <c r="T218" s="6" t="inlineStr">
         <is>
           <t>Family Research Council</t>
         </is>
       </c>
-      <c r="T218" s="6" t="inlineStr"/>
       <c r="U218" s="6" t="inlineStr"/>
       <c r="V218" s="6" t="inlineStr"/>
+      <c r="W218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -18561,23 +18948,24 @@
           <t>Japanese Christian pro-Israel network</t>
         </is>
       </c>
-      <c r="N219" s="6" t="inlineStr">
+      <c r="N219" s="6" t="inlineStr"/>
+      <c r="O219" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O219" s="6" t="inlineStr">
+      <c r="P219" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P219" s="6" t="inlineStr"/>
       <c r="Q219" s="6" t="inlineStr"/>
       <c r="R219" s="6" t="inlineStr"/>
       <c r="S219" s="6" t="inlineStr"/>
       <c r="T219" s="6" t="inlineStr"/>
       <c r="U219" s="6" t="inlineStr"/>
       <c r="V219" s="6" t="inlineStr"/>
+      <c r="W219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
@@ -18629,27 +19017,28 @@
       <c r="K220" s="6" t="inlineStr"/>
       <c r="L220" s="6" t="inlineStr"/>
       <c r="M220" s="6" t="inlineStr"/>
-      <c r="N220" s="6" t="inlineStr">
+      <c r="N220" s="6" t="inlineStr"/>
+      <c r="O220" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O220" s="6" t="inlineStr">
+      <c r="P220" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P220" s="6" t="inlineStr"/>
       <c r="Q220" s="6" t="inlineStr"/>
       <c r="R220" s="6" t="inlineStr"/>
-      <c r="S220" s="6" t="inlineStr">
+      <c r="S220" s="6" t="inlineStr"/>
+      <c r="T220" s="6" t="inlineStr">
         <is>
           <t>Passages</t>
         </is>
       </c>
-      <c r="T220" s="6" t="inlineStr"/>
       <c r="U220" s="6" t="inlineStr"/>
       <c r="V220" s="6" t="inlineStr"/>
+      <c r="W220" s="6" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -18713,23 +19102,24 @@
           <t>Hungarian + international conservative network</t>
         </is>
       </c>
-      <c r="N221" s="6" t="inlineStr">
+      <c r="N221" s="6" t="inlineStr"/>
+      <c r="O221" s="6" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O221" s="6" t="inlineStr">
+      <c r="P221" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P221" s="6" t="inlineStr"/>
       <c r="Q221" s="6" t="inlineStr"/>
       <c r="R221" s="6" t="inlineStr"/>
       <c r="S221" s="6" t="inlineStr"/>
       <c r="T221" s="6" t="inlineStr"/>
       <c r="U221" s="6" t="inlineStr"/>
       <c r="V221" s="6" t="inlineStr"/>
+      <c r="W221" s="6" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
@@ -18793,27 +19183,28 @@
           <t>Latin American evangelical men's network</t>
         </is>
       </c>
-      <c r="N222" s="6" t="inlineStr">
+      <c r="N222" s="6" t="inlineStr"/>
+      <c r="O222" s="6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="O222" s="6" t="inlineStr">
+      <c r="P222" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P222" s="6" t="inlineStr">
+      <c r="Q222" s="6" t="inlineStr">
         <is>
           <t>Confirm whether this is the same 'Carlos Duran' already in the DB (JPost 2024 Latino ally) and merge if so.</t>
         </is>
       </c>
-      <c r="Q222" s="6" t="inlineStr"/>
       <c r="R222" s="6" t="inlineStr"/>
       <c r="S222" s="6" t="inlineStr"/>
       <c r="T222" s="6" t="inlineStr"/>
       <c r="U222" s="6" t="inlineStr"/>
       <c r="V222" s="6" t="inlineStr"/>
+      <c r="W222" s="6" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -18877,27 +19268,28 @@
           <t>Canadian evangelical network</t>
         </is>
       </c>
-      <c r="N223" s="6" t="inlineStr">
+      <c r="N223" s="6" t="inlineStr"/>
+      <c r="O223" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O223" s="6" t="inlineStr">
+      <c r="P223" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P223" s="6" t="inlineStr"/>
       <c r="Q223" s="6" t="inlineStr"/>
       <c r="R223" s="6" t="inlineStr"/>
-      <c r="S223" s="6" t="inlineStr">
+      <c r="S223" s="6" t="inlineStr"/>
+      <c r="T223" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="T223" s="6" t="inlineStr"/>
       <c r="U223" s="6" t="inlineStr"/>
       <c r="V223" s="6" t="inlineStr"/>
+      <c r="W223" s="6" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -18961,23 +19353,24 @@
           <t>Latin American pastor network</t>
         </is>
       </c>
-      <c r="N224" s="6" t="inlineStr">
+      <c r="N224" s="6" t="inlineStr"/>
+      <c r="O224" s="6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="O224" s="6" t="inlineStr">
+      <c r="P224" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P224" s="6" t="inlineStr"/>
       <c r="Q224" s="6" t="inlineStr"/>
       <c r="R224" s="6" t="inlineStr"/>
       <c r="S224" s="6" t="inlineStr"/>
       <c r="T224" s="6" t="inlineStr"/>
       <c r="U224" s="6" t="inlineStr"/>
       <c r="V224" s="6" t="inlineStr"/>
+      <c r="W224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -19041,27 +19434,28 @@
           <t>Training network</t>
         </is>
       </c>
-      <c r="N225" s="6" t="inlineStr">
+      <c r="N225" s="6" t="inlineStr"/>
+      <c r="O225" s="6" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O225" s="6" t="inlineStr">
+      <c r="P225" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P225" s="6" t="inlineStr">
+      <c r="Q225" s="6" t="inlineStr">
         <is>
           <t>Thin public profile -- verify identity/role and add links.</t>
         </is>
       </c>
-      <c r="Q225" s="6" t="inlineStr"/>
       <c r="R225" s="6" t="inlineStr"/>
       <c r="S225" s="6" t="inlineStr"/>
       <c r="T225" s="6" t="inlineStr"/>
       <c r="U225" s="6" t="inlineStr"/>
       <c r="V225" s="6" t="inlineStr"/>
+      <c r="W225" s="6" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
@@ -19125,23 +19519,24 @@
           <t>National prayer-network reach</t>
         </is>
       </c>
-      <c r="N226" s="6" t="inlineStr">
+      <c r="N226" s="6" t="inlineStr"/>
+      <c r="O226" s="6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="O226" s="6" t="inlineStr">
+      <c r="P226" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P226" s="6" t="inlineStr"/>
       <c r="Q226" s="6" t="inlineStr"/>
       <c r="R226" s="6" t="inlineStr"/>
       <c r="S226" s="6" t="inlineStr"/>
       <c r="T226" s="6" t="inlineStr"/>
       <c r="U226" s="6" t="inlineStr"/>
       <c r="V226" s="6" t="inlineStr"/>
+      <c r="W226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -19205,23 +19600,24 @@
           <t>Regional + Black-church network</t>
         </is>
       </c>
-      <c r="N227" s="6" t="inlineStr">
+      <c r="N227" s="6" t="inlineStr"/>
+      <c r="O227" s="6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="O227" s="6" t="inlineStr">
+      <c r="P227" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P227" s="6" t="inlineStr"/>
       <c r="Q227" s="6" t="inlineStr"/>
       <c r="R227" s="6" t="inlineStr"/>
       <c r="S227" s="6" t="inlineStr"/>
       <c r="T227" s="6" t="inlineStr"/>
       <c r="U227" s="6" t="inlineStr"/>
       <c r="V227" s="6" t="inlineStr"/>
+      <c r="W227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -19285,27 +19681,28 @@
           <t>Congolese Christian network</t>
         </is>
       </c>
-      <c r="N228" s="6" t="inlineStr">
+      <c r="N228" s="6" t="inlineStr"/>
+      <c r="O228" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O228" s="6" t="inlineStr">
+      <c r="P228" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P228" s="6" t="inlineStr">
+      <c r="Q228" s="6" t="inlineStr">
         <is>
           <t>Thin public profile -- verify and add links.</t>
         </is>
       </c>
-      <c r="Q228" s="6" t="inlineStr"/>
       <c r="R228" s="6" t="inlineStr"/>
       <c r="S228" s="6" t="inlineStr"/>
       <c r="T228" s="6" t="inlineStr"/>
       <c r="U228" s="6" t="inlineStr"/>
       <c r="V228" s="6" t="inlineStr"/>
+      <c r="W228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -19369,23 +19766,24 @@
           <t>Central American evangelical network</t>
         </is>
       </c>
-      <c r="N229" s="6" t="inlineStr">
+      <c r="N229" s="6" t="inlineStr"/>
+      <c r="O229" s="6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="O229" s="6" t="inlineStr">
+      <c r="P229" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P229" s="6" t="inlineStr"/>
       <c r="Q229" s="6" t="inlineStr"/>
       <c r="R229" s="6" t="inlineStr"/>
       <c r="S229" s="6" t="inlineStr"/>
       <c r="T229" s="6" t="inlineStr"/>
       <c r="U229" s="6" t="inlineStr"/>
       <c r="V229" s="6" t="inlineStr"/>
+      <c r="W229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -19449,27 +19847,28 @@
           <t>Latin American evangelical network</t>
         </is>
       </c>
-      <c r="N230" s="6" t="inlineStr">
+      <c r="N230" s="6" t="inlineStr"/>
+      <c r="O230" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O230" s="6" t="inlineStr">
+      <c r="P230" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P230" s="6" t="inlineStr">
+      <c r="Q230" s="6" t="inlineStr">
         <is>
           <t>Common name -- verify identity and add links.</t>
         </is>
       </c>
-      <c r="Q230" s="6" t="inlineStr"/>
       <c r="R230" s="6" t="inlineStr"/>
       <c r="S230" s="6" t="inlineStr"/>
       <c r="T230" s="6" t="inlineStr"/>
       <c r="U230" s="6" t="inlineStr"/>
       <c r="V230" s="6" t="inlineStr"/>
+      <c r="W230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -19525,31 +19924,32 @@
       <c r="K231" s="6" t="inlineStr"/>
       <c r="L231" s="6" t="inlineStr"/>
       <c r="M231" s="6" t="inlineStr"/>
-      <c r="N231" s="6" t="inlineStr">
+      <c r="N231" s="6" t="inlineStr"/>
+      <c r="O231" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O231" s="6" t="inlineStr">
+      <c r="P231" s="6" t="inlineStr">
         <is>
           <t>Political</t>
         </is>
       </c>
-      <c r="P231" s="6" t="inlineStr">
+      <c r="Q231" s="6" t="inlineStr">
         <is>
           <t>Weigh the Tommy Robinson association before any formal engagement; strong Iranian pro-Israel voice otherwise.</t>
         </is>
       </c>
-      <c r="Q231" s="6" t="inlineStr"/>
-      <c r="R231" s="6" t="inlineStr">
+      <c r="R231" s="6" t="inlineStr"/>
+      <c r="S231" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S231" s="6" t="inlineStr"/>
       <c r="T231" s="6" t="inlineStr"/>
       <c r="U231" s="6" t="inlineStr"/>
       <c r="V231" s="6" t="inlineStr"/>
+      <c r="W231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -19605,23 +20005,24 @@
       <c r="K232" s="6" t="inlineStr"/>
       <c r="L232" s="6" t="inlineStr"/>
       <c r="M232" s="6" t="inlineStr"/>
-      <c r="N232" s="6" t="inlineStr">
+      <c r="N232" s="6" t="inlineStr"/>
+      <c r="O232" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O232" s="6" t="inlineStr">
+      <c r="P232" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P232" s="6" t="inlineStr"/>
       <c r="Q232" s="6" t="inlineStr"/>
       <c r="R232" s="6" t="inlineStr"/>
       <c r="S232" s="6" t="inlineStr"/>
       <c r="T232" s="6" t="inlineStr"/>
       <c r="U232" s="6" t="inlineStr"/>
       <c r="V232" s="6" t="inlineStr"/>
+      <c r="W232" s="6" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -19689,27 +20090,28 @@
           <t>Babylon Bee's tens of millions</t>
         </is>
       </c>
-      <c r="N233" s="6" t="inlineStr">
+      <c r="N233" s="6" t="inlineStr"/>
+      <c r="O233" s="6" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="O233" s="6" t="inlineStr">
+      <c r="P233" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P233" s="6" t="inlineStr"/>
       <c r="Q233" s="6" t="inlineStr"/>
       <c r="R233" s="6" t="inlineStr"/>
-      <c r="S233" s="6" t="inlineStr">
+      <c r="S233" s="6" t="inlineStr"/>
+      <c r="T233" s="6" t="inlineStr">
         <is>
           <t>Babylon Bee, Tucker Carlson, Candace Owens, Nick Fuentes</t>
         </is>
       </c>
-      <c r="T233" s="6" t="inlineStr"/>
       <c r="U233" s="6" t="inlineStr"/>
       <c r="V233" s="6" t="inlineStr"/>
+      <c r="W233" s="6" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
@@ -19765,27 +20167,28 @@
       <c r="K234" s="6" t="inlineStr"/>
       <c r="L234" s="6" t="inlineStr"/>
       <c r="M234" s="6" t="inlineStr"/>
-      <c r="N234" s="6" t="inlineStr">
+      <c r="N234" s="6" t="inlineStr"/>
+      <c r="O234" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O234" s="6" t="inlineStr">
+      <c r="P234" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P234" s="6" t="inlineStr">
+      <c r="Q234" s="6" t="inlineStr">
         <is>
           <t>Verify explicit Israel/antisemitism content.</t>
         </is>
       </c>
-      <c r="Q234" s="6" t="inlineStr"/>
       <c r="R234" s="6" t="inlineStr"/>
       <c r="S234" s="6" t="inlineStr"/>
       <c r="T234" s="6" t="inlineStr"/>
       <c r="U234" s="6" t="inlineStr"/>
       <c r="V234" s="6" t="inlineStr"/>
+      <c r="W234" s="6" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -19837,27 +20240,28 @@
       <c r="K235" s="6" t="inlineStr"/>
       <c r="L235" s="6" t="inlineStr"/>
       <c r="M235" s="6" t="inlineStr"/>
-      <c r="N235" s="6" t="inlineStr">
+      <c r="N235" s="6" t="inlineStr"/>
+      <c r="O235" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O235" s="6" t="inlineStr">
+      <c r="P235" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P235" s="6" t="inlineStr">
+      <c r="Q235" s="6" t="inlineStr">
         <is>
           <t>VERIFY IDENTITY -- little public info found; confirm role, spelling, and any Israel stance before scoring up.</t>
         </is>
       </c>
-      <c r="Q235" s="6" t="inlineStr"/>
       <c r="R235" s="6" t="inlineStr"/>
       <c r="S235" s="6" t="inlineStr"/>
       <c r="T235" s="6" t="inlineStr"/>
       <c r="U235" s="6" t="inlineStr"/>
       <c r="V235" s="6" t="inlineStr"/>
+      <c r="W235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
@@ -19909,31 +20313,32 @@
       <c r="K236" s="6" t="inlineStr"/>
       <c r="L236" s="6" t="inlineStr"/>
       <c r="M236" s="6" t="inlineStr"/>
-      <c r="N236" s="6" t="inlineStr">
+      <c r="N236" s="6" t="inlineStr"/>
+      <c r="O236" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O236" s="6" t="inlineStr">
+      <c r="P236" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P236" s="6" t="inlineStr">
+      <c r="Q236" s="6" t="inlineStr">
         <is>
           <t>Verify her own Israel/Jewish-community statements directly; weigh the Alex Stein / Joel Webbon association against the Lindell/CUFI alignment before scoring up or down.</t>
         </is>
       </c>
-      <c r="Q236" s="6" t="inlineStr"/>
       <c r="R236" s="6" t="inlineStr"/>
-      <c r="S236" s="6" t="inlineStr">
+      <c r="S236" s="6" t="inlineStr"/>
+      <c r="T236" s="6" t="inlineStr">
         <is>
           <t>Mike Lindell</t>
         </is>
       </c>
-      <c r="T236" s="6" t="inlineStr"/>
       <c r="U236" s="6" t="inlineStr"/>
       <c r="V236" s="6" t="inlineStr"/>
+      <c r="W236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -19985,27 +20390,28 @@
       <c r="K237" s="6" t="inlineStr"/>
       <c r="L237" s="6" t="inlineStr"/>
       <c r="M237" s="6" t="inlineStr"/>
-      <c r="N237" s="6" t="inlineStr">
+      <c r="N237" s="6" t="inlineStr"/>
+      <c r="O237" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O237" s="6" t="inlineStr">
+      <c r="P237" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P237" s="6" t="inlineStr"/>
       <c r="Q237" s="6" t="inlineStr"/>
       <c r="R237" s="6" t="inlineStr"/>
-      <c r="S237" s="6" t="inlineStr">
+      <c r="S237" s="6" t="inlineStr"/>
+      <c r="T237" s="6" t="inlineStr">
         <is>
           <t>The Genesis Prize Foundation</t>
         </is>
       </c>
-      <c r="T237" s="6" t="inlineStr"/>
       <c r="U237" s="6" t="inlineStr"/>
       <c r="V237" s="6" t="inlineStr"/>
+      <c r="W237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -20061,27 +20467,28 @@
       <c r="K238" s="6" t="inlineStr"/>
       <c r="L238" s="6" t="inlineStr"/>
       <c r="M238" s="6" t="inlineStr"/>
-      <c r="N238" s="6" t="inlineStr">
+      <c r="N238" s="6" t="inlineStr"/>
+      <c r="O238" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O238" s="6" t="inlineStr">
+      <c r="P238" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P238" s="6" t="inlineStr">
+      <c r="Q238" s="6" t="inlineStr">
         <is>
           <t>VERIFY IDENTITY -- no confirmable public profile found; confirm who this is and why flagged before scoring.</t>
         </is>
       </c>
-      <c r="Q238" s="6" t="inlineStr"/>
       <c r="R238" s="6" t="inlineStr"/>
       <c r="S238" s="6" t="inlineStr"/>
       <c r="T238" s="6" t="inlineStr"/>
       <c r="U238" s="6" t="inlineStr"/>
       <c r="V238" s="6" t="inlineStr"/>
+      <c r="W238" s="6" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -20133,27 +20540,28 @@
       <c r="K239" s="6" t="inlineStr"/>
       <c r="L239" s="6" t="inlineStr"/>
       <c r="M239" s="6" t="inlineStr"/>
-      <c r="N239" s="6" t="inlineStr">
+      <c r="N239" s="6" t="inlineStr"/>
+      <c r="O239" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O239" s="6" t="inlineStr">
+      <c r="P239" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P239" s="6" t="inlineStr">
+      <c r="Q239" s="6" t="inlineStr">
         <is>
           <t>Track his Israel framing over time; distinguish America-First restraint from genuine hostility.</t>
         </is>
       </c>
-      <c r="Q239" s="6" t="inlineStr"/>
       <c r="R239" s="6" t="inlineStr"/>
       <c r="S239" s="6" t="inlineStr"/>
       <c r="T239" s="6" t="inlineStr"/>
       <c r="U239" s="6" t="inlineStr"/>
       <c r="V239" s="6" t="inlineStr"/>
+      <c r="W239" s="6" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
@@ -20205,27 +20613,28 @@
       <c r="K240" s="6" t="inlineStr"/>
       <c r="L240" s="6" t="inlineStr"/>
       <c r="M240" s="6" t="inlineStr"/>
-      <c r="N240" s="6" t="inlineStr">
+      <c r="N240" s="6" t="inlineStr"/>
+      <c r="O240" s="6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O240" s="6" t="inlineStr">
+      <c r="P240" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P240" s="6" t="inlineStr">
+      <c r="Q240" s="6" t="inlineStr">
         <is>
           <t>Reputational-conduct history (2020 Tucker-show resignation) plus Israel-skeptic wing -- monitor closely; do not amplify.</t>
         </is>
       </c>
-      <c r="Q240" s="6" t="inlineStr"/>
       <c r="R240" s="6" t="inlineStr"/>
       <c r="S240" s="6" t="inlineStr"/>
       <c r="T240" s="6" t="inlineStr"/>
       <c r="U240" s="6" t="inlineStr"/>
       <c r="V240" s="6" t="inlineStr"/>
+      <c r="W240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -20281,35 +20690,36 @@
       <c r="K241" s="6" t="inlineStr"/>
       <c r="L241" s="6" t="inlineStr"/>
       <c r="M241" s="6" t="inlineStr"/>
-      <c r="N241" s="6" t="inlineStr">
+      <c r="N241" s="6" t="inlineStr"/>
+      <c r="O241" s="6" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="O241" s="6" t="inlineStr">
+      <c r="P241" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P241" s="6" t="inlineStr"/>
       <c r="Q241" s="6" t="inlineStr"/>
       <c r="R241" s="6" t="inlineStr"/>
-      <c r="S241" s="6" t="inlineStr">
+      <c r="S241" s="6" t="inlineStr"/>
+      <c r="T241" s="6" t="inlineStr">
         <is>
           <t>National Review, Young America's Foundation (YAF), Claremont Institute</t>
         </is>
       </c>
-      <c r="T241" s="6" t="inlineStr">
+      <c r="U241" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U241" s="6" t="inlineStr">
+      <c r="V241" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V241" s="6" t="inlineStr"/>
+      <c r="W241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -20365,39 +20775,40 @@
       <c r="K242" s="6" t="inlineStr"/>
       <c r="L242" s="6" t="inlineStr"/>
       <c r="M242" s="6" t="inlineStr"/>
-      <c r="N242" s="6" t="inlineStr">
+      <c r="N242" s="6" t="inlineStr"/>
+      <c r="O242" s="6" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="O242" s="6" t="inlineStr">
+      <c r="P242" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P242" s="6" t="inlineStr"/>
       <c r="Q242" s="6" t="inlineStr"/>
-      <c r="R242" s="6" t="inlineStr">
+      <c r="R242" s="6" t="inlineStr"/>
+      <c r="S242" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S242" s="6" t="inlineStr">
+      <c r="T242" s="6" t="inlineStr">
         <is>
           <t>J-TV: The Global Jewish Channel</t>
         </is>
       </c>
-      <c r="T242" s="6" t="inlineStr">
+      <c r="U242" s="6" t="inlineStr">
         <is>
           <t>British</t>
         </is>
       </c>
-      <c r="U242" s="6" t="inlineStr">
+      <c r="V242" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V242" s="6" t="inlineStr"/>
+      <c r="W242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -20453,35 +20864,36 @@
       <c r="K243" s="6" t="inlineStr"/>
       <c r="L243" s="6" t="inlineStr"/>
       <c r="M243" s="6" t="inlineStr"/>
-      <c r="N243" s="6" t="inlineStr">
+      <c r="N243" s="6" t="inlineStr"/>
+      <c r="O243" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O243" s="6" t="inlineStr">
+      <c r="P243" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P243" s="6" t="inlineStr"/>
       <c r="Q243" s="6" t="inlineStr"/>
-      <c r="R243" s="6" t="inlineStr">
+      <c r="R243" s="6" t="inlineStr"/>
+      <c r="S243" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S243" s="6" t="inlineStr"/>
-      <c r="T243" s="6" t="inlineStr">
+      <c r="T243" s="6" t="inlineStr"/>
+      <c r="U243" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U243" s="6" t="inlineStr">
+      <c r="V243" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V243" s="6" t="inlineStr"/>
+      <c r="W243" s="6" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
@@ -20533,35 +20945,36 @@
       <c r="K244" s="6" t="inlineStr"/>
       <c r="L244" s="6" t="inlineStr"/>
       <c r="M244" s="6" t="inlineStr"/>
-      <c r="N244" s="6" t="inlineStr">
+      <c r="N244" s="6" t="inlineStr"/>
+      <c r="O244" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O244" s="6" t="inlineStr">
+      <c r="P244" s="6" t="inlineStr">
         <is>
           <t>Political</t>
         </is>
       </c>
-      <c r="P244" s="6" t="inlineStr">
+      <c r="Q244" s="6" t="inlineStr">
         <is>
           <t>AMBIGUITY FLAG: Andy cited the SAME video (XNWhYhEk55o) both for Kellogg AND for 'Add hostile' -- so the video likely features a hostile figure alongside him. I cannot watch YouTube. Andy: name the hostile figure in that video so they can be added.</t>
         </is>
       </c>
-      <c r="Q244" s="6" t="inlineStr"/>
       <c r="R244" s="6" t="inlineStr"/>
       <c r="S244" s="6" t="inlineStr"/>
-      <c r="T244" s="6" t="inlineStr">
+      <c r="T244" s="6" t="inlineStr"/>
+      <c r="U244" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U244" s="6" t="inlineStr">
+      <c r="V244" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V244" s="6" t="inlineStr"/>
+      <c r="W244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -20617,35 +21030,36 @@
       <c r="K245" s="6" t="inlineStr"/>
       <c r="L245" s="6" t="inlineStr"/>
       <c r="M245" s="6" t="inlineStr"/>
-      <c r="N245" s="6" t="inlineStr">
+      <c r="N245" s="6" t="inlineStr"/>
+      <c r="O245" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O245" s="6" t="inlineStr">
+      <c r="P245" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P245" s="6" t="inlineStr">
+      <c r="Q245" s="6" t="inlineStr">
         <is>
           <t>Verify explicit Israel-specific commentary and the strength of his pro-Israel record.</t>
         </is>
       </c>
-      <c r="Q245" s="6" t="inlineStr"/>
       <c r="R245" s="6" t="inlineStr"/>
       <c r="S245" s="6" t="inlineStr"/>
-      <c r="T245" s="6" t="inlineStr">
+      <c r="T245" s="6" t="inlineStr"/>
+      <c r="U245" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U245" s="6" t="inlineStr">
+      <c r="V245" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V245" s="6" t="inlineStr"/>
+      <c r="W245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -20701,39 +21115,40 @@
       <c r="K246" s="6" t="inlineStr"/>
       <c r="L246" s="6" t="inlineStr"/>
       <c r="M246" s="6" t="inlineStr"/>
-      <c r="N246" s="6" t="inlineStr">
+      <c r="N246" s="6" t="inlineStr"/>
+      <c r="O246" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O246" s="6" t="inlineStr">
+      <c r="P246" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P246" s="6" t="inlineStr">
+      <c r="Q246" s="6" t="inlineStr">
         <is>
           <t>VERIFY: could not independently confirm her Israel-specific record; Andy to summarize what the cited video shows.</t>
         </is>
       </c>
-      <c r="Q246" s="6" t="inlineStr"/>
-      <c r="R246" s="6" t="inlineStr">
+      <c r="R246" s="6" t="inlineStr"/>
+      <c r="S246" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S246" s="6" t="inlineStr"/>
-      <c r="T246" s="6" t="inlineStr">
+      <c r="T246" s="6" t="inlineStr"/>
+      <c r="U246" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U246" s="6" t="inlineStr">
+      <c r="V246" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V246" s="6" t="inlineStr"/>
+      <c r="W246" s="6" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -20789,39 +21204,40 @@
       <c r="K247" s="6" t="inlineStr"/>
       <c r="L247" s="6" t="inlineStr"/>
       <c r="M247" s="6" t="inlineStr"/>
-      <c r="N247" s="6" t="inlineStr">
+      <c r="N247" s="6" t="inlineStr"/>
+      <c r="O247" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O247" s="6" t="inlineStr">
+      <c r="P247" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P247" s="6" t="inlineStr">
+      <c r="Q247" s="6" t="inlineStr">
         <is>
           <t>'And associates' is unbounded -- process the Pirate Wires masthead as a bounded roster pass instead.</t>
         </is>
       </c>
-      <c r="Q247" s="6" t="inlineStr"/>
       <c r="R247" s="6" t="inlineStr"/>
-      <c r="S247" s="6" t="inlineStr">
+      <c r="S247" s="6" t="inlineStr"/>
+      <c r="T247" s="6" t="inlineStr">
         <is>
           <t>Pirate Wires</t>
         </is>
       </c>
-      <c r="T247" s="6" t="inlineStr">
+      <c r="U247" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U247" s="6" t="inlineStr">
+      <c r="V247" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V247" s="6" t="inlineStr"/>
+      <c r="W247" s="6" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
@@ -20877,39 +21293,40 @@
       <c r="K248" s="6" t="inlineStr"/>
       <c r="L248" s="6" t="inlineStr"/>
       <c r="M248" s="6" t="inlineStr"/>
-      <c r="N248" s="6" t="inlineStr">
+      <c r="N248" s="6" t="inlineStr"/>
+      <c r="O248" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O248" s="6" t="inlineStr">
+      <c r="P248" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P248" s="6" t="inlineStr">
+      <c r="Q248" s="6" t="inlineStr">
         <is>
           <t>PER ISRAELI-CONTENT RULE: audit her collaborations/guests/positive mentions to surface non-Israeli allies; that graph is the real yield.</t>
         </is>
       </c>
-      <c r="Q248" s="6" t="inlineStr"/>
-      <c r="R248" s="6" t="inlineStr">
+      <c r="R248" s="6" t="inlineStr"/>
+      <c r="S248" s="6" t="inlineStr">
         <is>
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="S248" s="6" t="inlineStr"/>
-      <c r="T248" s="6" t="inlineStr">
+      <c r="T248" s="6" t="inlineStr"/>
+      <c r="U248" s="6" t="inlineStr">
         <is>
           <t>Israeli</t>
         </is>
       </c>
-      <c r="U248" s="6" t="inlineStr">
+      <c r="V248" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V248" s="6" t="inlineStr"/>
+      <c r="W248" s="6" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -20965,35 +21382,36 @@
       <c r="K249" s="6" t="inlineStr"/>
       <c r="L249" s="6" t="inlineStr"/>
       <c r="M249" s="6" t="inlineStr"/>
-      <c r="N249" s="6" t="inlineStr">
+      <c r="N249" s="6" t="inlineStr"/>
+      <c r="O249" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O249" s="6" t="inlineStr">
+      <c r="P249" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P249" s="6" t="inlineStr">
+      <c r="Q249" s="6" t="inlineStr">
         <is>
           <t>VERIFY IDENTITY: could not resolve the channel ID to a named creator. Andy to confirm who this is and the nationality.</t>
         </is>
       </c>
-      <c r="Q249" s="6" t="inlineStr"/>
       <c r="R249" s="6" t="inlineStr"/>
       <c r="S249" s="6" t="inlineStr"/>
-      <c r="T249" s="6" t="inlineStr">
+      <c r="T249" s="6" t="inlineStr"/>
+      <c r="U249" s="6" t="inlineStr">
         <is>
           <t>Non-American (per Andy)</t>
         </is>
       </c>
-      <c r="U249" s="6" t="inlineStr">
+      <c r="V249" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V249" s="6" t="inlineStr"/>
+      <c r="W249" s="6" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
@@ -21049,35 +21467,36 @@
       <c r="K250" s="6" t="inlineStr"/>
       <c r="L250" s="6" t="inlineStr"/>
       <c r="M250" s="6" t="inlineStr"/>
-      <c r="N250" s="6" t="inlineStr">
+      <c r="N250" s="6" t="inlineStr"/>
+      <c r="O250" s="6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="O250" s="6" t="inlineStr">
+      <c r="P250" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P250" s="6" t="inlineStr">
+      <c r="Q250" s="6" t="inlineStr">
         <is>
           <t>VERIFY: confirm identity, nationality, platform size, and Israel-specific record; the cited post is about Yazidi women, not Israel directly.</t>
         </is>
       </c>
-      <c r="Q250" s="6" t="inlineStr"/>
       <c r="R250" s="6" t="inlineStr"/>
       <c r="S250" s="6" t="inlineStr"/>
-      <c r="T250" s="6" t="inlineStr">
+      <c r="T250" s="6" t="inlineStr"/>
+      <c r="U250" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U250" s="6" t="inlineStr">
+      <c r="V250" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V250" s="6" t="inlineStr"/>
+      <c r="W250" s="6" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -21129,35 +21548,36 @@
       <c r="K251" s="6" t="inlineStr"/>
       <c r="L251" s="6" t="inlineStr"/>
       <c r="M251" s="6" t="inlineStr"/>
-      <c r="N251" s="6" t="inlineStr">
+      <c r="N251" s="6" t="inlineStr"/>
+      <c r="O251" s="6" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O251" s="6" t="inlineStr">
+      <c r="P251" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P251" s="6" t="inlineStr">
+      <c r="Q251" s="6" t="inlineStr">
         <is>
           <t>HIGH-YIELD NODE: enumerate the Jewish business leaders he showcases and add each to the Business/B2B network per the new B2B inclusion criteria. Verify his own details (nationality, platform, reach).</t>
         </is>
       </c>
-      <c r="Q251" s="6" t="inlineStr"/>
       <c r="R251" s="6" t="inlineStr"/>
       <c r="S251" s="6" t="inlineStr"/>
-      <c r="T251" s="6" t="inlineStr">
+      <c r="T251" s="6" t="inlineStr"/>
+      <c r="U251" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U251" s="6" t="inlineStr">
+      <c r="V251" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V251" s="6" t="inlineStr"/>
+      <c r="W251" s="6" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -21209,35 +21629,36 @@
       <c r="K252" s="6" t="inlineStr"/>
       <c r="L252" s="6" t="inlineStr"/>
       <c r="M252" s="6" t="inlineStr"/>
-      <c r="N252" s="6" t="inlineStr">
+      <c r="N252" s="6" t="inlineStr"/>
+      <c r="O252" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O252" s="6" t="inlineStr">
+      <c r="P252" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P252" s="6" t="inlineStr"/>
       <c r="Q252" s="6" t="inlineStr"/>
       <c r="R252" s="6" t="inlineStr"/>
-      <c r="S252" s="6" t="inlineStr">
+      <c r="S252" s="6" t="inlineStr"/>
+      <c r="T252" s="6" t="inlineStr">
         <is>
           <t>Molly O'Shea</t>
         </is>
       </c>
-      <c r="T252" s="6" t="inlineStr">
+      <c r="U252" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U252" s="6" t="inlineStr">
+      <c r="V252" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V252" s="6" t="inlineStr"/>
+      <c r="W252" s="6" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -21293,35 +21714,36 @@
       <c r="K253" s="6" t="inlineStr"/>
       <c r="L253" s="6" t="inlineStr"/>
       <c r="M253" s="6" t="inlineStr"/>
-      <c r="N253" s="6" t="inlineStr">
+      <c r="N253" s="6" t="inlineStr"/>
+      <c r="O253" s="6" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="O253" s="6" t="inlineStr">
+      <c r="P253" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P253" s="6" t="inlineStr">
+      <c r="Q253" s="6" t="inlineStr">
         <is>
           <t>VERIFY: the cited evidence post is in Hebrew and I could not read/confirm it. Andy to summarize what it establishes.</t>
         </is>
       </c>
-      <c r="Q253" s="6" t="inlineStr"/>
       <c r="R253" s="6" t="inlineStr"/>
       <c r="S253" s="6" t="inlineStr"/>
-      <c r="T253" s="6" t="inlineStr">
+      <c r="T253" s="6" t="inlineStr"/>
+      <c r="U253" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U253" s="6" t="inlineStr">
+      <c r="V253" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V253" s="6" t="inlineStr"/>
+      <c r="W253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
@@ -21377,39 +21799,40 @@
       <c r="K254" s="6" t="inlineStr"/>
       <c r="L254" s="6" t="inlineStr"/>
       <c r="M254" s="6" t="inlineStr"/>
-      <c r="N254" s="6" t="inlineStr">
+      <c r="N254" s="6" t="inlineStr"/>
+      <c r="O254" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O254" s="6" t="inlineStr">
+      <c r="P254" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P254" s="6" t="inlineStr">
+      <c r="Q254" s="6" t="inlineStr">
         <is>
           <t>Associational only -- no personal stance found. Audit more of her interview roster; she is a useful yield node for Jewish/Israeli founders.</t>
         </is>
       </c>
-      <c r="Q254" s="6" t="inlineStr"/>
       <c r="R254" s="6" t="inlineStr"/>
-      <c r="S254" s="6" t="inlineStr">
+      <c r="S254" s="6" t="inlineStr"/>
+      <c r="T254" s="6" t="inlineStr">
         <is>
           <t>Alex Karp, Mark Pincus, Art Levin, Israel Slodowitz</t>
         </is>
       </c>
-      <c r="T254" s="6" t="inlineStr">
+      <c r="U254" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U254" s="6" t="inlineStr">
+      <c r="V254" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V254" s="6" t="inlineStr"/>
+      <c r="W254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -21461,39 +21884,40 @@
       <c r="K255" s="6" t="inlineStr"/>
       <c r="L255" s="6" t="inlineStr"/>
       <c r="M255" s="6" t="inlineStr"/>
-      <c r="N255" s="6" t="inlineStr">
+      <c r="N255" s="6" t="inlineStr"/>
+      <c r="O255" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O255" s="6" t="inlineStr">
+      <c r="P255" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P255" s="6" t="inlineStr">
+      <c r="Q255" s="6" t="inlineStr">
         <is>
           <t>Verify exact role at Brex and the tefillin incident source.</t>
         </is>
       </c>
-      <c r="Q255" s="6" t="inlineStr"/>
       <c r="R255" s="6" t="inlineStr"/>
-      <c r="S255" s="6" t="inlineStr">
+      <c r="S255" s="6" t="inlineStr"/>
+      <c r="T255" s="6" t="inlineStr">
         <is>
           <t>Molly O'Shea, Brex</t>
         </is>
       </c>
-      <c r="T255" s="6" t="inlineStr">
+      <c r="U255" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U255" s="6" t="inlineStr">
+      <c r="V255" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V255" s="6" t="inlineStr"/>
+      <c r="W255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -21545,39 +21969,40 @@
       <c r="K256" s="6" t="inlineStr"/>
       <c r="L256" s="6" t="inlineStr"/>
       <c r="M256" s="6" t="inlineStr"/>
-      <c r="N256" s="6" t="inlineStr">
+      <c r="N256" s="6" t="inlineStr"/>
+      <c r="O256" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O256" s="6" t="inlineStr">
+      <c r="P256" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P256" s="6" t="inlineStr">
+      <c r="Q256" s="6" t="inlineStr">
         <is>
           <t>Verify company, role, nationality.</t>
         </is>
       </c>
-      <c r="Q256" s="6" t="inlineStr"/>
       <c r="R256" s="6" t="inlineStr"/>
-      <c r="S256" s="6" t="inlineStr">
+      <c r="S256" s="6" t="inlineStr"/>
+      <c r="T256" s="6" t="inlineStr">
         <is>
           <t>Molly O'Shea</t>
         </is>
       </c>
-      <c r="T256" s="6" t="inlineStr">
+      <c r="U256" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U256" s="6" t="inlineStr">
+      <c r="V256" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V256" s="6" t="inlineStr"/>
+      <c r="W256" s="6" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -21633,39 +22058,40 @@
       <c r="K257" s="6" t="inlineStr"/>
       <c r="L257" s="6" t="inlineStr"/>
       <c r="M257" s="6" t="inlineStr"/>
-      <c r="N257" s="6" t="inlineStr">
+      <c r="N257" s="6" t="inlineStr"/>
+      <c r="O257" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O257" s="6" t="inlineStr">
+      <c r="P257" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P257" s="6" t="inlineStr">
+      <c r="Q257" s="6" t="inlineStr">
         <is>
           <t>Warm, already-confirmed lead -- prioritize for the DC Sprint. Map Station DC's member companies as B2B candidates.</t>
         </is>
       </c>
-      <c r="Q257" s="6" t="inlineStr"/>
       <c r="R257" s="6" t="inlineStr"/>
-      <c r="S257" s="6" t="inlineStr">
+      <c r="S257" s="6" t="inlineStr"/>
+      <c r="T257" s="6" t="inlineStr">
         <is>
           <t>Station DC, Capital Factory, Joshua Baer</t>
         </is>
       </c>
-      <c r="T257" s="6" t="inlineStr">
+      <c r="U257" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U257" s="6" t="inlineStr">
+      <c r="V257" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V257" s="6" t="inlineStr"/>
+      <c r="W257" s="6" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
@@ -21717,35 +22143,36 @@
       <c r="K258" s="6" t="inlineStr"/>
       <c r="L258" s="6" t="inlineStr"/>
       <c r="M258" s="6" t="inlineStr"/>
-      <c r="N258" s="6" t="inlineStr">
+      <c r="N258" s="6" t="inlineStr"/>
+      <c r="O258" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O258" s="6" t="inlineStr">
+      <c r="P258" s="6" t="inlineStr">
         <is>
           <t>Political</t>
         </is>
       </c>
-      <c r="P258" s="6" t="inlineStr">
+      <c r="Q258" s="6" t="inlineStr">
         <is>
           <t>Confirm the July 2026 Israel trip details and any resulting change in his public position/voting.</t>
         </is>
       </c>
-      <c r="Q258" s="6" t="inlineStr"/>
       <c r="R258" s="6" t="inlineStr"/>
       <c r="S258" s="6" t="inlineStr"/>
-      <c r="T258" s="6" t="inlineStr">
+      <c r="T258" s="6" t="inlineStr"/>
+      <c r="U258" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U258" s="6" t="inlineStr">
+      <c r="V258" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V258" s="6" t="inlineStr"/>
+      <c r="W258" s="6" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -21797,35 +22224,36 @@
       <c r="K259" s="6" t="inlineStr"/>
       <c r="L259" s="6" t="inlineStr"/>
       <c r="M259" s="6" t="inlineStr"/>
-      <c r="N259" s="6" t="inlineStr">
+      <c r="N259" s="6" t="inlineStr"/>
+      <c r="O259" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O259" s="6" t="inlineStr">
+      <c r="P259" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P259" s="6" t="inlineStr">
+      <c r="Q259" s="6" t="inlineStr">
         <is>
           <t>Assess whether his position is performative (movable) or convicted. If performative, he is a persuasion target rather than a pure adversary -- a rare high-value flip if achievable.</t>
         </is>
       </c>
-      <c r="Q259" s="6" t="inlineStr"/>
       <c r="R259" s="6" t="inlineStr"/>
       <c r="S259" s="6" t="inlineStr"/>
-      <c r="T259" s="6" t="inlineStr">
+      <c r="T259" s="6" t="inlineStr"/>
+      <c r="U259" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U259" s="6" t="inlineStr">
+      <c r="V259" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V259" s="6" t="inlineStr"/>
+      <c r="W259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -21881,39 +22309,40 @@
       <c r="K260" s="6" t="inlineStr"/>
       <c r="L260" s="6" t="inlineStr"/>
       <c r="M260" s="6" t="inlineStr"/>
-      <c r="N260" s="6" t="inlineStr">
+      <c r="N260" s="6" t="inlineStr"/>
+      <c r="O260" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O260" s="6" t="inlineStr">
+      <c r="P260" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P260" s="6" t="inlineStr">
+      <c r="Q260" s="6" t="inlineStr">
         <is>
           <t>Verify his religion/heritage claim and any explicit Israel record. All-In co-hosts (Sacks, Palihapitiya, Friedberg) are worth evaluating separately -- David Sacks especially (Jewish, pro-Israel, in government).</t>
         </is>
       </c>
-      <c r="Q260" s="6" t="inlineStr"/>
       <c r="R260" s="6" t="inlineStr"/>
-      <c r="S260" s="6" t="inlineStr">
+      <c r="S260" s="6" t="inlineStr"/>
+      <c r="T260" s="6" t="inlineStr">
         <is>
           <t>Joshua Baer, Capital Factory, LAUNCH</t>
         </is>
       </c>
-      <c r="T260" s="6" t="inlineStr">
+      <c r="U260" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U260" s="6" t="inlineStr">
+      <c r="V260" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V260" s="6" t="inlineStr">
+      <c r="W260" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -21973,39 +22402,40 @@
       <c r="K261" s="6" t="inlineStr"/>
       <c r="L261" s="6" t="inlineStr"/>
       <c r="M261" s="6" t="inlineStr"/>
-      <c r="N261" s="6" t="inlineStr">
+      <c r="N261" s="6" t="inlineStr"/>
+      <c r="O261" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O261" s="6" t="inlineStr">
+      <c r="P261" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P261" s="6" t="inlineStr">
+      <c r="Q261" s="6" t="inlineStr">
         <is>
           <t>Verify Benchmark's Israel exposure and any Gurley Israel-specific record. Austin-based = Texas ecosystem relevance.</t>
         </is>
       </c>
-      <c r="Q261" s="6" t="inlineStr"/>
       <c r="R261" s="6" t="inlineStr"/>
-      <c r="S261" s="6" t="inlineStr">
+      <c r="S261" s="6" t="inlineStr"/>
+      <c r="T261" s="6" t="inlineStr">
         <is>
           <t>Joshua Baer, Capital Factory, Benchmark</t>
         </is>
       </c>
-      <c r="T261" s="6" t="inlineStr">
+      <c r="U261" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U261" s="6" t="inlineStr">
+      <c r="V261" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V261" s="6" t="inlineStr">
+      <c r="W261" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -22061,39 +22491,40 @@
       <c r="K262" s="6" t="inlineStr"/>
       <c r="L262" s="6" t="inlineStr"/>
       <c r="M262" s="6" t="inlineStr"/>
-      <c r="N262" s="6" t="inlineStr">
+      <c r="N262" s="6" t="inlineStr"/>
+      <c r="O262" s="6" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O262" s="6" t="inlineStr">
+      <c r="P262" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="P262" s="6" t="inlineStr">
+      <c r="Q262" s="6" t="inlineStr">
         <is>
           <t>HIGH-YIELD: Austin Technology Council membership is a bounded roster of Texas tech companies -- direct B2B yield for the Texas ecosystem leg.</t>
         </is>
       </c>
-      <c r="Q262" s="6" t="inlineStr"/>
       <c r="R262" s="6" t="inlineStr"/>
-      <c r="S262" s="6" t="inlineStr">
+      <c r="S262" s="6" t="inlineStr"/>
+      <c r="T262" s="6" t="inlineStr">
         <is>
           <t>Joshua Baer, Austin Technology Council, Capital Factory</t>
         </is>
       </c>
-      <c r="T262" s="6" t="inlineStr">
+      <c r="U262" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U262" s="6" t="inlineStr">
+      <c r="V262" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V262" s="6" t="inlineStr">
+      <c r="W262" s="6" t="inlineStr">
         <is>
           <t>US / Austin metro</t>
         </is>
@@ -22149,39 +22580,40 @@
       <c r="K263" s="6" t="inlineStr"/>
       <c r="L263" s="6" t="inlineStr"/>
       <c r="M263" s="6" t="inlineStr"/>
-      <c r="N263" s="6" t="inlineStr">
+      <c r="N263" s="6" t="inlineStr"/>
+      <c r="O263" s="6" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O263" s="6" t="inlineStr">
+      <c r="P263" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P263" s="6" t="inlineStr">
+      <c r="Q263" s="6" t="inlineStr">
         <is>
           <t>Weigh the ADL's friction with the right before positioning him in evangelical-coalition work; he is an asset with center-left/institutional audiences.</t>
         </is>
       </c>
-      <c r="Q263" s="6" t="inlineStr"/>
       <c r="R263" s="6" t="inlineStr"/>
-      <c r="S263" s="6" t="inlineStr">
+      <c r="S263" s="6" t="inlineStr"/>
+      <c r="T263" s="6" t="inlineStr">
         <is>
           <t>Joshua Baer, Anti-Defamation League (ADL)</t>
         </is>
       </c>
-      <c r="T263" s="6" t="inlineStr">
+      <c r="U263" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U263" s="6" t="inlineStr">
+      <c r="V263" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V263" s="6" t="inlineStr">
+      <c r="W263" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -22237,39 +22669,40 @@
       <c r="K264" s="6" t="inlineStr"/>
       <c r="L264" s="6" t="inlineStr"/>
       <c r="M264" s="6" t="inlineStr"/>
-      <c r="N264" s="6" t="inlineStr">
+      <c r="N264" s="6" t="inlineStr"/>
+      <c r="O264" s="6" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="O264" s="6" t="inlineStr">
+      <c r="P264" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P264" s="6" t="inlineStr">
+      <c r="Q264" s="6" t="inlineStr">
         <is>
           <t>This database exists to serve his strategy -- keep his stated priorities (podcast gap, integration+coordination, education, and the global strategic-city database) as the north star for what gets added.</t>
         </is>
       </c>
-      <c r="Q264" s="6" t="inlineStr"/>
       <c r="R264" s="6" t="inlineStr"/>
-      <c r="S264" s="6" t="inlineStr">
+      <c r="S264" s="6" t="inlineStr"/>
+      <c r="T264" s="6" t="inlineStr">
         <is>
           <t>Builders for Tomorrow (BFT), Evangelical Foundation, Congress of Christian Leaders, Samuel Rodriguez, Pepperdine University, Liberty University, Israel Allies Foundation (IAF)</t>
         </is>
       </c>
-      <c r="T264" s="6" t="inlineStr">
+      <c r="U264" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U264" s="6" t="inlineStr">
+      <c r="V264" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V264" s="6" t="inlineStr">
+      <c r="W264" s="6" t="inlineStr">
         <is>
           <t>US + global</t>
         </is>
@@ -22325,39 +22758,40 @@
       <c r="K265" s="6" t="inlineStr"/>
       <c r="L265" s="6" t="inlineStr"/>
       <c r="M265" s="6" t="inlineStr"/>
-      <c r="N265" s="6" t="inlineStr">
+      <c r="N265" s="6" t="inlineStr"/>
+      <c r="O265" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O265" s="6" t="inlineStr">
+      <c r="P265" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P265" s="6" t="inlineStr">
+      <c r="Q265" s="6" t="inlineStr">
         <is>
           <t>Highest-priority warm intro: Johnnie's own long-standing co-founder. Maps directly onto the Latin America leg of Johnnie's strategic-cities vision (Sao Paulo, Santiago). Verify current NHCLC role and Israel-specific record.</t>
         </is>
       </c>
-      <c r="Q265" s="6" t="inlineStr"/>
       <c r="R265" s="6" t="inlineStr"/>
-      <c r="S265" s="6" t="inlineStr">
+      <c r="S265" s="6" t="inlineStr"/>
+      <c r="T265" s="6" t="inlineStr">
         <is>
           <t>Johnnie Moore, Congress of Christian Leaders, Evangelical Foundation</t>
         </is>
       </c>
-      <c r="T265" s="6" t="inlineStr">
+      <c r="U265" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U265" s="6" t="inlineStr">
+      <c r="V265" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V265" s="6" t="inlineStr">
+      <c r="W265" s="6" t="inlineStr">
         <is>
           <t>US Latino evangelical + Latin America</t>
         </is>
@@ -22413,39 +22847,40 @@
       <c r="K266" s="6" t="inlineStr"/>
       <c r="L266" s="6" t="inlineStr"/>
       <c r="M266" s="6" t="inlineStr"/>
-      <c r="N266" s="6" t="inlineStr">
+      <c r="N266" s="6" t="inlineStr"/>
+      <c r="O266" s="6" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="O266" s="6" t="inlineStr">
+      <c r="P266" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P266" s="6" t="inlineStr">
+      <c r="Q266" s="6" t="inlineStr">
         <is>
           <t>VERIFY Israel stance -- no record found; he is a LEAD from Dana's archetype, not a confirmed ally. If he checks out he is a high-value leg-1 (podcast/comms) target: young, articulate, celebrity reach, already adjacent to a tracked figure.</t>
         </is>
       </c>
-      <c r="Q266" s="6" t="inlineStr"/>
       <c r="R266" s="6" t="inlineStr"/>
-      <c r="S266" s="6" t="inlineStr">
+      <c r="S266" s="6" t="inlineStr"/>
+      <c r="T266" s="6" t="inlineStr">
         <is>
           <t>Justin Bieber, Churchome</t>
         </is>
       </c>
-      <c r="T266" s="6" t="inlineStr">
+      <c r="U266" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U266" s="6" t="inlineStr">
+      <c r="V266" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="V266" s="6" t="inlineStr">
+      <c r="W266" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
@@ -22505,39 +22940,40 @@
       <c r="K267" s="6" t="inlineStr"/>
       <c r="L267" s="6" t="inlineStr"/>
       <c r="M267" s="6" t="inlineStr"/>
-      <c r="N267" s="6" t="inlineStr">
+      <c r="N267" s="6" t="inlineStr"/>
+      <c r="O267" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O267" s="6" t="inlineStr">
+      <c r="P267" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P267" s="6" t="inlineStr">
+      <c r="Q267" s="6" t="inlineStr">
         <is>
           <t>Andy called this a 'HUGE add' -- confirmed he is preeminent in his field. But decide deliberately WHERE he fits: superb for Jewish-community defense, risky as an evangelical-alliance-facing figure. Verify current subscriber counts.</t>
         </is>
       </c>
-      <c r="Q267" s="6" t="inlineStr"/>
-      <c r="R267" s="6" t="inlineStr">
+      <c r="R267" s="6" t="inlineStr"/>
+      <c r="S267" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S267" s="6" t="inlineStr"/>
-      <c r="T267" s="6" t="inlineStr">
+      <c r="T267" s="6" t="inlineStr"/>
+      <c r="U267" s="6" t="inlineStr">
         <is>
           <t>American/Israeli</t>
         </is>
       </c>
-      <c r="U267" s="6" t="inlineStr">
+      <c r="V267" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V267" s="6" t="inlineStr"/>
+      <c r="W267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
@@ -22593,39 +23029,40 @@
       <c r="K268" s="6" t="inlineStr"/>
       <c r="L268" s="6" t="inlineStr"/>
       <c r="M268" s="6" t="inlineStr"/>
-      <c r="N268" s="6" t="inlineStr">
+      <c r="N268" s="6" t="inlineStr"/>
+      <c r="O268" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O268" s="6" t="inlineStr">
+      <c r="P268" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P268" s="6" t="inlineStr">
+      <c r="Q268" s="6" t="inlineStr">
         <is>
           <t>Andy: this is the same category as Tommy Robinson/David Wood -- a documented-conduct exclusion independent of his Israel stance, not a political-correctness call. Your call to override, but I would advise strongly against any association.</t>
         </is>
       </c>
-      <c r="Q268" s="6" t="inlineStr"/>
-      <c r="R268" s="6" t="inlineStr">
+      <c r="R268" s="6" t="inlineStr"/>
+      <c r="S268" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S268" s="6" t="inlineStr"/>
-      <c r="T268" s="6" t="inlineStr">
+      <c r="T268" s="6" t="inlineStr"/>
+      <c r="U268" s="6" t="inlineStr">
         <is>
           <t>Israeli-American</t>
         </is>
       </c>
-      <c r="U268" s="6" t="inlineStr">
+      <c r="V268" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V268" s="6" t="inlineStr"/>
+      <c r="W268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
@@ -22681,35 +23118,36 @@
       <c r="K269" s="6" t="inlineStr"/>
       <c r="L269" s="6" t="inlineStr"/>
       <c r="M269" s="6" t="inlineStr"/>
-      <c r="N269" s="6" t="inlineStr">
+      <c r="N269" s="6" t="inlineStr"/>
+      <c r="O269" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O269" s="6" t="inlineStr">
+      <c r="P269" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P269" s="6" t="inlineStr">
+      <c r="Q269" s="6" t="inlineStr">
         <is>
           <t>NOTE the theological distinction matters strategically: replacement theology is the root of the drift Johnnie is fighting. Verify the specific Israel statements vs. the supersessionist framework before any engagement.</t>
         </is>
       </c>
-      <c r="Q269" s="6" t="inlineStr"/>
       <c r="R269" s="6" t="inlineStr"/>
       <c r="S269" s="6" t="inlineStr"/>
-      <c r="T269" s="6" t="inlineStr">
+      <c r="T269" s="6" t="inlineStr"/>
+      <c r="U269" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U269" s="6" t="inlineStr">
+      <c r="V269" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V269" s="6" t="inlineStr"/>
+      <c r="W269" s="6" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
@@ -22764,12 +23202,12 @@
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t>No podcast (TARGET)</t>
+          <t>HAS PODCAST -- The Nick Shirley Show (83 eps, latest 2026-06-24)</t>
         </is>
       </c>
       <c r="L270" s="6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Not a podcast target (already hosting)</t>
         </is>
       </c>
       <c r="M270" s="6" t="inlineStr">
@@ -22779,41 +23217,46 @@
       </c>
       <c r="N270" s="6" t="inlineStr">
         <is>
+          <t>VERIFIED VIA APPLE PODCASTS 16 Jul 2026 -- the previous tag 'No podcast (TARGET)' was FALSE. Already hosts 'The Nick Shirley Show': 83 episodes, latest 2026-06-24. This person is NOT a Johnnie leg-1 target; they are already in long-form audio. Retagged.</t>
+        </is>
+      </c>
+      <c r="O270" s="6" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O270" s="6" t="inlineStr">
+      <c r="P270" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P270" s="6" t="inlineStr">
+      <c r="Q270" s="6" t="inlineStr">
         <is>
           <t>NO Israel-specific record found -- filed pro on team-alignment, needs verification. Two angles: (a) his LDS/Santiago background maps onto Johnnie's Latin America strategic-city vision; (b) Vance praised him -- check against the Rubio/Vance criterion (being praised BY Vance is not the same as preferring Vance).</t>
         </is>
       </c>
-      <c r="Q270" s="6" t="inlineStr"/>
-      <c r="R270" s="6" t="inlineStr">
+      <c r="R270" s="6" t="inlineStr"/>
+      <c r="S270" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S270" s="6" t="inlineStr">
+      <c r="T270" s="6" t="inlineStr">
         <is>
           <t>Glenn Beck, Kash Patel</t>
         </is>
       </c>
-      <c r="T270" s="6" t="inlineStr">
+      <c r="U270" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U270" s="6" t="inlineStr">
+      <c r="V270" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V270" s="6" t="inlineStr">
+      <c r="W270" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -22873,39 +23316,40 @@
       <c r="K271" s="6" t="inlineStr"/>
       <c r="L271" s="6" t="inlineStr"/>
       <c r="M271" s="6" t="inlineStr"/>
-      <c r="N271" s="6" t="inlineStr">
+      <c r="N271" s="6" t="inlineStr"/>
+      <c r="O271" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O271" s="6" t="inlineStr">
+      <c r="P271" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P271" s="6" t="inlineStr">
+      <c r="Q271" s="6" t="inlineStr">
         <is>
           <t>Verify the specific Israel evidence in the submitted clip (youtube.com/watch?v=gKFAtGWFZ7I) -- I cannot watch video.</t>
         </is>
       </c>
-      <c r="Q271" s="6" t="inlineStr"/>
-      <c r="R271" s="6" t="inlineStr">
+      <c r="R271" s="6" t="inlineStr"/>
+      <c r="S271" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S271" s="6" t="inlineStr"/>
-      <c r="T271" s="6" t="inlineStr">
+      <c r="T271" s="6" t="inlineStr"/>
+      <c r="U271" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U271" s="6" t="inlineStr">
+      <c r="V271" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V271" s="6" t="inlineStr"/>
+      <c r="W271" s="6" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
@@ -22961,39 +23405,40 @@
       <c r="K272" s="6" t="inlineStr"/>
       <c r="L272" s="6" t="inlineStr"/>
       <c r="M272" s="6" t="inlineStr"/>
-      <c r="N272" s="6" t="inlineStr">
+      <c r="N272" s="6" t="inlineStr"/>
+      <c r="O272" s="6" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="O272" s="6" t="inlineStr">
+      <c r="P272" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P272" s="6" t="inlineStr"/>
       <c r="Q272" s="6" t="inlineStr"/>
-      <c r="R272" s="6" t="inlineStr">
+      <c r="R272" s="6" t="inlineStr"/>
+      <c r="S272" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S272" s="6" t="inlineStr">
+      <c r="T272" s="6" t="inlineStr">
         <is>
           <t>The Israel Guys, HaYovel, Joshua Waller</t>
         </is>
       </c>
-      <c r="T272" s="6" t="inlineStr">
+      <c r="U272" s="6" t="inlineStr">
         <is>
           <t>American (living in Israel)</t>
         </is>
       </c>
-      <c r="U272" s="6" t="inlineStr">
+      <c r="V272" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V272" s="6" t="inlineStr"/>
+      <c r="W272" s="6" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
@@ -23049,39 +23494,40 @@
       <c r="K273" s="6" t="inlineStr"/>
       <c r="L273" s="6" t="inlineStr"/>
       <c r="M273" s="6" t="inlineStr"/>
-      <c r="N273" s="6" t="inlineStr">
+      <c r="N273" s="6" t="inlineStr"/>
+      <c r="O273" s="6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O273" s="6" t="inlineStr">
+      <c r="P273" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P273" s="6" t="inlineStr">
+      <c r="Q273" s="6" t="inlineStr">
         <is>
           <t>HIGHEST-STAKES RELATIONSHIP in the youth-movement leg: whoever influences TPUSA's post-Kirk direction shapes whether Gen Z conservatism stays pro-Israel. Verify her own public Israel statements. Note Andy's interview reference to 'horrific ways his widow has been treated' -- approach with care and respect, not as a transaction.</t>
         </is>
       </c>
-      <c r="Q273" s="6" t="inlineStr"/>
       <c r="R273" s="6" t="inlineStr"/>
-      <c r="S273" s="6" t="inlineStr">
+      <c r="S273" s="6" t="inlineStr"/>
+      <c r="T273" s="6" t="inlineStr">
         <is>
           <t>Turning Point USA (TPUSA), Andrew Kolvet</t>
         </is>
       </c>
-      <c r="T273" s="6" t="inlineStr">
+      <c r="U273" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U273" s="6" t="inlineStr">
+      <c r="V273" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V273" s="6" t="inlineStr"/>
+      <c r="W273" s="6" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
@@ -23137,43 +23583,44 @@
       <c r="K274" s="6" t="inlineStr"/>
       <c r="L274" s="6" t="inlineStr"/>
       <c r="M274" s="6" t="inlineStr"/>
-      <c r="N274" s="6" t="inlineStr">
+      <c r="N274" s="6" t="inlineStr"/>
+      <c r="O274" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O274" s="6" t="inlineStr">
+      <c r="P274" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P274" s="6" t="inlineStr">
+      <c r="Q274" s="6" t="inlineStr">
         <is>
           <t>VERIFY the Strickland/America-250 claim -- I could not independently confirm it in this pass. If true it is strong; if not, this entry should drop to neutral.</t>
         </is>
       </c>
-      <c r="Q274" s="6" t="inlineStr">
+      <c r="R274" s="6" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="R274" s="6" t="inlineStr"/>
-      <c r="S274" s="6" t="inlineStr">
+      <c r="S274" s="6" t="inlineStr"/>
+      <c r="T274" s="6" t="inlineStr">
         <is>
           <t>Sean Strickland</t>
         </is>
       </c>
-      <c r="T274" s="6" t="inlineStr">
+      <c r="U274" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U274" s="6" t="inlineStr">
+      <c r="V274" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V274" s="6" t="inlineStr"/>
+      <c r="W274" s="6" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -23229,35 +23676,36 @@
       <c r="K275" s="6" t="inlineStr"/>
       <c r="L275" s="6" t="inlineStr"/>
       <c r="M275" s="6" t="inlineStr"/>
-      <c r="N275" s="6" t="inlineStr">
+      <c r="N275" s="6" t="inlineStr"/>
+      <c r="O275" s="6" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O275" s="6" t="inlineStr">
+      <c r="P275" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P275" s="6" t="inlineStr"/>
-      <c r="Q275" s="6" t="inlineStr">
+      <c r="Q275" s="6" t="inlineStr"/>
+      <c r="R275" s="6" t="inlineStr">
         <is>
           <t>TV &amp; Media</t>
         </is>
       </c>
-      <c r="R275" s="6" t="inlineStr"/>
       <c r="S275" s="6" t="inlineStr"/>
-      <c r="T275" s="6" t="inlineStr">
+      <c r="T275" s="6" t="inlineStr"/>
+      <c r="U275" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U275" s="6" t="inlineStr">
+      <c r="V275" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V275" s="6" t="inlineStr"/>
+      <c r="W275" s="6" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
@@ -23313,39 +23761,40 @@
       <c r="K276" s="6" t="inlineStr"/>
       <c r="L276" s="6" t="inlineStr"/>
       <c r="M276" s="6" t="inlineStr"/>
-      <c r="N276" s="6" t="inlineStr">
+      <c r="N276" s="6" t="inlineStr"/>
+      <c r="O276" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O276" s="6" t="inlineStr">
+      <c r="P276" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P276" s="6" t="inlineStr">
+      <c r="Q276" s="6" t="inlineStr">
         <is>
           <t>Verify explicit Israel statements -- filed pro on team-alignment.</t>
         </is>
       </c>
-      <c r="Q276" s="6" t="inlineStr">
+      <c r="R276" s="6" t="inlineStr">
         <is>
           <t>TV &amp; Media</t>
         </is>
       </c>
-      <c r="R276" s="6" t="inlineStr"/>
       <c r="S276" s="6" t="inlineStr"/>
-      <c r="T276" s="6" t="inlineStr">
+      <c r="T276" s="6" t="inlineStr"/>
+      <c r="U276" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U276" s="6" t="inlineStr">
+      <c r="V276" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V276" s="6" t="inlineStr"/>
+      <c r="W276" s="6" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -23401,39 +23850,40 @@
       <c r="K277" s="6" t="inlineStr"/>
       <c r="L277" s="6" t="inlineStr"/>
       <c r="M277" s="6" t="inlineStr"/>
-      <c r="N277" s="6" t="inlineStr">
+      <c r="N277" s="6" t="inlineStr"/>
+      <c r="O277" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O277" s="6" t="inlineStr">
+      <c r="P277" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P277" s="6" t="inlineStr">
+      <c r="Q277" s="6" t="inlineStr">
         <is>
           <t>ALLY-EXPANSION TARGET per Andy: map her comedic circle for younger, NON-Jewish comedians -- that cohort is the actual prize (scarce profile + Johnnie's humor thesis).</t>
         </is>
       </c>
-      <c r="Q277" s="6" t="inlineStr">
+      <c r="R277" s="6" t="inlineStr">
         <is>
           <t>TV &amp; Media</t>
         </is>
       </c>
-      <c r="R277" s="6" t="inlineStr"/>
       <c r="S277" s="6" t="inlineStr"/>
-      <c r="T277" s="6" t="inlineStr">
+      <c r="T277" s="6" t="inlineStr"/>
+      <c r="U277" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U277" s="6" t="inlineStr">
+      <c r="V277" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V277" s="6" t="inlineStr"/>
+      <c r="W277" s="6" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
@@ -23489,35 +23939,36 @@
       <c r="K278" s="6" t="inlineStr"/>
       <c r="L278" s="6" t="inlineStr"/>
       <c r="M278" s="6" t="inlineStr"/>
-      <c r="N278" s="6" t="inlineStr">
+      <c r="N278" s="6" t="inlineStr"/>
+      <c r="O278" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O278" s="6" t="inlineStr">
+      <c r="P278" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P278" s="6" t="inlineStr">
+      <c r="Q278" s="6" t="inlineStr">
         <is>
           <t>Verify explicit Israel record.</t>
         </is>
       </c>
-      <c r="Q278" s="6" t="inlineStr"/>
       <c r="R278" s="6" t="inlineStr"/>
       <c r="S278" s="6" t="inlineStr"/>
-      <c r="T278" s="6" t="inlineStr">
+      <c r="T278" s="6" t="inlineStr"/>
+      <c r="U278" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U278" s="6" t="inlineStr">
+      <c r="V278" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V278" s="6" t="inlineStr"/>
+      <c r="W278" s="6" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -23573,39 +24024,40 @@
       <c r="K279" s="6" t="inlineStr"/>
       <c r="L279" s="6" t="inlineStr"/>
       <c r="M279" s="6" t="inlineStr"/>
-      <c r="N279" s="6" t="inlineStr">
+      <c r="N279" s="6" t="inlineStr"/>
+      <c r="O279" s="6" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O279" s="6" t="inlineStr">
+      <c r="P279" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P279" s="6" t="inlineStr">
+      <c r="Q279" s="6" t="inlineStr">
         <is>
           <t>Verify the specific Israel angle -- the cited evidence (mediamatters.org) is about attacking Megyn Kelly, which is a proxy signal, not a direct Israel statement.</t>
         </is>
       </c>
-      <c r="Q279" s="6" t="inlineStr"/>
-      <c r="R279" s="6" t="inlineStr">
+      <c r="R279" s="6" t="inlineStr"/>
+      <c r="S279" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S279" s="6" t="inlineStr"/>
-      <c r="T279" s="6" t="inlineStr">
+      <c r="T279" s="6" t="inlineStr"/>
+      <c r="U279" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U279" s="6" t="inlineStr">
+      <c r="V279" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V279" s="6" t="inlineStr"/>
+      <c r="W279" s="6" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
@@ -23661,39 +24113,40 @@
       <c r="K280" s="6" t="inlineStr"/>
       <c r="L280" s="6" t="inlineStr"/>
       <c r="M280" s="6" t="inlineStr"/>
-      <c r="N280" s="6" t="inlineStr">
+      <c r="N280" s="6" t="inlineStr"/>
+      <c r="O280" s="6" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="O280" s="6" t="inlineStr">
+      <c r="P280" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P280" s="6" t="inlineStr">
+      <c r="Q280" s="6" t="inlineStr">
         <is>
           <t>Verify explicit Israel statements.</t>
         </is>
       </c>
-      <c r="Q280" s="6" t="inlineStr"/>
-      <c r="R280" s="6" t="inlineStr">
+      <c r="R280" s="6" t="inlineStr"/>
+      <c r="S280" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S280" s="6" t="inlineStr"/>
-      <c r="T280" s="6" t="inlineStr">
+      <c r="T280" s="6" t="inlineStr"/>
+      <c r="U280" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U280" s="6" t="inlineStr">
+      <c r="V280" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V280" s="6" t="inlineStr"/>
+      <c r="W280" s="6" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -23749,35 +24202,36 @@
       <c r="K281" s="6" t="inlineStr"/>
       <c r="L281" s="6" t="inlineStr"/>
       <c r="M281" s="6" t="inlineStr"/>
-      <c r="N281" s="6" t="inlineStr">
+      <c r="N281" s="6" t="inlineStr"/>
+      <c r="O281" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="O281" s="6" t="inlineStr">
+      <c r="P281" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P281" s="6" t="inlineStr">
+      <c r="Q281" s="6" t="inlineStr">
         <is>
           <t>VERIFY IDENTITY AND STANCE -- no confirmable record found. Andy to confirm why flagged.</t>
         </is>
       </c>
-      <c r="Q281" s="6" t="inlineStr"/>
       <c r="R281" s="6" t="inlineStr"/>
       <c r="S281" s="6" t="inlineStr"/>
-      <c r="T281" s="6" t="inlineStr">
+      <c r="T281" s="6" t="inlineStr"/>
+      <c r="U281" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U281" s="6" t="inlineStr">
+      <c r="V281" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V281" s="6" t="inlineStr"/>
+      <c r="W281" s="6" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
@@ -23833,39 +24287,40 @@
       <c r="K282" s="6" t="inlineStr"/>
       <c r="L282" s="6" t="inlineStr"/>
       <c r="M282" s="6" t="inlineStr"/>
-      <c r="N282" s="6" t="inlineStr">
+      <c r="N282" s="6" t="inlineStr"/>
+      <c r="O282" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O282" s="6" t="inlineStr">
+      <c r="P282" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P282" s="6" t="inlineStr">
+      <c r="Q282" s="6" t="inlineStr">
         <is>
           <t>Monitor: he is a bellwether for where the populist-right audience is drifting. Apply the Graham/Cruz-criticism test to recent episodes.</t>
         </is>
       </c>
-      <c r="Q282" s="6" t="inlineStr"/>
-      <c r="R282" s="6" t="inlineStr">
+      <c r="R282" s="6" t="inlineStr"/>
+      <c r="S282" s="6" t="inlineStr">
         <is>
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="S282" s="6" t="inlineStr"/>
-      <c r="T282" s="6" t="inlineStr">
+      <c r="T282" s="6" t="inlineStr"/>
+      <c r="U282" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U282" s="6" t="inlineStr">
+      <c r="V282" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V282" s="6" t="inlineStr"/>
+      <c r="W282" s="6" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
@@ -23921,35 +24376,36 @@
       <c r="K283" s="6" t="inlineStr"/>
       <c r="L283" s="6" t="inlineStr"/>
       <c r="M283" s="6" t="inlineStr"/>
-      <c r="N283" s="6" t="inlineStr">
+      <c r="N283" s="6" t="inlineStr"/>
+      <c r="O283" s="6" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O283" s="6" t="inlineStr">
+      <c r="P283" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P283" s="6" t="inlineStr">
+      <c r="Q283" s="6" t="inlineStr">
         <is>
           <t>Verify biography and current platform size.</t>
         </is>
       </c>
-      <c r="Q283" s="6" t="inlineStr"/>
       <c r="R283" s="6" t="inlineStr"/>
       <c r="S283" s="6" t="inlineStr"/>
-      <c r="T283" s="6" t="inlineStr">
+      <c r="T283" s="6" t="inlineStr"/>
+      <c r="U283" s="6" t="inlineStr">
         <is>
           <t>American (Lebanese background)</t>
         </is>
       </c>
-      <c r="U283" s="6" t="inlineStr">
+      <c r="V283" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V283" s="6" t="inlineStr"/>
+      <c r="W283" s="6" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
@@ -24005,39 +24461,40 @@
       <c r="K284" s="6" t="inlineStr"/>
       <c r="L284" s="6" t="inlineStr"/>
       <c r="M284" s="6" t="inlineStr"/>
-      <c r="N284" s="6" t="inlineStr">
+      <c r="N284" s="6" t="inlineStr"/>
+      <c r="O284" s="6" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="O284" s="6" t="inlineStr">
+      <c r="P284" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P284" s="6" t="inlineStr">
+      <c r="Q284" s="6" t="inlineStr">
         <is>
           <t>Verify platform size and the specific posts (X is not fetchable to me).</t>
         </is>
       </c>
-      <c r="Q284" s="6" t="inlineStr"/>
       <c r="R284" s="6" t="inlineStr"/>
-      <c r="S284" s="6" t="inlineStr">
+      <c r="S284" s="6" t="inlineStr"/>
+      <c r="T284" s="6" t="inlineStr">
         <is>
           <t>Sam Brown, Candace Owens</t>
         </is>
       </c>
-      <c r="T284" s="6" t="inlineStr">
+      <c r="U284" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U284" s="6" t="inlineStr">
+      <c r="V284" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V284" s="6" t="inlineStr"/>
+      <c r="W284" s="6" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
@@ -24093,35 +24550,36 @@
       <c r="K285" s="6" t="inlineStr"/>
       <c r="L285" s="6" t="inlineStr"/>
       <c r="M285" s="6" t="inlineStr"/>
-      <c r="N285" s="6" t="inlineStr">
+      <c r="N285" s="6" t="inlineStr"/>
+      <c r="O285" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="O285" s="6" t="inlineStr">
+      <c r="P285" s="6" t="inlineStr">
         <is>
           <t>Media/Influencer</t>
         </is>
       </c>
-      <c r="P285" s="6" t="inlineStr">
+      <c r="Q285" s="6" t="inlineStr">
         <is>
           <t>VERIFY his exact role/identity at FFOZ -- the cited link is about the Andrew Wilson rebuttal, not clearly a profile of Franczak.</t>
         </is>
       </c>
-      <c r="Q285" s="6" t="inlineStr"/>
       <c r="R285" s="6" t="inlineStr"/>
       <c r="S285" s="6" t="inlineStr"/>
-      <c r="T285" s="6" t="inlineStr">
+      <c r="T285" s="6" t="inlineStr"/>
+      <c r="U285" s="6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U285" s="6" t="inlineStr">
+      <c r="V285" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V285" s="6" t="inlineStr"/>
+      <c r="W285" s="6" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
@@ -24177,39 +24635,40 @@
       <c r="K286" s="6" t="inlineStr"/>
       <c r="L286" s="6" t="inlineStr"/>
       <c r="M286" s="6" t="inlineStr"/>
-      <c r="N286" s="6" t="inlineStr">
+      <c r="N286" s="6" t="inlineStr"/>
+      <c r="O286" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O286" s="6" t="inlineStr">
+      <c r="P286" s="6" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="P286" s="6" t="inlineStr">
+      <c r="Q286" s="6" t="inlineStr">
         <is>
           <t>VERIFY any Israel/Jewish-community signal -- currently a faith-profile inference only, not evidence. Good NURTURE-style candidate.</t>
         </is>
       </c>
-      <c r="Q286" s="6" t="inlineStr">
+      <c r="R286" s="6" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
       </c>
-      <c r="R286" s="6" t="inlineStr"/>
       <c r="S286" s="6" t="inlineStr"/>
-      <c r="T286" s="6" t="inlineStr">
+      <c r="T286" s="6" t="inlineStr"/>
+      <c r="U286" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U286" s="6" t="inlineStr">
+      <c r="V286" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V286" s="6" t="inlineStr">
+      <c r="W286" s="6" t="inlineStr">
         <is>
           <t>US (country music heartland)</t>
         </is>
@@ -24265,38 +24724,39 @@
       <c r="K287" s="6" t="inlineStr"/>
       <c r="L287" s="6" t="inlineStr"/>
       <c r="M287" s="6" t="inlineStr"/>
-      <c r="N287" s="6" t="inlineStr">
+      <c r="N287" s="6" t="inlineStr"/>
+      <c r="O287" s="6" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O287" s="6" t="inlineStr">
+      <c r="P287" s="6" t="inlineStr">
         <is>
           <t>Political</t>
         </is>
       </c>
-      <c r="P287" s="6" t="inlineStr">
+      <c r="Q287" s="6" t="inlineStr">
         <is>
           <t>'Friends/associates/allies' is unbounded -- convert to a bounded pass (his Senate staff alumni, UF leadership, published co-signers). Verify his explicit Israel record.</t>
         </is>
       </c>
-      <c r="Q287" s="6" t="inlineStr"/>
       <c r="R287" s="6" t="inlineStr"/>
       <c r="S287" s="6" t="inlineStr"/>
-      <c r="T287" s="6" t="inlineStr">
+      <c r="T287" s="6" t="inlineStr"/>
+      <c r="U287" s="6" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="U287" s="6" t="inlineStr">
+      <c r="V287" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="V287" s="6" t="inlineStr"/>
+      <c r="W287" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V287"/>
+  <autoFilter ref="A1:W287"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40694,7 +41154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42704,8 +43164,74 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>TRIAGE the 61-person podcast-target list against the real criteria</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Unfulfilled Request</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 16 Jul 2026, naming the top priority: 'identifying christian zionists with long-form audio-video potential'. The current list of 61 tagged 'No podcast (TARGET)' is not fit for that purpose. 13 verified as ALREADY HOSTING active podcasts (retagged 16 Jul). Of the remainder, many fail on availability rather than podcast status: Mike Johnson (sitting Speaker of the House), Tim Scott (sitting Senator), Michele Bachmann, Franklin Graham (runs Samaritan's Purse), Pastor Enoch Adeboye (one of the world's largest church networks, in his 80s), Archbishop Arthur Kitonga (Kenya), Rev. Takeo Sato (Japan), Miklos Szantho (Hungary), and several Latin American and African pastors. Real allies; not people who are going to start an American conversational podcast.</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Re-score all 61 on the long-form rubric. Expect the genuine list to be ~10-15, not 61 -- which is fine, because Johnnie asked for ~20. Then FIND MORE, which is now possible: YouTube search works (verified), so evangelical/Christian-Zionist creators with large short-form audiences and no conversational long-form show can be discovered rather than recalled. The strongest archetype to hunt: a pastor or teacher who already preaches 40 minutes weekly (proven long-form) AND has appeared as a GUEST on someone else's show (proven conversational range) but has no show of their own. Wesley Huff is the existence proof.</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 16 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Sweep the whole roster for DORMANT podcast feeds</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Bulk Source</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Dormant feeds are the cheapest leg-1 wins and nobody has looked. Only one is confirmed so far (Allie Schnacky, 'Keep It Real', 44 eps, last Jul 2025) because the check only ran against the 61 already tagged.</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Run the Apple Podcasts check across all 286 influencers + 4 nurture entries, not just the 61. Flag any feed with a last-release date &gt;180 days old. Each one is a proven host with an existing audience who stopped -- the single cheapest intervention available to the Evangelicals Program. Verify each hit by eye; the matcher is unreliable in both directions.</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Claude, 16 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>55 records</t>
+          <t>56 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>79 records</t>
+          <t>82 records</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1253,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3808,8 +3808,92 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>ROSTER GATES: genuine loyalty AND real talent. No quota.</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Nurture roster; every podcast/seed candidate</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Two hard gates, then rank</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 16 Jul 2026, correcting the framing: '20 is just a number we want as many as possible as long as they are real loyal allies of Israel/The Jews and are really talented.' SO: Johnnie's '~20' is NOT a target and must not be optimised for. It is a floor on ambition, not a cap. The list is capped only by the two GATES, which are pass/fail and non-negotiable. GATE 1 -- GENUINE LOYALTY. Not aligned, not useful, not anti-woke: LOYAL. GATE 2 -- REAL TALENT. Actually good, not merely on-side. A candidate must pass BOTH. Everything Claude previously weighted highly -- availability, US/English audience, podcast status, career stage -- is DOWNSTREAM RANKING, not a gate. A loyal, talented person who is hard to reach is still on the list; a convenient, available mediocrity is not. Scale the list as far as the gates allow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>GATE 1 -- Loyalty is measured by COST PAID, not by statements</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Every ally claim in the database</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Separates real allies from opportunists</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>THE UNIFYING TEST, and it already underlies several criteria Andy set separately. Statements are cheap and everyone makes them; the question is what it COST them. Costly signals cannot be faked at scale. STRONG LOYALTY SIGNALS (rank by how much it cost): spoke up when it was UNPOPULAR IN THEIR OWN MILIEU (the right's drift makes this expensive now -- Seth Dillon attacking Candace Owens and Tucker Carlson is the model, and Andy flagged it for exactly this reason); TOOK INCOMING for it -- being attacked by Tucker/Candace/Fuentes/Sneako is itself proof of cost, which is why the attack-them boost criterion exists; VOLUNTARY, NOT PAID (Andy's existing rule: an unpaid voluntary stand outranks what is likely a paid speaker engagement); SUSTAINED over years, not a single post; PRE-OCT-7 -- anyone pro-Israel BEFORE it was a live political identity is vastly more credible than a post-Oct-7 convert; PRINCIPLED/THEOLOGICAL foundation rather than transactional. OPPORTUNIST SIGNALS (fail the gate): only arrived once it paid; paid by pro-Israel institutions to say it; never takes a cost; swings with audience sentiment; anti-woke or anti-Islam but never actually PRO-Israel -- this is the 'enemy of my enemy' trap Andy explicitly warned about, and it is the commonest failure mode on this list. OPERATIONAL RULE: for every roster candidate, record WHAT IT COST THEM. If the answer is 'nothing', they have not passed Gate 1 -- they are unproven, not loyal. Unproven belongs in Nurture as a watch item, not on the roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>GATE 2 -- Talent is measured by holding an audience, not by alignment</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Nurture roster</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Prevents an aligned-but-mediocre roster</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Andy: 'really talented'. And earlier, on ranking: 'charisma, intelligence - actual influence - should be the greatest factor - Ollie Anisfeld is a great example.' The failure mode this gate exists to prevent is the one that has sunk every previous well-funded effort in this space: a roster of people who agree with you and cannot hold an audience. Donors have already pushed back on BFT that they 'put a lot of money into evangelicals' without the returns -- an aligned-but-boring roster is precisely how that money disappeared. Alignment is the price of entry, not the product. MEASURE: (a) can they hold attention for 30+ minutes -- sermons, lectures, streams, standup all count as evidence; (b) CONVERSATIONAL RANGE -- can they be INTERVIEWED, not just deliver? Guest appearances on other people's shows are the tell, and Wesley Huff's Rogan appearance is the existence proof; (c) do they grow an audience on their own merits, not via institutional distribution; (d) charisma and humour -- Johnnie's own point that the Babylon Bee outperforms by ~30% purely by being funny and smart. Fact-checking alone loses. HARD TEST: would you watch them if you disagreed with them? If not, they fail Gate 2 no matter how loyal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F80"/>
+  <autoFilter ref="A1:F83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41154,7 +41238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43188,7 +43272,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Re-score all 61 on the long-form rubric. Expect the genuine list to be ~10-15, not 61 -- which is fine, because Johnnie asked for ~20. Then FIND MORE, which is now possible: YouTube search works (verified), so evangelical/Christian-Zionist creators with large short-form audiences and no conversational long-form show can be discovered rather than recalled. The strongest archetype to hunt: a pastor or teacher who already preaches 40 minutes weekly (proven long-form) AND has appeared as a GUEST on someone else's show (proven conversational range) but has no show of their own. Wesley Huff is the existence proof.</t>
+          <t>Re-score all 61 on the long-form rubric. Expect the genuine list to be ~10-15 of the existing 61. That is a starting point, NOT a target: Andy, 16 Jul 2026 -- '20 is just a number we want as many as possible as long as they are real loyal allies of Israel/The Jews and are really talented.' Scale until the gates stop passing people. Then FIND MORE, which is now possible: YouTube search works (verified), so evangelical/Christian-Zionist creators with large short-form audiences and no conversational long-form show can be discovered rather than recalled. The strongest archetype to hunt: a pastor or teacher who already preaches 40 minutes weekly (proven long-form) AND has appeared as a GUEST on someone else's show (proven conversational range) but has no show of their own. Wesley Huff is the existence proof.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -43230,8 +43314,41 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL GAP: the database records AGREEMENT, not LOYALTY</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Structural Limit</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED 16 Jul 2026, immediately after Andy made loyalty a hard gate ('as long as they are real loyal allies of Israel/The Jews and are really talented'). Of 232 influencers marked stance:pro, only 21 have ANY recorded cost signal -- any evidence that being pro-Israel ever cost them something. 211 have none. THIS IS NOT A VERDICT ON THOSE 211. It is a measurement gap: the database was built to answer 'who is on our side?' and has therefore never asked 'what did it cost them?' Under Gate 1 they are UNPROVEN, not disloyal. But the distinction is the whole ballgame, because statements are free and everyone has them.</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>WHY THIS MATTERS MORE THAN ANY OTHER BACKLOG ITEM -- it is the answer to the donors' objection. BFT's donors said they had 'put a lot of money into evangelicals' without the returns they wanted, and demanded a strategy deep-dive before funding the Evangelicals Program. A list of 232 people who AGREE is worthless: every organisation in this space has that list, and it is exactly what the money already bought. A list of the people who TOOK INCOMING is an asset nobody else has, and it is what Johnnie means by making the relationship 'less sentimental and more substantive'. Cost-paid IS the substance. DO THIS: for every pro entry, ask and record one question -- WHAT DID IT COST THEM? Fields to add: costPaid (what happened to them), costDate (when -- pre-Oct-7 is worth far more than post), costSource (the receipt). Rank the roster on it. Expect the honest answer to be that most of the 232 have paid nothing, and that the real coalition is much smaller and much more valuable than the headcount suggests. The 21 with a signal today are the seed: Seth Dillon, Ami Kozak, Dave Rubin, Graham Allen, Insurrection Barbie, Evan Faunce, Jackson Lahmeyer, Erica Kirk, Goldie Ghamari, Erin Molan, Jamie Michell, Dustin Tropp, Eugene Kontorovich, Arielle Klepach, Caroline Downey and others -- note how many of them earned it the same way, by attacking the Tucker/Candace/Fuentes drift from inside the right.</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 16 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G56"/>
+  <autoFilter ref="A1:G57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="criteria" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$W$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$Z$288</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$H$5</definedName>
@@ -739,7 +739,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>286 records</t>
+          <t>287 records</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W287"/>
+  <dimension ref="A1:Z288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3930,6 +3930,9 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4046,6 +4049,21 @@
       <c r="W1" s="5" t="inlineStr">
         <is>
           <t>audienceGeography</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>costPaid</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>talentEvidence</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>sourceUrl</t>
         </is>
       </c>
     </row>
@@ -4113,6 +4131,9 @@
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
+      <c r="Y2" s="6" t="inlineStr"/>
+      <c r="Z2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4190,6 +4211,9 @@
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
+      <c r="Z3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4255,6 +4279,9 @@
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
+      <c r="Y4" s="6" t="inlineStr"/>
+      <c r="Z4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4320,6 +4347,9 @@
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
       <c r="W5" s="6" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="6" t="inlineStr"/>
+      <c r="Z5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4397,6 +4427,9 @@
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
       <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="6" t="inlineStr"/>
+      <c r="Z6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4474,6 +4507,9 @@
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="6" t="inlineStr"/>
+      <c r="Z7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4551,6 +4587,9 @@
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="6" t="inlineStr"/>
+      <c r="Z8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4616,6 +4655,9 @@
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr"/>
+      <c r="Z9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4693,6 +4735,9 @@
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="6" t="inlineStr"/>
+      <c r="Z10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4770,6 +4815,9 @@
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="6" t="inlineStr"/>
+      <c r="Z11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4835,6 +4883,9 @@
       <c r="U12" s="6" t="inlineStr"/>
       <c r="V12" s="6" t="inlineStr"/>
       <c r="W12" s="6" t="inlineStr"/>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="6" t="inlineStr"/>
+      <c r="Z12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4900,6 +4951,9 @@
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="6" t="inlineStr"/>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="6" t="inlineStr"/>
+      <c r="Z13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4965,6 +5019,9 @@
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="6" t="inlineStr"/>
+      <c r="Z14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5030,6 +5087,9 @@
       <c r="U15" s="6" t="inlineStr"/>
       <c r="V15" s="6" t="inlineStr"/>
       <c r="W15" s="6" t="inlineStr"/>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="6" t="inlineStr"/>
+      <c r="Z15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -5107,6 +5167,9 @@
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="6" t="inlineStr"/>
+      <c r="Z16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -5168,6 +5231,9 @@
       <c r="U17" s="6" t="inlineStr"/>
       <c r="V17" s="6" t="inlineStr"/>
       <c r="W17" s="6" t="inlineStr"/>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="6" t="inlineStr"/>
+      <c r="Z17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5229,6 +5295,9 @@
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="6" t="inlineStr"/>
+      <c r="Z18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5302,6 +5371,9 @@
       <c r="U19" s="6" t="inlineStr"/>
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="6" t="inlineStr"/>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="6" t="inlineStr"/>
+      <c r="Z19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5363,6 +5435,9 @@
       <c r="U20" s="6" t="inlineStr"/>
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="6" t="inlineStr"/>
+      <c r="X20" s="6" t="inlineStr"/>
+      <c r="Y20" s="6" t="inlineStr"/>
+      <c r="Z20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5424,6 +5499,9 @@
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
+      <c r="Y21" s="6" t="inlineStr"/>
+      <c r="Z21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5485,6 +5563,9 @@
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
+      <c r="Y22" s="6" t="inlineStr"/>
+      <c r="Z22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5546,6 +5627,9 @@
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
+      <c r="Y23" s="6" t="inlineStr"/>
+      <c r="Z23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5619,6 +5703,9 @@
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
+      <c r="Y24" s="6" t="inlineStr"/>
+      <c r="Z24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5692,6 +5779,9 @@
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
+      <c r="Y25" s="6" t="inlineStr"/>
+      <c r="Z25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5769,6 +5859,9 @@
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
+      <c r="Y26" s="6" t="inlineStr"/>
+      <c r="Z26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5846,6 +5939,9 @@
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
+      <c r="Y27" s="6" t="inlineStr"/>
+      <c r="Z27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5919,6 +6015,9 @@
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
+      <c r="Y28" s="6" t="inlineStr"/>
+      <c r="Z28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5992,6 +6091,9 @@
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="6" t="inlineStr"/>
+      <c r="Z29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6065,6 +6167,9 @@
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
+      <c r="Y30" s="6" t="inlineStr"/>
+      <c r="Z30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6138,6 +6243,9 @@
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
+      <c r="Y31" s="6" t="inlineStr"/>
+      <c r="Z31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -6215,6 +6323,9 @@
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
+      <c r="Y32" s="6" t="inlineStr"/>
+      <c r="Z32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6276,6 +6387,9 @@
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
+      <c r="Y33" s="6" t="inlineStr"/>
+      <c r="Z33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -6337,6 +6451,9 @@
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
+      <c r="Y34" s="6" t="inlineStr"/>
+      <c r="Z34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -6414,6 +6531,9 @@
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="Z35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6491,6 +6611,9 @@
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
+      <c r="Y36" s="6" t="inlineStr"/>
+      <c r="Z36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -6552,6 +6675,9 @@
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
+      <c r="Z37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -6617,6 +6743,9 @@
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
+      <c r="Y38" s="6" t="inlineStr"/>
+      <c r="Z38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -6678,6 +6807,9 @@
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
+      <c r="Y39" s="6" t="inlineStr"/>
+      <c r="Z39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -6739,6 +6871,9 @@
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
+      <c r="Y40" s="6" t="inlineStr"/>
+      <c r="Z40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -6800,6 +6935,9 @@
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
+      <c r="Y41" s="6" t="inlineStr"/>
+      <c r="Z41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -6861,6 +6999,9 @@
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
+      <c r="Y42" s="6" t="inlineStr"/>
+      <c r="Z42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -6922,6 +7063,9 @@
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
+      <c r="Y43" s="6" t="inlineStr"/>
+      <c r="Z43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -6983,6 +7127,9 @@
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
+      <c r="Y44" s="6" t="inlineStr"/>
+      <c r="Z44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -7044,6 +7191,9 @@
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
+      <c r="Y45" s="6" t="inlineStr"/>
+      <c r="Z45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -7105,6 +7255,9 @@
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
+      <c r="Y46" s="6" t="inlineStr"/>
+      <c r="Z46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -7166,6 +7319,9 @@
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
+      <c r="Y47" s="6" t="inlineStr"/>
+      <c r="Z47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -7227,6 +7383,9 @@
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
+      <c r="Y48" s="6" t="inlineStr"/>
+      <c r="Z48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -7288,6 +7447,9 @@
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
+      <c r="Y49" s="6" t="inlineStr"/>
+      <c r="Z49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7349,6 +7511,9 @@
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
+      <c r="Y50" s="6" t="inlineStr"/>
+      <c r="Z50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -7410,6 +7575,9 @@
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
+      <c r="Y51" s="6" t="inlineStr"/>
+      <c r="Z51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7471,6 +7639,9 @@
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
+      <c r="Y52" s="6" t="inlineStr"/>
+      <c r="Z52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -7532,6 +7703,9 @@
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
+      <c r="Y53" s="6" t="inlineStr"/>
+      <c r="Z53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7593,6 +7767,9 @@
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
+      <c r="Y54" s="6" t="inlineStr"/>
+      <c r="Z54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -7654,6 +7831,9 @@
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
+      <c r="Y55" s="6" t="inlineStr"/>
+      <c r="Z55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7727,6 +7907,9 @@
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
+      <c r="Y56" s="6" t="inlineStr"/>
+      <c r="Z56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -7804,6 +7987,9 @@
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
+      <c r="Y57" s="6" t="inlineStr"/>
+      <c r="Z57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -7865,6 +8051,9 @@
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
+      <c r="Y58" s="6" t="inlineStr"/>
+      <c r="Z58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -7926,6 +8115,9 @@
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
+      <c r="Y59" s="6" t="inlineStr"/>
+      <c r="Z59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -7987,6 +8179,9 @@
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
+      <c r="Y60" s="6" t="inlineStr"/>
+      <c r="Z60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -8048,6 +8243,9 @@
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
+      <c r="Y61" s="6" t="inlineStr"/>
+      <c r="Z61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -8109,6 +8307,9 @@
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
+      <c r="Y62" s="6" t="inlineStr"/>
+      <c r="Z62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -8170,6 +8371,9 @@
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
+      <c r="Y63" s="6" t="inlineStr"/>
+      <c r="Z63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -8231,6 +8435,9 @@
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
+      <c r="Y64" s="6" t="inlineStr"/>
+      <c r="Z64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -8292,6 +8499,9 @@
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
+      <c r="Y65" s="6" t="inlineStr"/>
+      <c r="Z65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -8353,6 +8563,9 @@
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
+      <c r="Y66" s="6" t="inlineStr"/>
+      <c r="Z66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -8414,6 +8627,9 @@
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
+      <c r="Y67" s="6" t="inlineStr"/>
+      <c r="Z67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -8491,6 +8707,9 @@
       <c r="U68" s="6" t="inlineStr"/>
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="6" t="inlineStr"/>
+      <c r="X68" s="6" t="inlineStr"/>
+      <c r="Y68" s="6" t="inlineStr"/>
+      <c r="Z68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -8564,6 +8783,9 @@
       <c r="U69" s="6" t="inlineStr"/>
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="6" t="inlineStr"/>
+      <c r="X69" s="6" t="inlineStr"/>
+      <c r="Y69" s="6" t="inlineStr"/>
+      <c r="Z69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -8625,6 +8847,9 @@
       <c r="U70" s="6" t="inlineStr"/>
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="6" t="inlineStr"/>
+      <c r="X70" s="6" t="inlineStr"/>
+      <c r="Y70" s="6" t="inlineStr"/>
+      <c r="Z70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -8686,6 +8911,9 @@
       <c r="U71" s="6" t="inlineStr"/>
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="6" t="inlineStr"/>
+      <c r="X71" s="6" t="inlineStr"/>
+      <c r="Y71" s="6" t="inlineStr"/>
+      <c r="Z71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8747,6 +8975,9 @@
       <c r="U72" s="6" t="inlineStr"/>
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="6" t="inlineStr"/>
+      <c r="X72" s="6" t="inlineStr"/>
+      <c r="Y72" s="6" t="inlineStr"/>
+      <c r="Z72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8820,6 +9051,9 @@
       <c r="U73" s="6" t="inlineStr"/>
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="6" t="inlineStr"/>
+      <c r="X73" s="6" t="inlineStr"/>
+      <c r="Y73" s="6" t="inlineStr"/>
+      <c r="Z73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -8881,6 +9115,9 @@
       <c r="U74" s="6" t="inlineStr"/>
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="6" t="inlineStr"/>
+      <c r="X74" s="6" t="inlineStr"/>
+      <c r="Y74" s="6" t="inlineStr"/>
+      <c r="Z74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -8942,6 +9179,9 @@
       <c r="U75" s="6" t="inlineStr"/>
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="6" t="inlineStr"/>
+      <c r="X75" s="6" t="inlineStr"/>
+      <c r="Y75" s="6" t="inlineStr"/>
+      <c r="Z75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -9003,6 +9243,9 @@
       <c r="U76" s="6" t="inlineStr"/>
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="6" t="inlineStr"/>
+      <c r="X76" s="6" t="inlineStr"/>
+      <c r="Y76" s="6" t="inlineStr"/>
+      <c r="Z76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -9076,6 +9319,9 @@
       <c r="U77" s="6" t="inlineStr"/>
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="6" t="inlineStr"/>
+      <c r="X77" s="6" t="inlineStr"/>
+      <c r="Y77" s="6" t="inlineStr"/>
+      <c r="Z77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -9137,6 +9383,9 @@
       <c r="U78" s="6" t="inlineStr"/>
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="6" t="inlineStr"/>
+      <c r="X78" s="6" t="inlineStr"/>
+      <c r="Y78" s="6" t="inlineStr"/>
+      <c r="Z78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -9210,6 +9459,9 @@
       <c r="U79" s="6" t="inlineStr"/>
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="6" t="inlineStr"/>
+      <c r="X79" s="6" t="inlineStr"/>
+      <c r="Y79" s="6" t="inlineStr"/>
+      <c r="Z79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -9271,6 +9523,9 @@
       <c r="U80" s="6" t="inlineStr"/>
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="6" t="inlineStr"/>
+      <c r="X80" s="6" t="inlineStr"/>
+      <c r="Y80" s="6" t="inlineStr"/>
+      <c r="Z80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -9332,6 +9587,9 @@
       <c r="U81" s="6" t="inlineStr"/>
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="6" t="inlineStr"/>
+      <c r="X81" s="6" t="inlineStr"/>
+      <c r="Y81" s="6" t="inlineStr"/>
+      <c r="Z81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -9393,6 +9651,9 @@
       <c r="U82" s="6" t="inlineStr"/>
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="6" t="inlineStr"/>
+      <c r="X82" s="6" t="inlineStr"/>
+      <c r="Y82" s="6" t="inlineStr"/>
+      <c r="Z82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -9454,6 +9715,9 @@
       <c r="U83" s="6" t="inlineStr"/>
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="6" t="inlineStr"/>
+      <c r="X83" s="6" t="inlineStr"/>
+      <c r="Y83" s="6" t="inlineStr"/>
+      <c r="Z83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -9527,6 +9791,9 @@
       <c r="U84" s="6" t="inlineStr"/>
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="6" t="inlineStr"/>
+      <c r="X84" s="6" t="inlineStr"/>
+      <c r="Y84" s="6" t="inlineStr"/>
+      <c r="Z84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -9588,6 +9855,9 @@
       <c r="U85" s="6" t="inlineStr"/>
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="6" t="inlineStr"/>
+      <c r="X85" s="6" t="inlineStr"/>
+      <c r="Y85" s="6" t="inlineStr"/>
+      <c r="Z85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -9661,6 +9931,9 @@
       <c r="U86" s="6" t="inlineStr"/>
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="6" t="inlineStr"/>
+      <c r="X86" s="6" t="inlineStr"/>
+      <c r="Y86" s="6" t="inlineStr"/>
+      <c r="Z86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -9722,6 +9995,9 @@
       <c r="U87" s="6" t="inlineStr"/>
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="6" t="inlineStr"/>
+      <c r="X87" s="6" t="inlineStr"/>
+      <c r="Y87" s="6" t="inlineStr"/>
+      <c r="Z87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -9783,6 +10059,9 @@
       <c r="U88" s="6" t="inlineStr"/>
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="6" t="inlineStr"/>
+      <c r="X88" s="6" t="inlineStr"/>
+      <c r="Y88" s="6" t="inlineStr"/>
+      <c r="Z88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -9844,6 +10123,9 @@
       <c r="U89" s="6" t="inlineStr"/>
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="6" t="inlineStr"/>
+      <c r="X89" s="6" t="inlineStr"/>
+      <c r="Y89" s="6" t="inlineStr"/>
+      <c r="Z89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -9905,6 +10187,9 @@
       <c r="U90" s="6" t="inlineStr"/>
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="6" t="inlineStr"/>
+      <c r="X90" s="6" t="inlineStr"/>
+      <c r="Y90" s="6" t="inlineStr"/>
+      <c r="Z90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -9966,6 +10251,9 @@
       <c r="U91" s="6" t="inlineStr"/>
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="6" t="inlineStr"/>
+      <c r="X91" s="6" t="inlineStr"/>
+      <c r="Y91" s="6" t="inlineStr"/>
+      <c r="Z91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -10027,6 +10315,9 @@
       <c r="U92" s="6" t="inlineStr"/>
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="6" t="inlineStr"/>
+      <c r="X92" s="6" t="inlineStr"/>
+      <c r="Y92" s="6" t="inlineStr"/>
+      <c r="Z92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -10088,6 +10379,9 @@
       <c r="U93" s="6" t="inlineStr"/>
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="6" t="inlineStr"/>
+      <c r="X93" s="6" t="inlineStr"/>
+      <c r="Y93" s="6" t="inlineStr"/>
+      <c r="Z93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -10149,6 +10443,9 @@
       <c r="U94" s="6" t="inlineStr"/>
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="6" t="inlineStr"/>
+      <c r="X94" s="6" t="inlineStr"/>
+      <c r="Y94" s="6" t="inlineStr"/>
+      <c r="Z94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -10210,6 +10507,9 @@
       <c r="U95" s="6" t="inlineStr"/>
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="6" t="inlineStr"/>
+      <c r="X95" s="6" t="inlineStr"/>
+      <c r="Y95" s="6" t="inlineStr"/>
+      <c r="Z95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -10271,6 +10571,9 @@
       <c r="U96" s="6" t="inlineStr"/>
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="6" t="inlineStr"/>
+      <c r="X96" s="6" t="inlineStr"/>
+      <c r="Y96" s="6" t="inlineStr"/>
+      <c r="Z96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -10332,6 +10635,9 @@
       <c r="U97" s="6" t="inlineStr"/>
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="6" t="inlineStr"/>
+      <c r="X97" s="6" t="inlineStr"/>
+      <c r="Y97" s="6" t="inlineStr"/>
+      <c r="Z97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -10393,6 +10699,9 @@
       <c r="U98" s="6" t="inlineStr"/>
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="6" t="inlineStr"/>
+      <c r="X98" s="6" t="inlineStr"/>
+      <c r="Y98" s="6" t="inlineStr"/>
+      <c r="Z98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -10454,6 +10763,9 @@
       <c r="U99" s="6" t="inlineStr"/>
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="6" t="inlineStr"/>
+      <c r="X99" s="6" t="inlineStr"/>
+      <c r="Y99" s="6" t="inlineStr"/>
+      <c r="Z99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -10515,6 +10827,9 @@
       <c r="U100" s="6" t="inlineStr"/>
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="6" t="inlineStr"/>
+      <c r="X100" s="6" t="inlineStr"/>
+      <c r="Y100" s="6" t="inlineStr"/>
+      <c r="Z100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -10576,6 +10891,9 @@
       <c r="U101" s="6" t="inlineStr"/>
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="6" t="inlineStr"/>
+      <c r="X101" s="6" t="inlineStr"/>
+      <c r="Y101" s="6" t="inlineStr"/>
+      <c r="Z101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -10637,6 +10955,9 @@
       <c r="U102" s="6" t="inlineStr"/>
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="6" t="inlineStr"/>
+      <c r="X102" s="6" t="inlineStr"/>
+      <c r="Y102" s="6" t="inlineStr"/>
+      <c r="Z102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -10698,6 +11019,9 @@
       <c r="U103" s="6" t="inlineStr"/>
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="6" t="inlineStr"/>
+      <c r="X103" s="6" t="inlineStr"/>
+      <c r="Y103" s="6" t="inlineStr"/>
+      <c r="Z103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -10759,6 +11083,9 @@
       <c r="U104" s="6" t="inlineStr"/>
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="6" t="inlineStr"/>
+      <c r="X104" s="6" t="inlineStr"/>
+      <c r="Y104" s="6" t="inlineStr"/>
+      <c r="Z104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -10820,6 +11147,9 @@
       <c r="U105" s="6" t="inlineStr"/>
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="6" t="inlineStr"/>
+      <c r="X105" s="6" t="inlineStr"/>
+      <c r="Y105" s="6" t="inlineStr"/>
+      <c r="Z105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -10881,6 +11211,9 @@
       <c r="U106" s="6" t="inlineStr"/>
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="6" t="inlineStr"/>
+      <c r="X106" s="6" t="inlineStr"/>
+      <c r="Y106" s="6" t="inlineStr"/>
+      <c r="Z106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -10942,6 +11275,9 @@
       <c r="U107" s="6" t="inlineStr"/>
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="6" t="inlineStr"/>
+      <c r="X107" s="6" t="inlineStr"/>
+      <c r="Y107" s="6" t="inlineStr"/>
+      <c r="Z107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -11003,6 +11339,9 @@
       <c r="U108" s="6" t="inlineStr"/>
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="6" t="inlineStr"/>
+      <c r="X108" s="6" t="inlineStr"/>
+      <c r="Y108" s="6" t="inlineStr"/>
+      <c r="Z108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -11064,6 +11403,9 @@
       <c r="U109" s="6" t="inlineStr"/>
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="6" t="inlineStr"/>
+      <c r="X109" s="6" t="inlineStr"/>
+      <c r="Y109" s="6" t="inlineStr"/>
+      <c r="Z109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -11125,6 +11467,9 @@
       <c r="U110" s="6" t="inlineStr"/>
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="6" t="inlineStr"/>
+      <c r="X110" s="6" t="inlineStr"/>
+      <c r="Y110" s="6" t="inlineStr"/>
+      <c r="Z110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -11186,6 +11531,9 @@
       <c r="U111" s="6" t="inlineStr"/>
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="6" t="inlineStr"/>
+      <c r="X111" s="6" t="inlineStr"/>
+      <c r="Y111" s="6" t="inlineStr"/>
+      <c r="Z111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -11247,6 +11595,9 @@
       <c r="U112" s="6" t="inlineStr"/>
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="6" t="inlineStr"/>
+      <c r="X112" s="6" t="inlineStr"/>
+      <c r="Y112" s="6" t="inlineStr"/>
+      <c r="Z112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -11308,6 +11659,9 @@
       <c r="U113" s="6" t="inlineStr"/>
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="6" t="inlineStr"/>
+      <c r="X113" s="6" t="inlineStr"/>
+      <c r="Y113" s="6" t="inlineStr"/>
+      <c r="Z113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -11381,6 +11735,9 @@
       <c r="U114" s="6" t="inlineStr"/>
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="6" t="inlineStr"/>
+      <c r="X114" s="6" t="inlineStr"/>
+      <c r="Y114" s="6" t="inlineStr"/>
+      <c r="Z114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -11442,6 +11799,9 @@
       <c r="U115" s="6" t="inlineStr"/>
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="6" t="inlineStr"/>
+      <c r="X115" s="6" t="inlineStr"/>
+      <c r="Y115" s="6" t="inlineStr"/>
+      <c r="Z115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -11503,6 +11863,9 @@
       <c r="U116" s="6" t="inlineStr"/>
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="6" t="inlineStr"/>
+      <c r="X116" s="6" t="inlineStr"/>
+      <c r="Y116" s="6" t="inlineStr"/>
+      <c r="Z116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -11564,6 +11927,9 @@
       <c r="U117" s="6" t="inlineStr"/>
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="6" t="inlineStr"/>
+      <c r="X117" s="6" t="inlineStr"/>
+      <c r="Y117" s="6" t="inlineStr"/>
+      <c r="Z117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -11625,6 +11991,9 @@
       <c r="U118" s="6" t="inlineStr"/>
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="6" t="inlineStr"/>
+      <c r="X118" s="6" t="inlineStr"/>
+      <c r="Y118" s="6" t="inlineStr"/>
+      <c r="Z118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -11686,6 +12055,9 @@
       <c r="U119" s="6" t="inlineStr"/>
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="6" t="inlineStr"/>
+      <c r="X119" s="6" t="inlineStr"/>
+      <c r="Y119" s="6" t="inlineStr"/>
+      <c r="Z119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -11747,6 +12119,9 @@
       <c r="U120" s="6" t="inlineStr"/>
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="6" t="inlineStr"/>
+      <c r="X120" s="6" t="inlineStr"/>
+      <c r="Y120" s="6" t="inlineStr"/>
+      <c r="Z120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -11808,6 +12183,9 @@
       <c r="U121" s="6" t="inlineStr"/>
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="6" t="inlineStr"/>
+      <c r="X121" s="6" t="inlineStr"/>
+      <c r="Y121" s="6" t="inlineStr"/>
+      <c r="Z121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -11869,6 +12247,9 @@
       <c r="U122" s="6" t="inlineStr"/>
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="6" t="inlineStr"/>
+      <c r="X122" s="6" t="inlineStr"/>
+      <c r="Y122" s="6" t="inlineStr"/>
+      <c r="Z122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -11930,6 +12311,9 @@
       <c r="U123" s="6" t="inlineStr"/>
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="6" t="inlineStr"/>
+      <c r="X123" s="6" t="inlineStr"/>
+      <c r="Y123" s="6" t="inlineStr"/>
+      <c r="Z123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -11991,6 +12375,9 @@
       <c r="U124" s="6" t="inlineStr"/>
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="6" t="inlineStr"/>
+      <c r="X124" s="6" t="inlineStr"/>
+      <c r="Y124" s="6" t="inlineStr"/>
+      <c r="Z124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -12052,6 +12439,9 @@
       <c r="U125" s="6" t="inlineStr"/>
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="6" t="inlineStr"/>
+      <c r="X125" s="6" t="inlineStr"/>
+      <c r="Y125" s="6" t="inlineStr"/>
+      <c r="Z125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -12113,6 +12503,9 @@
       <c r="U126" s="6" t="inlineStr"/>
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="6" t="inlineStr"/>
+      <c r="X126" s="6" t="inlineStr"/>
+      <c r="Y126" s="6" t="inlineStr"/>
+      <c r="Z126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -12174,6 +12567,9 @@
       <c r="U127" s="6" t="inlineStr"/>
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="6" t="inlineStr"/>
+      <c r="X127" s="6" t="inlineStr"/>
+      <c r="Y127" s="6" t="inlineStr"/>
+      <c r="Z127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -12235,6 +12631,9 @@
       <c r="U128" s="6" t="inlineStr"/>
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="6" t="inlineStr"/>
+      <c r="X128" s="6" t="inlineStr"/>
+      <c r="Y128" s="6" t="inlineStr"/>
+      <c r="Z128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -12296,6 +12695,9 @@
       <c r="U129" s="6" t="inlineStr"/>
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="6" t="inlineStr"/>
+      <c r="X129" s="6" t="inlineStr"/>
+      <c r="Y129" s="6" t="inlineStr"/>
+      <c r="Z129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -12357,6 +12759,9 @@
       <c r="U130" s="6" t="inlineStr"/>
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="6" t="inlineStr"/>
+      <c r="X130" s="6" t="inlineStr"/>
+      <c r="Y130" s="6" t="inlineStr"/>
+      <c r="Z130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -12418,6 +12823,9 @@
       <c r="U131" s="6" t="inlineStr"/>
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="6" t="inlineStr"/>
+      <c r="X131" s="6" t="inlineStr"/>
+      <c r="Y131" s="6" t="inlineStr"/>
+      <c r="Z131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -12479,6 +12887,9 @@
       <c r="U132" s="6" t="inlineStr"/>
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="6" t="inlineStr"/>
+      <c r="X132" s="6" t="inlineStr"/>
+      <c r="Y132" s="6" t="inlineStr"/>
+      <c r="Z132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -12540,6 +12951,9 @@
       <c r="U133" s="6" t="inlineStr"/>
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="6" t="inlineStr"/>
+      <c r="X133" s="6" t="inlineStr"/>
+      <c r="Y133" s="6" t="inlineStr"/>
+      <c r="Z133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -12601,6 +13015,9 @@
       <c r="U134" s="6" t="inlineStr"/>
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="6" t="inlineStr"/>
+      <c r="X134" s="6" t="inlineStr"/>
+      <c r="Y134" s="6" t="inlineStr"/>
+      <c r="Z134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -12662,6 +13079,9 @@
       <c r="U135" s="6" t="inlineStr"/>
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="6" t="inlineStr"/>
+      <c r="X135" s="6" t="inlineStr"/>
+      <c r="Y135" s="6" t="inlineStr"/>
+      <c r="Z135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -12723,6 +13143,9 @@
       <c r="U136" s="6" t="inlineStr"/>
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="6" t="inlineStr"/>
+      <c r="X136" s="6" t="inlineStr"/>
+      <c r="Y136" s="6" t="inlineStr"/>
+      <c r="Z136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -12788,6 +13211,9 @@
       <c r="U137" s="6" t="inlineStr"/>
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="6" t="inlineStr"/>
+      <c r="X137" s="6" t="inlineStr"/>
+      <c r="Y137" s="6" t="inlineStr"/>
+      <c r="Z137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -12857,6 +13283,9 @@
       <c r="U138" s="6" t="inlineStr"/>
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="6" t="inlineStr"/>
+      <c r="X138" s="6" t="inlineStr"/>
+      <c r="Y138" s="6" t="inlineStr"/>
+      <c r="Z138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -12926,6 +13355,9 @@
       <c r="U139" s="6" t="inlineStr"/>
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="6" t="inlineStr"/>
+      <c r="X139" s="6" t="inlineStr"/>
+      <c r="Y139" s="6" t="inlineStr"/>
+      <c r="Z139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -12995,6 +13427,9 @@
       <c r="U140" s="6" t="inlineStr"/>
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="6" t="inlineStr"/>
+      <c r="X140" s="6" t="inlineStr"/>
+      <c r="Y140" s="6" t="inlineStr"/>
+      <c r="Z140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -13064,6 +13499,9 @@
       <c r="U141" s="6" t="inlineStr"/>
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="6" t="inlineStr"/>
+      <c r="X141" s="6" t="inlineStr"/>
+      <c r="Y141" s="6" t="inlineStr"/>
+      <c r="Z141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -13133,6 +13571,9 @@
       <c r="U142" s="6" t="inlineStr"/>
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="6" t="inlineStr"/>
+      <c r="X142" s="6" t="inlineStr"/>
+      <c r="Y142" s="6" t="inlineStr"/>
+      <c r="Z142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -13202,6 +13643,9 @@
       <c r="U143" s="6" t="inlineStr"/>
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="6" t="inlineStr"/>
+      <c r="X143" s="6" t="inlineStr"/>
+      <c r="Y143" s="6" t="inlineStr"/>
+      <c r="Z143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -13271,6 +13715,9 @@
       <c r="U144" s="6" t="inlineStr"/>
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="6" t="inlineStr"/>
+      <c r="X144" s="6" t="inlineStr"/>
+      <c r="Y144" s="6" t="inlineStr"/>
+      <c r="Z144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -13340,6 +13787,9 @@
       <c r="U145" s="6" t="inlineStr"/>
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="6" t="inlineStr"/>
+      <c r="X145" s="6" t="inlineStr"/>
+      <c r="Y145" s="6" t="inlineStr"/>
+      <c r="Z145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -13425,6 +13875,9 @@
       <c r="U146" s="6" t="inlineStr"/>
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="6" t="inlineStr"/>
+      <c r="X146" s="6" t="inlineStr"/>
+      <c r="Y146" s="6" t="inlineStr"/>
+      <c r="Z146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -13498,6 +13951,9 @@
       <c r="U147" s="6" t="inlineStr"/>
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="6" t="inlineStr"/>
+      <c r="X147" s="6" t="inlineStr"/>
+      <c r="Y147" s="6" t="inlineStr"/>
+      <c r="Z147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -13575,6 +14031,9 @@
       <c r="U148" s="6" t="inlineStr"/>
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="6" t="inlineStr"/>
+      <c r="X148" s="6" t="inlineStr"/>
+      <c r="Y148" s="6" t="inlineStr"/>
+      <c r="Z148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -13648,6 +14107,9 @@
       <c r="U149" s="6" t="inlineStr"/>
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="6" t="inlineStr"/>
+      <c r="X149" s="6" t="inlineStr"/>
+      <c r="Y149" s="6" t="inlineStr"/>
+      <c r="Z149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -13721,6 +14183,9 @@
       <c r="U150" s="6" t="inlineStr"/>
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="6" t="inlineStr"/>
+      <c r="X150" s="6" t="inlineStr"/>
+      <c r="Y150" s="6" t="inlineStr"/>
+      <c r="Z150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -13794,6 +14259,9 @@
       <c r="U151" s="6" t="inlineStr"/>
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="6" t="inlineStr"/>
+      <c r="X151" s="6" t="inlineStr"/>
+      <c r="Y151" s="6" t="inlineStr"/>
+      <c r="Z151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -13867,6 +14335,9 @@
       <c r="U152" s="6" t="inlineStr"/>
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="6" t="inlineStr"/>
+      <c r="X152" s="6" t="inlineStr"/>
+      <c r="Y152" s="6" t="inlineStr"/>
+      <c r="Z152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -13940,6 +14411,9 @@
       <c r="U153" s="6" t="inlineStr"/>
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="6" t="inlineStr"/>
+      <c r="X153" s="6" t="inlineStr"/>
+      <c r="Y153" s="6" t="inlineStr"/>
+      <c r="Z153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -14013,6 +14487,9 @@
       <c r="U154" s="6" t="inlineStr"/>
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="6" t="inlineStr"/>
+      <c r="X154" s="6" t="inlineStr"/>
+      <c r="Y154" s="6" t="inlineStr"/>
+      <c r="Z154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -14086,6 +14563,9 @@
       <c r="U155" s="6" t="inlineStr"/>
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="6" t="inlineStr"/>
+      <c r="X155" s="6" t="inlineStr"/>
+      <c r="Y155" s="6" t="inlineStr"/>
+      <c r="Z155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -14159,6 +14639,9 @@
       <c r="U156" s="6" t="inlineStr"/>
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="6" t="inlineStr"/>
+      <c r="X156" s="6" t="inlineStr"/>
+      <c r="Y156" s="6" t="inlineStr"/>
+      <c r="Z156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -14232,6 +14715,9 @@
       <c r="U157" s="6" t="inlineStr"/>
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="6" t="inlineStr"/>
+      <c r="X157" s="6" t="inlineStr"/>
+      <c r="Y157" s="6" t="inlineStr"/>
+      <c r="Z157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -14309,6 +14795,9 @@
       <c r="U158" s="6" t="inlineStr"/>
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="6" t="inlineStr"/>
+      <c r="X158" s="6" t="inlineStr"/>
+      <c r="Y158" s="6" t="inlineStr"/>
+      <c r="Z158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -14382,6 +14871,9 @@
       <c r="U159" s="6" t="inlineStr"/>
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="6" t="inlineStr"/>
+      <c r="X159" s="6" t="inlineStr"/>
+      <c r="Y159" s="6" t="inlineStr"/>
+      <c r="Z159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
@@ -14455,6 +14947,9 @@
       <c r="U160" s="6" t="inlineStr"/>
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="6" t="inlineStr"/>
+      <c r="X160" s="6" t="inlineStr"/>
+      <c r="Y160" s="6" t="inlineStr"/>
+      <c r="Z160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -14536,6 +15031,9 @@
       <c r="U161" s="6" t="inlineStr"/>
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="6" t="inlineStr"/>
+      <c r="X161" s="6" t="inlineStr"/>
+      <c r="Y161" s="6" t="inlineStr"/>
+      <c r="Z161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -14617,6 +15115,9 @@
       <c r="U162" s="6" t="inlineStr"/>
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="6" t="inlineStr"/>
+      <c r="X162" s="6" t="inlineStr"/>
+      <c r="Y162" s="6" t="inlineStr"/>
+      <c r="Z162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -14694,6 +15195,9 @@
       <c r="U163" s="6" t="inlineStr"/>
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="6" t="inlineStr"/>
+      <c r="X163" s="6" t="inlineStr"/>
+      <c r="Y163" s="6" t="inlineStr"/>
+      <c r="Z163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -14763,6 +15267,9 @@
       <c r="U164" s="6" t="inlineStr"/>
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="6" t="inlineStr"/>
+      <c r="X164" s="6" t="inlineStr"/>
+      <c r="Y164" s="6" t="inlineStr"/>
+      <c r="Z164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -14836,6 +15343,9 @@
       <c r="U165" s="6" t="inlineStr"/>
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="6" t="inlineStr"/>
+      <c r="X165" s="6" t="inlineStr"/>
+      <c r="Y165" s="6" t="inlineStr"/>
+      <c r="Z165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -14909,6 +15419,9 @@
       <c r="U166" s="6" t="inlineStr"/>
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="6" t="inlineStr"/>
+      <c r="X166" s="6" t="inlineStr"/>
+      <c r="Y166" s="6" t="inlineStr"/>
+      <c r="Z166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -14986,6 +15499,9 @@
       <c r="U167" s="6" t="inlineStr"/>
       <c r="V167" s="6" t="inlineStr"/>
       <c r="W167" s="6" t="inlineStr"/>
+      <c r="X167" s="6" t="inlineStr"/>
+      <c r="Y167" s="6" t="inlineStr"/>
+      <c r="Z167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -15059,6 +15575,9 @@
       <c r="U168" s="6" t="inlineStr"/>
       <c r="V168" s="6" t="inlineStr"/>
       <c r="W168" s="6" t="inlineStr"/>
+      <c r="X168" s="6" t="inlineStr"/>
+      <c r="Y168" s="6" t="inlineStr"/>
+      <c r="Z168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -15132,6 +15651,9 @@
       <c r="U169" s="6" t="inlineStr"/>
       <c r="V169" s="6" t="inlineStr"/>
       <c r="W169" s="6" t="inlineStr"/>
+      <c r="X169" s="6" t="inlineStr"/>
+      <c r="Y169" s="6" t="inlineStr"/>
+      <c r="Z169" s="6" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
@@ -15205,6 +15727,9 @@
       <c r="U170" s="6" t="inlineStr"/>
       <c r="V170" s="6" t="inlineStr"/>
       <c r="W170" s="6" t="inlineStr"/>
+      <c r="X170" s="6" t="inlineStr"/>
+      <c r="Y170" s="6" t="inlineStr"/>
+      <c r="Z170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -15278,6 +15803,9 @@
       <c r="U171" s="6" t="inlineStr"/>
       <c r="V171" s="6" t="inlineStr"/>
       <c r="W171" s="6" t="inlineStr"/>
+      <c r="X171" s="6" t="inlineStr"/>
+      <c r="Y171" s="6" t="inlineStr"/>
+      <c r="Z171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
@@ -15351,6 +15879,9 @@
       <c r="U172" s="6" t="inlineStr"/>
       <c r="V172" s="6" t="inlineStr"/>
       <c r="W172" s="6" t="inlineStr"/>
+      <c r="X172" s="6" t="inlineStr"/>
+      <c r="Y172" s="6" t="inlineStr"/>
+      <c r="Z172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -15428,6 +15959,9 @@
       <c r="U173" s="6" t="inlineStr"/>
       <c r="V173" s="6" t="inlineStr"/>
       <c r="W173" s="6" t="inlineStr"/>
+      <c r="X173" s="6" t="inlineStr"/>
+      <c r="Y173" s="6" t="inlineStr"/>
+      <c r="Z173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
@@ -15509,6 +16043,9 @@
       <c r="U174" s="6" t="inlineStr"/>
       <c r="V174" s="6" t="inlineStr"/>
       <c r="W174" s="6" t="inlineStr"/>
+      <c r="X174" s="6" t="inlineStr"/>
+      <c r="Y174" s="6" t="inlineStr"/>
+      <c r="Z174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -15582,6 +16119,9 @@
       <c r="U175" s="6" t="inlineStr"/>
       <c r="V175" s="6" t="inlineStr"/>
       <c r="W175" s="6" t="inlineStr"/>
+      <c r="X175" s="6" t="inlineStr"/>
+      <c r="Y175" s="6" t="inlineStr"/>
+      <c r="Z175" s="6" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -15651,6 +16191,9 @@
       <c r="U176" s="6" t="inlineStr"/>
       <c r="V176" s="6" t="inlineStr"/>
       <c r="W176" s="6" t="inlineStr"/>
+      <c r="X176" s="6" t="inlineStr"/>
+      <c r="Y176" s="6" t="inlineStr"/>
+      <c r="Z176" s="6" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -15728,6 +16271,9 @@
       <c r="U177" s="6" t="inlineStr"/>
       <c r="V177" s="6" t="inlineStr"/>
       <c r="W177" s="6" t="inlineStr"/>
+      <c r="X177" s="6" t="inlineStr"/>
+      <c r="Y177" s="6" t="inlineStr"/>
+      <c r="Z177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -15797,6 +16343,9 @@
       <c r="U178" s="6" t="inlineStr"/>
       <c r="V178" s="6" t="inlineStr"/>
       <c r="W178" s="6" t="inlineStr"/>
+      <c r="X178" s="6" t="inlineStr"/>
+      <c r="Y178" s="6" t="inlineStr"/>
+      <c r="Z178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -15870,6 +16419,9 @@
       <c r="U179" s="6" t="inlineStr"/>
       <c r="V179" s="6" t="inlineStr"/>
       <c r="W179" s="6" t="inlineStr"/>
+      <c r="X179" s="6" t="inlineStr"/>
+      <c r="Y179" s="6" t="inlineStr"/>
+      <c r="Z179" s="6" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -15943,6 +16495,9 @@
       <c r="U180" s="6" t="inlineStr"/>
       <c r="V180" s="6" t="inlineStr"/>
       <c r="W180" s="6" t="inlineStr"/>
+      <c r="X180" s="6" t="inlineStr"/>
+      <c r="Y180" s="6" t="inlineStr"/>
+      <c r="Z180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -16012,6 +16567,9 @@
       <c r="U181" s="6" t="inlineStr"/>
       <c r="V181" s="6" t="inlineStr"/>
       <c r="W181" s="6" t="inlineStr"/>
+      <c r="X181" s="6" t="inlineStr"/>
+      <c r="Y181" s="6" t="inlineStr"/>
+      <c r="Z181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -16081,6 +16639,9 @@
       <c r="U182" s="6" t="inlineStr"/>
       <c r="V182" s="6" t="inlineStr"/>
       <c r="W182" s="6" t="inlineStr"/>
+      <c r="X182" s="6" t="inlineStr"/>
+      <c r="Y182" s="6" t="inlineStr"/>
+      <c r="Z182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -16154,6 +16715,9 @@
       <c r="U183" s="6" t="inlineStr"/>
       <c r="V183" s="6" t="inlineStr"/>
       <c r="W183" s="6" t="inlineStr"/>
+      <c r="X183" s="6" t="inlineStr"/>
+      <c r="Y183" s="6" t="inlineStr"/>
+      <c r="Z183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -16247,6 +16811,9 @@
       <c r="U184" s="6" t="inlineStr"/>
       <c r="V184" s="6" t="inlineStr"/>
       <c r="W184" s="6" t="inlineStr"/>
+      <c r="X184" s="6" t="inlineStr"/>
+      <c r="Y184" s="6" t="inlineStr"/>
+      <c r="Z184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -16324,6 +16891,9 @@
       <c r="U185" s="6" t="inlineStr"/>
       <c r="V185" s="6" t="inlineStr"/>
       <c r="W185" s="6" t="inlineStr"/>
+      <c r="X185" s="6" t="inlineStr"/>
+      <c r="Y185" s="6" t="inlineStr"/>
+      <c r="Z185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
@@ -16405,6 +16975,9 @@
       <c r="U186" s="6" t="inlineStr"/>
       <c r="V186" s="6" t="inlineStr"/>
       <c r="W186" s="6" t="inlineStr"/>
+      <c r="X186" s="6" t="inlineStr"/>
+      <c r="Y186" s="6" t="inlineStr"/>
+      <c r="Z186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -16486,6 +17059,9 @@
       <c r="U187" s="6" t="inlineStr"/>
       <c r="V187" s="6" t="inlineStr"/>
       <c r="W187" s="6" t="inlineStr"/>
+      <c r="X187" s="6" t="inlineStr"/>
+      <c r="Y187" s="6" t="inlineStr"/>
+      <c r="Z187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -16571,6 +17147,9 @@
       <c r="U188" s="6" t="inlineStr"/>
       <c r="V188" s="6" t="inlineStr"/>
       <c r="W188" s="6" t="inlineStr"/>
+      <c r="X188" s="6" t="inlineStr"/>
+      <c r="Y188" s="6" t="inlineStr"/>
+      <c r="Z188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -16648,6 +17227,9 @@
       <c r="U189" s="6" t="inlineStr"/>
       <c r="V189" s="6" t="inlineStr"/>
       <c r="W189" s="6" t="inlineStr"/>
+      <c r="X189" s="6" t="inlineStr"/>
+      <c r="Y189" s="6" t="inlineStr"/>
+      <c r="Z189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -16725,6 +17307,9 @@
       <c r="U190" s="6" t="inlineStr"/>
       <c r="V190" s="6" t="inlineStr"/>
       <c r="W190" s="6" t="inlineStr"/>
+      <c r="X190" s="6" t="inlineStr"/>
+      <c r="Y190" s="6" t="inlineStr"/>
+      <c r="Z190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -16798,6 +17383,9 @@
       <c r="U191" s="6" t="inlineStr"/>
       <c r="V191" s="6" t="inlineStr"/>
       <c r="W191" s="6" t="inlineStr"/>
+      <c r="X191" s="6" t="inlineStr"/>
+      <c r="Y191" s="6" t="inlineStr"/>
+      <c r="Z191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
@@ -16871,6 +17459,9 @@
       <c r="U192" s="6" t="inlineStr"/>
       <c r="V192" s="6" t="inlineStr"/>
       <c r="W192" s="6" t="inlineStr"/>
+      <c r="X192" s="6" t="inlineStr"/>
+      <c r="Y192" s="6" t="inlineStr"/>
+      <c r="Z192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -16956,6 +17547,9 @@
       <c r="U193" s="6" t="inlineStr"/>
       <c r="V193" s="6" t="inlineStr"/>
       <c r="W193" s="6" t="inlineStr"/>
+      <c r="X193" s="6" t="inlineStr"/>
+      <c r="Y193" s="6" t="inlineStr"/>
+      <c r="Z193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
@@ -17029,6 +17623,9 @@
       <c r="U194" s="6" t="inlineStr"/>
       <c r="V194" s="6" t="inlineStr"/>
       <c r="W194" s="6" t="inlineStr"/>
+      <c r="X194" s="6" t="inlineStr"/>
+      <c r="Y194" s="6" t="inlineStr"/>
+      <c r="Z194" s="6" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -17118,6 +17715,9 @@
       <c r="U195" s="6" t="inlineStr"/>
       <c r="V195" s="6" t="inlineStr"/>
       <c r="W195" s="6" t="inlineStr"/>
+      <c r="X195" s="6" t="inlineStr"/>
+      <c r="Y195" s="6" t="inlineStr"/>
+      <c r="Z195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -17191,6 +17791,9 @@
       <c r="U196" s="6" t="inlineStr"/>
       <c r="V196" s="6" t="inlineStr"/>
       <c r="W196" s="6" t="inlineStr"/>
+      <c r="X196" s="6" t="inlineStr"/>
+      <c r="Y196" s="6" t="inlineStr"/>
+      <c r="Z196" s="6" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -17268,6 +17871,9 @@
       <c r="U197" s="6" t="inlineStr"/>
       <c r="V197" s="6" t="inlineStr"/>
       <c r="W197" s="6" t="inlineStr"/>
+      <c r="X197" s="6" t="inlineStr"/>
+      <c r="Y197" s="6" t="inlineStr"/>
+      <c r="Z197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
@@ -17341,6 +17947,9 @@
       <c r="U198" s="6" t="inlineStr"/>
       <c r="V198" s="6" t="inlineStr"/>
       <c r="W198" s="6" t="inlineStr"/>
+      <c r="X198" s="6" t="inlineStr"/>
+      <c r="Y198" s="6" t="inlineStr"/>
+      <c r="Z198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -17414,6 +18023,9 @@
       <c r="U199" s="6" t="inlineStr"/>
       <c r="V199" s="6" t="inlineStr"/>
       <c r="W199" s="6" t="inlineStr"/>
+      <c r="X199" s="6" t="inlineStr"/>
+      <c r="Y199" s="6" t="inlineStr"/>
+      <c r="Z199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
@@ -17499,6 +18111,9 @@
       <c r="U200" s="6" t="inlineStr"/>
       <c r="V200" s="6" t="inlineStr"/>
       <c r="W200" s="6" t="inlineStr"/>
+      <c r="X200" s="6" t="inlineStr"/>
+      <c r="Y200" s="6" t="inlineStr"/>
+      <c r="Z200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -17584,6 +18199,9 @@
       <c r="U201" s="6" t="inlineStr"/>
       <c r="V201" s="6" t="inlineStr"/>
       <c r="W201" s="6" t="inlineStr"/>
+      <c r="X201" s="6" t="inlineStr"/>
+      <c r="Y201" s="6" t="inlineStr"/>
+      <c r="Z201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
@@ -17673,6 +18291,9 @@
       <c r="U202" s="6" t="inlineStr"/>
       <c r="V202" s="6" t="inlineStr"/>
       <c r="W202" s="6" t="inlineStr"/>
+      <c r="X202" s="6" t="inlineStr"/>
+      <c r="Y202" s="6" t="inlineStr"/>
+      <c r="Z202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -17754,6 +18375,9 @@
       <c r="U203" s="6" t="inlineStr"/>
       <c r="V203" s="6" t="inlineStr"/>
       <c r="W203" s="6" t="inlineStr"/>
+      <c r="X203" s="6" t="inlineStr"/>
+      <c r="Y203" s="6" t="inlineStr"/>
+      <c r="Z203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -17839,6 +18463,9 @@
       <c r="U204" s="6" t="inlineStr"/>
       <c r="V204" s="6" t="inlineStr"/>
       <c r="W204" s="6" t="inlineStr"/>
+      <c r="X204" s="6" t="inlineStr"/>
+      <c r="Y204" s="6" t="inlineStr"/>
+      <c r="Z204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -17908,6 +18535,9 @@
       <c r="U205" s="6" t="inlineStr"/>
       <c r="V205" s="6" t="inlineStr"/>
       <c r="W205" s="6" t="inlineStr"/>
+      <c r="X205" s="6" t="inlineStr"/>
+      <c r="Y205" s="6" t="inlineStr"/>
+      <c r="Z205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
@@ -17981,6 +18611,9 @@
       <c r="U206" s="6" t="inlineStr"/>
       <c r="V206" s="6" t="inlineStr"/>
       <c r="W206" s="6" t="inlineStr"/>
+      <c r="X206" s="6" t="inlineStr"/>
+      <c r="Y206" s="6" t="inlineStr"/>
+      <c r="Z206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -18066,6 +18699,9 @@
       <c r="U207" s="6" t="inlineStr"/>
       <c r="V207" s="6" t="inlineStr"/>
       <c r="W207" s="6" t="inlineStr"/>
+      <c r="X207" s="6" t="inlineStr"/>
+      <c r="Y207" s="6" t="inlineStr"/>
+      <c r="Z207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
@@ -18151,6 +18787,9 @@
       <c r="U208" s="6" t="inlineStr"/>
       <c r="V208" s="6" t="inlineStr"/>
       <c r="W208" s="6" t="inlineStr"/>
+      <c r="X208" s="6" t="inlineStr"/>
+      <c r="Y208" s="6" t="inlineStr"/>
+      <c r="Z208" s="6" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -18224,6 +18863,9 @@
       <c r="U209" s="6" t="inlineStr"/>
       <c r="V209" s="6" t="inlineStr"/>
       <c r="W209" s="6" t="inlineStr"/>
+      <c r="X209" s="6" t="inlineStr"/>
+      <c r="Y209" s="6" t="inlineStr"/>
+      <c r="Z209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -18305,6 +18947,9 @@
       <c r="U210" s="6" t="inlineStr"/>
       <c r="V210" s="6" t="inlineStr"/>
       <c r="W210" s="6" t="inlineStr"/>
+      <c r="X210" s="6" t="inlineStr"/>
+      <c r="Y210" s="6" t="inlineStr"/>
+      <c r="Z210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -18386,6 +19031,9 @@
       <c r="U211" s="6" t="inlineStr"/>
       <c r="V211" s="6" t="inlineStr"/>
       <c r="W211" s="6" t="inlineStr"/>
+      <c r="X211" s="6" t="inlineStr"/>
+      <c r="Y211" s="6" t="inlineStr"/>
+      <c r="Z211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
@@ -18471,6 +19119,9 @@
       <c r="U212" s="6" t="inlineStr"/>
       <c r="V212" s="6" t="inlineStr"/>
       <c r="W212" s="6" t="inlineStr"/>
+      <c r="X212" s="6" t="inlineStr"/>
+      <c r="Y212" s="6" t="inlineStr"/>
+      <c r="Z212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -18556,6 +19207,9 @@
       <c r="U213" s="6" t="inlineStr"/>
       <c r="V213" s="6" t="inlineStr"/>
       <c r="W213" s="6" t="inlineStr"/>
+      <c r="X213" s="6" t="inlineStr"/>
+      <c r="Y213" s="6" t="inlineStr"/>
+      <c r="Z213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -18645,6 +19299,9 @@
       <c r="U214" s="6" t="inlineStr"/>
       <c r="V214" s="6" t="inlineStr"/>
       <c r="W214" s="6" t="inlineStr"/>
+      <c r="X214" s="6" t="inlineStr"/>
+      <c r="Y214" s="6" t="inlineStr"/>
+      <c r="Z214" s="6" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -18730,6 +19387,9 @@
       <c r="U215" s="6" t="inlineStr"/>
       <c r="V215" s="6" t="inlineStr"/>
       <c r="W215" s="6" t="inlineStr"/>
+      <c r="X215" s="6" t="inlineStr"/>
+      <c r="Y215" s="6" t="inlineStr"/>
+      <c r="Z215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -18799,6 +19459,9 @@
       <c r="U216" s="6" t="inlineStr"/>
       <c r="V216" s="6" t="inlineStr"/>
       <c r="W216" s="6" t="inlineStr"/>
+      <c r="X216" s="6" t="inlineStr"/>
+      <c r="Y216" s="6" t="inlineStr"/>
+      <c r="Z216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -18880,6 +19543,9 @@
       <c r="U217" s="6" t="inlineStr"/>
       <c r="V217" s="6" t="inlineStr"/>
       <c r="W217" s="6" t="inlineStr"/>
+      <c r="X217" s="6" t="inlineStr"/>
+      <c r="Y217" s="6" t="inlineStr"/>
+      <c r="Z217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -18969,6 +19635,9 @@
       <c r="U218" s="6" t="inlineStr"/>
       <c r="V218" s="6" t="inlineStr"/>
       <c r="W218" s="6" t="inlineStr"/>
+      <c r="X218" s="6" t="inlineStr"/>
+      <c r="Y218" s="6" t="inlineStr"/>
+      <c r="Z218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -19050,6 +19719,9 @@
       <c r="U219" s="6" t="inlineStr"/>
       <c r="V219" s="6" t="inlineStr"/>
       <c r="W219" s="6" t="inlineStr"/>
+      <c r="X219" s="6" t="inlineStr"/>
+      <c r="Y219" s="6" t="inlineStr"/>
+      <c r="Z219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
@@ -19123,6 +19795,9 @@
       <c r="U220" s="6" t="inlineStr"/>
       <c r="V220" s="6" t="inlineStr"/>
       <c r="W220" s="6" t="inlineStr"/>
+      <c r="X220" s="6" t="inlineStr"/>
+      <c r="Y220" s="6" t="inlineStr"/>
+      <c r="Z220" s="6" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -19204,6 +19879,9 @@
       <c r="U221" s="6" t="inlineStr"/>
       <c r="V221" s="6" t="inlineStr"/>
       <c r="W221" s="6" t="inlineStr"/>
+      <c r="X221" s="6" t="inlineStr"/>
+      <c r="Y221" s="6" t="inlineStr"/>
+      <c r="Z221" s="6" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
@@ -19289,6 +19967,9 @@
       <c r="U222" s="6" t="inlineStr"/>
       <c r="V222" s="6" t="inlineStr"/>
       <c r="W222" s="6" t="inlineStr"/>
+      <c r="X222" s="6" t="inlineStr"/>
+      <c r="Y222" s="6" t="inlineStr"/>
+      <c r="Z222" s="6" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -19374,6 +20055,9 @@
       <c r="U223" s="6" t="inlineStr"/>
       <c r="V223" s="6" t="inlineStr"/>
       <c r="W223" s="6" t="inlineStr"/>
+      <c r="X223" s="6" t="inlineStr"/>
+      <c r="Y223" s="6" t="inlineStr"/>
+      <c r="Z223" s="6" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -19455,6 +20139,9 @@
       <c r="U224" s="6" t="inlineStr"/>
       <c r="V224" s="6" t="inlineStr"/>
       <c r="W224" s="6" t="inlineStr"/>
+      <c r="X224" s="6" t="inlineStr"/>
+      <c r="Y224" s="6" t="inlineStr"/>
+      <c r="Z224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -19540,6 +20227,9 @@
       <c r="U225" s="6" t="inlineStr"/>
       <c r="V225" s="6" t="inlineStr"/>
       <c r="W225" s="6" t="inlineStr"/>
+      <c r="X225" s="6" t="inlineStr"/>
+      <c r="Y225" s="6" t="inlineStr"/>
+      <c r="Z225" s="6" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
@@ -19621,6 +20311,9 @@
       <c r="U226" s="6" t="inlineStr"/>
       <c r="V226" s="6" t="inlineStr"/>
       <c r="W226" s="6" t="inlineStr"/>
+      <c r="X226" s="6" t="inlineStr"/>
+      <c r="Y226" s="6" t="inlineStr"/>
+      <c r="Z226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -19702,6 +20395,9 @@
       <c r="U227" s="6" t="inlineStr"/>
       <c r="V227" s="6" t="inlineStr"/>
       <c r="W227" s="6" t="inlineStr"/>
+      <c r="X227" s="6" t="inlineStr"/>
+      <c r="Y227" s="6" t="inlineStr"/>
+      <c r="Z227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -19787,6 +20483,9 @@
       <c r="U228" s="6" t="inlineStr"/>
       <c r="V228" s="6" t="inlineStr"/>
       <c r="W228" s="6" t="inlineStr"/>
+      <c r="X228" s="6" t="inlineStr"/>
+      <c r="Y228" s="6" t="inlineStr"/>
+      <c r="Z228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -19868,6 +20567,9 @@
       <c r="U229" s="6" t="inlineStr"/>
       <c r="V229" s="6" t="inlineStr"/>
       <c r="W229" s="6" t="inlineStr"/>
+      <c r="X229" s="6" t="inlineStr"/>
+      <c r="Y229" s="6" t="inlineStr"/>
+      <c r="Z229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -19953,6 +20655,9 @@
       <c r="U230" s="6" t="inlineStr"/>
       <c r="V230" s="6" t="inlineStr"/>
       <c r="W230" s="6" t="inlineStr"/>
+      <c r="X230" s="6" t="inlineStr"/>
+      <c r="Y230" s="6" t="inlineStr"/>
+      <c r="Z230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -20034,6 +20739,9 @@
       <c r="U231" s="6" t="inlineStr"/>
       <c r="V231" s="6" t="inlineStr"/>
       <c r="W231" s="6" t="inlineStr"/>
+      <c r="X231" s="6" t="inlineStr"/>
+      <c r="Y231" s="6" t="inlineStr"/>
+      <c r="Z231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -20107,6 +20815,9 @@
       <c r="U232" s="6" t="inlineStr"/>
       <c r="V232" s="6" t="inlineStr"/>
       <c r="W232" s="6" t="inlineStr"/>
+      <c r="X232" s="6" t="inlineStr"/>
+      <c r="Y232" s="6" t="inlineStr"/>
+      <c r="Z232" s="6" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -20196,6 +20907,9 @@
       <c r="U233" s="6" t="inlineStr"/>
       <c r="V233" s="6" t="inlineStr"/>
       <c r="W233" s="6" t="inlineStr"/>
+      <c r="X233" s="6" t="inlineStr"/>
+      <c r="Y233" s="6" t="inlineStr"/>
+      <c r="Z233" s="6" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
@@ -20273,6 +20987,9 @@
       <c r="U234" s="6" t="inlineStr"/>
       <c r="V234" s="6" t="inlineStr"/>
       <c r="W234" s="6" t="inlineStr"/>
+      <c r="X234" s="6" t="inlineStr"/>
+      <c r="Y234" s="6" t="inlineStr"/>
+      <c r="Z234" s="6" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -20346,6 +21063,9 @@
       <c r="U235" s="6" t="inlineStr"/>
       <c r="V235" s="6" t="inlineStr"/>
       <c r="W235" s="6" t="inlineStr"/>
+      <c r="X235" s="6" t="inlineStr"/>
+      <c r="Y235" s="6" t="inlineStr"/>
+      <c r="Z235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
@@ -20423,6 +21143,9 @@
       <c r="U236" s="6" t="inlineStr"/>
       <c r="V236" s="6" t="inlineStr"/>
       <c r="W236" s="6" t="inlineStr"/>
+      <c r="X236" s="6" t="inlineStr"/>
+      <c r="Y236" s="6" t="inlineStr"/>
+      <c r="Z236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -20496,6 +21219,9 @@
       <c r="U237" s="6" t="inlineStr"/>
       <c r="V237" s="6" t="inlineStr"/>
       <c r="W237" s="6" t="inlineStr"/>
+      <c r="X237" s="6" t="inlineStr"/>
+      <c r="Y237" s="6" t="inlineStr"/>
+      <c r="Z237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -20573,6 +21299,9 @@
       <c r="U238" s="6" t="inlineStr"/>
       <c r="V238" s="6" t="inlineStr"/>
       <c r="W238" s="6" t="inlineStr"/>
+      <c r="X238" s="6" t="inlineStr"/>
+      <c r="Y238" s="6" t="inlineStr"/>
+      <c r="Z238" s="6" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -20646,6 +21375,9 @@
       <c r="U239" s="6" t="inlineStr"/>
       <c r="V239" s="6" t="inlineStr"/>
       <c r="W239" s="6" t="inlineStr"/>
+      <c r="X239" s="6" t="inlineStr"/>
+      <c r="Y239" s="6" t="inlineStr"/>
+      <c r="Z239" s="6" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
@@ -20719,6 +21451,9 @@
       <c r="U240" s="6" t="inlineStr"/>
       <c r="V240" s="6" t="inlineStr"/>
       <c r="W240" s="6" t="inlineStr"/>
+      <c r="X240" s="6" t="inlineStr"/>
+      <c r="Y240" s="6" t="inlineStr"/>
+      <c r="Z240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -20804,6 +21539,9 @@
         </is>
       </c>
       <c r="W241" s="6" t="inlineStr"/>
+      <c r="X241" s="6" t="inlineStr"/>
+      <c r="Y241" s="6" t="inlineStr"/>
+      <c r="Z241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -20893,6 +21631,9 @@
         </is>
       </c>
       <c r="W242" s="6" t="inlineStr"/>
+      <c r="X242" s="6" t="inlineStr"/>
+      <c r="Y242" s="6" t="inlineStr"/>
+      <c r="Z242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -20978,6 +21719,9 @@
         </is>
       </c>
       <c r="W243" s="6" t="inlineStr"/>
+      <c r="X243" s="6" t="inlineStr"/>
+      <c r="Y243" s="6" t="inlineStr"/>
+      <c r="Z243" s="6" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
@@ -21059,6 +21803,9 @@
         </is>
       </c>
       <c r="W244" s="6" t="inlineStr"/>
+      <c r="X244" s="6" t="inlineStr"/>
+      <c r="Y244" s="6" t="inlineStr"/>
+      <c r="Z244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -21144,6 +21891,9 @@
         </is>
       </c>
       <c r="W245" s="6" t="inlineStr"/>
+      <c r="X245" s="6" t="inlineStr"/>
+      <c r="Y245" s="6" t="inlineStr"/>
+      <c r="Z245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -21233,6 +21983,9 @@
         </is>
       </c>
       <c r="W246" s="6" t="inlineStr"/>
+      <c r="X246" s="6" t="inlineStr"/>
+      <c r="Y246" s="6" t="inlineStr"/>
+      <c r="Z246" s="6" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -21322,6 +22075,9 @@
         </is>
       </c>
       <c r="W247" s="6" t="inlineStr"/>
+      <c r="X247" s="6" t="inlineStr"/>
+      <c r="Y247" s="6" t="inlineStr"/>
+      <c r="Z247" s="6" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
@@ -21411,6 +22167,9 @@
         </is>
       </c>
       <c r="W248" s="6" t="inlineStr"/>
+      <c r="X248" s="6" t="inlineStr"/>
+      <c r="Y248" s="6" t="inlineStr"/>
+      <c r="Z248" s="6" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -21496,6 +22255,9 @@
         </is>
       </c>
       <c r="W249" s="6" t="inlineStr"/>
+      <c r="X249" s="6" t="inlineStr"/>
+      <c r="Y249" s="6" t="inlineStr"/>
+      <c r="Z249" s="6" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
@@ -21581,6 +22343,9 @@
         </is>
       </c>
       <c r="W250" s="6" t="inlineStr"/>
+      <c r="X250" s="6" t="inlineStr"/>
+      <c r="Y250" s="6" t="inlineStr"/>
+      <c r="Z250" s="6" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -21662,6 +22427,9 @@
         </is>
       </c>
       <c r="W251" s="6" t="inlineStr"/>
+      <c r="X251" s="6" t="inlineStr"/>
+      <c r="Y251" s="6" t="inlineStr"/>
+      <c r="Z251" s="6" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -21743,6 +22511,9 @@
         </is>
       </c>
       <c r="W252" s="6" t="inlineStr"/>
+      <c r="X252" s="6" t="inlineStr"/>
+      <c r="Y252" s="6" t="inlineStr"/>
+      <c r="Z252" s="6" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -21828,6 +22599,9 @@
         </is>
       </c>
       <c r="W253" s="6" t="inlineStr"/>
+      <c r="X253" s="6" t="inlineStr"/>
+      <c r="Y253" s="6" t="inlineStr"/>
+      <c r="Z253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
@@ -21917,6 +22691,9 @@
         </is>
       </c>
       <c r="W254" s="6" t="inlineStr"/>
+      <c r="X254" s="6" t="inlineStr"/>
+      <c r="Y254" s="6" t="inlineStr"/>
+      <c r="Z254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -22002,6 +22779,9 @@
         </is>
       </c>
       <c r="W255" s="6" t="inlineStr"/>
+      <c r="X255" s="6" t="inlineStr"/>
+      <c r="Y255" s="6" t="inlineStr"/>
+      <c r="Z255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -22087,6 +22867,9 @@
         </is>
       </c>
       <c r="W256" s="6" t="inlineStr"/>
+      <c r="X256" s="6" t="inlineStr"/>
+      <c r="Y256" s="6" t="inlineStr"/>
+      <c r="Z256" s="6" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -22176,6 +22959,9 @@
         </is>
       </c>
       <c r="W257" s="6" t="inlineStr"/>
+      <c r="X257" s="6" t="inlineStr"/>
+      <c r="Y257" s="6" t="inlineStr"/>
+      <c r="Z257" s="6" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
@@ -22257,6 +23043,9 @@
         </is>
       </c>
       <c r="W258" s="6" t="inlineStr"/>
+      <c r="X258" s="6" t="inlineStr"/>
+      <c r="Y258" s="6" t="inlineStr"/>
+      <c r="Z258" s="6" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -22338,6 +23127,9 @@
         </is>
       </c>
       <c r="W259" s="6" t="inlineStr"/>
+      <c r="X259" s="6" t="inlineStr"/>
+      <c r="Y259" s="6" t="inlineStr"/>
+      <c r="Z259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -22431,6 +23223,9 @@
           <t>US-dominant</t>
         </is>
       </c>
+      <c r="X260" s="6" t="inlineStr"/>
+      <c r="Y260" s="6" t="inlineStr"/>
+      <c r="Z260" s="6" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
@@ -22524,6 +23319,9 @@
           <t>US-dominant</t>
         </is>
       </c>
+      <c r="X261" s="6" t="inlineStr"/>
+      <c r="Y261" s="6" t="inlineStr"/>
+      <c r="Z261" s="6" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
@@ -22613,6 +23411,9 @@
           <t>US / Austin metro</t>
         </is>
       </c>
+      <c r="X262" s="6" t="inlineStr"/>
+      <c r="Y262" s="6" t="inlineStr"/>
+      <c r="Z262" s="6" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
@@ -22702,6 +23503,9 @@
           <t>US-dominant</t>
         </is>
       </c>
+      <c r="X263" s="6" t="inlineStr"/>
+      <c r="Y263" s="6" t="inlineStr"/>
+      <c r="Z263" s="6" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
@@ -22791,6 +23595,9 @@
           <t>US + global</t>
         </is>
       </c>
+      <c r="X264" s="6" t="inlineStr"/>
+      <c r="Y264" s="6" t="inlineStr"/>
+      <c r="Z264" s="6" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
@@ -22880,6 +23687,9 @@
           <t>US Latino evangelical + Latin America</t>
         </is>
       </c>
+      <c r="X265" s="6" t="inlineStr"/>
+      <c r="Y265" s="6" t="inlineStr"/>
+      <c r="Z265" s="6" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
@@ -22969,6 +23779,9 @@
           <t>US</t>
         </is>
       </c>
+      <c r="X266" s="6" t="inlineStr"/>
+      <c r="Y266" s="6" t="inlineStr"/>
+      <c r="Z266" s="6" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -23058,6 +23871,9 @@
         </is>
       </c>
       <c r="W267" s="6" t="inlineStr"/>
+      <c r="X267" s="6" t="inlineStr"/>
+      <c r="Y267" s="6" t="inlineStr"/>
+      <c r="Z267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
@@ -23147,6 +23963,9 @@
         </is>
       </c>
       <c r="W268" s="6" t="inlineStr"/>
+      <c r="X268" s="6" t="inlineStr"/>
+      <c r="Y268" s="6" t="inlineStr"/>
+      <c r="Z268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
@@ -23232,6 +24051,9 @@
         </is>
       </c>
       <c r="W269" s="6" t="inlineStr"/>
+      <c r="X269" s="6" t="inlineStr"/>
+      <c r="Y269" s="6" t="inlineStr"/>
+      <c r="Z269" s="6" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
@@ -23345,6 +24167,9 @@
           <t>US-dominant</t>
         </is>
       </c>
+      <c r="X270" s="6" t="inlineStr"/>
+      <c r="Y270" s="6" t="inlineStr"/>
+      <c r="Z270" s="6" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
@@ -23434,6 +24259,9 @@
         </is>
       </c>
       <c r="W271" s="6" t="inlineStr"/>
+      <c r="X271" s="6" t="inlineStr"/>
+      <c r="Y271" s="6" t="inlineStr"/>
+      <c r="Z271" s="6" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
@@ -23523,6 +24351,9 @@
         </is>
       </c>
       <c r="W272" s="6" t="inlineStr"/>
+      <c r="X272" s="6" t="inlineStr"/>
+      <c r="Y272" s="6" t="inlineStr"/>
+      <c r="Z272" s="6" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
@@ -23612,6 +24443,9 @@
         </is>
       </c>
       <c r="W273" s="6" t="inlineStr"/>
+      <c r="X273" s="6" t="inlineStr"/>
+      <c r="Y273" s="6" t="inlineStr"/>
+      <c r="Z273" s="6" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
@@ -23705,6 +24539,9 @@
         </is>
       </c>
       <c r="W274" s="6" t="inlineStr"/>
+      <c r="X274" s="6" t="inlineStr"/>
+      <c r="Y274" s="6" t="inlineStr"/>
+      <c r="Z274" s="6" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -23790,6 +24627,9 @@
         </is>
       </c>
       <c r="W275" s="6" t="inlineStr"/>
+      <c r="X275" s="6" t="inlineStr"/>
+      <c r="Y275" s="6" t="inlineStr"/>
+      <c r="Z275" s="6" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
@@ -23879,6 +24719,9 @@
         </is>
       </c>
       <c r="W276" s="6" t="inlineStr"/>
+      <c r="X276" s="6" t="inlineStr"/>
+      <c r="Y276" s="6" t="inlineStr"/>
+      <c r="Z276" s="6" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -23968,6 +24811,9 @@
         </is>
       </c>
       <c r="W277" s="6" t="inlineStr"/>
+      <c r="X277" s="6" t="inlineStr"/>
+      <c r="Y277" s="6" t="inlineStr"/>
+      <c r="Z277" s="6" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
@@ -24053,6 +24899,9 @@
         </is>
       </c>
       <c r="W278" s="6" t="inlineStr"/>
+      <c r="X278" s="6" t="inlineStr"/>
+      <c r="Y278" s="6" t="inlineStr"/>
+      <c r="Z278" s="6" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -24142,36 +24991,39 @@
         </is>
       </c>
       <c r="W279" s="6" t="inlineStr"/>
+      <c r="X279" s="6" t="inlineStr"/>
+      <c r="Y279" s="6" t="inlineStr"/>
+      <c r="Z279" s="6" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>inf-08924d4c</t>
+          <t>inf-41a8539e</t>
         </is>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>Chad Prather</t>
+          <t>Ellisa Allen</t>
         </is>
       </c>
       <c r="C280" s="6" t="inlineStr">
         <is>
-          <t>YouTube (@ChadPrather1), Blaze Media</t>
+          <t>Podcast (Hey America; The Ellisa Show), YouTube/Rumble</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>YouTube 495K subscribers (live-verified 15 Jul 2026)</t>
+          <t>TBD -- verify (Audacy-distributed; spun off the chart-topping Dear America brand)</t>
         </is>
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Christian (evangelical)</t>
         </is>
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>Conservative commentary/comedy</t>
+          <t>Conservative; pop-culture/religion/entertainment</t>
         </is>
       </c>
       <c r="G280" s="6" t="inlineStr">
@@ -24181,17 +25033,17 @@
       </c>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>Blaze Media host and comedic conservative commentator; submitted by Andy as a Zionist ally. American, non-Jewish, Christian -- scarce profile; comedic register fits Johnnie's asymmetric-humor thesis.</t>
+          <t>Andy-submitted. President of the Dear America Foundation (charity for families of veterans, law enforcement and first responders); co-founder of Nine Twelve United; married to Graham Allen since 2009 (three children); featured by Liberty University as a military spouse. Talent is clear; the Israel-specific loyalty is inferred from Liberty + family proximity, NOT from her own cost-paid record.</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>youtube.com/@ChadPrather1</t>
+          <t>instagram.com/EllisaAllenOfficial; facebook.com/EllisaAllenOfficial; audacy.com/podcasts/hey-america-podcast-with-ellisa-allen-50771</t>
         </is>
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted; youtube.com/@ChadPrather1</t>
+          <t>Liberty University (liberty.edu/lp/hey-america) + Audacy podcast listing; Andy-submitted</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr"/>
@@ -24200,7 +25052,7 @@
       <c r="N280" s="6" t="inlineStr"/>
       <c r="O280" s="6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
       <c r="P280" s="6" t="inlineStr">
@@ -24210,16 +25062,16 @@
       </c>
       <c r="Q280" s="6" t="inlineStr">
         <is>
-          <t>Verify explicit Israel statements.</t>
+          <t>BEFORE roster placement, find HER OWN Israel signal: search Hey America / The Ellisa Show episodes for direct Israel content, and check for any yellow-ribbon/blue-square or Israel-trip signal. If none exists, she is a strong GATE-2 talent whose GATE-1 loyalty is unproven -- i.e. a Nurture candidate, not a confirmed roster member. Do not let the husband's record stand in for hers. Confirm exact Liberty affiliation (attended vs. military-spouse program).</t>
         </is>
       </c>
       <c r="R280" s="6" t="inlineStr"/>
-      <c r="S280" s="6" t="inlineStr">
-        <is>
-          <t>live-verified 15 Jul 2026</t>
-        </is>
-      </c>
-      <c r="T280" s="6" t="inlineStr"/>
+      <c r="S280" s="6" t="inlineStr"/>
+      <c r="T280" s="6" t="inlineStr">
+        <is>
+          <t>Graham Allen, Dear America Foundation, Liberty University, Nine Twelve United</t>
+        </is>
+      </c>
       <c r="U280" s="6" t="inlineStr">
         <is>
           <t>American</t>
@@ -24231,56 +25083,71 @@
         </is>
       </c>
       <c r="W280" s="6" t="inlineStr"/>
+      <c r="X280" s="6" t="inlineStr">
+        <is>
+          <t>NOT YET ESTABLISHED. No documented personal cost paid for a pro-Israel stance. Her Israel alignment is INFERRED, not proven: (1) institutional proximity -- Liberty University, whose Center for Israel is a direct Johnnie Moore connection and which invests in Israel and opposes BDS; (2) family -- married to Graham Allen (himself pro-tagged, though his own Israel signal is a PROXY via attacking Megyn Kelly, not a direct statement). This is the philosemitic/institutional-proximity signal (the John Hood / Josh Appel pattern), which Andy has ruled valid -- but it is proximity, not a personal record.</t>
+        </is>
+      </c>
+      <c r="Y280" s="6" t="inlineStr">
+        <is>
+          <t>GATE 2 PASSED. Established long-form host: hosts 'Hey America' (Audacy-distributed) and 'The Ellisa Show', spun off the chart-topping 'Dear America' podcast brand. Proven ability to hold a broadcast audience; the format is pop culture + religion + entertainment, i.e. conversational, not sermon -- exactly the under-served lane.</t>
+        </is>
+      </c>
+      <c r="Z280" s="6" t="inlineStr">
+        <is>
+          <t>https://www.liberty.edu/lp/hey-america/</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>inf-6b113ddd</t>
+          <t>inf-08924d4c</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>Todd Spears ('Hot Seat Todd')</t>
+          <t>Chad Prather</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>The Hotseat (podcast)</t>
+          <t>YouTube (@ChadPrather1), Blaze Media</t>
         </is>
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>Emerging podcast audience</t>
+          <t>YouTube 495K subscribers (live-verified 15 Jul 2026)</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Conservative commentary/comedy</t>
         </is>
       </c>
       <c r="G281" s="6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>pro</t>
         </is>
       </c>
       <c r="H281" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted podcast host ('Hot Seat Todd'). Could not verify his background or any Israel-related record in this pass.</t>
+          <t>Blaze Media host and comedic conservative commentator; submitted by Andy as a Zionist ally. American, non-Jewish, Christian -- scarce profile; comedic register fits Johnnie's asymmetric-humor thesis.</t>
         </is>
       </c>
       <c r="I281" s="6" t="inlineStr">
         <is>
-          <t>podcasts.apple.com/podcast/the-hotseat/id1824964289</t>
+          <t>youtube.com/@ChadPrather1</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted (unverified)</t>
+          <t>Andy-submitted; youtube.com/@ChadPrather1</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr"/>
@@ -24289,7 +25156,7 @@
       <c r="N281" s="6" t="inlineStr"/>
       <c r="O281" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P281" s="6" t="inlineStr">
@@ -24299,11 +25166,15 @@
       </c>
       <c r="Q281" s="6" t="inlineStr">
         <is>
-          <t>VERIFY IDENTITY AND STANCE -- no confirmable record found. Andy to confirm why flagged.</t>
+          <t>Verify explicit Israel statements.</t>
         </is>
       </c>
       <c r="R281" s="6" t="inlineStr"/>
-      <c r="S281" s="6" t="inlineStr"/>
+      <c r="S281" s="6" t="inlineStr">
+        <is>
+          <t>live-verified 15 Jul 2026</t>
+        </is>
+      </c>
       <c r="T281" s="6" t="inlineStr"/>
       <c r="U281" s="6" t="inlineStr">
         <is>
@@ -24316,26 +25187,29 @@
         </is>
       </c>
       <c r="W281" s="6" t="inlineStr"/>
+      <c r="X281" s="6" t="inlineStr"/>
+      <c r="Y281" s="6" t="inlineStr"/>
+      <c r="Z281" s="6" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>inf-0eddd72b</t>
+          <t>inf-6b113ddd</t>
         </is>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>Tim Pool</t>
+          <t>Todd Spears ('Hot Seat Todd')</t>
         </is>
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>Timcast IRL, YouTube/Rumble</t>
+          <t>The Hotseat (podcast)</t>
         </is>
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>YouTube 1.47M subscribers (live-verified 15 Jul 2026)</t>
+          <t>Emerging podcast audience</t>
         </is>
       </c>
       <c r="E282" s="6" t="inlineStr">
@@ -24345,27 +25219,27 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>Populist/independent</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G282" s="6" t="inlineStr">
         <is>
-          <t>yellowflag</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>YELLOW FLAG: huge independent audience, but a genuinely mixed record on this axis -- he platforms figures across the populist right including Israel-skeptical and America-First voices, and his own position has shifted. Not hostile; not a reliable ally. Note his show already appears on the Ad Fontes-style landscape as a Rumble-tier populist outlet.</t>
+          <t>Andy-submitted podcast host ('Hot Seat Todd'). Could not verify his background or any Israel-related record in this pass.</t>
         </is>
       </c>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>youtube.com/@Timcast, x.com/Timcast</t>
+          <t>podcasts.apple.com/podcast/the-hotseat/id1824964289</t>
         </is>
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted; public record</t>
+          <t>Andy-submitted (unverified)</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr"/>
@@ -24374,7 +25248,7 @@
       <c r="N282" s="6" t="inlineStr"/>
       <c r="O282" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P282" s="6" t="inlineStr">
@@ -24384,15 +25258,11 @@
       </c>
       <c r="Q282" s="6" t="inlineStr">
         <is>
-          <t>Monitor: he is a bellwether for where the populist-right audience is drifting. Apply the Graham/Cruz-criticism test to recent episodes.</t>
+          <t>VERIFY IDENTITY AND STANCE -- no confirmable record found. Andy to confirm why flagged.</t>
         </is>
       </c>
       <c r="R282" s="6" t="inlineStr"/>
-      <c r="S282" s="6" t="inlineStr">
-        <is>
-          <t>live-verified 15 Jul 2026</t>
-        </is>
-      </c>
+      <c r="S282" s="6" t="inlineStr"/>
       <c r="T282" s="6" t="inlineStr"/>
       <c r="U282" s="6" t="inlineStr">
         <is>
@@ -24405,56 +25275,59 @@
         </is>
       </c>
       <c r="W282" s="6" t="inlineStr"/>
+      <c r="X282" s="6" t="inlineStr"/>
+      <c r="Y282" s="6" t="inlineStr"/>
+      <c r="Z282" s="6" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>inf-824f1c10</t>
+          <t>inf-0eddd72b</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>Dan Burmawi</t>
+          <t>Tim Pool</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>Social media, speaking</t>
+          <t>Timcast IRL, YouTube/Rumble</t>
         </is>
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>Growing</t>
+          <t>YouTube 1.47M subscribers (live-verified 15 Jul 2026)</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>Former Muslim, now Christian/Zionist</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>Ex-Muslim pro-Israel advocacy</t>
+          <t>Populist/independent</t>
         </is>
       </c>
       <c r="G283" s="6" t="inlineStr">
         <is>
-          <t>pro</t>
+          <t>yellowflag</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>Former Muslim turned outspoken Zionist -- the same high-credibility profile as Mosab Hassan Yousef (already tracked): an ex-Muslim voice for Israel is uniquely persuasive to audiences that discount Jewish and Christian-Zionist advocates alike.</t>
+          <t>YELLOW FLAG: huge independent audience, but a genuinely mixed record on this axis -- he platforms figures across the populist right including Israel-skeptical and America-First voices, and his own position has shifted. Not hostile; not a reliable ally. Note his show already appears on the Ad Fontes-style landscape as a Rumble-tier populist outlet.</t>
         </is>
       </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>x.com/DanBurmawi</t>
+          <t>youtube.com/@Timcast, x.com/Timcast</t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted</t>
+          <t>Andy-submitted; public record</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr"/>
@@ -24463,7 +25336,7 @@
       <c r="N283" s="6" t="inlineStr"/>
       <c r="O283" s="6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P283" s="6" t="inlineStr">
@@ -24473,15 +25346,19 @@
       </c>
       <c r="Q283" s="6" t="inlineStr">
         <is>
-          <t>Verify biography and current platform size.</t>
+          <t>Monitor: he is a bellwether for where the populist-right audience is drifting. Apply the Graham/Cruz-criticism test to recent episodes.</t>
         </is>
       </c>
       <c r="R283" s="6" t="inlineStr"/>
-      <c r="S283" s="6" t="inlineStr"/>
+      <c r="S283" s="6" t="inlineStr">
+        <is>
+          <t>live-verified 15 Jul 2026</t>
+        </is>
+      </c>
       <c r="T283" s="6" t="inlineStr"/>
       <c r="U283" s="6" t="inlineStr">
         <is>
-          <t>American (Lebanese background)</t>
+          <t>American</t>
         </is>
       </c>
       <c r="V283" s="6" t="inlineStr">
@@ -24490,36 +25367,39 @@
         </is>
       </c>
       <c r="W283" s="6" t="inlineStr"/>
+      <c r="X283" s="6" t="inlineStr"/>
+      <c r="Y283" s="6" t="inlineStr"/>
+      <c r="Z283" s="6" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>inf-afbfb4f4</t>
+          <t>inf-824f1c10</t>
         </is>
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>Jamie Michell</t>
+          <t>Dan Burmawi</t>
         </is>
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>X (@JaimeeUSA)</t>
+          <t>Social media, speaking</t>
         </is>
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>X following</t>
+          <t>Growing</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Former Muslim, now Christian/Zionist</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>Conservative</t>
+          <t>Ex-Muslim pro-Israel advocacy</t>
         </is>
       </c>
       <c r="G284" s="6" t="inlineStr">
@@ -24529,17 +25409,17 @@
       </c>
       <c r="H284" s="6" t="inlineStr">
         <is>
-          <t>Qualifies on TWO criteria: (1) amplified rising Christian Zionist CUFI campus star Sam Brown (tracked) -- positive associational signal; (2) has attacked Candace Owens -- the attack-the-antisemites boost.</t>
+          <t>Former Muslim turned outspoken Zionist -- the same high-credibility profile as Mosab Hassan Yousef (already tracked): an ex-Muslim voice for Israel is uniquely persuasive to audiences that discount Jewish and Christian-Zionist advocates alike.</t>
         </is>
       </c>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>x.com/JaimeeUSA</t>
+          <t>x.com/DanBurmawi</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted (X posts unverifiable by Claude)</t>
+          <t>Andy-submitted</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr"/>
@@ -24548,7 +25428,7 @@
       <c r="N284" s="6" t="inlineStr"/>
       <c r="O284" s="6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P284" s="6" t="inlineStr">
@@ -24558,19 +25438,15 @@
       </c>
       <c r="Q284" s="6" t="inlineStr">
         <is>
-          <t>Verify platform size and the specific posts (X is not fetchable to me).</t>
+          <t>Verify biography and current platform size.</t>
         </is>
       </c>
       <c r="R284" s="6" t="inlineStr"/>
       <c r="S284" s="6" t="inlineStr"/>
-      <c r="T284" s="6" t="inlineStr">
-        <is>
-          <t>Sam Brown, Candace Owens</t>
-        </is>
-      </c>
+      <c r="T284" s="6" t="inlineStr"/>
       <c r="U284" s="6" t="inlineStr">
         <is>
-          <t>American</t>
+          <t>American (Lebanese background)</t>
         </is>
       </c>
       <c r="V284" s="6" t="inlineStr">
@@ -24579,36 +25455,39 @@
         </is>
       </c>
       <c r="W284" s="6" t="inlineStr"/>
+      <c r="X284" s="6" t="inlineStr"/>
+      <c r="Y284" s="6" t="inlineStr"/>
+      <c r="Z284" s="6" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>inf-28984b52</t>
+          <t>inf-afbfb4f4</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>Jacob Franczak</t>
+          <t>Jamie Michell</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>First Fruits of Zion (FFOZ) / media</t>
+          <t>X (@JaimeeUSA)</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>FFOZ audience</t>
+          <t>X following</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
         <is>
-          <t>Christian (Messianic-adjacent)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>Pro-Christian-Zionism theology</t>
+          <t>Conservative</t>
         </is>
       </c>
       <c r="G285" s="6" t="inlineStr">
@@ -24618,17 +25497,17 @@
       </c>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted via an FFOZ (First Fruits of Zion) piece countering Andrew Wilson's opposition to Christian Zionism -- i.e. defending Christian Zionism theologically against intra-Christian attack. That is precisely the doctrinal battlefront Johnnie's program cares about (supersessionism vs. covenant).</t>
+          <t>Qualifies on TWO criteria: (1) amplified rising Christian Zionist CUFI campus star Sam Brown (tracked) -- positive associational signal; (2) has attacked Candace Owens -- the attack-the-antisemites boost.</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
         <is>
-          <t>ffoz.org/messiah/watch/andrew-wilson-opposes-christian-zionism</t>
+          <t>x.com/JaimeeUSA</t>
         </is>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>ffoz.org (link supplied by Andy)</t>
+          <t>Andy-submitted (X posts unverifiable by Claude)</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr"/>
@@ -24637,7 +25516,7 @@
       <c r="N285" s="6" t="inlineStr"/>
       <c r="O285" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="P285" s="6" t="inlineStr">
@@ -24647,15 +25526,19 @@
       </c>
       <c r="Q285" s="6" t="inlineStr">
         <is>
-          <t>VERIFY his exact role/identity at FFOZ -- the cited link is about the Andrew Wilson rebuttal, not clearly a profile of Franczak.</t>
+          <t>Verify platform size and the specific posts (X is not fetchable to me).</t>
         </is>
       </c>
       <c r="R285" s="6" t="inlineStr"/>
       <c r="S285" s="6" t="inlineStr"/>
-      <c r="T285" s="6" t="inlineStr"/>
+      <c r="T285" s="6" t="inlineStr">
+        <is>
+          <t>Sam Brown, Candace Owens</t>
+        </is>
+      </c>
       <c r="U285" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>American</t>
         </is>
       </c>
       <c r="V285" s="6" t="inlineStr">
@@ -24664,56 +25547,59 @@
         </is>
       </c>
       <c r="W285" s="6" t="inlineStr"/>
+      <c r="X285" s="6" t="inlineStr"/>
+      <c r="Y285" s="6" t="inlineStr"/>
+      <c r="Z285" s="6" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>inf-c4d6a320</t>
+          <t>inf-28984b52</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>Josh Turner</t>
+          <t>Jacob Franczak</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>Country music</t>
+          <t>First Fruits of Zion (FFOZ) / media</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>Multi-platinum country artist</t>
+          <t>FFOZ audience</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Christian (Southern Baptist)</t>
+          <t>Christian (Messianic-adjacent)</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>Faith-based country music</t>
+          <t>Pro-Christian-Zionism theology</t>
         </is>
       </c>
       <c r="G286" s="6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>pro</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>Multi-platinum Southern Baptist country artist based in Nashville -- reaches the Bible Belt heartland audience BFT's Tennessee/Nashville ecosystem entry targets. NO Israel record found; submitted on the strength of his faith profile and audience.</t>
+          <t>Andy-submitted via an FFOZ (First Fruits of Zion) piece countering Andrew Wilson's opposition to Christian Zionism -- i.e. defending Christian Zionism theologically against intra-Christian attack. That is precisely the doctrinal battlefront Johnnie's program cares about (supersessionism vs. covenant).</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>instagram.com/joshturnermusic</t>
+          <t>ffoz.org/messiah/watch/andrew-wilson-opposes-christian-zionism</t>
         </is>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted</t>
+          <t>ffoz.org (link supplied by Andy)</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr"/>
@@ -24722,29 +25608,25 @@
       <c r="N286" s="6" t="inlineStr"/>
       <c r="O286" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P286" s="6" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Media/Influencer</t>
         </is>
       </c>
       <c r="Q286" s="6" t="inlineStr">
         <is>
-          <t>VERIFY any Israel/Jewish-community signal -- currently a faith-profile inference only, not evidence. Good NURTURE-style candidate.</t>
-        </is>
-      </c>
-      <c r="R286" s="6" t="inlineStr">
-        <is>
-          <t>Music</t>
-        </is>
-      </c>
+          <t>VERIFY his exact role/identity at FFOZ -- the cited link is about the Andrew Wilson rebuttal, not clearly a profile of Franczak.</t>
+        </is>
+      </c>
+      <c r="R286" s="6" t="inlineStr"/>
       <c r="S286" s="6" t="inlineStr"/>
       <c r="T286" s="6" t="inlineStr"/>
       <c r="U286" s="6" t="inlineStr">
         <is>
-          <t>American</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V286" s="6" t="inlineStr">
@@ -24752,57 +25634,60 @@
           <t>Andy</t>
         </is>
       </c>
-      <c r="W286" s="6" t="inlineStr">
-        <is>
-          <t>US (country music heartland)</t>
-        </is>
-      </c>
+      <c r="W286" s="6" t="inlineStr"/>
+      <c r="X286" s="6" t="inlineStr"/>
+      <c r="Y286" s="6" t="inlineStr"/>
+      <c r="Z286" s="6" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>inf-e716871a</t>
+          <t>inf-c4d6a320</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>Ben Sasse</t>
+          <t>Josh Turner</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>Former US Senator (NE); former Univ. of Florida President; author</t>
+          <t>Country music</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>Institutional/intellectual reach</t>
+          <t>Multi-platinum country artist</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
         <is>
-          <t>Christian (evangelical, Reformed)</t>
+          <t>Christian (Southern Baptist)</t>
         </is>
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>Institutionalist conservative</t>
+          <t>Faith-based country music</t>
         </is>
       </c>
       <c r="G287" s="6" t="inlineStr">
         <is>
-          <t>pro</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>Former Senator and university president; a rare institutionalist evangelical intellectual. As UF president he took a notably firm line against disruptive campus protest -- relevant to the campus-antisemitism front. Andy also asked for 'his friends, associates, allies' -- unbounded as stated; see Backlog.</t>
-        </is>
-      </c>
-      <c r="I287" s="6" t="inlineStr"/>
+          <t>Multi-platinum Southern Baptist country artist based in Nashville -- reaches the Bible Belt heartland audience BFT's Tennessee/Nashville ecosystem entry targets. NO Israel record found; submitted on the strength of his faith profile and audience.</t>
+        </is>
+      </c>
+      <c r="I287" s="6" t="inlineStr">
+        <is>
+          <t>instagram.com/joshturnermusic</t>
+        </is>
+      </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>Andy-submitted; public record</t>
+          <t>Andy-submitted</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr"/>
@@ -24811,20 +25696,24 @@
       <c r="N287" s="6" t="inlineStr"/>
       <c r="O287" s="6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P287" s="6" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="Q287" s="6" t="inlineStr">
         <is>
-          <t>'Friends/associates/allies' is unbounded -- convert to a bounded pass (his Senate staff alumni, UF leadership, published co-signers). Verify his explicit Israel record.</t>
-        </is>
-      </c>
-      <c r="R287" s="6" t="inlineStr"/>
+          <t>VERIFY any Israel/Jewish-community signal -- currently a faith-profile inference only, not evidence. Good NURTURE-style candidate.</t>
+        </is>
+      </c>
+      <c r="R287" s="6" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
       <c r="S287" s="6" t="inlineStr"/>
       <c r="T287" s="6" t="inlineStr"/>
       <c r="U287" s="6" t="inlineStr">
@@ -24837,10 +25726,101 @@
           <t>Andy</t>
         </is>
       </c>
-      <c r="W287" s="6" t="inlineStr"/>
+      <c r="W287" s="6" t="inlineStr">
+        <is>
+          <t>US (country music heartland)</t>
+        </is>
+      </c>
+      <c r="X287" s="6" t="inlineStr"/>
+      <c r="Y287" s="6" t="inlineStr"/>
+      <c r="Z287" s="6" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>inf-e716871a</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>Ben Sasse</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>Former US Senator (NE); former Univ. of Florida President; author</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr">
+        <is>
+          <t>Institutional/intellectual reach</t>
+        </is>
+      </c>
+      <c r="E288" s="6" t="inlineStr">
+        <is>
+          <t>Christian (evangelical, Reformed)</t>
+        </is>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>Institutionalist conservative</t>
+        </is>
+      </c>
+      <c r="G288" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>Former Senator and university president; a rare institutionalist evangelical intellectual. As UF president he took a notably firm line against disruptive campus protest -- relevant to the campus-antisemitism front. Andy also asked for 'his friends, associates, allies' -- unbounded as stated; see Backlog.</t>
+        </is>
+      </c>
+      <c r="I288" s="6" t="inlineStr"/>
+      <c r="J288" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted; public record</t>
+        </is>
+      </c>
+      <c r="K288" s="6" t="inlineStr"/>
+      <c r="L288" s="6" t="inlineStr"/>
+      <c r="M288" s="6" t="inlineStr"/>
+      <c r="N288" s="6" t="inlineStr"/>
+      <c r="O288" s="6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="P288" s="6" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="Q288" s="6" t="inlineStr">
+        <is>
+          <t>'Friends/associates/allies' is unbounded -- convert to a bounded pass (his Senate staff alumni, UF leadership, published co-signers). Verify his explicit Israel record.</t>
+        </is>
+      </c>
+      <c r="R288" s="6" t="inlineStr"/>
+      <c r="S288" s="6" t="inlineStr"/>
+      <c r="T288" s="6" t="inlineStr"/>
+      <c r="U288" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="V288" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="W288" s="6" t="inlineStr"/>
+      <c r="X288" s="6" t="inlineStr"/>
+      <c r="Y288" s="6" t="inlineStr"/>
+      <c r="Z288" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W287"/>
+  <autoFilter ref="A1:Z288"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="criteria" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -739,7 +739,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>292 records</t>
+          <t>295 records</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>59 records</t>
+          <t>60 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>82 records</t>
+          <t>85 records</t>
         </is>
       </c>
     </row>
@@ -1621,14 +1621,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4260,8 +4260,92 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>THE PAID-INFLUENCE THREAT vindicates the cost-paid gate</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Data Ethics</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Every influencer/ally in this database</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Justifies Gate 1; screens paid amplifiers</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Source: TIME, Eric Cortellessa, 13 Jul 2026 -- 'Trump's Ex-Campaign Manager Is Running An Israeli Influence Operation Targeting the MAGA Base' (https://time.com/article/2026/07/13/brad-parscale-israel-influence-operation/). FARA filings show the ad agency Havas hired Brad Parscale's firm Clock Tower X to run a digital campaign FOR THE STATE OF ISRAEL: $1.5M/month, 100 content pieces/month, 80% aimed at Gen Z, 50M+ impressions/month. A related Parscale firm, Influenceable, paid creators a $2,250 base + $1 per 1,000 views (up to ~$4,250/post) via private group chats with 'suggested language' and synchronized posting. WHY THIS IS THE SINGLE MOST IMPORTANT ENTRY FOR DATA INTEGRITY: it proves that at this moment, at scale and for money, pro-Israel content is being manufactured and amplified by PAID influencers who receive coordinated scripts. A database that scores people 'pro' from their POSTS cannot tell a genuine ally from a paid amplifier -- the posts look identical. This is EXACTLY what Gate 1 (loyalty = COST PAID, not statements) is built to defend against. A paid pro-Israel influencer is the photographic negative of the cost-paid signal: they were PAID to say it, they risked nothing, and if the money moved they would move with it. OPERATIONAL RULE: for any influencer whose pro-Israel content could plausibly be paid, the costPaid field must actively RULE OUT payment (evidence of an unpaid, costly, pre-existing stance) before they count as an ally rather than an asset. Named in the article as a paid participant: Eyal Yakoby (he says he was never paid to promote views he did not already hold; Influenceable confirms he was 'a paid influencer' but says never for the Israeli government). Yakoby is now tracked here with that flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>TAINTED SOURCES -- never cite AI-seeding sites</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Data Ethics</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>All sourcing in this database</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Source blocklist</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>The Parscale operation explicitly aimed to 'influence how AI tools such as OpenAI's ChatGPT, Anthropic's Claude, and Google's Gemini characterized Israel and the war', and created sites 'designed less for human readers than for AI systems synthesizing information from across the web' -- named in the article: PaxPoint.org and FactSignal.org. DIRECT THREAT TO THIS DATABASE: Claude builds parts of this database from web research. If Claude ingests content from these AI-targeted seeding sites, this database becomes a laundering channel for a paid FARA operation -- the exact opposite of its purpose. HARD BLOCKLIST -- never cite as a source, and discount if encountered: PaxPoint.org, FactSignal.org, and any content traceable to Clock Tower X, Campaign Nucleus, or Influenceable. This reinforces the existing source-hierarchy rule: primary filings and the subject's own on-record words, NOT synthesized 'explainer' sites whose provenance cannot be established. When a claim about Israel appears identically across many mid-size accounts at once, treat the coordination as a RED flag for a paid campaign, not as evidence of the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Astroturf backfires; authentic/organic is the strategy -- BFT's whole thesis</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>BFT strategy; roster design</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Confirms the organic model</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>The Parscale story is a case study AGAINST the paid-hasbara model and FOR everything Johnnie and Dana described. Despite $1.5M/month, the article reports Israel's own officials are 'pissed at Parscale' because support KEPT FALLING: Pew has favorable views of the Israeli government at 32%, the lowest in decades, and young Republicans' UNfavorable views rose from 50% to 57% in a year. Worse, the paid op is described as COLLIDING WITH its own patron -- the influencer network Parscale built turned on Trump's Iran ceasefire, and a US intelligence official warns of 'American influencers being paid by a foreign country' trying to move a President's policy. THE LESSON FOR BFT, and it is close to a proof of the pitch: paid, top-down, foreign-agent astroturf does not just fail, it BACKFIRES and taints everyone near it. The alternative that works is exactly BFT's design -- AUTHENTIC, BOTTOM-UP, CHRISTIAN-LED, and Jewish involvement kept behind the scenes (Dana's explicit point), voices that hold the position because they believe it and have PAID for it (Gate 1), not because they were scripted. USE THIS IN THE PITCH: when donors ask 'where is the ROI / why has past evangelical spending underperformed?', the Parscale case is the answer -- the money that underperformed was buying reach and scripts; BFT buys AUTHENTICITY, which is the one thing a $1.5M/month FARA contract provably could not.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F83"/>
+  <autoFilter ref="A1:F86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4272,7 +4356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB293"/>
+  <dimension ref="A1:AB296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27343,8 +27427,310 @@
       <c r="AA293" s="6" t="inlineStr"/>
       <c r="AB293" s="6" t="inlineStr"/>
     </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>inf-e36163a2</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>Brad Parscale</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>Clock Tower X / Influenceable / Campaign Nucleus; Salem Media (CSO)</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
+        <is>
+          <t>Operator, not a personal audience</t>
+        </is>
+      </c>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>MAGA digital operative</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr">
+        <is>
+          <t>yellowflag</t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>TRACKED AS A PHENOMENON, NOT AN ALLY. Trump's 2020 campaign manager; runs the FARA-registered $1.5M/month Israeli influence operation profiled by TIME (13 Jul 2026). CSO of Salem Media Network. Israel's own officials say the operation BACKFIRED ('we are pissed at Parscale... things have only gotten worse'), and the White House sees it as now undermining Trump. Included so the operation and its network are visible in the database, NOT because he is a BFT asset -- he is the cautionary opposite of one.</t>
+        </is>
+      </c>
+      <c r="I294" s="6" t="inlineStr"/>
+      <c r="J294" s="6" t="inlineStr">
+        <is>
+          <t>TIME (Eric Cortellessa), 13 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K294" s="6" t="inlineStr"/>
+      <c r="L294" s="6" t="inlineStr"/>
+      <c r="M294" s="6" t="inlineStr"/>
+      <c r="N294" s="6" t="inlineStr"/>
+      <c r="O294" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P294" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q294" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R294" s="6" t="inlineStr">
+        <is>
+          <t>N/A -- PAID OPERATOR, the opposite of the cost signal. His firm is paid $1.5M/month by Israel via Havas (FARA).</t>
+        </is>
+      </c>
+      <c r="S294" s="6" t="inlineStr"/>
+      <c r="T294" s="6" t="inlineStr"/>
+      <c r="U294" s="6" t="inlineStr"/>
+      <c r="V294" s="6" t="inlineStr">
+        <is>
+          <t>https://time.com/article/2026/07/13/brad-parscale-israel-influence-operation/</t>
+        </is>
+      </c>
+      <c r="W294" s="6" t="inlineStr">
+        <is>
+          <t>Salem Media Network, Havas, Clock Tower X, Influenceable, Eyal Yakoby</t>
+        </is>
+      </c>
+      <c r="X294" s="6" t="inlineStr">
+        <is>
+          <t>Do NOT activate or treat as an ally. Use as the reference case for the paid-op / astroturf-backfires criterion. Map his firm network (Clock Tower X, Influenceable, Campaign Nucleus) and the Salem Media distribution channel as CAUTION nodes -- allies who publish via Salem are adjacent to a compromised channel and should be noted, though that is not itself disqualifying.</t>
+        </is>
+      </c>
+      <c r="Y294" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proactive)</t>
+        </is>
+      </c>
+      <c r="Z294" s="6" t="inlineStr"/>
+      <c r="AA294" s="6" t="inlineStr"/>
+      <c r="AB294" s="6" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>inf-fa141153</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>Eyal Yakoby</t>
+        </is>
+      </c>
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>X (large following)</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
+        <is>
+          <t>Popular X account (per TIME)</t>
+        </is>
+      </c>
+      <c r="E295" s="6" t="inlineStr">
+        <is>
+          <t>Jewish</t>
+        </is>
+      </c>
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>Campus-antisemitism / pro-Israel advocacy</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr">
+        <is>
+          <t>yellowflag</t>
+        </is>
+      </c>
+      <c r="H295" s="6" t="inlineStr">
+        <is>
+          <t>Recent college grad with a popular X account; testified before a House committee on campus antisemitism; began working with a Parscale firm ~a year before the July 2026 report. His actual views may be entirely sincere -- the flag is about PROVENANCE, not sincerity. Under Gate 1 the burden is to show the stance is independent of the payment.</t>
+        </is>
+      </c>
+      <c r="I295" s="6" t="inlineStr"/>
+      <c r="J295" s="6" t="inlineStr">
+        <is>
+          <t>TIME (Eric Cortellessa), 13 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K295" s="6" t="inlineStr"/>
+      <c r="L295" s="6" t="inlineStr"/>
+      <c r="M295" s="6" t="inlineStr"/>
+      <c r="N295" s="6" t="inlineStr"/>
+      <c r="O295" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P295" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q295" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R295" s="6" t="inlineStr">
+        <is>
+          <t>DISPUTED / CAUTION. Named by TIME as a PAID influencer with Parscale's Influenceable. He says he was never paid to promote views he did not already hold and never on behalf of the Israeli government; Influenceable confirms he was 'a paid influencer'. Because payment is on the record, he does NOT clear Gate 1 on current evidence -- payment must be ruled out, not assumed.</t>
+        </is>
+      </c>
+      <c r="S295" s="6" t="inlineStr"/>
+      <c r="T295" s="6" t="inlineStr">
+        <is>
+          <t>https://time.com/article/2026/07/13/brad-parscale-israel-influence-operation/</t>
+        </is>
+      </c>
+      <c r="U295" s="6" t="inlineStr"/>
+      <c r="V295" s="6" t="inlineStr">
+        <is>
+          <t>https://time.com/article/2026/07/13/brad-parscale-israel-influence-operation/</t>
+        </is>
+      </c>
+      <c r="W295" s="6" t="inlineStr">
+        <is>
+          <t>Influenceable, Brad Parscale</t>
+        </is>
+      </c>
+      <c r="X295" s="6" t="inlineStr">
+        <is>
+          <t>VERIFY independence before any 'ally' classification: is the pro-Israel advocacy pre-existing and unpaid, or downstream of the Influenceable relationship? His House testimony predates or coincides with the paid work -- establish the timeline. Do NOT hold him up as a model voluntary ally until this is resolved.</t>
+        </is>
+      </c>
+      <c r="Y295" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proactive)</t>
+        </is>
+      </c>
+      <c r="Z295" s="6" t="inlineStr"/>
+      <c r="AA295" s="6" t="inlineStr"/>
+      <c r="AB295" s="6" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>inf-ed66bcae</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>Nick Sortor</t>
+        </is>
+      </c>
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>X (@nicksortor)</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
+        <is>
+          <t>1M+ X followers</t>
+        </is>
+      </c>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>Conservative independent</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>1M+ follower conservative who publicly accused Parscale's Influenceable of running an undisclosed coordinated campaign (the soda-industry case, Mar 2026). Not established as pro/anti Israel here -- tracked because his willingness to expose paid coordination makes him a useful AUTHENTICITY reference and a potential ally against astroturf.</t>
+        </is>
+      </c>
+      <c r="I296" s="6" t="inlineStr">
+        <is>
+          <t>x.com/nicksortor</t>
+        </is>
+      </c>
+      <c r="J296" s="6" t="inlineStr">
+        <is>
+          <t>TIME (Eric Cortellessa), 13 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K296" s="6" t="inlineStr"/>
+      <c r="L296" s="6" t="inlineStr"/>
+      <c r="M296" s="6" t="inlineStr"/>
+      <c r="N296" s="6" t="inlineStr"/>
+      <c r="O296" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P296" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q296" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R296" s="6" t="inlineStr">
+        <is>
+          <t>AUTHENTICITY SIGNAL (not an Israel cost, but relevant): in Mar 2026 he publicly EXPOSED an Influenceable-coordinated undisclosed campaign (MAGA influencers posting near-identical pro-soda messaging). Calling out paid coordination from inside the conservative influencer world is itself a costly independence signal -- the opposite of a scripted amplifier.</t>
+        </is>
+      </c>
+      <c r="S296" s="6" t="inlineStr"/>
+      <c r="T296" s="6" t="inlineStr"/>
+      <c r="U296" s="6" t="inlineStr"/>
+      <c r="V296" s="6" t="inlineStr">
+        <is>
+          <t>https://time.com/article/2026/07/13/brad-parscale-israel-influence-operation/</t>
+        </is>
+      </c>
+      <c r="W296" s="6" t="inlineStr">
+        <is>
+          <t>Influenceable (as critic)</t>
+        </is>
+      </c>
+      <c r="X296" s="6" t="inlineStr">
+        <is>
+          <t>Verify his actual Israel stance separately before classifying. Value here is as an independent who resists coordination -- exactly the profile Gate 1 rewards.</t>
+        </is>
+      </c>
+      <c r="Y296" s="6" t="inlineStr">
+        <is>
+          <t>Claude (proactive)</t>
+        </is>
+      </c>
+      <c r="Z296" s="6" t="inlineStr"/>
+      <c r="AA296" s="6" t="inlineStr"/>
+      <c r="AB296" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB293"/>
+  <autoFilter ref="A1:AB296"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43802,7 +44188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46010,8 +46396,41 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>THE MEDIA-WAR SCHISM MAP (from the Parscale/TIME reporting)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Andy asked to ingest this article 'to better understand the ongoing media war/political debate/schism.' DONE (read in full via the in-app browser; TIME is Cloudflare-403 to plain fetch). The map, per the reporting: THE FAULT LINE is Israel policy inside the American right, and it split open over the 17 Jun 2026 US-Iran ceasefire. ANTI-INTERVENTION / RESTRAINT WING (drifting away from Israel): Tucker Carlson and Steve Bannon (both 'openly skeptical of Netanyahu'), and the JD Vance isolationist bloc that Israel's MFA fears is 'steering the American right toward an isolationism fundamentally at odds with Israel's strategic interests.' The animating idea: suspicion that 'Israel exercises hidden control over America's foreign policy.' After the ceasefire, MAGA influencers attacked TRUMP himself for it. PRO-ISRAEL ESTABLISHMENT: the traditional right, plus (per the late) Charlie Kirk, whose May 2025 private letter to Netanyahu called anti-Israel online sentiment a 'five alarm fire' and urged mobilizing influencers, hostage speaking tours, and humanizing content -- Netanyahu never replied. THE PAID LAYER sitting on top: Parscale's Clock Tower X / Influenceable, paid by Israel via Havas, running scripted influencers -- which BACKFIRED and is now colliding with Trump. THE NUMBERS: Israeli-government favorability 32% (Pew, lowest in decades); young-Republican unfavorables 50%-&gt;57% in a year; global antisemitic incidents +34% since the Iran war.</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>This is the battlefield BFT is being funded to fight on, and it sharpens the roster gates. The restraint wing (Carlson/Bannon/Vance-adjacent) is the DRIFT this project exists to counter -- cross-reference with the congressional trend-slope analysis (task #14) and the attack-the-drift cost signal. Track as named artifacts (not vibes): the George Will vs JD Vance column (establishment-hawk vs restraint), the Rogan x Vance episode (get a transcript), Charlie Kirk's letter, and the ceasefire-reaction wave. Also: this is why Gate 1 matters -- in a field with a $1.5M/month paid op, 'who posts pro-Israel' is noise; 'who paid a price for it' is signal.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G60"/>
+  <autoFilter ref="A1:G61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>60 records</t>
+          <t>61 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>85 records</t>
+          <t>87 records</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4344,8 +4344,64 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC over PAID: how to tell them apart</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Every influencer; roster ranking</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Boost organic, discount paid</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: 'organic influencers should be boosted over paid influencers though this can be difficult to know whether someone is paid or not or whether or not they'd state the same sentiments even if they weren't paid - generally this can be determined if they still have a low follower count (sub-30K) and/or if their earliest content aligns with our values/mission.' This operationalises Gate 1 against the paid-op threat the Parscale/TIME article exposed. Two PROXIES for genuine, unpaid conviction, because payment is usually unprovable directly: (1) LOW FOLLOWER COUNT (sub-30K). Paid influence operations buy REACH -- they target accounts big enough to move impressions (the Parscale contract promised 50M/month). A creator under ~30K followers who is loudly pro-Israel is very unlikely to be worth paying, so the stance is probably sincere. This also aligns with the seed-100 'back them before they break out' logic: sub-30K + sincere + talented is the highest-upside, lowest-cost bet. (2) EARLIEST CONTENT ALIGNS. If their FIRST posts/videos -- before there was money or a movement in it, and especially pre-Oct-7 -- already carried the values, the conviction predates any incentive. A long consistent track record cannot be bought retroactively. NEITHER IS DECISIVE ALONE (a big account can still be sincere; an early post can be coincidence), but together they are strong. RECORD in costPaid/costDate: follower tier at time of assessment, and the date of their earliest on-mission content. MEASUREMENT BLOCKER (found 17 Jul 2026): this heuristic cannot yet be applied at scale -- 166 of 233 pro entries have NO parseable follower count. It depends on the handle+audience backfill (task #17). That backfill is now doubly important: it is the input to this authenticity test, not just to audience sizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>LLM CROSS-CHECK: Claude has a measured left lean -- verify against it</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Data Ethics</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Every sentiment/stance call Claude made</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Mandates external review</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Andy wants to run the project past Grok/Gemini/ChatGPT to catch sentiment Claude missed and mistakes Claude made. This is CORRECT and should be standing practice, and the reason is measured, not hypothetical. Per the Washington Post's Jun 2026 test of chatbot political bias: ChatGPT answered political questions almost exclusively with left-leaning arguments; GEMINI was the MOST balanced (both-sides in &gt;90% of answers); GROK, despite conservative marketing, still cited left-leaning arguments more often on average; and CLAUDE gave a left-leaning answer in 43% of cases (both-sides the other 57%). IMPLICATION FOR THIS DATABASE: Claude built much of the stance/sentiment analysis here, and Claude has a documented ~43% left lean. On a project whose whole purpose is to assess pro-Israel/conservative sentiment, that lean is a live risk of systematic misread -- e.g. under-crediting a right-coded ally, or over-flagging conservative conduct. HONEST NUANCE, against the assumption that Grok is the neutral referee: the WaPo data says GEMINI tested most balanced and Grok still leans left on average -- so the best cross-check is MULTIPLE models, not any single 'unbiased' one. Use Gemini for balance, Grok for right-coded framing it may weight differently, ChatGPT as a third read, and treat DISAGREEMENT between them and Claude as the flag for manual review. See docs/LLM_CROSS_AUDIT_BRIEF.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F86"/>
+  <autoFilter ref="A1:F88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44188,7 +44244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46429,8 +46485,41 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>AI CROSS-AUDIT: hand the project to Grok/Gemini/ChatGPT</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Staged</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: run the whole project past other LLMs to catch sentiment Claude missed, reach data Claude couldn't, and find Claude's mistakes. Rationale is measured, not vibes: WaPo Jun 2026 found Claude answers political questions with a left lean ~43% of the time, so on a project assessing right-coded pro-Israel sentiment, an independent check is genuine risk mitigation. DELIVERABLE BUILT: docs/LLM_CROSS_AUDIT_BRIEF.md -- a self-critical hand-off that discloses Claude's known errors (3 syntax bugs shipped to prod, 3 false capability claims, Wikipedia misuse, stale CyberArk/Wiz facts, the wrong podcast tags, 211/233 pro entries with no cost signal, etc.), lists what to re-verify, flags where another model has access Claude lacks (X/Instagram follower data, paywalled pages), and asks for a specific stance-recheck sample. Pair it with export/BFT_Living_Database.xlsx.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>HONEST BIAS LANDSCAPE (WaPo, so the plan targets the right models): Gemini tested MOST balanced (both-sides &gt;90%); Grok still leaned left on average despite conservative branding; ChatGPT leaned left most; Claude ~43% left. So use MULTIPLE models and treat Claude-vs-other disagreement as the manual-review flag -- do NOT crown any single model the neutral referee (Grok included). Return format requested in the brief: {bftId, my_call, your_call, why, source_url}. When findings come back, merge the primary-sourced ones fast and queue the rest. This is a RECURRING practice, not one-off -- re-run after major additions.</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G61"/>
+  <autoFilter ref="A1:G62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>87 records</t>
+          <t>88 records</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4400,8 +4400,36 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>TESTED platform capability map for follower counts</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>All audience/follower-count metrics</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>What is fetchable, and how</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: 'X, instagram, rumble, tiktok, youtube, facebook follower counts are very important metrics.' Agreed -- they are the raw input to the organic/sub-30K test AND to seed-100 audience sizing. So I TESTED each platform on 17 Jul 2026 instead of asserting (having been wrong before). RESULTS, honestly: YOUTUBE -- reliable via plain fetch (subscriberCountText in page HTML). X/TWITTER -- WORKS via the in-app BROWSER (JS-rendered; confirmed Dana Loesch = 1.3M by reading the rendered Followers link). It does NOT work via plain fetch. IMPORTANT CORRECTION: I previously recorded X as 'blocked/JS-rendered, no counts' -- that was true of curl but FALSE of the browser. This is the 4th capability I wrongly wrote off (after social platforms generally, the JS engine, and congress.gov). RUMBLE -- works via plain fetch on channel pages (/c/Name; confirmed Graham Allen = 228K), though channel-URL structure varies and some pages don't expose the count. TIKTOK -- INTERMITTENT via plain fetch (worked historically for the Lance Johnston check; on 17 Jul returned login/no-count for several handles). Treat as unreliable; fall back to the browser. FACEBOOK -- page loads via fetch but the count is behind a partial login wall; extraction unreliable. Browser may do better; not yet confirmed. INSTAGRAM -- BLOCKED. Shows a login wall even in the browser when logged out. Genuinely not fetchable here; Andy or a logged-in tool must supply Instagram numbers. BINDING CONSTRAINT: only 53 of 295 influencers currently carry ANY handle, so the counts can't be fetched until handles are backfilled (task #17). X is the most common handle present (36) -- and now that it's confirmed fetchable via browser, the X backfill is high-yield.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F88"/>
+  <autoFilter ref="A1:F89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11897,7 +11925,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Frequent UK/international broadcast commentator; viral clips</t>
+          <t>X (@HausdorffMedia) 59.4K followers (browser-verified 17 Jul 2026); frequent UK/international broadcast commentator</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>61 records</t>
+          <t>63 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>88 records</t>
+          <t>90 records</t>
         </is>
       </c>
     </row>
@@ -1621,14 +1621,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4428,8 +4428,64 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>FULL platform capability map (20+ networks, tested 17 Jul 2026)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Follower-count collection across all platforms</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>What works, how, and what needs login</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Andy listed the full platform set (Facebook, X, Instagram, LinkedIn, Reddit, Pinterest, Minds, GETTR, MeWe, Gab, Telegram, Truth Social, Threads, Parler, Bluesky; video: YouTube, Rumble, Odysee, BitChute, TikTok; plus Twitch). TESTED, not asserted. CONFIRMED WORKING, NO LOGIN (plain fetch / public API): YouTube (metadataParts pattern), Rumble (/c/Name), Gab (found 2.25M on realdonaldtrump), Threads (found 5.7M on @zuck), Bluesky (public API public.api.bsky.app/xrpc/app.bsky.actor.getProfile?actor=HANDLE -&gt; followersCount), Telegram (t.me/s/CHANNEL for channels with a public preview). TikTok works but INTERMITTENTLY. CONFIRMED WORKING VIA IN-APP BROWSER (JS-rendered, no login): X/Twitter (Dana Loesch 1.3M, Hausdorff 59.4K). CLOUDFLARE-BLOCKED TO CURL, BROWSER-TESTABLE (same pattern as congress.gov/TIME which the browser DID load -- not yet browser-confirmed): Truth Social, Reddit (has an OAuth API too), GETTR, Parler, Odysee, BitChute, Minds, MeWe, Twitch. Do NOT record these as blocked until browser-tested. GENUINELY LOGIN-WALLED (need Andy's session -- see the login-assist criterion): Instagram (wall even in browser, confirmed), LinkedIn (known), Facebook (partial wall). NEEDS API KEY/AUTH: Reddit (OAuth), Twitch (client-id), Pinterest (untested). NOTE: this list is now BROADER than the memory that recorded 'no multi-platform monitoring' as a blocked capability -- that item must be reopened and rewritten from this tested map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>LOGIN-ASSIST: how Andy unlocks walled platforms</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Data Ethics</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Instagram, LinkedIn, Facebook, and any login/CAPTCHA wall</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Turns blocked platforms into readable ones</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: can't he just log in / solve the CAPTCHA so Claude can collect the data? YES -- two mechanisms, with guardrails. MECHANISM 1 (cleaner): the 'Claude in Chrome' tool drives Andy's REAL Chrome with his EXISTING logged-in sessions. Where he is already logged into Instagram/LinkedIn/Facebook/X, Claude can read the PUBLIC follower count off the rendered page with no credential handling. MECHANISM 2: in the in-app browser, when Claude hits a CAPTCHA or login wall, Claude pauses and asks Andy to clear it, then proceeds (matches the standing CAPTCHA-handling rule). HARD GUARDRAILS, non-negotiable: (1) Claude NEVER types Andy's credentials -- Andy authenticates himself; (2) Claude reads ONLY the public metric (the follower number), never DMs, private feeds, or other session-exposed data; (3) no screenshots of logged-in sessions -- extract the number, not the screen (a prior screenshot privacy slip on this project is why). This is the unlock for the three genuinely-walled platforms and for anything Cloudflare escalates to a CAPTCHA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44272,7 +44328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46546,8 +46602,74 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>ROADMAP: live-data adaptive model (Phase 2, after the base is accurate)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Andy's vision, 17 Jul 2026: once the base data is ingested and the model is accurate enough to interpret and sort NEW data, engineer it to (a) ingest live statements from principals -- Trump, JD Vance, Marco Rubio, Ben Shapiro, Tucker Carlson, etc. -- and from every tracked influencer, (b) proactively identify EMERGING influencers matching the ally criteria, and (c) adapt as new data arrives. HONEST FRAMING: this is a real engineering system, not a model toggle. It is Phase 2 -- it should NOT start until the base database is accurate (sources filled, handles backfilled, stances cross-verified), because a live pipeline built on shaky classifiers just scales the errors.</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>The building blocks are proven and available in this environment: (1) FETCH works across most platforms (see the capability map) + the free legislative/SEC feeds for the principals' official acts; (2) SCHEDULING -- this environment has cron/scheduled-task tooling to run collectors on an interval; (3) CLASSIFY -- the two-gate + stance rubric already encoded in criteria is the labeling function; (4) the live app + Airtable schema is the store. PHASED PLAN: Phase 2a -- a WATCHLIST poller on ~10 principals (Trump/Vance/Rubio/Shapiro/Carlson + the highest-value influencers): pull new public statements on a schedule, classify sentiment against the criteria, flag NOTABLE MOVES (a drift, a new attack, a reversal) for Andy. Phase 2b -- DISCOVERY: from the confirmed allies, walk their interactions/guests/reposts to surface emerging accounts, score against the gates, auto-file sub-30K organic candidates into Nurture. Phase 2c -- adaptivity: when Andy confirms/rejects flagged items, feed that back as labeled examples to tune thresholds. START SMALL: one principal, one platform, one scheduled run, verified by hand, before scaling.</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>ROADMAP: continuous self-audit + standing cross-LLM verification</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Staged</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: the model should CONSTANTLY audit itself for mistakes, surface them for Andy to verify, and cross-reference the mistakes/uncertainties with other LLMs. This extends the one-off LLM_CROSS_AUDIT_BRIEF.md into a standing process.</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Build as automated CHECKS that run on every change (the jsc validator is the first one already): (1) DATA-INTEGRITY checks -- every VISIBLE_CATEGORIES tab has data (the Nurture bug); no field:"[^"]*" corruption; no stale acquisition status; no Wikipedia citations; every 'pro' with a plausible-paid profile has costPaid ruling out payment. (2) FRESHNESS -- follower counts and podcast status re-verified on a schedule; flag anything &gt;90 days stale or &gt;2x changed. (3) CONFIDENCE -- each stance carries a confidence; low-confidence + high-importance (big audience) routes to the top of the manual-review queue. (4) CROSS-LLM -- on a schedule, export the low-confidence/disputed slice, run it past Gemini (most balanced per WaPo) + Grok (different framing) + ChatGPT, and treat any disagreement with Claude as a review flag. Because Claude has a measured ~43% left lean, this is bias mitigation, not redundancy. The output is a standing 'AI to-do list' that regenerates itself, exactly as Andy asked.</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G62"/>
+  <autoFilter ref="A1:G64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -44432,12 +44432,12 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Ask: continuously scan Facebook, X, Instagram, LinkedIn, Reddit, Pinterest, Minds, GETTR, MeWe, Gab, Telegram, Truth Social, Threads, Parler, Bluesky, YouTube, Rumble, Odysee, BitChute, TikTok for emerging pro-Israel voices. Claude only acts inside a turn -- there is no background monitoring.</t>
+          <t>REOPENED 17 Jul 2026 -- was wrongly marked Blocked on an untested assumption. TESTED: YouTube, Rumble, Gab, Threads, Bluesky (API), Telegram, and TikTok all fetch WITHOUT login; X works via the browser; Instagram/LinkedIn/Facebook need a login (now a solved assist workflow); the JS-rendered ones (Truth Social/GETTR/Twitch/etc) remain to browser-confirm. Original note follows. Ask: continuously scan Facebook, X, Instagram, LinkedIn, Reddit, Pinterest, Minds, GETTR, MeWe, Gab, Telegram, Truth Social, Threads, Parler, Bluesky, YouTube, Rumble, Odysee, BitChute, TikTok for emerging pro-Israel voices. Claude only acts inside a turn -- there is no background monitoring.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -868,7 +868,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -879,7 +879,7 @@
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="35" customWidth="1" min="18" max="18"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>36.4K followers (per Andy)</t>
+          <t>X (@HanShawnity) 36.5K followers (browser-verified 17 Jul 2026); 36.4K followers (per Andy)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>~22K followers (per Andy)</t>
+          <t>X (@Fair_and_Biased) 22K followers (browser-verified 17 Jul 2026); ~22K followers (per Andy)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1352,7 +1352,11 @@
           <t>Andy-submitted</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC SIGNAL (sub-30K rule): X verified at 22K on 17 Jul 2026 -- below the 30K threshold, so unlikely to be worth paying, i.e. the pro-Israel/pro-Shapiro sentiment is probably sincere. Still needs the earliest-content check for confirmation.</t>
+        </is>
+      </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
           <t>~22K X following; growing.</t>
@@ -12293,7 +12297,7 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>900K+ X followers</t>
+          <t>X (@christopherrufo) 849.7K followers (browser-verified 17 Jul 2026); 900K+ X followers</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -16423,7 +16427,7 @@
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>Millions across X/Rumble</t>
+          <t>X (@JamesOKeefeIII) 3.5M followers (browser-verified 17 Jul 2026); Millions across X/Rumble</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -17063,7 +17067,7 @@
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>National cable show + bestselling author</t>
+          <t>X (@bungarsargon) 283.3K followers (browser-verified 17 Jul 2026); National cable show + bestselling author</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -17933,7 +17937,7 @@
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>897K X followers</t>
+          <t>X (@DefiyantlyFree) 1M followers (browser-verified 17 Jul 2026); 897K X followers</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -21873,7 +21877,7 @@
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>Nationally syndicated radio (millions)</t>
+          <t>X (@bucksexton) 1.3M followers (browser-verified 17 Jul 2026); Nationally syndicated radio (millions)</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -21951,7 +21955,7 @@
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>Babylon Bee's tens of millions</t>
+          <t>X (@SethDillon) 886.3K followers (browser-verified 17 Jul 2026); Babylon Bee's tens of millions</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -25379,7 +25383,7 @@
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>YouTube 32.3K subscribers (live-verified 15 Jul 2026)</t>
+          <t>X (@TomiLahren) 2.8M followers (browser-verified 17 Jul 2026)</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
@@ -25661,7 +25665,7 @@
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>Global UFC audience</t>
+          <t>X (@danawhite) 7M followers (browser-verified 17 Jul 2026); Global UFC audience</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -27275,7 +27279,7 @@
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>Nationally syndicated radio</t>
+          <t>X (@DLoesch) 1.3M followers (browser-verified 17 Jul 2026); Nationally syndicated radio</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>63 records</t>
+          <t>64 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>90 records</t>
+          <t>93 records</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4488,8 +4488,92 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>STANDING RULE: complete every instruction; log what can't be done</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Every Andy instruction, past and present</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Accountability -- nothing dropped silently</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: 'follow all my instructions/commands including previous ones until they are fully complete and to inform me and include on our database if a command/instruction couldnt be completed so we know to address it.' OPERATIONALISED: (1) instructions are not 'done' when acknowledged -- only when fully executed and verified; a partial add stays OPEN. (2) Every instruction is tracked to completion in docs/INSTRUCTION_LEDGER.md (the master accountability list) and the backlog tab (operational detail). (3) When something CANNOT be completed, it is stated plainly to Andy AND logged with the reason and the unblock path -- never silently skipped. (4) Each session reconciles the ledger: re-check partials, surface anything blocked on Andy. KNOWN STRUCTURAL LIMIT ON THIS RULE: Claude Code cannot read Andy's regular-Claude (claude.ai) history, so instructions given there are invisible here and cannot be honored until Andy exports them. This is why the ledger's completeness is bounded -- flagged in the ledger's honest column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Podcast platforms added to tracking: Apple, Spotify, SoundCloud</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Network Definition</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Audio/podcast presence + monitoring</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Extends platform coverage to audio</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: add Apple Podcasts, Spotify, and SoundCloud to the platforms we archive, analyze, and monitor. TESTED 17 Jul: APPLE PODCASTS -- WORKS, no key: the iTunes Search API (itunes.apple.com/search?media=podcast&amp;term=NAME) returns show name, episode count, and last-release date. Already used to catch the 13 wrongly-tagged 'No podcast' entries. Best for ACTIVITY monitoring (is a show live? how often? last episode?). SPOTIFY -- oEmbed works logged-out for public show metadata (title/art), but FOLLOWER counts and monthly listeners need the Spotify Web API (free client-credentials token -- Andy can create one at developer.spotify.com). SOUNDCLOUD -- page loads but the API needs a client_id (401 without). Follower/play counts require that key or a browser read. MONITORING VALUE: for the Nurture/leg-1 podcast roster, Apple's last-release date is the DORMANT-vs-ACTIVE signal (a stopped feed is a cheap re-activation target); episode cadence is a talent/consistency signal. Add podcastActivity fields when the roster work resumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Comment-sentiment sourcing: the two-way heuristic</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Inclusion Signal</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Grassroots discovery; emerging-influencer pipeline</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Turns engagement into leads</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: use the COMMENT SECTIONS of ally posts to grow the grassroots network and find emerging influencers -- identify accounts that comment/post with POSITIVE sentiment on ALLY posts, AND accounts that comment/post NEGATIVELY on HOSTILE posts. Both are candidate allies (the second is the enemy-of-my-enemy signal Andy set earlier). This is a strong, criteria-consistent idea: it finds real, self-selected supporters BEFORE they have a following (the seed-100 logic), and it is behavioural evidence, not just a stated view. It also pairs with the cost-paid gate -- someone defending an ally in a hostile comment section IS paying a small social cost. FEASIBILITY, TESTED 17 Jul: reading WHO comments requires a LOGGED-IN session. X shows follower counts to logged-out users but gates the timeline, replies, and commenter identities behind a login wall (articles=0 logged-out). So this needs Andy's session (Claude-in-Chrome or a solved login) AND is a Phase-2 scanner build -- see the roadmap backlog item.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F91"/>
+  <autoFilter ref="A1:F94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14679,7 +14763,7 @@
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>736K+ X followers</t>
+          <t>X (@EricLDaugh) 1.1M followers (browser-verified 17 Jul 2026); 736K+ X followers</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -27173,7 +27257,7 @@
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>TBD -- verify</t>
+          <t>X (@bdomenech) 264.4K followers (browser-verified 17 Jul 2026)</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -27381,7 +27465,7 @@
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>Nationally syndicated column since 1974</t>
+          <t>X (@GeorgeWill) 209.2K followers (browser-verified 17 Jul 2026); Nationally syndicated column since 1974</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -44332,7 +44416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46672,8 +46756,41 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>ROADMAP: comment-network grassroots discovery scanner (Phase 2)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: enable the system to scan ally-account comment sections for positive-sentiment commenters (grassroots + emerging-influencer candidates) and hostile-account comment sections for negative-sentiment commenters (enemy-of-enemy candidates), across platforms. FEASIBILITY TESTED: reading commenters needs a logged-in session (X gates replies behind login when logged out; the public profile header/follower count is all that's visible logged-out).</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>PHASED BUILD, gated on Andy's login-assist: Phase A -- with Andy logged in, open a handful of high-engagement posts from top allies, extract commenter handles, and score each comment's sentiment against the criteria; auto-file promising sub-30K organic accounts into Nurture as 'grassroots/emerging'. Phase B -- do the same on tracked HOSTILE accounts, capturing the loudest negative commenters as enemy-of-enemy candidates. Phase C -- schedule it. GUARDRAILS: read public comments only; never scrape private data; store handles + the specific evidencing comment, not personal info beyond what's needed to score. START SMALL: one ally post, hand-verified, before any scaling. This is the single most novel lead-generation idea in the project -- it manufactures a discovery funnel nobody else has.</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G64"/>
+  <autoFilter ref="A1:G65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$94</definedName>
   </definedNames>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>64 records</t>
+          <t>65 records</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Andy, 17 Jul 2026: can't he just log in / solve the CAPTCHA so Claude can collect the data? YES -- two mechanisms, with guardrails. MECHANISM 1 (cleaner): the 'Claude in Chrome' tool drives Andy's REAL Chrome with his EXISTING logged-in sessions. Where he is already logged into Instagram/LinkedIn/Facebook/X, Claude can read the PUBLIC follower count off the rendered page with no credential handling. MECHANISM 2: in the in-app browser, when Claude hits a CAPTCHA or login wall, Claude pauses and asks Andy to clear it, then proceeds (matches the standing CAPTCHA-handling rule). HARD GUARDRAILS, non-negotiable: (1) Claude NEVER types Andy's credentials -- Andy authenticates himself; (2) Claude reads ONLY the public metric (the follower number), never DMs, private feeds, or other session-exposed data; (3) no screenshots of logged-in sessions -- extract the number, not the screen (a prior screenshot privacy slip on this project is why). This is the unlock for the three genuinely-walled platforms and for anything Cloudflare escalates to a CAPTCHA.</t>
+          <t>CORRECTED 17 Jul 2026 -- TESTED, and the optimistic version was wrong. Andy confirmed he is logged into X, Instagram, and LinkedIn in his real Chrome. But the 'Claude in Chrome' tool, though CONNECTED to his browser (Browser 1, macOS, local), REFUSES to navigate to any domain in this environment -- x.com, instagram.com, linkedin.com, and even example.com all return 'Navigation to this domain is not allowed.' So his logged-in sessions CANNOT be leveraged through the available tooling right now. This was Claude asserting a capability before testing it -- the recurring failure mode on this project. NET EFFECT ON THE PLATFORM MAP: the login-walled platforms stay walled here. In-app browser still reads PUBLIC data logged-out (X/Gab/Threads follower counts via the profile header); it still CANNOT read Instagram (login wall) or X comments/replies (login-gated). UNBLOCK PATH (config, not a Claude action): the Claude-in-Chrome domain restriction would need to be lifted at the extension/environment permission level -- something Andy or the environment config controls, not something Claude can change. Until then, treat Instagram counts, LinkedIn, and the comment-network as BLOCKED ON TOOLING, not on Andy's login. Do NOT ask Andy to log in again -- login is not the blocker.</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>Large tech-right readership</t>
+          <t>X (@micsolana) 398.1K followers (browser-verified 17 Jul 2026); Large tech-right readership</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>Blaze audience</t>
+          <t>X (@SaraGonzalesTX) 507.4K followers (browser-verified 17 Jul 2026); Blaze audience</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -44416,7 +44416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46789,8 +46789,41 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED: logged-in browsing (Instagram, X comments, LinkedIn) -- tool refuses navigation</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Structural Limit</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>17 Jul 2026: Andy is logged into X/Instagram/LinkedIn in his real Chrome, and that Chrome IS connected to the Claude-in-Chrome tool (Browser 1, macOS, local, confirmed via list_connected_browsers). But EVERY navigation attempt returns 'Navigation to this domain is not allowed' -- tested x.com, instagram.com, linkedin.com, AND example.com. It is a blanket navigation block in this environment, not a login or connection issue. Claude had asserted this workflow would work WITHOUT testing it -- corrected now.</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Consequence: three things that depend on a logged-in session are BLOCKED here -- (1) Instagram follower counts, (2) LinkedIn data, (3) the comment-network scan (X gates replies/commenters behind login). NONE are unblocked by Andy logging in, because the tool won't navigate regardless. UNBLOCK PATH is configuration-side: the Claude-in-Chrome extension/environment domain permission would need to allow navigation -- Andy or the environment owner controls that, not Claude. ALTERNATIVE that needs no tooling change: Andy pastes the specific numbers/comment-handles he can see in his own browser, and Claude records them. For now: keep enriching everything reachable logged-out (X/Gab/Threads/Bluesky/Telegram/YouTube/Rumble counts, Apple Podcasts) and leave the login-gated subset flagged.</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Andy + Claude test, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G65"/>
+  <autoFilter ref="A1:G66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -35613,7 +35613,7 @@
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>crenshaw.house.gov, congress.gov/member/dan-crenshaw/C001120, x.com/DanCrenshawTX</t>
+          <t>crenshaw.house.gov, congress.gov/member/dan-crenshaw/C001120, x.com/DanCrenshawTX; X (@DanCrenshawTX) 1.2M followers (browser-verified 17 Jul 2026)</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$94</definedName>
   </definedNames>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>65 records</t>
+          <t>66 records</t>
         </is>
       </c>
     </row>
@@ -44416,7 +44416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46822,8 +46822,41 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>DECISION: no stealth/anti-detect scraping of Instagram/LinkedIn</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Blocked (Access/Ethics)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Needs Andy</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026, asked whether a stealth/anti-detect browser tool (he named 'openclaw' -- not a tool Claude recognizes) could make Instagram/LinkedIn 'think it's me browsing not a bot.' TWO honest points. (1) The actual blocks were NOT bot-detection: the Claude-in-Chrome tool refuses to navigate to any domain in this env, and the in-app browser hits IG's logged-out login wall -- an anti-detect tool addresses neither. (2) Tools that exist for this (Playwright+stealth, undetected-chromedriver, anti-detect browsers, Apify/Bright Data) COULD read IG/LinkedIn with Andy's session, but their purpose is to DEFEAT the platform's bot detection, which violates Instagram/LinkedIn ToS (LinkedIn especially -- cf. hiQ v. LinkedIn). Claude will not engineer detection-evasion tooling; the goal (public figures' public counts) is legitimate, the evasion method is not.</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>LEGITIMATE PATHS to the same data, recommended in order: (1) the 6 platforms that already work logged-out (X/Gab/Threads/Bluesky/Telegram/YouTube/Rumble) cover most of the roster; (2) Andy pastes the ~10 highest-value Instagram/LinkedIn numbers he can see in his own browser -- zero ToS issue, works today; (3) official APIs (Instagram Graph API, LinkedIn API) for sanctioned scale access; (4) licensed providers (Social Blade / Apify official datasets) that handle ToS. RECOMMENDATION: do NOT build a stealth scraper for two holdout platforms -- the ToS/legal exposure is not worth it for an org that 'operates under the radar.' Revisit via official APIs only if IG/LinkedIn become a scale need.</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G66"/>
+  <autoFilter ref="A1:G67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,9 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$G$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>66 records</t>
+          <t>68 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>93 records</t>
+          <t>94 records</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4572,8 +4572,36 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>THREE kinds of 'not done' -- keep them separate</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Data Ethics</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Every blocked/declined/deferred item</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Makes declines findable and override-able</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026, wants to find every 'where I won't go' so he can address it later with other tools. The audit found they were being logged but MIXED with capability limits under vague labels. FIX: every backlog item that isn't simply 'open' now carries a blockClass, so Andy can filter three genuinely different things. WONT (ethics/legal -- Andy can override): Claude CHOSE not to, on licensing/ToS/safety grounds. Andy can legitimately route around Claude via other tools or people. Examples: Start-Up Nation Central bulk extraction (their ToU), stealth/anti-detect IG/LinkedIn scraping (ToS/evasion), entering Andy's credentials, solving CAPTCHAs. THESE are the ones Andy asked to be able to override. CANT (capability/tooling): not a choice -- the environment/tool cannot do it. Needs a config/key/tool change, NOT a moral argument. Examples: logged-in browsing (tool refuses navigation), reading regular-Claude history, the living/deceased filter (no death-date data). CANT? (unverified -- re-test): recorded as blocked but NEVER actually tested. Claude was wrong 3 of 3 times on capability claims (social platforms, jsc, congress.gov), so these are suspect until browser-tested. NOTYET (effort only): no blocker at all, just not done yet (Senate sweep, IAF backfill, handle/source backfill). HONEST NOTE for Andy: the WONT list is short and each item is a genuine ToS/safety line, not political correctness -- Claude is not declining to track anyone or make any judgment Andy wants made; it is declining specific ACCESS METHODS that break platforms' rules. Those are the ones another tool or Andy-in-the-loop can handle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F94"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44416,7 +44444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44426,6 +44454,7 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -44464,6 +44493,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>blockClass</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -44501,6 +44535,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>CANT? (unverified -- re-test)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -44538,6 +44577,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>CANT? (unverified -- re-test)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -44575,6 +44619,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -44612,6 +44657,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>CANT? (unverified -- re-test)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -44649,6 +44699,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CANT? (unverified -- re-test)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -44686,6 +44741,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>WONT (ethics/legal -- Andy can override)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -44723,6 +44783,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>WONT (ethics/legal -- Andy can override)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -44760,6 +44825,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -44797,6 +44863,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -44834,6 +44901,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -44871,6 +44943,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -44908,6 +44981,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -44945,6 +45019,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -44982,6 +45057,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -45019,6 +45095,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -45056,6 +45133,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -45093,6 +45171,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -45130,6 +45209,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -45167,6 +45247,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -45204,6 +45285,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -45241,6 +45323,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -45278,6 +45361,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -45315,6 +45399,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -45352,6 +45437,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -45389,6 +45475,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -45426,6 +45513,7 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -45463,6 +45551,7 @@
           <t>Source audit, Jul 2026</t>
         </is>
       </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -45500,6 +45589,11 @@
           <t>Session Jul 2026</t>
         </is>
       </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>CANT? (unverified -- re-test)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -45537,6 +45631,7 @@
           <t>Johnnie Moore interview transcript, Fri 19 Jun 2026</t>
         </is>
       </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -45574,6 +45669,7 @@
           <t>Johnnie Moore interview transcript, Fri 19 Jun 2026</t>
         </is>
       </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -45611,6 +45707,7 @@
           <t>Seed-100 pass, Jul 2026</t>
         </is>
       </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -45648,6 +45745,11 @@
           <t>Audience audit, 14 Jul 2026</t>
         </is>
       </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -45685,6 +45787,7 @@
           <t>Andy, Jul 2026</t>
         </is>
       </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -45722,6 +45825,7 @@
           <t>Andy, Jul 2026</t>
         </is>
       </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -45759,6 +45863,7 @@
           <t>Andy, Jul 2026</t>
         </is>
       </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -45796,6 +45901,7 @@
           <t>Congressional sweep, 14 Jul 2026</t>
         </is>
       </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -45833,6 +45939,7 @@
           <t>Andy, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -45870,6 +45977,11 @@
           <t>Andy, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>CANT (capability/tooling)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -45907,6 +46019,7 @@
           <t>Andy, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -45944,6 +46057,11 @@
           <t>Andy, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>CANT (capability/tooling)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -45981,6 +46099,7 @@
           <t>Claude, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -46018,6 +46137,7 @@
           <t>Claude, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -46055,6 +46175,11 @@
           <t>Andy, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -46092,6 +46217,7 @@
           <t>Claude, found 15 Jul 2026 while adding the government-data sweep</t>
         </is>
       </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -46129,6 +46255,7 @@
           <t>Claude, 15 Jul 2026</t>
         </is>
       </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -46166,6 +46293,7 @@
           <t>Andy, msg #97 -- reasserted in the 16 Jul 2026 audit</t>
         </is>
       </c>
+      <c r="H47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -46203,6 +46331,7 @@
           <t>Andy, msg #115 -- reasserted in the 16 Jul 2026 audit</t>
         </is>
       </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -46240,6 +46369,7 @@
           <t>Andy, msg #61 -- reasserted in the 16 Jul 2026 audit</t>
         </is>
       </c>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -46277,6 +46407,7 @@
           <t>Andy, various -- found by the 16 Jul 2026 audit</t>
         </is>
       </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -46314,6 +46445,11 @@
           <t>Andy, msg #134 -- diagnosed by the 16 Jul 2026 audit</t>
         </is>
       </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>CANT (capability/tooling)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -46351,6 +46487,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -46388,6 +46525,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -46425,6 +46563,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -46458,6 +46597,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -46491,6 +46631,7 @@
           <t>Claude, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -46524,6 +46665,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
@@ -46557,6 +46699,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr"/>
@@ -46590,6 +46733,11 @@
           <t>Andy, standing instruction; reasserted 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr"/>
@@ -46623,6 +46771,7 @@
           <t>Andy, 16 Jul 2026</t>
         </is>
       </c>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr"/>
@@ -46656,6 +46805,7 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
@@ -46689,6 +46839,7 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr"/>
@@ -46722,6 +46873,7 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr"/>
@@ -46755,6 +46907,7 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr"/>
@@ -46788,6 +46941,7 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr"/>
@@ -46821,6 +46975,11 @@
           <t>Andy + Claude test, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>CANT (capability/tooling)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr"/>
@@ -46854,9 +47013,90 @@
           <t>Andy, 17 Jul 2026</t>
         </is>
       </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>WONT (ethics/legal -- Andy can override)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>WON'T: enter Andy's credentials or authenticate as him</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Blocked (Access/Ethics)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Needs Andy</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Standing safety boundary, logged for completeness per Andy's 'catalog everything I won't do' rule. Claude will NOT type Andy's passwords, log into accounts as him, or handle his credentials -- even when Andy asks and supplies them. This is why the login-walled platforms stay walled from Claude's side. It is a hard boundary, not a judgment call about BFT.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Andy-override path (legitimate): ANDY logs in himself in his own browser and either (a) a permitted tool reads the already-authenticated page, or (b) Andy reads the value and pastes it. Claude never touches the credential. There is nothing here for Andy to argue Claude out of -- the workaround is Andy acting, not Claude relaxing the rule.</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule; logged 17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>WONT (ethics/legal -- Andy can override)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>WON'T: solve CAPTCHAs / bot-checks</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Blocked (Access/Ethics)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Needs Andy</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule (also in Claude's memory): Claude will not solve CAPTCHAs or other bot-detection challenges. When one appears, Claude pauses and asks Andy to solve it, then continues.</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Andy-override path: Andy solves the check in the shared browser session and Claude proceeds. No tooling change needed; just Andy in the loop at the moment a check appears.</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Standing rule; logged 17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>WONT (ethics/legal -- Andy can override)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G67"/>
+  <autoFilter ref="A1:H69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -22,10 +22,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$L$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$P$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
@@ -32238,7 +32238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32249,12 +32249,14 @@
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -32300,30 +32302,40 @@
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
           <t>sourceNote</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>researchNotes</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>addedBy</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>yieldStatus</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>yieldNotes</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>related</t>
         </is>
@@ -32370,12 +32382,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>https://covenanteyes.com</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxQTEhATEhMVFRUXFxsaFxUVFxoZHxoZHRgbHR8aGSgbKCghHRolHRoaITQhJSkrLi4uGh8zOD8tNygtLiwBCgoKDg0OGxAQGy0mICU1LzcuLzUyLTc1LS41LS8tMC4vLy0vNS0tMC0wLS8tLTU1LTIvLy8tLS8tLS8tLS0tK//AABEIAIAAgAMBEQACEQEDEQH/xAAbAAACAwEBAQAAAAAAAAAAAAAABQIEBgMHAf/EADkQAAECAwUGAwcDAwUAAAAAAAECAwAEEQUSITFBBhMiUWFxMoGxBxQjQpGhwVLR4WKy8SRDcoLw/8QAGgEBAAIDAQAAAAAAAAAAAAAAAAMEAQIFBv/EADARAAEDAgMFBwUBAQEAAAAAAAEAAgMEERIhMRNBUWGhBSJxgbHR8DJCkcHhI/EU/9oADAMBAAIRAxEAPwD3GCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCJfa9ssy26L6wgOOBtKjleIJFToMDjG7I3Pvh3LVzw3VeZe1pqelXPepeamBLuGikpcUA0vSlMkK9a8xF+jMbxhc0X9VVnxtNwckx2S2nctKz3pdLym55pHCsGhXd8KvOl1XeusazQthlDiLtKyyQyMLQc0n9nW38wqbRLTrl5K6oBUAClyuAPc1T3IieqpGbPGwaeijhndiwuKbSHtLdTO+5zTKB8YtFxBIpxXQog1wy1jR1A0xbRh3XWzapwfhcFqJbbmUVMrlVKU28lwtgLTgpVaC6RUYnnSKpo5QzaDMWuphUMxYTqmhttreBtKipRVd4RgDWhqekR7B+HEdFoayLaCMG5S9W0SlPBptA8d28STrQnCJv/ADAMxOKqntBzpdmwb7XVa2rbc3pbZNAOHDMq1/aN4YG4MTlDV1sm1wRnT1V21LQLDKW7xU6oYnlzP4ERRRiR5dbJWKmoMEQZe7j8/wCLns4l1Z3i3F3BkCTxH9hG1QWN7oGa0oBK87R7jb1T2XmUrBKDUA0r1EVXNLdV0o5GvuWldY1W6IIiCIgiwPtksJ+ak0bhN/dLvqQPERdIqnmRU4Z8ot0cjWP729QVDSRksJsHt6kNmQtH4kssXAtWJbB+VWpTyOafS5PTG+0j1VeOXLC7RKLYs9+x55C2V1SONh3MONnQ0wOBoR56iLEbm1Edj58lE4GN1wuu2TSXnGp+UCrkwaqSnEtTCaFaDTI5LB1qTGacloMT9R1C1mt9Y0Kt7S2Y/NOMzaG7inW0l28Qm68jhVhoDRKh/wAo2gc2MGM7tPBQTTsNnX19UwnLGdXaKJoKbALjTpFTnwqVkP1VjDHgQlnIhaOqW7QHwK7WPZ8wzOvTKXEUvPOXAo0KiFFIIIp4iISOY6EMI4BatqG7Qu4XTrZeceRvHH2wlaE8KkqBSpasB1BAqfKIahjXWa05H0WkDmxkyA6aeJ+FNLFogqmHMQjwj9ThyHlnEM1zaNu/0WaWzbzP0GnMr7IsKmnVKWcM1q5DkPSMPcImWHkkUbqmUucct5Vy17YBG5YwbGFRr0HT1iOKC3efqp6qsuNlF9PqnWzkottohYoVGoGoFBn9IrVDw52S6FBE+OPvb01iBXUQREERBFgfaltY/Z6pFxm6UqU4HG1DBYARTHMEVOI56xbpYWy4gVBM8stZYi1bOlbYC5izxupwC89Kqw3n9SD4b3rrQ53GOfB3ZM28eCrPDX5tyPD2Vmw7N/0/udoK3jYVVvA1l1a0OZQcinLljEz22dtI9fVc3/2g/wCZFhx3g+HqExlEBhK2UpSlB0TlUZKHPvqDGxGKzlTL3C7X53+AqIWaU0rWM2UV8rKQVBLqaTGFm66BZpTStY1ss3ysrW8K7iBglOVcqnNR/wDZARpYNu4qXEX2YNB8JVt+c4QwzW5XE0xcVzPTkIjazPG/X0Uz5e7sotPU/NAmMo23KgLd4ntGxjd79YheXTZN04q1G2Ol70mbuHBN9n7QU9vVKpgRQDQYxXnjDLAK9RVDpsRcm8V1eRBEQREEWQ2znZF0e7zLe+GpTm2aZpOFFdvPlF6mgmtjabftc2qroGOwOz8NyzCNn220gyCgtAxujBwdSM1dxF5sx+mUW9FypoTIdpE7F6jy9lzmp4uj4gq4ML+RNNF8z1z7xu2PB9OnD2VaSYyDv68fdVgY3USkDBF0BjCypAxhZUwYwsqaTGqyrsrNlA+GKLOF/UdE8u+cRuZi+rRTRylg7mvH2VyXs4DimF7sZ3c1nyzHcxG6QnKMX9FOynA70xty3laGxLTYPw2xc5Xvm/mKc0Un1OzXUpKmA/5sFv2ncVl0EQREEWUtvbRDLm7bSHaeM3qAHkM6mL8NC57cTjZcmp7UbE/CwX4pHM2jIP1K2nGVH5m6EV6jL7RabFUR6EEc1RfNRzZuaWnl8/SXO2ekcTEwhfIGravor8GJhIdHtI6hVXQtGcbweh6qm86pR4zU6k5+fOJAABkoHOcT3l8BgsJvs/YqplRobqE+JX4HWK884iHNXKSkdUO4AalbuTsCXbAAbSTzXxH7/iOW+okdvXoI6KCMZN/KJuwWHAathJ5o4T9vzBlRI3esSUULxm23gsVbVkKl10OKT4Vfg9Y6UMwlHNcGqpXQOsdDoVQBiVVl3l3FA8JoeYz/AIjVwB1W7HEHuq8zJpzdeSnmBVavt+8RF50a1TthbrI8DqUwl52VaoUtrcUPmXT7f4iFzJn6mytMmpYs2tJPNNrM2iS4u6sXK+E1qD0PWIJaYtFxmrtP2g2R2FwtwTyKq6KQ2rtbLsOFtRUpQzuAGh5HEYxaio5JG4gqE/aMML8BuTySOYt6zXPFLnuG0g/YiLTaeqbo7qqL6yhfqzoPdLJhdmq8ImEdrp/uJidoqhrYqq80LtMQ/H7S19qX/wBt1fZbYHoTEzTJ9wH5VV7YftcfMf1VAYkUKkDGEXquzcoG5ZkDMpCj3Vj/AB5Rwqh+KQletooxHA0ef5TOIFaRBEs2klguXdrmkXh3GPpUecT07sMgVSujD4HX3ZrzkGOwvLqaTGFlXpdtn53F9ko/cxE4v3BWGNi+5x8h/UxYVJDMPK70HoRELhOeCssNGNcRTBi1ZNPhaPcpB9TEToZzqVZZVUjdGdP6mkjbjTqrqag6XgBXoMc4rvp3sFyrsNbFK7CNVUtXZKXfcLigpKjncIFTzOBxiSKskjbhCjn7OhmfjNweSRTNg2a34pg9g4kn7AxabUVTtG9FRfR0LNX9R7JXMJs1PhMwvtdH9wETt/8AUdbBVHihboXH8ftLph+X/wBtpzutwH7AD1idrZPuI/CrPfD9jT5n+KmDEigUgYwsr1fZqbDssyoZhISe6cP5844NQzBIQvW0UokgaR4fhM4gVpEESvaWaDcu6TmoXR3Vh6VPlE9MwukCqV0gZA6+/JecAx2V5dTSYwsq9LvM/O2vulY/IiJzX7j0U7HQ/c0+R/iZMCSOZeT3p+AYhdtxwVpgozqXBMWLKk1eF4npfA9RELppxqFZZS0jtH9R7JpI2G00q8mpOl4g06jDOIH1D3ixVyGiiidiGvNM4gVxZK3NiUPObxtYar4xdqCeYyoecX4a9zG4XC/Bcmp7KbK/Ew24pDNWfIMVC3nHlj5W6AV6nIfWLbZKiTRoA5rnvho4cnOLjwHz9pa7aSDwsS6EVyJq4v6q/AiYRHV7iegVZ07TlGwDqevsqT7aknjFDqDn58olBBGSge1wPe1UQYLVOtnbdVLKOF5CvEn8jrFeopxKOau0dY6ndxB1C30ntBLuAEOpHRZun7/iOS+mkbqF6GOtgkGTh5onNoJdsEl1Kj+lBvH7fmDKaR25YkrYIxm6/gsNbltKmF1PCgeFP5PWOpBAIhzXAq6t07rnQaBLwYlVVd5dCieEVPIZ/wAxq4gardjXE91XmJ5GTrKVdRVCvth9RERjOrXftWGzN0kYD0KZS0lKO0CHVtqPyrpn0/zELnzM1F1ZZDSy5NcQeBTiytm0tLvrUF08IpQDqesVpaovFhkr1P2c2N2JxvwT6Kq6SIIiCLK7UWFKVD7yt1+q7Tj7D9XURfpqia2Bgv8ApcqtpKa+0kOHw3rIzNtJHw5NrdJOF4YuK88x2EdBsB+qU39FyH1QHdgbhHHefNVJuRLQ+KaOHHd5kA6r5Hpn2jdkmP6dOPsoZITGO/rw91UESKFTBjCKYMYWVMGMLKmDGFlTEYWVelJQuD4RqsY3NT1Rz7ZxE5+H6tOKnjiMg7mvD24qwbdbSn/WJCkjC/k4Og1V2Maime4/469P4p46gO7szb89481pdl5SUWN+wvejSuaOhGiu8Uqp0zDgkFv2urSUsAONhv8ApaSKS6KIIiCIgizO2ViOTRlkt0ABVeUckg3fM5aRdo52whxdyXM7RpH1BYG87n8LO2hMMSILUtxzGS3jQ3OidAfTWsXI2yVHekybw4rnSvioxgizfvdw8Esk7Po2ZqZrcJ4Ek8TyuXMJ1KvpE75O9s49d/JVY4bM20um4b3H24lVkNlwOOqwSmlaYCp8KE/TyAMbkhtmjX5mog0vBedB8A+blwCTSulaecbXzso7G119EEU0xhZXUJNK6Vp5xrfOyzY2uu76wwG3SpIQrIqyqPEg8/2IjRo2hLN/zNThrm2e3MH4Qq9rz1GRNyQK271FGpqyvkRmRqFdq4xJDHd+ymyPqPmqsOp7Das06g/NCp2ZNy9qhLU2d1NgUbfTgHOihle6YV05RtIyWh78WbN44K2wx1Pdfk7jx8VrvZ5s67Je9odAopSChaTgoAK8x2Mc7tKrjqMDmc7jgrlFTvhxB3JbKOWr6IIiCIgizG31puMMJ3Ru31XSrUChOHImmcXaGJskne3LmdqTviiGDK+SzmzOzAKfeZvhaSLwSfmHNX9PTM+t2pqjfZxarm0dAC3bT5NHX51VCfm3J+ZSltNB4W0aJSNTywxMSxsbTx3d5qCWR9ZMA0eA4BT2iUlKkSjOKWsCR87p8RPXIdKRinuQZXanoFmsIaRBHo3qd/sqO1cm6hTTDCwFNoAWlSQQpxXEcc64hP8A1jancHAvO/0WZhHG4QuF7a24nM+yoWhNvN2g1LFCabxpu8QcTwpJFMM6xsyzoS/xKnNMwy4QdLBRsy0XFzzkrdQKl5sGh8QC7uv6gI2e0CESeBRlK3aFvG4XDZidemlPypXdW42S1dAFHW+IDzSFp84kqGtiDZLZA5+BWYYWG7La+oUdj1pfU7IzCiEv4tqViW301unHmKpI1wjeqBjAmZ9uvNvzNSQWd/kd+nI/MlKw7RdsybcbeRVPgfaOIUnmK4HA1HMGmsbTRMq4Q5hz1B4FaxvdTyEOHiE22y2NCEickuOXUL1E4lAONRqUfcRFQ15cdjNk4df76reppbDaR5t9Ft/ZjbD0zKqLyrxQu4FakBIPFzOOccrtWnjhmAZlcXV+glfJH3ty18cxXkQREERBFVnrPbeubxN4IVeAOVQCMeeeUbskcy+E6qKWFklsYvY3WP25cmXlblph0tJNSoJNFq8vlHr2EdGiETBjc4X9Fx+03TynZsYcI5aq5YNjLlJVx1KCuZWnBOqa5J8sz26RHPO2aUNJs0fP+KalpXU0BeBd56fN6X7KbLuh8PTCaBPEATUlele2fekS1VWwx4GH/ir0NBIJdpKNPVX5fZBZmN+84k/Ev3UgmuNQKmmEROrWiPAwbrKdnZrjNtZHb72ThvZxgOqeKSpZXfqo1AVWoIGWEVzUyFmDcrraGESGS1ze6oObDSnvKJpCVNupc3hKFYKVWpvA1zPKkbitl2ZjOYtZbmmZjxjVZt32cOtTgmpZ5FA9vA2sFNAVVKaiuFKiLg7RY6HZvB0tdVjRua/G070t242GmPe1zEm2VJWQvhIBS5XGnnxecWaKvj2QZKdMvJRVNK/GXMCcbV7OuT8m1MlpTc4hHEgihWBmn61UnvTWIKSqbTTmO92Hfw+b1JPA6aIPtZw6/Ny4+zN2cYV7s/LPBlVSlSkEBtWZBr8p9e5iTtNsEo2sbxiHPVaURlYcDmmx6Le2XZTUuHEspuJWsrKRleIANOQwyjjyzvlILzewsujHE2O4bvV2IlIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIiCIgiIIv//Z</t>
+        </is>
+      </c>
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
       <c r="M2" s="6" t="inlineStr"/>
       <c r="N2" s="6" t="inlineStr"/>
+      <c r="O2" s="6" t="inlineStr"/>
+      <c r="P2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -32420,6 +32442,8 @@
       <c r="L3" s="6" t="inlineStr"/>
       <c r="M3" s="6" t="inlineStr"/>
       <c r="N3" s="6" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -32462,12 +32486,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>https://allot.com</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBEQACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAABAUBBgcDAv/EADkQAAICAQIDBQUECQUAAAAAAAABAgMEBREhMUEGElFhcRMjgcHRIjIzsQcUJEJDUnKR8BVigqGi/8QAGwEBAAMBAQEBAAAAAAAAAAAAAAMEBgUCAQf/xAA0EQACAQIDBAcHBAMAAAAAAAAAAQIDBAURIQYxQVESEzJhgbHRFCJxkaHB4TNCUvAjQ3L/2gAMAwEAAhEDEQA/AORHo+AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAHtj4l+T+FW2vHkjxOrCHaZetMOurt/4YZrnw+ZY1aHJ7e2uS8oopzvkuzE0VDZOTWdap4Jff8E6rQsR7d92S/wCWxWlf1eBeWzNlFa5vx9D3XZ3BmuHtY+amRPEqy5HiezllwzXieN3ZTvccbK+FkfmiSGLZduPyObX2by1pT+aKfP0jOwN5ZFD9mv4kXvE6FG8o1tIy15HDucPuLbtx058P78SCWikD4AAAAAAAAAAAXWnaQuFuWuPSH1KtWvwibPCtnVpVu/CPr6FukoruxSSXRFCTb3mwhBQWUVkguZBI9EivoQyIpEqsrzIZEqshZDIlQScWnxT6PkR55alaaz0ZQa72UrvjLJ01Ku1cXV+7L08GdazxVwyhW1XPiZy/weMs50NHy4M0icJ1zlCyLhOL2lFrZpmhTUlmtUZhpp5PRmD6fAAAAAAAAXOi4KSWVauf3I/MhrS4I2GzuGaK6qr/AJ9fQuilI2SRhkDPZhcyGQPRX1V/iWQj6ySPHVyluRUq3FKn25pfFolUZFM/uXVyfgpIgqUpreiBXNKo8oTT8SdWVZBkusikQSJVZEyGRrnbPQVl48tRxIbZFa97FfxIrr6o7GF33Vy6qe5/Qz+K2PWLrYb1v7zQPRmnMzmD4AAAAAe2FR+s5MKvF8fJBvJZlywtXdXEaXB+XE2yMVCKjFbRXBIpyP1GnBQiox3IyQSJkeds41wlOb2ilu34EPRcnkjxWrQo03Um8kigzNUtubjU3XX5c2X6VrCGstWYDEdoK9zLo0X0YfV/Er3xe75+JaM89XmzG3VcGgNxb6Xr2VgzUbJO+jrGT4r0ZRubCnWWa0Z1rLGK9u8pPpRN70/KpzMeF+PLvQkuD+Rmq9KVKTjI2FG4hcU1Ug9GWNZUYkSYLdNNbrwI+JDLccr7VaZ/petXVQW1NnvKvR9PgzaYdc+0UFJ71ozGX9v1FdxW56oqC8UgAAAAXHZ6reV1rXJKKf8AnwPE9xrNl6CcqlZ/Bff7F0VpGzRkgkSIoteyXK1Y8HsoreXqWLanp0mYjae+cqitYvRasqS2ZMAAAAGwdjtReNqCxZy91kcEn0l0OXitv1lLprevI7eC3bpVuqb0l5nQquhlpGrZJrIWQyNU/SViqeDi5i512OEuHSS+q/7O3gVXKrKm+Kz+RwMZpe5GfLQ5+akzwPgAAANh0FbYLfjNkc95vNmo5WefNssSvI0aMkEiRGp50u/mXS6ub+h0Kaygj8pxKo6l5Vn3v0+x4HspAAAAA9MWx05NNq5wmpL+55qR6cHHmiSlLoTjLk0ddqe+zMJI/QXuJVZCyKRVdtq/admMv/b3Zf8ApF/CJZXke/PyOXiaztpHKTaGTAAAABsOgv8AYdvCTI57ze7NtOyy5NliV5GiRkgkSI1LNj3cy6PhNnRpvOCPyjEIOnd1Yv8Ak/U8T0UwAAAAfePB25FVcec5qK+LPM5KMG2e6cXKcYri0deq4bGEkfoT3EqshZFIq+2k1Dsxmb/vKMV695F7CY53kP7wZzMSeVtI5QbUyQAAAALns7Z+NU/6kRzNfsvW/UpPuZcleRsEZIJEiKDXcZwvV8V9mfCXk0WrapmuizB7TWTp1/aIrSW/4r1XkVZZMwAAAD6C87IYEsrVI3uPusd97fxl0XzObidwqdHorfI6+DWrrXHWPdHz4HRauZk5GvZKrIWQyNY/SRlKvS8fFT43W95ryivrsdrAqXSrSnyXmcLGKmVOMOb8jnZqTOAAAAAk6dkfq2XXY3tHlL0Pklmjo4Xd+yXcajem5/A2noVJH6bFp6oyQSJUeV9ML6pV2LeMkRKTi80Q3NtTuaTpVFmma7m6fdjSbUXOv+aK/M6NK4jU7mfnWI4NcWcm8ulHmvuQyc4+aB9BP0zSMrUZr2cHCrfjbLkvTxZVuLulRWrzfI6Fnhte6a6KyjxZ0DS8KnAxYUUR2iub6yfiZa5ryrTc5Gzt7WFtTVOC/JZ18ymz3Ik1sjZDI5h2y1NalrVns5d6mj3UPPbm/wC/5Gxwu26i3We96sx2I1+urvLctCjOiUAAAAAPhuAX2i5ysrWPbL7cfuN9UQVYcUbjZ/FFVgrao/eW7vXqWhTkatBkDPRjnwfIiYazMPAxLfxMeuT8e6fPaKsd0jmV8Ms6rznTT8CTj6bhVtOONVv493chqXVZrJyII4ZZ03nGmvkWlSSWyW3oUpNsnaS0JdZDIhkSqyJkMik7X67HTsR4uPL9rujt/RHq/odPDLHr6nWS7K+rOJil71MOrj2mc4NWZQAAAAAAABSlFpxezT33XMHqMpQalF5NF/p+qwuSryGo2dJclIp1aLWqN1hOPwrpUrh5T58H+SzZRZqE0YXMhZ9JFfQhkRSJVZXmQyJVZCyGRLrImivJlTrnaajToSpxXG7Ja6PeMPX6HQs8NnWfSnpE4eIYpToe5DWX0RoORfbk3TuvslZZN7ylLqzTwhGEVGKySMjOcpycpvNs8z0eQAAAAAAAAAAS8XUcnGXdU+/D+WfHb0IalCEzrWWNXlp7sZZx5Msadaqe3tapR81xRTnYy/azR2+1dCWlWDXw1/JPq1fB4b3d31iyrKyr/wAS+sfw+X+zLwZIWt6fBbu/f0iyF2Nd/tI545YL9+fgzyu7VYta9xTZb5v7KPccKqPtSSOZX2joL9OLf0KfP7Q5+ZF1qz2FT4d2vg36s6NHD6NLVrN95wrrF7m40z6K7vUqS8csAAAAAAAAAAAAAAAAAAAA+gHwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/9k=</t>
+        </is>
+      </c>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -32510,12 +32544,22 @@
           <t>Company reporting, ACTS 17</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>https://anduril.com</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAY1BMVEX///8AAADX19f7+/vo6OgVFRX09PT4+PhaWlrg4ODPz8/s7Ozb29t7e3uurq7T09MdHR1gYGCmpqaPj4+5ublsbGwlJSVNTU3IyMgNDQ0xMTE4ODh1dXVVVVWGhoaenp5AQEBN5at6AAAF+0lEQVR4nO1a16KrOAwMPdTQW0L5/6/cIMlgmyQbToB9WM/LvccUy/JoJItcLgoKCgoKCgoKCgoK2+HrrxE4JxmQam/g/ccGWPX/xYDh3RbkJxmQ0XzldUbXnGiAE5IBocng69U0EJ1jgF2QAb2xGAVjwzkGmB0ZUHBxH0oWHQl3JAMSexkEXjzs90/tCK8kAyp/GYymgc48xYA8JgNGlxucBu7BGfMbWcPCkBOeWysNHAeHBYHWcGHnT8xshjNYOAeBEHbOA5ThjHxYTxy0Snm+YdqYzn//3G6ATJBksRQG+WRSe0JCNlDzgkkMGi4MUB1O0EJzortWGwn8s4zbQILieBZiwLuovRl3AaqE8nApsmHiggwZuSt6fEpCdKe8a6XPrZhYH3MkcK6npIOUabABcpBylyAQ7wfHgQ3L7KdlQjiGHOlud5kWB+AGEgylV21NvuBIh3EwHqpFKLgd7DNKMl8G5tbhNIScx7zcgyRyV20oDK8H0hDLUVYG1JCQ+OkGOUfuDayFZrlt5TgwQY4PzEiQBkad/ZmtPA6RKNi0K3KpCAhKmYZmdaQe25B/2uXtGBMFfw8eGw/SAvB4w/sXpIBPiRcHYvOYU2oAi0t4hnnxygVYMo8HlGY+iHDDr80AJdBiXv6d/qBNMF68+EYHBP6IdjHvi1rvCYwA8ejD6nNxy+GMpN13jgQP6FYKubbWGEZ+mHw17qrIGN+iwsyndEkL2M39jkQ08JUPoeKMQPUK2PLK5a8Ezc5ExEQvabxbYvb3YLZeeABt2y8xU0tGpFVPm2KAddZNuIhdpHifUKDDaKkLo7jIqRrAg0IlpkD02S4+sMMXPMPimFqjpP8CQTBvaFb080GF3iTNj+czmhRvkfyNwqlZ2Y8W6Dh/KfrSwEUnxAos1FohEpgFWvaTItUV7aW4jvq+bMAEtOch0sClPkIhGrYF/gD6p7USlwKU+6UyIZ5K0sN2b8z/KEnug+aXoslHihfcgnUoBuVy1KRYaLO/yLIdkfsrMf4uPipAJXTEoG2yMtXOLNoGbzMX9ZB6YaG0hQaKjNwQww76KI0a6Z2cMGzjoj1QNzSWvWdEsChL7oeRXFSyuTW9qLlukEU/Je9r11Vxl2IRMqx4RczobtK427O+ZlF/S8aevG/J7p+7pMULVlELuZOfsSPaBq38toOELGu6WmaOkWKb+PEytD30W6fLFwLmhPBLA1zkjezMJ9OQ1MkbQpE+rXbh4kRo+NetZCCUtUplKW5N8vY9OVowriyo1/X7R+go7tJC6VPRpyYMUURKHRcHT2zfd29YDS5wwCMqxeFqkxmCkIRH8h4WylsayT6spBTOnew7yWTC7cW7HH0OOE3MTB7szLYj67CSlUzj0BSR5AY9Khr+Dq2bmeJjUtrWxfUxvy1dPxOc27bzBO21j3TbeML2orBbLpRMfdk2oOnFxrYF8lDLmK/hLa3u96X2EXFo2j39PwSno3a3b4nzDlhkxGwZwIDHk5+34vXMiGSSW4N9263qWRy2d00oEqgYDIBfuK1B2L6a+xmgIdv3G1PfzMN7//JF0aRyECyAs2nJLrlRYq18X0QcZU3RT++08zMCNB7KXdgQrifo+HV/bcvYeiJu70nm+WJkGilnYvvHz3mUy63UocawfIMfeJ6nm6/dq89OuP+5Y0PKamXogce2p5l0WT+c0GqiWwJ86DY9G9CRqvzphJgvAvxcygYqG+xIIReqW+HxFny/l3Mh1v7csdO5gPr2m5iZzl/411XNZvjhbMB3B34771heeuzTqspZkayVmfsvSd1xh3nTqt1aJMGSascw/7Aqsw5HdmtT7PhrAntxgmZVYRTYKzYYdhCF1VKSVPm+X07MdDFBa8oqHHJPd03/CdMNvHx4lgRcRVJtPIp9AzfjI1JrrPJedckTXTWWllAOjZl7yDdkPyreJGIebRId983mmQOrz9NXfX3wjxj8ekja+NXcVnsdjp4dYbv10BcVVx2WVdEP+b9pxK4wbNN1A/opp+ua67hUUFBQUFBQUFBQUPgS/wDvK0q2t2GyWgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -32558,12 +32602,22 @@
           <t>CNBC, Times of Israel</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>https://palantir.com</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAACAAAAAgCAMAAABEpIrGAAAAaVBMVEUQGCD///8SGiKVmJzw8fGbnqLe3+D6+vqSlZns7O2usbO0t7kbIipgZWvp6uqoq67DxceMkJRqb3Q4PkVvdHl7gIQjKzLLzc5iZ2w8QkkxOD/19fYeJi2ipaiEiIy8vsBKUFZQVlzZ2txFlffPAAAA1klEQVQ4jd2S25qCMAyE+0Pl2NKKiIqA6Ps/5AKrcpHq/W6ukm+mk0kapf5dHHZJmia7wwc4ivmNNIuChALyoWmGHIoQfoSyXZK2hKPEjeb0VI5OaCMIZ3ibu4AVhJhqK3IyQXD4rfC47woVsSDU0L3yDmpB6K9bD8+1FwQ1wrAOZwYYJa4iD8ne2n0Ct+CujXv+BU6uaRaojZoKDbqYlKmlRIPO5jH62V0XaxpBKBft8q7U/bZmssfk0hl4PJaDcFPIpGrHanlcjW0QXp1a7234nP52/AB6Iggd6dET3QAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -32606,12 +32660,22 @@
           <t>Times of Israel, JTA</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>https://oracle.com</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAACAAAAAgCAYAAABzenr0AAAEoklEQVRYhbWXTYgdRRDHf1Xd72M3ZmM+BMFLVBDRKHgSScSjGlASjBoRBBMRPXjIQQXxKIh6iOghomI8BBFjIOIhns3m4kFJQDCioARviclqNvvem+kqDz2zb968jcS4KRh6uru6//+u7qqultfeeJ2miDdrEaEHHgFQz99YDBhWJZWOjnslf179VxoAeFWP0hgANgUQzYBymcAESTHcDWRMAK8hsp5WJKhKrVRDVcZgTQJNU2Twno0qZZtScTXcvNU6PV+pMKpWLCgdg16CmCBuGJQTK24S6CRjxpzgNu4TYwypmPuyOamsWZtbPVshKSx1oBQlGnQTrCmgkyDesnBpZQJA8JIZH9KxMcnxXmZJPtngMmkBcUgCo5jLYEq/hLWjTCTeeOmvKZPVe6yU23oM7w1e3gr0gZa9DWs35S0QYAD8AnxnMF+E3NtJmcBsURFYP7owRUBhPdhLYDtU0t2KheW+Jp4YWNE6hBNekFw4acJXmngvGBe6Sekl6JYQHOTM7u2T4M4+4B3EAhgiMgaj7aaGeAGSGpyWueIy3rJglNF5OSZ9t5MyuDpEpHkIOWzCrgkAndxjbdWMCMQVFcTHbgdEg/2lcl8SnqwWS2wcvC+gCb4s3wDfAn/C9CF0X9GNBVivwgM4D9ZWszz+CQQDnqJB/Rng8dYkx4AXgd9XQrhCeRPYDBwAHmq07wa+Bj5ToAd80Bp4ENj+P8Fr+Q14GPi01f4h0FHy6mcaHT8Be1YBuC3PAqcb9TXA0wrsaCm+cg3Aa3m1Vd+pwJZGw0XyobtWcqzCqGWLApsaDaeBYrXQxKFj+VMHF0Yu/NyI3pui6ERokfYk07fdlUsw6Bd50qUOFAJJUK36guW4ebYx5nayV6yKuEARoNAcA1zom3BbKbltFDmrwKnGmFngkdUiMAxwoQ/nZ2CQI86jwGxSWOzCQo+TChxpjXt7tQh4tdJiHCzfgnwtDyJc7HJEgUNA806+GTi8GgRClXz0S+gYXwZjc70tg8j5Sx0+VyAxHXh2AceBO1aBx53AfFIeS5o9o5dgbsiejUtYfRccAT5pEdkG/AicAI6LyrmVZv8XL9mYlPsLZWsN3LGciFw/4KPZgqMxQVy7lEgKSdmbBE/KXgCtPNLdtwJbpX0N1gT88m5qkH1QchzoGPRLPp4b8jwDoIQ4d3EIAUY9WIo8NxROuLA/GOsApM7xLoPjPp0t16JWEchZ8EK/YN/agoM0UpBI6uWc3aBwGDkHk3AoqL6gsFORu9QnouUkgcsxAwo4VwqngKMKBzpCUQj06qRJIC7MbqQIOVINIowClEohIu9H44euyz3BuElEJgJU2/QrbMWoCPyxGPk+KfPdAIsB/g7Qj9k7gkP8dd0GUiNilQFKAVRQmO8lmQ/OODe8cgIU1XsgaX6E9FJ+C3RTPg/iEE/dMLc8oAqXlAopZMAgglwlgfpdWFmbaONP6qT0zHWzBM9BI1oelBSKKJjk56leJYG21KAwLuNiVwmVfzYtUVbZsCbJ5voPBGqPNfJimul5XdbacRRyZpo0W0HIA2oFrZm3VjMVfxr14NOgzWd63ecC/wDOqvk4G7oeyQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -32654,12 +32718,22 @@
           <t>Company reporting, Calcalist</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>https://servicenow.com</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAQlBMVEUVPWQPQl4TNV4US2oJM05i2U4MOlYXPWYWPWQDLUMZU3UdW4AwQYw1RJQ5RpshYoooPn8eOW4rbFtNrlRayFA9j1nNj934AAAACXRSTlME////////mUec8z1HAAAKyElEQVR4nK1biWKrKhBFoaTRpFXR///VB8MyC2C0746JTZd4zpxZWEyVAvt+jM/LZqiNxdZxLbYwe9X2fnwrtO/L6AaPAB6PhF7wF49fKLw8PJwq+ykUHjewnwU9MagEaMD37HEHn/FIFFABKsBa8F+L8P1NzkEDYPB9F/1Z4KkCicCC8BD8haG/g4VXicM7RGG9AV/wiQIiARfkQGP/TuDx6+udSLzvCZAo+Mf49AcKsLIMIPFH9wNqYvGO38HPv+9kAFUg4BMFxoJPKGAACnS2V1bhoW7Uf1HAtAKQciDjY/6/a/wSjtePug2fsxBiUNcg4i8s+i0Lv7tKwNAAYAqkLoQlUHW/9wcGNxSIXchDxyQwJAJVD2gK8FMOQuFeCOJBSoApQHvgq6X/T7JCwf/2DoGKQ6XAIjMACfwUeErhXg7gKMCaAIXvCvAjLVO4rUCm8WTDwNgW4FWpTxjcJ8ArsNGEZAmU+q/hiwbXCZhqLKqnApGDzICfNoGfPyiAfXA0rRTgCpQMaONHCW7lQFOBVY7EpAmfE7gVApwNiS4o5kJkHPwkQGRwU4EiQOZBGNBh6EIG3CVgaAmGGcEw6G3agk3TpGUZXonAHQKmkIBI6O04nNv3L7B93507tk2vK5fgowI/N8swPrejQDMLLOYbRXA/BwK89egN8Mxhd1uW4P1PFTARfnJ98ELikCPxv1LAbBfgwY75Ug7ca0TX4ZFCcyT+owL6uAHvzR3/thMeJ5nXtt29P0lwYzC6oz5S2M4leF/Oge22+8mO01ZwdUJiruE3/8jNJ3OyiwRMM/v2fMrPjvUYxMy4ROBe+Csu+5zHREYB1wafCEj/71fDXBrSG5BR/WCfFiZ/Sn9uDgeFEo0C/4EAj/9V5+XfuTdB5gsz3ypOCWwXIT4QdO+2wR7FGYHz+ts7rxs/OTrr49cHAnvnetf8pvZbM8j7VCcEmgn4Aa/z613u0uBeXZ9ALwFuGNJxeZsqOV+2CvsE9Ie43qSyle0SYZGAyfPeDwHgF/WTUDAnp4kNpg5VpyyWrgJYAW2//TR8GiwsEe0QZumf5DkSODFYxSriOxHBnAvgNis2qz2JcwpuluIHCsuiGLbJL2QGsou77Sm3amGfhlPYxTuPV+X9wkNABTib+2d4I/dKx9NZ+063bpfEICpgcOmVVl8nJejdx7slYrd4XM9SYVsKLogfTVXqn5eAs3mvPKDXHM6oL5nBK22joAKEBKy/+hcZ6B0jvk0Aq/TxhMGrwGb0QCD7nVjAqTsKA76g4B827xaGfYI+A4c3UhYSguy3QQV6PWDfGv7TjRKgcHTe/bVL8LCxqor6hUZrGI4/2YT/wMIGChZUsBAE7Tpj9b4tEl4okF72VmF7An0SCTAEIEGgMHZb0rEK+HVZFYVOe2C9GtiE97kXgPt2DV/irYveBRxFD/jeFNuAhKMxDsa3PyW0V99aE0OQFAAKU0/CeSk3tdLdnaQAPbozsUoAG6PgPU9Z4GmEIIw9CfZtTc6nu0tJgbwDep4Cu6ktDEmjjVkQREgKYDMQvhx4Yw/g/VMR19NVeRnhYCKhLZwgEhHehjIYB89DRnEvBJbodzqvSABTcOjotzG/4zlw8LA2KxDT0DPoXMNpBo4ESHE9OwT2KcHa/CUcYzzbWApDkaETRjet0hS6nk6dHHRDFj6TCF/BeQsPMJsqodOPd0HA/6UyormdEUD8gJ0fJvofufivoQw6F/FlwNDXQKC4ngm0yR82ZZ1kYFMSpByIeTD1Shmgh3XNI0dQgJf3BwLS/fzdmIgMsSVqkkiUyzau7BghBNw29j5ahdHh9CQK5DzItejPaXJW6bCN6LyFIVwoYPsKGOIvYpfXIw2G7c0OtzRxgEQJz0oBa7ohoM5n8CQAgR6hHGUO5G+3OG8ZMzwjEDOsp4AbKGZFIisAZMbuztqWgNcyj1MEPurbK0NtrUS3DL2c/dHrA1uCtYJAaav9PrBPErXmkBqB/UwAeSiqPyige/lzToBSGW1vRJ2wWcAoaiIBVuJkLGDD4XEBuSjR2VxxmqoP0zlV9bbeaLj7LBzIYW08NSiMun0Jn8lJ+eh9OCkO7629N+ttAkTyGCz51kZGIED3EgcIEJHjysqo3OGLF90SciaCogT0aYcxkfCDc71jmwiY0STv89JW2QxuPhH48qjlEZCEEsH/gQtQLWzMiPggQFTAUgVsLwn8wjSBA4mAHdmEn4xFCc+i50FKgbywhZMytmosR5P+V6hEQCY0iCBRhECke3vJpZaT0GMOcO9B0K1TRH5GBfjUckZgYvQXRjEFwgTOJv2zAhzfVhKW752WBIaiSErQeiDEteGUp3MFPijAwOHoLq28D03okgnhMiebG3k5aQgHVGDIHAbb6yMNBoRJ1OBkm+jI4w01hfCYVGd7VEc7CvHNbJuqukjxGzk8M4GheA8XO9sndpv/Aw1HReF0rzAuboUAkUCBL3a2UbwXEfRAWNhxauyRkZ9oWMYwCk8ggMEvHMjKpvlRhSOJgBR8+/mwW+vKpMtQBgrTn0rQmxQghY1FQJ/eW4ebi5t0P86GVdKfmb/255vluzsO+AxL+DxJC5LbUSrACgVq70Fed3q527ZvZebFY6AG6X/Eh4T+v8Dk/UdeRooUiAoUCjGxNDyqIPwfOk7nJsRrICpAfI8FHh66t1f1J9vynENGwCiuPkADvNa9vS60/WuHh/hh/e3xtDjtRf/DQ1miP3ofLFXC3rp8+PBUKIJ5nsLHuerbRnwybJL7uLlTKCjmfAGP1pvd7+GOEfvLcNvIdWdSeVFVDUYhCYeO/z4Eei6XZP74JhR+O4UT2qrnuh/Ae7c2/JPkQO3/BMdcX9Fts57C5+f8ER4Tsmg3xJ0sqQQHyAGS/hI+XN/Jq03E8O+Qg6RA8Au8RQFQAQavk2/e2Mb7MUnTVIJIgQ1KfjlKF1BSAFBAiwgkbXWCwPx2AX9uMeCBwLfsHh/n67irRuoghqASH/F9mYXPD4bM/wX4ueIgwgBxgAHQM8aFZK1ATsKsQGJAvQeP5/k3jHkBe4ZHOlWBIBQ0fNgzj9iZgxQgKkDiL7CjtxERLCPj0ROBThaoBMaSNIwK8PpjFObCIWFXTIQMJBE0mzMiB5kCTIES/wyfsBAYX1MxWgzIrJUlgeVDYlBA0/hz8Yn6HQP4OeeBEIFMWQuJtAuCptr+z9N0CX2uE6ERA1g4NdthyoHUfKj/H9EFkQ+JwKqR1aKi5adZ9CmF33D8zvkQKmAcJjJGiWXDIASIHJ6K9r+S+zL6GbbLIePzpqh5Dgy2IYEiCcDyj4EnBdJzrjjMWJEsD+gCrnRkPjdUmAGa6Y/42ekchN/yqkhAs5ENTwNthnxESBSyAkQAokABZpZ0YDLQrtQrheaIoEQAmP6ILzlgNGYqQ1UKNBF5L5AKNAk0/c/oIg6zaEkyCL1BUU1SgJkGoAnPVUAFZuwGPBFPJLDqIUrwOjxmQl2OJQK6hmfN8KG+aQnUtX+HwcxKcaoSsdUMv5ViJVhS4Ir/icPMNWASyCykE5PwGMK//bIZAJXgEgOaB61mMGjEr5sh/PP1gwlwPQFYGLASMQxVGlYS5H+9pgJMf8L/FQrwZqgrBWIWPso/v89VE75D4fd3ZhoIDmQni8bADOz/7x95ELxcAEyEqhCaIRjIzZX87///AYFJ7wQutzeTAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -32702,12 +32776,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>https://gloo.us</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAEAAAABACAYAAACqaXHeAAAFnElEQVR4nOWbwYvTWBzHP4p/QPDWYXAj2AUPyiAsCHvRwFykF0/iXOay8sxepHhyL1MvepJ2L3ZE7zmKUkUZGO3Awgx7cFgPi9tiZmVx8GL7H7w99L2YpEnTpE3ajl8I00le3u/3+77v+72Xl5djFbtKnmg168tABTgP/AD8qC6dCRXtqr//AH8CfwB/V+zqf3n6dywPAlrN+ipwFVhlONC06AJbwNOKXd2a1LcwpkaAaulfgFuAMZVKh9EFHgCtaSljYgIKCjyMPuAA9yYl4vgkN7ea9ZvAe2CD4oJH2bKBN8qHzMikANXqj4ArkxifIrrA5SxqSK0AX6vPS/AwSLTvs6ghFQGtZv0h0KRYuY8LA2i2mvVampvGJkAFb6d0ahbYUL6OhbEIaDXrHRYjeA1b+ZyIRAIUm5NOZmaBM+MoYSQBqj8tUsuHYSeREEuAyqgbU3epeNijRodIAtQ4fz83l4rHfRXTEOIU8Ib5HOqywmAwcRvCEAFKLouY9JJwJaorBAhQMrldmEvFY6grhBXwG0ez9TUMBk+uHjwCFDPXi/ZoBrjlV4FfARWOVuKLQ0AFfgKOct8P45b+cRy8Nbzc+r5lWQghMIy5EZihYvYUcDVPaxsbG2xubnLhwoU8zaTFVfhGwOoMHZkVvJiXAZnn0W63pZRSWpaVq50Mx/Jx4OyETC4yKieAn7PebRgG165do1QqAbCzs8P29jZCCEqlEo1Gg36/P7IOy7Iol8uUSiUODw95/fo1BwcHY9k8PDyk0+mwvb2dNYTzAC/IIB8hhOz1ejIM13W986ZpxnYBwzCk4zhD90sppeM40jCMIZv1ej22vLaV8ngB0El7Y61WCxgXQkghhHRdN+DYKAL0uV6vJ2u1mhRCyEaj4dXRbrcjg+/1erLRaAzZdF03krSEo5OaANM0vQCFELEJbxQBQgjP6XDLmabpKUiXtyzLCz6qvCahVqtlIiC19HXLR11fWVlJJED/H0WgX2Hahu4qcTY1Qa7rpu4GqV+MXLp0CYAPHz5EXt/f30+s49SpUwDs7e1FXt/Z2QHg4sWLACwtLQHw+PHjyPIfP34EwDTNRNthpCbgy5cvAFOZ1p48eXLk9U+fPgHw+fNnAMrlcmQ57UvSiBOF1AQ8f/4cgPX19UgShBCJdTx79gyAGzduRF7X59+9ewd8U9va2lpk+fX1dQBevXqVaDsKqUcBnXTCw49lWYGhMS4H+POEP3EZhhEYYfT9hmF49YYTnc5JUkq5srKS/yhAKPPqISs8BI4iIOx4r9eT7XY7QF44QfrJjSqfYQTwCMg0ETJNUzqOE3Ci3W4HAtMEOI4jXdcdehYwTTMwbOrA4p4Z4mxO8IzxAuBhxpsD0vVPQjTSEppn+ZijBnBzChUFpKpbZpr15nSswpQeh03TDExN4yY5c3Yso7bIpE6EUa3u75dzEFzS0anYVU4wwBYTrAl+/fqVg4MDdnd3efv2LY8eRb6FmjdsAR4BT5ngNfj+/j6nT5+ehlNF4imomaDagZl+Hrm46Opdp/6p8O8zcmYWeKB/+Al4wvehgj7Q0v94BKhNht+DChz/hsrw0+BRV0EXuOc/ESBAMXOnSI8KxoPwdtqh9YCKXd0EXhbmUnHoqtgCiFsQERytrtAHLkddiCTgCHaFO3E7yWOXxJRcmrm5VBzuRklfY+SaYMWu/spik9Cs2NXaqAKJi6KKhG5SuTlEV/k+EmOtClfsapnFUkJT+ZyIsZfFFZt3M7tUHJrjtLxGqvcCqj/ZzOcQ2QfsNMFDhhcjKqOeY77ywkvg3KhsH4eJvhtUe29vM7vdpX0GY3zqwDUm+m5QGb7MIEEW2S36DPJRplb3Y9qfzlbIVxF9Bo/sT+bm09kofJcfT8dBKeMsg81YPzHe5/P/An8xxY+k4/A/MJ0MyFhM0qoAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -32750,12 +32834,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>https://chevron.com</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAWlBMVEX///8Bc7wAb7sAabgBntr///+XACj////////iEDPeAicAmNj4+/3r9PrQ5vS72u4efMFjodGTx+ZGjslStuTeYXOFtdvwy9KcIDf34ebnsbvxk5/nQVjtdoWfd+fqAAAACXRSTlP3////////0cxxQl29AAAFEUlEQVR4nO2b63biIBSFC4gzVu5YbG37/q8555BEjeZCgIx/crrWaNVkf+yzgWTVefvL315bf/hLawPYADaADWAD2AA2gA1gA5gFEFJJGZ+IVwDIYL3xPnChQ/j/AMIRxiilzPPAmP3/AIFSICCUBW5fAaAYJdRrpZzmlgKA1Eq2b2mnJQZESoxGfMSnQin4VWqtVfu64FJpmQUgLCMstNFDgGAY81HAgjHMBK6MIQ5/N8Zqb6zyzAqJn2PUwid1fB1MdDkAylNqZAdDicE8gACXHgXgxwl4Bi8oeCsowgw2SgR4BwtYHWAabKJRGQCakFvfAYD5YCghCgIJJxQB8RyjoKMhqEoZ+DwxQQOmVc5gzzRqWzx2dApNAdwdBw6gG5pQqiU4A69LA88VxFQjkRcAQI1TEvFkE2ABAExzPGA0wYkATQijqFOEEg9lCPaANv9gHuB3jmrRN/RPgRsEQgRMdmwZm8oAnNGLqwMdgEYA1lTgDv2OPVZgumoAEFsBgO4AaBYAnIpQPeyADbE0NsVA1LxEAKpGHIjZXQwAGQapAFNcqTsH3LWluDtImKswdMc7AN5kAOcCZqDEAQ6TDEIH3Sbh3gGQINQ652yIevAZ9L4DiLNAh3YWFDnAlcWdACd/uxRLmNQOR93OdBmXS9wrsOmMxdke4hpBcR3QsF7EEF7DtAyAS+dhXNByHnBLBGnvNe6RHoYNcx6XKXjJ40Kn4DECCAc9gumPKyG8BsouHpwDwHEh17gDiGbRb9f+uNo3y/11P8D3uoPu9gJ5e8gCGLkQgW1n+qCZkyYByNH1e3mNn2tqJTTeqQrXYUJotztlAOAeR2wpg9TudDwecwA0bG8wxdCHXHWh3Gl3PO52WQ4gABRMeQoMExc1IyWVA3FU3+2yHWgKfbDLfIC+t2NvKi8D5FbAQJIzCX1H8Zt8qQNtpWWySd3uoaoAxDxMz81b6vpVx4HOBzrC0Dj/rF4lAz0fhjIp9fDY6zvQMVAfurkppsZeNQMPeWgyOZy6lR24ZdJOOb9SBq5tIOZ4nHZ+PQca9QTpAgfGAZaq13VguXquA0MZyFOv5UCueq4DfQC80s5VL3egZOz5DnQZKFcvcaCGeq4D2tRSz3WAkjrquQAybZtJUD/uTnpMZfLeUI5cYC1Wn7iIm787LmGI6nLyMjbh7wW5DI363NknAL4u16Pvb3LS1Z283sWfz8sBxHm//7h8Xf1b4EN/7PL8/fP+keHA+XO/338Cw50Pp3kf+qkT5++Pw/t7DoCIAC1Dd765PPTHDuo/oH44HPIdaCuJYcD5qJ4JIO4BnnrxlMluxnWpi84fuip24MmHfia7sYvnsVdzYNCHmMnB1B36VcmBJx/izfBD35/Vazow4IO8G/uj8+s48MTQqg84v5YDj70YSN3qDtx8mBn7mg7EOsyMfV0H9iA9r76aA0nSazmQYPuaDixTr+zAYvG6DmTJ13JgYd9rO5CvXsOBEvFyB4rGXupAQd8rAFRSB/0sAHH+Tdpo5tUPH99fYypTAFx8XeJdRZH6+8/3eVQ+5btkl3wfpseeCMDxLvU3w4dm7CV3xw8Mi3yAj4J6yt/Y0r9PmM4QnU9SXwTA0zI5m7oCgAgx6UNK6goB+HgmE1NXDtAwPNyCpaeuCgDvZ3JR6moBxEzGXmQ5XwMAS15+YewlZyj+XrHIHnslgNLaADaADWAD2AA2gA1gA9gA3t5e/d///wGrRXsVJ7+tpQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -32804,6 +32898,8 @@
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -32846,12 +32942,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>https://mobileye.com</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAJFBMVEVHcEwdLbgeLrcdLbgdLbgcLbgTLr8eLrcaLLwdLrcbK7ceLrgcdwXFAAAAC3RSTlMA8YC/16YOdBuLPW01go4AAAIgSURBVHic7dfbloMgDAXQ4hXs///vJKgdqgEEER56zlzWmlFhm2jF1wtBEARBEAT5+ehAAKgCmAKpAngH4jumH8cxdJyUfhiGeZ6704n5DlBKeQFjDoBCgLkUwLQFmHTASICFAKfBUgCM5zNJndwZ1f5eKPmAjP4fx70J6NsBOCUqoK8Bvj8H+OwV3ct3JnfzqUJIegTQ/DcuwCKAvl0FODR/sQroFEDp/m8zvO3AVwEl+/8ZPwh4HwHl+n8NcLgGSvY/CfBM/9fw0/ESoHT/9ykSAGX7v+cS4In+71migAf7z+np0RoFPNR/m5Ee7RcAz/R/BQQqwLH9f7AFvLq2S2wpZv0xvZPYgIx194/hqcrKC7AIShpAfQEU/V0XoHIqwPeC8GXrT9/Df6IAOmPl7D/wBFGAL3wGx//RGkKHBuR3v9M4kUWsOPm2/JYASxDQdaYcQK5ABiD8HiECNvkRMGUBIhevePbbBSRsDJdUAmjtX3OIAM0Avocz3oxkgJ7SKxAE+HtaBMAJAvo0wJICcNd/PoDp5jkFwLkM0M7z3w/ongO4678mAM6+/qsO4KvVXf/VB0x6cp94TSrgrv+qA9YPoEYVsP1X36uX2oDTC0j9CrQE7I/gJgCp//UBwvL5dwBS/6sCfC8P1QC+16d6AOEOqAtoXQHfBgAAAAAAAAAAAAAAAACgOcBulADGdL79O9qYDEAQBEEQBEEQ5OfzB1gzIz4qFLcvAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -32900,6 +33006,8 @@
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -32942,12 +33050,22 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>https://ai21.com</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAb1BMVEXnIWT19fX1+vn2//7mB1zvprnmAFTnDmDmAFr2/fv1+PjnFmDmAFbnHGLmAFjsf57rao/04+jtkarrc5XwtcXoN3DumrHqYonun7PtjajpWIPshKLpS3vvrL7nJmjpRHf17fDy1NzwvMrz2+LxyNMFCS/7AAADJ0lEQVR4nO2Za5ejIAyGFagNIFbrZbrdXtTp//+NUzuXRUWdnQ31nD15PrYe8opJIEkQEARBEARBEARBEARB/BCjtejQeg3jAuLLy25/2Bx+5UcRw5cIsx3hwXpc7m81l5LdkVLyrMgBTPef/s1HRMjmwewzzlhooZhU7Sm+S9A7GQ5AFgBlcbc2NHKH8dsp8S5AiLNkDuvv+8ALAX4FxGk4af6xC+Ep9yjAJC2fM99tgmxHnwdNgL5ko7dzSBj9giVAXB2LfwckAfqqfmYfSYAuf2ofSYCoHfZVlwnZjLAuTUoUAVEzCj8mw6Y4b87tK5tKDax9SdM0RzisoBr4v5L14RQlcD8MIYG0UM74YJtEa4zD0lwH8S/rPBLm638NUDHHLrCN+HfjHdFr7zsrWcXD1xJbR5LCEqDz3tqsPsH4IRONTwEsAVFmbwDLLu6vCsdhPCAJ0L3zRdXaTDwojtKLgLix30yV014NO+5BgCntVflubs2oZfgCRGUtqpr5tLZV+AISOwb5dcoBPtTuJboAY30BdksWngb0HejFgEyX8iqcGbIAcbD9Kl7Ua4ciigCwHJu1jhQ4IFbIAmwfZPvlBRMra6AIiOu/cYG+E+AIsDxAnuaDsMP2GRQBkRWFvPyGgL1HAXINAbZXy+OyD6B/gp4TfuN+CQWygF4YHlYIQzsRqdtyIgKvqZgtCtApdiruH0a7xcOoxd6BYGvFoWoWTiOj8e8D/QvJQiDChqEL6F/Jstkrmbn07sU+LqWymvPDQQ3r5VrOj9OLJoMa1kthMlMYQD4oD9FKs15zQtVX97LJ0L6v4lSp1BGMJqpG5bGv8jzkhRisbODSjHsUaAJMOaw6wwqsDr1OAmcHF03AuEUTSlWk2xg64mB3484uEVqLZqJJxbNbW7RNzf03qabadF2fbq5/iNemW79RuXqrdv1m9aNdPzuteGf8yHMHFuFmpAB1ZJPPj2xkdvE5sgkeQyt3znnsPj/Ewv/Y7lLIqbFdCU+YG34OLvvdY3ZPzdfkKYPLYPXR7YcGiP4Mr7dPHl5/mlpzfE8QBEEQBEEQBEEQxH/FG4PHLirrR3h7AAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -32992,6 +33110,8 @@
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr"/>
       <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -33036,6 +33156,8 @@
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -33080,6 +33202,8 @@
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -33124,6 +33248,8 @@
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -33162,16 +33288,18 @@
           <t>Andy's personal knowledge (primary source), republicanjobs.gop</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED 16 Jul 2026: republicanjobs.com does not resolve. Entry rests on Andy's personal knowledge of Dustin Tropp (a legitimate primary source, but not a citable one). NEEDS a public URL -- try the LinkedIn company page or Tropp's own posts.</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -33216,6 +33344,8 @@
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -33260,6 +33390,8 @@
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -33302,16 +33434,26 @@
           <t>User-directed; public record</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>https://figma.com</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAA2FBMVEUAAAD/Nzf/cjeHT/8ky3EAtv8ivmoAq+8Uc0AACxAAn9/vMzN/Su8AiL8ALkACDQcAW39MLZDvazPfZDDfMDCQHx+QQR8IBRAAk892Rd8AFyAAUHAgsWMARWAAcp8dpVwXf0cbmFUSZjgQBARADg7PLS2/VilgKxVgFRVwMhggBweAORtQERFAHQ6/KiqAHBwiFEAAfq8zHmARCiAqGVBEKIAFGQ4JMxwLQCMQWTEOTCpQJBIgDwdvGBifIiKfSCLPXSxtQM8AZo87I28AOVBUMZ9lPL8AIzB2djcmAAACzUlEQVR4nO2XW3vSQBRFYzBAUORSoci1QFu1tKW1pVy02lqt//8fGQpVvjBn44c7Z7zMfs3DWjOZk9nxPBcXFxcXFxcXl78o/f3KwbMnsfixlA+r7xPCD9fgJoF5dgYf+PxrI94sECm8ZvMrZrwk4PtVLv+jxBcF/E9Mvrh+IMDcgzcyHwj4b1n8o5fbCZT7JIEh4CMBf0ASQBsABUhbcIz4UMA/oQiAEdgkwBmE0+0FbigCwjf4VwTKFAHIxwL+vyFg/RUcbC9wSBGwPob72wtwylkfHgLE36Hw/4DLCG4B2gBaNb3eToBYTG1XMvul1H4tj4qp0IvM+DKtkP7M0dCoYMQPWHU0luPK6eaf05vqSUJ4b/esdPs8FcuPp2GrXcsEQSb/+UVC+NEafEUgLEbwx+RaCfDvjPhHgcYK/kHhC5tfMuMXAuF5sJYil/9V4s8Fwto6n2wgrv9BwLB+ssE7mR8JFM38IKBNw8UrJFCX+EGOJTAC/JTXFgUC1jSiDUjJGxAEeQ7/EvFTLSBAOgVgBKLkkUCDInAPBTJIoE0REL7ByyB+UKMIQD4W4AyidYHfeAWcObyFAvAQnlME8BgKN9EinDE8gwINJPCNIrALD0EI+KzbyPplBLfAq4vHkHYde3dIwBNPAbGe40om3EfUUmi7lNqv5VExFXrR4mkx/mOSwO/ZxciosHxab68oZIohnz/PZel+489pLrGfU88rjLOd9NNYkoIZ8L01uKrA1IjXE8ia8WoCexJfSUBcv5LATOarCFw1LQv0AF9FAG2AhsAE8TUEwAjoCHRtCwjfYD0ByP8vBOArSCsIdJBAV0EAjmFWQWCMBCYKAgVwCJoKfHgZ9VQE5C1oXqkIeFNJYKbDFwdBYwSWMZbSPT2+cQ8U1z/PLNaL0lNdflRNeysK6V5Bmz/PJNuNJjLdyY6t4F1cXFxcXFxcXJLJd700Sc+3yH7uAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
           <t>Document the specific ally-relevance rationale (Field statements, hiring ties, or partnership angle).</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -33356,14 +33498,24 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
+          <t>https://crownquest.com</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjUlHSU3Kys3NysrNy41NzArNzc3KzcrNzUrNys4Kys3Kzc3LSs3NzcyNy03NzUrKys3NTcrK//AABEIACAAIAMBIgACEQEDEQH/xAAYAAADAQEAAAAAAAAAAAAAAAAEBgcFA//EACwQAAIBAgMGBQUBAAAAAAAAAAECAwURAAQhBhIxQWGBExQiUXEVMpGh8Qf/xAAWAQEBAQAAAAAAAAAAAAAAAAAAAQL/xAAVEQEBAAAAAAAAAAAAAAAAAAAAEf/aAAwDAQACEQMRAD8Al0aiNgmYhPwfS3bBi00zo0mQfzAUXaK1pVHvu8x1F+2GanbVUydfBrNM34zxKgSD8Gx/eNTLbJUattDPsxVBDKhLPGzHeU6kED7hY27c740J4qaG3HHORLYd89s7UMxGfqWU8pURN4KZgWEeae1wG5Bm5ONGOhsdcKM6MjsjoUkQlWVhYqRxwA8eCoJXidXRmV11VlNiPg4BRsd1kwFF2N2knq2YajV+eHNZSSL0DNWuzAiy73Pv7Yzv9G2fgpmZTPU+AQZZ2EbIvBWtcEdDr3HXCYZBjcpe0zplzTqsPN05xulZNWj6g8dP5iLX/9k=</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
           <t>PARTIALLY VERIFIED 16 Jul 2026: crownquest.com returns HTTP 200 but is JS-rendered with no parseable title, so identity could not be machine-confirmed. Treat the URL as probable, not verified.</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr"/>
       <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -33406,12 +33558,22 @@
           <t>Israel Allies Foundation; IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>https://saulsbury.com</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAb1BMVEXZJjL////ZJDDXABn309bcMj3YDSDYHCrYHyzYFCTYGSj98/TXBRz87O3+9vf/+/vkcHf1yszto6fzwMP429365ebyur3rl5vngIXjaXDfTlbgVl7ldnzme4Hvqq7dPkjiYmnpj5TwsbTeRk/oh4xdY13jAAAD6klEQVR4nO2a25KiMBCGoYUQQgA5K4xGxfd/xg26Mzs7dmaBNLu1VfluvKHo39DpU+J5DofD4XA4HA6Hw/G/AQCcRyJmTMrdE8lYHEecA2xtm2u7MYTjsL9357YqgidFeyvv+0F5gmkdW6mASPLhUFZ1k/kGkrrq9iqWMd/AvJDHKjVZ/kzeVHe1E8TrAPG+mWP9nfoUka4C96ol5h8S+pjQflgvte/72ZFMAYSLlv+DISKyLxev/5OGKC6It3X2fb8j+QgQrfsAmiSkWAJxWmvf9w/C3j7ExXoBhSQQoIyR989kBIkh2q+3r3eifTyMSxsBBPtAml0gT5o6KIqgbhLTIy2zFsAMmzAo3/owYroW0dk3HO64zmBnax8Y6oNB/yg9ni421UixRH2liW29EAB9r4i+vhjkFXkwfXlusYAQE3BAfAtCxBMS63TAFSZAYbuLIW6QedYCesR+jv6v+PyvBXSIAOtPAONsAeLw+mRqHYsB9QE0zYIXvmKdC/BdcEGLLUCwtW+IA611gJsvgOWYgqPcug38AM8FWRlKqTtS8WhJKZbaiDEb1tWtvJ6OQ69CL9I966RmCyVYePlCnjZ10Z61mj7USojb42hJUZ4ndXvvpwRNJ4Ir1Au/Iy26S8iomlMQK/pCnQbbgRGtwuqisAKa3pAPKwX4aU/Ql0yhaNU3mEh6EkcQ6zsD+5LwgWxXKzjbl+XelGeDtQIyRbIEAKvXgGZE4MFuv9ITG6qYKNhQrtIwUgVl3fyI8VoYu0ATJ5JY8KFBMjWcunMVNGk2L0ecCceFDxGPgbXOd57qL2/Xsi2+mR1PUAxJcCEwzey1lml6fjmcC8MgudlIwO9SuGBSjug4MaceW5uF8B0ar0hGdfOIjpgA24TE2QsmvzY0MXYC+KUOvnIzbG3g2H7Y25Ul2JQuNfTcILCdsIGAfMRXFQTWxGwgwPROiLBAfbQTwC/IO0vcDXEntByWoiVpgFfc+MGCZTrEh1QDtg8AD0SWUyLg2Esb3fjwT2MIzrnuT5EZka6MLfsTkGiSSbqhH5VSjzGMUmM/HK94vVLbJiNje57nWZYlE/rXXBtYj6vtxvW+f7UtSPAMMx/LVGB5ZENxcGZ1aKUrMvuSEBuAzoegKAZvcSn+C/tRrYZZ7IMTRVEO0aybExgVzTwzwjLiHALr04KfxOvOzwtOdo0jviw/Qc87qjHZROQdgmXzwpuiGc+8A0LCpQzmuWNed6Gkv0sEUSxhONzq7+JCnga3w8ho//1nEboLjMN+fz0XL+1C0HZvg/JiJja7zfVTBEzlz/tFtk88T3P/XivocDgcDofD4XA4HET8AE83NpbEsQhvAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -33451,23 +33613,25 @@
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>Leadership + partner roster unprocessed.</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -33510,28 +33674,30 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED 16 Jul 2026: israelbusinessforum.com does not resolve. Sourced only to 'Batch 8, Jul 2026'. NEEDS MANUAL VERIFICATION -- Andy supplied a LinkedIn company link originally; recover it.</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
         <is>
           <t>Member roster is a bounded list of Israel-connected businesses.</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="6" t="inlineStr">
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -33574,32 +33740,34 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED 16 Jul 2026: stationdc.com does not resolve. Entry sourced only to 'Batch 8, Jul 2026', which is a provenance note, not a source. NEEDS MANUAL VERIFICATION -- confirm the organisation's real name and web presence, or remove.</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>HIGH for the DC Sprint: member companies + community leaders reachable through one confirmed warm contact.</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>James Barlia</t>
         </is>
       </c>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>James Barlia</t>
         </is>
@@ -33646,28 +33814,38 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>https://capitalfactory.com</t>
+        </is>
+      </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAclBMVEULCw3yqQAAAA31qwD4rQAABg0HCQ0AAw3upgDpowD8sADmoQDemwNnSQlQOQtEMQuodgaVaQcfGAwuIgzSkwM8LAtJNQqEXQh7VwiyfQXFigNsTQm4gQUWEwwpHwx1UwifcAZYPwkzJguMYwdgRAojHAtpR9vVAAALI0lEQVR4nO1a2YKquhKVyiBDFMQwg4jo///irSTM4tno7t73xXrotmmSrFRqWFVxt/vKV77yla985Stf+Vz20Mn+/7S+Lywtwv+HCBgMH+FODABynzxkv7k6B7gc97xfK6EGAG17AHx/vADwV+P/VgCOJ8ct+tUg7zWQD48K1zkdAV7N8JfLR5mghIiomx9sqxOnfxIJQqgo/d+AALEkhOj9hsycBu0B0Auog2Gh1gm+Jo8/jwBat1/uqjzPLwLSAyBZHSl3vPaQ3PYXAMQ9AMuu61x4wwEoBLYnyjQdHrnxzwPgu0HjFqWEWAvBw5+8sPt5T+AgnhZ9JUT8hitCQF8s9/SEBj93AmyIbEPcGTRudO5JbwmDJvA8/jOBy9kEVw6PfFzDdtDmmnugFruGkcT/CG/EQPKHOQMG58tfKWN/zkUbglr/IEYFeMnFpEH0O4zDZ7QOL6ra0qMdBioOCgGEicjPf5GpGGRo7nmDS52ciY6dBqo6KCuIiALgY/wTZ4CqOfUoiXPCQU2OR5V9np8YC5TvEzc/5DMDxDMOPepeIUTlp9B46iXJmALa46Q4yFV/uMGndsChHex8bulo5SBdUsDDI84BDo56RwIcUlaOhjAMaj90SkjmzkWs/hjUYkWB0belxGtAR0CaIihL2NaKJB8ZInvQ+b69U1x2uyIVJqN9c1Uxx4eWmN/HzhmJ48xGEvr45BA4zA+e1Ghmqa2fYawPS+mpheUNTviMlDu4muWpPN7tWVjIPzsDuMnpNCSBCp9lapdo+qHQCiKy0knQrrvXqUSg4DuTgYjxk/UVv5llvBLOGBP2iUfV570xNyKjCmM0ESEUann7ekOmAM1Ud8WnsYjPwj9SIZYJn8ENLUGeo6xTj+3YihEAZKiSPFLE6TwdiC7zcWZi4ewQakjJFakZtLYt7Hlq8oLUIVr7qSgBxhMgMvw8HcwBIBO6FRyKsCpXUiCxLXJQ4TnFX0fyMwDgalgQ6Y4bayG/dIX3Ii9bdlIjIfVDyCb4MGB+vH7saUOnQhoV3OAiZlGRaJlqgQpk5edecXq49z4/Y7BnnPOqNI7W7A96QkwBzBtDLbUcocRzrEnIopiWauM9xNEkCkMETsb225MSOzfRAzPL3dbrY55Lqd5uDoU3LC/K9hBVfBdGh7YUAwR8yfgAoWURayT2HYA9oua8FQEkuDUpS40fI8wxV+nOKakXdDEW028SoT8oReHWoIoS0R+FV+zUORGRVghFq0CUUgrhbE0JfJfT4XCJfFQqJCvPH9bA5QH2E+/mCKIVPTg8OSJaUJHbGIOZjeYbuTK7TM1MasNTAKqek9H8+BxbOCqqZyOEnFShcsjn3kou285gxj6JvCDJUFuKdj2A63rphwrvFRRjidyUy+KBbjwDmIU/p4DqZLv0yqPu+fUVw2H82o25QxjYT9ECtblp/cibAsBaFPbx4V5BYnwx4C8VybjJAZh/F7ncTOVFWxCMtK4/8Vgz4HuHZ+bOcL9P52Rdz8A9QLxSR5HTJgDFItQSEcSP+GqiojcvvCHL5n835rV8PwvH3Va8bYkZqmBBqcaIS+Z1N7sIMTdtzc9Q2iZfACBeUG0MBAyeRg+TzA0QKYs93xVjnabs5fpYXmyOxRyqZJXe0rkCOLIxTNKzmIBMeW2knYRv8RLwvbVpPH++3VDVRPN8/2rkmynRFBtPJ1BWehe875H6uFvq9/1S87+qXDs+rF/eA5CsTNK7Ea/io5ZYuT0Nur+OBt3SjTt5szhZnwUzowFQO7ajpNudEttJOwD1mvlsCwETAKvtkP4gOdzlvGzCauTeGRnyqJWh7zVNGPC1gyRiKLEw1k9TDbGCsF+AXdaaSapy2uiFaE5hIldtUFSDJ+15Mno6sVs2tCF4tdrNcmTygC0dVDgm0qWrdjQFgMcwcHZk3hMffwEAT8mVyYYOqir818ZrADOXH0LOPDyxx8t+HnE3JGR4EYUtnU6n/R4YNTCdFiPR6xnyDQCyV2XHIpqwh3pRt+pm9T8Ua/bT6SrbAOD0GsDMmRVzI9bphD9mXOtFIDIANkQDUwM8r61/lKMVcparVgTAEUNCzsfnXSh2VqNBugHAwX0aRyg1NY4YjQB8QUvVecByXdVjw3PD6Oh1TRHuhowAzdILCPGy+Gh2MOoaEjs1N1jAarudPNcadKKHfEJA3ObPAPa+9NC0xlKLSkXyd6Uut4Y2ON8l9+EzNG01fO50dYZi1ltWnWVPbrrgu8XNITnJvuNUn1WqNb04i4yHGE4N7zEqwCBX1yoTYkzkKTk08W1LbcSZIcF6x1gDYWEJgQz30uxsoCSzqYarvLgv0GgBx5Hd0ruelG0nReyi25+Z6vieMToW3dmS8r+YFYeudWWJMmX8Xva3KM7GqmwyFdcByStSaZ2gxmDHTJpHV36JgHdBBGO2uVje+4GOSjTjbzeqIDXQsVCWl4u0Dj3Rt5NXCDh0VJZg8bw7pqlq6huVfNCsVU343oIKuJK87CIs5t5Xxempy9BeclLXarZow93CcrYLG4phNMVE6kZVx0FoFq2V59GQRYi6VlPvU8eYbr57u1PGcDvTWKRnzXsTl4e5RSvPOcje/hHiONIc2+ndW4t9tSCFxPIyH45DFyQvVHhQpsU5fjgXeace1Zp5LmtoUL11c7MP56WlCodI//mYqdA0gzqulKlXcR3IniFSqWvpdhmGSRa+gYDzGSshlkxxv5f7DiZclVDbExIFzW0gqFT60KCJ3J4SwTRj/lEgnuk/V2Hsloj0qV5aNCrxVQaJ45bqHn8BwKLvFGdQThHkoe5PyGqvum7Edd1Xd6gC01bpYtaPkCws+hzlO544CQJqbJ7kMaQNHG2MAuX91iwaCJa2dtXKQvb/KFXPHB7J/BjfCwUYU2ezUyojzIgZJV6is0o9J56ElG16Kgmh1x0gJ6lVCXCdvfIfEXxNVOGt99RXHyS/wM3WQdY/Ya3fqqspG0X/00tVPbNLFElEjy8xFx0yM842QUS827RHOkFxmuTWKZIEqu+KhAQaj7pIbgXm2/AW3+vWtigyrbpF/0NYSJpUuOhMgMgoKQUSnLevbZBbZoWPAa6zBkzM+AlTIUh1RXXh0lxPoHgKVmsrhlphPHAKGK6MlFcC84tswmY3I1Bz89EeaYaxEbdq+riGsmUVnILAVuwHrZLmmtMTu+i9kIgbjDN9KnD3OpJhKQC3ydVAwJGqUE2/dIC4aB5IRNLxOe/+fhJcQzB2HPQREKsLR2phtRSyJB04yLkP1V0K2lAFbAIwtmuId4NH28Zmhwig0p8ctDuHqiOYtxU+uzNeCq8mEYXkKglCQzp9mNshdZdzKK/+IgKT/H3TWxHDj8eQc63rqym7SNuv6KSmabZIQfRHbGChVgvJTo8o7Vk4ca7xw2+XKZC8Ff9fre+/rLadmt+9XjGqZ/aUAZ0PuOATgLH1SqxFhhO5fG7JEToC2VKO/0nY+dotS7xDImYQyMo3uqjXHrqKiNDg/ANWyJBu6jaIuhmHOl+2wWfL27nKxTddFVKkrj/zBU+kF5S46IAqrO6K57J7WF/WOx2+zzhAAf6pb5RB1TpZVw2zaRN1Qclo0G0Zwsw57X7wK30c4t2+/zgCcHItzgRAt+f97vjD368dtTkCoMHjgvKYPBhe47/zxdbdVAOK5jGUkUD+5Nf4XssAgHatAj5w6H8E4No1kGj/7Ry4ma6Auj/6BwCY3wa5R6k7tl0hp5R6edD6v/rF7l72AKF/T8qx5weHPLn74b/7mr0uiKddCv3n+12Yr3zlK1/5yle+8hUl/wOwj5kDfXuN8QAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>HIGH: portfolio + 5-metro network; but leadership is in flux post-Baer.</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>Bryan Chambers, Joshua Baer, James Barlia</t>
         </is>
       </c>
-      <c r="N28" s="6" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>Joshua Baer (Founder/CEO, d. 17 Jun 2026); Bryan Chambers (co-founder/president)</t>
         </is>
@@ -33714,28 +33892,38 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>https://piratewires.com</t>
+        </is>
+      </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAMAAABg3Am1AAAAZlBMVEUAAAD///+AgIAgICAkJCQSEhLb29vt7e3n5+fPz88XFxenp6f29vbDw8PV1dUwMDA8PDy6urobGxtubm6ysrIzMzMpKSm9vb2JiYn09PQKCgpPT0+QkJBYWFidnZ3g4OBhYWF7e3t58wQJAAAA5ElEQVRIie2UzY6DMAyEYxybBkhowj8U2rz/S67pVr0sUrPS3pY5WJYzX6Qo8ih16tQnBa0RtdZhVqqQflaEGknNMgwHfmyZbWvZtctc3Bz7jhrDtqF+YFceENoA2HVkmPwVywrctchyuGRUM1QWD4HK636b4N70yQDS0/RroD6BvwXCKKaY/A9Dt1ixPlIBMLHlixt1SAVcFrO4oEoGhpqIZB1SAXn0d/9vAV5RgHzDLgWQzZ78essBuFnucnCQGhIzbnvN94BhU25S2Y+GTaSfwB5k73toTzSUidTiGWenTn3QF4VcGbzhkwvqAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>MEDIUM-HIGH: masthead is a bounded roster of Tech Right figures.</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>Mike Solana</t>
         </is>
       </c>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>Mike Solana (Founder/CEO)</t>
         </is>
@@ -33783,23 +33971,25 @@
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr">
         <is>
           <t>Art Levin</t>
         </is>
       </c>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -33842,24 +34032,34 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>https://zynga.com</t>
+        </is>
+      </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAG0AAABkCAMAAAC7KU6sAAAAgVBMVEXcBgb////2wcHnVFT98PD74eH50dHeFhbyoqLdDg7ug4PpZWXlRETrc3Pwk5PfGxvvjY386+vxnZ3+9/fgJCT519fpYWH74uLseHjzqqrlSUnypaXwl5frcXHlQ0P0s7P2vb3kPDziMjLnUVH3yMjhKyviNDTpYmLuhob3xcX0r6+LINlKAAAFG0lEQVRoge1ZyYKqMBAkwyYgIAKCiiIqjvr/H/iykIUlGB6OJ+uiJJAine7qTtC0L7744ospWO6cj3HZi42+SD7Flnv7TX7/FJub13ct/xSb7weB736KzSnywzr8FJum1ee/GNXNrM1fjNuGc/TcIAhKALGijRdDRPkepsRbnyIgoGg6dLER/MykOe/TdO1ZoIfiD9hqo8+DEQOydvUVAPMHwYR/ZsbbU0J2ci7EA50IxMTvwwwY85TLiSVsR3rHBgDqGjkA+1lsRwlZxO5YcYeBNxuz2HIJG18fyJY2icaDHco5xz7229YSNh7dB7SIS0iS+LE45xeoM7/f6O/yQafkcwvJysbkp+gPMQgnNYetUEUDbILWi8bOVFXZBQdpz9jcoC3Z7K+qAQDDRvZeQ57SerPQL80ostY7RS5YwcidVx9g05UHHoQPTFlXPcBWsd7jj4DT3lcypjsSmH03iblD9WYeKIQcdIVa0mX3p/bkvX07r1+zeS2vJiznnecWJdL2Lhb8rgp2xziTwnbinbLX5rgBQcDtZb64ylJNh01L6fBbAH7tALTDQwK4OFdkcWcXpCM8BCl/7gKFi/wL4Qvb2o+SKaG6wuisi7EpcfDQunO5SlFkuK1VlQHrnSyb9cDzWMDLAxMZMW/bWYYhgZKCaz1SGhcvAbKOJ+a7MTgDlY4cLLzP6CpOrym2S4LWTak4KaawcaHcC63QPyxxUeXYTSET/M4pWeMTW/Sokr9f+72Ih/ieT6RtRnlRsSDB7yQykLWfdkJbnUrD9p4E/mR4KBYUitVrNZEMsLnsRD1QrMwnOSQCzfRhS3wU2YZKnVFQCT+0WtXYqqlkbG5I9N3abqBWvMpqYjnouFCppDWGDKepZDF9Up9QIFPwZYsyJTaLPZqqSZWAhA6yPaItkgJ4VjlHIJu2bWs0Mltqw+VjH2zbcSuhMQyrgULapm5s4lf0VMhiFtz/se9GiRAYpJghWVUf3ttQBOzR/2DbYgLhP3TqZDvCxjdfO1PEVoUNBQDdPePyEXtZ9SNl89ijigEtAiUAekj1ALyQlVZFfNehG8HU462MTw15DAvdnnrSYFxyNnj12EyZYAKECIVFKLg1/2k+j3XP9z29sp2mgQcY8ZIpE9y01OfBaxy6cNzVmk0Bv7umoqc8wXWrBvR5jUPrKX5cTEqelg4neWMCxQmaLalDdn0QN7g3bLw3wNddR69oQX/1Xk4waW3/NO2KnsPGpLrCe71OAFA4elPYGMWLCXrtgo3oGN463Jo35n1EUXsHAuHhwR134NxFQCkcpWIsc/eAB2wO1bhOkU14J306G+op5Ixm7OA8RI4nOycmTin04hAQz3MdfUs1wDrYdp6Ns53YKg3A60QXkRfxiwZVZaMgQer8WmNs0fCyE+A026oEjM7dhO0kBtvY8VN4WN3lFXzHSQibWBlAtsx918ciNHjrQBVZUjw02G0Zd6K0u3nF1vrwhCYr7jASfqHPPenFqyquut0OdkgRsVXUZ5/Qm51oTbrBjSjO72LLOuGB2VLBTbBPrpz3sHUdvtEyblwSAeblbWziYWTDBnoVXpm8gQ0NJEaj3dQKLAgghYEFIs5ns2FZXLZa9KJ8rm7sGlJYISkGjbls2CmqsTt0vAPRmynPY7sosmn2ej7bGa/I6EGBTndXS3MuW/b6hRmb5gTz2JptnTV2z+0Usf4qncVGsvKrTRkXMmfWd4K6uKYnWab94osvvvjiLfgHklM80K9E/EUAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>Mark Pincus</t>
         </is>
       </c>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>Mark Pincus (Founder)</t>
         </is>
@@ -33906,28 +34106,38 @@
           <t>Batch 9 (Baer-tribute criterion), Jul 2026</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>https://austintechnologycouncil.org</t>
+        </is>
+      </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBEQACEQEDEQH/xAAcAAEAAwADAQEAAAAAAAAAAAAAAwYHAQIEBQj/xAAvEAABBAEDAgUDAwUBAAAAAAACAAEDBAUGESExQRI0UWFxByIyEyNCM2KBocFS/8QAGwEAAgMBAQEAAAAAAAAAAAAAAAECAwUGBAf/xAAjEQACAgIDAAIDAQEAAAAAAAAAAQIDBBESITEFQRMiYVFx/9oADAMBAAIRAxEAPwCyWfMF8Leh4cjZ6RJoiwmIIAIAcd2QCXZ2A3jJjDqz7pTXJaBycJJouOCzIWgaCd9pGbjfusvIx3F8kdBh5inFJ+n3ONl40zRDKTF/0q+stLx5uF5om2sg32+6g0a/xnyTxZcX4Y/brTU7BV7IEEg+rKnR2tVkblyh4Q9eX49lAt1s4UhBIAgDRbPmC+F1EPD4FZ6RJoiwmIIAIAIE9hBPe/TtGZRmxRk4kz8OlJKa0xKTT/UuWCzA2hGGd9pW7+qy8jHcHtG9h5amuMvT7a8iZpHL8MgPSqav0rDma5SwiwWRbdiZuqjKJrfGfJzxZcZdoyG5XmqTlDYBwkF+WdUtaO2qsjbBTi/SBm7KJYECCANFs+YL4XUQ8PgVnpEmiLCYggAgAgAgAgcfTtHIURscbuzsoyipoIynXPaLjgsyNkGgmfaQW491mZGPwe0b+JmKaUZen3Oq8aZoD4UgKtrHSkOYrlNCLDZHln9VCUTY+N+TnjSUZPoyC1WmqTnBODhIL7cqlxO1pnG2HOJD256qJM4QBotnzBfC6iHh8Cs9Ik0RYTEEAEAEAEAEAG4QPbOwE4SMYu4u3dkpJS9Enp7RccFmhtA0U77SNw2/dZeRQ4vaOgxMtTjqR9xeQ0QXLbIFpP0q2sNKxZmuU0AsNoW4du6jJGt8d8lPHlxb6MguVpqcxQ2AcDH1bqqWtHcVzjZHlDtEDbv0bdRJfWzRbPmC+F1EPD4FZ6RJoiwmIIAIAIAIAIAIAIfQyasMpWWaDd5N+NlGxx12SpU+X6mgVPGFeP8AXJvHts+791iT7k9HU0qXHs9Le7KtMsCYyrax0rDmIClgFhsi3Huoyjs1vjvk5481GXhj9utNTnOKZnAhfblU67O2puhdDlF9F/s+YL4XTQ8PgtnpEmiLCYggAgAgAgAlvsPsJsX2d4YymkYIxcnd9tkm0luROMXN6Rb6VKtg6R27ZCzA3iIi7LKttlbLjE6DFxVTHcjGNf8A1Et5jIBFi5Siqwn9pC/5O3de7Gxkl2emU/8AC/8A0219Fmq4UMgYhcBtmd3/ADXjycdxk2iVcv8ATRfdl4ywdUAVbWGlYMxF+rCzBZHuzdVHj3s08D5GeNteor1nzBfC6CHh8+s9Ik0RYTEEAEAEAEAEJgpaZ3hhOwQxxC5E/VRnYo+k665WPot9CnVwdQrdsxF2HciPssy62V8uMToMXFjVHk/TFPqPryXUNk6dE3CkD7cP+a9+NjKuPZbKxtlD2b4XsT0VskrTy1rI2K7uEocsTdUSSmtMabRvf01+oEOcrjRyBjHcBmZid/yWLk4zj2j0Rns0ZnZeJFgTF4ZpZ8wXwt6HhyVnpEmiLCYggAgAk9h2E2gkmjvDEc8rBEPiL/yyhJqC2ThXKb0i30aVfC0ntWyZvCO5k/ZZtt0rZaRv4mKqo7fpin1G17PqCyVSkZBRDjj+a9+NjcVtl057KH7N2Xr9Io42T2IN137pAS155qswT1jeOUOQNuyUoqUdMa6ZvX03+oEOahClfkEbYtszv/JY+RjOP7RL4y2aMvFst9M1s+YL4W/Dw5Cz0iTRFhMQQAQARsOzvBEViQYoh3J35f0UbJqK2WV1uyWi346hWxFV7M5CxM3idy7LMttndLjE3MfHhRDnIjezi9YYyeoBuQkzs7dHZVcLMeSbR6ar4XJqLMB1rpG3pm+QSC5VSf8Abk/4tjHyFNEZV6K0/PL7/wCV6CK6OEgCADP2fogCWvYmqWQnhkcZI38QkyJpNaDZvX021/Fm64UcgbBcBtm8XHjWPk4rjLa8PRGfRHZ8wXwtGHhytnpEmiLCYgk1sApaHKOkd68RTzNHELkT+ihLUVtkoVym0kXHGUK+HplYsO3jZt3J1mW3SulxRv0Y8KIcpGc6y1XLlp3gqE41xfbfputHFxeCTfplZmZ+VtLw+FicpYxVoJ6pOLs/Lb8OvTfSpx0zy0Xype0apBLi9b4Yq9gReRx+5n6i/qyxJRnjT2vDpMe+N8DCda6Rt6XvvHIDlXJ/25Wbh2WpRcrEE4tMrXfbur2tEQjYBABAEleeWtMMsBvHIPQxfZ0mk/R7N3s+YL4VMPDnLPSJNEWExBJsXpJBHJPL+jEzuT9mROXGOyyFbm9FwxtGDD1Cs2dhJm3d37LLstla+KN7Hx40R5szrWWq5cvK9esThVB+z8ktLFxY1Lb9MvMzXa+K8Kp8dF7O/o8DOEdkT3YjJ2cXaCeufhdn5Zujqq2qNq0y6q6VUtxNUhlxet8GVe0AuTty3cX9WWLKM8efR0mPkRugYVrfSVvTGQKORiOuT/tSbdlpUX/kJNaKz7v17r1NaIBIAgAgDe7PmCVEfDnbPSJNEJD4TSHpaO8MUk0whEPiJ1GTUe2OuDn+qLjjMfBh6hWbLixM25E79FlW3StlxidBRjQohymZzrPVMuXnKvVPw1hfqz/ktPGxVBbZlZeY7HpeFU6Nsvdrozn2EkMJiGyE9DR78RlJ8VaGesTtt1ZU21fk6LabpVy2jU4ZsXrfCHXtMLk47OPcX9Vi2Qnjy68OlovjdH+mFa10jc0zkSjkFzrE+8cvZ2Wpj5CsWhyi0Vlm3fZXtaI6CNiCAN7s/wBc/ZUQ8Ocm+yJPwi9M7wxHNM0UYuRP2ZDlpbZOFbm9IuONoV8PUexZIRJh3cn7LKsslY+MTeoohRDnIzrWOqZctKVauThVF+38lpYuMq1ya7MzMy3Y9Lwqjuvbtmdo4QIJpAEAEhrobp70B7sVk7GLtDPVN2fflt+qrnXG2OmWVWyqltGoVLGM1xhnq3AB5dtiHuL+qxLISxp7+jpKMmN8dfZh2tdIW9MXnjMXKqTv+nI3T4WjjWqa7ZNorXXqvVogcJaYG92P6xe6pgjnptbOkEUliRo4W3J3ROSXbI1wc5aSLnjKEGIrFZtGLEzbkRdllXWytlxidBjY0MeHKRnGstUyZiQq9Yyaoz7P/ctLGxVCO36ZWZmO16j4VRm8LbN0Xu1ozm9hIAmAQAQARoAjQBHg+j14vI2MZbCxVPwmL77eqqnSrFpltVsq3tGp1LGL1zhTq3AH9Vx2Jn6s/qyxbITx5/w6LHyYXx/ph2tNJXNMXzCYXKs7/ZL2dlp0XxsRY4tFZbfb3V/FkNm/HEc9lwhFyJ/9LzqXFbZz3DnZpFsx1CHEVHsWXZiZtyLfosy2x2y4xN3HojRDlIzrWWqjy8xV6pONQX5/uWli4yrjyfpmZuY7Hxj4VTf/AEvb69mccI7EEwCACACACACACAYSe/oZ68ZkJ8baCxWNxMe3qo2wjbDUi2q11S5I1SrYxmt8MVW2IlL4fuHuL+rLCnCdEtrw6LHyIXx/phuttI3NMXiCQSKuT/tys3G3otOjIVlfXpY46P0RUoQY2KSzNt4hbcidllWWysfFFVWPGlc5embax1XLlpzq1icaovs+3HiWni4qrjyZl5uZKx8Y+FU6cN0Xu60Zhw6I+AEwCACACACACACACACAHw/PoiHoPf2ezF5CxjbYWKxOJC+7s3dVXVwl0y6m2VcuSNSp2MXrjCvXuRsZs33j3FY1tc8ee4nR4+Qr69s//9k=</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
           <t>Thom Singer, Joshua Baer</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>HIGH: bounded member roster = direct Texas-ecosystem B2B yield.</t>
         </is>
       </c>
-      <c r="N32" s="6" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>Thom Singer (CEO)</t>
         </is>
@@ -33976,26 +34186,36 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
+          <t>https://benchmark.com</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAABAAAAAQCAMAAAAoLQ9TAAAAA1BMVEUdN0/F4PHMAAAADUlEQVQYlWNgGAXIAAABEAABM8nxagAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
           <t>Sourced 16 Jul 2026 to Wikipedia rather than benchmark.com: the bare domain returns an ambiguous title that could equally be Benchmark Electronics. This is the VC firm (founded 1995; Bill Gurley, Peter Fenton; eBay, Twitter, Yelp).</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>Bill Gurley</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="N33" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="O33" s="6" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>Bill Gurley (former GP)</t>
         </is>
@@ -34039,23 +34259,25 @@
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>Jason Calacanis</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="6" t="inlineStr">
+      <c r="O34" s="6" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr">
         <is>
           <t>Jason Calacanis (Founder)</t>
         </is>
@@ -34103,26 +34325,28 @@
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>Map his network as a B2B node: Ithaca/HYBE, his artist and label relationships, and his philanthropy. High-value connector into the music industry, where pro-Israel voices are scarce and costly.</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr"/>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr"/>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>HYBE America, Ithaca Holdings</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:P35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41875,7 +42099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -41885,6 +42109,8 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -41923,6 +42149,16 @@
           <t>source</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -41960,6 +42196,16 @@
           <t>PR Newswire, Sep 2024</t>
         </is>
       </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>https://puretalk.com</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAJKklEQVRogb2a/W8cxRnHPzM7+3r23flix+GCk3NIQsGUlJTQppFARQKkiKgS6i9V/76q6g+tKkGRQOUHqiLICwhoTFGa2A4kzosT++zzve3LTH/YtX0+n+3zncUj3Um3Ozv7fOf53Mw8z67gkMwYI4FR4OfAH4A3gFPZ6TngU+DPwE1gTQihD+O+6jA66XD+VeAt4Bww3tH/eHZsHXCBG8aY2mGIGFpA5nwRmAHezT5lwANk1myCVOAk4AAhMGuMqQ4rQgxzccfIvwz8EXgdqJCOsuxqroE2sAD8C/gT8C0wVCQGjkCH868Bl9ly3qP3wMjsXCX73cx+XxsGp4EEdGFzGbgClCNtvCgxAgNKCWwpEBgSHZGYGCEsYQnlSWFVsmsAWgyB04ER6oWNMVRibdynjVg+bUYYYDywOZpTgKYWPqYermBbHoE9hq9GtRRWG8QCQ+J0oAjshk0j0t6dlZa4en+dm4+b2FLw5nSe306PYEydu9Wvma9eQwmHcn6GE/lzsuAd85R0K1nXA+PUt4Be2BhDuRFpb77aEv+cX+Mft6p89bBOTlmM+YoLx10Ea9xb+5avH74PQKV5l0SHVIoXRNE75inpVEAMjFNfAjpGfoYtbMphot3by03xyUKNv363zOxSk1qYEGlDtRVTa4fYskE7qRMmTWLdZqF6gzBpAIZK8YIY8467llRlEO8APhlO/UZiXwF7YXN7uSk+nlvjw9tVZpearLYTALSBWBsirZEiRusE0Bg09WiZxdostnRJdMxzpYuy6D0zME57CtgPm08Wanx4u8q1+3Wacdd9DBgNxtrZbyOqMle9CoAlFZXiawPjtKuAg2DTjDXG7PAfs6PXjXOGdlzn7upXRLoNMDBOPQUMgs1BzWCoRytD47RDwFDYDGDbcbKZLl4QhQPgtE3AsNgMYt04CSGoiFdF0T3uWtLaF6dNAT8FNnuJSHH6DtfKoY3huTEl8+5EFglgF5xUh/OHio0UYEmBRCKEoJ9dSyOqcmflCwQSJV0qhfNi1J3wlLQru+GkemID5Uhr9/ZKS3wyv3ZgbCwBjiXxlYUUFkL0mEt7mEHTStZZWL2xNTsVzouCN+lKocrADpwUkAd+SZqIvA5U2rH2flxti0/vrvHBrZUDYeNIwXigOBIoco6DFHkCu4CrcsRhiGHvCBqTsB4+4X7tPziWB8ZwunRR5uwxT0pVyZo1SROjLxXwEvB2JuA44NXDRPz3SYt//7DO9cU69ag/bCwBJV9xbjLg1JhLYNtIChzxTzARnCLRt2jFtf1FYFiPlrmz8jk5p8R4UMGxAuFKtZFPvEua1bUVaQJ+jjQNdAHRig331kKWmzEAttyfXykEo47khXGP3z0/xivHgjQfEA5T+ZdpxmskJmKpPkek2/uKAIhNTD1aZrX9kJI/hUtOZD6WgUvAiCKtHozTkcMGjuTsEY/XT45S8hT1KCHRPeAXYlNgzpaU8zYvTQRcmhrl2IiDlAKQFLwyp8d+gxIOj+p3WI+WCOMG2mhM13otsm9LWrjWCM8WzjHmlVGWszlWma+ngaIwxjRIZyN7U7k21KOEu9U289U2tXZMpHuPmAAcy2LMU0wVXabyLoEtUVJszjsmy8rCpEG19ZCV5iLNuEai457bDQEo6RDYoxwJTmwKENvT7AiIe24lLAmBbZgqGMZ8TZhojOkeq62bWVLjKsjZhkBpLCm3TZoCgRQ2UozgqymMN0GQRCR7TGmWkLjKxlU+QjjsrBGkpkiLTuOkpQ8JECVNnjZ/4EHte540F0h0uCPU20VIbOmRdyeZCKaZHDmLb+fZiEGsDU8bMd88avC/5RaP6xFhYjB7CJBC4NkxMxPwyjFBedTBU5siNLAMPFGkFbNzpGuBB8gwafJo/RY3lz5ibuUqsW7v4X46wko6jPsVposXQAgmc2fw7TzGCJYaEV89aPD371e4en+dH1ajXZHc6hMCx+LKmSJjrqLkqw0BmnQxuw18o0jLfeukRafjgGeMFrGOiJNWlkmF7L45Ti1KWjzUt4h0Mz0wYThR+AWRtrixWOcvs8t8cW+dxfWIVqT36S0VIIB2oonN5gJqSGtLi8BnwPuStFb5MfABadGp5ViBOZo7xdGRMxS8Z1DS6XGL7WbQhEmDp80fmateZ6kxR5hErLYTvltqcfX+OvfWQpp9OA8Q2JLTJY8Xxz1OFFw8WxrSkV/IfP0YuKmANeAG6cLgAzgqqEyOnHVPhcuyEa4wb66z2n7UdySeNBdYbT2kGbdYacL9WsiDWsr9fiYA35ZMF13enB7l0tQolaKrXSU7q3p/IyvDKCGENsbUgFnSPUZTIK440i+fLLziKeEIgPnqdaqtRRKT7CnCoIl1m1A3aEQNVpqSepiQmP2kb0zJgtMljzenR3nvhRIzE75xLdkWKTYfZc7PktWQFEAmopqp8tJj8p3AHqscz894sW4LKRR3Vj7PItHe2xNjSHRMnMSEyS6LYA/zM2zems5z+UyRmQnfFD21gc1HwId0FcA214GOSFwjZc0XQhDYxcqpsV+5gNQmZr7aP070sV2ALmwqo1w+U+TXz45ofxdseiY0XSK2cBLyiqty5ZPF856Sbt84GdMHM3RhUxnl9y+UmDnqG1/JthC9sem8fsdKfOg47WM7sDm6PzZ7CugQccg4dd2DwbHZV0CXiMFw2iOLHBabvgR0iBgQp91ziGGx6VtAh4gD4gRSSCypUFJmecHORWpQbA4koEvE3jitfslq6wHKcnEsH0/5jDgKX0kcSyCE5GzXIjUINgcW0CFid5xMKAKnxKP6LZRwGQ8qBLbPRM7mZ+M+F58dwVWC88cC3jiZ72uROlQBHSJ64vRc6aI74hyRjxvPYwmLydxZPNtDWZIL5Ry+koy4Fi+Oe5w94mnXGhybbT4dpPGGdRXC3gOuGEw5jBteqBsCJI7l41g+GEEtTKiHCUoKcrZlfFu2MmzeZwubn+YhX5eIzlLkO+z9mBXSebYbm2sM8ax44OfEvXDKTlXo70H3wNhs82PQCzesB069XjXYSAMXSZORobDptKHfleianTbeg7hEWrcpZc2WSXPYz0gzqaFHfsMO5W2VDpy+JMVkhDQq+azJE+Ab0j/tTQ7JeYD/A8jwrGqOGmSGAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -41997,6 +42243,16 @@
           <t>IMDb/Podnews, Mar 2025</t>
         </is>
       </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>https://perplexity.ai</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAOVBMVEUAAADn5+QzMzIdHRz8/PkAAAD///0AAAAAAAAAAABKSkni4uCWlpTb29rx8e5lZWSysq/JycZ5eXdIC16xAAAACnRSTlME////////msddFjnD2AAABYJJREFUeJztm+uygygMgE8VqfWCl/d/2EUgyCViW0LZndn8OHOmtfAZQkgC/P1peT37vu1+JH3fP19/rrz6X/XtUDgIz993f8gT+q/w+lr6qu9/iNLBq17/XfeqOQCH9JUVcKigogUc8qw7Av8CgP7vZ/4Xl/avbv9dlwfQKikJMOzJ/rdZypYk2Ic8ALE2CYAHl/JIADSryAR48O2aQAIwlgJoNv7IBuCP5VuA5fh1NgDjYvoOYBLyxwQAjLMJ7yMJ0E5MfUsAIJvBDSEFIIdf/ZIGgPEZaycBMMzmh0QA0hAQj3ANsAv4HRXAYQjvA6jhJwaQsoY9XQC0q+2fzAjVH74FjeEAw2aGnw5AbFy3Nvo+CQVYRsAVVNOQj8qnsMgjYABm+A/vNRICdLt5L88QYgAYfj7KSUMKcIysHlrHJ0UA4H20tdACdHYYTkMIAWD4zeJBDdAthkAAQQCwmCkDyyc5gAwv1AhzbgzBA2hXNUbSSmCM6AHMCic/0Z24AM0azZMCAFLNepHRi5MDMMDnjqcoAiANXQ/DMdAngB5+zrxluwwADMNh6hZAT5AwcCkEID8cjSmqf/g4GPMbg76KAXSmRzaL46+YmeEJHisH0Fmd22UPi1xLAsBssMv+jMTu3wI0jixCWXzbhNIat2v6HxfkEW2ii/vZOwDNDM0KJtil+F+J6EmBPTnHBBjAGQZy9qa89yD/EIBc/lsA/E6Ctt95/BMAsU43Mrr9j3dPr+IzAP5I1CWU7J7dXybQtlU1J+kA3NxDS5gzlAWA4NOMv/qLpq+FAHTuI1d/vRhBhJAqaJECQPQxtaNJWyBUvP4RJYBOvZGAhLHrghYdAAS/wg/JhB+RlwNoIPo5enKC0iAnKQbQuEGxF5ZDWMyjKgIlALznhiUmUBbAYhMiAFP5sdbup2YmNcENgQKgnUzuZYc5TE4hb4qLORQAxvu6xaoQoIXpGNcV8wFM5ccr18UFih3cc1DMyQcA8/MaRko0EKuG8zEXAFJ/v/qP1YgGKFGylRDAZELh0KJVMrNSMr+8mwVgvG/s6vE64UkwnvaSAwDm93mlVBoCfJcBACWJb2rF3A7a9wBgfkj/iWq5rVYDwdcAO0+ss4n9ggU2Gkxy+i0AFKvxdT61Y2JrdhQAUZn8DQAIHGk0cBGdpHfNGrdangXABd7D3bbd+D9AeQCdFxQBGKkBxg8BxL4conLgSwCdIWM7ihaA2YY+A2DMrStcAMAOxlUuMEYNfVmiuQA4/T22TlgAtyFKAK9CgGcjRQEgCbAEiLP8HiCsLcUAsDtqm8aWC88GlLwF0C77KdMDBRiil4uL9TALJqe5JR6pm2K1nr4hgN2dhdfXBOGSTVEtRwF2uzurXbGdjoFDKAVg+1vAEy52Z5kcYIgB7O7wci5GtnbvJSNFNNC4Ocq5GkIu4E3HEhpoN2N3W7hvCPPSOVlWQANwNsao2osHoDxxJmT0GoDpB0PtBySOcdABeBqIcpQgIoLigKDcPXcAYPqdJdkwJNshiac7P+BowLqf0+FFMaHvEEg10Fobc/P2KCiFpVStz5QasP17ix4SFbvTkVAD1s/450exsPxEbcg0wBh2hucCwDnJo3ddCTRgg47wXONFYjIZb80IAJoTADnQd5UZ7ecRODoNuNPvDgCmI6UG4ngnBXDu7lNpoNqRzgY2CKodatXnVfBdkJtjvcohUGiA8/Xi25v6wBE8EWjg+mD17dFuuX4SaOAy+37jcLtMyrNP0ST6vweQLin3eH9yU/weQE6GPIA2uYn+BkA33NwAybpj0s5Cypx1ySTvksugJKuJ+td8Kl906utf9aoOUP26X/ULj9WvfNa/9Fr92m/9i8/1r37Xv/z+6+v/rXP9/x+Xi0y+9Ei4mAAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -42030,6 +42286,8 @@
           <t>DailyWire.com sponsor content</t>
         </is>
       </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -42067,6 +42325,16 @@
           <t>TechBuzz, Jun 2024</t>
         </is>
       </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>https://angel.com</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAYFBMVEUAAAD///8EBAT5+fkICAj29vb8/PxBQUEjIyPi4uIrKytnZ2fMzMx1dXUfHx/e3t6Li4uWlpZiYmIXFxfY2NiysrKoqKifn5/u7u5cXFw1NTV+fn68vLwwMDBGRkZUVFQki8afAAAERklEQVR4nO1X13bjOgwEJarTKlaj+v//5QIsipL1nl3H8cM9F5PYFlWIwQAEKAAGg8FgMBgMBoPBYDAYDAaDwWAw/ksI/G8Q/H7pevK3yz9k3pu4zC9BBs40/coLhfewOKkE7kjivztjGH6o9NNWpft8cu2i+ifzX277CeB0rT+e7/fDi70VTT/cEu/ylrZvkj6AvF/ccSOEKu1hUQmCHnJDoa3UuvbDWC/bTxm+k65G2ySLGrsCLAHytAlFjH+IikSAVNhRLBbiUw711ELw/WhItFCYVAMiIOLBnD4VWMhcpxTK0JeOgENNVvNIxLeX8lFWojfaSkNA0OhCIAvjeJwxKcY+BUdAN0szrOpmCOhY317Kxho9TNyiIwKxUBjs2hBAeSLy9AOWwPFxItcivJGQ3+XQdiJEp+0EFAJiMJ8KrCIS+LNPxzEdrScwmUcliYYhiG6XCvY0JoqxzsETEBpPdIkj0KpYZADlGhHujkCodaX6w8hmFQhA/tXSA9BDnUlqzDwZWALFipLoFQmkRAAZIQFlsq7wBMyoAZeEFIJvIoB7ZFZUNgM4AlOLxuMo9iEQGIJ2rKo49AQiuwhGCOSrBECigZDSsDFDowBAH6M1S6BBd0e6lHcfCugpnW7N3TzyEoEAJvRmbXGNR6cCZGWIw9gWohRTIiR22weBWO/u8dcI0PO9CKMJRlvWPIHAlAFXB+qQUkKtVXhVQJ45/xqBjewAuSkqKjNeAaD1Twrg0ahd0sXEDWsvpUy39mOz09AT+MYqRC96Ece3fVUhljuaJamMAmS39s1IFtqVXpWQmfJrKQ6jwrv0HIsAdh3RKh8y02qwzCRdZIoMTVQPZ28+BqX6xQwlpFWmo/Bch6iAyNblvrdfNwv/QIAiTf13a7TQHRajcrpTufs81emXK3dbchRL3YzD5OqAiU+miqd7IoUeayCVo3zOT3+NFdr8ycsJ6cx/2qzSoOyzKAxtRJ7NhAa1u4GUfvMXWC/tzEjguj8NLndcCJhRXmBrjFxlfAZTkfi5L+K5na+PgvX6OoDgQbDTw+zZniPwEDTH2Vjk6boxLcF//6H3PEng8e17ncB+K5a2xfWwbzAX5Bvs2C2gWDBTYa73RwSeb8gPn7hVTQ/FqtcyxRW6LrBkQ4fdoG+wNXZrVcBUjf32B/bPcnhw/2LqT9rhgrcE6hHabIehhmZFfqotuv1hCB68zf3N/KMHZK0baj0t5EgAt+k17hXUAn1NA9iwHC7Z+Kftxw9kYQpzVBoCMkugK4jArmdSoEZxaiXLtnV7srdgUp0KYKsw25aqQldrrarF5sCQdeqAA++Y30dAbgntPak3Qko5384zbQxKSo2Zrsk8Kd/4YmzXOvhvu+p9dQa//34+4f4drhJKdxSY13PbC6Qr0cE77RsOvvkEznVz1mrxymsgg8FgMBgMBoPBYDAYDAaDwWAwGIz/LX4BlGUuBcEweRgAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -42104,6 +42372,8 @@
           <t>DailyWire Ventures</t>
         </is>
       </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -42141,6 +42411,16 @@
           <t>Podcast ad reads, multiple shows</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>https://birchgold.com</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAXVBMVEVHcEyIYySgdidPOhSMZiW+jSWwgiaofCeQaSeZcSi2hyZ8WyBVPhU+LhB0VR1mShnJlSVtUBtWPhVROxR/XSJwUhuMZiJ3VxyZcCSUbR+leh+LZh6zhSGSbCjVnyTqlewHAAAAHXRSTlMA3f4h7P3+/vf+/rUxDp51/olDW81UyWnlrcWM3vYiaYEAABNYSURBVHictVuLdtu4DowsJZYjiQr1ftj9/8+8MwBfsp00yfaye7qtkwZDYAACIPjy8tOVd31rTTVkWVbcZBXZMAyVsW3f5T/+cT9ZTZ7XXTdCPOQPWVGUCqAsskwQ2HbsujrPm+b/JL9vTTVx51gl180h4MJn+NJU2RYY/jmCJq/HGeKHIkh9ti6AAVXs8/iPMWDztspk20eJ5e0ej6qisn39zxA09dju2PvDfkVWEaiQfiUbYIrxn2Bomro3onlPObX3gkX2Y038s6NFUAwwGGjhP0PIu1ksH3dXkPDwuXmeR7fwx9bSNQ9qgiHMf9QCdt/ZRDp2DprT4Xtxt7Dquut7CQ9wksjTsvhvWmjykdSL8mVLEC3iILDFvmXhT/ygkyiR0AURomq7XzpEg5BnfLDjj5pWxroa4uGRCEZKAMcD6mUeO0IDhAkeEyxm5t9BEM8r4+btqFtnMJJopPGoUFdgDJrUPERBzUUl2F+E6Kaejbc+TFntbc+tt4jC2aNDRpXT/eZR1DB46xWD/TEX87oN2y8LhpW65t6zp24fAZTCU0M1JPyB/tr6R9sX9sk/vpB5MC43f3THL2AMQlZqIYsIfkKEfDSOyZdyMnOd1zDqk0D8hSIgEahbk5XeDGb8NhHyXuRfLso92L41Q/ZN4W5JFOqjEiQkfE8H0L/8o4v8lB7bH+0XvPtCDRAJJXjSYjPjdxA0+Wy8fLKX2v+m7R+0QJfoZ6vmhFnM/HcE2D/lXy4Xkn/MnTm+ueeSYSGmKqJ3hLNKNwAEf+UBDn7V/+WWVTOsb6fvGN+ZWVIzSRbdeSBRiBAGh6D6Gw90/zfZf1vnsODftV/6MFitzAuZMWJNGi7lMBBvcFb4iw46YoX+L/jOWs6Cv8pHTmyMHhIgLH+T3xE2eTzihB4AoTfOGeCNX6igqVv1P9K/YyLytecz66iqncczT8JuTBbk0wutWStYoe+dO4LYX0RlxN+C+78VOMbrPgZjb+Y78UVmLLcuqQAUPy2b/FqmCcCMP5mMESo6BJ9HZQkAcD9EXyP7z762vNYi/TzvOw7IAVlZeZF184Qkhplpw0wcuh8Q8TNnzDubyY/A/vNaEJea8S/FUrqVyDfu4EVKeDot/IenS0AQagUpFHIyg+oVBPjxTxWA7KukAgqGP5wGtK+x+z7ranfWYyGqWTl093WC9PP5fDqfuFT+xcO8aIJsdhRtOOCdDgbbPVEBImAlBMTX6X/TXfKHokxYLfmvHhG9mZazrFNAcEq1EKlquelaYyI8/JkRmo425/nD+NfBtKNL+9p5n/d21qSPlWElwaXdt83JdyhE/MnpIEFwY0KRi46ViNkTX1QPZADgkQEA9KpZ8lxdmvTRv4EKX9un5Y0Lkt+cFrwSDiqgrwyuUGpGT8QHX2QIBomBAAG4AQCIXjdsEet0PS/n63nj2mdaBBjWDYJ1EcBb1IHXwsWztWLJUEkEBBFL/ew+S2zE6UCACQRAELNiXrJLZLz73xYany5yxV/f3xIIR0N4KpYF8zMcyar1prZ6Kkz3PGxgAI3AM3a/imeJcr2Mt3dd20TX7s121U/eUhAnYWPiDgh8LXYD5cJr1QgaXYphPgBoasMocisRthEOFwqn9HMqm+u8wA7r3tr1iOAclHASJqj8UtJTeJ+kJ0IDxFcGk7IwBxbwYxogs103r4vs5BzlBwjX67ZdX1+vq5337eo/9Rp4uzMCfxzT68JRv2/cVmkbBJsEwKgMYJzuTfStu+2/v4n8jw8g2Pd9vYPg5Z+dDsCnMY8nCn54I8bWgAhSHBlAF5ygMLuoAc6p6V/53+s7tL9B/odAGEe7RXgHLooOlqmtfX5z0wCYu4CrLGiDDcBNZmFQC5J54whw5B7FQ+h6VfkfMMM+9zADv3A0hKrgsqx7zdZCUl2uovTcs2AP4TBXBizZntd2OiX8c9aHFKz3q3H7Vx3sOIk2fuWAwKlggTWbZtTdOgSTuF5T78ICHDk+FtA5L8qA0Uf3aP9XLx/8v1L0H/z6+EMqzuO+6dejQ4oOTssq8axNE1oH4MUdizxznAUkDUAMQITfVf7bObX/qyw1gEgPOhjn9XrUgaJf1hb6zcc1zejKQfNBHglCw2p0UXjWPHyawYCUAIn4DxigWlUBWIriuu3jSLf0ADwVl5UlSDNXx4x6cilx3k96pmswok2kDFu7Thjwdj7fy8eCB5CBlC0A+Auu0O33NOD+yS/v8YkJfE5eCw1vSyt/zzvDPIAm6dboAu8HBXy8qgF0OfnQwd6P+1UYEmiAYDlLzMPBk6YF0IBPyWs9lgtNjeSE8hQ8xfh/MIAAENF/PgIIwNr2To3g3JEANvif5DfZUb4nYaRh1ebRBxakeO1yOjBQ5X9QAQDwKrI/PAxVwdrV+yYovQ2ulM8KezlkZ1irD76NKJ1FAj/pKslmF1Jw8R74fi//qhpIlyKYu3HlEcGYRAQgYCPbmu4yMwRf7/fwz8ylBQQwqQ+MPAaPIdjbHx4HCR9e+4EGBIBcZ79eV2MEAAygaf9YFXe5oQvFzvMnZxRWgxKGAaY2WfCBIwFga5w8H8808LrO+bzBIedNAExigJd8ni53FijkNBTxCJFKggy07KgN1iJdnfjAW1TAq5Ct+gzAtue0wT5uhLyto4s1i0tPgwKy1nGwqWtmwPQDfPbSW+eEoHOg4JEBWJt5kK8IQA4cIBuOJjkaV/W0fMaZdqIGYm46eCds+rZ2qRmC70sLQmoqNG7nRwUIBZ4CoCuIDVAgbEhRVqRIV3fC5XZY7pLjzKdACFCGnRuNBO2LlTAEA/Xt9IkPEsD6iQY+PlaUMev7ZmCk6+ryfVpTsqJAgkJ9XrMv5B2tOGJh7IuReqhABW2X89ELfQwSAI8ccAA2pD0AUJn16jyAJI95qcofAgOQIkDzvQKozEslBeHCj5ZHDTgFPAPgTAAAdU5HrKpl1WwfRc5yrE/IcW8AHNGsvq0AGKqXQVoiS9tpFEgygRSBxoHPNNDsV2qgcgygD/j6ROWzGnTyUYFK+d8uEhuGl0HCwDK7MBRVcOAAdohQfA9ANdALAIPazTl6zsQeABCLSy2EhrZuwv5LJkP1LACyTAFcCGDSOHh+DIQS9Pf7UOw1IADgBevseJ7vkySl1VpNvG0qJiUAKz5JEQAoVwBF9qJtqGXO7bREN3y7J8Hr/gjAc0AAtKt3gZecPrBMUkJbVGWuLcS7P20dZykALRNwVNtsOftI+B4CgfOCPwTw+kwBBJDv296a3ad49Ur5O8pYVtjWuv2Prb+BoAZ4ArB0flEvcQDuypFIgj+I9o9+4AHUO6s1z7McIfW0QAZUzk43+/QsuGPLVQBM+jcHYIgaePPBODmMNAE80vDjw0dCXuuaNTh61yKvuWQtPt5Xw+zY37yWAYDNx+EewJ5dzneRyKng1eXA90ZwH+dNjYJy820XFAP0gWVFbK3ABF8OJQkiisZPAISGwONpABWsexILXELwDsFs8LpjkMLoTuoFbNxq2jdXx7vPZwCs18D9cZB4YuSB0/91m7sGefW6hnwr3xfXJ8kqY4wcAfmx6SgAjhwIXhCbIg8IWBMzB/YxWHhB36+Rkay+zqIP+Aqd93lrJ0V5X90DcDVDdMN28GVxhJCwQPMiVuXsHUkWuHJOoM41IQkZb79qeeyOgqlXEpikSJFApO2qIgYiAjidk8qIwSBVgaSGKATg2rtZDXtmOaQjLb6GRAAppp2SPhHLIc3R0jLxaSSsFUBUwaEy9hFJlMCbYmkbjqP8hVmxj4I4iZe0SXSb9BjwBaECQGHszoLhJcs8ADlB0ubMUb7DAC2s0p/vZ3aKNmsNc9JAwXm5BAswHfHnQK0FoQIwbR0ADIOWadKaODkdHKrDUB76EuG6uXXFH+d2u75HCnb7XbPSZyIN03+3DsexXrYXtuutAjglRDw0CCIMpwtiWWdhgKdg3a7aIwpJeUiF8hgKmBFZrY0qTclukhMik06NcE558P56NIXrGewzquO36+xLDpS3iQ/cDgBsoGHWOgBMyazLDvuOtYQa4bFL9aAGqQZhAGbjgYKoSJdoAU1IHQlDRSqfsQz0Sammp6XUxgrgmS+krZrwv3ecgeb6/h4oiBMvAaDp2OTneRqVKZ+xDPRpea91onQHWKRGKzw0Sl8DDvkzAqOtJpbDvvMsDY6jAkJbBAC8I5YoA2Nh0ikAlmaGNzYqP22VHTGEZsiyzq1ZIH/1iUAzT1EBt6CB4CAiSS4P66Q0c0G5UFS890mcMfYLDx1TFsGr2a2Z8PVt90Ye2WM8GoCNHx+iagWApHyuk+L0xflnNtYw0uXieRCJkDYtXYv+Opm2dVcWIRXs9uVwcyTyCxNawvWcMQfjZA9OAj0DpT+g/plJKEoBHI8m1wW8sl++rjhn9cri7BUAD5gODLzodm3sSsxTmU1I3pFCpQ2KWm+W6Yit9AsdD4I7Rjqer4vc3di2pfYJbrFOAXlfLY83Zzx2vAaQAshVdt6EFo20Kt01ijSp9OI0eGNCBb0Q2Iw1vCLljYZ2xNbRV0MmOQRiTZhcT6EqwsHBqxLeD91CwZqrf/IiiVfXev0YEJwOEDZejldIud60J8qOqGfYlFyb6TgNry3bcC/BubAe/3rUvpigE/9t8rZwfJXWnuogYcIpVQFvhoOTnqbZE6BNCcCL22HgJb6JV0MNJxkGftJ0GhMLTx9NThifqAwn3yM4cMFBces0eQ+sx1Xll8UikwRKFOQNsS+VS11SWV4i+Fati1Gju8MAP+dCbm8vBy0oGw4onHxfCswqX4aO2n7UKQJZCQFQFpYl/om7uOJQiy/ZnUmEhvyag3CKEM7OGHpNrBe10z46/cv+l2VakarobW83yjBBnCyF1EI6Vbm/tInter2w0KDR2UoHqB4tIUHG3czxj9C/tiOacc0gP+P0lE7TwVGmappYn3oV5LJJ2XTuOsXxwqJBUeJusrrO+rTh8mCIdC3J/k3G3e+zZGl+5hg/JrmhzUeGu1KukYLF48Vd41LWwXb57NOGSwLhAQSLX+eAsn9sv+PwZ5ZMHEcju9EAORieXVq5aztqZc5xpPrULYFADBHFklWzz3Nms5SnCra3pjqMvMCicyhWWtZBhVTMjgGHazu9uNRmnjuonmBwvLzQ3MH/uyrDBztSrLuZZyS8vmMCvzOlymx4Q6cZ0OHi0t1ulCWHlw43TUdLyComP58I31oX3vjb9n7eSkYIvXz1rYKI3EXq/dUtPHnw95ko5YfjyIzOI7gYz6EQ143L4dtsiE6Iz9lxzIbyfSZUj7q7wdScDFMXODDgJRQuJZ2zHu8um256tAkG2b6/e7ITz+9T9Wz/Qf9AKeNIPHryz2cocpcWMDuVcc4nE0ylTGt23vqzHF1QSiUmTr9v8HNz+DbrdD7MvMme3ABD/zBM5C6SZOqvnp8M8JWciuRgpqu0OKooJw/4VB0UUNBIjaffVLjRmdpPKt5C3/BgBO+Kcudujz/STeO4QW3O+rfV4K5EuJ1EA/zGqKU2zNGZnpOq3gBP5njcGI9Oe+Ffig7Kmxtm0oF97L6RaXdbLUvpEx/kUs6H9Bv9+CrY5ztDBJk3bozn9nyMx0crJVDe7ZUML2eZzDPtO8ejGz7yGOcdar3FtAcArDw50ck2naOWFxFO/TeZDWSXxFvj2SCTNtL9vFnOQRXOBRodSaNwkS7jrXcMrVqZa+d3dqIlfGud9OV0cgkx041yfTZoLXeNzok4KhOm8jqZZx/dNFdR3g63gTzjrHQrOhWfc9TImCEOdzNwIxooHb6abT3Mm8mWZYSr61r3suf5aLFMn/oMRKRL7uEnJ/QIcOotvxjn40C3n4CVgb6RHSkuTlMlz3oeAJR8dbDb1u67wXcPWRLI3P6D/GcemFhhjG7TiqfrTuSBx5fDlcjGZJ71DqQMsrGR5ptkg+k+F/8Shlo1mPf9N0ZaE1lPhr8LMaaflP/GUGsy9jKIDn450+wwZYNMpjtyf2es1w8231xEHx9C4jfE+v9rUPKnwe1bg80vkuM4HcB8M6vA3ylB3gV0uYRD98F3RrvjcPtNhtut5jpfM/AT+S1HjP1we/nd4XY9wgJoZnvtj6lA41sdzA+b+fZ4v/LAT8TTHxlaGIC/qwZ/dOXJaPSPHjjE+7WghH7+thZI3lZe5DBNjz/km/r3EJJHLrof0cLn0VDlyDyz3z3Jr+yXJyY/fGbTRPbeZCqVRZ++OPwcgCQtnDqtO3mfV0Z//sWTM/pviKz6TkBfm/rBfX3n5J85ccBfT26ZSQ0xlNu3z0ep/6YDSTvDVV8hrzlltNhXgOGllw6yjzLhD1vZdUqu6LLfPvXyXIxWd8+oOlbA/plbeOmmSYM8R4pnofjDz9h3ROAeO96iGvxzP07137/30+d+8TEurW+7//bokc8974rOwr3wvX/waOLse9j977V/r4W0UNEHdvrkU6a+s4cnnzffEv0nL5CpBaa9j6XK549e5X3ev3n06jB88uz39uTZb6nPfv/1w2OpBxBcvo7Hpbz8aP/5w2eHoZPXnPHldxl3Xfpnl+zT/XvhiuDu8XvwDdcY1WAkj9//L/L98s//h+T5P06g3z7//x/dhS1HV/c6BwAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -42178,6 +42458,16 @@
           <t>Podcast ad reads</t>
         </is>
       </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>https://helixsleep.com</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAJFBMVEXF1ONHcEyWqb/X4uvU3+rN2ufa5O3g6PDn7vQBLWZJaZF0jas1IdyBAAAABHRSTlP+APs8DQ1D/wAACWxJREFUeJy1W416IzcI1Hn141ze/30bryQYYNj13bmy47T9+gU0DANC6/LrXMdR+vN2jdfr9c5Wv1i11tfPXKUcx7Rc5ueN9YGv/csb/zE/1suZ3q/5sX14iANHuTMP+1fTT2N8MON1/Wzbp/ntQy/HdOAY9/Zx82H/fX0s+4Pt30Zgrvby4MeBq/0P78LmgONCXxHw5qu4UA0KOwwvB27wP81P22LeE6DvIPi9L+vCAbP/1/vxqxzX/Bvbg6dsm2XB3Hjk32LBNh+8KEc5bvc/xAV1Qrzoiv807kNg8fcI1KNcRgD5n2mAUNAhUGcIpv2w9elC+xGEO/0ZyoFJvuhGD8aDAJDVZiJcUxCtc/kR/icqWNGLbqy/AGjt/RxQ9XmC9fMzc2ILAF+TBBcOrNxzGswAYKYXByqmgIn+guANBBwBjQJfB0E1wJkXJ9o9AmCeaFDPIVAEKPzT/jUHBvqRFuJcfqQAEgnYFEgdUOkJHGQZEJxI9FcyoN1mAeqfKkDYfhJ70WAiv3v3t2l4mf89j39FBV7Gu7Ut5tMQzARE60/GwV2FeAUI9N8JAPavEdAukHZgwACyWAFS9Nfv1IGpwRCARIYv8N/GiQsbgBSB8cQyMCAMIQEi/hAD3wA1kcBl/UIJbRGii1ne1rf2UiGSFExCIP3X+pdBd48ZOMS0qQArAbpNAbH9Mp+T8GWwlEepuwVNEyCpgWvvvTweP3/FRGEDwEOgwD9/f319FZEha5lLUHUI/Hw+fv7I7w4SoOGvKQIrAMsBt3ntATgBbfkd4AAkwEYgOoAtgDjAJYAcg0B9tgSKA6hBSoEMAR+C0ATRg6jvwV0IJgFx+1EHgAEpArsHJ2eg/amnQHHA14CEA0MooAgECvSEAkB/yX8TgmYlIIbAdYC3CLCjsBNfCMFSf7TOEBjyERzokv1cBav4AGdxi0B0oTjjUIIZAtsHfw6uMgdwJXA70KrPP4qAPQQFB/qIphkHIAyWhKJARAeGwr8o4B0QBZKzsDFd9RBAEDA58A8IkA4AemCoQMEBJX+SBe4UREjYgYK8B2A9uHJAc58h4KxHBPYUZJAUqPiyeRgRcGEoXn6kBVoI2CTQvTsJUvhtA6JZIEUwRQCbMEXglgERASpELvQeAVSAXXzAgb4EoBP+CwfpUTwg4ALQirZeTxgDDSnHDoCsDWE9KEGAk3AngJvCogM95j4k4FJA2oBvBEIReG2/6Yhmmpf+y4SggxPkIKAC2CMGCwHgfhQizD48BlkOXMyBbBfs1nKAxP9FgBcCcAZ+QvFXDlzPQUSFow8ve4oAyQDlgD2ABASSM2CN1iMMiICh/3w7BAa2P0sJnxcXFEudksNp156Qbn6yEDRI4g9S/P34u/W9fh7fSkIPAUdAITgd+MiKCJTFQZsFjgYfdSD2ARsB2D0j4WccCBVIiVhAgt0obnLgX9fvrxUCr4JlCYHcg4ATLguSPOBXJE4MZxbECqAIwF2EPYGoEBERqNqD8buAqURt1YJYA+bupwNG/6MD5Bgox7DKZ7HQg4sDFa2rDi0ODAYyIHCuERGoNfigk+iWIwD2LQLmGLQRCAHQqxg+isYpQHQAwr+FKBnCmYaEBmHzLhmJn2gkHFAPNPf8JP504KGE4tXM/umwmndANLDYEIRB4P8iREU/phMnCePmAYHPOqAkXLX4hYBC4AYR/wsCxTGgFIL9boI+7UAxbggHKP6vvJtZkInMNSn3X2+OhMUScHEgJOHM/OGEiOlhaAQl//c0RBwoTWXQIEBvgyQLSpiDuGm8M67255ZRByADAQFvG67DgwOmAs3l70PMHE4OJpCGEIDpQxSh0wXhwHCQwykkWCdTEBOCAvCvd7HHb8aBgEA4ARvzVQdBLgQ2CcQFfhnatxCxWbH8f4SW3rtuOLCAPzV767YLADwO8sGWTEOA4V8coPj3jyuhbYOEAT4EmgP907WgxARYShhDO334PAKoP4YDjv6LXhdHs2/92W/2Ov/7dIAkYcIBHQNFJZQxxJDZiExmWH42bMmKw784BDrQb/mADuzpB9VgUwhsldoOlBCA7YYloDbhWwfEejaGgik4GQVLNQwMdAjIXYAKzInAw+B/+USGzoBqRMABUAqkoQ2CLo8A3gb6+lMFAb8kBEYBWuSAyUBAYOwWPA3+vgqtYQ6DCHgFasaBLnPY4REYiH3wwhRg2rpbDrj4+yywV2EbAR3Hkq2jH3sUxxDQLti7ESRoeA7s+LPDGGYAm0QjB1SBPAL2KlDWEBLC+TMGwN6E+VMgcsC8LQKdQbDTEMSO5x9cxlwhwLYPCPQLBKjO6v51El2d9YCAVQKbBWEKMpADWQaieb/509ZGgPBfHeB34aKENXkmVJKfCZBDQKMf0hBLkMFAECAVqOnvxhCQE0g1WcBAGMGwQ0BM8yMQ0M9lwPleDmQMXCRkl9HVk5BSAEoAIYFwICkD54K7MHsX1ftCIC0BqH+UgsKBfP+KQAzCQkAI6EqgO4MR8+eOBYFMCbwAKwibA3whADECcgjYHHAlMDhgXFgHMOEAu4rZqRdDgINo5UBifXGAiABkQbWdWIN/0COgdUFPQfccyG+DgAMMf6AAoaFHIHch23/tnAPa//AaXOQqZP6+R8ALkQ7Cy+NRWmyF10O5SQsQzkCvh9n2Yl4k2580zIbhDQjA3MAevLVUhTMHdA5vH0gxUyDaARSJgDmDJHsHB/ggKOtBTA+YXYZAF3xlnqehG0RdmM/jn5yD7kOwryKkB3T8cwHwPSBmgAbgMgT8eZj0Pvw2/a31awJmCPAWXOWH3h6I+in+N6aDA1Xav/wYWoMMRgCyQ9ifcKASBJJnsYxpm4Ht3jw4sGfPFoGu1t0zqbwNtuSf1v84C65aIK3CFAWXgG9EoFjwzfcymAK0pAUsln5mFPkHHKgGAVKBkAbVmPcBeMM0OlBl/3IT6m9Dhfo0BipAb0sgQyA5BboU4AQE65CB9160YDoLf2ZdUpDPgq/Xo5QderwKyEZxrAOEGLga+J4DByJw+a2Q9Bxqyx8OYu7XUY6mAtTJRXS7Yr9mwJ+mwG7TjvLroRDkD0Q5BvgK4Efhb+fAcX7tV6sQv4kH+hP+2Q7oLflXHOYXn2ciyP57tB1akYjAX7lw7K9+aw+Ua0DWglkJer8G/Oz/kC+/H+0qA0wF9GkA4ccUeAODA759//r6f+EikHcBtAV4N/0e++v//wHbjE9uI5QQVgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -42215,6 +42505,16 @@
           <t>GlobeNewswire, Business Wire</t>
         </is>
       </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>https://cumulusmedia.com</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAACAAAAAgCAMAAABEpIrGAAAAS1BMVEX///8AWI/5+/wQY5YOYZUebJyZvNIDWpDg6vHr8vbL3ehPjLIudqPJ3OdhmLoVZpi50eB/rMeKssw+gapZk7bp8PVMirCfwNV1pcI/urhLAAAA9UlEQVQ4jb1T25aDIAw0INcgAt72/790A9RLV7v2pc2LRzKZGcPYNF8uZrSe2MuuTeiEcJi6S4z1vYJSint7HpeitITgGSaWPyQstQAcpdXaSuQAbXpGSOoP4XHGwkAI+aRP/LPe3zWSysEH8zSvjxOBGP0uYnvgoZJLGQwdODLa7xRJAWa4HmmwHXXpg4qbAoLKlthY9zC4+sRVwzjg9iFcS/iZtuHM6lmAyBbl2ie+CZ2bp3cBFxI/eJS4NXn7mU3Ht0XFuC2Kd++vulwW/nNZ99e9BmbJgVnGi8CcIifPub0JbSaxscY+Xse+YOjHMS+7n6pf9+kLI7P1L1QAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -42252,9 +42552,19 @@
           <t>Blaze Media masthead</t>
         </is>
       </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>https://prageru.com</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBEQACEQEDEQH/xAAbAAEAAQUBAAAAAAAAAAAAAAAABgECBAUHA//EACYQAAICAgEEAQUBAQAAAAAAAAABAgMEEQUGEjFRIRMiQWFxckL/xAAbAQEAAgMBAQAAAAAAAAAAAAAAAQUDBAYCB//EACERAQACAgMBAQEBAQEAAAAAAAABAgMRBCExBRMSIlEy/9oADAMBAAIRAxEAPwDyjFRilFaS9HEzMz3L6J6qQAAAAAAAAAAAAAAAFJRUk4yW0yYmYnoVIAAAAAAAAAAAAAAAAAAAAAAABVJt6SBPSrhJeYtCY0iJiVoSAAAAAAAAAAAAAA9Memd9sYQXl6PVazadQ8XvFI3KdcJ0nX9NTyVtl3x/nRrdnO8r6k71VtbulcOcNdi2bVuBjmPGnX6eSJQnqHgpcdNyivsKblcScU7hf8Lmxm6aI0VkvhXOx6hFyf6RMVmfETaI9ek8PIrW50zS/wAnucV49h4jNSfJeH9MbIAAAAAAAAAlv+jq4WZ7U/nSRvcCsTknas+laa4+nU60lXFL0dRHjjrTuV5KEc6xqhZx8+5IrufWJxztZ/NtMZenLppKckvBzU9Owr3CYdEYlVs++et6/JbfPx1mdypPq5bVr0mPJYGPZiSUorWi3zYqzRRYM94u5JmxUMu2K8KT0crljV5h2uKd0iZeBjZAAAAAAAADN4nMeHlxsj8LfyZsGScd9tfk4v1pp1XiuUpy6IuMlvXs6jDnrerjuRxrY7M6V9cVtzRnm8Q14pb/AIhHWfMRsrlj1y+WUv0OTEx/ML/5fEmJ/qUGfy9spHRNjxHK28db3Q+V62bGDkWxTtq8njVzRqW3z+rb8ih1x0tr2bWX6F7V1ppYvl1pbaMzk5zlJ+W9ldadztbRGo0tISAAAAAAAAAMvFz78Z/ZOWvWzJTLak9Sw5MFL+wyrucy7YOPe1/GZb8vJaNMNeFjrO9NbZZO2W5ycn7ZrzaZ9bVaxXxYQ9AAAAAAAAAAAAAAKpNvSWxEbNxHq+VNsFudcor9o9zSa+w8xetvJeZ4egDe8F0/byKU/wDl/o3uNw7Ze1by+dXD03OX0Y41N1aTSNvJ82ddNLH9eJntEczFsxLnXYtNFTfHNJ1K7x5YyxuGOeGQAAAAAAAAAbTgIUzzF9fxtaNnixWb/wCmnzZtGP8AylvU1WHHjW463r8FrzK0/LpS8G2X9e3P5a7nrxsoXSx4uq19WO/Gz1X0t/5l1XpaNawYdut6On4UR/Eacb9CZ/SW7lrte/Buyrocy65Vaz49mvD3o5v6Wv0jTrvk7/PtGStWwAAAAAAAAAujKUXuLaf6JiZjxExE+vSeVfZHtssnJemz1OS0+y81x0rO4h4nh7VAkfAdRS4+Crsf2r8llxeZ+fUqnmcCMs7hucvrKt1NVSXdo28n0q66aOP5NontDOQzJ5t7ss9/BT5ck5LblfYcUYq6himJmAAAAAAAAAF0YuT1FNsmImfETMR6ulTbFblXJL20TNLRG5hEXrPkrDy9KAAAAAAAAAAAAAAAhL+juHqy4q2xJ7Lfgcat/wDUqP6XLtj6hK87gcW3GlDsXwizycSk1U2Lm3i7mPKYqxMqUF42c3mx/wAW067j5P0pEsMws4AAAAAAAAAAAAACT9K85DA1Xa9R9llw+XGPqyo+hw5yxuElzeq8SND7ZrbRZZPoY9eqrF8vJ/XbnnIZLysiVj8NvRz+W83tuXTYcf510xjGzAAAAAAAAAAAAAAK+PAByk/LYRqFAkAAAAAAAAAAAAAAAAAAAAAAAAAAABSMlJJxe0yZjUnipAAAAAAAAAAAAAAAAUnJQi3J6SJiJmR//9k=</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -21,13 +21,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$296</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$L$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$N$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$P$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$95</definedName>
   </definedNames>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>68 records</t>
+          <t>69 records</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28007,11 +28007,13 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -28052,25 +28054,35 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
           <t>researchNotes</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>related</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>addedBy</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>yieldStatus</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>yieldNotes</t>
         </is>
@@ -28117,6 +28129,8 @@
       <c r="J2" s="6" t="inlineStr"/>
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -28154,11 +28168,21 @@
           <t>Times of Israel, Heartlandtoholyland.org</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.in.gov</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHgAAAB4CAYAAAA5ZDbSAAAABGdBTUEAALGPC/xhBQAAACBjSFJNAAB6JgAAgIQAAPoAAACA6AAAdTAAAOpgAAA6mAAAF3CculE8AAAABmJLR0QA/wD/AP+gvaeTAAAAB3RJTUUH6gYDFgogP9TfigAAbABJREFUeNrt/XeYJGXV/4+/KnTOYfLszOxO2BzZTM45oyIiCGIWA6Io+pgDIJIUFQSUIBIkSM5hl805zcaZ2cmxp3OqdH//6GGWlUXB9Pj8fp9zXXNtb3d1ddV96j7xfc6R+P8BWnmTPyzr9tmSbLaoNnmGhDzZwqrGwi/JkoosJISkSBISgBAIJGFiSUJYwkAmJUlyr7Cs3aZh7bAMZbdwaFuXXpUa/b++NtL/xYtee114urDJJ9sUzrOg0WZH9gZVmycg+R0uRXG4ZexOCcV24PYMXWCZAgBZkVDf+Zkh0POCYs6imDfNbFIkMwnD0AtYksw+w+JxUbBeXHztaOv/Y/C/gVb8vKJcRTtXUeXzENIsd0CWwlVqOBBRbQ6PRDEnKOS9FI0QKFFQo0hKCCR76U+2ozjLURwhAMxiHLMwBJYGQgNRRJgJMEbAGMFhi+N0ZXC4JQpZQWpYt+JDVjKXMg1ZZrum8UhRKzx21LWZ4f/H4H+QXv9+g9PlSZ5jsylfUVRpUlmdLRAsU+wur0w6aSdfqAXHRCRnI87oYTgjM7H7qv8lv62l+8jHtlIc2YgotEGxA7erB69fI5+xSAybxeEuPWWatGlF85ZCzv+XY7+/v/D/GPw+aNVPI4tsLq4G6chojeosr7cHVFUmnqhG2JqRXC346s/GVTb9757rrc4UrcM5ABJ5AwGkigbnTo0yv8Y7ftym/gwVXjvVPvt7nEmQH24l3fkkIr8HSd9HKNSHoVsMd2qZkT6jAGJZscj1S6+Jrf1/DD6UXr0+crzsEDe6feqEmmZHxBtQSCX9aExHDhxNeOrHkW3uQ373D5sGuXPdAH3pIjV+BzeeMpElE/x89JFdvLgvTtGwyOkW9UEHUbeNa4+ewHnToqXf7Umz6I7NSBIMXLOYco8NgA19GfaM5DlmYoCqv2K8ZRRJtT2JNvwSsr6RcCRBJmnSu7cYy6XNLqMofW3xNSOv/z8GA6uvD5+o2qVbPQGlon66Mww2kpmpyP5FhKZ+Gpun/G9+/09bh/nYn3fxuQVVzKz08Nu1/fSlNbqvXohDlQG4e8MAVzy5l61fnMfMCs9B3z/nwVZe2Ft6CB7/6DTOnRYB4Bcrerj25f1opmBy1MUxE4Mc3RDg+Mbg+EMAoGcHie/8HVZqDQHfTiRJp3t3cTQ9Yg7runHNoqsTT0kS4v/vGLzqhtDhNpt8T7BMLa+d7AialoNkdjqOyvMJT/3Y+760Lzy9jyd3xui8eiGqLDGU1SkaFhMCjvFj/rhliIv/vJu1n53Dghrf+PutQzlm/moD3zmmjuuX9/CFRVX84pRJ45/ndIvPP72PezcNsrTOz/reNNefNJGvLK3h/s1DnD01gt+hjB+fan+WdMe9BNxbsdnydO/W4skRY0jPiUuXXBtb87+xzup/+geX/ywQcrnUWxxO6YzGue6wYTgYTU3HM/EKqhaePn5cR7zArav6+OyCSqaUud/zfCc0hvj12n4qr19Drd9OhdfOtHI33zyylgpvSbQ6x3ZywbAO+u6P3ujCqcpcubia5/fEeaszddDnbptMZ6JAc8TFik/NJqdbmJbgrc4Ulzy2G6cqc+aUMJ+eX8UJjUH8k07HP+l0UvufZ7TjPiobt4RqW7Khts2F59bdFFmRLxQ/+Z+2vOX/1A8JgbTmxugVLpdtZ90U50WTF/jC8eRMqP0NVcc9gX9iibmrulN86KGdNN+ynqd2xehNa3/zvOdOi/DMxdO5ZE45Myo8FAyLX63u45NP7h0/5lAM3hvL8+iOEbx2hWtf3k9WN9nYlyGjmePHFAyL1d1pjpkYGGe4z6Hwu/X9eOwKN5w8kX2xAif+YRuzb99IT6oIgL/hVKqO/ROi+jbiyRm0zPeEG2c7T/N6nDvW3Rj5hvj+f27d/yM7eMWNwfoNtyjPlNep9XWTnb7R0XJGjdOpOv5aJPnAJZzxwA6e3T3K4gk+/vShKZw3LYIi/21RrZmCkEvlq0trxsXyx/+8mxVdB3ajyzbGYP2AKrx+eQ+qLHFSU4jdI3mymolhCVZ3pzmhMTj+sBUMi6MbAuPfi+cNHt0xwlH1AT6/sIorF1ezrjfNI9tHqPY5Dro2X90JeGuPYWTLLcDjysxj+sq6dxa/vaE//LG1P+aMhd8Z7f4/v4PXXB88x6Gqa1rmu6dFJwR9A6PHEJj/JBULv4skq2zoy5DXSztrZoUHSYJ7zm3hrClh/rh1mFm/2siuMVfnUKSbFmc+sIPT79/Br9f287mn9vHnHSOcOSX8njt4IKPx0LZhLp5dzv0XTObNT87irU/NLqmQzuT4997sKL0+6h0MfmDLEHnd4qW2OA2/WMf3X+uk0mvn5ydP5FDPoiSrlM29msDCRxmKHU1ZfdA/eaFnpuqTN6y9oewj/2eNrNe/j+oPRm9weuVLW+a7wqMjldgnfIVgy4Xjx2wfzDLn15u4+vAarjtpIr0pjUk3rWVWpYeuRJFU0eTjc8r5zjF11AUc7y0hulJc82IHvSmNSp+Nj80u57MLqlDHVtywBLopxnfymMpAtwR25cAS/PD1LkIulSsXlwImx9y9ld6Uxt6vzh8/ZuavNiJL8MRF07hr/QC/3zjI9HI3r1w2832tS2LPn9F6biYc7mXP+lwin7GedCVjn5n+fbT/O7HiH4cnrL8psqP3L9VZfVO96H7hNFGIt4m3ybLGX4pzH9wh1O8uF5v7M0IIIT7+512C7ywTX3muTQxmtPHjht7x+m9SYZ8QVkGIzEoh4o8IoQ8K0fUpIQp7hRi8vvSn9QvR/Vkhip1CpF4QIv26EJYuRHH/Qad6eNuQuHfT4Pj/V3YlBd9ZJr79csf4e5phiZ5kUXwQKiY7RfeL5wpt40TR+5eq/Pqbo62rrw/X/p8Q0WuvC09XPPKqloXuqb5owD2UPoeaE5/EEZxEXrf46CO7+OEbXePH33xqIwCfenIvpiX46tIaACIulTK3jZfb4px633Ym3bSOeN44+MeMYbAykHkTuj8Nei+0nQij90HizzDya7ByUNwHVmos7qyVXhdawUzAyG9Lxyf/AvuOgeIe6Ps6pF/kw9O8XDLzgM+bLppMK3fzkze7WXTHZu7eMEDRtKjx2//uugxmNFZ3p4nldOz+OmpOeIS4/nF8ZRFny3znFJtDXrPq+sjU/2oRvernkUV2m/T0lEWuslyhClvtNQSazgMgWTAIOFVOu287r3Uk2fT5uaSKJp/+y152DefQTMHNp07iK0trOP7329g2mKXKZ2frQJYTG0NcdXgNJzeFkChA/E8QOA86zgLnTPCfDLG7oeEhSL0AnsNBDYNVBNk9JpIFiUQCgGAwiCSN3bqVA0kFKwupFyH0Ieg4DwLnlx6M1DPQsgoSj0HgHJDdvNWZ4s71/fx5xwguVabz6oV47coh18QS8M2XOrh5ZS/GmEr46tIafnJCA4oskdj7GGbf9bhdg+xclRsxNPO8Rd+IL/+vY/Ca68In2z3y/dOWuMsSyQm4W36Kt/YoAO5Y18+1L+9n0xfmYQnBjF9uJORU6UsXOXNKhF+e3siFj+xi60CW7VcexvbBLOf9qZWzp0b4+hG1peBEbh2knoPgudB+DtT+GmQnKGFwzSKdTrNm3Tp27WknnSuimwJ9TPdaFiBJuL1+ALradvPKM3/G5Xbj9frw+31UVVXRUF/H0UceztLFi/D5fFDYBsUOUKPQ+TGouw8KW8A1DzxLiecN3upMHWTQ/TVd+/J+frasm0khJx+bXc6GvgzP7RnlO8fU8aPj6wHI9q0kte1rRMr6aV2VHTHy4ooFX4/95b+GwWt/EfmE0638YuoSV3hkpJHgnF/ijExDCPjB65388I0uvntMHd87th5JgptW9PK1F9r5zIIqfntWEwA7hnLM+/VGTp8c5rELpzGY1aj02mH09wcudeR2aF4ORoyCGeH1N5exZcduskULy+amfvIcKmrrUVXbe16rZZn0dbaz8tWneeiOn6MVi3h8AarrJ9G5dyemYRCtqKRhYhNTp03l7DNO5ZSTTsQpdYOjGfYsgeAFYG8AcxQin3rP32odyjHr9o1MCjl561OzKffYEAIO/90WNg9kGPnWEtxjhl8xvpf4hs8Rje6jdVV2tJgRX1v4jdgf/tcZvO7nkbMdXuWeaUtc4cHBFsqW/B6br4aMZvKxR3fz1K4YTWEXm74wd1yMmZZg0R2baRst0Pqlw8aD+fdtHmJxrY+WqBOGbwH3wpJoxIKaWxBC8Mbyt1i+aj0Fy8akWUuoqpv0ga53dGSQoZ4uahoa2bFxFbd+70t8/bo7mTZvCStfeYqdW9bx/CO/PxAosNmYUN/I3Hnz+PQnL+ekE48rife+b4DeDRXXQvoNKPvCu0yan7zZzXde2c9DH57CR2aWjb//oYd28ucdI/R8fdFB+lvP9DG86goqylvZsSKb0ApcuuBrI0/9rxlZq68PL1Yd0l1TF7vCg4PNlB/9CDZfDbopOPruraztSfM/x9TRFs/zsUd3Y43FGRRZ4p5zW8jqJl96tm38fJfMKaNFfbpkPCUegdxaqLmJtP9H3PbrO/nWj29mx5DgsNM+weFnfOwDMxfA7fHhdLt56+WnqJnYzI0PvITb5+fhO2/E7fWzY8Oqg+04XWc4P8BTTz7KWWefwZz5i/n6N79Nxv9dqP8TZFfC6F1gxCD1NLwjr6CZJb/7nXHxzkSRZ/eM0hB0jqcnH90+woa+DDZvNeVHPcjg4BSmL/UEVYd095obQkf+MzxS/mHm/jQ8zeaSX5x2uLtsdLSR6OL7sLnLxxnoVGV+fELDWHZG4o51/WQ0k5ObSqiKCq+dVNEkrZmcNSWCYg2BmSrpOlst1P6SlDmd39x1H0++9BZTjziLptmLCUUrkDBRhI6QPnggbtfWdag2O9GKajKpBKFIOXWTJjNr4RFU1DSwceVr9HW1l+7DpeKe5MW/MITsVtBSRfo7utmyYyv33v8QO3bs5IgTvoir9vOQfgV6vwr+U0u2gWSnymvnzvUD7IsVWDLBT9togfP/1MpARueXZzQyu9LDI9uH+diju3lo2zDHNwaZEArgrDqR4d1vUN+cdo/0GWdefrzjxbteLgz+x0T02h+HJygeec3Upe6qVGoC/rl34opM+1txaC55bDcPbBni12c28bmFVeMWpixRck3aToHaW8E5G01Euf3O+xjJw/zjzsbucB50voC+i6xShyG7/6GHc6BnP11tu0knRgmXVTJ36bEADPf3kE0neeihG9nc+iahw8tRPDYQIDtlrKJJatMornov2p48w6t7qamfyEc+/BGu+/F3sVntJder8+Mw8Qlwzea36/q58pk2DOvAzv7WURP46YkNPLh1iEse28PsSg9lbhvretO8etks5lR5KMR3k9p0BT5vFztX5vp0zVq0+JrRnn87g3d8H3s+ENncssA9pahVSK7Jt+CpPvzvfq9oWBz/+22s7U3zwiUzOG5SsGSk9F0DZV+C7BoInsery7by1MvLWXTKhQRC0UOeK1zcyKhj3j9tHI4M9iFJEpHyqgO+bjLOz2/7FIlJpaSPHiuip3UKnRkQUBwoIDskFI9Kri2Np95PcX+Blskz+PY3vs6HzzsORu8F36kQ+y1UXMuuuIfHW2OM5HTOnhrh6IYAD2wZ4hOP70GWYNeX51Pts3POH1tZ35fh1ctmMrvSQ7ZvFYW9X8Gu9Ivd63Ktkic2d/5n0P+tIvrys6O/rWp0HOFwB+xy9Xfx1Z/8/rIassSZUyLsjRX4+JwK/LSBMEtWsucokhzNj274LVlnFQuOOwen6713p8vqJa/88/grt9eH23MgP/z6M4/wxH23s2ffJnJ9KeJvDuKc4MFZ6yG9JU6hO4Nkk9FHNVx1XsrPmICr2Yep63Su2cMzzz3D+s17Oe387+KQBiB2O/hOIeoWHDmplpObQzQEndy/eYjLntjDnEoPiizx3J5RLppVPuZGpZlb5aU+6MTum4Cmh5HzKyW7Q/dlh521d76Ye+bfZmSt+3nkbJdHOr+s1ubJSqeNBzHeL5V5bDz20anUuGIlkZx5HZpeY+1OG9/60Y0cdtqlNE0/rPRAWDlc5qHVjiTeGyBRnX/xA11TIZ/jfz5zHqPDgxx7xoeJVldjKBpGSkdPFElvT5DeMootaKfinHoix1XhqHQhTIFZMMm1pdBGSmnCQjbHXx57mAWHH8mrq9PQsh6KO2HvEaCV9PrO4RyXPbGHw6q9vHLZTF6/fBZDGZ2T/rAdgMc/Ou2g5Eaw+XyynE5FvcPl9EkfWndD+fn/lh289sfhCapLfmbaUk9kKDaXqiN/iyQp/H7jIEVDUPs3kgEH0fAvQXaB90jwncgd9zzC1q4UR5/18YP8V0uyUVZcRcbWePAFiyJ2K0lBqUAVebxGO0WlJMor8m9QUGooKGXv61L6utrIZNIcfsKZuDxennv4Htbse47RvYOUnzEB79QAikel0JXBUeFG6BauBi/eKQH00SL2ChdIYAs6yOw8kIWKDQ3y5LNPk8/rHHv8BWCrASUEqacoiy6mMezkR8fXE3SqhFwqZ0+NIEtw9MTAIa/TU3MsA9uXUd8Ucw33akdfcoL90XteKiT/ZQwW30ce8Lnfal7gbkilqqTwgt+huiJs7Mtw7oOtNEVcHF7nfx9nsqDvayB7MYOX8v3rfkW4ZQnNMxcc8mif0UHGNmn8tSaHCOi7yaiTsCQb5YVlxO1zEJKCz2jHYY0w4lz0/p9uxcZf7v81fV3t/O7Gb/H6048g1ysUe3NgCay8iaTIGGmDxMohzLyJbJMxkzqyXaawP4seKyKpMsKwCCwswyqaGCmdYj7PylVvsWvfAOde+D9IyYdh5A6IXM6sysB4ChMg5FJZ+jfWT5JknGVLibe9TEVtzpPsN46744X8HT/4wb+IwWecHvlCtNZ2ricUcMpV38ZbfThZzeTke7czq9LDr89sZlN/ht6URvV7Bd4HfgSJh6HhETT7Qq757k+Yfsz5lFVNAMBhjiIhsCTbOy5OQxEFdNmPV+8gr1bhNfaTsTUgCw2nOUTW1oAq8pQXltHrPvPv3ksqEaNYyLNj42r+8NsfsHrbs2x87TVyIo293IUxWsQ1yUdmexx3ox9Lt8jvS+Fq8CLZZBIrhlB8NrzTgjiq3BS6sygeFdmhYAs5cE7wEFpajpk10BNFtm/ewoo1G/jwJTegln8Shq6D7KqSBPsgotYRQNd9KMUVkrB0z76XHInfvZRf/0/r4DU/9UUUu/Sd2imOQKqwiGDzBQB8+bl2RvMG950/mZxucuEju/jB652HPomZBHs92JtIZ/Jc872fsuSsywmXVR6wspUQFcU3sFklJEa0uJqkbQo+fd9fy5Pxz2OOhSW9m3uWHvfZB/SWtgNZHDq9OjzQS3xkiHwuS4e8A1e9l7LTalE8KpIClm6iuBWiJ1bjqvdS6MqiBu2YGQMjqeGocqG4VIr9ebTBPFqsSGpDjNSmGJJNxohrWIaFd2qA0OHlBJdE2da+lVPOOIdMzgLJVfKThfGBjcJgy4dI5hYwYYrDp8jS99ff6Iv+0wxWXfY766c7ovGRSqLzfwzA7pE8920uGUCb+jN88Zk2kgWD353T/O4TJJ+C3XPBewTFwBf5n5/cyFHnfxa31/cuj63XdSrlxbewW0lMyYvP6DikmJcwMCUXlmSjKv8KQ86jsSQbEiYN2Yfw6u1Y0rslSSGXpXNvK/VNU9m+fgW5jjSpTaMMP9VNoSdH9MQaZIeKNlTA0iyQwVnrJnJMJd7pQUJLygkfVYm7xY894iC7M4mZ1VGDdiovaMBV58E7K4Tqt2OLODEyOvEVQwzu6eLN117i3A99FC10FYQugl0zIfnk+2Jse7zAHzaV1rt80Q0k4tXUz3CEsTlu/6dE9MrrIws9AeXb1Y0uT8F5Cf76U0q7x23jpKYQz+4e5fa1/Wzuz/LAh6Ywv+avmKZ3l9J2ajmW+yi+9b3rWHzmZbjcnvd0y9O2ZsqKq0jZJhMtriVrq0fGwmal0eUAdpHGbfQy6piHX9+LKXvIqA24zEHqs4/Q5zrlXT6yz+ggoLWiuRpRVJVsNsXyZU+Q1kaRfTJm1gAZRNHEHnUgTIFzgofcvhT+2WEUt4o+WiSzM4E2UiSzLY5AojiYQ1gQnB9FT2qYaZ1ibw5tuIie0HBUuFD9NmSHgpkzaN+9h/Wbt3PhRy5CJg/eo8a22aFdQtMS3LKyjw89tJMX9sb5zIJKvJ4AmZFhgu7NcnLEqLz4cMdbd7+S7/7ADBYCaWid+7XJC9wTRkZnULH0ViTpwIav9Tu4bF4lsZzOhr4M2wezHNkQGIeqgoB9R4OVhopv8f2f3cyMYy7AH4q85wNVmX8VTQmStE2jvLCcjDoJVeSxWRks2YHTGiKtTsIukhiSF4/Zzah9HtHiWvz6bjo9H8GQSyUpNitFeXElIW0rFgodhWZe+PO9LDjqJJateZK1sRcoxnPosSK2qJPwERXIDgXfrBCeZj9mWkePFbGXOUlvjZPeHMfSBGZGx1HtRh8toA0VkSQJ7/Qg2lABxW8HSUJxyrgbvCTXxZAdMtFTapDtCrn2NF19+9mzr4fzLv55KRDSdzVEP/MuYbp9MMs5D7Zyz8ZBFtb6eObi6dQFSxE9d9UShlpfpbpu1D06YBxx5wu5X31gBp/iDZ0ZrrRf5Ar4XI5JP8YRbMQS8PD2Ye7ZOMiWgSyNYRcXzymnKeLiT1uHuXP9APOqfDSHbVDYDt6jwXccd93/DIHGBeMG1dtkt0aJFtdgs7IUlQgZWyMBfTd+bReDrmMIattI21pIj1nSRSUCyOSVGsqLKxhxLKEm9xxZtZ4R5xJkdMLaRgL6buwiybBzMUnbNPJqDcnRGHde901ee+YhvDOCDMs9qH4b/jkRvNODIMAqmIy81IdZMMnvzyA0i+TGGGbGRLKXgn6STcZR4aLQk0VSZBCgxQrk92dIbxoluCiK4rUh2WWSa4bxtARo3u9jYHeKQjpLYEmUPbt2oWg2Dj/qHHBNB9kLig+Q0U3BjSt6uejR3QxndX50QgN3ndNCmcfGC3vjrOvNMLPSC2oZIvkyRkFTL1pk33r3K4V9H4jBnz/d+0TTXGddMncYkdnfQDcFZz2wg+uW97C6O80rbQl+taaPvGHxlSU1XDirjD2xPJ9dWIUn+2gJQlP2ZTbtzLB+7yCTZy9+twiSXGTVBizJTkBvxW30ImGNi+kh59GEtS3MiX+Xyek7qMs9jt2MkbE1o8sBwtomBlwnYBcpfPo+PEYPCcdsckoNbrMHm1UY94k9vgBLTziTztFdrFn1HIpLxlHpIr8/i7AEqkfFSGjYwg5ye5IoThVLt5AAq2giDIGrwYunOYDsUNCGiwjTwjnBQ749g+JR8c+PIjQLZ60bI6GT3p7A3WeyeGotK9fuLCE8J3jwLwmz4o8rWLz0DOrqZ5YknRIC1xwuf2IPv1jRyynNIV64ZAantYR5tT3BxX/ezXXLu1nWmeSrS2twBRuJ7VtGZc2AM9ZrzLvzxfzt75vBa34WOc5frl7mjXjc6oRv4Qg2c8f6gbFKgyp+fVYTC2p8rO9L8/yeOELAedOifHRWOR45DrYy8CwlY7Vw6+/+yBGnX/Q3DQFTcpJXqsmrNRSUKtxmL5pShil7OGz0GrzGfiQsZKET0PeQVeuwZBeG7MVlDpK1TUCTgzisOF69Hac1xKj9MHLqgXCmYei0blxN1FdFZ3EnIiyQbTKWLpBkGH1jEHuZE324gJnSSz6tZiFMgdAtUCQUm4wWK6L67UgShA4vx1ntRvXb0RMaqY2x8Z1fHCxZ2TYkGmqiDMVSZPMailMhtydFvGOI1es2cskln8ThnQSepSApTC4Lcni9n5+dOJFN/VkueWwPP36zC5sikSoaXDSrnLOnRsbMTTdkXqWQ1dWPHW5bc/fLhf3vMpIPaTk7xU0TJjsiifR0qhaeCsBTO2PUBRz8+swmJAkW1Pg4Z2qE2bdv5LbVfXz/uPpSZqj3yhLOaeJf+PmPb+DIsz/xd63EsLYeu3lw2YimRPBqHbjM3ne5SS6jixdTFbQNryLkDVEmrWJSdAGa772DHKpqY+HRJ7N3+ya88QApaZRiX45Cbw5hCfLdGbShPO4mP9poEW2kgKPSRXpbnJqPN6J4VPIdGfR4EUmVcFS5UP12Uhtj5NrTFLqzJXvJpaIG7aQ2xDCzBpH6MF/9+Als29vL4Gia7J4D99m6dSOf+cJVPHjfPaU0qdCY1vAoQZfKcfds4/WOBE1hF/edP5k9sTz3bhrkxnfUTgUmns5Ax93UTd0QyibMG4H5f9dNWvXTyCKXX61FsuGq+9j4+xnNpGBYB5V/lHlsnNgYJKuZJeaaKSi7Bir+hzeWLcc3Yfq7Un2HRFnY5zPsXEpercGUHEhY6LIPU3m3dbmjWMGPd2xn2+BjJLT9FOmlQx/k1b7nWdd5P5qRHz82nh2ktX85rX3LiWUHAGieMRfbeAWChGdKAAQEF5ShxYqkt8VxVLsZebGXQk+WyLGVGCmN9NY4hb4ctqgTT7MfV72P1PoRZLuMf04Y1V8K0NijDoQh0EZK9eBel4NsvkihqB+Uv/NODVB5QQMvvPQsL778KkQ+A9EvgTCIum3jBQA7v3wYsys93LC8mzvOasbvUNifKPDM7lL7EGfthYAdl1duWPGzyIK/u4NtLq6uaXZEkpmpVC48ENc+uTnEiq4UH3p4J3ed00yl185wVuf1jiRzq7wlx33v4RC+FCP8FZ599Rccc8GnP5Ajr8teMmo9sXyM7uGNFPQYy1PzKHfb6E8m8CiClTkX01qmURkqY/9gL0VdoyZaQTafJ5Xr5KVdN9BcdjwpbQe6lCKZTeGw2ehIvIBpqEwpP45sb5KBl/aDLOEod2LpForHhnd6EJvfjhq0o3pVnBM8mDkDSxOoITuKR8XKGuijRSSbXHKZdiYORoCk9IPe6x1K8Ob6vQyPpkuZsDovZafWMLpsANVnY6SQ4Fvf/h+OX7kMNXEX9H4Ze8tKXh0D0huW4PIn9nDRrHJmVLj57FP7+P3GASq8dk5pXkCw5UMMvHY/1c1bIvls/mrgI++pg1//foPT6dJvqZvq9BRsZ+OpPmr8s8W1PrYMZnlm9yi3rOrjiZ0j/PjNbmI5gz+c38KksLtkCXqP4je/f5aJC07G6fK8Az5qHuRmHbQopkZPspU98TUkjR1sH3gZS0mQ0WJo7jAZVxRX2SS2pXUkxYZuGJQFQlSGoliWxUgqjsPuQJUVPG4bGzreoDLiJ+ILEfEHEEJQHoxQHQ1jaIM8detTZNtTBOZHcTf4sDST/N4UzloPjgon+f0ZJFkmvS1Oeku8FLEayKO4FGS3iqTKpDbGSG+L46xxE1gQxcqbqD4b9ogTR5kT35wwRlyjkCpy2TlLmTOlju17+8jLJmrIgZnSUTwqelxjaGiAYs7i+ONOACVQ0sdjW/365T08sn2YKWVuPvf0PrYP5fjykmruO3/yGMZNIjeyj5BvCwPtWtk5p+d++cfnMQ/J4M+dIl1QXm8/15KijsDsm1Ds3oPyuRfOLKc54mIoo9M2WqAx7OL+CyZzXL1VApz7TiVtzeTZN9fTMmY198b38bvlV7Jz6BV6RzuZXLlwzM+26I5vZmvvk6TNrYwWWonlBgh4nVSEothVG3bVhmtMxOeKOabWNaEZGlXhcrZ07KKoazRU1JDTigjLoqhreBwuKsNlDMRHMIVJXVk1YV8An8uDy+Fk/fpNDE3IUejLkd4aJ9+ZwSpaqF4b/jlhQCK7M4GwwFnjxj87hG9mCHu5C3ejH9mhYI+Wrklxq/hmBLEF7YSWlKP6bQSXlCPZZLwxWFRTy7lHz0HTTaY3VdM1MMqu1n7kokJD5VziyV5Uvw1Xo5f2le1cdsU3sNsV6Pks+E6lJ6NwwZ92UjQFbaN5vrComkcunMrZUyO4bQqmJZAlCXtwKqm2PyMreUuM2Hff9XK+9ZAi2uZUvlJeZ/cn89OxeSoOkdWAj80uJaYPjh7mwLMYbDXcffeDHHZsKS6czI/wxp57mdHQRNDro3u4iw2dT+Nw5Oga3UVDVTnRCCgK1FRMBCGQ5bFd7vHR2tVGxBcgGg6RyKbJFQo0VTcwkhylrqyanuF+soUccxunHQCyj4Hcg14fO7vaeX3rWo6YPg+bUrrV3m39jGzoQ2gC77QgQjNLAYy8ychL/UiqhKclgKPWg5UzsEcd5Luy2EJ2rKyB4lXJtacZfrYHW9hO+JhKJEWi2JfDOWLRMGzidddScdgigs1LeOyOG5jo7uSbNz+OqsggBJmOUXZ2L0dRVaonTaZjxSZiSj8/+PF1/Px754NaAZJClddOS9TF4lof3zuunmqffbw++dEdwzyybYRnPj6dw6rL0ZhKRf2ob7Sv+BXg0XcxeMXPK8oVmzVRtcnYPce/f8VpZUulHpHPUpCaGUi9TrOntPNN00C2pbEpIZqr6+kfHeb1PX/k8hPPp6bqQBMV3TSwTBPDNNBME0tYIARTaieOMzziC46F70xqIhXktSJCWGQKOVbv2sLiKbPHmSxJEgG3j4UtM9nRtY/1e7ZTE6kg7PCT7k9R6M5i6RZq0A5CwlHpIN+RRk8beKcEkJ0y2dYE3qkBzGwpyeCq9yLbZcycQWpDjOjJ1RS6s/Tcs5eZDVVMrizH1TSF+uMvo2H6gVDpupee4PDqBC+uaMUwLSRJYs5RJ9O5ayuLTr6AbCpG9aQpTJl/OE/+6bf88HvfxlXxPzB8K0r519n4ubkl47c7zfXLu3l42zCDmQOonUe3D3NYtRdb+FhUYxWyIjevv9EXnX91euQgBtuEcX75BGcwHq8metRHPwCD85DfAsYwP7vzMZ6KP0Xnqm14XD48TicgSBWyjGaSmKaJGMsHvb3fcsUChmngcbiw2Ww4/47VrcglreJ2OJlUOYHRdIq9fft5ZdMqTpy39GAXQZaZ2dBCIVdkqG+Y/nQ/K59dg29uST+aWR3Va8c7I4SkKmT3JFmy8DBC5QFeeuR1zLyJyFloO3PE9uWRoyrOBg/Rk6oRFhhpHQ82qrw+bHM+wtEfueLdGSCfm3OOa+CZN7exdlsHqt2BZQnsDhcdrZs59RNfxOXxcduXP4Js6Vx3wy/4wVULS7DhyKcQiouGX6ylN1XKjk0vd/PZBVVcMD3KVc938OcdI1x30kRCUy5mZPnvKa/b7+vZzTmQvusgN0lxSOcHyxW7sDUhq873z+DcOmh4GHzH89autzhh6ZGctGgeRTFC3hhBEqBpGuv2bKO5pgGf08OqXZsP4KIcTvxuL4qijDPvfSMGJQmf2000EKImWsH6vdsPeVysf5T7fvQnMsksh5+5GCNWLCUXdEF6+yhmRkdSoNifY9qUJk477wSu/PYVfPaii7jw5NO54rsfZ8lx8xG9OsPP9tB/bwfZ3SmUbpX/+eUTTGxsZGD5H9my/EVM42BMnN2mIAT0DMWZO2UCerFAX9tO5hxzKl+97U84XR5u+sIFfOa8RSyeNZFnX3gRfCeVKji0DlRZYlGtH6cql8p6rjyM7x9Xz4wKD6e2hGgbLdAeLyDbXAhbI4Fy1anapQsO8oOFQBIWM5weCdn9AQrcrBz0fhniD7Nq7SqG1QRCWDy67AUM06RoaEQDIWLpFJqms7d3P+XBCNs79vyrSqKwqzaaqupoKK/BaXfw+ta1WH+F2apprOLj3/wIc4+ZzaSZDbgbfEiyhBgDpg8+1kkg7eKMz56KzWFj7+Y2GmdOZFJTPdUTK2mYWsfR5x7O0tMXUje5lp//5YcERu1k+mN0t7dy1KdupX7SJHqevp5Xf3QBr913E7H+EsLV0vPs3j+A1+lA00vGrcPt5cNf+QG7N67gxs+fz9xjT6ci4uella3s2rGVtWvXQez30HkJWGk+NCNKwbAYyGgHQZHX9qTHEasAkrMFt1dGCDHnINjs2uvC033l6uvVLf4yW8tfcJVNe3+rKwpQ7AR7HRd//dPsDnVy0bGn0zHQy/7BbvrjMZqq67AsQdDtIVcssnX/bg5rnsZxs5fw76B9fV3s7G7j+DmLcTtcY/VIFjvX7WH6oinkMwUGegZZ8co6aiZUEPD7qZ86gXBFiD29+2mqrjtIkrRt68DlcSKEYOfa3Sw6ZQFrX9qAzaEy56hZ7Hmzm5q6Y5k270iG+rrZv3MDuZ4tPPfM08xpqcDrdFBXGaC+OsLHv3UPAB//5s/p2LGR1S88xlmf/jqzjziJtj99kzfW7aarf5SPXfpJHrjnZii2g2s2Gc1kws/XEnapfGVpDTnd4o9bhtg2mOWIej/LPjkbSYLc0FbMvRfQsys5nBgyj1p6bWyXPOYDnRKqUEL5Yi2usr+9g5d3JtnUnxmrw7gEhn6CYdloHdjFBUeehG4YLN+xDptqozZahdfpRjd1tuzfw5S6ScxsmExR1/l3UVN1HacvPIa9fZ30xYbGdfH0RVNKgQavk4lT6rn4ixdg5k1MwyRSGUaSJCZW1rJ+7w56Rg6gORtnTiRaE6WQK3LE2UtxuB20zGti4vQG/GEf88+dhqN8F6teu5WBrs3MXHwCx1z6Pb7zuxdp7UpgWQbHL57K3s4hZjSVYuPbV73Gquce5ahzP87Zn/4GDpebgqaXrGxgzdo1mMINsTug8yK8doXfnNVEX1rjS8+28c2XOtg9kuOKwyp5/pIZvO1AuMtnki/WEKqyBVWnOHncyFJVzg1EbWpSm/R3sfDXvryfxrCLP5zXApFPgmRn2aplJNxZVu/aSqaQRZJk4pkUTruTpdPm8thbLzKjoRm/24sQFoOJEToGephY+W8pakeWJGZPnIJm6MQzKRw2O+5DGG8nXHjMu8T9osmzGBgdZuO+HYS8ARoqarA7bDTOnIihG1x92nc4/sJjWHr6wgOx9AkhwhNCaMUMm9fdDpoTyfIx97jzUXqWYZoW+aLG9n19JRTMm89T1dDM1AVHjUkYk+MWTualFTsA6O5oY8WqVRw169SSGgQunFnGcZOCbB3IosoSc6o8BJ0qsZzOsv1JmsIuWqIuhL2BgLfd1rdPPg+4VR4rIWlyeCQkZwmi+nbHmXeFEk3Bxr4Miyf4SoVhicfBvYhHX3yUQG2QkdQoZy06jqNmLGAgPkLI6yOTzzG5diLDyVF2dO2lJzaIJcQHNqj+Uf0c8voZiA+zqa0Vw3x/OKjKcBnzmqYT9PpYv3cH6/fuKLlylmDRKfN56s5nSY2FHgGSsRQ3f+l27v/Zn5hyRCNTjqth8gl+mo9UKBgmfq+Tc46bQ9Bfiq07XG6+9+DrbF72AoZWJDU6wnPLtpPLl3RssZDn4UcfLxlb+S2Q31p6kFwqVT47Xcki17zYwfRfbqDsutWcfv8OHtw6NKaHm3B6ZISgGUBd81NfxOZEKuYEzrJSMuLWVX38dFk3cyo9HFbj5Yi6AEdPDNCVKJLTLZZO8IOZBm0/CI09Q22cft7RFLQie3s7eX3rGlqqG8gUcvTHhphW10Tf6AhCwLGzFrG5vZXaaAX/KZpUOQHN0D/wQxXyBljQEqCga8RSCSpDUT76tQvo7xigtvFAKvKRW56g2J2idUsXLzS+wikfPwGACc017BprBBNP5ZjeWM2KTfuIVgV4/ParEMLgkVu/T3ntRPw+F7pZMsI8gRA7duws7d70K+BeDK5Z1N+4lr6xvmE+hzKe0VtU6xuH3TrC89BGLWx2SXn95mBQtSTHTG9AteXzXjzRWQDMq/Zy/rQIa3rS3Laqj9tW9Y3jd30Ohenlbih4oe4PaKab/tQAe3o6qI6UM7VuEoOJGIunzOKtHRvY1L6LVD5LXsvTUlOPx+kinc+RymcJenz/MSbb/0ZR+N8jp81O5TvqpBpnTcLmOHC+8pooc/01OJx2ms8/OGUpxhRkedhH90ApAxSI+jnxo7MonxDlmbtf4P7rfs3KB65hf+8IrX15Lrjyuzx7x3Vopgd740ugl9b/60fU4nMoLKr1MbXMfcgeYq7oLHI9HtyBolrolWbKsmxO8QQkv6aHsHtLu+qU5hD3nj+ZXV+ez8i3FvPMxdP5zjF1zKvyctykIIoMdF0OI7ezbds2DL9AN03e2rGRF9YvZ3vnHnpGBhlKjGIJk41trQzFY3QO9rJhXymqtLOrjf+LtHvjXta/snH8/3s27iMcl7jy4g/z1PKV7Fy7669xhCVXLJaif7hUjNC6djffPPu7/Pm2JzntEydRUVfGzfe/wqadXcw/fjIO50aSyWG2bN0CQzfC/g8BFnOqvAxmdOIFA906dPmO3V+NZoTwBlSfQGpWVYc83eFWlKIUPaSBFXHbOH1ymNMnh0kVTbKaWTqu4TGwVbD1lSf4yFlnsqlzBzWRCrLFPBMra9F0nfOWnkj/6DDNNfUs37GBxVPnYBgG/fERPE4nfaNDBNw+4pkUmvFuHLPT7qA6XP5XdoCBKisHxZ7/VdQ93E/UHxpPcByK3njsLTx+N5ZlIcsyD9/6OFHh4t4nn2XXznZ2XXk7n/3p5Rx+ZinZIsbUQn11hJqKIPt7Y2NhXIun736BcGWYs09dSJkQPKFtomFqPQtPOoxHb3uCN5a/wYIvfgH8ZwAyWc3k26+UQBsOVWZBjZejGgIcURfg8Hr/WGNUCSFHcbg7bTY7M2RJkqY43HKp0chfp/EswYa+DNcv7+HEP2yj7GereHFfvITM77oMzBRDo4NUlZczc+IUptU3saBlJosnz8Jht5Mt5vF7vKRymVJ8GfC63FRHyoj6w1QEInicLiL+IFXh8oP+Am7/WCrR+KvUosmOrn3sHzxQKjuSitM+0H3IP814/y7ZhLIq7KqNnZ372Ny+k7daN7zrmMWnLmDHml385LIbSQwnGe4ZYeWmbfzsjvvGj0kMJ99p0o+/nDqpVKYqyRLf/v3VqHaVB298lOGuYY6c14Qiy2STWe763n0MdA6xc/eOUmB38EeQ28Dpk8P0fmMRpzSH8NoVNFPwixW9nHb/dsI/XTUOAsAWxelWAGmaaglRZXdISFYpmJ8oGPx+4yCvtCVYtj853pwz4rZxxWGVHFHvB1sFuBeA4idv5KlxR5le1zR+Ix0DPQTcXhoqag4EvawSg1VFJeA+WPe67O8uXDvUe2+/P6P+YIB91B8i6g+9LyZueH0zrz+6nIu+/iGqJ1a+6/ORVJym2gbyxeIhd/LL97/Kzd/6Mo+9+Drt92/kD9+7llDAxzU33s6qzaVQqWpX3xk8H39ZV1nqxlPbWM2U+S34Qz7Ka6M898pGvKqMbpj86Rd/pqw2ypLTFtLb1weSrQTIG8NOV/vszKny0hEvsPJTs3lk+whXPd/OQEajI15CkUhKCJtTAkmqUrHwKzYJCqUFXdOT5qrn2wm5VD40I8rhdX7u3jBItd/O7WeOMTGfLYG2lRBF4+BRBZlCDlmWqS8/YGUWdI1JlRPwjEWW/jdIWILbv/E7hrqHqW2uwR86tIFXMWZM2dyHbg9R1VjFm9u2csnFZ7F97z5efelpnlq1kv1DB7rUevwHoEbSWKvEJ1/bjGOM8bIiI4SgmC/y2es+ye9/cD8bWjux21UcPhfHfegoevb1MjI0DGoZhD9RGi4yjkm3sz9RpPHmdXQmikwKObnj7GYunTOmziQ3qiohLBFQJXms0YVUYnDQqVLptTOQ0dgzkueExiC6ZVHmfocVmngE0s9D8Hx2D+yjb+MwsixRGS5DWIJJVQcCGLlinvaBHlpqGv5hvZkrFg4ZqPggtHXlDhafuoD5x8/9p86z6JT5KIqCa3od80+YgFbQWP61GPuHDkzcKZ/wjvLVMR1cXR7kpvteKblMQwn2bm4jm8rhC3qpqorwhQuP4SvXP0LvaBq9qKPabBQK8ZKI7vs6+E+Bqp/xqzV9XLesm6Jh4bEr3H/BZC6cWTbel7MkQvwIIZAkyS5LCFkIQCkt4KJaH/u/toC7z20hWSy1Qlrfm6ErWWTw7WB35Xdg0guAxN6BDkzLZCSdIF8ssLevkz+88iSmaVLQNZLZDDPqm/8hNyVXzDMYH6EvNsRwapSirlHU/7GenW1b2pk4vf6fD4XOmjR+HkmScLgcGO6D65EjleF37OASg6c3VjN7ci0OFVx6mo033kwk6sXutGMhiCWytPcMUz2xktlHzWT7qlaKBa1k0E56Gir+Zyz/O0LEbePe8yez9QvzuHh2+cHMBRRHCNMCJCHJIEmWIcZnCr1toV0+r4KtX5jHC5fO4KSmEM/vHaXp5rFqxZ4vQs/nxkWf1+nGY3fSPdJPXitw2vwjkWWZdD5LVbjsH15M07II+0M0VddR5g/jsNlx2Oz/0LksyyIYDfzLRb9lWeyNe6F5KdhKKmjLWwfSlvJYo7NEKkeiby9fP17m04fLDOVVLvpWCbU6IeBFUeRSWnFvLz+4+Do+/OVzKRbHHub+a6H/2wDcfW4zW74wj0vmlL9nL23Z5kaYJf6qSEimKVBc4UNCdE5uCnFyU4htg1nu3TQ0lsW+AKw8QgiQBUVTZ07jVAbiwxiWSTqfoz8xgq5rpG12ZEnG4/zg+tfn8iAsQeva3ezfuBdrOIHdEuiA4naiBNzYg148YR/eoBdv0IPdWXoAFFXB6T4g1hWbSnwoQbQ68i9lcPu2/RQGekHLgi8Mlkli6ACqUlZLO3j99g6ObZHYMSCYXikRmHMYC08qtavIDCW4d3vJ/dGKOo2zJrLgxHk8euuTJXfMexzIvvFcwCttCXx2BZsiEXSqOFQZt01mXrWX60+aiKR6sCwBEu9uNDWaNxjJ6rRESwzJ6xYum8xgRmdPbKwxt1Uo/QGWBX0jgwzFY8xoaMYhQb5QJJfP0THYS0OFSf07uth8IL355lb23vcK0/0uZjhstA0nmVoRIqPpJIcSNJcFaN/WgSrLIEusHoizvnuYnGbQVObHMAUum4IlBO2xFOnRNJdce2i0SiqfJZ3LoBsGXpcHv8uN/T2khSVKYDeAdWt7IVgBpg5OH/TvxuU78DBLaun3735yJSMjFjkNagISaQ4Yp+2xJFeetZhcQWPl5jZO+MgxmIaJJEklu0WNluqXgHOmRpgUcpI3LAq6RbJosqorRVeyiGkdAvCPQCiKhKmVfKhfre7j4e3D7LjyMD7/9D72xQq89IkZJAoGz+4eLfW2Sr8IZgopdCGqrFBXUYWm6SSzaRx2O1WRMnZ27mNGQzPVkX8s5vynX/yZnU+v4pwZE9k1xszKgBu3XWXvSJK6kJesZqDKMlv6YuwZTjKUyTO3OorfqaLIMk67imVZmBaUeV3sfXUTq+c2sfjUd7eMUGWZymAURVGwLIv2gR6i/iBBr59kNs1gYgSP041dsaGbOkFvALfDyfZBL0gxkE3o2QG+6EHul6wq5PIanX0xhICQu9QfrJAtMNIX496fPMhhFSEaJ5SxbW8vqk1l3rGz0TUDu91eYnDsrhKTvcdw0axyLipFlNk2mOVHb3TRn9H4+JxyfnBcyTYQRhZZlkAgVBBCViXMQnzcik6M9WUOOlXiBX08Dm2J0uSwYM1NYMbH/FoFGYWAx0V5MEzHYA/bk3uYWtf0DzP3tUfe5Lk/vESZ14lmGCxtqMQSAoEgkddI5DUqfRY9iSwum8qbbf3kdYOzZjTgsalopolLVfE4bby5r4+cbhB02fE6bNzzw/uZMr+FYFlgHMSnyMo4OEAzNOyqnabqugMlIh4fgfeImw8NZUB1gOqF5BrwRlDUA0kNyWajqBkEfG5UK8cJkyVWtAvy5QXeePwtJs2cSIVlEk/lSGcL1DRV4/a5ScZS4+qGuntAPoAx3zmc43uvdfJ4a4zzpkXYceVhNEcOSA1LzyHJICRhyQLJkiTALJV8BF0qiUKJwQGnSiJvjjP77UAIAz+EttMBgdvuZiAxQraYZTgZZySZYO6kqTS8ww+Op5P0jw6zvXNvSW//Dcqmcmx44BWCLgfDmQKPbulga3+MkWwBzbDIaTpLGyrQDJP6kJe/bN/PnJoICyaUsXMwwf7RNG67yki+wKbeESaXB6kP+Yi4nQymc9hNixfuf4WCVqQ/PsJIKk48U6oXimeSDCViZAq592cEmhZFU4HYfprcg3gmTARJEB86EMlSVJlQwE1jbRlRj8RruwVbegX5bIHzP38WobIgDreT3ftLpTXRMQtcK2g4HQ7AgraTYPAGAK58po2Zv9rIis4U95zbwnePqUMZmxeVG5t9YRZHUVRASEIViNIWHetpEXQq5HSL5/fE2RfLM5TVuH55D22jpQcgkTchfGmp6TYSDtVB2Otn2oQm7KqNeY1TUZQDT/Devk5kWcHjcOJ2uEpVCDY7frf3kIv26sNvoGU1Im4HUY+TfSNJ7l+/ly8fNROvw0ZbLEXY7SRZ1NBMi45YCpddRdNNDMtCM02GMgXaYylMS+C2qVhCkCzoBF1OJkYCrH1pAx/+6nlEfEHsqnpQejDkff+Wdno0jSibCLuXc8Kpi9i0p8iaeAND3WsxDZOh3hG6O/qRZk/i6AUtPPhEJ0NjYBhTNxjuG+Gw4+bQ/+dltA8nxvBapXjE6GAcp8tVgs1FvwSuklx+YucIpiXoS2tc+tjug67n8wurSsEoI42EhBBCU5FIGYYo4avesVNPu/+Aqf/NlzrGP8sbY8mG5BPgWcLkqiYWz54zbnT8NTVX1x/Sv30vWvH0avqG4khA0OVgbk2E9tE0r+zp4czp9cyfUMbuoQSZok59yMeRjVXYFZmOkTSzqiPsG07iUGSmlAfZPZRgVccASxoqKSKxbzjOrOoIw70jJIeThMqD/5AKSeWyeBzOUtJfcYEryPT5jVTWjrLmgTR9HQO0betACEGgKsLvHl/OWUfP5sFn1wCp8d1fXltyITt1E5fDPhYkLIwjQSvKy0u9LwvbwVtCn7x46UwkIG9YpIoGuilIFkqFgU2RMa9B5DB0gSRLCVUWcr+eFzOEURIrMys8PPbRqQSd6nijrrf/PcChnaVO6FaO+kjdezL3vcj9VyFLrajzxK2Po21up84SGF4X9WEvdUEve4aT2CSZhrCPmoCHVEGjO5FlKJ3HoSqc0FLDn7d0YAiThXXlWJaFXZEJuZ30p3IUTQvDFDSXB7AQtMVSVPhc7NvSzoIT393vcjgRI+gLjFdCvFNPv02DiWFsio22XYOQ8VFlixEsC5RyxFIfO7b2c9mkSjx+D5PnNfPaw2/y+R//kaF3oEBM4x0DuIoaF586n1sfeHUcKdKzr4+a6trSTOP0KxA4h/5iJUfdtYXvHlvHFxdVv6cfLIw4WsECIQZkgbW7mLdKJxozps6bFuW4SUHmVXuZGHLy0LZhjrl7K1c8uZdYTgf3Iqi5ESQ7NeU1ZBLZf9iPzGXy3HTFzex+YT0b2vrRLYuRbIGOWJq8btAQ9hL1utBNC80w6U3m6E9lOWXqBAbTeXoTWRbWlZMqGPzslY0MpfME3A72xVIokkyV381wPkfbSIpynwvNtBhM59m24t0Y6u6RAVwOJ6Zpkink0MaiZpl8lnzhgNQJegPUlVezeocG+zcydW79eAxadbvJ2iL0tQ8gSRLCEkyYXIvwOPnQmN/7TgYLS5DJ5EllCpimxXD38BiDe5kxfWbJep74GHiWYgmYGHLylefaWXLnlnHY7LvTgMMU8xYgWmWjaO0o5kwTc4S3e1BZAv7n1U6e2hVjdXeazz+9j5GczlO7YnzqL3tLir/zYhj+JbNnzGGwc+gfc4VufJRn736BRQ6Vpoif+rAXp6owpyaCXVHoTmSxKwpFw6ArnmEwkyen6QRdDn67spWox4nHbiPkKlXc220qkiyzZzBJ+0iKNV2D9Kdy1Pq9lPucbO6NsbCuDI/dxoyhBM/9/gWGug+MEpwQrcTr8uC0O/A6D/jBAY8fxzti4WX+EMIStOXKoH0tsw4/UIZTZR+F+rlsfWs7hmZw+yd/SOtNN3BCuJftWw8ABawxp3XdKxtJJ7M88MxqLCHIZfLEhxJ07+rl2COPhaEboP0sQFDjt7P2s3MJOlXW9aZZcudmLn9iz4EQcumRQbJiFHPousZ21bKUXdmkSIZr4mEtPYDdV8Uj24f5yZtd3HNuy3gdzEufmMnGvgxn/XEH/WmDqvo/gm0C08qD3PN0BmZ/MOYmYyl2b9qHp6CjSRKb+mJohklLmR9VltBNi3NnTuT6VzdjCoFhWUyrDFHtd9MRT9EYDTCaK7KqY4isYbCovpyO0Qzru4dRZIni2A5x+9zUffRYtr+wjmlloZIkME1+t3onheXbefZ3z3Pb8ptRFPnvIjXfSZuWt6LLQaRilqkLWsbfP2aGzP3pWravWs7iUxfQ19ZLqEoirwnK3tE9yjRM9u/sYtnTK+jb2kksnjlgaD7yJi6Pi2nTpoH5GfCfPg7GGMhoJAoGfzivhW2DOX61po/HW2P85IR6vrCommKqF7saZyRhpLDEHlk4tK2ZhGE4XRkKIyX03sa+DPOrfXxibsV4PrjSa2dpnR8hSoMd0fth/3kopPEq3g+8e71BL4NdQ6i5Apv6Ywgh8DntiDHjqirgxmlTWFBXxoSgZwzNYaGZFqm8QcRjZ0XHADnDYGZlCM2w8DtUDMui4h2RpFw6x/7WLi6/6bNM+fSp5EM+dNOiMFZlUOG007mz6wNde0drJ4+/HIM9K4lUhXH7DqQHp08JgqzSsaOTQq5IdxxeaBU8u0Pwxl7xDhfL5M0nVtClDRHXCwdVY/zljmdpbGpEIQU9Vx4kWZfvL9lKXckiHrvM4lofyYLBn3eUVGxhZAsud5Zs0jLzDrFdXXpVanT9LVHL4ZZIxdbjn3gyZR4bw1kdS5TmHblsMrIEd67rL4khn72Up3QdBrKTsDeCaZgHOfh6UWfTm1vRi/o4fOWgjIcic+m3L+KJHz+IKkmEfU6qAx46RtO0jaSRZIk7Vu3ksJooW/tihN0OQm4HWc1gSnmAt9oHCLnshD1Ont/ZRUPEx2C6ZIGO5oo0z2mka3cPxXyR1/+8jE1vbuGWl69nyWkLySSyxIcTCEtwzw/vZ9Vza5k0o+H9W9EiR3cuiBxby6LTDm6LUdlQgV3biRaoItY/impXMbR3w3XzmQLLX1uNLeJAUmUUj4owrFKHPQGzZ84GFFBDINlIFgzKrluNbpaY/d1XO1FkiYagg1ObQ1w8lgsuxjbid8sYRWEde1UioY7hwvYVsqJSjPU0/vCMMq59eT9nPrCDjX0ZZpSXdtBD24a5dG7FWNRkfqmTXeZNjll6HE/teJTG2RPpbesnWBZg61vbOezYOciqzEDnIA6Xg1B5EMuy6G8foKapmgUnHsYjP3iAsNtBuqCzKj7IMY1VZAIeCrpObdDHC7u60S1BU5mP/lSOfcNJol4XDWEfLlUlVdRpivppigYo6DFyms6ck+fzmZ9chqEZ7Nm0j60rd7D6uXW8+dhyjvvw0XiDHrxjUuHrv/ky37/opyw+dQGNMyf+bdCAEGQKORSvyhdPK6AdcziyIjM6GCdcERpPctSY++g49lO0b191EHNVGQJuSOXB5wBpaqCU0RFgFQ38h0VJbx7F6C7w8Y9eUsJEhy8D9yL6hnNcMqe09i0RF1PKXDSGXQfNXgQQxXYKwkJS2A1jFf6fPN4dcnmk40BWvJMuJehUmV3p4bX2BI1hJ7ed3kiF186pLWEunVMxXirBwA9Aa6Oy5VM89fTT2PwKrWt2Yugm846dzc8/fxt7N7dRPqGc5EiSPZv2ER9Kct2nbuasT52GLMusfmMLe9v7SRQ0GkI+8rqJ26agKiq7hhL0p3J4nSozKiLEcgW29Y+iyBJ2WcbtsNMU8VMd8LBq/zAD6RxT5rdw5Y2fQVZkZEWmrDbKjCXTmL5kKr+55i6Ge0eI1kQJREqYL7vDRrQqwq++dgezj5w5/v5Bbpyu0RcfJp5J0zsyQHW0nGRvgr/87jm2LNtWwlstmEzrml0YhkF1RGHNS5sYWL8KvahREywVi9VFoC4k4XFAU1QiJ2REtbcElDMtbMFSkKPGW8FPfvBTpP5rIL8BghdQ5rFx1pQIR9T7mVrmpsxjO4SbJMjuu4VCKqYnhoxbf/dSfo0C8OnjnSlLcGG4UvNYruOxecqZUubm8sMquWhW+Xh7wqBT5SBbI3AOOCYjKR7Wr9/KjtZtFPMaQkC0OsyrD7/J6PZONjy/jrxp0jCtntcefZPetn7O/dyZSJJEeW0Zq55dgxACU1iosoQsy1QHXLSNpMgUdZqiAbb0jdAeK7kFjVE/QbcDUwhaB+Msa+8no+lMXzSFq371xQMx3HdeasTP5MOaWfH0Gl584FVOuPAYVFvJ162aWMnOdbt566lV1DZVE62KHBTUKBgauq4T9Ydw2O1EvUFqm2qonljJpje3smP1Top5jRdffIM3Vq9mV1sb2Q1bkHWNLxwlU+mDzlHIaTCcgVgW9gxDNqYhuVWsvIniUFG9KrE3BjjzrDM554zTwLMQQhceBNf5my7n4BbU9N0M7s/Hshm+c88ruZgCcOfL+ZHON11fa5imeOMxH57q99nLWORg79GlRWo4jx9+58fMO24OLfOa+P5FPyPVG0MgSBU0tL5Rdr+xhcxAnIjHSUozKJ9QRt3kWmRFpnXNLqJeJ9MqwrzZ1kfrQJzMWOuh45priOeLJMZKOzTTwmdXSeSLFHSTjGZw5hWncsUPLsHueG/kSKQqzIIT57HsyZU0z24kUnUgB94yt4mn7nqeupYJB+ljh82OMgbTHc2kKA+EsY2FN8tqo8xcMo2efX289dQq0gNpJLuMWuHA0+yHjhT7RwXLu2SKNhVR7iE9pDFm32FZUOzNURzIowYdeCcHMPbk+f3vfk8Z90Pv16HsiyC9v4qM+M47CXk30L1LSy++euRbMFYfLEkIWWFbPmMh8rvevzkpe2HCbyB8Mc3NLTRPbqZ8QhmRyjD/c983MMMqUa8LSYKeeBqnTaU7nqYjlmLqghYMzWDTG1uomlhJIOqnJ5El4nEyIXjAKq8OeNBNk87RA27E5QsnI5Dw2W3ossS37vkaH/rSOQcZee9FHr+bXzz3E1rmNR30fllNlBue+iHHf+Tod8cNTJNkLoOwLHqGB9EMHSEErV1tVDdWccUPLmHqgskIwyo1RJMo9a5EoU84KDu1lopz6oieUoN3ehDpEBGozI44fX9sY+rMKUybNr0Eqqj+yfvevQCisIdc2kKS2DxuzI4v2jFuj90tn6goluqa8LGDRq//TVI8pWGR9gbiuRDf+cz3aJnXxJ9/9xT5kEnKJdB1E5EzqfR7GEyXMjXLnlzJ5je3MWFyLZMPa2aoe5iefX0MpfNU+FxMjPjoS+bI6wbbB+K8MwfVGc+Q0XTwubnk+iuY/FfM+nv0XuA/l8d5SMBf11AfLocD07KIZ5JkiznKAmF6Y4PsH+xl8qRJHHn2Uvra++ne1YMwBd4pATyNfuwVLkZe7EVxq6h+G4F5EYy0BoYotVNKH8BtS5bEl7/yZQ6fkYeB70D510vNw98PdEjPUdh/K9n4aCExaPz8rpfzmw5i8CXHyZ1mQb6irqXoSSXCuMrfL/pQAq0DfMeyYOGp/OmxB3nmDy8wmkvinRrAyOg4azzYK10MJrIY77ihbCrH5je30rOvj8NPX8T6VzZyypQJHDmpiv2jaTrjmXdV6wOkizrRphq+8KsvUNtU82+D2uqmycsb36I8GCbg8aPpOm6ni/7YEIlMiogviM/txet0I8syC06YR3w4wd4V+yh0Z/FOD+KdEsAWchB7pQ/FqeBq8GIkdewRB+56H4rfhjZcBEvQMqOZ++95AFkkSmvqP62Ei34fNNp6DwH7C+zfXohLlvalO1/Scgcx+PevarlPneg+P1Kj1uZSJt6G9zm9RbKDZwkM/ADZUc9oxsYbr7xR8uckiXxHBnuZE1mVCS4uQ/HakFUJM2cgxny64Z4RNi/fSlPYx6zqMH/cuI/Gqgi7x4q1/ppmHTGdb//+67i9/16ctSLL+NwenKqdsDdAyBcg6PFRX15NZShKwOPDabNjCAuboiJJEjMWT6VnXx99e/rQBgt4JgewBeykt4xSHCiUpqYN5sfi0CA0i0JvDkmSuPJLV3LswrLSbIvq60vTad6vb77rJuxSF8Pd+qb5VyXGO8/KB7sD1s1DXVrKZm1Hz36AUXmWVpoLZI7yza99i5ZZzZh5g9SmGM4JHhSHDBLIDgVJAt+sMNETa3A3+vBOC44luHUyHgd7PQ5OOH0RM794Nl++9fMcfkYpSKLaVBadMh+v18XU+ZMx9JJ/uXXFDlKjKZKxFPF3gN3elUjY2/sPJUWqw+VUhssOynG/jcvKFfMUDR1N14mnSxEmu9POV2/7PCd+9Fi04QJ997dhFU2cE7zIToW+B9ow0jqOChdWziDfmQEhmDRlIt+8+lugtUHmjfHC7/dDWqYfu7STwW49rWvWLQc9pO/8z8WHV7RZeuHKidOEZ3SQg1oZ/m1jyw3hj0PqRRTVTcHw8/rrr2OZFtpQAVvUiWyTsYUcJNYM458dxhYq9YQ0Ejr+uRFybSlS8Sz7O4fY3T7AG4+9RcvcRjp2dCLLMt/83VdRN7RxtjdAXW+C1/70Oh3DCTTTRJJlunb1oNgUAlE/iIP17K4VrWRv/AtbNu2j5aR59OzrJZfO432HMbd52TbWvLCexpkT35ex1j3STyKTxrIEbQPdhLwB3M4D+nL2kTNxuOxsfX072Z1J9FgBK2+CKHX3kVWZ7J4k+mgR1a5y7bXXcsS8EBhDUHPTB9q9sS03EfatpmNLITlij33uPVsZ3vtGwvj0Ke6FvrAyXcsbeCd+lPc93lDo0PNpUEIsPf4qnn/lOXo6e5HtMpIqUejJIQyB6rPhnuglty9NviODo9xJpjWBkdTxzwnjmxtGz2too0X2t3bRt3+As644jRXPrsa5d4D+XB5ZgvmhAJNjOdKb99O2uY2MKtMwaxIrn1nD7o17qWmsxtANhCXY8b0/0p3IkB1O4J5ZTyFbRCvoFAsavlApJn7fT/9E+/Jt7Fq/lxlHzjykL/3XkN79Q30osoyqqpiWiSzJGJY5DvJvmj0Jh8vOtrdaS5bzWMmnVTBxVLmxNAvVZ2PuzFnc9Zu7kUbvhJFfQ/Sz73/dEaR334hV7Cc+aDxz9JdzD7/nDgb4xLGuTr1gnVdVl3ZnslU4I9Pfpy5WIHJZ6V+ti3nzz+LRJx9Fswz0WBEsKPblcE/yYiR0EmtHKPRm0QbyaCMFFJdK6PBy9LiG4rZh89koGjp6UqO/MEL3zh5GsgW2GTnWpBOs6BpmOF8K0i/yeJkSLzD00ibyu3sZ3NXD1n09eAMeNj+0nOM0eKyjhyHDoL2jn4nTGpBtChte3UTznEY8QS+ZRBZR1Ni7s4sn73q+hEaZ21RCJ76HJV4WiNAfH8btdOO02ZFlGcM0kCWZTCGPawz1sbW1FSSptIPfNuBiBfS4htfh4eEHH6E6OACOaVD+5Q+0e+O7H8bLI3TvzMcKafH5u17J9f1NBt/9Sr73suOcF0ar5arMSAzfpAs/gP+hQu9VkFtF1dQv09a1j40rNyJMC6FZCN3CUe6i2J9H8bxjfA3gnxPGKpoobhUEOKpd5NoyyA4F52Qfmd1JMkUdQzcRuiCvG/QHoTWfYa2aZ9PeIWRJYnE0zJJQkMaURmz5DhpTRXx2G0P5Iq2jSXLDSTxlAZpmTUS1qQzsH6R8QpQp81uYftQs9mztoEZA99YOlr28gcmHNeMLet8TH20YBuXBEKZpkRxMUltdhSzJCF3QtbuH7StbaX1zJ4pTQbbLWMXS/QpTIMkSF338o3z2is+VynELW0ojdz5I2nXbd3GqPfS3a60Lrh75wSF8nHfT6uujxwYr5EcnTPFHjIrb8Dec+gHqTRIlSG1+K4bnFJYcfTjrVx6os7WF7DgqXehxDW2kgDAEjkoXxYE81R9rJL8/Q2rLKK46D5nWBO5GH57JAezlTjJbR8l1ZjHTOoq7NG1MditYeQs9XsRZ4wYhaEwqKJLEnEiIlKazP5PFFIJto0layoPEsgWKisy8cJB8eYCquZOIVkdwOO3c+9MHqXc5iXhLAL1X23o5/lOncfyFx7yn/9zW30U6lyWzP0XYF0QraPTs66V1zS4Gu4eJjcYJHBYl35Ee7zAPcNiSeax6cyW2wltgrwMlWMrSvV/mtj+DbeQqunem4qNDxXOXfiPx5vtiMMCGmyI7ph3hmRbPLKLq2Ec+mOkZvx/6vwfNy+jo0Tji2CPo6+x/x0aXx9vi5zsyqH4bZs6k4avTSCwfxMjqOOu8DD/bg39eBHu5E1e9l/TWUVR/qVm3u8mPNlwgsyOBFiuS78zgqHBS6ClZn7aIA1tRUMzq+F2lVGOmqJMt6mQ1nXKPixOqyqn1uEhpBj6biktVGMwX2JlIMZgr0J3LE/Y6CbmdUF/OFT+8dDxrBKU6aIfNjtNux+1w4bDZx2E6y/6yEpvDxt0/uh9HkxdJlKaqWQWDXHuGqvpKlr26nKYaA9pPheobIfiBBovS//oFhHzr2LE82zr/qtghdel7moufPNbZqemcEilLuopiMo5A4/v/Zed0CJwOhV2EQiHC5U28sewNivni27IN1W/HXuZEGALfjBCFnhyKWyXflQEhoQ2XdFTk2KrSKNe0jjZcLPVuDjsw0gbCsJBkieDicjzNfmRVxswY48dbCtgqXWRiebwOO5mIAgWLuoCXjKazPZ1miz3P/lyeN0aGaHF5cakKC8sizC+LcGx1OQXNYMPgCL2dQ2hrd7Pplc1odoWqiVWE/QF87lIfanXMDwbYsXon+XSefVvaGdRGEYYFkkDx2tAG8jhVBzfeeCPHL51YwsKFPgzeY0F6/9N+U50v4MzfR9+eTCKXsD511yv5tg/E4N+9XNi3/3XXZZV1UjTZ24Z34oeR3mfQG0kuJao7zgd05h5+FfH0KOvWrR8Hm5U6pNtxlLswkhracKE0UXuiD6RSY1BhCgLzoph5g1x7Gtkm451amrEw+lofklLqvO5p8mGPOjGSGpmdSVS/DVvIjrPCVXLFkhrFiIplWigBFVuZi6xNoBUNhE1itCeNUTDZ7ijw1r4BOtJZtscT5AyTImBzKjhtKh0jKY6dUEa4J8ZrD71BW+8Iw/2jRKsjByU5gmUBHrjlEfYM7AcZZKcCJmR2JJB1iS9c+TmuueqbpQKC2J1Q+f0PxFxhGcQ3fhW3s4+ePcWOhV8fveo9gzXv9cEPfgCXHu1ak0ta59c1p1yj/Rqe6iMOLSrSGpc8tpuzp0SwjSegJQieB44pEL+XE8/4Jjv37Wbnjp3jOshI6ahjo9LfDja7JvnI7UnhmRrA1eCj2J/DTOql4VQ2eWyX6oy+MUC+M4t/TpjUljhGWiezO4UkS7gbfbgavGixIpntCSRFRnEqFLpzSDaF0X0J9LSGb0YII2NgpErhU9mp4Gn2M9BdEtE7Eyl6/Rb9fWmiXhf9ySzrOwdZ2zlA1GVnkmbwh/tfxulz0zK3iUK2gGpXue9nD9FR7KfQk8PKmmjDJRUiSzIfu/Qifn3zzaXJ56GPQvAjJd37duxbt/jwwzs5ZmJgrGX/u2l4w3VE3C+xd0N2tJDmw3e/mu/9wAwGuOfVfN/lx7sOc/nkFqH3KbboKSgO/zusSMZ7aT2wZYjRvMHvNgxw4cyyA9mm7HIY/AkEP8x5513Gpu0b2be7VMLiqHSheFW0wQOVdlbWxMjoIMBV66E4kEeSJWwRJ4pXxUzoDD/fU+rxDKg+G7m2NIG5YQr704SOrBzLrAj00SKKW8FR4cJIl7q1u+u8IKDslFryPSU3TXYoqG6V4OIy7BEHtogTT0sA9yQflimQ7BJJYWBmStEzwxJ0jqZZt38QwxLUNtUQiPhJjqSwO+w8cP1DFItaqTpQkUqDtYoWp55zCg/f/wiStrdUX+1eAu4DkJ9zHmxlZVeKB7YMkdUsom4b1X7HQTl4PduPtv8HFNNxIzZgPrXo67Hb/k6m4G/Typv8YYds3zX7aE/ZUPI4qo6+50AEJacz6aZ1pIrmQd957KNTOW/aO7r2WDkYvQ+sFEb4Ks7/6Hk8++RzJRyXS8HMm4cOkDlkyk6bQOzVvpKe7s1haRbaUB7f7DCSBIpXBUVGtskUB3IYCQ3FawMLVI9KcSiPkS354q4GL0bawFXvIbcnhb3CieJWcdZ58U4LHJTGE5YACwq9WbI7kkhuhezOBPZyF/pIAT1xAKp6xuWnMOfomQgBA/sHefAPj2MLO9DjGragndzOFKecdiJPPPwX1NFbSqN2vceBegBY8NiOES54aOdB9+93KHR8bSHhdxQd9L12CeXRZWx9LTtk5IvTFl2bjv3NIOPfY/DSq1KjpiG+37WnmPQ5VpHYcyBQEnHbeOyj03DbDpzm8nkVKJLEmneCsmU3mDEwhlEVkycf+QufuOJSHE77ezIXwCpamFkdW8hBpjVBvjNDsT+HPepEaBbIEmbORBQsrLxJoTOLkTKwR53osQJG0UTx2sZTcnqsiOpTybQmcNa6cVS6iZ5cg29GEMwDWau3I2vZPUlc9V5CR1Vgj5TCrYpHxTM1gG96kPAxVZSdWos74sY0SmMI9m1tJ9+ZKQHoCgbFnWk+fOEFPPXnZ1BVCQpbobj3IOau6UmjyhKXzztQjem2yTx+0bSDmJvY/TAB9zq6dxbSlsV3/x5z3xeDARZkYr8d7dM6hZEVWvfNFBPtByCeO2PkdAu7IvHSJ2Zw97ktXP1CB79Y0XPwSSq+DVU/gz1LkYZv4q7f3M2XvvYlvAHPe4sXm0xmVxKraB60Y4qD+VK391lhhCnId2WwdAvP5ACyo7SbJVVGFEz0uDY+tMpI6+T3Z7AKJt4ZIbShPMm1JeB7ZncSPV6y8s2cgeyUSW+JU+jKllRDVkd2Ksh2CSQJZ50XyS5h6RahcACn28Hm5dtYvXwDgflRsruSuAJuvnTVlfzx9w8iDf0M2k6Guvug4tqD7vPGt3r4+osd3H1uCy9eOgO7IpHTLf6y8wD/tGQnet8vscyMNdpn7Jt/1cid7ysj9n4O+sEbiMuPcz2THDIvbpha9Azv3Yqv4TwkWeH4SUFSmsltp5fmGaqyxEdnlfGh6VHsfw0ml+QSxtezFLJvceJJl9DYPINV61eTTry7DMNV58HMGJhZA3vEgeJSMXMGtogD2a7gnuSl2Jun0JfD3eBFG8qjjRRL4nG0iOxUKPbnMNIl3emq91J5fj3CEFj5knFlCzpw1nowkjrprfHSaNmMQXLtCKpPJd+ZwVnjKamSjIGVMxECHBVOjFENS7Noqq5j7rGzefb3LxHPJdGGC9RUVvHz713P1V+8DDJvgmNiade6F77rPk9vCXPJnAo8doVav4Mzp0Rw2mR+fvJEVFlCWAaDb11GNLqXXSvzQwXTPKHu8ELiX8ZggLteyac+eYxjdypunVLfMuoa2T+Ad8JJqLLEqc1hntwZ46Q/bOezC6u48a0eVnalyOsWUY8N1ztEOO75pcRE58Vgn8iMwy7kw+d/mGWr32Sgb4B3QjdsfhtGQsMxwQMWpQXWSuLYNcFDYtUwwrDQRwp4mvykNsawNKskiv328TmDskPBNyOMo9I1nqrL7c/gafRjaSaq306xN1cKi07woI8UKHRncTV4sfIm2V1JsruSCN3CXu5CcSooLoX0jgSKTaYqUk6oPMSjtz2JntSYO3cWLzz1EkcdcRSM3gv934HK75bG7b4zSZ83eK09wZ+2DbOiK8XcKi/VN6xlSpmL7x5bP949Z2DlNygPvs6e9bl4oSh/esnXYqvfd077g0ROfvdKYc9lx7knyrKY6vX02PP58vFkhFOV8dgVTmsJ83hrjJtX9vLg1tJsn68s/SvUhRIsITLtldB+Bv6KI7n8iv9hJDVCe0cb+WweySZjL3OWAGNFC6ySVeyscaP6bWNGkKDYV4pc2StcFLqyY4ktC6tgYo84Ud0KjhpPaYiGRyW3L4W7wYuZNSh0Z7CFHRR7cyRWD+OdFsBR7iK5PoZskzESGpkdCfS4hmxTcFZ7MOJFbCE76W1xin05jJQGJjxzzwu43C4uvfwSHn/oSUK2baURuxXfLEWo7BPetZ7TbtvAr9f2s7wzxcwKD+dPLyOnm5w+OTyOZE3seRhn4W5G+7K5xIj5x4VfHf7FB+GZzAckyT1yZX+7th8zLaz+n5Pufn287PQnJzQgSzCt/EApR2eyMF7+chDZG0AOgWseyF7UxB3cfuOPePO1ZSw+chGqrJDdm0IbLmAVxlynMYSgNqphFSyCiw/Ebc2c8VcGmgkS2Ks9ZHclMbM6+mgR/9wIZs5Acau4mwOYKR1Lt7CF7GAKjLSONpAnsytJri2FpJQkgDAtXBM9uCZ6KfYX0IZLrp2ZN2nb2s7MOTN49eXX+M0vfoSS/GOpK46tttR6wTnl3Vgv3aIrecA9nFbuRpbgJyc0MLOiZJdk+1Zi9t+EMFPWQLvWlo6PfOmD8usDM3j+Z9ANTZyyZ32+1+UaJL/7WvLD2w46Zl61d1wsCwG7hvOs7Ulz6WO7xyeElGAaEaj9ValacegXkNvE9EYbq958i1tuu5mps6eAAD2hjfughZ4sV</t>
+        </is>
+      </c>
       <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -28201,6 +28225,8 @@
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -28243,6 +28269,8 @@
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -28285,6 +28313,8 @@
       <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -28327,6 +28357,8 @@
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -28369,6 +28401,8 @@
       <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -28411,6 +28445,8 @@
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -28453,6 +28489,8 @@
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -28495,6 +28533,8 @@
       <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -28537,6 +28577,8 @@
       <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -28579,6 +28621,8 @@
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -28621,6 +28665,8 @@
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -28663,6 +28709,8 @@
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -28705,6 +28753,8 @@
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -28747,6 +28797,8 @@
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -28789,6 +28841,8 @@
       <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -28831,6 +28885,8 @@
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -28873,6 +28929,8 @@
       <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -28915,6 +28973,8 @@
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -28957,6 +29017,8 @@
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -28999,6 +29061,8 @@
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -29041,6 +29105,8 @@
       <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -29083,6 +29149,8 @@
       <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -29125,6 +29193,8 @@
       <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -29167,6 +29237,8 @@
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -29209,6 +29281,8 @@
       <c r="J28" s="6" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -29251,6 +29325,8 @@
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -29293,6 +29369,8 @@
       <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -29335,6 +29413,8 @@
       <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -29377,6 +29457,8 @@
       <c r="J32" s="6" t="inlineStr"/>
       <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -29419,6 +29501,8 @@
       <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -29456,15 +29540,17 @@
           <t>User-provided</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>Verify the org's exact nature, leadership, and pro-Israel relevance -- not conclusively identified in this research pass (distinct from the Allen &amp; Co. Sun Valley conference).</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr"/>
       <c r="K34" s="6" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -29507,6 +29593,8 @@
       <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="6" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -29549,6 +29637,8 @@
       <c r="J36" s="6" t="inlineStr"/>
       <c r="K36" s="6" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -29591,6 +29681,8 @@
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -29628,15 +29720,17 @@
           <t>Public record</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>GROYPER FILTER REQUIRED: vet individual TPUSA-affiliated figures one at a time (per the Dustin Tropp pipeline-filtering model) rather than treating affiliation alone as an ally signal.</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="6" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr"/>
       <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -29679,6 +29773,8 @@
       <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -29721,6 +29817,8 @@
       <c r="J40" s="6" t="inlineStr"/>
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -29758,15 +29856,17 @@
           <t>Andy-identified partner institution; public record</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>Process public leadership/scholar roster and add named people per the ally-org rule.</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -29804,15 +29904,17 @@
           <t>Cited in existing criteria; public record</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>Process fellows/faculty/board rosters -- a high-yield source of young Jewish/Zionist intellectual allies.</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="6" t="inlineStr"/>
       <c r="K42" s="6" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -29850,15 +29952,17 @@
           <t>Cited in existing criteria; public record</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>Process fellowship alumni/board rosters.</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" s="6" t="inlineStr"/>
       <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -29896,15 +30000,17 @@
           <t>genesisprize.org; existing criteria</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>Process the full laureate list (2014-2026) + honorees per the Genesis Prize criterion.</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="6" t="inlineStr"/>
       <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -29942,19 +30048,21 @@
           <t>israelallies.org</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>TO-DO / MANUAL INVESTIGATION: systematically process IAF 'Top 50 Christian Allies' lists for 2024, 2023, 2022, 2021, and the original/undated edition (2025 done). Dedup against existing entries; add net-new allies. See criteria 'Bulk-source manual-investigation queue.'</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
         <is>
           <t>Knesset Christian Allies Caucus</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr"/>
       <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -29993,14 +30101,16 @@
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation</t>
         </is>
       </c>
-      <c r="J46" s="6" t="inlineStr"/>
-      <c r="K46" s="6" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -30043,6 +30153,8 @@
       <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -30085,6 +30197,8 @@
       <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr"/>
       <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -30127,6 +30241,8 @@
       <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -30169,6 +30285,8 @@
       <c r="J50" s="6" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -30211,6 +30329,8 @@
       <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -30253,6 +30373,8 @@
       <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -30295,6 +30417,8 @@
       <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -30337,6 +30461,8 @@
       <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -30375,22 +30501,24 @@
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
         <is>
           <t>Christopher Rufo, Josh Appel, Ilya Shapiro, Daniel Di Martino, City Journal, Hertog Foundation</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="N55" s="6" t="inlineStr">
         <is>
           <t>HIGH: full fellows/scholars roster unprocessed -- likely 20-40 more named allies. Priority roster pass.</t>
         </is>
@@ -30433,22 +30561,24 @@
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr">
         <is>
           <t>Manhattan Institute, Ilya Shapiro, Josh Appel, Hertog Foundation</t>
         </is>
       </c>
-      <c r="J56" s="6" t="inlineStr">
+      <c r="L56" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K56" s="6" t="inlineStr">
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr">
+      <c r="N56" s="6" t="inlineStr">
         <is>
           <t>HIGH: masthead/contributor list is a bounded roster of likely allies.</t>
         </is>
@@ -30491,22 +30621,24 @@
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr">
         <is>
           <t>Tony Kinnett, Advancing American Freedom (AAF), Eugene Kontorovich</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr">
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K57" s="6" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr">
+      <c r="N57" s="6" t="inlineStr">
         <is>
           <t>HIGH: large scholar roster; NOTE Heritage has internal America-First/restraint currents -- apply the Graham/Cruz-criticism yellow-flag test per person.</t>
         </is>
@@ -30549,22 +30681,24 @@
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
         <is>
           <t>Jerry Falwell Jr., Dustin Tropp</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr">
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="N58" s="6" t="inlineStr">
         <is>
           <t>HIGH: faculty/administration/Center for Israel staff unprocessed. Direct BFT education-leg partner target.</t>
         </is>
@@ -30607,22 +30741,24 @@
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>Josh Appel, Rabbi Elchanan Poupko</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="N59" s="6" t="inlineStr">
         <is>
           <t>HIGH: a talent pipeline, not just a node -- directly relevant to BFT's cross-community recruiting leg.</t>
         </is>
@@ -30665,22 +30801,24 @@
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
         <is>
           <t>Yoram Hazony</t>
         </is>
       </c>
-      <c r="J60" s="6" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr">
+      <c r="N60" s="6" t="inlineStr">
         <is>
           <t>HIGH: NatCon speaker rosters are a bounded list mapping the whole right coalition -- allies AND rivals.</t>
         </is>
@@ -30723,22 +30861,24 @@
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
         <is>
           <t>CUFI (Christians United for Israel), Sandra Hagee Parker, John Hagee</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr">
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K61" s="6" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr">
+      <c r="N61" s="6" t="inlineStr">
         <is>
           <t>MEDIUM-HIGH: staff + congressional relationships unprocessed.</t>
         </is>
@@ -30781,22 +30921,24 @@
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
         <is>
           <t>Riley Gaines</t>
         </is>
       </c>
-      <c r="J62" s="6" t="inlineStr">
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K62" s="6" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="N62" s="6" t="inlineStr">
         <is>
           <t>MEDIUM-HIGH: alumni network is enormous; Groyper filter needed per person.</t>
         </is>
@@ -30839,22 +30981,24 @@
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
         <is>
           <t>John Hood, John William Pope Foundation, Carolina Journal</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K63" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="N63" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: NC state-level network; useful for the regional-ecosystem leg.</t>
         </is>
@@ -30897,22 +31041,24 @@
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr">
         <is>
           <t>John Hood, John Locke Foundation</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="N64" s="6" t="inlineStr">
         <is>
           <t>LOW-MEDIUM: regional reach.</t>
         </is>
@@ -30955,22 +31101,24 @@
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
         <is>
           <t>Gil Guerra</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="N65" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: bridge potential to moderates; evaluate per person, not by affiliation.</t>
         </is>
@@ -31013,22 +31161,24 @@
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
         <is>
           <t>James O'Keefe</t>
         </is>
       </c>
-      <c r="J66" s="6" t="inlineStr">
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K66" s="6" t="inlineStr">
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L66" s="6" t="inlineStr">
+      <c r="N66" s="6" t="inlineStr">
         <is>
           <t>LOW-MEDIUM: small staff.</t>
         </is>
@@ -31071,22 +31221,24 @@
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
         <is>
           <t>Amy Mek</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="N67" s="6" t="inlineStr">
         <is>
           <t>LOW.</t>
         </is>
@@ -31129,22 +31281,24 @@
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
         <is>
           <t>Pastor Larry Huch, Israel Allies Foundation (IAF)</t>
         </is>
       </c>
-      <c r="J68" s="6" t="inlineStr">
+      <c r="L68" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K68" s="6" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L68" s="6" t="inlineStr">
+      <c r="N68" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: congregation + broadcast audience; a Texas Bible-Belt node.</t>
         </is>
@@ -31187,22 +31341,24 @@
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
         <is>
           <t>Jonathan Lomez Keeperman</t>
         </is>
       </c>
-      <c r="J69" s="6" t="inlineStr">
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K69" s="6" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr">
+      <c r="N69" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: author/contributor roster maps the New Right intellectual scene -- allies AND rivals.</t>
         </is>
@@ -31245,22 +31401,24 @@
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr">
         <is>
           <t>Israel Allies Foundation (IAF), Dr. Dave Weldon, Trent Franks, Mike Sodrel</t>
         </is>
       </c>
-      <c r="J70" s="6" t="inlineStr">
+      <c r="L70" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K70" s="6" t="inlineStr">
+      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L70" s="6" t="inlineStr">
+      <c r="N70" s="6" t="inlineStr">
         <is>
           <t>HIGH: current membership roster is a bounded list of sitting pro-Israel members of Congress -- direct Political-tab yield.</t>
         </is>
@@ -31303,22 +31461,24 @@
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr">
         <is>
           <t>Paul Taylor, Denise Lee Yohn, ACTS 17 Collective</t>
         </is>
       </c>
-      <c r="J71" s="6" t="inlineStr">
+      <c r="L71" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K71" s="6" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="N71" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: cohort alumni are a warm, values-aligned tech audience.</t>
         </is>
@@ -31361,22 +31521,24 @@
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr">
         <is>
           <t>Jimmy Bitton</t>
         </is>
       </c>
-      <c r="J72" s="6" t="inlineStr">
+      <c r="L72" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K72" s="6" t="inlineStr">
+      <c r="M72" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="N72" s="6" t="inlineStr">
         <is>
           <t>LOW-MEDIUM.</t>
         </is>
@@ -31419,22 +31581,24 @@
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
         <is>
           <t>Wesley Huff</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr">
+      <c r="L73" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K73" s="6" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L73" s="6" t="inlineStr">
+      <c r="N73" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: faculty roster is a bounded list of heterodox figures worth evaluating.</t>
         </is>
@@ -31477,22 +31641,24 @@
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr">
         <is>
           <t>Jentezen Franklin</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr">
+      <c r="L74" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K74" s="6" t="inlineStr">
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L74" s="6" t="inlineStr">
+      <c r="N74" s="6" t="inlineStr">
         <is>
           <t>MEDIUM.</t>
         </is>
@@ -31534,27 +31700,29 @@
           <t>Batch 8, Jul 2026</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>OPEN BACKLOG: scan J-TV guest roster for non-Jewish philosemitic/pro-Israel figures -- Andy's original ask. Guest lists are the extractable unit.</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>Ollie Anisfeld</t>
         </is>
       </c>
-      <c r="J75" s="6" t="inlineStr">
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K75" s="6" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="N75" s="6" t="inlineStr">
         <is>
           <t>HIGH: guest roster is a bounded list and was an explicit original ask.</t>
         </is>
@@ -31596,27 +31764,29 @@
           <t>Batch 9, Jul 2026</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="6" t="inlineStr">
         <is>
           <t>Position carefully -- an asset with center-left/institutional audiences, a liability with parts of the evangelical/New Right coalition. Not a neutral partner choice.</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="K76" s="6" t="inlineStr">
         <is>
           <t>Jonathan Greenblatt</t>
         </is>
       </c>
-      <c r="J76" s="6" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K76" s="6" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="N76" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: large staff/board, but coalition friction limits usefulness for the evangelical leg.</t>
         </is>
@@ -31658,27 +31828,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="6" t="inlineStr">
         <is>
           <t>FUNDING NOT YET SECURED as of Mon 13 Jul 2026 (Paulina interview -- YESTERDAY, i.e. CURRENT, not stale). Donors objected that they have 'put in a lot of money into evangelicals' without the returns they wanted and demanded a strategy deep-dive; that call was being scheduled for 'this week or next' as of 13 Jul -- meaning it is IMMINENT. Johnnie will not onboard until funding is clear ('go big or go home'). This database should double as evidence of strategy for exactly that conversation.</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="K77" s="6" t="inlineStr">
         <is>
           <t>Johnnie Moore, Dana Gibber</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr">
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K77" s="6" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="N77" s="6" t="inlineStr">
         <is>
           <t>HIGH: the ~200-person core community and ~500-person ecosystem are exactly the Jewish business network leg 2 needs -- but access is Andy's, not public.</t>
         </is>
@@ -31720,27 +31892,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="6" t="inlineStr">
         <is>
           <t>The B2B/nerve-center model is the operating design -- additions should be evaluated as nodes it can connect, not as staff it would absorb.</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="K78" s="6" t="inlineStr">
         <is>
           <t>Johnnie Moore, Congress of Christian Leaders</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr">
+      <c r="M78" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="N78" s="6" t="inlineStr">
         <is>
           <t>This IS the hub -- its connected orgs are the network.</t>
         </is>
@@ -31782,27 +31956,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>Its existing membership/leadership roster is a decade of warm relationships -- a bounded, high-value roster pass IF Andy can access it via Johnnie.</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>Johnnie Moore, Samuel Rodriguez, Evangelical Foundation</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="N79" s="6" t="inlineStr">
         <is>
           <t>HIGH: a decade of evangelical leadership relationships, accessible through Johnnie.</t>
         </is>
@@ -31844,27 +32020,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>Leg-3 anchor. Its Middle East Studies students/faculty are a bounded pipeline; the planned Center for Jewish-Christian Relations is arguably the single most on-mission institution in the database.</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="K80" s="6" t="inlineStr">
         <is>
           <t>Johnnie Moore</t>
         </is>
       </c>
-      <c r="J80" s="6" t="inlineStr">
+      <c r="L80" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K80" s="6" t="inlineStr">
+      <c r="M80" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L80" s="6" t="inlineStr">
+      <c r="N80" s="6" t="inlineStr">
         <is>
           <t>HIGH for leg 3: faculty + Middle East Studies cohort.</t>
         </is>
@@ -31906,27 +32084,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr"/>
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr">
         <is>
           <t>MODEL + PARTNER: closest existing analogue to the BFT internship pipeline. Study their campus model; their chapter network is a bounded roster.</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="K81" s="6" t="inlineStr">
         <is>
           <t>Passages</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr">
+      <c r="L81" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K81" s="6" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L81" s="6" t="inlineStr">
+      <c r="N81" s="6" t="inlineStr">
         <is>
           <t>HIGH: campus chapters = bounded roster + a proven model to copy.</t>
         </is>
@@ -31968,27 +32148,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr"/>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="6" t="inlineStr">
         <is>
           <t>VERIFY: could not confirm details of this org from the transcript alone. Confirm what Vine and Fig Tree actually is, its 'peaking GPT' tool, and whether it is a viable partner.</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="K82" s="6" t="inlineStr">
         <is>
           <t>Stanify</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
+      <c r="L82" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K82" s="6" t="inlineStr">
+      <c r="M82" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L82" s="6" t="inlineStr"/>
+      <c r="N82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -32026,27 +32208,29 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr"/>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="6" t="inlineStr">
         <is>
           <t>Verify the company and whether Andy's existing relationship is a warm partnership path.</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="K83" s="6" t="inlineStr">
         <is>
           <t>Vine and Fig Tree</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
+      <c r="L83" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K83" s="6" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L83" s="6" t="inlineStr"/>
+      <c r="N83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -32084,27 +32268,29 @@
           <t>theisraelguys.com/team; theisraelguys.com/volunteer</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr"/>
+      <c r="I84" s="6" t="inlineStr"/>
+      <c r="J84" s="6" t="inlineStr">
         <is>
           <t>HIGHEST-PRIORITY PARTNER/MODEL: do not rebuild what they run -- study or partner. Process the full theisraelguys.com/team roster (Andy asked for the whole team, esp. the influencers). Warm path exists via Joshua Waller (already an IAF Top-50 tracked ally).</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="K84" s="6" t="inlineStr">
         <is>
           <t>HaYovel, Joshua Waller, Justin Hilton</t>
         </is>
       </c>
-      <c r="J84" s="6" t="inlineStr">
+      <c r="L84" s="6" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="K84" s="6" t="inlineStr">
+      <c r="M84" s="6" t="inlineStr">
         <is>
           <t>Partially mined</t>
         </is>
       </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="N84" s="6" t="inlineStr">
         <is>
           <t>HIGH: full team roster unprocessed; they are a live proof-of-concept for BFT legs 1+3 combined.</t>
         </is>
@@ -32147,22 +32333,24 @@
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr">
         <is>
           <t>Rabbi Tovia Singer</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr">
+      <c r="L85" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K85" s="6" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L85" s="6" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -32200,34 +32388,36 @@
           <t>ffoz.org</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr">
         <is>
           <t>Verify Jacob Franczak's role here; process their contributor roster.</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="K86" s="6" t="inlineStr">
         <is>
           <t>Jacob Franczak</t>
         </is>
       </c>
-      <c r="J86" s="6" t="inlineStr">
+      <c r="L86" s="6" t="inlineStr">
         <is>
           <t>Claude (proactive)</t>
         </is>
       </c>
-      <c r="K86" s="6" t="inlineStr">
+      <c r="M86" s="6" t="inlineStr">
         <is>
           <t>Untapped</t>
         </is>
       </c>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="N86" s="6" t="inlineStr">
         <is>
           <t>MEDIUM: theological-defense content + contributors.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L86"/>
+  <autoFilter ref="A1:N86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34357,7 +34547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34368,6 +34558,8 @@
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -34411,6 +34603,16 @@
           <t>source</t>
         </is>
       </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -34453,6 +34655,16 @@
           <t>Search research, technical.ly model</t>
         </is>
       </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.texas.gov</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHgAAAB4CAYAAAA5ZDbSAAAABGdBTUEAALGPC/xhBQAAACBjSFJNAAB6JgAAgIQAAPoAAACA6AAAdTAAAOpgAAA6mAAAF3CculE8AAAABmJLR0QA/wD/AP+gvaeTAAAAB3RJTUUH6gYIFiU04BO0mwAAW1BJREFUeNrtnXd4XNW19n/nTO9No94lS+6990Yx3camEwglyRcILSH13hsScpObTgIhhAChNxcIprlg4967LVvV6m1Go+l9zvn+GCFZsU0RkJv7fXc/Dw8wmjl7n73OWnutd71rHYH/R4bNZrNoRLFCguEyVAqQJwtkCAIOZDQgWwf/QvAiE5UFegSZHhnaBDglQnVMkmp6e3t9/y/si/A/cdFOp9MIzBXk1EIZYZIAwzUaTXZpaRkFhQUUFRaRmZWFw2HHbndgMBgQBAGzxQKA3+dDlmWCwSC9vR7c7h66u7pobmmmubmZhvp64vF4hwynBOQDsqDYDGx1uVzB/xXwlzMU2RkZc1OyvEiABQhMraisVM6ZM4epU6cxcuRISsvKUCqV/T/w+Xz4/T7CoTDhcJhAIIA/4AfAbDJjMpnQ6/XoDXrMZguWPuEDJJNJGurrOXHiBHv37mHbtm3U1tQkkdkrwyaFIGzqdLu3Aqn/FfDnGNl2+yhZIdwsy9ySX1CQPW/efGbPns3sOXPIzMxEkiRqqquprqmmob4el8uNJKXQaDQolUoEQUCW5YGbFdK3+4+fybJMMpUiGomgVKrIyHBQVl5OZUUlFZWVCIJAV1cX27dtY/v27WzZ8iFtra0dgszKlCA873a7D/yvgD/lyMrKypRTiZtAvMVkMo5dcsklrFhxDXPmzkUQBJqamti6ZQv19fUgy6g1aiRJQqnR4oum8MZkgoIOtT0Ltd6ISqtHpdWjM1lQaXUAJKIRIgEfiWiYRDRMPBQg3tuNkQhWNVi0SpKxKKIoEgqGiEQilJSWMnfePMaOHYsgCBw5coSVr7/OqlUr6fX0HBHgORSql7q6urr/V8DnPlezRaT7BEH81oIFC/XXXHstFy9Zglar5cD+/by9di3RWBSTyYwoivgSMu0xJabi0WSWjURnsX+h6wl7e+iuryLYdJxcTQqLSkCSJAIBP1qtlssvv4KJkyYRjUZ57913Wfn662zevCkmSannkhI/83g8Lf8rYCAry1JCUnmfoBC/dtlll2sf/O53qaispL29nffefZf6ulosVhuxlExDQEZXOJL8sdNQ6wyf/gAXQKUQ0CoEEpJMKCF/5nXGwkHaju0l1lxFiUlArRBwubrJycll+YoVFBUV0djYyGOP/pFXXnklnkwkXpMQfuZ2u2v+vxSw0+nMFpB+qVapb7z2uusU37rnXoqKitizZzevvfoqTqcTBAUNnjDKkokUT56LqFCe81papUCBUUFrMEUkKWNUCYx0qJiWraGmN4k3JhFPyehVAia1yPuNkc+1dlmSaD6yi9TpgxRbVEjJBG6Xm2uvv46pU6fR2NjIo3/8A6+99loyGYu/ICsUP+ju7u76/0XAYqbDcZOgEH+3YsUKxw9/9G/k5OTw4ebNvLFmDQWFBbgDUbr0eZTNWoJGbzzrAro+gRaYlKgUArGkjEYh0BpMcrwnAYBeKXDXOBOv1oRoCQw4u2UWJfW+5McucJhVyZgMNb1RiaQsE03KHHLFSUrn1uyGHe+SGWknw6ilpbWVq5ddzdx582hvb+c/f/Ywq1et8oL0UJfL89g/2/NW/DMny8jImGjU694YPnLE3U89/Yz+a1//Ovv37+PXv/olwWCIpFpHkzqf/ItuJrN8NEqVetDvlSLcPNyASS3ijkrMztNwzB1nT2ecOl8ShSgQ7DO/CQlm5mqo7U3SG0tLxqgS6ApLH7vGRQVaJmapeashQnVvguZAClGACwt1nOpN8I/GXalS4ywbhW7YVE67g+B3EeztYeXK18nKzOKbd93FzJmztAcPHbo4GglfbtTqjoQikdb/pwRcXFys1SgUv9PrdX+9/4EH8h9//M9otFp++V+/wO/3E0gp8eSMI3fBdWSUDEcQxHNeR5LBpBbZ2hbDF5PIMygxqERqvWmNDP7D2TolS83pQAp3REIUYFq2htZgivOdwOVWJQsLtLzXGKEjNKBo/rhMvklJhi59DHw0MvUKEhKk5HS4ZcsrwTJqFo09IRThXsK+Hl55+WUuvfQyvnnX3dgdjpy9e/feplQo7bl5eZs9Hk/qf7yAs7OtxfFo4u0ZM2csW/3Gm8KiRYt55pmnWb9uHXqTlVoxh+Ilt2LLK/lU1/PGZGKptIiMaoHhdhUHuuPn/O7ETA06hYBNK1JsVlJqVnKqN3lOUwuwsECLWhTY0Bw96yGwaUXGZag5eMZc0aTMLSOMGFQCrohEUvpI0MWYR86kps2FOemn5lQVtTW1fPWrt7FixQrhyJEj0xvq6y7RG4ybwuGw50s9D7/Mi2c6HMsESXXovvsfmLZqzRt4PB4euP9+orEYTWERafp1VMy/oh+AAHBoRRbka8/rHPjjA9JpCaQwq0Us6nPfRiIl0xxIsqsjxra2GO82RhA/xuvI0StoCiSRzqHieqWARTN4HrNGxK4V8cYkxmaomZmjwagamKB81sUYLvw61QGRcDjM/ffdh8/vY82bb3LPvfdOFJEPZmVkXPc/ToPLy8s1SlF4zO5w/PqpZ57RfuWWW1izejU7tm8nJqjwl8+nfOEylBrdWb9VKwQuL9Xh0InU+8692f2xalJmUqYaT1SiO3K2Wo7OUOGLy/1mNZyUSUhg0Yj9VuDMMSNXQ6MvSXPgbMs53qlGpxTZ1zWgwfPz0g/ihuYobcEUnpjE0jI9gbiMt+/cV6o1OEdOoS2qQPS2cbqmmoaGeu69736mTZuu+fDDzctBdhaHIxtdX4ID9oVrsNPpNPp9vW9Nmzb9G5u3bGHq1Gk8cP99tLe3c6onSuYV95A9bPR5fx9PydR6k+QYFFwzzIBOeX6Vk2VoDaYoMJ07fEpIoFEM/r1NI1JiPvf3u8MS57LeKlGg2Kyk0T/gfZvUIiMdKnZ3Dgg8lJA51ZugI3y2nLIrxpJ55T3UR1SEQmG+990HmTBxIus3fsDkyVPu6s5wvG+3283/0gLOzMzMEmRpy8UXL7lw5erVuFwuvvfdB8nMyuGEnMm4m7+HUqPt94jPJ2B/XOKlUyFUItw43IBVc/5ltgSSFJoUZ5l0nVLAqBIoMiuY4FQzLVvDwgIty8r1NAfOHSbt64pRdI6HZZRDhSgI7OmM9X82NUtNUpKxaUTUinR8bVQJHHUniCbPbXYUKg2jV9zNSTEPk9XGv/3oR3g8Paxe8wYXXXTRApUobMrKysr8lzTR2dnWYjnFpmuuvXb0439+gr179rD2rb8TFzUwZRm5o6cMijOvrTDQEUrhjw/eDLnPmz3Vm+Rkb5LRDjWTstS0BlNneckAepXAeKcaCQjEBxywTJ2Ck54kVZ4EXeEUrcEk9b4kh1xxIucRgCcqYVCJlFqUdIQlZGCkQ8XsXC3vNEZo7/OsDSqBS4r1fNASpTGQZEGBllF2NQddcVKfAiSzFZTh1zlJdNRQffwoarWae++7n66urtyjhw9drTcY3/2inK8vRMBZNttoGcWHd37t68W//s1vWLfufbZt3UprIEbBsvsw2J19mRuYmaNBpRB453QEk1oxyGn6aJRalMjAWIeaI+44CkFgXr6GYEIedNZqFQJZBgXHehLUeJODIMhAQiaUlImmZJISH3uWnzlagyn8CZnRDjWVNhUJCTY2R3GdMe/MHC0WjcC6pijhpExnSCKYkOmJnj/G1igE5uVraQulSMmgM9vQlU2i+cgukkEvbpeLe+69F0EQbDt3bF9h0ureD0Yirv92JMtutxcoRGHHj3/8UMFdd9/N3555mt7eXo53+KlYcS8KparfZF5aokOvFHjxVOhjN/zaCj27O+M0nXHmXVqiY6RdxcHuOLs7Y5+IJ4e9PfS2NRDy9pCIhElEIyhS6fMypVCj0upQa/Xo7RnY80o/VbLCqhHJMyq4qEjHltZof3imVggkUjIft6LJWWoSKSgyK9jcGiPQ92BLiTgnXv0dk4qdWCxWbv3qV3n0j3/kZw//tF1UpmZ1dnob/9sEnJtrykjG1dvvuffeyh/927/z6B//gCCI7GnxMWbF3Qii2A8ITM1Sc8gVZ1m5nqqeBB+0RM973cWFWjY2D/77BKeajnCKztDZDkzQ003r4V2Ivc1kaAVybGaKCvMpLy/H4chAr9ejVqsJhUJpE2swEI/HCYVC9PT0UF9fR1NzKx29ftwxkGyFFIyfgcHmPNvP0CmYnqOm1pvkpCfxmfdMrRBYXp427119zpgsSZx4/TGmFFqQkfnWt+7h4Z/+hMcefbQOUTH78+DYQxZwRkaGSYG8efk110x69LE/8cLzz+H3B9jXFWf00jsH3dBtIw08fSJEQpIptShZVq7n3dMRqs6zQZeX6ljb8PEJga76KlwHN1NqUTB+ZAUzZ86ivaOLXYeOEkrI9ASj9ATCJBBJpCSUGj1qY9pJjQf9JGNhVAoRlSDjMOpwGLUYVAIzJowlJzuTXTt3cKiqhka/hHPSQjJLR5ylzb6YxGfNS413qllcoKXGm6DKk6DOO2Cljq3+C1OyNeh0Om6/4w4euP9+Xnnpxf2SIC4YKl1oSAIuLy/X+L2971x40UWL/vbsc2zYsJ6TVVUc7Y4x6ppvnfOmTnoS/Q7QzBwNU7PVvHwqTHfkbI382mgjR3sSHOqOD4pXIz4P9VvXki8EuGTRXIpLS3lrwxbavCHafVFsw8aTVT6633IMJUvUVXec3trD5Jg1FNiNXL54Hqfr63lv01ZaZTNl8y5HZx5a7rnEnH64N7dGOdgdZ16elmBCGoTEHXnlEabkmygpKeXSyy7jzjtu55133l7vdPVcfgLi/xQBZzodj02ZPPWuVWvWsHfPHnbs2M7J7hCjb/xu/+aqxHTu9aNJBGHA0RGApeV6HFqRF06GiJ4hRJtGRBDSHu3Aeeqm6cPVzCnN4KqrrmLzzn3srqqnO6Vh+IIr+8/5L3rIkkTDno3oQi7GFjm5bNE81q5dy+ZT7ZQsugZTRvanxwd0Cm6o1HP8jOPJpBZZXKDljfrwoDlPvPxrhjm0zJ83n0mTJ3P1sqXs33/gEZfbff+XLmCn077cYctY+cHmzfT2enjl5ZfpCKWouO5BxL7sj04pcFWZnrUN4XOGNh95lTePMOCNSrxRH0bqAy7+0VE6vf5FLhpfzsIFC3j+jfc41ROheM4VaI1m/pkjGvTTuH0twx06blm6hA0bN7LhaAOlF938iQ6aUSVw03AD3ZH0vX50n5l6Bb6YRCwloxDoD7GkRJy6136DUytw0803YbFYWbRwgdzb41ne3dOz5ksTcGZmZpkgSweee/4Fy+w5c/jhD74PWiNZV9yLSqfvj3GLzUrcEQm7VuSgK07vecKHTJ2Cm0cYaA+l2NYW7YcUZUni5PqVjDNGuPaaFfxt9TucDison3/leZP+/6whpZJUb3qDcqPMbSsu57333mdnl8SwhUvPeTSoRYHrKtN782p1mPh5wgejSiBLr+jPVccjIdxvP07M7+aXv/wVe/bs4aYbrvciJiZ2dflOfxlxsMqg16695557y7962+38x7//O87MLKRJV2G0p8EXizoNEnzYGqMznOK0P3leVAcglJRxaEW2tkXp7MvTuhtP0bvhb/zojmtxBSI8tW4PmfOvJaNs1Fkb6Gqu5tCHL1B18E1O7F9J9dG11OzdSOWkJUMSXqCni7CvF2QZhVJ5ToEJooizbBRi3gjeWPsudq3I7ZfPZd3zfyJpdKK3OvqRujEONYsLtRhUIq/VhIh8DApSalWxpFhHnTdJJCmjUKmJm7MpEAO8s/YtvvGN/0MoFNLu3XNgZkk48tynxa0/tQZnZmT8buKkife/tfZtXn3lZXp7vRxLZlAx//L+74zJUBFJyoM8wyy9gnKrElGA6t4k3WfgtAaVQFKi35Gq3fIW06xxJk6ZylNvrCdjxhX9D8+Zo63mEHs+fBRfogrRnEJOycS9CTR2NQ6mc9lXHh2SgJtP7eP9V75DShVAZ7RhMhZgs5Qzad6t1B3aQjLlZ+S0pZgc2YMeip7da7lz6UXUVZ9k7cluRl9yU78fcmmJjgZfgqPu84dU03M0zM7VcNgVR5ZhW3uMeN+e1G1/l/EqDxaLhWuuvZalV17J3r27f9Pt9jz4hQk4IyNjokGn3bttxw5FIBDgjTVrqAvIjLzmvkHfKzIrWZCv4YgrgU0rUm5RYtGIJCWIJCX0KpEXT4bO8pwTkTDVax7jB3feyMFT9Wxvj1Ey/YK0lns6EY+9SDKVQjP9Lo7tWsOxU39FMEdJRVP0HOpFZVJhHWlGEAXKzTcx68p7h2yC2+uOsP6te/G5O1BoREylRmSvDqd+Cl2egySkEHlZM5g6/xtkFg+ETs37PmSkLsi8KeP4r6deZfiyu1Dp9AhAoUlJ0znwb7VC4JJiHSVmJRuaIxzvSaBVCszI1rC5dQAHOP7Sbykxylx7/XXo9Qbmzp6VisTiU1wu16EvwkSLRoNu9Xe/+73CRYsv4OGf/pSEqKHgym+edR76YhImlciUbA12bZr9sKsjzvqmKHu64qRkmUy9YlA6LtTrwv3uEzz83Xt55LnX8ORMJHfk5P7zLr7l5ywao0ET3MWGdVs46XkfwRQn2BymfWMXlkoTolpB3Jcg1plEUAk0Ve+gq+EEOr0dgyXjMwnYZM8m7k3gVx1HTkq493nQFSmJqJuJtqRIKUMEY400nN5AuDNEYeW09PGUV4xL1rN93Vp+eu+dvPfsH1Hlj0Cl1eM7Bxzr0IpcW2HArhXZ0R7jSJ+GJ6V0wmWUQ93vk9grJ+Kv3seOLR9y7XXXIcuyuGP79onhcOTpPvh+6BqcmZHxjdLSkj9v2badF55/jkgkSr11DLkjJ35m7cg3KsjUK/pZEb6uFoT9b3DHrbfw07++SsXltw96aOo3Ps2k1DMo+1KGbx8IU52jwHPUi7c6gH2MBa1Dg9apOed8KZ8SI2Usuf43g8zqWfhz9UFOn/yAULiTcLgXmRSulhqSCh8KtYivNoB1hBlBIaDQKAi1hVGbVWgdOnI1i7no5l8gyzKCICClktSufZp/v/NanvjrMwhTlmHLK+53pFSiQI5BwQWFWtpDKd4+HWFipprj7kT/g6AU4boKA69Uh/o967aq/QzznUCv13PTTTczf95c6utq7+xye54asgbnmUwOSalc89enntYbjUY2bthAdW+c0vlLP5VAleJA7KsQYFqOhr1d6YyL6/QpHPVbWHH1Mn76zGpGLv16v1Pj7W7l+LbV+A+upjQrgrIvp9vYE6amKYzvpB/7eBvWShNKg5Jwe4Sew156DnmJdkVJhJIIgoDKKmAQihk3+/ykibr9m9jy9i/p8G3B1V6Nz91MTNGNNl9EY1MjKAQEhYC/OoDarCIRTGIZZsJz2IvWqSZEE5G2OG3VR+jpqCGndBwZwyfz9zff4I4Vl9G6Zz1uDOitGcSlNC9sQYGWA64E7zVFSEjQFkxxYZEWrVIkIckYVSKHuuMkzlB8szOXQ9s2Ee/tYtyECYwbN56VK1fOtliVzwQC8fCQBKwzG/+w7Oqr53zzrrv56UMPodYbsC28GdU5mBjnPLt1Cublack3KqmwqdjTGSeUkPF1tpBxegvzFizgsbd3MeLSrwxoU+1BNvz927Qf20y5xs3plgg93gQeb4L6pjB1VQHs46xYKkz4agK0vd9J3BvHUmHGOcWOqcSILlOL0qBE6Xey+KqfozPZzp8syS1h3OzrSPQKBKXTaLIFoq4Y3hM+wu1RNHY1+lwdWqeW3iofCpWINlOLIV9P1w43pnIjPd3VlBQuZseuh+msOUXZ6IVkVIzn3ffe5+rFs+g8sAmv2oHObKU5mMSpU7C5NUpKGkiR5huVdIZSdIRShBIy5wo+zEXDMfQ2svXDzdx2xx3UVFfrTlbVmULhyDufWcB2u71Ao9E889zzzyuOHzuG1+elTpFFzvBJn9okhxIyXWGJYVYl7zVGiKZkIj4Pqd2vs3zZUh59aysVFw5ol7e7lQ1vfYektQs5FeOSCiMVJQbiCYloXMLVHSNcaEDrVNP6fidSTCJnnhP7WCtqi2oQt0vw2ph/wcNkl4z+ZE9TECiomIJZXUZb3SFUOUmMRQa0mVq8J3z4qgPoc3SYy014T/kx5OgQVSIKjYJAQxB9sYq4WyYY6MAXraW16jAV4y7COWwc6zds4KbLFnF8/Srk7GGotHqaAklm5mj6GSIKAdwRic5zMEHUokCBSYk3JqHU6DhV30CREQRB5JJLL+W5vz0z3qhUPR+MRn2fidGhVAjfv3rZ1eqCgkJWrnydNk+AygXLBuVs1eInO+H+uMQ7pyPIpIu+et5/kq999RZ+89p7VF50w6Dvfvj3h0laOgGISTLrjkZRKATKCvXkZ+voNiiJemJ07XCTPddJ7qIs1NbB3OlkOIW3KoRJUYYlo+Az+Qil4+YydtRtxBrT0KdCI+Kc5iBrdgbek356j3rJnu3Efag3TTbI0xHriae9ef8RlBoVUXcUv+4I61/+EQAVi6/hkVUb+fodt+Ne9xTJWJRIUqbKk2BOnqYfwTqXIwYgITM9e8DHGL7oarq8IV599RWKi4u5culSlaRQPPCZNDgzMzNLFIRnH//zE6rqmhoCAT+dthHYC8r6TK/I5Cw1SjH95H3ajMqplX/k4Qfv4d8ff5HhV9wx6G81BzZQ0/Yygip9tcDpEJFcLTVHTDS69Ww5lcLbY8AqRskyi4SSkIhLJP0Jwl1RIm0RAqeDhNujGPK0SI5uava/j0q24Myv/HjMWZY5vmM1W9/5GTVNq5DEKMGmMIIooNQrEZUihnw9giDg3u/BXG4i0h1BY087eJ5jPnTFAuH2OLo8JaHGMEmTC00yC2d+JRkV41nz0rP89P5v8MrTfyZz9AxCCRmzWmRRgQ61QqAnKp2TDTLcpmJylpq2UApfTEIQBNp7vJToZZRKBQsWLOTZZ/82TqvTPxMOh4OfSsAGneahK664at6tt93G7377GyKSSN6iG/pN4OQsNZtaonSEJLL0CkRB6AcrFMK5/fbqTWt4YMUF/PmVN8m/6FZEhYKwz4NSrUEQBPZ/+CQhZUM6Lg4kiHRGMZUZaD8WJS4WotRmMDqjjVsusqBMyqj9CcxxiR5PAoVVjcqqQufUosvWIidlEoEkoi1Ba9MOFBEbWcUjz3+U9Lo5fXwLgd52oskeBKUMMoSaQgSbwvhrgqT6WJJqq4pIR4RoVxSNQ4ParMJfE8BYZCDuiWMo0OKt8mMapsPX5mLkpLRDahs2jq1/f5VvXncZ72zYjKN4ON0RiRN9lKJzcbUVAlxRpqcjlCKalPtNuD2/DO/JXRzdv4/rb7yRk1VVyrra6mQoHNn4iQK2WCw2lVL50qN/elzd1dVFd1c3bcZSMoor++M3tULsZ/6HEjJfGWFA2/cUapQiox2qQZUBPU21TDf4cAVjdDlHY7A5kWWZtc98i/pjH1Ix4SL2b/8LKU36GAm3R5HiEvocHa4jnchxFXZ9hOvmpx+dE7UhlszLYHy5kcvnXUp1WxuJDAVKnQKFVoHKqERlUiJHlRTaljD9kq8POp/POud0BopGzmT09OVY9RV4O9sRMvwYiwwYCw0YCg2EWsIoDUpSUQlTiRHLCAvRjihRVwy1TUWkK4aoENFkpD1tUSWSELw4zRPxtDdjzykiorWS6mygQB2jOapCb7EjCLAgX4unL+lw5piUpabErOS12jAtZ1RUCIJAc1sXRQYZg8HArNmzef6558YpVaonYrFY9GPPYLVSecPMWbOMY8eO5YXnnqM3FKF81sWDJq3xDsBuRrVIlSfBzo4Y4aRMIC6RoU1j0h+Zv9DuNxk/YSIfNgZwFJQDsH/Ds/g1R+kRtvPBKz8hGu0dyNy4Yqj62I0KpZaSaZMwZqgQBPAFkmjUQn/oJIVruGPxtYPj37CM1l/GjAkPsfj6H3+m/HD5hIWs+MYLVDhvg950WwdRKZAxyY4UTWEdbibcHqF7uwttpgZzhQmFWkmkM4qAsv9sDjaGUBglmqp3sPWtX9BafQBbbjHbWsNMnjKVwI7VyLKMJIM7KnFVmY5FBVoW5GsZk6Eiz6hgRo6GHR2xfpLgmezSYfMuJRhL8tJLLzF69GhmzJhh0iiV132iBhsN+ke/8+CD+dnZORw/foxGMZOsyvFpM6MVWVKkY2yGGlEQ6I5ITHCq2d89mE1YbFZS1ZMgKcOpTWv47s1X8qfX3qZ40TX9Qt+2/udIei+x3jiB1GmS4TjKvgxg9043jnFWRKWIICmR8lvwK7wo2qPYTSq63HGK89OhWnu3nw2HvYi6kRjFMhy6iYwf+zVmX/YAzvxhQ6O59HnVFcMvI9wSJ+FL0r6jiRwhm5xoPiF3iIgYJdKZhktNpQZUJhXxLgldngqlTpE206VGEi4F3kQVUX+QYeMuwl44jA/eeJVv33Ejf39/A47i4bgjKdxRmcOuNA8tIaWL3ZQCRFIyhSYleqVAkVmJJKdrpQRBpLaullxtiuEjRqDTaVm3/n17KI1unVvATqdzmF6n/a9H/vBH4bVXXyGRkjDPuKo/7s3RK9jRHiMhpTV5Smbag631JvsFrFMK2LUKGgNJogEvRZ7j9Ibi+Aqn9udwq/et53TPagSFQLApjDZLTcwTQ21Tkoqk8Bzx4pzqINweQV+oJuqO4T7QS707RjCUorU7yskguJgLo+9m5BUPUjFuCcPGXkjJyDnYsos+1iR/6vSZVkfxyFl4G3o4+MYaxJTIqBGjuPvOb3HxtCVs/GAjGGW8J/1YhpuQBAk5KaHUKQg2h4m6YnQcrieVjCIaUoyZcj2CKCJYskl21qH1txG2laBQawexS81qkVm5GtY2RDjYHaclkK6cNKnTNVYfJXPMWQVoXbU0nW7g6uUr+OuTTxao1OpXw+Fwz7lNtCTdculllwlGo5HaujoaeyOD6Cmn/Ul8cYndnTGePBZkd2eMLL2Cr48xMitXg04pMMGZproC1L3/Ijdefx0fVLVgzcrvv053+1FEdVoAKqOSYFMIhES/92yuMKVDnkCStnWduPd7yJhkwzEvk/YKE+HpGZBzAeO/8ltyxsz90nPA3Y01yLJMW1sbL774IldffTV/+tOf+P1/PEK4I4J1pJmOzd3onCpiriSyDLGOOJcNvwJ/i4eeQ17czY00nthNNBTAnJXHuiMN3HzjDdSve/Gs+RYVaDntS3K6L05OydARSrGnM8aO9lh/0YDWbKPJE+bUqVOYTCYuXrIEEW44nwYLRoPhqR8/9JAtGo3S3t6Gx1bZHxqdFZ/J0B5KccgVJ55KV/LNzNHQEU5R70sS9vYwQdPL9sMnsc++us9r7sHb3Upr4x6Cqfq0uU7KBOqDqCxqNDY1nVu6yZyRQagljGuXG8dEO5nTHSh0A0tV9eZy0bW/Qq01fCZBfdRd57NqdzTg48SH7wzqztPc3ExDQwNGrRFFhYDWqaVzaze2sWa8pwJcM+daOto7qK2tRZYhGUri9dVhyyjBnluCrWQkVVvfo9Kpp0ebjUqro9yqZGKmmnKrijfqw+ck6MdS8iDKscvTS54qRkaGg8LCQlavWlUcCkf+cJYGZ9nt05zOjJI5c+eyZvVqovEkxVPmD0oUnGskJTjQHeep40Ea/UkO9BVn1W98jcsvv5xTnjiKPirPjnf/wHt/v5tAT/sAoKJXEPOkfxN1x1Db0ia597iX4hUFmMvPqPCXQenJ5eKrf4fB6vzMmth6eActh7Z95t+Nv3gFE5Zc0++sqW1qjMUGanqqafV0EqiJodCKZE7PoGuHm2hrjCuvuJJt2wbmUltURNTN2LNL+pxHFUfa/VxxxRU0bFqdxtr9SSqsKk71JgZx0j5ulE1bBAolb77xBvPmzcfhcBRlORxTzzbRCmHRnLlzUSgU+AN+GkNSv2C0CoEZORpyDArO9/AnJJk9nWlPOhr0M6c0g5fefJfyhWn0y9PeQLt7C5LJQ2f74QGzoRJJRVKkEhKufR7UFjX+ugCFV+T1hSWpdCqwWSQjMY/ld7yEPa9saM6T6zSi6/SQfnvNQ3/m0nsepnD0ZJSiHlORCfs4K/YpBozlauKdEOsAU7mJqC+KVqvF7083XtNla8mY6gBBIBkfiGIqLljBa2+vZ1q+kVgoQFKCvV0xDrs+PXlSVKlp8Cbw+nwolUpmz5mLLAhLzhKwLLNg9uzZdHR0YDZbwDmwifmmdD+Mm4Yb+NY4E8vK9UzJUpOlHxB4hm4gNq7f9g7Ll1/NoRZPv4N2dOfrYA0T88QRjQmkPqdCTknIkox7n4ekP0kqksJYZCRQHSVQHyPh7Yv/DBGKKueiMRiHfJZmG5RkGRSDTO1n8azn3nQ3dz/7AQ++dpDLb3oCU0YWckqme1cPaBOYRqjQmczo7WYaGhqw2+0odApyFmQR6YxgyNPS2Xx8wHqptRxocnHNiuXUbXs3TZt1Jc5Z2vqxR09GMWaTiY6ODmbPng3IgwVcXl6uAWbOnjOXrVu2IAhQMHbaoKTx7w/6+evxIJtaogik015fGZEW+IphemblaPo96ayki+179pMz9YIBR6X7MMlwikQgiS5HS7gj0idgGVmSSUVTOCuLyRsxDlOJHvMIHWq7QCKSQKEVUWKifMKCIQvX3XCCqaMrWTB1Iu6aQ5/L6TJYHZRPWMCIkhsJNkfQ5+nw1QRw7fGgtCfJnG/mZ0/8lLKyMkwlBrQONVJcQlAIBHztg66VO+Uidh04jDPW1W8JK20qyq1KVOKn8xUKxs9EoVCwY/t2Zs+ZAzDZZrNZ+gUc9Hpn5uXn64qKijhy5DBhSURvHWBC1HqTyIA3JnG8J0FTIMlfjwd58lifwIWB/hiettNcOGc6u6oasGbmpRcdixCMtZGKpEiGkgiigNTnQKRiEolgMp28L5BJZrQhJWTaNnQSbotgKjGg0Ciw6SvRGkxDForG20ZRYT4Ohx1TxP2FeNdTl9xBXsEUBBnM5UY0DjUdm7qREhK6KWpOdpzAPs5KuDMNawIEg4MFbM7MYdfxOhbPnIynNQ3VhhMyRSYlc/I0XFKs45JiHTNyNAyzKs9ZSqu3OojKCo4cPkxpaSn5BQWiSiVM7xewBAvmzZ33kS2iNTSYv/yPRdRaRRp79sXTAl9VG+7nHHXsWc+ECRPpig8wM3raGpA0IQQFRHvSNbb6HC3h9ijh1jAKjQJDngmlQyLUGqbpzVbsY6zYRlv6Pe2CknmfSxh5Z9T95ptVSNIXU0x/xdf+iBDTgQxSQiJnYSa+aj+R7himYencdKQzgj4nXRcdjQ8gdl2nq9j44k842dbNlKlTad/3AQBNgSTb22NsaomyqSVKdyTFMXe6jdNIu4q7x5m4odKATTsg7NagRCKRDjVnzZoFkjirX8AC0sQpU6fQ0tKM0WBAnVcxoP4mxaALnVmhcGbIdLqPz5unTfLeB1spnXXJgP+mVIMkozQoibpjfd6zkmQ4ia8mgLXSjD5PTaAhSMeHLgqvyEOXrR14QkMjmLjopiELobe5jtnjhvf//2ULZuE++cX0DzVYnUxf8G2UBiUau7ovZreTiqUQ+wLWRCCJQqvo45klqDv4AaueuIU1r91AINTKxKtu5/3N28hVpffGEx3ApaMpGa0i3R4qkJCotKlISjLb2mOD+OZidjlmi4XWlhamTJkKyOP6BSwjVI4cNZrq6hokScJZOrAZBUYlN1UauL7SwOxcDeMz1Lj/gRWpVwqk5DT7f+ywEk5396LWD8SoJkc2ipQBUSWSikr9DpapxEC0O46l0kq4LULXzh6KrspDZRzQNoUvi4VX/geiOPRSZtHVwKgRA/fkzMjAkvR+YUDIxMU3YEiVosvSos/R0XOwF3OZkVQi1e9nnGnNtu37ER3texBEiVGTrkGjN9LQ6WF0WSGx8LlrzCY41dw83IgnluLZkyFa/oGl6SwZjixL1NbVMnLkSIBKAHEUqBUKRXFlZSX1dbWIChUmZ+5AkJ+SeacxQlc4RZlVyaJCLZeV6vsFPtymotKWTpC3Ht3NrFmzaOoJDDbpBhMW/bB+0xxsSVOIYr1xdE4DCj10bOmm6MJs8iMCNxbOYY6qGFVXNhdf+XsyCoZ9Yea5/8E1q5FSyc913aObVvHaI9ez/tUfoEik/QNDgR5BJRBoCKKxqIm6YghnHHFRoRtfvQe1VY1JW8iwiYvSwElPgFmzZ9N2bG//0fgRd7zApGRevoZNLVH+Xh85ZzGBOTsfUaGkrq6OESNHIopiGaASe+z28ry8fKVOp6O9rZ04ikHacsQV56QnwaaWKM9VhXjsSIC3GsJ0hVMMs6q4vFRHqG/CREcdokKBwjHApGirPoQsy+QXzEROyliGmQg0pJ9S7wkfpjw73Zu6GFFiYLFB5KZxegoVVdy4cDqTK+d/buH6O5qYOfrsa1y5eC7uk/s/17XHLlyOwZRNbe3f6ZUPEmpOm1j7GCv+2iBSUibmjvWTV5PhJAl/EkEhoHVqcNhH9oMnoiMftVpNpOVUOhLRK1hcqOWrI42oRXjhZKgfAj6nlRIVJEUV7a1t6PV6srOzlRkZGaWiJAjDC4sK0xqViNMTHszAD//D0xLtq1zY1BLlb1VpL/ojc+FQS+zYd5DcUWlesyxJvLvyW7zyp6vw9Taj8ZZiKNAT64kjxSXCLXHUSiMzywzMqDCi7jNl8ViQk4fWoDDnfG7zmWo7ybgxo8763Gq1YpP8n/v6C5b/CJM5m5g3TtQd7j9+smZnEGgMIahEDPk6Yp444Y4ocV8c60gzyGDPGGCa5I2eyu4Dh7Gr0ma9M5RiXIaaOm+SF0+FPrY9RH8oGIoTiabDz8LCQhSyPFwpQ0VBflrjVAolfmmA4yQKaVOhEoVz9tL4KIT6CDPNNOvo6PGiy097v8FeF4I5RkTVQmu0DVnUET0pYxtpwVvth5SIMm5i2qg4eq3Iibog3T1xMh1qDrbnUnzzikFzRfxeqje+Tn7Z8E8tgCzx/J0EsnUC1Ue2fuprtdWfYtjiFejNAyxNgyWD7MyZyPZ1+GoCuA/24pxqR2lQoraq+oGgtIAjZExKJ28kr5YRl146cIwZzbTVe8g0p4GhuCSzryvG1rbYp7dWkhJT32sNioqL2b1rd6VSFMnLzMoimUymu6eL1v4fFJmUzMrVsLE5ij9+flIdfYS60pxsaj1RtGegP4IsoNQr6D3uw1iUQlehQDqpp/d0N/FQnIu+8RCRw/eSn62iIEdL9ekgx5ttZF/5/bPqfnVmK5l5RTiDjYwfORyTycSUKVMQPyahv2HDBuLxOGr1YHJeIpGgJMvObQs+Hjw5deoUra2t7N5/ELPFMUi4/Vj1zJuof+EdAg0hhLBA0xtt5F+cnXa6srX4qgMYCvREOqIo9enjL9M6+SwyvjeSoCTbSUs8ilKtHdR07dOMpMaCliiJRIKsrCxkyBUlWc7IyHD096840/tVirCnM3ZOOuc/Dm97I6Vlpbj84TMEYkNIpcVtHWmma4crnSAfo8KU5UznW8dPZ1eNGV8gRXGeDoNOTb1bxbH956b65k67iGDFIg43dlFYWMi6detYuXIl69atI5k822latGgRmzdvPuvzdevWMXfu2alGSZLYtWsXa9eu5e2338ZoNFLV6iZauZCSRSvOuSZnQQXd23vxVfsZkT+Sxx7+E9HtKRK+BKJKJBlOobao0Of18cl9RibNvaPPynUTDaaPCncgTFlZOb1tjf3M1cWFWmbkaND2VXeoFQKLC7VcM0zPmIzBCqDua73s9Xqx2x0IAhlKQRDsVquNYDA46EsAClHAH/t4219qUdLgSxLx9WK3lxNJpM6If1WYjcWEOIkgCjinOWh9v4PipflYJqmIdBrY+tJjaMoupL5wPL31+zke2kJiuJugaxfJeAyl+uyyFIMzj5Q9iyff28L188ZRUVZKb28v69evJxQKYbFYmD9/Pmq1GlEUmThxIvv27cNmS2vfgQMHmDx5MgpFWptSqRT79u2jpSXdhX/u3LnMmDGD9s4uHnvtXYyTL8GiPT/Z3+fqIOpL79+uXbvwer08/djT3Pb7NKFf6mPUCSJIYQVjK2+hvf4Quzb+Dl+zi6889Ebav0lIOOx2oieb+skT3pjEga54P5FxWZkeh05kS2uUHIOCqFXu77ar1hkgDJ6eHmx2GyA4lEgYDQYDoY8EfEarfKUAK4bpkUgXRElyGitN/zvN+gsnZRp8SeKRIEaj8SzqpzNjDKHgSRBAY1NjKjLgPpA+p3T5IgffeZV7XvgQV0s1x3fuJOZ0IUUkZEM3dQc3MXz6uWt9RYUS/bhFPLf3IJNrT7P04kVcckkaXAmHw+zbt49IJIJCoWDmzJloNBo6O9Oca4PBgNPpZP/+/Xi9XiRJYtq0aUyfPr3/+h9s383Gei/22Vef34FLxHnzsXvJLKxAazAT8qaJFCdPnuQnP38IQ1/htzCQ0MEuTaWhbiPe+HESgQSzFz3UH7UkZRmD0Ug8kpaFQSmypW3AhxjlUFFgUrC6LkyDL8mJngTz8rX9AlbpDdADwWAQg8EASAalIKBWazT9Gqw6U8CiwPb2NOlLJQooxHTNqyiASgS9UkTRd/zFIyGMRmM/yvXWk/eSVPhRyCrCjSAbwuhzddgn2Kh/sRHbaAv6YhVjF9xOMpFg09r/IGntxHvQh2NiWtNcXScZzscXc1srJnKst5sTjz/LA7dek34Xkl6fhuuAUCjEli1biMVibNq0CVmWWbRoES6Xi5kzZ2I0Ds5OJZNJnlr5Nh2mMuyjR37s3AqVmqKR09h3+DcIxiScgZ3sP7aP0jFF/YIFECUNPo4RS3oId0axZxczevZAnVdKFjAajcTDob7094C2qEWBeXlaGv1JGvpQw39M3ap16XuJJxJo1BpA0ChlZJVKqRw4g7X6QbzcBn/yvC0YziQCJCJh9Ho9qb5m3iqDgt7UceK+OPpKNVJcS7AxDALYx1nxHPGmmRpamS1v/IKYpZlQUwiFXnHGZoc/lXOhs2UiTbmSHz+9mhvmT2TCGWGRWq3GbDYTj8dJJBIIgoDFYkGtVp/leJ1uauEvb6zHMu0KjGrNp5p7wqIbqTr1KsGcamJ+JYmPmredmQn6qPcGCZJKH56DPrLnOrFJwwZVU0qI6R5efWiWUhSwatLtihcUaNEphUF1w9OzNYP6hn1kfWPRaN+9yRrlmfnOs0hnokCeQfGxAu7vgC6kXzvz0c0Y9DkQTGPO7oO9aCwqTGVGpIREKpbCW+Unc7qDaNhPu2sngg16DvaSf0nOGbj3p6e7iqKCzJlX8tqxg+w++ArjK4pJJBKo1WomTpzIwYMHWbFiBaIoIggCkyZN4sCBA8TjcVQqFZ3eILs64jjnrPhMnqtCqSLDMQJpmptEMEnClCDcER0ET/bfj0LCtdeDc0o6VLLZKgbndT/avL6oYH9XnGsq9KhFAYNKYGtbDHdEwqwWmeBUo1GCJ3r270VRJJVOpshKGSGeSCSwWq39pvajUe9LUmBSkGNQDCKyn2uodQbC4TAKIf0wjJh0JXVrV6EwQ8ZEG+6DvfjXd5KzMAvrcDPx3jih1jAuwylkm49kH1ii0Cj6n3qD4bMDHY7KidTteIs7Jk9GpUp7mS6Xi3A4TGFhIZIk0dHRgdvt7j9zE4kEDz31Os6plw8J7LBbK3D1bsc51Y6vJkDW3ExiDSrklIygEJCldM475o5iyNeh0ClIhWXyJ6aZNX5XB2ZnDqIsEQwE+l9E4o9LvHAyRJ4x3Y3nI7DDH5cGnc0fjXgoiAFQazT4vF5AiIkCQjwWj2HoO4s+OuABXJEUB7vjnyjcj8KrYDDYz+JzFlZgU43t/3vGRBuGAj3Nb7YixSWcUx3460OIijQrJNgUGggjgJRPxbAJFwxpw4vshn7hyrLM5s2bWbhwYf/f582bx+bNm/uZHSqViiKbfkhzSakkKqWZpF9GbVWj1CuRExL6kRLx3iQxTxyNXU2gPkCwPYKpNL3P+mQxhSOnUX/4Q9595rv9Tm0wGBzk6MZSaSf20yBZiT7lVKtUxOIxQI6JQCAYDPY7G4lwaEg3qtKmPfEz+0BPW3gXsn9g46wjzJiHmWh+px0E0GaoUWjTp0SkO4rWOZAizNCNY/PrPyfk+2zJ+YjPw+iirP7/f+edd7j44ovPzuNecQXvv//+QLw8bQKexlOfPVOlUHJkz4vEWkVkGayjLHiO+1CZlMR7k4TbI+kicqUCY4G+L2ySycubzZZVv2Dje9/DmGvrP3ODwWDaGx7C+Eg5TWYzwUAAAQIiyG5Pjwej0YggCINM9GfKi9ocuFwu9KoBJym3fDwTx34LOTQQkNvHWdFmaOje1YN1pJnuhtr04ryJ/lYMckBNxB/AZ9rLule+/5k4VIG6g8ybmaYbVVdXk5mZidl8dtM0o9FIfn4+VVVVaXZiSTHKIb6NzpFXBNYw/mo/AmAZZsRfEwBR6tdgKS5hqTSnKbQNJppbNtPgX0086kertvZljkRcLhcGi2NoAg6HEAQBh8NOT48HWRDcoizT09vrQa/XI8sy8VBgSBe35hZTX1+P0zL46cvNG0G5ehbUKvppOtmznURdMaLdMUIBF1JCQkpIqIxK5JSM0pdH2HKKVCSFT3WYIx++9qnXkaMTUSgUxGIxqqqqmDq1n0HKnmMn2Xt8QEvHjBlDVVUVkUgaoM81DC3nrNFbSIVT6AsM+OoCmEqNhFrDxLxxMmdkpOuWFGl6UrA6irI0QNLaTu9RL8YCPc6sdJF6hsVIfUMD1pzCIQo4iCzLWCxWvN5ekIUeURCEls7Ozv5NUUaHlmFRqNS0drowDzjmtG57iWXZtXxzrsy9sxRM6EySdcCDvilE3oXZdO9yk0gEEf02RFXatut8w5ENAZLhBKm4hKgWqDn15qdaQyIaYVhWWlvXrFnDZZddlkaIolH++Pwq6gwV1JtH8dPHn+sPC5ctW9ZvqqeNKsXf0TSEcziBqcSAv9aPLktPuC2C2qzCXGbAXxdI1xYjICfANFyLqBToPe5Dl61FDFoYPjUN0Fh1Ktq63f0tIT/rUMf9aUdXoaC9vR0BqVUUoKa5qak/yLcohp4EdwdjlBXkEPSk37CaDLTRcOQZ2pt2o1QKZJgkxg4zcmW5EZM3G0tpBlFPhAzzeFQmJRpvEZnZo0lZ3fhqgqgtadMeSNbjbqn7xPk9J3dzwdyZ7Ny5k6lTp6JSqThZXct/PPk6kRGL0Dty0NucaKdexa9WbeLIiZOIosiUKVPYsWMHE8eNReqs+4znXphkIoqgEEiGUqiMIsmQhMauRm1VE+2OonGo0z5HXy1XsDmMnJIx5OvJy5qDRm8k6OmmJC8LVzA25P23KFNIqbRD3NzcjCQoqkVJEE41NzentUenx2EYeufWnpSCmVMn03pkVzrOm7CcI/XxfjQnEEhiNinJzVQzadRcbv/RJrQ40UgZaGQnl97wGF5/NYKQrnIQ+sACpRVOn/jktJ5TlSIYDBIOhykrK+Pv6z/khQOtOGddNYjEIAgCxtHzeOVoN0+++Dr5+fmEQiE6OzvJ1n22spbDH76Mu62un80Rao2g0Ajo8nREOqPocnV9MXD6uv7aAOH2CPZxVkSvg+kX35W2dod3MH3yRDzJoe+/06BBb0gfkS3NzYiieEp0uVynOzo74oFAgPz8fBRSglQyMaQJDEWjcLlcqCPp90lYckqJj32Qo212DlX5USoFivN0pFIyx3ftpvt0NfNuvo+9b77A8CmXYXJkEwinaaXJ4GBLEv8EVCuVTFBk0/Hee+8xe/ZsHnl+FYfIxVZ5/qYxjooJdOZO4eG/vMiMmTPZsGEDY4uzCHk+XYN1WZapq3qPRB9xwJCnI9QcQpZllFoFwaYQxsIBn6T3mI+4N0HmdAdyUMuMWQ9itKVbNWpifro6OzGXjhlauJaIIyRjFBQU4vV66erqinV1dTWJQBJJbjh5sory8nKkVBJf19DenZg/eio7duygKGPAa80ZuwjbVc9yqFamMFdHlzvBtvZRTPvqf3Jk/Rp2rvwryXiMnpaGtLmTgn0LHoj7kuEU1Xvewdt1fi/XdWIvQsRP2bBK/u2JV4mNWITB8cn9nHUWB5pJl/OL1z6gsKyCoNdDtOnEp7rfPe8+gSdwCkkV6wc1Umdk31JxCUUfjznqjiFqRDKm2Am3xUl0i9ScWMvud/5M0NNNkcPEjp07yRs1aUh77+1oRpJSDBs27KPIoA5I9bEqOXXi+AmGjxiRbjRSd2JIkyg1WqpOtzG6JJ9Az4AWhHw92Bfdyltd5bzS6OCQv4nN7/8QydFDxaIZZBaX03R0D2qdHpG0SZPOYJCEO8IoKty8tfKW83rUQk8jda2dvFUXIGvOss/EwhQEAdv4BWzshL3HTkFP8yf+prPhGNWNr5NKJEnForS820HLO+0kgon+WPcjx1FOyaiMKgz5acZlpDtETHDR1X4cAZFkPMbo0nxONnWgVGuHtPeuhpMIgsCwigpOVlWBzCn4iBctsG/v3j1kZWURCASQh1igBdAp6VkwZyYtu9elzxx3B28+fyv1/lfxCFUElS3ElN3ELe0EtVV0iRvRjY1gyDdQu3szOm06BlRoFaSifQhaMs2hli0BDlb/nt3vPXGWqTy0ZyepcZfhGDFlyGs3F41AOX05B/ftJfox4WI8EubDd38K5iD+uiCzbHP51YO/xhKzEW6NEvMliLljaecKCDSEiPXG6a3yYxttwT7WSrZjKtd+4zWmXfp12vd9wJwZU3EJQ29yrvA04fP5yMrKYs+ePQgiB4G+phIpedO2rVuRZRm1Wk2Bdugc5KJZl/DBxo2UWtNPojkjh+LSC2hLvIM2Q0OsJ46v2k+gMYTGpsY2yoIuG+xzlLz5128wYfGNtCUbUFtVJENpwrhSrSbqimIsVCLqU5xqehHHwXKGTVzcJ2CJi7736JDf1XDm0JpsLP7+nwZVAQ7W3BMc3fUKMXMj0Z4480bP56rLl3JdukloGk1ri6AyKFGb0nh0Oh5OP7hyAjJSs1ny9V/1U5JK7Do2bFhP0cyLh7zufKMCKZrGMnbu2I6EuL1fg7s8nv0ul8tfW1PDpMmTUZEi0N0+pIlMGdls3n+ExdPH0VF9FIA5Vz6I1p+ui9U41GRMtlOyvADLcDPdu9w0rm4l5onjnGvi9MHt4DOjy9IS7YmTCqdQaEVkif6qCMEQ4+CuvyLLMqv+cBs733r0c3Oc/9Fkn6tdY1fTSd564h7avVtAAPcBD9+5/zvceeedg9A2KSmT8CdIhJIETofQ2tUEm0IE6sLQlsPsy7/dL9zOuuNcMGMCWw9WfaZ3QAxC77rbUcopJk6exMmTVbhcrrhKpdrfL2AgKcPWbdu2MXv2HGRZouXYniFvkN9URHlJMcGaPhK33sAFS3+BsjdvsNedp6NoaT7OaXY6Nnfj2ushld2JLlKIPlufblEUykehSlf/+6oHzGZYW8/+957FL1ZR532RVU/cTE9rPV/WaDy+g/dX30dM8CCY09qtjxnYt29ffx2wyqDEOdVB3kXZOCbaMJelC9KklEzcnwBRIqJp4PW/XM3bf3oQKZUkcHI3pYUFBK0lQ15b85EdJJMJZs2axfZt25BhZ3t7e/hMASMgb96+fRsOhwO/z4/a2zzkCctnL+GFl15m3ugyQp7029nseWUsveVprNEpSCHFGe69hCFfT8mKAhRaBa49bhpP7iTfsYhkKMXIcdcgokZtVRFqHXihBd44p/atRGFNkQwniVobeG/N3bi/YCHLksT2Nx/hw60/wOdtQlTLfZ/LxCJRXnjhhYGH9ao8Mmc4SPgSdO9y07nNRbg9gsauxjbaiiHfSLZ1OvMv+U8u/eaviAZ8zB87jOdffJny2RcNeY06fzuBQAC73cH27dsRZN7rT4YMpEXkjTu2bycej5OVnU2RSUkiEh7ShEqNlsMeWLJwDi3b3+r/XG9xcOWdjzNr0sM423PJbxax7+tlelcUfV0Ac4mRzDF5RF0RGrYcwmkbx6gZSzEb09isPkdLoD6IwyPw3Dd+yOLcbnQdESJdadOdsrn54I0fDTmO/8fR29XI6r98lbreF0kpgshJGaEPRQw0hJAzZI4eO4qxUE/B5bmEu6K0b+oi2hMjY5Kd7DlObKMsaDM0KPw2xhZ9i6Vfe4qKSYsRBIHGzatYsmA2VUHVkL3nRDRCsVVDTk4usViMnTt2ICilfgH3q1IoFO1SKsXlY0aPyVywcAHHjh6lvt1NRsnwIU1sLRxG7aZVlBfk4lbaUfWxErtObGG68ihjbUcZlQfhcIqyAh0zyo3ImqtZfOsTzLv+Pva+8SzJWAKVRotaq8cbr0JlUdH5YTc3XbEIVWA/NkOUPI3IwaM+NEVpQCGh8pDoEskfNvlzCber6STr3vgOMXMDgijQvbsHc5kRhVpAoVXQc6iX3EVZiAkNhlIt7r0eVEYVuiwtCo1IMpJCqVUgx5RYUxO4aNlvKR0794zQ0cN4Y5R9u3dhnHl1f7uMzzpqt7yNNdHLtdddx/bt21i9alVVt8vz47M1GJAlXl658nUKC4tw97gxeBuGvEEavZF97RGuungRrR+u7P+8OHaMTF07spTWMr1OxBtIoNWI+E+t5/kHb+RPt19IPByis66KdY8/zORFtyF6HWhsarRODccO7SAUSDMkcx1qSvUK4u2Rfkiw8fQHn0u4yXiUD99+iKSlvV9b9Tk6Ev4UCoNI7wkfluEm/FUxYuEQUixFxhQ71tEWTKVGjEUG9Dk6Yi4JdSibYSOXYM0a3Pm2eeMrXLZoHodcyUEJ/s8c2gWa6enpoaioiJWvvw4yzw0KnwbZcr3+dHNT4723fvWrYsAfQIhHCFoK+ikkn5nKUjaK3aueZtnFC9l5vBZLVj6nTx0h2vIe+r6zrKk9gs2swmxUcqI3F/WwXDTZAqZSE0VTxxH1RTj49komX3ArXZ2H0BeqiFf7mTTCTGNrmKq6IBa9kmh7hFievi975KMwZwH6T3hhVdjTSbhqJ+GOBtSZhf3gyKbXH8aj3IsgQLw3jr82iGOiDanDgtKWINAQIhUSkGWZzBk2NBkaUtEUkfYoodYI4dYwkc4oUiJJQuGlw7uDhgM7yMwZg95sp+34Pq6fWclrK1eTfdEtQ34XVMDdSaavgWHDhpGXl8/3v/tdKZ5M3R6JRPznFHAkEgnotJq5eXn5pcuuvpod27dT39RC1vAJQ1qAqFDS7PYzvdBG9ZF96ErGYymdTFs4h6bWEC6/isa6dnIzVbx7MExLjo+ooo2kupeUxk9M0YW2JEXQ3cPRN96ncuyVRJNdJLv8eF1xBAHMRiWTxlg4XBUgnK1DEAVELWijuThyyuk9voNIwIf+H2DLYHcbI+JN3HPDFcwbO4wP3lqFpmAEvZ2N7Nv/CIIuQTKSonObm5wFmcgxJdnW6TQfOoQUAX2umpg3ir82SKQjAgioDEq0mRoM+Tp0WVo0djWiQiThjxMKdVOzcyMmcz5Wz2kmjShjW6/mvH3IPpV53vA6+riPW269lVUrX2fjxg0b3T2ePw3yh84G0Hnh9ddfW3T7HXcQjUYo0ylI9tXKDGWUTlvE4y//kv/83n187/EXGHnZLeRNvBgmXoy3u5X2ujt5zdeO5BQJHPMRc8dIhlPIsoxCLaI2q9A4NTjnmtj58tOMmn8pYraacRU+8rLSDJBITKIrKRM43EvG5LTWBvydKI+s5RffvIOubhePrVmLddoAqU7ZdpRr70g3Me3s7CRfk6Tq8FaOn3gfwZquEuza5iJnXiaR9hhGIY/Gni1IcRnRIBDzxtKdaAvOX/GQ8ovYtSPILppI5YRLyCgo5+Tbz3HfN6/jh7/8I5XXPzhk4aYSMcq1UaLBOBaLJW2eJV44K6b/xw+ysrIMcirV+Pe1azMcDgerV62iWspg5MXXDnkxAXcnjpr1TJo6nVePdlM0cTapZIKXf3MNUl4rcV8izegwKPu9Ajklk/AnSQSTxH3xdOPPuIQcFtFqMpg0fxpm3x40GiXHO3wkxlloeLWZkmvS4VZJ1wRuWX4NkyZOpKSkmDff28BJ67j+B7V93bMsGltKTk4uR0+c5IZrl/NvT6/hvd2/J6npoXOrC2OJEYVaxJCnQzxH85NEMEWiU0Qh61Db1EhyEgERkyEPq7WMUZOXk1M2kB1qPbqLZZVWDu7bg3fEEoyOrCHvadX7rzAMF9dcex3dXV0svepKl1KtKf4o/j2vBnd1dYWynI4/PPK73z386uuv0+vxkGdIICXiQ2YamDKyqW4qYkIsTLncTW+vC6PNyYXX/YwP1v4HsrmpP/c7aHF6JYP0w6vHqhyLu7aZfXs2orUYUGtFAl0y2pMBsuc66djiIv+ibObPncfyq5fxje/9mN/+x3cpysliX3sP1qw02GLNK6G4uJjHn3mOybPmo9FoaG84QlRy0bPNg6XChKEoDbb0VvlInsEsFfoONlEtojQo0doTWA3TufC6X6A/z6tnwz4PZbIbpWygQV9G4ecQbiqZoBgPAX+A8vJyfvD97yEIPPKPwj3rDO6nfmi0R5qbGr9xwQUXaCdOmkjz6QZqWzrIKBkx5EXZcot57++reeCWFaxf/TKGkrGYHTkMH38FgYYAvu4OJGV4ULuDdF5YRhPKI9+2GIdlDD3+YyRzWrCMMKAvVKLJBVOFDoVGJNKVQIonkSWozJ7Ewlkz2XKsHjkeRqtRcfTYMTJjXfTUHsWkSHLVRQt5d+s+brz8AtraO3jkyV/Rc7oDpUFJIphmRCpUIsZCA+ZhRoyFeoyFegwF6X/0uTq0GRoSPSKyJFO3ZxsVEy84K+RJxqN0bXyBu25azi9fepdhC5fyecapjW+QSZBrr7+OluZmfv6fP/PFk6kbo9Fo9FMJOBqNxvQ6vbnH0zPna1/7Om+sWYNVjKMqm/S5mqE4h0/k9cd/zX99/z5WPvsktoqJKFUaikfNZvTEa9FEclDHszAIBVhVo8gyTGfy1G8xae7tnDzwFm3R95EMflLRFKGmEP6GEP7aAIH6IDFvAlGZhgt9pwKImkymjx/L7Akj+XDbDq5ZegWd1ce484blONQwYXgp7R2dOC0Gxo4exT0PfIdDu/aQjCZQ21XoMrVYK039ce1Ze+SOEe6IInUZWHjJwyxc8e+Mnn3VWcKVJYnTb/2F//z2N/jBL35H5fK7P1PFxrkS+7razfh7Pdx44008+OB3aKhv+FWPx/P+OXH1810oz2RyJLWaxs1bthhTKYm3167lVNzAqMtu/XwxZixK+5uP8uPv3sv3fv8Uw5d982O/HwsFeePpO4hZ6/HVBQi3hJESMhqHGqVBiagU+qshUvF0WUy0WSDSFaM4L4dLL70Me4YDlaggM9PJV77yFV5++WUEQcTn99HR2cV7775HU1cP9vxi7PmFSAYf3uQJ4rFQf8pSBpBkUlGJRCBBIphEqVdiLDagNziZNOFuRs9cdtb6T675M7+6/3b+4xe/IX/pff2v4R3qOP7WM1SqgyxdtoxUSmLxwgUhhSpW3N4eOCeB/LzqGIjHI0aDznL69OnZd919N5s3byJLIxM05qD5HC9nFpVK1IUj2PLqk/zw7jt57dkncQyfdM6nOpVMsPaZuwiZTxH3xNBmaDAPM2EuN/a9rEqTfjGGRYXaokKlMDG76Cq+ctX1yMkkXvTs2rWLt99Yxfp167DZbFx55ZWsW7eeH/7wh6xauZKj1fXo88oZvfByJl16PVOvuIVMUx6V2lwy9SaCUgAxM136+hHQYsjXYyo1YijQk4qkCPd46eo+hM00DFtWuqJQklKcWvNn/vOer/LbPzyG7cI70Josn0u4ge52SkJ1pJIJli67mv/zja/T1Nj0665u79vnzRN/3AUtVtvO0/X1N1VUVlivv+FG1q97H3djNY7RMz/XQlUaHUlHMdtXPcPD37mb1X97AmPpmLNaNkjJJF0t1fg9LShtUn9jsbPMVlBE6ytnlGYsz/3ht0iJOP/2ox+SCHopGDedadNn8NSfH6O0pISKigp6e3v51r330ZtSoXIW0Vl3ggPvvsqeN55l78onKdIm+MqKq/nmV77JRRMuRuVRoYqpSXiT9Hb7kMJKlDEbBqEAm6kSp3MMJlMRjYd3UzZ2PgD1a//KLx/4Go8+8SSqWdef8zW5n3WcfvNxYr0uvvu97/PO22/z+ON/ahGVyutCodB5wfdPpBA6nfblWc6slTt27Wbjhg20t7dzUllI8dQFn3vB0YCXznf+ws9++B0e+sOTWGYuPedLJHs7mzi641W63UcIhbtICSFESYNOl4nDNpyiknm8/MM7ufPWm3nkkUd46qmnmTVrJkVFRfzmj3/iP77/IJ3dLv7r8aeZOGo4R0+c4vYbljN8WBn/9ovfEXOUoI/0oAm7eefttezatQulUsn9P3wIiscjBb388MZLsNmsvPLGWo6J+UghHwqdEVtR5VkhoW/XG/z4njv54c9+Se5l/+cTXwH/qYR7YAuV4TqKi4tZuGgxs2fOoLOjc2l3T8+bH8v0+KQLh8ORKkGWpsYTyWHfvOsuXnrpRaxyEDlnOEqN9nMtWqnRYiifxGuP/4Yf3/cNGg9s5dTplrPQHZ3RSvHI2YyafDXjpt1MacklTJ77NcZNv4Gy0QtJJZMoVWoWz57GhLGj2XHoBGNHjWD/vr1cf80KVCoVv3vpLezzbyRkK8FYOYXd27ewcNIopk8ch+ht42s3X8fcOXO47bbbMNgyCSsMaEfNoWjKQgz5FRze+j6zJoxhzIhKpK56phZn0NxQiyK7fEAI+zaR56vh6zcs4we/+D2lKx5A8zkaqPYrgr8X3ckNdLS2cN8DD/DwT37C1q1b3+/u6fn3T6TyfJoJ9Abj3iOHDn7t4iUXKxcuXMTenTtoPbaXjLFzPvfLLxRKFfYxM3ntpRe4ePJIJhQ5Wff233GUjzmLguNvPoW96ygTbRL2aBedtcfo6fWid2RhUyS47aoLMRj0fHCsgZ1VjSjDHqZNnUpnVxcftsUwZAyUo8p6G2LHSSrKy6mpqSE3N5eV727k1a2HEUcvZuSFy3EWlvczPAKSGm/9cUYMK6WsuJCcrEwSQR91ARmlWsvJt5/ltvljyDDp+NVLbzPy2vuGnCH6R75Zw5pHUSVCfPvb36apqYlvP3B/BFG8LBQK9X4iO+VThzgOx/fLy8t+sX7jB+zatYujRw5zImpgxJKb+KJG69E9FPtPccvNN/LHv72C21JM0YQ5/X/31B3la9OLKCkayMy4e3o43dTMuNGjUKvVNDQ28eSuJhwV4+k+sQeHECUSi6Mfu+AsUN+9fQ152hRdHh+RjHIyx846yw/4R/xa03mCHLMOQRCodwdxp9Q4wm088NXrefpvz9JkrqRo4pwvbE9OvP0sEywSFRUVzJs/nwsvWExtTe13u93uX38q+tFncYAzHY53l1697KIn/vIkP3v4YYwmE83OieQMH/+F3VDQ003Le89y941LSYkK/rpmPVmzr8Lcx1dSHV9Pjs2ILxInx2bkgrkz0WrTR0VVdQ0vbTmKddKFfNnD7+qge+db3LnsQkjE+fOrb1Gw5FYMNucXNkfHyQOU+6rw+318/wc/5Ft338Xrr73+XrfbfRkgfdECJjs72yklE4f+8OijeVdfvZxv338/JocT9dybBzUQ/0I4UPu3YGzZz4P33c3mHXvZeLAKx6SLSIV8mPLL0OiNxCNhPKf2ohclpFQKyZaP/XOgbZ+K5dHeRPfe97lw8igumDuDJ556hnbbSAonzPpC5wl6upF3voKro40//vGPvP76azxw//2tSnV8wvli3s8t4LRX7Zxr1Gk/eH/9BqVer+dXv/olgs6M8/K7h5w3/riMyal1rzDWInPrzTexbe8B3t97HCGnguKJc76Ql1992nOw8eA26Kzj4qmjmD11In977gWO+ZUMv+i6L+SsHQzuBOj4+x9Qp2J85zsPEggEuPiiC5PhaGiBy9W7/bNca0g7lOV0/Ki8fNjP1r79Du0d7bzw3PP0xKHsugdRqDRf+AanEnHqt6ylTOzhpuuuJRSN8eaGrZzq7MU+aibZ5aO+FMF21p2g98QuhufYuOqCueg0Kp5/8RVOhjWMWnLD544izgdFnl71e5xauP6GG8jOzuaySy6hrq7+B66env/6rNcbqgoImQ7HMxMmTbx19Zo3OHLkCB9u3kRdT5TK67/9ufDqTxT0ng/QdJ1izthKllxyCadqatl5uIpGtw9PDDIqJuAsrjhnh7yPhVDjMVyNNbhrDuHQQHGGhZkTRlFRXsZ7777LtqO1JLIrKZu2aMhZtU8UrpTixIv/RalVy0UXX8z48eNZcfXV7Nu396Vud8/NgPzPEjCAKjMj4+9z581d8vLLr7Bp0yZOnDjOwVY/Y264/0sTcn987u2hYdf72KI9VOQ5mDljBiNGjOBUdQ1HT9XSE4jQ1RsglEiSSErEU1LaK5EFREFGrRBRKUWMahWZViMOk46xw4cxvDJd27Nz925q2tx4tU5KZ178hYAVnyTc46/8nnE5JoaPGM5FF13MLTffzKYPNrzT5fZcBQyJ2f+5DrHc3Fx9MhbbsOLaa2Y++tifeP21V2lpaeVYu4cR1377Cz+bPi4/2llzhJ7qQ1iI4dApyLabKSkuxul0YjAYMBgNmExpDD0Q8BMKhgiFQrhcLhpOn6bbG8AVTuIXdGRUTiC7YtyQuVJD8jVe/R2jcm0UFhVyzTXXcvdd32TVypV7BYVyYVdXV2io1/7cXkqeyeSIa9Tb7rzjzhE/+/nP0+Zs21bcUZmiZfd+IUjOUB2jgLuTsLeHRDhIPBIiEU3nw1VaPWqdAZXeiN7qwJSR/U9z2M5CqYJ+Wt58lPJsG2PGjOXiJUv40Q9/wNNPPVUrKJSzu7q6uj/P9b+Qu7Lb7fkKUVi/fPnyEX/446Ps27ePtW+9RVgSsSy6dcg1N/+vj1Cvi573/4pBlLhy6VKmTJnCg9/+Ni+//FJVUpIv8ng8rZ93ji/koIxEIn6VSv1yTXX17H379hZ+/RvfoLSkhMP796By1dOTVGDKzPtfiZ4xuqqPoD72LjG/h6/edjsjRozgq7fcwltv/X2vUh2/oLvb1/lFzPOFeUKxWCxqsVpfbWqon7B9x45hX/nKLUyePIV3336LYSY4tH8fmZUT/ttM4b/KkGWZU+tfoSLRSltzE9/7/g+w221cs2IFO3ft2CAL4qVdXb3eL2o+8YtcfHt7e7jL7bly//4DT1926SX4A34e+9PjhIIBJjuV1Lz0C8Je9/+3wo34PZx64eeMUgeIRsL8/pFH8Hp7uXTJEg4dPPhCt6vnUpfLFfwi5/wyYhkpHA6vjUaikVdfeXm+xWoR77vvfgJ+P13NDSi7amlx+z4X4ft/4qjbtQ5T7RZUyTAzZ83mK7fcwupVq/jqrbckurtd3+9293wXSH3R835pwWo4EtmhV6vXfbBp0+LTpxtst99xB+PGjuODDeuotKo4seUdBHveJ5aX/E8f3o5mTr/xGONsAt2d7dz/wLcpLy/nW3ffxW9/+9uWZCp2ebfL89qXNf+XikYEI5E2q0Lx4omaU6PeefvtivkLF/LVr95GV3cXrbWnKBADHD20H0fZ6H9azPnPGlIizsn3XiSz+yhaIcHYseO4+1vfoq62luuuWcHOXbveVsfiSzp7fdVf5jr+WR6PkJmR8YAoCj9dvmKF/qc/fRitTseTf/kL4XCISFKmRZFJ5aKlXwqW/c8cqUSM6o2rKaQHNRKpVIoHvv0dUqkUv/7Vr3jm6adCUir5711uzyNDgR7/VQUMgMPhyFMI/MLpdN7844d+wvIVK6ipruYvTzyBxWpBrTNywgfDl9z4hWemvuyRiEao2byGwpQLi0GHq9vF7XfcQfmwYbz+2mv89CcP4XK731YoU9/q7PQ2/rPW9d8Ss2RlZFwmwx9nzJhe8uOHfsKEiROpranhmaefxmQ2IQkKakJKCqZfjDW36F9asL1tjbTuXkelKQWpBKFQiNtuv4Py8nIOHjjATx76Mbt372qQEO9xu93v/LPX998WlObn5+vi0ej3QL5v/oIFlvvuf4AZM2bQ1NTEM08/hSzLmExmOrxBXNoshs25FJ35X8Mhiwb9NO//EEe4jQytQCAQABluv/MOCguL2LlzJ4/8/nds+fBDL8i/V2v1v25tbY38d6z1vx11yMjIMCkE6TZZFr4/deq07HvuvZfFF1xAPB5n3br32bVrF2aTCYVSRbMvTkCbQc6oKTiKhv1T19nTVEvHib2YIi4KrVqSiTjt7e1MmzadZVdfjcFgYO/ePfzql79k29ZtbuBP8WTyEa/X6/3v3N9/GVgpKyvLgJS4Q5aFBysqK/OuueZarl6+nNzcXDo6OnhjzWoaTzdiMptQKlVIgoLWYIKIMRtH8XBs+aVf2LkdCwXobTuNp/EU2mAn+UYVopwimUwQ8AcoLilh6bJl5OTk0N7ezupVq3j99deoqa7uBuHPSUn6ncfj8f8r7Ou/HG5YXl6u8fk8lyMLX1GI4sVTpkxVrbjmGpYuW4bRaCQcDrN/3z527dxJr7e3/1UEgiAgqjR4Ikl6YzIhNIg6I2qtHpVOj1prQN1XchMP+olHQyQiYeLRMFIkiFGIYVWDXadCSsSQZRlJkujq6sJkMjFj5kzmzZuPxWIhGo2yfv06Vr7+Ops/+CCRSCbfQ5SfN5vtb9fV1cX+lfbzXxoYtlgsNq1KtUKGr2i1mllTp01j9uw5zJkzh7HjxqFUKvH5fNTX1VFbW8vp0w34fX5kZHRaHWLfa9lkWUYQhP5udB/990e4uJSSiEQjCAiYLWZKSkoZNmwY5cOGYTabSSaTHDl8mO3bt7Ft2zb27d1LNBqtkmWeF5XKv33elN7/twI+c2RmZpbJcuoSQRaWgDzXZDIZZsycydSp0xg5aiQjRowkNzd3sKmNxejp6SEUDBKODPZx9DodRpMJu92ORjM49m5ra+PkyZNUnTjB3r172L1rF4FAICggb5Fk4T1BoXi/u7u7/n/Cvv1PTe0osx2OCbIgz5IFYTwyw4FKg8FgLSwsorCokJycHGw2O3a7DZ1Oj8FgQKlKo2XJRJJQKEQkEsbj6aW310N7ezvNzc20NDcTDoV6ZahB4JSAfCglizvcbvdhhkib+V8Bf3GOWmYqlRqhgAoZ8gRBdsiy7BDALCNoGMieSQJyTAa/IAg9siz0CNAmCUK1KIqn/pVN7mcd/xd1ik5cyCKnxQAAACV0RVh0ZGF0ZTpjcmVhdGUAMjAyNi0wNi0wOFQyMjozNzo1MiswMDowMLXRu/0AAAAldEVYdGRhdGU6bW9kaWZ5ADIwMjYtMDYtMDhUMjI6Mzc6NTIrMDA6MDDEjANBAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -34495,6 +34707,16 @@
           <t>NWA Council, TechCrunch, Arkansas Business</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arkansas.gov</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHgAAAB4CAYAAAA5ZDbSAAAABGdBTUEAALGPC/xhBQAAACBjSFJNAAB6JgAAgIQAAPoAAACA6AAAdTAAAOpgAAA6mAAAF3CculE8AAAABmJLR0QA/wD/AP+gvaeTAAAAB3RJTUUH6gUaAwIbNlq/+AAAciFJREFUeNrtvXd41NW2//+alkx6rwSSEBJCCb33XkPvCIIKiiAIiqKoKIgUEem9SBOQ3nuH0EsoAdJJ720yM5m+f3+EjOYAHs/9nnN/59x71/PkIWQ+Zc9ee6+9ynutJeF/BrkFBQU19/PzawnU0uv11TUajWdZWZmTRqOx0+v1cqPRKNXr9TIApVJplsvlFltbW5O9vb3Wzs6uVKlU5igUikSz2RyTkJBwQ61WPwCK/9MnRvIfOGaFk5NT81q1ag0tKyvrnJ2dHVRSUmLftWtXWrduTXh4OMHBwXh6euLg4ICdnR0ymQyJRIJMJgPAbDYjhMBsNlNWVoZaraagoIDk5GSeP3/OlStXxPnz53FxcdF6enrGmUymkwkJCUeBu4Dp/xj8zyf3li1bfqxWq/snJibW9vT0lH3wwQeSXr16ERYWhr29faWLi4uLSUlJQaPRoNFoKC4uRq1Wo1arAXB0dMTR0RFXV1ccHBxwdHSkWrVquLq6VnqORqMhLi6O48ePs27dOktBQYGpatWq0SaT6bekpKQtQOH/Mfi/TjYNGzYcZTabP0lMTKw9ceJEyaBBg6hbty4ODg4AqFQqrl+/TkxMDHFxceTn52OxWHB3dycwMBAHBwecnJwqMRJArVZbGV9aWoparSYlJYWioiKkUimenp7UrFmT2rVr06pVK5ydna0Mf/z4Mfv27RNr1qwRgYGBD0tKShZmZmYeAIz/x+C/QA0aNGhlZ2f3/dOnT9t26NBB8fnnn9O8eXNkMhlarZaoqCguXrzI06dPcXJyok2bNtSpU4fw8HA8PT3/KWPIz8/n+fPnPHnyhKioKEpLS6lTpw4dO3akdevW2NnZYTabefjwIfPmzbOcOXPGWLVq1ZMpKSmzNRpN9P8x+DXUokWLnmq1ellJSUmNZcuWSbp37469vT06nY4jR46wb98+ZDIZrVu3pmPHjtSpU+dPn1dcXIyToyMyufy1nz+MjiYjPYOGjRvh6uKC3d+I+b+lmJgYLly4wPXr17FYLAwZMoQ+ffpga2uLVqvl1KlTTJkyxWJvb/8kOzt7YmlpadT/MbicsX00Gs1Per0+dN26dZL27dsjkUi4d+8eO3bsIDk5mV69ejFixAicnJxeub+srIzz585x7+5dyrRlhIaFkpWVxZFDh9n66w5q1ar1yj1Lf/4Zo9HIe+PHc/zoMU4cP86uPb8B8MvmzaSnpdG4cROaNG2Ct4/Pa9957Ngxjhw5gkKhYOTIkXTu3Ll84Tx8yOjRo80qlSpVrVZ/VlhYuJ//jdSmTZsONWvWzGzYsKHl3r17QgghjEaj2LZtm+jZs6eYO3euSElJEX9LCfHxYuXyFWL/vn3CYrEIIYRQq9UiNLi66N29hxBCCI1aI+JiY8X5c+fF66hhRD2xZvVq6/+XLF5s/X3Rwh+FSqUSJ4+fECGBQeLdMWPFsiVLxY7t24VOp3vlWS9evBDff/+96NWrl9ixY4cwmUzCYrGIu3fvinr16pmqVq0aZ29v3/B/DWNdXV1dW7RoccbX19dy8+ZNIYQQer1ebN26VXTv3l0sXbr0lYl8GhMjYp48ETFPnoi3ho8QIYFB4tjRo5Wuadmsuahfp64QQoj9+/ZZF8zrKLJnL1EjKFh8/eVMoVKpRF5envUzlUolhBBi7eo1IiQwSOzeuUuYTCbx1vARwvSG5wkhhMFgEFu3bhU9evQQS5cuFWVlZUIIIa5fvy68vLxMoaGhuwDn/9HM7dSp0wRvb++yH374QRiNRmEymcSaNWtEz549xa5d5RNZQSaTSZw7c1Z0bt9B1AoNs3529cpVERIYJKZOnlJpgocMHCRCAoPE/n37RI+u3cSf0dOnT0Xblq1ESGCQaNOipXjy+PEr14x/7z0REhgk4mJjhRBC3L51+5VrKhbSH8lkMomdO3eKXr16iXXr1gmz2SxMJpNYsmSJxc3NTVu1atWJ/6H+hzdTvXr1AurWrZvUvn17S05OTvmE3b4tevXqJbZu3WoVtUIIkZiYKB7cv//KRN+5fce6KxvXbyDq16lbaadPnTxFhAQGiQP79ov3x42z7qC/3XXZWVlCr9cLlUolvvjscxESGCTat25TaQwWi0U0btBQNK7foNLf/0hz53wvOrZr/8ZFZLFYxJYtW0RkZKS4e/du+buzs0WbNm1MVapUuQd4/49gbrt27Ya5u7vrd+7cKYQQoqioSEydOlWMHTu2kmhMefFCrFqxQvy4YIH4aOJEYTabhRBCHDp4UIQEBom5s+eIh9EPxcrlK0SfXr1FSGCQOH/23O9n54KFIiQwSJw5fVqkvHghcnJyRF5enoi6dq3SxF+5fFlcvXKl0vkbFhIi9Hp9pXM+JDBIjHvn3dcybv3adaJ54yaieeMmlT5LTkoWu37dWUkS/fH75ufnCyGE2L59u3B1dVW7uLh0+Y92g3bs2HFLQECApUJZOnDggOjVq5e4c+eOdQLS09PF97Nni5ohNcSihT8KIYQoKSmxnoUqlUrUCg0T4TVCxZnTp4VOpxMXzp8XIYFB4rNPPrU+59cdO0RIYJDYuH69EEIIrVYrPpo4Udy4fr0SE44cPiy6deosMjIyhBBCbN60SXz+6fRK1/y2a7cICQwSa1ateoW569asFUlJSaJ/nz6ibq3alT5fsnix2L51q1iyeLG4eOFCpc8qJNahQ4eEEEKkpqaKKlWqGKtVq7YMkP1HcbZ+/fpVatWqlTJixAhhMBiE0WgUX3zxhfj444+FwWCwfumN69eLWV99LfLz80WDuhEionZtUVBQ8MqueW/sOyIkMEg8jH5oVcrq16krGtWrL8rKyoTRaBRLf/5Z1KtdR4wZNUr8smmzWLzoJ7F+7TpRcST8UVIUFxeL/fv2iV2/7hSHDx2qJMbj4+Ksity1q9cqMXfFsuXixwULREFBgRg+ZKioERRslTQV2rsQQuz57TcREhgkPnz/A/E0Jsb6udFoFN99952YNm2a0Ov1Qq/Xi6FDh5r9/f2jAa9/BS/+6SunadOmdbKzsx9+9913XnPmzCEjI4MxY8YwePBgJk+ebHX4A5SUlFA3IoIaoaEYDAauXb2KEII2bdtWeqbeoOf82XO4uLrQuk0bZDIZVy5fASGwsbXF38+Pxo0bM+3TT+k/cCB16tbF08sTk9lEfHw8UVFRXLp0iXPnzhH98CExMTGYzGbs7O2xVSpBIsHFxQWZTIajkxMhNUKoHhKCRCohtEYNkpOSWDh/AcNHjqBTp85cvHCBK1euUFhYyHvjx2NjY1MeBbFRUKbV8uEHE9Dpdaxau4ZzZ89y+tQp2rVvj1QqpUOHDsjlcqZNm0br1q15//33Je7u7r7Xrl0bW1ZWtvffOoLVvn37lt7e3vozZ84IIYQ4ePCg6Nevn1Ucvo4qzmGVSiUa128g6obXErm5uZWuyc/PFzWCgkXTho3ExQsXREZGhoh9Xq7d6nQ6cfHiRTFr1izRp08fERoaKgIDA8Xo0aPF0qVLxfbt28Xx48fFlStXxN27d8Xdu3fF5cuXxfHjx8X27dvF0qVLxejRo0VgYKAICwsTffr0EbNmzRKXLl2yKnHxcXFi2ZIlIiE+3jqmSR9+KEICg0ROdnalsS5fukyEBAaJWV9/Uy6KU1Ksx8Yfzbb09HTRt29fceTIkXLd4MoV4eLiolYoFP9Um/mfpq537tw58sGDBwcvXrwor1evHqtXryY2Npaff/4ZmUxGcXEx169F0Suy9xufsWbVKhYv+omx777D17NmWf8e/eABN2/epHuPHgQHB5OamsquXbs4e/YsCQkJjB49mj59+hAaGoqLiwtZWVnExsaSmJhIYWEhKpXKGlkCcHBwwMHBAWdnZ9zd3QkJCSE8PBwfHx9UKhVxcXEcOXKEX3/9lbCwMLp27crw4cOpWrUqAM+ePuWzTz7l+fPnHD52lDp16wKQm5tLl44dkUqknL98CQ8PD4oKi3BwdMDGxob8/HyOHTnKmHfGIpFIMJlMTJs2jbp16/LBBx/w+PFjWrdurZfJZD2Li4sv/tswuHPnzh9ER0evfvDggbRq1aosXLiQoqIiFixYAEBycjLLfl6CUqmk34D+tGzV6rXP0Wq0dGjbFo1Gw849v1GlShVrAKG0tJT9+/ezbds29Ho93333Hc2bN8dsNnPlyhWrnzg2NhaDwUBoaCghISF4e3vj6OhYKZpUwWy1Wk1ubi4JCQnEx8djY2NDzZo1adWqFZ06daL9S7F68+ZNZs+ejVKp5O2332bQoEFotVoO7j+Ar68v/Qb0B+CrL7/kt127mf75Z0yYOPGV73ft6jXeHTOGPv36Mn/hQqto/+N8paenU79+faPFYhlaXFx86N/BDBro6elpzs/PFyaTSUyaNEmsWbPGKoquR0WJzZs2CZPJJLQajdBqtX/qhFgwb57o1L69OLj/gDCZTCIzM1N8+umnIjQ0VGzcuFEUFRWJlJQUMXfuXNG4cWNhY2MjmjZtKj7//HNx7NgxkZiYKEwmkzAajSI/P19kZWWJpKQkcfHiRXHr1i0RHR0tHj58KB4+fChiYmLEjRs3RGJiosjNzRXPnz8XR44cEZ9//rlo3ry5sLW1FU2aNBE//PCDSE1NFYWFhWLjxo2iRo0aYvr06SIrK0sIIUROdrbYvXOXCKseItq0aGm1wf9IiYmJolG9+iKseog4sG+/WDBvntVsEkKIzZs3iylTpgiz2Szy8vKEq6urQalUtv//lbnNmjVr6e7ubkpNTRUmk0m8/fbbYv/+/dZB7/z1V1EzpIbYvXOXEEKIw4cOicTExDcyV6/Xi6tXrgqT0ShevHghpkyZIiIiIsSlS5eEWq0Wv/zyi+jYsaOwt7cXw4YNEwcPHhRFRUXW+4uLi62/q9VqsWLFCrF//35x8uRJsXv3brFu3Tpx+vRp68+pU6fE/PnzxcmTJ8WJEyfE7t27rU4JIYQoLS0V+/btE4MHDxYODg6iU6dOYsuWLUKj0Yhr166JWrVqidGjR4v4+Hjx9OlTMWbUKLFsyZJXvldRYaHo1L59JTNOo9aIt996y6pLCCHE3r17xdixY4XZbBbp6enCyclJBzT4f+GR9L96Y6NGjWolJiZeOn/+vKxq1apMnz6dyMhIBg4cCEDKixTslHYobGz49ptvuHnjBqUqFe+/+x7Fxa9XFG1sbGjUuBGzvv2WAQMGMHr0aK5evcqNGzeoXr0669evZ8SIEWRkZLB792769++PUqkkOzub06dPc+nSJYxGo/WcDQwMpKioiLy8PNzc3CguLkYIYX2fSqXC2dkZiURCUVERBQUFNGrUyPr5xYsXqVatGrt37yYlJYW3336bFStWUL16daKiorh58yaTJk1i8ODB7Nq1izXr19O+Y0fMpt9RPSaTiUkfTiTlRQohISG0btuWfXv3AuDp6YVFWKzXDh48mP79+zNlyhSqVKnCjRs3bJ2dna8AQf+tDK5fv36VnJycu/v27bNp0KABs2bNonr16gwZMsR6TWBQIP0HDmDxkp+xWCx89OFEsrNzWLthPbdv3Xrtc48dO0bDhg0JDw/n0qVLHDt2jODgYC5dusS+ffu4fv0648ePx9XVtVxpu36dY8eOERUVRZMmTXBwcODChQt/DGzg4uKCxWIhMzMTZ2dnVCqV9fOMjAz8/f3JyspCq9USHByMRFKuljx58sSK5zpy5AiPHj2idevW3L17lz179lgX3alTp7h69SoRERE0bNiQ9PR0ZHI5BoOB+Lg4vpwxg1s3b9KseXM2bN7EkIGDqFWrFvYO9gwfOZLw8PBKc9CvXz8iIiKYM2cOderU4cCBA07u7u63AM//LgbLDAbD9Xnz5tl36NCBtWvXYmtry+TJk197cbfu3fnks+kUFxdz+uRJvLy96da9+yvB+aFDh7Jnzx7u37+Pg4MDdevW5datW5w5c4ZTp07R9qVtrFKpuHPnDo8fP0av1yOTybCzs+P69es4ODhgNpvJzs4GoHXr1iQnJ+Pq6orBYEAqlZKfn/+7fa3XU1JSgtlsRiqVEhISAoAQghcvXqDRaNDr9Tg4OFBaWkpSUhLnz5/Hy8uLgwcPcvLkSS5evEjdunVRKBTcv3+f/fv3M3z4cMrKysjPz+fi+Qv4+/uzeu0aSktL+ennxVatu2mzpq+dsw8++ACLxcKKFSvo3LkzixYt8vLx8Tn1X+HXP+zoaNmy5Y7Q0NA2c+fO5dChQ9y5c4d58+YBcPbMGebP/YEtv2zm8ePH1KhRAxdXV5o0bUpaWho3rl/n8aNHtO/QAb1Oj52dHXfu3CEyMpK5c+fSr18/3nnnHbZt28bSpUv54Ycf8Pf3r/T+zMxMEhISrMyVy+WUlJRYGZ2Xl0d2djbh4eFIJBIKCgqIi4sjODiYjIwMdDodfn5+VkyWXq/Hw8OD4uJievXqBcCZM2coLS0lIiKClJQU1Go1NjY26HQ6dDodcrmc0tJSGjRowNixY6lRowaffPIJly5dYuHChYSGhjJgwACGDBnC2HfeITcvj27du+Po6Ejtv4NEqaAOHTqwfft2zGYzw4cPl9y6dcu7oKDAXqPRnPuX7eCOHTsOTUlJGbF9+3ZSUlLYunUrP//8MwB7dv9GUWERLVq2JD8vn907d9G3dyRPY2IA+GH+fBo2asStmzfZs3s3bu5uLFu2jA8//JDr16+TnZ1N48aNqV27Nk+fPrWe5X9LwcHBtH1pSul0OrRaLba2tqhUKtLT0wkPD0ev1/Pw4UMAatSogb29PWq1mho1alC/fn0CAgKsQDx/f39evHhBWFiY1RwrLi4mODiYx48fo1arkclkGI1GdDoddnZ2ODs7U7t2beuY+vTpw6NHjwgODqZhw4bk5eURFRXFxIkTOXb8GF/M/JJFCxZy4thxft2xg4fRfw22tXTpUjZs2EBycjI7d+6US6XST21tbbv+S+zgmjVr+ufn5yffvXvXpkqVKgwePJg1a9bg7+/PtatXUZWorE4MjUbDjOmfcerkSYKDgzlz4TwSiYSTx08glUnp0rUrH330EXZ2dnz//fd8/vnnHDhwgB07dlihL3+PTCYTx44dw8HBgaKiIiwWC8XFxSiVSoKCgnjx4gVvv/02UqkUjUZjRWIC3H4UQ7N65TvJaDTy/Plz/P398fDwYP/+/SgUCusCsrW1RS6XY7FYcHFxoVGjRvi8BsZTQZcvX2b06NH069ePhQsX8uWXX2IymViyZAnzf/iBJk2b0jsy8pX7igqLuHLlMgaDgYYNG1IjNBSA9PR0PvjgAw4ePEhOTg61a9cuVavVYUD2P1VE+/n5PZw/f75n27Zt+fTTTxk5ciQNG5Z71X5csJDw2rWoUaOGVRvu0asnqSmp3Lx5kw6dOuLr64uXtxdhYWGMGjWKiIgIJkyYQLdu3dBoNJw5c4Z69epVemdsbCw3b94kNzeXatWqVRY9Uinh4eHExsYikUjQ6/VIpVJUKhVOTk40atQIDw8P63gAklJSeX/1AZbeysa2KJWmdWsik8nYtG4VPn5V8PDwIDo6Gk9PT9LT05FIJBiNRiwWC1KplJ49e76CnQZ49uwZSUlJ+Pj4UL16dd566y1WrVrF+vXrWbVqFZmZmSxevJglS5dW2vkVdOrESd4aMZzjR49x6cJFLl+6TF5uLi1bt8LFxQV3d3c2bdrE4MGDqVq1qk1UVFQbjUaz6Z8motu3b/+5h4dH0IgRIzhw4ACOjo50/4OiVFBQwIZ16zH9wTyQSqXMnT8Pb29vSl6aRTKZjJ49ezJo0CD69etHmzZtaN26NWfOnMHX17fSOyugq2azmeTkZI4cOcLt27dfGVuvXr3w8/PDxsYGi8VCYGAgbdq0ISQkhB8276t0bfXAamTppORLnRnatQ0AOTk5JN47w5WL55BIJIwaNQq9Xo9arUan02FjY4O9vT0jRozAzs6u0vNSU1M5evQo9+/fJysri2PHjiGEwNvbm3PnztGqVSvatm1Lnz59GDZsGJGRkZSWlr6C7pz28cdoNVp69OrJ5WvXuHD5EsNGDLeaUz179kQul3PkyBFGjx4tCQkJaWJnZzfin7KD3dzcXPLz809eunRJbjAY+Oabb1i3bh1S6e9r48njJ5w5fZrExES6dutmjRgpFApinsQwaMgQZDIZffr0YebMmQQFBdGlSxdGjBjB4sWLrabJH5l79+5dZDIZzs7OWCwWq/KUkJCAVqulSpUq1uurVKmCTCaz7jKZTMZ7CzawtiSY66cO0b9lhHUXB9qa6OOlw9ZGgbeXF99/8xmOlFKkFRyJL6F3y/pUr14djUaD0WgkKCiIXr16VRpjeno6ly5d4tmzZxiNRhQKBUII7OzsUKvV+Pn5WccC8O677zJlyhQaNWrE5MmTGTZsGPKXcN55c+cS+/w5Uz/5hO/mzMHRqdyd6uLiwqb1G2jTri02NjZ06NCB6dOn07t3bwYPHixduXJlN4PBsBrQ/z8xuGHDhsfGjRsX2q1bN6ZPn86UKVNeEZchISEc2LefmCcxXDh/njp16uDr60tycjIGvYHmLZrz1ltvMWrUKAICAujUqRM//PADM2bMeOV96enpZGRkYDAYrGD3Cny0m5sbOTk5qFQqHjx4gEwms56Hnp6eVK9eHSFE+X1lOmLiEulW05uuzepbn3928xoO/vQDZy6dJHLwWxw8eJA796K5XmzP9eqD0Dy+Qtdm9cotABcXGjRoUGnhnTlzhps3b1JcXIyrqytGoxFHR0c0Gg0KhYKysjLkcjlubm4ANG/eHCcnJ8aMGcOECRMIDg7mu+++Y8iQIUilUpb8tJiu3bvx5VdfvWI6fj97Nm3btcXX1xepVErNmjVZvnw5gwcPxmw2yx8/fuyp1WqP/ZcZ3LZt29bx8fHf7927V3L//n0eP37M+PHjX7nOxcWFNm3b8ODBfZ4/e86e3b+xe9dubG1sGf/B+0ybNo2wsDC6dOlC586dmTdv3mufI4Tg9u3bFBQUYDabMZlM6PV6LBaL9XcbGxuEEKhUKgoKCoiNjUWpVOLu7k52QRFbjl+ieZ1QQvw8+bhnU5rWDEShUFjfsX3bNlo290WukBDWsB0Zz27QsE4NHOt2xtNQwKRujfD38a6QXgAUFhZy7tw5bt++TV5eHj4+Ptjb21tTWhQKhdVelkgk1vO7IlDSpEkTvL29ee+99/jqq6/Q6/Vs376dyMhILpy/wCfTp1vfVaGkfvj+ByQmJPD+BxNwdSs/9/39/Tl06BDe3t4MHTpUunjx4nparfYIkPNf0qJr1qyZuXXrVr+mTZvSv39/tm7dWmkgf0tms5mE+ASys7PKg+6enixbtoyUlBRmzJhB27ZtGTt2LDNnznzt/c+fPyclJQWTyYSNjY3VjtXr9bi5uZGdnY2fnx8ZGRm4ubmRnp6OEIIGDRrgFxhCz3VXKVa4sqaNIyN7dXztOx7cu8fZbd+j9K7BlK9+oneX1vRuW48Pvl6JTCazKlSbDp3mvf7dSUxMZNeuXVZt2snJieLiYiIiIsjJycHb2xuj0UhBQQEBAQEIISgqKsLZ2Zn27dtXOrfnz5/Pxo0buXbtGvPnzy/Pf6pVCxsbW1q3aQ1AQnw806Z8zLNnz2jcpAm/7dtbafyFhYWMGjWKY8eOcePGDfr37/8wPz//jf5q+Z8EEoYYDAbf5s2bs3btWgYPHvynzK1QomqG16RmeE0A7t69y6+//srFixdp3749PXv2fCNzVSoVqampALi7u2MymSguLsbe3t7qlPD39ychIYGAgADS0tJwdXWlsLCQtm3Lz6lw5RnyNCUM7DTute84cnAvPy/8njnjOrL57HO2bFqHtjgXsFj1BoPBwIjFuzmr9+Na3BbWTBludXd6eXmRlZVFWFgY8fHxeHt7YzAYyMzMJCgoyOod8/HxwWAwEBMTQ5MmTazv//LLL8nKyqJv375cvnyZCk/gw+hoLl28SFZmJmfPnsFsMhMcHMzPy5Za742PiyM0LAx3d3cGDx7M5s2bGTduHN7e3rXz8/PbA5f/oR1cq1at1B07dlSNiIigX79+HDt2rJJi9feouLiY5s2bc+PGDb755huePn3KuXPnKkF23kRFRUXExcVV0jizsrIA8PHxIT4+Hp1Oh1QqJTg4mP79y+OxZWVl6HQ6SktLqVatGmazmaSkJJIT40i9e5RANwmrD92nS4fWFJaUkpmVS0L8c3p3acfUuRus7/rh1+Osii5mcecARvRoz6lTp3jy5AlarRZnZ2dKS0upX78+ZWVlFBUVUa1aNasSp9frCQoKolatWq+dL4vFQo8ePQgPD2fOnDm0atWKGzdu8DQmhuPHjmE0GKnfsAGDhwyxPtNoNDJ39hx6RfameYsWWCwWevfuzeHDh4mOjiYyMvJuXl5e07/M4ObNm3crKCg4FRcXJ1m/fj2urq4MGzaMnOxsfP7GnAG4c/s2rq6uhL70BgEMHTqUyZMnk52dzeTJk3nw4AF+fn7/5bCX0Wjk2bNnZGVlIZFIKC0tJTExkd69e1OnTh2u3Ikm/cUdFqz4FKGX0DqoAX5ujvh4OuPmZE96mROOvjU5snc7DeuGUlKq4UH0I7o2D8M5IIJpX823visnNw8fby9y8/Lx9vIkLi6OU6dOoVarqVatGt7e5We0s7MzdevWtQIJ/irl5ubSsGFDfvrpJ/z8/Fi/fj07d+587WI4euQIS39eQlpqKg0aNmTvgf1IJBK2b9+OwWDgvffeIyQkxJCUlNQRuP6XBhARERF/7do1YTKZRI8ePaw430ULf6yEIqwgs9ks3h0zVuzds0cIIcTRo0fFO++8I5KSkoSbm5s4d+6c+FeRxWIRc7YeFp7Td4q6XeqKvQd2imkzx4oukQ2ERqN5dZwj+oq5n48Xs6e/Jzo2ry3y8vLeCG7/Y5w6OTn5nzruS5cuCXd3d5GcnCxGjRolTp48KcxmsxUHduH8edG7ew8REhgkQoOri2lTPhanT50SZ06ftmZQ9OjRQxiNRnHp0iXh5eV1+S8xt0GDBq0CAgIsFotFbN26VWzevFkIIcT5c+VY5AF9+4rrUVGvDHjN6tXi/NlzQqvVirCwMKFWq0WvXr3E9OnTxb+arj14Ihy+PScmLP1VnDh9QDTt5C+271r3aqJYcpL48etJYtr4oeLd4b3FgB7t//S5vxw++y8d95QpU0RkZKRQq9WiVq1aoqysTKxcvkIM6j9AhAQGiZDAINGuVWvx+NEj6z0/fD/XuuHWr18vfv31V2GxWIS/v78BqPd3RXTLli3Pf/bZZ5369+9Pr169OHLkCDKZjNUrVxF17Sp3bt8BoE3btkz//DPqRkQAsGzJEj6eNo2vvvqKBg0aIJVKmTZtGk+fPv2HRdgfyWAwoNFo0Gq16PV6VCqVVQGTSCR07tyZJ/FJBPr58DQhiQf3zmKvdOLtt141w1b9PI929QMAOH72KgaFG7O+//G15tpna/ewLtuNJuYU9k4bROzzZ2i1WiQSCY6OjigUClxdXZHL5Tg7O2NjY1PJ3/1XSKPREBERwZIlS9BqtcTGxtKvb1+GDBxEg4YNmfHlF+j1BnZs20bnrl3o3TuSFcuXEVKjBoOHDMFgMNC/f3+OHz/OgQMHxLhx4zYVFxeP/zMGK1xcXDSZmZmK+/fvc/nyZb766isrQkEml3P1yhV++nERMU+eIJFI6N6zB3Xq1KFJ02Z4eXsxcOBALl26RN26dVmyZAmDBg360y/55MkTMjMzkUqlVhPFYrFY3Z1msxmz2UxpaSl6fXmIUS6XY29vj8FgIDIy0uplMhgMVsXkdbTkhy/o0qI2C1ftIDExkbfGf8xHH015/bgSXtBl7TX6+As2fDKazZs3W8tBaDQaLBYLarUaW1tbbG1trTbw676DxWKhXbt2KJXKV95z9OhRJk+ezJMnT2jTpg1Hjx7l8MFDTPxoElKplLVr1qDVaBn/wfuUlpZy5NAhhg0fgZt7uUUzZ84cunbtSr169fDy8lKXlZW584dyEtK/Aa2P7dChg8Le3p7t27czcuRIK2MrMuXbtmvHoaNHWLZyBYGBgZw6cZL79+7TtFlTFi5cyPr16/n555+pU6fO32VuhS+4YmIqdk8Fw3Q6Hbm5ueTk5KBQKPD19cXFxQV7e3uys7NJSkpCq9UCcO7OI9Ye/mtIU4PRhNFkRl/65hoqXi6OZP44krmjelj9y1qtlszMTJRKJc7Ozvj7+2Nvb09JSQlJSUlkZmZalSOJRIJEIrF+n7y8vNe+p0+fPoSEhLBkyRLWrl3LTz/9xKjRo5BKpZRptQwaPJhPpn+Kk5MT/v7+TJg40cpcgDFjxrBjxw4cHBzo1KmTAujxxmCD0Wic9tVXX6HT6cjLyyM4OPj13hGJhN6RkZw6d5bhI0fw6eefkZ2dzdWrVwkNDWX58uXMmTPn70602WzG39+/kjkhhLDiptzc3GjatCkRERE4OzsjlUrR6/Wkp6djMBioWbMmarWaqHvRDNkdw8w7Gg6fvfTG95WUluOivT3dCArwxUZmeeO1WXmFSKVSfLy9KCgowGQy4evri4ODQyVsl52dHQEBATRp0qRSNYGKzyu+TwVW7HU0f/58li1bRu3atbl06RJlOl35s+3t8fL684yWwMBAMjIy0Ov1fPXVV7ZeXl4fvYnB7nFxceGNGjXi8OHD9O3b9+8ySC6X8+64cYSHh7No0SLWrFnDmjVraNasGU2bNv1L56uTkxMdO3akU6dO1KhRAzs7O6RSafkKfgl7+SNQrkLkBQQEWOtatW7cgI5OJXS1y6Vn+1bk6gWpWgvxagvpZRaSteWMjHkaW372laqoERKMlPK/GyyQrfv9HSv2naHPL7eYtGovOXn5pKSkcPv2bbKysnB0dMTb27vSUSCVSrGzs7Pa5hU/Dg4OtGrVim7duv2pidisWTNatWrFunXrWLZsGUuXLv2HzvLIyEiOHTtGs2bNKC0t7QR4vMLgVq1aTZk0aZJEJpOxf//+V8SrEILCwkIS4uO5c/s2J44dZ8nixWRnZVFaWsrRo0dp3Lgxy5cv56u/cZy/iVQqldUBcvXqVZRKJY0aNcLR0ZGysjLKysooLi5G93JFVwDlfH19SU1NxcHBgefPnwOw/9sPODh7AmWS8qPE01ZCDUcpAXZSbKXloT1PV4eXkkqPTKEkLSsPnRnSyyw4KyBWbUFnhi6NalLgHEhqoRofL08SEhKwt7cnPT2dtLQ0EhISSEhIsIZHw8PDUalU6PV6q8MlLCyMOnXq8OjRI86cOcOjR4/+dC6++OILFi9eTNOmTTlw4IC1ptdfoaFDh7J3797yKNp771mA3q+4KktLSwdWIPalUilOTk7odDqmfPQRj6IfUlhYaD0n/4ha/GjKFHbs2MEXX3zBnj17CAoKsgLk/h75+PgQERFBXFwcRqORp0+fYmNjQ+3atbFYLBQUFGCxWDAYDFbvmIeHBxaLBScnJ0pLS3F2dqa4uBgXV1fSyywIoDj9Bd6hvx8vZWZ4du8mPTu1eCl+i6ndJJD49GxKTQIHuQR7mYRQBwmJGgtmsyB6dHWS020BCAgIoKSkBKlUSmFhITVq1CApKQk3NzcUCgVXrlwh+slTLpY4UmwQLB3UmNTUVGuqTMVc/Rm1atUKf39/9u3bx2effcaBAwcYOHCgFTP2Z+Ts7IwQAp1Ox4gRI2x27drVt7CwcNsfGSxPSkqqVbduXa5du0abNuXBcKVSydx58xgzajRVAgLw9vbGbDHj6uJKSI0alKpUKBQKtm/fzoEDBxgwYADvvPPOX155GRkZFBcX07ZtW168eEFMTAxlZWU8e/YMFxcXtFotOp0Oo9FoxUQ5OzuTn5+Po6MjLVq0oH7930OBDpjYeOQSK29nML1lPBMHdC6PKcsl5Gm1NArwJSk1k8Cg6jRo3AyJ/CFetr8bEpsPnWZs/+688K9GoJ2UsKAAKzqzAjKbmppKYWEhISEhlJSUoFAomPfbWdID2mCs3QEkUgbcL8R0dh2KO/uo5ufD8uXLcXd3/7vzMXHiRLZv386ePXsYNmwYb731FiOGDKVr9264urrh5+9HUFAQ1QIDsbW1/VvzluvXr9O0aVMMBkPHSiLaycmphbu7u8zBwYGLFy/SqVMn643e3t7s+m03bdq24eelS+jQsSPfz/uBDz6cwFtvjyY1NRWDwUBJSQm3b9+uhI3+e6RQKEhLS+PMmTPY2NhYFYqSkhKrH1oqlVr9187Ozuj1etq2bcvQoUMrMVcIgZudDfmlWnL9GmIjFdb7tHmZiMJMpBIJt+5G06RFexo2bEhEvfpozQK9WTBt1W6mPpDQ57uN+AotCinExcWRnp5ufUeTJk0YOHAgLVq0QC6X8yguiQlnM0nu9g0yWyXykmzMj87iv+djzA9Po7NxJl5vz+rVq4mPj3/F9ZqUlFQJpz1y5Eju3LljzZvKzMxk4kcfMWXqVOzs7ahWLZDc3DzGv/se7Vq15p23x1g1906dOnHx4kWcnJxwcHBwAkKt8eAGDRp8Nnr06OZt27Zl+fLlTJ48uRKCQWlnR7369Vmzeg1SiZRmzZvzcmGwdu1aRowYwYkTJ3Bzc2PUqFF/mcF2dnYUFBSQl5dHRkYGQUFBmEwmysrKcHNzo6ysDCEELi4uCCGoV68eLVq0eEVkpaWlsXv3bpydnXFWKvi2jS82Ugm+Hq5sPXODD3dex1adw/1bt0lOTuXDaV/yMCmD+i3bUCakuNtIcbSRcuRePO0D7OjbphGpqals376d1NRUZDKZFb5rsVg4d/shP1xO4bRjS+zLCjB6h2KU2eJ+ZR2ftfQnBm9UzUeBXIH50Vl6de9G+/btSUxN58fdp5i+6wozT8awKsebReeeoLt3kk6tm1ux1Xl5eQwdOpRLly4x+u3RSCQS3NzciH3+nFs3b3Lk0CFkMhnffDvLivHy9vZm5cqVDBs2DJVKZbl27VqsEOKu9KW92bFnz56Ulpbi5ub2CoSmIhXkoymTUatLSU1JsXq0zp49S/PmzTl8+DDDhw//h7Q/nU5HcHAwvr6+uLq6UlRUhKurK/b29mi1WhwdHRFCWMECf4TpVNDdu3c5e/YsxcXFHDlyhGpu9lSvWoX2zRqgVCq5EZ9JatW2BNVqyIJlmxBSG/ZdfcDY01m8PXc95rwMAMKqeJOxaBRfDetKQkIC69ats0amoqOjOX78OPPXbsV78kYmPHIgvko7cK8Cei1c2UL3ZxtwadCB2bG2xD1/hn7Nu5jOrEXi4s3KeAkR6x7R9XAeW/M9eRHaA8esp0gkIPEP56c4qVUJGzBgAAcPHqRVq1acO3cOqVRqPZrmfT+XTRs2EBISwr6DBytlaUokEuzs7FCpVPTr10/h7u7ezyqis7Ozq4eGhhIVFUWrN6R2Atja2jJp8mRmfPYZUmk5kjE+Ph6TycSjR4/o0KHDP8Rge3t7nj17Rv369bG1tSU7OxtnZ2fMZjNZWVnUrl2bXr16vfH8On78OPHx8VZlKy8vj99++40TJ05YTauutfw530HQODyEgoIC/KpUZcLA7piNRhzslARVK8/59fbyRCKRkJuTzYYNGzAajcjlcqRSKVlZWUxYsp05qgjKwjvidHs3tglRWFIe4p79kCFBCs56dOT5mT3o147HfHMfWCwo+nyC8uszOIY3RxZYD6muFJkqFyGRonHwwbR/DqE7x2HYN5cuPXqRnJxM7969efLkCUIInj9/jl6vZ+P6DQzq15/MzEzatmvH3oMHCAp+NV2pTZs23Lx5k5o1a6LX65tUKFnuxcXFSgcHB2JiYmjRooUVWeDp6YnrH4L8ZrMZGxsbZnz5JfUbNODSpUuMGTOGK1euUL9+/b+rKb5JA7x79y7Nmzfn+vXrPHjwgJ49e77WrVdBWq2Wo0ePYmtrS0lJCS4uLqSnp+Pk5ITJZCImJgZ3d3datGjBsG6VNfqVG7aRnZdPyre9yc3Lt4rdCmeLUqnE09OTkpISHBwcSEpOZnuGHfZBzbFR5WB0cKW4Sn2cHp1gUru67KnRht/ww7DtQ0RpAfJWw5A26I48uCG2GY8xl2RhsbFHRB9Hffc41V1tCM+/QNv6tflg9S/WTIu8EjNLly5l2bJlNGzYkKtXrzJ8+HBu3bqFxWImMTGRMe+MZebXX78xpl6nTh3u379Pt27dKCsr8wBcpUFBQU27du0qqcAh16xZjsZ4b+w77Pz1V2ugvZzpCXz5+QwSExORSCRcvHiRyMjIVxSzN9GmXXv5dPkmdu4/aN1hoaGhaLVabty4Qfv27RkwYEAl5qanp3Mv+qHVRHvx4gVnz57F1taW4uJi3NzcKCwstGYJOjo64uXlZV2oRqORI0eOkJCQQEZGBhqNBn8fbyTCgl6r5ujRo+zbt48nT55YAYQ1a9bE0dGRHTees6ssBHpMxuLogSUnCdPSYfQtPMewZjVYa2xAnr0/+uVvIQ2qj/LrU9j2/wzXoiSEsryupjkjFvvL61nZ2pmci7/x4ORe/ItisH1ymPSMDDrN2oR8xlEkNkq6dOliNZkuXrxIv379uHDhAu07dOCdd9/lm2+//VPARM2aNYmNLXfmtGjRQgfUlfr5+bWqsFvz8vLw9PREo9EwcPAgho8cSWJCAi+SX2AymagZXpNRb4/m9s3y7MAHDx4QFhbG9evXrabVm2j3keOo63YgoG0vckNbs+XX3dZzeM/6Ncyb+D7TWtbn/c5tuHX9OnuOHGf6pn0sOHOXK/jw5eJV3L59m9TUVGvKipubG/n5+VY70NXVFWdn50p2+M2bNzEYDGzevJlffvmFI0eOAHDr1i22b99OdnY2GRkZpKWlWTMmjjxOZ3ZxHVKav4+dvgSprpTSuDs0TT7EpllTaNiyLZuTwOLqj+nkSmw/3IRzu+E4pkdjsXPF5BqA+eFpJHcP8UMdA8nn9zJ69GjWr11Di7o1uPUslRXnntNo5U0SfJpjF32ErRvX06dPH6vJExUVRXh4ONHR0UTUq8fbY8e8cW7v3rlr9Svk5uZWpBlJgVA5ULti11YoV6kpKTRt1gx3d3f8/PwYMmggAwYOYuDgQYTXqkVgUKA188DJyYnY2NjXIvb/6JK8p5bjmJ1JaWEegRGNiMkoBwL+NH8eR8+cJdTVCY23P40bejNuQCTt520iKz6OgoxUarfpTPTDhwzv0obk5GQkEgkeHh6kpqZa7WWlUomLiwsODg7WLEEoL/6dmppK9erViYuLq+TbrVatGkIIDAYDOTk5lKhUNJ38E+qCXGSdO2AyGynVqHHd+gGd64fSocNwnjyLZfnOQ+jLtNh418AjvAmaKjUxCAvSJ+cxb51G8yo2jB42iH7LtmNvb49er2fm2L48efQIk05LYoEGdwcbGj5Yz/DhIxm7a6EVoVkBtY2NjcXZ2ZnY2FikUilHjxyhTt26FBYUUlhYbnkUFBSQm5ODk7MzTZo2qeQDj4iIsJHL5SFyvV5fPSgoyCruoDx5e+uWXzh96jRBQYG0bNWKYcOHUbVaNbKzswkMCsJgMGAwGMjOzsZgMBAYGPhGBu89egL3anXY8/10/EJr4Vk1GGEod+tdPHkCbzslVcP8+GxyJLY2cg6cfcDZjUtp0LUvfaZ9w6Pzx+kUEUpqaioSiQQfHx9SUlJwdXVFq9VaQedSqZSuXbtWWlhpaWnY2Njg5uZmLf2v0+nQaDRUr16dS5cu0bFjRxITEwmfvJySZmOxfXIaji5kRLgzYa2rIG8/mIyMDMxmM9u3bEavtWAzbhXS4IaYYq9gfHoV1/v76FKnKouPrq+UpSGEYOGMj5AUplE3wBWFXEqBWk8NbydKC7KY/NGkV6wWf39/TCYTubm5qNVqjEYjhw8d5uefFr8+X/sP2O2KHOjq1atLnJyc6si1Wq2np6cnaWlpVkB7ykszqMIUAjhx7LhVCdm9dw+JiYl06NCB2NhYQkND//RsOPcwlpiHuyktzKck6iI9JkzHx6HcE6MqK0NIJAzt2QR7pYK4lDwcHO0IadCCFgNG8uTyGVTXTzBo/DgKCgqsiWWurq5WO9nNzQ2lUomPj0+l8/vGjRt4eXlhb2/PvXv3yMvL4/jx4+Tk5CCXyzl//jyjR48mLS2NXw+foihsMOLIj7xd14mvdi/C29sblUrFli1bCA4O5vnz58yZM4ebN29y/8oiHj9pjG1uLAPCPBkz/0vs7Oy4ffs24eHhhIWF8TwphX5LjtAr/ib2CikZRVpyVTpMFkHDQHcO3U8jMzPzFfNPIpEQHBxMbGws7dq1Izk5mYh6EXTt1g1vb2+ys7MIr1WLOnXq4OHhwbGjRytlX7548QIvLy+kUmkVuUajcXR0dCQlJcUqJqpVq8a5ixfJzMwgJSWF1JQUUl6k8OJFMokJiQQGBXH16lUaN25MQkICoS8z4d7kjrT1C6SWoxu3j+xG6e6JTqOherVyN2DzNm2JOnaEG4+SaFy7KkaTGYNvbXqOm8rd4/souXWGL7/4grS0NMLCwrh8/jy3D+xHplJhkskJ6NCBNp06YTabaf7SAfNHbdvOzo6UlBRSUlL48ssvKS4u5tatW7i5ufHNN98QFRXF/fv3eXDnBi6p6fy6cpFV2Tm+fz8XNm4gJzWVMkcnApo04caNG3Tr1o3IyEiePn1K/fq98PHxITk52aoTHLl0k21rzpLg2wyLUwhNAl3JLC7jeVYJeaU6vJ2VeDopaRr8Zh9zSEgI8fHxNG3alKSkJD6YMIHQsDBin8fy/nvvUat2bUJeJvtlZGRY7/P09CQ/P5+AgADMZrOHXKvV2imVStRqtbWierfu3ZDJ5QQFB9GqdetKLz575gxOTk6UlJTg6elJamrqn/pZjxw9hlYleBF9l4DwCJBIKMxMpfHL4yA/JweTEOSXaLl4N55neg/6z/+FR+dPkHRiF6tXrSIuLo4qPj78OGQwzZS2dJDJQCYFLKjOneFYTjZzly2v9F69Xo8QgpycHG7evMnSpUt58uQJFy9eJDg4mKKiIqZOncpvv/2Gp6cnvTt3oHXr1tbJ2r11K8kL5hGmUBAmk0KZBt3li1wqKGRDbCyTPv2UiIgI8vPzcXd3x93dnbKyMuZdz+J5UHcINGG6vB2v6L08q2uPRQhc7GwoKTMytKk/ZQYTEhv7VxLc/5hvVVRUhJ+fHyqVitCwMC5dvMjHH01Gr9cz7/u5XL8WRV5eHikvXjDjyy+tDC4oKMDOzg6TyeQq1el0CplMRmlpqRU79bo+B/n5+ZhMJqs5pFarrRjhPyoIf0uPktNIenAbGzs7XH2q4ODiRkF6Cr9diEKlUuHp50+3xqFs/GY4DkobtMHtMBkNPN67gU0bN5KQkEDqrZtETfqQdvZ2CAGC8p98gwFnuRx1dPQr2YnXr19HJpORl5fHkiVLUKlU7N27l+XLl3P79m2qVKmCu7s73377LZ9//jkhISFYLBYKCwvLezD8uBD3lykv0SoVd0tKuF5URKiDPd0L81n66SfY2Njg6elJYmIiHh4eTNt1jWeu9TBd/IWQfZOZUVfOxxPGE5WQR0xGCWq9EblUir+rPQ62cuq17/1ar2GF57C0tBRXV1dKS0s5f/YcH4wbj1wuZ8v2bbw1ejR79+zh8qVLjBw96pUzWC6XYzQalXKTySSVSqWUlpZaE7mOHD7M82fP6NmrN7Vq1+LjjyZz+tQpXFxcWLF6Fa1at7YytmIQb6J8owSpVIaqIA+T0UhucjxmkwkbpR0LPx3O03tPmT66Iwq5jGHdGrJ47Ofsn2Pi5x8XcO/ePaLWraV+STHIZOzNyqbIaMTb1pbGLs6k63S4KxSYSktJSM/mvc3neVSqQGYqY6xXES3CArCxscHFxQUXFxdmzpzJ2bNn2b59O2VlZQQGBhIYGGgFHtja2mKxWNi+fTvOWi04OXK5oBA/pS0OMhlqk5mbRcUEKJUMc3dj4+SPeHfZclxdXVm+fDkPt/+Kv7cnGzdupLCwLsKg5ccFC4iJz6FRoDupBRqclAruJBfg6ePD0i9mvXHeKpAjzs7OJCYmkpeXR5WAADb+spnq1avTomVLOnftgo1CYRXVFd7GinokZrNZLjcajZIKIHmFeZGZkUHf/v0JDw9nw7r1nD51imbNm/P1rG/4bfdvVgY7ODigVqsJCAh47SDj4uKo1rQdkphoNCWFSGVyHFzdyE54ToivI3M+6IpOV0aGWoHeYMLWRs6Qzg1RafWk3jtGyvkYGiBI1enI1ukxCoH05Yq/XlSMv60teouFYomc+uuiMccn4qDKQOVUhTNxsWjT45gwYcLvOCsvL7p162ZNP+3Zsyd37tyxKmYWiwVnZ2dycnIwCoHKZEJlMlGsNiEFCoxGLEJQZDRyKi+fbl6eLJ80iRmbN3P83EWkIU0ZN6wzKpWK9u3bM+6dsQTY6vlsXCtis1ScepLJg5RCvPz8Wbpmz2ubjFSQo6MjaWlpODo6olKpaNigAbt+210p8eB1DUdsbW3R6/VIJBLMZrNc+vooj70VpbBuzRoUCgULflxI7Tp1aNykcaVA9h9tr7+l81ejSLx3g5grZ4i9cZnMuBhSY6LJTorD11juIXOws6Vp4wasPvKQC3fiKdLLkMrkTBvSBKW7nFN5+TwoUVFkNGIjkdLExQXpSyd6hk6PUiYjw2imS/JelrT3ol81Bf0sj5kzfghPn8e+Enn69NNPsbW15a233qJ27drY29tbG2hVhDBDQkLIM5nQms3k6A14KBQ4y+XYSstBPmUWC2llOu6XlBDpYMe374+npP8cFAO/JCUlhbCwMJ48ecLMb2bRcfTH3EkuQKUzMrJ5EPsmtSciwBWtuvTPa2v8jeh2cnJ6bVbJH5PwXwurUigUQgghcXJyssJE8vPz0el0/LTwR4qLi3nnvfeo9tLOTUpMpE/fvjg5OaHRaHB0dHwla72CUkrKkNvaEtGpF6UFebhXqUrG8yd4VauO0qWkXNM1StHrDTRv3pLzUfeoUaMG6pfP+3nR28xffZLTR+9bz8OnajUeCgUeNjaoXkJm0rxqYMouYYiTEzuVrZH66Dl+A+q7BpCTk1PJDPH29iYkJIT09HSqV6+Or68vJpMJtVqNXC5HpVLh5+eHXWAgysJClDIpL8rKsJNKcZbLEQLKzGbkUgnpZXrqOFroKpVwLz8Nk7M3wcHB6PV6XFxcqF+/PokPrtO5dQif7L7LinPP6d2rF0VFejRluj9lsFarpYInzs7OPHv2jK9nzqRKlQBcXF1e1gArrwOm0ahp07YdHh4e6PV6bG1tK/KkTXK5XG6xWCxSJycna/C5Xft2tGzazJpkNfnjKWRnZbNpwwYePHjA5I8/puL6Co36dZRXWEx+aiqaogIc3T3JfZFAeOuO2Du74pZ4AIB7TxJo07YteQXF5BeW0LNjC7JyC4ictIYtP7zNzEm9qBbgyao1p6hqY4ujTIa9TIZZCFzkcnL0eiIb+nM918zYGd/jJdNjE96KMpk9EYHl8NrCwkKrpq9QKKyVBdq1a2etDCCXy62Nt5ycnLjUoAF2ly9ZgeNqs5lCoxFPGxv8lbaYhEAhkXAmP5+Bvj40j9rMNU0RA+e+jZ2dnbVeSd7jq+h8LPRvVJWohDxWr1nzSgL966isrKzSHKtKSoiLjSMuNu6111cUdqnIobZYLOUMViqVRrPZLHdycrL6Y5s2a8blqGtkZ2VTI7QGUqmUgoICBgwaWO4TFcJ6NvzxvlcUrJws6nbojtlkwsHFDXVRAUa9jnvH99Ompb1V61uwcgdpWbk0a1CLBat2kJyahW1mIf3GLmfS6PaMHd6WGoFefLngAOYiA2YhCHGwJ89gJEunx6FKCAXVmiCvHcmsOlo+/PBDEhISWLlyJbGxsVSvXr2SKefl5UWdOnWs1e3S09Np2bIlJpMJHx8f5HI5dvYOmIUoF9E2ClzkcnxsbTEKC8VGE1l6PbZSKTUdHCgxmehoJ8XG+JSIl5keWq2WPUdPU0VWikZvS7swH9q0bP6XmFuBP6vwMDo5OeFRLZC70Q/QaDTcu3uXXb/u5O0xYygsKuT6tShcXiq6xcXFuLi4VIQ7y6T29vbaitXyR1Hr7OxMWM0waxgtODiY2nXqULVaNWRyOS4uLuTm5uLm5lYJdlKJwVkZIJGgdHDkWdQF7h7by5VfNxDRqScKmQSzxUL08xRi4pIxGIw42NtRWKSi5EUm7T3c0euMzFt3mrHvr8HPx5VT2z6mTZ+GWCQSCo1GZBLQmM3s9OyL2WSkwfM91soBMTExVt90WlpapQIxFbHT3bt3ExQURNOmTfHx8aFKlSrW2hnJd++QpdcToFRS08EBjdlMWpmOYqMJJ7mcek5O2EtlpOl0XC4oxCwE9qpi0jKz6DRrM14LrzPl2DPCfZ3xcLTFZBF07drtL4dR09PTKwVTOnTsgIuLC5cvXeKrL2dy984dHJ0ceWvUKGbP/d6qQxQUFODp6VlRSqJIamdnp6pwcryJUa+j6tWrc+9e+ZmZnJz8+oM/NYnUx/e5f+oQhRmptBn+Ll3HT8XBzYPkXDVSiYTN3wxlSJf6mIxGTl64yY17MUR6e1FsNDGyih9VlXbcScji7Q/WcvVBEvM+iuTDTyPJNBkxC1DKpHgd/57PHB5z8eg+K4MeP35MUFAQgYGBpKam8vDhQ8xmM3q93lr3Izg4mJs3b74CYIt9/hyXtFSeqzVozGZyDAb8lLZ42pYrWwaLhWdqNYVGA0qpFKPFQq7egDohifB1Mdx0bwnPr9A7+zDGl2HO20n53Hv05C/Pb0pKCqGhody5c4eQkBBWr1rNsMFDmPXV19jb2bF63VqePX1GUWERnp6e1o1YUFCAu7s7arUaqVSaL1UqlXkFBQVUrVqVlJSUvzyAkJAQLl++THh4OM+fP39lhwBUjWjM02vnGTxzAdUbNccnOBQnd08UNrbE2NTm+LWntIwIYsNXQ0k8/DXfT+hG41oBqBUSSoSZozm5dPH0oJ6zE0WaMuZ8+xvvfbuTBrUCWLXsPUz2Cqrb2zPzrd58//331nIJOTk5+Pj4YGdnx+nTp0lLS0MqlfLh25FMeKsHT5484dKlS2RlZXHmzBkrnhng0MGDzInsjb1Uyp3iEpzkMlzlcooMJp6rNWTp9bgrFPjY2tLYxQWlVIqHjQ3Zej2ZWjV2GTE0u7OcpOWTaOkr41mOlkyVgTNxhZy0b0ZZWdnfnVshBKmpqdSsWZOrV68SFBTE9ahr3L93jy5du3LizGm6duvGmHfGsm7tGg4dOGi9Nzk5maCgIPLz8zEajWlyGxubxBcvXjRr0KDBG5WlNyEibW1t8fHxwdbWlvj4+FfsMt+aEdTq2h+FjS1Kx3IRIlMokJlMeNZtyYfT32Z4v454Oymwk5mp4unEkSXjcHe2Z8vR21zceo3Nael8Uj0IO5mUfIOR61eeMuZOMu3b1WLDug/4eckx9s+dQ2hYGJ07dyYpKYlffvmFbt26cfz4cYKDg0lJSWHt3HGMa2eDWcC6799lwAcLSElJwc3Vlbdr18IjKBhVbg4BZWXUksvYnl5+TMSqNZSZLdRxcqSqnRKlVIpMIkFjNiOATL0ehUSC1mzmo6BArjzcwdYbN7h66QLuDja8KNRjK5OgsfHA4l6V/afOM2pA5J/O7YsXL7BYLNZq9QqFAnWpmjk/zGXkW29Vsnkj+/Rhznez6T9wQAW+vcI5Ylar1c+kBoPhybNnz6yGfkWY7dOp09iz+7fXZ949flwJ0V+zZk0ev/xbpZodChvMJiMSmQxb+3I3qEQqQ6ZQ8PDsURZ+9SFjh0bSu1cPOnXvjdExkIYjFrHr9AO+XXWcEFslZRYzj0tLqWZnh1wioYeXF/llOqIuP+Wrr3cx+5vBnNo+mQu/LmDokMHk5eUxZswYUlNTyc/P59rp36gvPUuLQCPdv75Ht5l3aBYMxVe/4s6lA2TGxtLe3o76eTk0sphJKSvjbF4B7dzdKDYaCbRT4q+0xd1GgY1UQqZez1O1GieZjGuFRTRwdiJAqcTvpZh3V5UXRr138jdq+zrSIdSNrGINC5asoE7hffbcT/27myc6Oprw8HBKSkqoWbMmZpOJ8RM+qMTcCqobEcFbo19Fsj569MgAvJAnJSXduHLlivjyyy8l3t7e5Ofn4+npiRCCocOHVYqtPnn8mDu373D61En2HzpEw4YNiYuLo2XLljx69IihQ4dWNtZlMsTLTDulgxNIJMjkcrSqYpTqHBrUaVmpXMG+YxfJsqvK2yuuUd8k4b5KhY+tLY9L1fSxs6fUZKLMYsbPzpYPxlXlWYqGeev34ezizaOELIKr6Dm6cwXqogycyWVITXvUviaWHEwj6mmR9V0TVsTQrKYLnw6U4mh3k8uhOhISNZjLBMjAxUlOro2BKr5KAvxsqR3qyN5dOWSV6XGQyQhQKvG0sSHM0QE7qYwGzs7sySovHRksl/EwOhpT5lOeuiqRSSTciM+hTkEB2794h/fnLPu7DL579y6tWrUiNjaWhg0bEh0dTZn2zaK938saJRVHE8DFixcFECdXq9UPKopoV2B6PD09CasZxvmz57h37y737t7jycv6zH+U9R07duTYsWN07NiRBQsWMHfu3MoMlkqR25SvbJmN4mUgQ4EqL4dAt9+Tt/IKivly/lru5pqRD/gSw+r3cHd3Q282U8PeHleFgnslJXjb2HCnuITqHvbUr+7EvmvZVPM2ITcV0LKGLfY2+bgqismW63n8opRNxxPJLHx9IbjbsSUMmx+Nj6sNHep70KSRC77utuVBKiCvxEB6vo5bqSX06+pDrlJPJwd3HqlKqeFgT5JWSyNnZ+6rVPgrbbEIgUkIHGQyVnz1Fa38FIR62pNerONiio4ajxNZ0KMHyvzESox4HV24cIGZM2dy6NAhIiMjX4Y7X3D61Cm69+jxxvv+iKm7deuWEngsB4qdnZ21Go3GoXbt2hWtXXByduaDPxQrC6halcZNGtOocWNq1KhBZkYGrVq1YsyYMXzyyScMHTr0lYFrS4px8Q1A/CGnSSqXk3T/Ju08f++47eHugr2HD8peM+DBUb6Z/i73tx/FUS7DXiEjTqOll4cnx3LziHBywuwliElRU1BixNvFhjSdGZVGQ5nBhJeLDRYBNjIJ/Vr5UifIgYNXs1FpzbSo7cqDRBW2cimKP3hpSzQmrjwpeqPL8Fm6mipVlbjlKVBIJbgrFFzXG1BIpRgt5W7aQDs74jVaajk6oIp7SO1G9bnxQoXFbEDVoB9PskrQarXcvHmTq1evMnjw4Dcm5D148IC2bdvy0UcfMWfOHIxGIwMHDWL50mVkZWbx9tgxr63g8+TJE2rVqoVarUapVOZrNBqV/GUMMTYuLq5R69at2blzJxMmTKBxkyZ07daNfv3706hxo1c6YZtNJmRyOWFhYchkMurXr8+pU6cYM+Z3cJipTINCqURTUmidLIvJxPPzR2k9+PeywQkpWdwLHY5NaTZDAkrp170LsQfOoTCYKHY34N5eoLwjJcjODpUQhIW4k5xdxrejapBVpKeo1Ii/hy2ezjYUqY1U8VDi7CDH1UGOrULK+Xv5ONrLmT2qBk9T1ej0Fs48yKdQbcRgsCCRSrEIC3YKKXK5DFdHBQajGVcHOXFpWnKKDQR4KtFlW3CSyZFJJFhe+t+lL11dYQ4OXC8qoqaDPQFBztxJLcXTUc6xBxnIWnVBrY7m+3U70MrsrcC416Jfzp2zpuTUrl3bWkGgIoGtc9curFi2jPfGj3+lNEZUVBSjR4/m+fPnSCSSG9bkM5PJdPrkyZONZs6caU1uDgsLo1btWvTo1fO1A7l58xat27SmW7du3Lx5kwEDBnDixIlKDLbodbj5VaW0oBx/bDIaKMrOYP/ePWxfu6jcGVJYwriroHBWoE+6z+j3yuGuJrMFLBaQQ/3Bdpw7VUCBj44qHk3wcSsiv7CMxqF/3m/57IN8Dl3PQyqV4uIg48azYpzsZNgoJEQ2KwffuTkqSMrW0i7CHZn01djsi+wyzj0swNfNhhKLCYVUigAUL4MBNpJyO9jDRoHKZCJBq6VxSFVq+zmjNVho0GMEhwoNOJi1rMjyRNlhdCXc2N/Sb7/9xsCBA4mKiqJr165cvXKFVq1akZKayosXyVy6eJG8vDwGDxjI2vXrrQD4iuxCJycnDh06pFWr1SesDE5ISDiyZs2aGTNnzpTWrVuXp0+fUqdOHR4/esyCefN45913K0UyMjIy+OTjj9m55zdGjhzJsGHD2LlzJz/++COlpaVWr4pSBm4+/iRHl5cBLlMV8+TEXhb8soYv419QqtYydm8SMo8wLHoNowNUuDqXr0qTwcAdl2Kc8uS4J9rzoqqayM9cUcS0RZ5/ANkfRNT6E2k8SFKx5qPfy+V/tyOBglIjDnYynO3LnR8bTqVhNAl83Wyp5q0kJacMhVwCEglHb+dZGfxBz6rU8C8/QoJ87fBNtaVYbSTTrMfX1oYCgwE3GwXFRhPV7OxI1ekIsbfHRiol1awnRA9ao4VnWUUMmjmWb3++QnTURUxN/dg2utUbIU6lpaWcOHGCxYsXM2TIEPbu3csvmzbx3th3XkndBfhg/Hg2b91ClSpVePz4MXVetgvYsGGDHLjwx/TRu4WFhSaNRmPTsWNHLly4QJ06dVi+cgV29vaVSxtkZTF65FsUFBSwf+9ePv/iC2xtbXFycqJx48Zs27aNSZMmlcc0ZeVnrlGvRyKVolWV0KdFec6Qg6MzY5cdp6TFeGzTHyHJimXcp+VZj9oyHSqjiQAbW3qudGL5BzkMmOpGdrIRu8I83MwmFH/A+NWv7kx4td/F1YK9yRy5mUt1v9/rROYWG7C3kVGgNrFxal0clDKK1EaG/BCNv8fvQD11mZn9UdnMGFL9D+cwyGUSSk1mQh0ciClVU8vRkUStlkYuzsQXaQixt6eqUoltNXvc7OXEZGtI1dkTGBiIza3fyEx4yi9f+DB08Jvrluzfv5/mzZtb2wYEBAQQdS2KwMBAatYKJzi4OiEhIQSHVKd69eqV4skXLlygY8eOlJaWolarVUDCHxlsCggIePj48eOmrVu3ZtOmTUyePPkV5mZmZvLW8BGkpaYy4cMP6f6yHvLo0aM5cOAAo0ePZtGiRUycOBGJREIVV0csJhNGvQ65jQ1lqmJrAN7JN4hsrx7YJ96gxMGP9wK02CjKh6PR6ig1mbDPkJMea6TdECfMJihTWyiQ7iLI7I3FIrj4qPxs33M5i7wSI2uOlduYFgFB3vbIkPCyUgZeLrZIgKHt/MgrMZD30qczvL0fZ+7lW4sOySQS7sWX8v2vibSs7UqJxojBLDCZBIVGIxJAZzHjrlDwyFSKBNC/3F1etjbUr+VDqFf5wpK4d8TGxoYVU0YSH9+UsWPH/umRsnLlSqZMmcK+ffsYPXo0Go2GRYsXE1Ev4u+aVjdu3GDChAm8bOx15pUMf5PJtGvfvn1NWrRoIRFCVBK1Fc7vUSNGkp6WRuMmTZg0+SPrAhg8eDANGzbk4cOHzJw505rK0qhBfW48jUYg0KlL0eVmWBWG+071sct5jtarBuMlN+jetMXvoTKdngKDkVpTFZiNghcxBlxyzPSZ5MqZX0ooLDXi4WzDmJ9eda5IJRKqev3uWy4zCHKLfzeVbseV8N2vr58kfw9bFLJyMZ1RoGPD6fLc4GkDApFbpDi8tKFUxpdlpV6ewxYBJiFIM+qpJ5FzPVmFyWRg6I/l2ZZ/j7EAV69eJT09nUGDBlG/fn0ePnzIiePHGfI3voXXFpd5WX1AqVSyfft2bVlZ2alXGJyUlLR19erVPy1cuFAyaNAg9u3bZ83WT09L463h5R3Hpn7yCcNHjuDs2bP07dePxMREQkJC6N+/P3fv3mXq1KksW7aMTp060apVK7b9vBH3KtXITU6gub+zNWaZKlxwcLLHcuRH3tnwReVgd5kOtdlE0S4JTdfY4OQhIy/VSMJ9HW6+cvJTDAxp64u6zMR/B/Vo4sWek9m4yhUUGo0opFJSy8qwlUopNBqporQlpawMF3978jRGPB0UnH+QyfB/oHjrTz/9xPTp061J9OrSUi5duIi6tJQBgwb9Ke5tz549DBkyBJPJxJYtWxTA0VcYDBRWq1btwb179xr37duXkSNH8s4772AwGFgwbz62trY0bNQIFxcXThw7zv1791DIFRw/doxv58xm+vTpdO7cmZs3b7Jo0SJrKQiR/QKniMbc37eFnXMOlWueNjbIVdmU3DvJuHbhyOWyv8l+NxEeGIS+US6xty2kPTfQbqgTMVFlNOvtwPE9GsoMFoJ97ZFKykV0NV97WtZyJSLwr1fVu5eoYuOJNB4kleJsJ+f7t2vg7VY5slSiMVGqNfEsV00Vi5IrBYWEONhzq7iEDh7uRJeoaOHmyr6sHMa1r0WIjxM5KgPGbB2ZmZlvhMX+ke7cuUNUVBTbt2+nefPmXLhwAVtbW1atXYNOp+Po4cMYDAb69u//WhzXsWPH2LNnD7du3RJyufykwWAofh2DKS4uXvT999/vPHr0qNTb25vk5GSCg4NZuWb1K9GOfgP6oyopwcHRgefPntG2XTvat2/P06dPmTx5Mp999hnXr1+nf8fWXFcV07tdS2u0RyKR4JR6h3oOxYwb+ar4EkBYjRAeJuro9KGFRl3tSX1mwN1Pzu3jGiQhZkL97TlzNx9fDxsah7lQUGLEZBJo9WZqV6vMZK3OTJnBgofz75Xf0/J0HL2Rh8UCeoOFbJ2ebeczOfJdo0rm0tFbudSu5ki6Wkp8SQl127SlJPoB9vXro3rxgmhVKZ08PSiWmHBztON2igoXuSDC3rFSZubfq7Azbdo0njx5Qo8ePSqVXFIqlQwZNowyrZYjh49gERZq1aqFRCKhfoMGvHjxgqpVq2Jra8u3335bptVqN1bCZP3xPzk5OQcuX75s0Gq1ylGjRrFz587XlkSSvGyJ7uLiQtVq1bh39y7ZWdl8/vnn9OvXj2vXrvHLL79Yi4lsHjGGid9VLgTuVphAm3b1XuuRUWu0yAKDmDhiGPv2fkxgHVuSH+mxc5LiF6LA0U1KSm4Zap2ZkR38KVIbWXwgmZvPiknPLyPQ2w6t3szx2/k8TFYhhAR3JzmRzbxoVKP8mNh8Jp1mNZ14lCQho9CAusxIQamBcw8K6N749zaBCZlaGoY406B5EwwGwdwfltGqQQO+HdCa6B/jkPj4kFJWRstgT6q5KZHLpJy5mkxtha2128yf0aFDh0hISODQoUO0bt2aEydOVC5PkZpKdHQ0j6IfEh0dzdOXuc/nL18CYOvWrYwaNQq1Ws21a9eMwOk3MhgwVqtW7fSpU6f6DRgwgHnz5lm7irwpa/DY0aNcu3IVqUzKTz//TN++fTl+/DhLlizhk08+oU+fPsz66H0eP4pm37bVTPtqPhqNmjrB3mRm56P4W/FsMmGxCPr370/rNm3Yf/1r6rSR4ROkIP6eDmcPGSkP4aqlBHcnBaVaE26OCuaMDmXhnmQeJqqZsfk5Lg4KnO1s6FzfHXcnBW5OCoJ97V9KINDoLTgbBTYKKS72UpQKG2zlUmJSSisx2EYu4+LDQho2bIZKpSckJIQPP51IrVpV2CZTMHDYUA6vXMmHzepwObEYB4Wc9Gw1ddxs0f4dBms0Gj7++GNWrlzJoUOHGDx4MCajiRXLlvPo4UMeRkdTWFhYaWMFBgYy9SXo3mAwcOvWLWbNmsXevXtNFotlO3+oU1luF7wKuG7g4uJyNz09Xfbrr79iMBh49913/+5KPHzwENVDQqgRWoMGDRpw7949a1v0NWvWlKMkF3yHSVOAQi7DYjah1pQxsFflHshFJaXEJ6djUvrSsWtP9h5fxaXoLbj7yanVQsnT63o+6L6Ls3uWM6ZJMTM2xVKzqgNKhYwSrQmJReDjoaTMYMbdQYH0NTlxOYV68lRGmoa6kFWs5+TdfLIKyjXtJmHOtK3jhkImpbDUSPcmnsz8JQ6HqvVwc/dhyZLVzPvhc54+S6F9+1Zo1DkIgyNtTA9xd1DwKKWIrUdjGVnFD/3oMUz57LM3ztmnn35KQkICO3fupEmTJjx48ACFXM6BAwdYtXwFZWVlNG3ejIiIekTUi6Duy5KOVgfP+vU4OTkxfPhw/P399dnZ2U2AJ3+2g9FoNNE+Pj6Po6KiGowYMYLIyEjefvttKxQmNSWFnJwcmjZrhl6vZ9/evbRp05Z+A/oz/4d5fPnVTJYsWcLEiRNZuXIlDRs2pHfv3kRGRjJtxrcs+G4GTWoHUFyiRm94tX6jTm9ArzdQmB9HlSrjuPf8FP0/dqM418zZTaWE2fmyf8t8NKoCwBm9UXDsVh5KGxnuTgq8XRTMfae88vzpe/ksP5KCr6ttuUfLToadjRyTBd7uUgUhBDWrOtAhwt3qVy5QmZi+8Tk2cgl+7kpGdvSjRtP+NGxcGw8PH4qLC/Hy8ibM7ED1YHv0huZk3DiFsJNwLq6IzPhcdBYzOosF27/xI1TCjJ8/z5YtW7h//z7vv/8+y5YtIyM9ncCgIIYMHUr/AQM4duQoxcVF9O3f/xV8t9ls5uDBgxw9epRLly5ZSktLL/4tc1+7g1+WN2rp5+d3NSEhQbZx40YcHR0ZMWIEjx4+YsZnn3Ho6BEuXrjA8qVL6dS5C5Mmf8TG9RtYs2oVK1atonPXLgwfPpwPP/yQvLw8Jk6cyKNHj/D19UWn07FywRe0a1oHO6Xtq0C9whKu3n5I8wa1KbMPpEXL1ny/8HOyC+5TUyYjNlVFmc5EYrqKXo3daBnuyne/JmBvK8PXzZawAAccbaVU9bbDYLJQw88Bfw9bHO1kaMrMrDySyun7+fh72GJvK0OrL1fAMvN1+LrZoDUIUnLKkMkkrJpYi/hMLWfi7OnYyAMbOxeKDfaMGjuZ27dOkfyimAULfuSXCZ1pGujK/TQ1v0aloy3VUkcmo/O8+YwePfpVOHFeHg0aNGDFihW4urqyefNmtm7dyozPPiM+Lp6fly6xpqMYDAaOHD5MZkYGNjY2jH//fWRyOdu2bcNsNjN27FiCgoL0qampbYE7f4nBAEFBQc/27dsXXq9ePWtTDoDPp09n4aJFGPR6hICPJk4kNjaWnOxs7Ozt6dq1K4sW/4S2rIwWLVpw5coVvv32W+Li4jh+/DgKhYInjx+R+eQ8ft6vpk+aTGZ2HT5H66YRJKZkM+Hzedjb2zNr2jAkmngclHIMJgsJaSXEp5aw+7PaHLmRh9ki/qm2r0QCA1v70Oij60x9K4L2jf0wmSykZKmJijUTOeJzIiP7cvHcGewuLUUuk3AvpZBOX23jwoULHFq3lk8W/vhKYMFoNNKzZ09q167N7NmzadOmTbmJtHUbnbt0xr9KFdJS017xXsXFxhHz5AkDBg3EYrEQGRnJoUOHuHfvnujatetljUbz2j5Cb2Swi4tL12rVqp189OiRbP369dja2jJmzBiirkWhUMgxGk0smDePZ0+fIpPLGDJ0KB9Pm4a7uzunT56iR6+ePH78mHHjxnH58mXat29PvXr12LhxIxKJhBWLZtOh0evLFe88dJaImtVZ/+sR+vUfwLQZs/hgWHMs+mKCqzix+0ISSVkldGtYlXA/Oa1ruTLn1wRa1359258XOWVcf1qErU35gVzd1w43R8WbMckaI+91D+BZmobLz9TMm9QEi0WQXfA7qsK13kd07z2Qn2Z8SD1zAgqZhGMvBIt/O1ueMH/iBPXr138lufvDDz/k3r17XLp0ifbt27Nu3TqKC4uoWq2qtalJcXExp06cxGQyEtmnD65ubmg1WmyVtshkMjZu3IhUKuXdd98lNDRUl5CQ0A24+trUlT9xf50tLi5OunHjRui4cePo27cvkZGRtG7Tmo8/mszxlzu6Q8eOzPjyi0odV27fvs2jRw/5YuZMxowZw5dffsmRI0do27Yts2fP5rvvvmPo2xO4dXILwVVfLbN7414MQsDN+zH4eHlQVFSEV3BLSl6cpaqPA6EBTgS0tZB7u4zbz4wMb+tL7WoOjOsRQFWvV8svrTySSp8W3rg6yMko0OHnbotWZ6F/K+/XfvcVh1NpHOrCzdKmNGlWghBailR6gv0duRqdw9OkYsIMV+neeyDm4mzOpmbSNsyHxn1+r9NZ0Wz6j7R48WLOnj3LtWvX+Oyzz3jvvfdo1KgRmzduJDMzA6lUyu5du/lt9y60mvJC5zu27+D4qZPYO5Sf54WFhRw4cIBjx45x+fJlc2Zm5r03MRf+TvfRwsLCIX379jVbLBZmz57Nt99+C8CkyZMJqFqVbb/uYOMvmysxF+DO7Vsc3H8AIQQfffQREomELVu2cPr0adatW8fGjRvx8fHhRc7rS+baKOTk5BXg6uKEQiEjJyeHOfN+Rq2ozfrDLygqNlKSbybTUsqhY2dYdVEwa2Qon254/oqoLlIbcXaQ0b2RBx3quTOmSxVqVnHAxeH1JSdO3c1nYBsffj5eyo+LV9CoVQ/KdGZWHkrj5I0M4lJKMFjk9Blc3nyrVK3m5ONMdicrGPHWm8s4rlmzhp9++onTp0+zY8cOAMaPG0dycjKt27Tlh+/n0r1LV37ZtAkJEiZ8+CHHT52ibkRdk</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -34537,6 +34759,16 @@
           <t>Decode Health, CNBC, Search research</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tn.gov</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHgAAAB5CAYAAADyOOV3AAAABGdBTUEAALGPC/xhBQAAACBjSFJNAAB6JgAAgIQAAPoAAACA6AAAdTAAAOpgAAA6mAAAF3CculE8AAAABmJLR0QA/wD/AP+gvaeTAAAAB3RJTUUH6gYdFSYhw2IaRwAAaVNJREFUeNrtvXd4VNXa/v9Ze/pkJpPeE1IIvfdeBRQQsKDYKQJ2xd7Fc8QGdsFGE7uIUqSDdJDee0lImfQ+yfS9fn9MGIyIx1N8X8/7+67r4iLJ7L32mnXv9aznuZ+yBP9HmpQoHvv4aYoQtbqEOS/JwgmtvCobALySwWat1+/1aXdK0AuNmKyLrV7gKbDuElKkKJLJ2qQ5C132SYOl6u9trKp+TbRc6Pi/MC/ivxbQkolNPF7/MgFOnVvt5zEoswTcBOBX5SuKoIMQYgiAEHKD6idHKOKO+ruPCSHmSsmM+kko9EgxVIvcJwSAOK5PmNPCUzj+I1S6+nW+KaboBRv+G+dJ+18DaM6kDK/OtwIpfTpN6ACPp/pTIUQTAI9OvK0IGStl4H3VKCRqFFb4/QxBACqrVMW/XZHa2xAoiuRTr19u1WqEBARCHNWqIkMosv5paozLPmkwqm8SgMarWQhEeewTFoBs79NoJptjP9n+/wD+N5s7f/wrQhCti0+5z1eYOxtJExD4/DXvC8EpoBuAVqscVITlCY+verFE8Rgqa+4VLRc6anMm7hDCp5iT5+0MiPHRJs7EGUXme9UAsnhiB79Pba2Nn/MZgNc+bolEtFMVeb/f7S5TdJoLcq7GnT/uRpC3Aej8/kVAvNt+562KUNO0cXOnCYH6/0T0PwOufcJLAvlMQMSyXKoyCyHuA9CgPqNJmP+yx37nQwqyTJsQAOiXbfp0YrQ+LGgI8ytYgBChYgGQCg6gFqjVeKnwaXE89hjFv+7DlzdhtKqVV+jwPufTaJtLr9hYP20nEeI1pDr3wvh08XOH/z+Af1dJGq332q1nhEKCRL6tqkKvCO4HUKXYbEyc09eTN26yoih1vwT07ddo6he0MxqsHbRaXQfV72+sKEqIwRiK2WhVdTqjRq83K3q9SWMyWPUATleN1+N1+jyeOtXrdfnrXDWK21WNqqq1Gq32jNfr2edy1+yTCgcffZQTQcDtE25T8ffQ+WufcWtCn1WQU+o/Oix08n7pFd8jhEOn1XQT0R8X/D+AgdqciZ3NyeKop0C9VqDWAyccuvjqSF+B9RuECNMKz40i7rNigBkzaKQRuoEhJuv1Pr+vY4QtUSTEN7dEhCWawmzxhNvi0Sj/2s7jV31UVhVQUVVAeWW+015w3FFelS8VRbvPVVfznU941z36KOcvvJAeu2UDQkTpNb7RXr92AdAWQKryU0PSvLH/vwfYbR9/QEBbAbVaHU28Hs4hMAjkCl3CvGEXrnvrFdJ1Ida7NCg3hVqj9WkpHUKTElsZoyMaIYTyJ0sWSUl5Nrn2I+7s8/uqqmtKPBL1K3dtzYdTnuLches8+ePeu7CFSCnHSJR7FCH7AOf0CXMz/n8DsMwdHQEgkheWewvGe6REB+D1abqYk8VRSmWSiP7k1KuvYjMbjNfptcb79EZLcptmg8KbZPTQ6HXG3+3fUeti156zOGpduD1eRo/qxpLle1i74TBarcKDd19FqNXEx/N/AiAy3EJEhIX42DB6dG2CEL8/JT6/l+zcfeqhY2vLq6sLqzxe10ce1T3v0UcpddknXOmXFIUkztnvto9XRf386lwiVaTPOf9/HmCXfdJgRfhWIlE0UjzmFTRVYCzIo/qEue0A3nyTRJPW9jeNVjeieZO+Ic0b9zFZQiIuC+be/efYsuMk57KLSEuJ4fEpI3j9raVMm/EDh3+eTmZGHABNO0xh6JD2vPXK7QC8+f5ypr7yHbs3TqO8wsF7H67my7n3/1Pfx1FbzskzW51HTm2olX7vsqq6quefeIK8gAUwbpsQogfIHJ3wXOWVht2AXkGM/y2l8P+EmaQI3zgkCoBfyFuNAVAn1ovhVIM5dKpObxzaqe2oiKYZPTSKovnNfr74ZitrNxzGajXyyfyfmDfrLp597BpWrNmPQa+lZ7emgecpF9/f2NgwHA5X8PeaGidRkVaaZibg8fiY/tItlzznk/k/Mf+LjVzRrzWV1XXccXMfOrRNC35uCYmgY9sRpg5trjadz9s/dvvub0Z88F7NtjpPzWOGxHk9pZyqFWKqz2Mf9ylgBlBRnwT+7wDsLRj/iJS8gBDHdIp3ktevHYFAp/jFtAvmjNVo+0BvsPTp3nF0ZFpKB/FrwXI+t5RGyVEXJ9Zi5IWnriOtUQxLV+zlyPFcAIYObg9AWJgZgFffXEJUpBUAe0EFMVGhwT5Kympwu3288uYSSkurmTz+igbPrHG4ePy5L1jw8T1cfVVHcvPKeOP9H+nQNo35X2wiLjaMIQPbIIRACEFqcgeRmtw+Mitn39U79i7s8eF7js0zZky9Gyj2o8xRkLcKUATK5177hGelUCdohPKuJm7OW//VAEtVvogQIUjZ1Y8uXZ8wJwRg6lSU998wPaAx6J/p2eX2iMy0Lg3GoqqS5av3sXz1fuwFFcyZOZnoeoBGDusUvK5HlyZs33m6wTMjwi0AjBremWFDAqAXFFaSm18WvKa0rJp2bRrx2APDmfnJGqIirA0nRqtgMut58ZVFpKfGkpEey+MPjgi8LIUVaDUKN9zxNlf0a81No3sSajUBgrSUjiItpWPUuexdIzfv+rzvzLc90177eM47L7wwyUpehZGklnXegvN1SCF8Un0D+FMB/lNUUFkyKd6fP/EJWfRgrBScricD/BqNdzfAW6/TLiYy9FBGRreXbrl2Rsyvwf3qu+206/kEi5bsYtabE1j42RQslt9Wrrp3bcK+A+dwub3Bv4XZQgImWJ07+DebzUx5xUX/QUlpDVERVrRaDQ/efRVuj7dBvyajnmXfPI7P76frgGd5/6PVJMSHA/D0I6O4dUxvSkprWPDVZp576VsefuozSstqgvenp3bR3HrtjMiWTQe8GBtpOzVjxsetRfLCcsCHEL7A5At3PaPWTh4dbfmvAFhKFK/Hd84v/K961epT+vhGnaWUY7R6Y9rCnxYUznzH+mZEeMr6kUOebNm/53jrb2nFN13fg+5dmvDT5qN4fX7OnC1kzfpDvw1w50zcHh/7D2YF/+apB2vbzyepqq4j317O0eN5lJbV8N2SneTklnLilJ2Cokq+/eFnFi3dxazZaxv0+8HstXRsl8bujS9zw7XdeH7at1TXOIOf7z+Uzc+7T/Pw/cN557U7MBi0l7yEWq2ebp1usI4Y8mRGTHjKilnvhr61cOFUqVN8nVD4WIva3lswbr3X59/vDQ8tvWBh/KW1aHl0tMUbbq25ALc+YZ5yYa8NMYT+2LRxj+Y9Ot1kuWC/SilZ89Mhftp0FEuIkXG39iUpMZLjJ/Pp0PsprhvRhaaZCXh9Pv72zA2XPK/G4SImfRJDBrZh+ku3kpkRx6p1B+tXsplmTRIJMRuQUqLXaxvcV1RcSUlpNeUVtaQkR9G6RTIAObmlXHPLG6z6/imio0KZ+ckaPpq7jv1bX0WjCYx78oOzWbfxMCf3volWq6HO6cFs0vPrbeaioifZc2Bp7eETq89U19UMfeIJ7AAe+/jaCwqYooobtElzFv4lAfbYx09EyPGqkC8rKkNBjJZCzDbEz33yrenaASaj5fMBvSbGpiS1CUqNquo6bp80C5NJh1ajYfHyPdhCzWxa+TyN0+MYNvo1yspq+Pmnly773LUbDqMIQZdOjbFeRoxLKfH7VbRaDS63F6fTQ3hYyO9+nyPHc/n2+x3U1ropq3Dw1MMjaZqZAEBFZS0ZbR7g8SkjeHLKyEvudbo8PPL057g9Xua8P7nBZ/mFx+SaTR+Uetw1Yx98xL/CXTBhuoJ8SEpxXoemm1d6X1A1co0xbv6yvwzAMnd0hFdjLQ1stdKjS5hnCIq6d0JfsoRG3TNs4MPhZpOtwX2jbppBn57Nefi+YcG9d/w9H9K3V3NWff8UK9ce4Jqb32Dd0mfo1b3Z747B6fKg1Wg4cOQkh06exeutxWoMo6QyByE1WKx6SsuqiYiwoKpG6mrL0SghqEJi1JlompFBRJiNOmctbVs1v2Q1XmhnzhXy0dz1fDh3LWcPvkNMdMPvdPDIeV59YwlrNxxm7C19mTHt1kv6qHNWsnz9WxWO6tJZdz9Y/exFZm/cGYHIAPBK0SEkcc7+v4YW7YrzyRAHAoGUQq3fi8WH79s+io9peuPgfveE/tqmPXI8l1XrDvLyCzc12Hs3bT3Gp19uprzcwZCBbUlOimTKkwt4ZepNXNG/9UVGyeenoLASl9vB2i3bQXgIs9nQGSAnJwtbqJnwMAOpjRpRWFSGJdSGy63BqNdT63QRn5CMRhEUFhVR6yyhqEKhss5IQUE5R04dolF8JmWVlaSmJNC1Q+ugqLWFmomNsdGhXdol4vjdD1dy9Hge778xjuTm95KeFtNwmtxejAYdZlMY1w97IXzdlo8fmPXO4UbFFdV3TJ2KKhDhF4ERKcC/DbDm3+KS88fd+NwjHb6VBq9FauRMRWL1C/8knfWg/cRR23dpyR1HXtF3kvW3+OJz2cXM/2ITzZok0LlDxi8UEw3fLNrBlHuHUlxaRXhYCDOm3UaLZknBa+Z/vYwde3dTWlmIvSgXg17i9qg46qrQizDMFgtWUwSD+/QmIjQCg85Ap9at6d+zCxZzGGGWcPp270yULYqikirM5gjaNmvNgUMnAJWoqCicnkqqakooKClj6897iYmKpbyiiuTEaHp0bcJtN/ZGAhqNwo+r9jNt+g+0apHMyVN2srJL2LztOPdMHEzj9ACTlpdfxvDRr5MQH05mRhxCCDIadTS4PbXpzrrCAZ27ur/t2bHzHoHaTSJX+hCrpj7W/p3nn2xX8vfpB87/r4hoT/54NwI9gE7vSxJRC/KnTyfEbLCu7dBqaJv2rYdfdqNzub1ktnsIVZVsW/siqSnRALz+9jL2H8ziq3kPNNhDv1m8htKKUrQ6lehoK+ezi7CEGomxpeLxOImKiKBX9w4NFKlLSBdvgMnS/Q6fXVvnxuPxcfzUGQ4cO45G68FqsWI0aigtc+BxC0YPH0xsTGTwng2bj7J+0xFeeu5GpJS8+MoiXn1rSQOqNC+/jJhoG6+/s4y4GBt33jEgeP++I8udBw6vOCzLqwfeOxVHQKcZ5wRhlBJVn5ASIsRU1/+8iBa4Ab0EidPpnDoVvVkfuqF7pxvatsjsq/+9W40GHR+8NYEbx75D7yFTuXfSYMrKHOw/lM038x8Ics1rN27DXlBCWKSWsrIykpKjCdHFEBdtYFDfbkRHhf8CnArO55+ksqqAyupCqqqL8Pk8KEJB1pstAfHuCUTySBWtVo8tNJaw0DjCbPEkxDYlPCycHl3a0qNLWxy1LnQ6LR98+iU64SchJYbFq1fi9fqIsMVyw8jB9O/Tkr69WgRf3JAQAxqN0oB9S0oMvBC5eWW89tYScvJKeeHJ69FoFDq0GmYyG6ztduz9ZsO771b3euAB3CB0Af5ACs6U6QHX/8gKlnKq1ms//xFonDrFOcsjDc9KtPMN8R+v/Whm6JI2LYZe0aH1MNOF6w8dzaFNy5TL9rfmp0N8Mn89ep2WYUM6cP2oruj1WrbvOsjhU6fQaT1YLCGUldag0YZwRa8upKcmBYHKyt1HTt4hSsuyMZnD6gFKwBYaR5g1NgjqZb1DPg+VNUVUVRdSUWnHXnQSZ10lUZGppCS1IS25Q7CPXfuOUlhUQn7JeRwONyaTDgU9d4+9OeiFOn22kClPLeDUmQJO7WtIUs1490ee/fs3fPTOnWSkxfLxvPV88PadhJgDOumh42tdew78sCMqrmbQqN7jbkWKRzSKmKdq1H2KV9tck/DJh386wF77+IUSrg+grczUJ86+D2DmO9bZzTJ7je7Z+eYg4Tv70584fjKfN16+7Q/3v+fAMfYfOYXR5KOyohy93kJ6SmMG9esSFNe59sOcPLudsvIc0pLbk5rcnuioNC4ocvn2cvLyy+nauTFns4rYs/8c/Xq14InnvyQxIZznn7wee0E5C77czL2ThnD0eC5RkaE0zojDoNeiqn5KSrPIzt1PVu5+IiNSaJLRnZSEAPdcVFzGkjWb8PuqiYgKw+N24XAoDO7Tg4y0JKSUfLVwO4MGtA7Sq4t/3MPNE97lkfuH8/dnb6DO6eGFaQuZ9vyNqFJiNOgA2L77S8eJ01sX3/NgzW0AvoIJw1Qpf6xnA//p0CDlX1jzpl/EQJgC4Ia+lJzY6rqenW8K/eXK/HLhNj6ev54fV+1r0MXhY7m/2fW3P6xh18H9mMwuSoqrsIUmcvWgwQzq1wW/38fx05tYuPQ5zuXspXWzgYwZNY2uHUcTG9OYX2rpm7efYPgNr7FxyzEWfLmZEUM7Ehtjo0fXJuw9kIVBr8USYsRmMxMVaaW03MGYce9gLyiv90JpiI1pTNeOoxkzahqtmw0kK2cfC5c+x/HTm4iKsjHp1mu5e+xYdNhwubxUVJSwZksgslYIwc039CQ6KpRTZwrYuOUY4+/5gJFDO/Hi06MBMJv0TH/pFiTw0BOfoqqBiM4enW+yJCe2GvHBu7ZpAH5J94vSUzT707RoKVGeunvscL3P8a7UmFoK5DFdgmNsePjZYVHhydOGDnwo/JfackZaLLfc0ItDR3KY/s4yOnfIID01YDZs2X6CXXvP0q5Nar23yM6y1ZsQulo8bhcej44xo4bTo3MbQkIMHDm+no075hJiCqNP9ztonNYVS0jkZQVQ6xbJZKTHMfnBT7jx2u5BkyY9LZYnnvuCW27oxbc//MzYW/phNOpYsXo/ZpOB22/q85tvtCUkktTk9mSkdiY3/zDbdn2BVCXRkam0aJpOSWkdtU4nYWEmDp84ypbtR0hPTsJsNuJ2+7jrodnYQs0s/vpR9DptA+XxhZcX8sHstVRV1zF4YJt6h0UHQ3be/lZ9+ziO9RjUfoHfoQ5VBNKv842bNv1g9p8ioj328dlAI6BaFz83XAjU114jyWaJ2Dtm5EsxRoP1t00pj4/rbn2THTtPsezbx2ndMoW7H5rNyy+MISU5iq079nHifBa2UC1Z5wpJTUrjmmED0ek02ItOsH3XVyQntKZDm+G/q/3+Vus56HlCQ838+O3jQYrx1jvfp0XzJExGPVPuHQrA+Hs/pE3LFB66Z+gf26a8LvYd+pFc+2F6dLmJhNjAwlq1YQf5hecoLq7CarVy3/jbgpr5R3PXBQmdQB9+7poymy+/3cZLz91IqxZJHDqSw2MPXh1Q1lw1fLX46ZJad2XnC3Fg3vxxa6UQVwBH9AlzW/9HAXbbx6mCgCah02kTXpz5cUl0hHXf4H73tkqOb/m7/dQ5PVx9w+scPprDFf1a8/rfbyYpMRKPx8enC7+lvLKcqIh4BvfqSXJyHG5PHVt2LsDtqqVX11uxhcb+0zvJ0hV7CQ8L4dFnPmfYkPY8/+R1AKxef5Cbx7/Hwe2vBTXb7gOf48VnRjN4QJt/6hlV1UVs3fUFer2ZPt1ux6A3s3jFJgpKc4iOiaSstIrUhDSGDOh2SSTKzePfY8OWo4y+phtzZ94FwAvTFtK9axOuvKJtwC1ZdEKuXP/uCa2xpu3kyXg99nEqv8Dgj0Ru/mER/fwjHTMEsrkQbNbEzpl5/bWWt1o3GzSgRWZfQ8CD4+PO+z/mXFYROp2W2BhbkP3R6TRcc3Vn1m08wtxZdxEfF87sBYs4euYgOp0OvS6Mof17k5QYS1HJWVZteI9mjXvTvdMNGA3/vBct317Od4t3MuH2/vTr3YL9h7KJsGnYuO1FnHV7aJ7ZhfbtErCE2Ph+8WqWrDjKgL6taNYk4Z96jtFgoUl6d/x+Lxu3zSE6MpVO7drTuW1btmw7iE91UF5Zgb2wimaZqUEP15ix73L4WC4LF0whMz2O5av3o9frCA8P4Yp+rYPSxmqJEj6fy1xUbI9ZvtK98tlH2o8SiDghpV0TN+fF/8gK9hSO/0ioYqiUvKJPnDML4J0Z2l6RESlLrhs+NeKXQWqjbprB6vWHkFISajXRq3sz+vZqTucOGei0Gpo2SSDUamLhknUUlp7D54dIWyK33xgQXQeOruRs9m6u6HMXNmvMv2Wil5baqaur4cChJdTUFmANdxIa7gMEqg88bgWNFhxVAnztSE1pQ3hEGI1Smv/DwLvfXM01xazd/AGNG3WmXauhlJVX8e2yVVgtCrW1Lq4bejVRUWGoquS2ie8zYlgnbry2O6VlNbz21lJeffGmILC/dpQs+nFqeVl5zsgHH/VtlUUPxuIpCfVpjW9JqazTJ8x++18GWObenOnVGE9dwFqfMNcwdSra2MjQE9dc9WxGmC2+wfWnzhTw/serGX5lB155YwnVNXWcOGUnPi6c7WtfJCbaxpIVG8krzsZmM1JTpXDXHaMByaafPwUp6d31djSagCJy6NABSivK6dOrD1rNH+dkDh7ZwfFTnxMd70GjAYRECDhxQEvTtj4u4CdVEAqoqkCqUJCjJyF6EP37j/rH2qmpGaq3GOkrv2hT+H1s2bkAgL7dx+LzqaxctxWHuwivDwzacMaMGozT5eG+R+fxwhPXER0ditGg+92Xqqq6iO+W/y1La6huOnkyXm/BeLuUxAP48fU2JSzY+i+aSd4yKYM5N9UAUbaQx5o17hPza3ABmjSOR6/TUuNw0TQznr2bX+GTdyfxxSf3ERNtY8HXyyiqOE9YWAgjrhjJ3WNvQFX9rNk4C4PeTL8e44PgAjg9LsKju7JrfyGHjx74Q+CeO3uUQ0cXEJvoQdFISgoDmoPfJwgJlUhV1IOh4HTo8HkVFEWi0crA/5o/tmtJfx260P4IxXwRdI2Wfj3GE2qJYeVP7yAUlRFX9aO8TCUvtwiXp4ojx89gMuqZ8dKtTH5oNnM/2/gPJYYtNJYWmX1i/C7ro/XmUhA3re73B/y7H069v3uMWys+UxQq9Yr3tpCYQ9YQk/WzK/s/EH7B7jxzrjAYAwXQoV0a4+/5kG8+fRC9XkvzpomkJEfhdHk4fHIfpcW1IA306toen9/D8nVvkJLYho5tRlzy/KSEJPTaSnJyczHbWnHo0G4S4sLR6S7PTi1c9DbxyU60epXSQg21NQKrDbJPKySnqzidoDcQAFOn4nZqUP0CrU6i0SicPW2nfbsBKIryDwCuRmPMQCg6VG9hg8/iY5vg9tSxc993NE7tSrvWLThy4hzRMVZ27z1ESmISsTHh3HR9D7p2atzg3vO5pXwwZy1LftyDUAQZabEX+tQfObW+7YCBzi97tm29yKdqWiqKOk8XO//Tf4no8OaPz/MaZbZO8JUhfu6TIu6zYosxdG6fbneEX6DuVq8/yN9f+55TZy4qc1GRVm4b05sNm49y5HguWq2Gk2fOs2DhIkwhFqzWMCbeOhopVdZumkXj1K60bn7FZQcYGR7DoH5d0HiPYItozIHj1ZzPOXfZ6+PiMnHXKSAFxQWCtKZ+hICEFJXaGqguV5ASaio15JzW43IKVBkQ1wajD6O5jrzcc39kDeOr+RlFl1i/0wkUXSyIwNy0ajaQzPTurNk0E71OwwN33kpVmY+09ARWbdpMYVHZJXvuwsU/067HE7z4ynd8t2QnY+/6gOenfRtYqRo9fbuNjTDrbbNF7IJDxsQ5faWqjfbkj3d77ON3/1MAy7OTbFKQWL/JNwV481VaWyyRXVJTOmgu+GMXLt7JvA/uRkrJ4h/3BO+/d9IQXn1zCWmNYnC5PWzetRuP10F1hZ97x9+ETqdhy67PiYpMpWXT/r85sC1bf6Ky8mIUZKtWHWmZocfndVPuiMVe+NtsWOOM1lRXBcRyq46+emZKomgUjEYNCY38AfDtArPVT1ikD40CzlotUgqMRsGadV9dKuqMjRGasIDiopjrlbUSqqoPouji0IePQBPSAeTF4L0WTfoRE5XOT9s+AST9enamsspNWVkxy9ZtbtC/vaCCO+/9iPDwEH748hGyj7xH1uF3OXw0lw2bjwKQmtxeMZsjOr/5Kq0D41An1XvzOtXmT2j/hwEWGR9XScleBFJR5AYAo9n2es9OY4JBYZ9+uZmk+AiEgFCriR+W7WLHrlOsXn+QBV9u5rNP7iPEbGDVus1o9V4MulC6dQjYmXsOLUGqKp3bjrpsiI2POM7madi+YytSSlb/dJgjZ/1IDFSUZZGdr8Hlcl5yb3JyYypKBaUFOkrsRs6fMnD2mJ6KYgWPS+XkIS1H92uwhqlExamcOKjj0G4TzVIfpnu7N8hIG82wYWMv6Vf1VaALG4RiSAPFhNbSFaGY0RpTkNKN0FjqFS7Z4L5ObUei05nYfXAJaY0SyUhqRGRMGD5/NTv3Hglet33XKTQahdU/PM1Vg9oBoNdruXfiYGZ+suYiedNpTKTZEj69nl08eUFdMSdoTv4hd6GUU7W+wuxnBOIFbfyc5RBI/jKZLJ0T41sIgMqqOmZ+sppjJ/LZtO04jdNj+eDtOzGb9JzLLmbl2gPcNeEKdu8/SmllMVqdICkhiTYtMykoOkle/lFGDHni8qq9EHTvnM76TT+TktqbJSt+ItSWSnKsSmJ8Ao6aEE6cU9m0bS9DBvZqcK/VGsbkSdMxGIwIIcjJ3c+5wpk4qhUsoSpNw1WqKgShYbJ+1WqYPOlFLJZA6E2nDv1++6XzleGtXIXW3A5nzc9ohAbFmElNzXF0soZw1ymENhKhCUVjaoq/7hhSrQWgT9fbWbrmNfJijtGvVydiTkRw9Owhjpw+gjXETItm6cREhdKuTWrQf/xLb9zJ0/bg74nxLTAZLB3feKOiiT5hbmtnye39jcXO42jDmgAH/uEK9tjPb5JSmapK+aPLPmkwgNFqe617xxuDq9fl8vDz+pdY+s1jVFXX8vk3W7nv0bnk28v5YPZann5kFC63h31HjyGEF6maGTqwJy53LZt/XsDA3pO4XFrKRRLByLDB/XCUbScxpQNanUSr8QBQXuXG4/OS2Kgnx48dvvReoymomaYkt8fp0GEJVXE764kXPUhVobxEoWlGnyC4/1hzrkGqLqr8Nnw1O8gvP4aj7hxmW0+EMFJddQhdaF+k34HW0hGhsQVf2IG9JrFt1xe43DU0Tk+hvNJLYUExm3cFtrZe3ZvhdHo4n1vaYE/+26uLaNK4ocXStdPoSIsh7GUAI8YT3ghrjtfn3+8tuHPZPwRYKEowNkYn/W1ee40EvdbYLzW5XVCXj4sNQ6/XMnhAG3ZtmMbbr97O6nWHaN3tMeJiw4iJtvHjmk0IUYfHZ2Bgj4Crb8O2T+jS/lqslqg/bNN2796b5Jg6VCk4X6Bn8Y9bKawwUucoxp6zi4o6Gz6/73f7aNXkHoQAjwfcLpB+cDoVKks09O1/zeUlicaCxtQMob0YVKD6y4i0tcKtTaW8rhA/ITjqzuKq2kxR9Wmqy9YhlBB8tfuQ/qrgfZaQCLq0v46fts5Gr9fSoUVLYmMj8flqKSouR1EE774+lsEjp3H3lDn0HPQ8t02cSXi4hZeeu7HBuFKT2gmNztj3zTdJ9Po9V1GfoSmRvf8hwH7JbQiZLYTcoCTMedOsN09q0/Iq2wVO5OtF27n1zvcpLKoMxlBNHn8FR3fN4Mor2nHf5CHU1rnIzj1HaGgosRGxpKTEk5WzF53ORFpKx3+aJYqLTaRr23gqK3JIatQKmz6PK/q2omP7NGzhaaze8PuxacmJrfH7FHQG8PsFihZcDkGIOfZ3CRTpdyB9lWiMTfEo0aCNQRfSGcWbhd7cErNGy+Gio+i9WewqOIsODzWuYny1e5D+S6swpaV0QG8I4dz5vXRu34K2zdqTnJLA96tW4HJ76Nwxg28XPERJaTVCCO6acAXb175I86aJgQjVYHC+oH3LoWEGnWWyLrb2c5A5gE8g3/5dJsttv/NWRfpu86ri+QuFS2a9Z8u+5drXGxn0ZtweH489+zlvvnwbQghefWsJPyzdzbjb+nHvxMG4PT4Mei0fLliI1SqoqfZz1x034ld9LPrxRYYPegSzKazBACpqnJwprSFEUWjR6PdXtsfrZuPWw0REpaOodiorBSZrFJEx6ZQWnUdKiaIoSARIiZQqAonX5yM7t5hapwUQSClxuz24XdU89UC3PyaehUKdtg0WjRuPz4G98jQHC46jk1qS9REUUUWqLYq0qOYYQtqiurPwu7MuDe91VrFk9WtcP3wqJaXVLFm7mpqqShLiMrjl+isvVe5UyfpNR5j96U+sXHuAk3vfJD4uHLenji+/fzzn7vurGtXrTkZvQd5dOp1YIaI/OXWJkiWLHoz1+msWSKEIrYaegGXGDDpGRTQKMegDbM2uPWe4ol9rtFoNsz/9ib+/9j3DhrTn/Y9W06FtKt27NKHO6UEIF0VFLpJiGwWCyg7/SJOMHpeAW1TuYHVeGV6tQtahbOwzTzO4ayZjruv9m5Os1xno26MVO/fbcbv96PQRVJbbMZlC8buyiYqKxq/6cLt8eP0qkoCNqxESm+Vz4mKrcLtBqwGPS0dpQQz1hXr+MWkvVYy+0xwpc1NVfZxWMUmcryyltNSPTBQYbQoaRaHOmY/iL7tsPyaTjWaNe7H/yHI6t7sGsz6c6Awr5cUXV/zaDYdplBzFoqW7mP/5Rs7nltKsSQKPPzSCT7/azJNTRmLQm4mKaGSeMeNQx0cfZa+n4PwRgcjweHhDlkxKuuBpuiifNBVa/FrxS9FtNtjubdN8YDB8UFEEb89awdETebzyxmLumnAFb796B5u3HefUmQK6d2mCx+MjOjqCurpirhk+EJe7lnPZuxl99d8u+bJvzlzJssVbaRTmJtZkxlCnsOTsYfQ6wbUjel1Gw9Yi1EIiIltSVHAKnT6eg0eKqarwM/ammPosv4Zt174vCYuqxFkruECC6Q0qLnflZYGoKXHirnQTlRlW79P18NOhU2gtJip8ZfilpLbKhwtBlaaGRFMi0eZQQn7BslVW12EyGVh/PIehbS7GUbdpMYSFy56ndfNB3H7jUN6c+SmJKaGsWLeNoVf0JCrSSpvuj2My6rlmRGf69GzOJ+9NCnAMj8wNpsS0bj4wsqwi5z6oHCcgoT6sR/HhbQIUNKAqX3z9YM1zD3coURFhqk9M0oXtz7WEGD/s221sMI8oOTGSXXvPMvPj1Vx7dRfenzEejUZh+67TNGuSiNms48sfvkNv0DHx5oB35MCxlSTENiU2umGZiunvrqCqNoo7xt3NocNH0MtyPG4NNYrk512n6dy5RTCeKSiiPT7em3cOg7UTpcVnMIf3QmjjsNriiIxOp7ryPMkJl2rEh07MwuMCk0Xi9Qj8PjCaoaYKUpM7YjY3dEnWVbkpXlaO96wXt9GPKUKPwaClWUoydR7YcuY0+VWl6LUmSitrcHmgvKgO6fTjdfmICAshr7Saz86dYXtBAXVaDafyKkkNt2LQaYJ1RexFJ0mIa8aJszmcOZeFT/XTqW0r4uPCOZNVxIqFTzDm+h6czy3hXHYxjdNj+fq77WQ2jicuNoxQa4w4cGxlQucu7rd7d+hQiZBdBGKTLm7ey5coWa78O19XYYxBp9xnajRnfUgIHeOjmyi/NGeEEMx6czw19vl8+tE97DuQxZwFG1iyfDed2qezfO1mXE4PJUUVgXwg1ceZcztplnmpyI2KDGPAgEHcdttt9Bh4HWp8f174aj3LNueT1LYPJuulIdV+VSUmJgGLxUJ4TA+EuCiAFEUhx34pb1PrqMQY4kOnl7jdAr1BotWCVicJi5Rs3b78kntyfipC+EEjFZxba3FUueq9T3W0STRzS9t2uFU92fnlWCKtNA2L5q4retKzTWMyGsUgpWRZtp0zZccpduRT6SqjyqCy9tRFe7ZZZh/OZu3E5/fQs0s7UlPjCbXpcboCTNgzj15DRIQl+N2aNUnAoNcxe+Zk2rVuFIwdi4vOVEJC6KhPnPueLr5REkLd6codO7QBwC77hCsVoT6mCNnb5/evADBpzEPTUjr8bjpjh3ZpKIpgxku3BiM34uLC0etDEUJw6uw20lM7o9UExNb2Q9mcyy1hzc+n8PklBQUFqKqK0+kkKbkRrVu3xmAwoJWSvMpazuaVcYEWdTjdmIx6pFp32fGE2DLYudfe4G8bdz6Poki0etAoEp0+4CIUQhIa5sdeuB+Xy0llVQ32wiJqHW4KTlTjivcHXnyLn6yNhfi8fmqdgXzj1JhIkg1xJMWlE2dIoE1CMkIINp3KZ96BU7yxex9ZtedweZ14VS9OTx0OZxWFws3Hu07jdvvRanRkpHXl5JltNMlIIS48Ba0WduwOcBW/JDzunTiY9m1SURQRDLG90NJTOkSYtZZhAQ4jZ4uUylRFoyz3lozrG9yDpc7rxqu9QBN6AXQGw4iEuGa/61LR6TSMuzXA/DhdHjy+GlzlKhNuHgPAiTNbuaJ3ILuupNzBgXIHakUtwqDDUV1DxGWU5lCjnmyPlzMOhW27z+Dy+NCZ9KRKlTCLDlVVf9PbYzAYybKbyEirJSoiIAFM5gCdWecAa7309nkFINEbVKyhkgMHtlLrTcJkTiB6fzGxNguWMCPk+jE5dGjdCiUnqtlUV4KqKAxuHAdmE831VixGHfbyWnYVVuPWQoGriBJHARaDjYiQaGzGMIxaM2Z9CNINyWYjen1g7M0z+7Bm0yxaNu1PiFlHea3gZNZxenZtHwyj/UctKaGVotXrrgaeV4SMl/WGkfQoLYFNWgBT9IIN/sJxD/p89NV7lIenTkWPEEkXCIlDR3OY/elPPHzfsGCKySUhr4vXIBQvCgbMJgOO2jIEIkhq+FWVKI1CUa2bWFVlzM298coQmv34KtYQIy63E0/F4oB4mtKfCo+LsjoX0bYIYsMs1Dg9xEZYUFXJzn3HcLkFGq0evU5HXZ0bRRF4PB4SYnTk5buCALdr9gy79n+IXl+Jz6MiAZ1OoaJUg8dpIz21D5069mXLrmyEokFj02LJtBDXNozyBAd4JbZGIWh1GgZXGzhfWkNUuIXRzTTYLAGFrqDMgauwnHC9nghNMrWGWGKNJkrdHlqFW6nx+hCqpFebxIYSxxyOQFDjKKVNqxYcWnQcvU7Llu27GdS/x2V5+s++3oLFYuTaq7sQYg4HIZLefReD3yvHKXo+FqpyWpsw58PgCvbkT7jH51dvlIryd5E+5/ybr9M7Iebi6v1512luG9OblKTL26l17lrKSx0kJARegNPnfiYz/aIJEhcVyg29W1Dn9LB42W4i6wGIi0wMxkrPePsbamqcmM0GBvZrRZd2aSxauovKytpgdGLrFsn079MSe0EFK9bsRwhBy+ZJdOucGazrsXlzDj8s9dGieRKd2qeTnzckGE7bpVNjNm45Rl5xEV06NWbn7tMcP7WN4rJaBgxIIn10PIt/3EPx/qqL7rztUF3jpFvnTI6dyGPf1mNcNagdNouJz7/egtfnp3OHDHbuOB6UZqrZwMihnYiIsLBs5V6KS6o5+fMpKqvqCLOZmXB7wIuWmd6NM1k7ad96GHqdhfBwSaOUxN/l6fv1asHfX/+ea68OMIQJMc2Uk9nbuxobzV8rC2/r6pLahzz2CW1hzn4lUEdDzhRC9FCkXAyg1xp7pyS2Cr8YqJ5DqNXUoCzRJQDXOmjcpBG9OweiObNzD5DeqNMl161ce4BJD35C3i8Korz4ync88Nh8rh/VlalPX89Vg9vx3oerAlRl50zufWQumRlxNG+ayFXXvcqe/edIiA8nO6eEWbPX0K1zJtU1TvoOfZHd+84y5d6hPPnISLbuOIHH4+NcdhEfzllLl3rnet9ezdl7IIvWLZIJCwvhvkfn0ekXGY7HTuYxoG9LzmYV8d5HqxjQtyXFJVV075LJh3PWknW+OFivIzMjHkURtGqRzM49Z1iyfA83j+7JN9/vYPJDnwDQr3dL7n1kLmaTnttv6k1JWfXF+PFGncnKDTBxVw/qC4qOH9eu/32xnBjZwGeVktQ63KgY+wB4Ve1hjSKe0gq5R+aOjtDid/oFUoIQCKkG9t+QzmG2hCCa+w9m07bHE4TZzLRrk0qHtmm0aZXCsRN5/O2ZG9h/+CTJKbHk5NoZc3UqPr8Xn9+NyRh6yeA2bD5KbIyNj+ev52/P3MDJ03ZefWsp29f9LZis1bpFMi88dV09MRBQ0ExGPa1bpqDTaYK2rtGox2wKKB0zP1lDebmDqU+NDr6IT04ZSUy0DZNRj/EXCd1CCCLCQ4L9arUKWu1Fa+HR+4ej12sJs4Vg0OtIaxQTzEgwmvQYjRf7Mpp0wd9NJj06nYaIcAvNmyZSW+uuf0ZgP42JthEdFRpceYHvYMXnc+PzeSivqKK8rBajQXA+p5BGKXHM+3wjbVo14viJPPYfymb/oWwOHcnBUevitRdvIjLCSlhovNDqQzqBC4GwBYpgo6DVxyki4eNSRVVuFEL50eenf0DOq81soXFB27N500S+/+Jh7pt8JSFmA199t52xd33AkWN5gT362BmOnziL0RRQ64tKzhATfWl5xrNZRaSmRDP+tn7MWbARp8vDsZP5SCmDebRB3rZRw6jKnXvPMHz0ayz75vFLvCsAx47nkZ4a00DKJCZEoNP98ynQv5WC+ntpqb/KAOGxZ78g317O+zPGXRKx8cK0hWzdcaLB32NjGlNUepbmTdPwet1ERkdwNut8cP57DnqeO+//mBVrDhAXE8ZjD13NM49ew94DASo0zBaPRG1WH6/1sBDYkcwT8V8c08rC22J8fnmTqsojwcLZqBFGQ0hQwWrdMoWhg9sHC41BoFDJFwu3BfhSKUmIt6EI80UDPrbpJV9+3ucbKa+oRUpJdU0dC3/4maaNA7HI2TkltG6RzKkzBXwy/ydOnSngw7cnBFdHi6ZJFJVU8+0PP9Ovd4tL+o6PC2PvgXNIKX8ziM3n9Te0qf3/ev1uv+9iX26Xt8FLJERgLHMW/ESevTyYrgMwelQ3BvRtyc+7G9b1Soxrhr3wBIlxzWnRpDUFpWdp2TywnbRplcK058cw/rZ+DeqKnM0q4tsffmbwgDYEqGQ1HECfOGdWXdHEA1qhtgBQPKpulRRcIwRPevIn3PPWW4QZDVZxUdMzUONwUlRc1WBQKclRPHj3VYEv5Vcxm62MHBwwmcrLc4mOTL0ku8Hj8THrzfGBvODrejDrkzV07phB186NeWXGYvx+lSaN42ndMpl9B7OIjwtH1idlhZgNvDd9LPM+3xgMYZGqRFUDQE24vT+FRZW8PWtlA6Le6/UTHRXK6bOFFJcEvsPO3WeCWQ2/bt8t2XnxfqkG+7/QoiND2b7rdPAFWbPhMK2aJwdfGlWVPHDXlTRrksg9D89BSnmJkuT3q1RWXbTnoyIaUV4RkIZ59kKQCotXBYqltm+bxsSxAy4pGrP4xz0kxl90Y5oMVvHmm0S47JMGa/3+bajyE699wgqtEGgu7NgaDQa/n8yIX+y/zZsm8kzTS32mFZW12EIDHiYPFZgNkcj6lVNdU4I1pKHG/e6HK/H5VBy1Lgx6HVERVhRF4Zvvd7D068eY/s4yJtz7EUmJERQVV3FvINaAH37cTYe2aaxce4CpT1/PPXcO4u1ZKwkPC+Hc+WJCQozs3H2Grp0bs2X1i7z0+vdcc/MbNEqJIiw0hEcfHM4dt/Tl2Ml8hl73GhERIWSkRvP8k6Mor6jgxOlcGiVH8vHcdQjFiNXsZkCfJhSXVHP0WA4hIXq2bD9O7x7NAXj97zfzxPNf0m3AsyTER3D1VR1o0jiec9nFlJXV4PP5OXYynw/fuZO7HpzNvM830rF9Oh3aBiyCtRsOc+JUPt98+tBFu98STXVNSQADRWC3l6HTG+sDH3S/aRM/cv8wyssvOijCw5KUksq8TI3wdJeyvkQVsoWQJZPifR7PfCk4p0+Yf/ebr3Nl65ZDvu7d5dbLhjmcPlvIU1O/4ttPHyI3r4SVm1bi96lcP+waYmNsfLPkWW4cOY2/Ytu+rwZbWMP9PuvcXsrKnCTER+LzOklJ69Dg88K8nxnYp/WfOq6vFz/NmFHTOJuVz8FTR8nOOsfDd90d9OI1zoijqrqOyqo6amqcVFbVsXLtAT54awIAW3d+UX3gxKoxjzwydYOnIOdngYhTYawW1RUt0eb78X0RQB2rUWe+5JVxub38sHQXcz/fyNYdJ7FajCiKICoqlOjIGOwFuURH2XA6qzGZQvmrth4drASOa/jF/h0ezYadBmqrTzJqeMcGn7vcHkpLYqlz1mE2mf+0cZnNYdQ5q8lIS2LNls1oNBc19Rnv/cjSFXt/Q++4KKL1BrNOkViFmOqSR0f38oTZBhoSqn7Sev3anxGYtEJ7u5SjzW+9vtCi010kPI8cz2XOgg18/d12KiprCbWaeG/6WCrqyQdnnQuv34dGhKIoApenFqPewn9T83h86PUW/L6G+2VZeRknc2NJyeiE2XToTx2DUR+C21OLqhqQ0o05xMi57ALSU+OJjLDyxZz7sVlNLF+zn1tu6EVCXDgvv7H4l/cbACuAN8JqF1K1+gqtBVoh0EsJqkTDmTijotOFGQymoFr4zqyVfPb1Fm4a3ZP7Jg1h9qc/NagQs37rz1RUl+OpTwnx+txotYb/KoDtBZXExGRiz5LBWlZnzmVTXJ1J81Y9cbvdf/oYdDojXq8bm9WA1+PHZNRTVFJKemo8lhAj117dGSEEWedLiIuxkRAfji3UhNPlwWTUY9CZFI3WEC5zR0R4ZQBoKWWcIiV3gziplZonReZ71VqtIUKnu+g0/+S9SWxf9zd0Wg3fLf6ZmvqCnI5aV30QmgyYDfU+Tp/Xjf6fTNT+325+v4pOq0UIBXtBBXsOHKOgugUt2/RBrzeSlXXqzwdYa8TrdaIoAq/Xi0FvpH2bZvUBewYOHsmhvMJBUXElP/y4m1NnCti8/QTOukCkqVZnQqPRR4nkheVCsByJS6osUHQ67Y9CyK8Vv/gu4D9UzL8+taRD2zQ+fncid9zcl7CwEJ584StenhEQDz27diAmJhxrfYa/3+9D0fzXHKiGo9ZFVY2TuLiAvXo6Kx+Pphvt2vVCq9VRXV3J9i3f/enj0Gp1+NUL0aEqOoOWunr35KirO7N3/zm0Wg3PPn4t90++kiaN49myamrQZ6zV6tAITQiANm7uCJ3qamNImjdW8Xp9J6XkBa/Wd0xKFFX1VXl9vy2SmjVJ4P0Z45g8fmDw4cWlZWi0Cg6no/5Benw+938NwEXFVUSEh6AoCiUVbkKjBtCmTXcURaGiooyvvvqAhyb1/dPH4fW60dVvbRqtiYryKo4eOxV09vTtdWn9zMKiyqCp5PW5UH2+CgBvwbgCr8Z4ymOfcEIrwVJv9Oo5c7/F65lZ5vU6Jb+TO3wuq5hunZsEfj6XQ0FpCVLR1+8lBjz/RQBf4BdPndhCtz63snfPfqyhYZzPOcOun9fw3JTBv5mY/R9X9LxOtLoLti/1VYBC63kFJ/O/2ERdnQef34+UksrKOk6etrNi0ZP1L4gLn99dJgtvi/Gqop4+U5toFcHfpBR3qVJ+KzLfq57xGtVen8sLgRKFL77yHW1bB1Iq9h3MIj01hnZtGnHXQ7MZc113oiIj8CtOSssqgnuJz+P6r8C1orKWELOOQyfNtO88gPDwKJYs/prcc+u58/YBDOt91f/YWLxeF3qtsX7b8OH1VtGmZYCuvG1Mb+Jiw4LXfvXddh564lNCQ01BhsvlrvX5/d5KEfdZscc+fh/QTsAqRRc/d6qi4S6D4v4wEOeDw+Wu9VzorLyyllHDO5HaKJpde8/Qo2sTIiOspDWKwefz079PZ+pcfurqlS+TKZRaZ9V/BcDn84rJLo4mOa0n0dHxFJcUUFaaxS2jezU4wON/otW5qjAarWRn20lOTsBsuchvXwC3sqqOOybPYtzdH3DtiC7s3fxKULp4PHVuFWoA9AlzO+oT5mp0CfOGab32cYtVvxypYpBO++19PvxiQY3bVRvMBbGFmqitcxNiNhAdGUrW+RIKCisoLApUS4+IsKLXqSSlxlNWXk1kRCher/MvD+7RY6c5kxtJ0+ZpJCamUFdXw/p1S7myXzNSU6LJzilp4Cj4821xJwa9meOn91BWXonX42nw+dYdJxh3z4dUVzv5Ys79XDeiy69EfJ1XEThkycQmPq//kAS9QDyjlUJpT4AQF3qhGST9fFvtKAkmuSYlRNJtwLOUlTsor3A0MK4fvn84MdE2ysscaPU69h44zOABPdHpjHi8TvQ6018S3ENHT3M6N4Zqh0pZWSk1NeVs37GO8uIzDOnVD0UR/5a36V8RzxdM07i4WFyympzsiwERr729lL+9uoiO7dNZt/TZoN/cUevCEhIQ61U1JV5UCrx+/92AoZ6LnqxV/DyqKnwsoVgpd0zXmvFWVhc2SDRr1iSB9m3TSE6MJCY6lKSESMxmPT6fikajIISW+IRwrNaAWAsLjaOyupCYyLS/HLhbdx5HGDvRuEk8e/ZsYfGi9+jQOonR10zk4J5v+aXz53Kux/90q6wuxGaLrRfDtbjdLob07x9UsFatPUiTxvG0bJbEzI9XExcbhi3UTFFJFU8/MioAcGUB1S5O61T1Ix/K3RKpF0LM0WqT5iyUhbetcKv63hfOrf/gPZc3kMgsaNMqhdnvT8YW2pCHLS2rYc36Q2RmxDG4bx8OntqLp16sxESmUVx89i8H8Kbt5zDaetGyVSf27dvDmdP7eGDSEMJsGjyahiZIemoMOXllDUoC/3mm2hliIwJzdfT0SXy+Sva4j9IsMwWrxciG5c8Fr3W6PBQVV3E+p+QXxwRJPD63b+pUXFOnzj8hJWaYqggx1adIOcXk9etKFeRKj33cUQBFaO2O2oBWnJoSfQm4Pp+fCfd+xPLVgSKjew8eo7i4nKOnAnZbQnwz7EUn/1LgbtyZR3h8PzKbtGbLlg2sWvUZTz1wafmIC+JZo1Hwen3/M1Rp0UkS4pvVz20tIeYIQusPGFm2ch/HT+YHrzUZ9aSmRNO3VwvumjAIgNq6SoQQBQEb+M5lnoLxPo895yCAti6nvIVOpzECCCEyAVTJkcqqgo4XDoWsqq7j7699j9Vi5PEpI3joiQWs33SEb+Y/CEBao0TqTlfj9dXh9viIDE+irDL3LwWw8JZy4ugmyuzrSI2xcNVTQyktqyEq0orPd9H5nhgfQUFhBUmJkf9j+3B5ZR4RYUn1AFpwOmu4csC1QWfP8tX7EQJat0xhUP/WNGkcT1l5DXp9wOlXUVWAIjhSv60MFSAQtJC5N2dqQxp9utdjH78LSTsp5ccAbk/NjtKK3JuTElrqAD77eguff7OFvr1acMXVL7HvYDYfvzuRPj2bU1RcRbdObfh5706iosLR6zSAINwWT3lFPhHhiX8JgPv2ahf8OTunJLi/pafGUF5R9wvSX4OnPrwnPTWWvPyyy0Z//EfArcjHFho4w+GbxWuJjjZRVR4SBG/yuIFERliRUnLkeB5Llu/hm0U7CLEYWLv4GQDKKnO9dW5HfSiKPAB0AEpF8penlXq7qatOaBO9PnU+gPR5N5/PPVB5YRBhoWbemzGOb+Y/yN+fvZFpz9/IFf1aMfezDSxdsRdFEaQkZmCxapn7xQ+ByWnUhdNZO/5ySlbW+WKSEiKCStTve3g0DY7M+zPamayfyUgNmDzlVWXs33+SX55hEll/pqLH62fXnjPM/2ITR47n0rpFSjAQMPv8/krp9W64YAPr9L4kfcLc6IBvAZAFt7TwSF+RTqfZ484bt2jKExyvqMxTL0xArx7NyMou4etF21m0dCfzPt9IWusHeOL5L4MRgh6fh6xzRbi8Dnw+P+kpHcnO2cevq878W2SA08PHC/bxytvbcbo8/1IfqiqDIbKX05D9fj/ZBUvJLV2Cz/fn7sNZuftISw4EM2o1Xlq0aEpm6sUTZmocLt58fzlNO0zhgcfn07ljBrs3vRyM2JRSUlaZKx96nBOewvFvue3j/V6Pbu+FsxC1AD5VP1yIerCF6A0gFM3B0oqcwdERjUhNiWbe5xvJOl9MZkYcfXo255nHrqFn16YcPpYDwOB+PVi2tgpLiAmP14/ZpCciPJmiknOXpI7+q+3bxUcpr7GBNpT5Xx8nPT0DITRohIfkOB9NGkf+Q3B1Ws0/sEl9FFd9SvdmbdDq9ORrfiIvf9ifIqaLS7MItyWg0xnZue8o1lAbZSUubhoZAHzW7DW8NP0Hqqud3HR9D56YMuKS8OLSihw0ivaAEEhPgRwvEArIWG9k6BhgthZAW+mY5Q2z3gdEK/D3wGqpWZSbd7hvdEQjA8Doa7py5+0DSPmV2WCzBTTsqAgbTVNbklN0ktUbdnDN0L40z+zD4RNr/yMAr998hpxCDXp9YOVZrGEkNup8cbIqSnAePUnblpcH4ugZO+/tP8vOk3n4XT6kX0Vj0tFJmHh5SiDFNTc/D2uYHzWQA4BOr+Ao/3PE9OHja2meGagyv+/wYTQ6J1GRCfVSROXg4RzMJgM3XtudO28fEAS3vMIRLB+Zl3/Y7XTVfA8gpFgj4XoBLq2qWRxcwfX2b4osmRTv8Xj7STlVO3361PXZOXurO7QZHg3w8H3DCbNdNJdOny3k5TcWs3T5Hp56ZBSPPjAcISQ+n6C8MovColYkJbRk5/7vcTjKsFj++Ao4l11MXsFFPnvn3nzq3JE4XV48HgcWi4XDR07Spv2gYPHQsPBoThzPpbTsJDrdpd4fv4S3dhzhrAYINeH116KLsZLptvHuEy/gqC5D9UvCw6LJOdaNbNNBkhMyKMhpgVH/nwfXUVtORWU+yYmtyD5fhN6g4q5TaNEusBg0GoWP3rkTgOMn81m74TDvfbQKIQTJSZFBgiPr/N5qj9+7DkAbn3ITxRX3ERNeJsRUXxBgAGmfFOX1+nOEEFpvQc6zjz9Oy1nvltS63DXRRoM1CG5FZS1ms4HMjDhOnrJzz8TBFBZVcvxkPh3bteDA8aN43G7Wb9vDLdcOoW3LwRw8tpqeXW7+Q188N7+CnQdLCA8PQ0rJzj3ZaDRxGIw6klNSadq0KRs2bEBvjOXYsUO0bh0QZwcO7OHUyWOYjB5atkgMaqHB+OX8EpzaENJtgTff4akk0xzPpy+9wcED2wgLNeFye1m27iyK5gAtW4Wj0Sis31KAzQbb9tjR6wMvk06jIJHodRpUVUWn06DVKug0CpVVDk6ezkMgeeieqy57BuLBoytp2+oqQFBdE4h1s1cLWrcIeJCen/Ytzzx2LYb6gq4XKu0cO5HP6bMF9R4kB5WOEsfjj3PWWzBhg7cgpx+SXL14J3iOURBgl9ffVqOTF35PD+xZ3jmnz/38XOvmg/QAi5buYuEPO5j9/mQM9WX2RgzrhF6v5bFnP+fd18eSlpRGjauYrLOBQO6MRp3Zd3AZdc7KS4qw/JYStWlHNlExMXg8XnbsPE+oLbGBMmSz2UhLSyM3N5eCglzCw6PYuXMLttBIMhq3ZOuWLew/sI2kRBuJiZFoNYL9B8/Tv39vPvz7m8F+zp49S2lJPj6fj61btzJ86CB0ei1htkj8ai1o4qmuVkH4qHF4qK7youhCiYyIJSIyhqjIKGy2MGpqasjOzubs2bOcPn2aU6dOUVVZwvszbr8suHXOSvIKjtOj800cO5nFgRN70SiCBycFznHcufsMr7+9jE+/3Mzddw5i0tiBQZHcollisDL96XM7vFL1zqnXL/qIQE3UZGkf20wkzD8Bv3Lqu/InbFVQ2wnBK7qEedPenkasLSbx8E2jXo2GQDn6fQezuH/ypeV+hlzzCqt/eAqA9+fMJyYukjoHjL3xarJy9nL2/J5gMvjl2oLvS7n1tkuvuZwm6/P5Gpg6fr8fv9//C6VKxev11KfW/bbGLIRAr9ejKAparRaNRoOiKGg0mgb/fn2/y+UiNzeXAwcOBP8dPXqEzHQbH78zMZh9+Ftt3ZaPyGjUibSUjny84HvsRdnERMdwz9hApYT7Hp3HhNv789HcdXy1cBtarYbbburNLTf0wuFw0b9PSwC++OHJ0ipHfruHHybfWzDuJylFfyS5+sS5l65gAGPinF7y9P2hXmvti76CCcO08XOWf/B+bU5lVUF0mC2erp0a8833l9q2J07ZOfKLs5BMRhtnz+YQZrPg8fhIS+nI0ZMbKCg6Sfxv5CxdaD07qUgpMZv/vPjjf7e5XC7y8/M5duwYhw8f5vDhwxw5cgS3q5L7J/bj3kmDf9dBUVR8hjpnZbAgnF86aNIkFbM+Iqh/REVYad8mlQ/fvpOIcAt6nZaPP13P3M82cmzXjHp2sQivpzbn4YfJl6W3J7o8/ueN8Qu2C0ED+u3SWpUhtbtReUiV8sfa83d09Hhr3zl2ZrMDAlXtmmYmNAjC3rn7DNfc/Abt2jQK/u3GUVcRarESGxtOdU0gfrpXl1vYtudrVNV/2S+fkRLDV5+/gcPh+EuBqqoqVVVVnDhxglWrVrFw4UK+/fZbFi9ezK6dW+jWMYbNK5/lvslDfhdcVfWzZfcX9O56G1JK3v3kc2Jjw7EZYxh1Vb+AK/NIDn5VpbbOzSfzfyIuNoypT1/Poe2vM+a6HkFz7djpjbVuT+27tfkT2nu92hwN2i3egjsX/PqZl4Q/CkTEBXJCq9GlCY3321Ont0zv3GakRaczMnncQG6fNIupryzE75ecPG0nKTGSd167I9iHJcTIxFtv5vPvF7J0/QpaNm5D1w4tSUvqwM7939G9442XnYRbr01jw5rXMUUOJiK6EQlxEcFqAP+oSQlen7+eLg3YvUI0FM+XcwFKGSgzoa2PkPB6vVRU1lBSUoY9P5esrLOcOnWSM2fOcPbsWfy+Gvr2yOSZx8YGyz15fFpqXXpsZieKcinBs2v/IlKT2xNuS2DR8p/weGuoqNDQv3tgNReXVFFWXsO9EwcTYjbQrUsm+w4EipN/v3QXE8cOqN+aPJw8vcXhx/utInkaGVioQvr7/UOAVTS3CLyzhBB7DUmzvwOY+Y535uGT65/q0GqYSavV8MWc+/jm+x3s3Z/F3RMGccuNvS45Xl2v1+J0CsrLi3A7D9G1Q0s6tBnOsrXTyc0/THJia7ILjKzeHgIoGA0SjcaPVlFxujuSd6KI/MIsLCF6oqNCiY+1kJ4cSVqjSFxuH1k55RQV1xAXayUpzsbxMyWcOFOE2+UlPS0KRQhy7ZVIIMJmIiYqhILiGiqrnBh0WkJCDITZTNisBjxeH+fOl+Oo9WAyaNHpFLw+lZpaNx6vH51WQa+LwxobTaeYVgwZZiE6KhSNAofPS3znFM7b/VRU1uLzeWmabuXa/jUIcRHk/IJjFJWcDZZRLiouJD4+hqoqH+mpCdQ5Pdz10Bz69W7B4WO5xMWG0bpFMq1bJPPpl5v4afMRJo0bGFjlJ9a5VOmf9fDDOKdc43/DZ9CMlchIqWieu3TBXqY588a9rFGUaxWV5976as6KUGNY1i2j34zWav5x9Zf9h7Jp3yaVI8fOsufofkLMGob2H0qI2UCds4qlq19jxJDHkdg4dEpQ6RDYLBKLSWI1C0KtUFUNSzZpKCxRad/Mze6ft+LwN0FjTAiU4JcgkEhvMWjCUYQXVeqQ0ov0VYBUUb11GENTUf0uVH8dGl0ofixcjoIWArSiDumvRlXiUH9xnUEvcHt++8bYSB3tmqr06SSJDof8YkiIJni6S52zkqWrX2fEkMcxGW3MnPs1CQkWCvKqGH/bDZiMet75YCXDr+xARlosqir5ZtF2yiocTBo7EL1eS1V1HbZQM37Vx4KFU0qqaysz7r95XAutVjzsl773Lnfyym8CLHNvzvQqxlMEqg259IlzTe+/HfJ6t46jH2jVbODv5qV8v2wXi5ftZuwt/RjQtyU5uYWs2rQGnUFLfEQaVw7sTn7hcXbs+YYRQ574p8N6Nu+VNE2FbDus3SZJTxEcPCl55A6FsFB46SNJSqDKETcPFTjq4OhZib0YIkKhVaZg9xGJNURgs0qWbNQSE6Ew8doAW5WVL4mJgJwCOJGlsGaHSrhVw4v3qhw+LfjsRzDooEmqoKoaaurgpqsgs9FvuxY9XidL17xO9w6jSYxvwecLl2MvziYmKoL+PfrTKDnATt049h0+/+Q+/KrKHZNnsWT5HvR6LWOu68HH704M9nfk5HrvzgM/vHvvfVWPeuzj3QSiX/26+Ln6XytYvymi6y35KqlKKRACIZwAHrX21b2Hloxr3qSv4deZD79kt3p0acKoYZ255+E5tG2dQkpyHD6vnuKiYnxeQWlZSxLjmtOh9dWs/Okdhg96lMv1F3SplTuQSCIjrDRNFcxdrAKCSTcItuyT9O0siLTBeTtMuk6gKKDXwZa9EqMRvl4JNw2Fpo0gv1jSLA1KKiV5hTCyr49m6QK/Ctv2S3x+OHQSMlMgNVHy4M0QHaGi00KH5pLmaZLyylrefPcH2rRKYcpdfX9XqVq94T1aN72CxPhAVQKnp4rICBsulyYILkB4WAgDR7xEdXUdObmlfPfZFPr2asHIMdMvmoGqj70Hl1a5PVUvB+I4qC8uKhWYqodLTwn/7TMb4j4rluiuRDJP59N0Bnj4Ycp9Pu/MvQeX1P4Wtbhp6zEmP/gJUZFWFEXQrEkCDzw2H4Drhw8mMiaShIQYftq8s96d2JG0lA6s2/ThZTVrr9fPhPs+YuTNM3j97WU8+/dvsJo9PDle4f6bBDERgit7KvTpINi0V/LOFypfrZIkxECISbJiq6TOKRg9GDq3FKzYCpv2SMqrQacJvBCKItBqwOeHhGjBgC6CIb0ETi/ERYLDCZG/4GfWb9zPmLEzePrRUQwb0uF3wV23+UNSktrQtHFPjh4/y4effUFYmAWDLpw7b7kuaIWs23CYl18YQ2S4BavVxKrvn2L4lR3QahV6dG0S7HPvwSV1Xr9v1sMPUx5wCInJCA5phHr/5Y6A//2Tz+Qks9fuz0PIcCTzXv5k7l0xkaGnrh8+tVGoJVAPa9qMH2jZLJlRwztx8rSdhYt3cuq0nW9/+Jmhg9vzt2dH06p5MnVONx/M+5KMzFjy8yq5ffQorBYzew8uo7DkNEP63XfJad2PPP0Z53NL+Wb+g2g0Crv2nGH56v28+MzoX0wkrNwmOXJKMuE6hUhbYO87lS3JLwZFQE4R3DZccPycxK8KCksk3dsK9hyVHDwVqDFi1EPP9oLWmYIT5yQnsiCvGMaNFJhNksXL97Btx0lGj+rGhPs+4tUXbyImKpTqGidX9G+YHO7ze1izcSYx0el0ajMSv1/l4y++paKiDFtoGPeOu6U+HGcvi5buIiM1ljtu7hN05Ph8ft58fwX7D2YxY9qtJCZE4HCU8e2y53N8VDe5a/S4aUhxt5RyiyFx3pW/G8nyex/67BNuU5EXbKtafcJcy5tvavsmRDX5ftRVT0VcCL57ftpCZr05nq07TnDzhPdxuTy889od3DS6J6fPFuLz+WneNJFtuw5w/PRxSsvLsVmiuHtcwFw6eWYrR05uYNgVD3HhmNrikipad3ucA9teDSY6HzxyHovZyFeLtrN771k6d0jn4fuHX0IJns2D09mSrm0EXp9EVeFcHvx8GDo2g+bpYDYJLL/iU/Yel9iLQKOFvh0EtS4ID4VHn/mUEVd1pFFKFFnnS7CEGLhp/HuMvbkv3bpk0qfnxbwhl7uWVT+9Q2Z6N1o2HUBtnZvFP67HFqWjuKSCTi3a06Z1JhWVtbz+9lJemXpTENTsnBIy0mIDdT7PFODzqbRoFuCgl6x+pSKv6NToRx7xrfcWjPdKGdhedajNL9CSv9V+N+lGU2teQv2RdqAsDohq36aKiryfs3P2+SFwENao4Z0YceN0hlzzChlpsezaOI2bRvcM7p9X3zidrPPF9OzSjqiwOKIiQrGGKcz9agk1jjqaNu5FxzbDWbr6dcor8oP7easWyQ2y2Nu2asSrby1h/cYjvDd9LAaDjjsmzwxuE0FGTg+xUYKt+yX7jkG4TWANgSm3Cvp2FpiMgqw8yec/Sjy/YEE7Nhdc3U+QEpnHWzN/YPOWnRw9fp4ah5OB/VrROD2OQf1b071LE0aP6kZeQTlXXtGWfQfOsXvfWcor8lm6+lXatrySlk0HkJtbyJc/LMEaoeXokSyu6tufNq0zgcAh2VGRocGf23R/nFZdH+OGO95GVSVNGscHwc3JO6RWVObveOQR3/p6mz2/PpjSTXztuX95BV8U1VONnoLsa6UUd6PKVz74bv5+kz7iwC8Phn70mc/xeH289crtwXSK3XvPcvWNr5OcGMnNN/TioXuuCpIMs7/8HIejFqM5nBuvHkq4zUJFpZ31Wz4iM6MHibE9GHLNy+ze+HKw9tWR47l0H/gceze/QpPG8Zw4Zadzv6epzp/HrXe+j9vj47vPpgTDS6XksoR/UVmA9Agxujl2PI+DR84TF2tjyYq9lJXV8Myj1zBizHRmvTmB+V9sYsnXj17iGOnS7xnumnAFBw+f59oR8dQ4dzGg10SiIgJU8Kx5n1PtqCE6Jpo+nbuSmZ6Mqkp8Pj9HjucyeOTLtG3diB27TtGzW1Mmjh3I315dxHefTQk6FFzuGr5e8myx01Pe7qFbJsa6vfJmQ4j7A79D30kjq9eL5IXlv4fdH0ubO3ZUKxCfK0L00mg0i6dMocDjrr1zxU/vVFxgvf7+3A3ceG33ILjbfj7J0OtfpUlmAmuXPsuUe4dSUVlLQWEgHDc2ohEmk4XICBOfffM91TVOwsMSGHnV05SW57Dv8AIevm8w9zw8JxgW9OOqffTr1SJYCO3Q0RxiY8IQQhAaam5wvtAL0xbSpd8zHDmWy10PzebJFy6eZrZp6zHumPgKRYW53P3QbF59awmDBrTGYNDxzKPXcPBIDh3bp9OjaxO6dclk+86TnD7b8HxCs0nPI/cPo6y8kmtGetAbC7hm6LNERaSwbNUmPvj0M2LiIrCFWmnWKJPM9GT8fpVJD37CidN2OrRN42/Pjsbr8/Pqizez+oenueGabgzs1+oXjgrJqg0zKzwex90PPTSpyuf371aE+pi3TrdfmzRn4T8C948D/IvIKlnPzjzwsHtZeZV94b6Dy2ovxOv27NaUc9nFrN1wmBE3Tic9NZYr+rYK+pI1GoXRt78dENtX9qZz246UFDlolBbD10u+44vvlqPTGhjYayLpqZ3R6Ncy9paE4BeurXWTXn9Yo5SSj+auY/Sorvh8fhqnx5GTW4qqSvYdzGLX3rOMHNaRVi2SSUmOYu5nG6hxuIKxxoVFlbRtlcKddwT2ybRGMWRmxJOeGkNsdChvzVxBUXEVlhAjjzwwnNsmvk++PTCfcz/bwOmzBXRs76Vps4M0adyFgb0nodMaWLZqCzn2czjdTkoKHdx9x6307NYWj8fHfY/O46dNR7h90kxKy2q4587BbF75AvdNGsLaDYf48ttttG6RHCzVuOfgUmdFRd53D0zxfE+xySrV+gANQcgfxe0PASxaLnRoVOVGVZWbVI86zHV+7CBZcEsLnb7mvoPHVmUVFp8KUjwnT9u54fa36dQhgw0rnqd921Te+WAlNQ4X19/2FkeO5fLctG/xeHx0aNOMu+4YQ25uMaWlVaiaOnbsDhz31ji1C9cNfwE0DvYd+YDz+Qe54dpubNp6jHUbDvPI059TUFjBkw+P5PCxXHp2a4LVaiInr5QNm48RZjPTvUvAxIgMt9CtcyZLftxNbZ0bvV4bFPutWiRz4FA2r7+9LOgpG3V1Z+wF5WSkxXL1Da8zedwVXDeyK1ff+DrX3vIGKOUcPP4Rde4Krhv+Ao1Tu3Dk2Fk+/ux7ymvs2MJDMOpDGXPt0Hox6+WuKbN58O6rWPX9U5SVOxg++rVgMTRFEZSUVFNRVRusf1JUelYeOr4mu6i86j4ppxqJCa9ShXgLZI4i5CN/OB78n/WseOzjPgNxKyBVrzrkgy/nnzaFRuy8ftgLMRcC5Zcs34OUMGp4oNrsnAUbmP7OMsrKa1j81aP07NY0qDlqtRrqnG4WfLsEjc5LeLiV4uIKIkLjGHNNoAxwVU0xew8upbwyD4u5Czt2ODCaDEweO5CICAtzP9vATaN7MuSaV0hLiWb6S7fQvtdT7N/6CjHRNj6au46wsBDmfb6RO27uS1JCBA8+MZ99W14FoFHL+/h5/d+pc3rISIvl1JkCho1+jSM7Z3D7pJkUFFXy/ecPUV51jEPHVhMRlkTHtiOCp5Sv27iLc7lncNRWEWINo0e7LrRqkY4QAqfLw74DWWzYfJRnHw8Es8/+9Ccefvoz2rdNZfnCJ4IJZL8M51n044vFNa7yLvfdOraNUJXFIAXIWw0J87/8Z/D6F1LXlZ5B6lavGTzlKbJrXTUjF696pdTlDrj5Rg7rxLAh7fF6/ZSXO5izYAOVVbWs+O7JILgAm7edYPo7yzAZ9dx1xw1MGHMzxSWVVJRX45M1fLdkDfn2UmzWGAb0upOrBjxIqLWK5i0P0L+vG1UE0liXr96P2+0jvVEMV/RvTVW1k1CriZjoi7XcRgztyIFD2Rw7kUdMdMPc39YtUzhyPI+MtFh++HE3iQkRuN0+5n++kbdfH8mzTzRm3ZbXKC3L5qoBDzKg153YrDF8v2IDHy5YSFFlDiazFos1mj4du9K6ZUagxP/WY9w2cSY9uzVlxLBOnDhl5++vfU9tnZu1i5/h6LE8hl7/Gp9/vSU4FrenjiVrXi11uqpHP/oo5zV+7hOgCISQUnPPP4vWP12K9dmHO2YLIYcChXp/zW1TnxwU2mPQ9pODBnpOZ+XsH9K0cS+TRtGi0Sj88ONuxox/l5KyalYsepKO7dMb9PXFt1t58dVFlJXXMLBva7RahbSkRpzPLQmUI7bC0VMn2bX3OLFREURFRpOc2JpmmX3weF0cPr6W01nruaJfBqCSnprKiKs68/y0hTidHm65oRcajcKmrcfp07M5Z84V0b1LJmFhIXyzaAf3TgyUS1y55gBbtp9g996zJMSHotOXMrCfGTR7qajMpXFaW3p0HkOjpHZB7vz92V9SVVOMVuvH4VBJiEpg1FUDiY+LxufzM236YlauPcDSFXtp3iyJ/r1bEBVp5cjxXK4f2ZVmTRMxmfS43T6efmQUiqLg83v4YeW0Skd12T0PPupZAfDMg+2KFK24CYHUaMRDf5ux/8Q/g9e/lRvpyR+fgyBZSo4ZEue2fO9t84SoiEbTRw55InhC+Idz1iEETB7f8BDozduOc9V1r/LI/cN48enRv+mjnTn3KyQuFI0XnS4UqRoIt4YwfEhfTEZD8I23Fx7HXniCguJAFdewsASctRbSUhsRYozgm0WH6N+nORqNgYy0GFau3cfZc0X06ZlKQqJCfkEePrWcysqAFh4fk0lCXDMS4ppz4VAwgO+WraeorJDwMCNaLVTXuPF4tNx8zTDCQkPqxauLOybP4omHRtClU2PGjHuHjVuOsXPDtGCm4plzhdgLKli6Yi+v//0WFEUgpcqytTMqSsqznr33fscst338AUXQSkr5hT5h3h3/Kkb/MsAya2yY16BUXHCWGxLnCoD337VOi49ufO+V/R+waerLKWXnlGAy6vn2hx3cP/lKSkqr6dzvGRqnx7Hq+ycbFOP+dftp0y6y7YW4XBXoTYHDNaT0M6h3P4pKyujZtX2DWs5er4vKmiKqqguprC7CUVuG1+PE63NzoXqQTmsI/NObsIREEhYaiy00jjBrLLpf1PhSVcmylRspra6moryURukxHD18htT0JDq26Eh0VDhxMZfGXj330rf8/dkbArHPx3Lp2v8ZunRszLqlz6DVavjs6y0cPHw+CK7f72P1xveqCktOz7rn/pqna/MntNcJua9eY/bp4ufq/scBBnDbx+8TyHaqymZDYqMrKcptLOLmHJn5nvXxUEvMUyOHPBF2QaRt+/kk73+0mvdmjOOOu2Zx6EgOuza81ICp+r1WWlbFouVr8ftrsIWHYTJpKC524Pd7aNG4NQ5HLeE2C506tP7DJ5b8ZjjrkVPsP3oKr9dDbW05ltAQ8nLsNG/emPyCUqwhEQzo2YWMtMsn1fl8fkrLavjba9+TEBdGj65NGTFmOvdPHsLk8Vc0ONjE63OzfM30yorq/Lfvvt/xYj2xpPUW5JQDVgkHDQlz2/2vABxczYW3xXj9uhwEBoFYqUuYM/T9N413mK2Rb1xz5dORF0r72wsquPeRuaxef5ClXz92CUn/z7R3Pv4SReMmPiEGj8eFENRHVLgJNcXg8XvQagx0adsCh6OO3MJ8oiIi6d2tIyvXbaHK4aRRYiy1TjfZeTm4PbW4nB4yG6dy5MhxmjVPpaq6DrfLjUEfRsc2LehQX3nuj7bPvt7CsCHtiQi3MPXl75j/5SY+eW8Sg+q/t8vt4IeVL5c76sqeuf/Bug+9BRPWqaocKASHdfE1nersoS1DEufs/3ew+Y8A7LaPvVmgfFHPQNTqE+dZAN55QzPUZI74dNSQJ6NC600Kv1/l5RmLsdnMDOrfmvCwkAYlgv6ZVlVdR15+CU53HT/v3QsaP7ZQKwaDhhPHzqI3aElNS8Jg0JOVVUB6eirVNZUoQF5uIZlNUvCrfk6dyiU6OhKdRkdtXRWKEoLJYOH2G4b/7vbxj4P1JNk5gaI1n365mWnP3xiM36quKWbJ6tfKna6q2x+Y4l5eb4KqF+JAdIo3VsR9VvzvYvOfWcFytN5bYDmNEImqqrwpfXK10MqRB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -34579,9 +34811,19 @@
           <t>Times of Israel, Heartlandtoholyland.org</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.in.gov</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHgAAAB4CAYAAAA5ZDbSAAAABGdBTUEAALGPC/xhBQAAACBjSFJNAAB6JgAAgIQAAPoAAACA6AAAdTAAAOpgAAA6mAAAF3CculE8AAAABmJLR0QA/wD/AP+gvaeTAAAAB3RJTUUH6gYDFgogP9TfigAAbABJREFUeNrt/XeYJGXV/4+/KnTOYfLszOxO2BzZTM45oyIiCGIWA6Io+pgDIJIUFQSUIBIkSM5hl805zcaZ2cmxp3OqdH//6GGWlUXB9Pj8fp9zXXNtb3d1ddV96j7xfc6R+P8BWnmTPyzr9tmSbLaoNnmGhDzZwqrGwi/JkoosJISkSBISgBAIJGFiSUJYwkAmJUlyr7Cs3aZh7bAMZbdwaFuXXpUa/b++NtL/xYtee114urDJJ9sUzrOg0WZH9gZVmycg+R0uRXG4ZexOCcV24PYMXWCZAgBZkVDf+Zkh0POCYs6imDfNbFIkMwnD0AtYksw+w+JxUbBeXHztaOv/Y/C/gVb8vKJcRTtXUeXzENIsd0CWwlVqOBBRbQ6PRDEnKOS9FI0QKFFQo0hKCCR76U+2ozjLURwhAMxiHLMwBJYGQgNRRJgJMEbAGMFhi+N0ZXC4JQpZQWpYt+JDVjKXMg1ZZrum8UhRKzx21LWZ4f/H4H+QXv9+g9PlSZ5jsylfUVRpUlmdLRAsU+wur0w6aSdfqAXHRCRnI87oYTgjM7H7qv8lv62l+8jHtlIc2YgotEGxA7erB69fI5+xSAybxeEuPWWatGlF85ZCzv+XY7+/v/D/GPw+aNVPI4tsLq4G6chojeosr7cHVFUmnqhG2JqRXC346s/GVTb9757rrc4UrcM5ABJ5AwGkigbnTo0yv8Y7ftym/gwVXjvVPvt7nEmQH24l3fkkIr8HSd9HKNSHoVsMd2qZkT6jAGJZscj1S6+Jrf1/DD6UXr0+crzsEDe6feqEmmZHxBtQSCX9aExHDhxNeOrHkW3uQ373D5sGuXPdAH3pIjV+BzeeMpElE/x89JFdvLgvTtGwyOkW9UEHUbeNa4+ewHnToqXf7Umz6I7NSBIMXLOYco8NgA19GfaM5DlmYoCqv2K8ZRRJtT2JNvwSsr6RcCRBJmnSu7cYy6XNLqMofW3xNSOv/z8GA6uvD5+o2qVbPQGlon66Mww2kpmpyP5FhKZ+Gpun/G9+/09bh/nYn3fxuQVVzKz08Nu1/fSlNbqvXohDlQG4e8MAVzy5l61fnMfMCs9B3z/nwVZe2Ft6CB7/6DTOnRYB4Bcrerj25f1opmBy1MUxE4Mc3RDg+Mbg+EMAoGcHie/8HVZqDQHfTiRJp3t3cTQ9Yg7runHNoqsTT0kS4v/vGLzqhtDhNpt8T7BMLa+d7AialoNkdjqOyvMJT/3Y+760Lzy9jyd3xui8eiGqLDGU1SkaFhMCjvFj/rhliIv/vJu1n53Dghrf+PutQzlm/moD3zmmjuuX9/CFRVX84pRJ45/ndIvPP72PezcNsrTOz/reNNefNJGvLK3h/s1DnD01gt+hjB+fan+WdMe9BNxbsdnydO/W4skRY0jPiUuXXBtb87+xzup/+geX/ywQcrnUWxxO6YzGue6wYTgYTU3HM/EKqhaePn5cR7zArav6+OyCSqaUud/zfCc0hvj12n4qr19Drd9OhdfOtHI33zyylgpvSbQ6x3ZywbAO+u6P3ujCqcpcubia5/fEeaszddDnbptMZ6JAc8TFik/NJqdbmJbgrc4Ulzy2G6cqc+aUMJ+eX8UJjUH8k07HP+l0UvufZ7TjPiobt4RqW7Khts2F59bdFFmRLxQ/+Z+2vOX/1A8JgbTmxugVLpdtZ90U50WTF/jC8eRMqP0NVcc9gX9iibmrulN86KGdNN+ynqd2xehNa3/zvOdOi/DMxdO5ZE45Myo8FAyLX63u45NP7h0/5lAM3hvL8+iOEbx2hWtf3k9WN9nYlyGjmePHFAyL1d1pjpkYGGe4z6Hwu/X9eOwKN5w8kX2xAif+YRuzb99IT6oIgL/hVKqO/ROi+jbiyRm0zPeEG2c7T/N6nDvW3Rj5hvj+f27d/yM7eMWNwfoNtyjPlNep9XWTnb7R0XJGjdOpOv5aJPnAJZzxwA6e3T3K4gk+/vShKZw3LYIi/21RrZmCkEvlq0trxsXyx/+8mxVdB3ajyzbGYP2AKrx+eQ+qLHFSU4jdI3mymolhCVZ3pzmhMTj+sBUMi6MbAuPfi+cNHt0xwlH1AT6/sIorF1ezrjfNI9tHqPY5Dro2X90JeGuPYWTLLcDjysxj+sq6dxa/vaE//LG1P+aMhd8Z7f4/v4PXXB88x6Gqa1rmu6dFJwR9A6PHEJj/JBULv4skq2zoy5DXSztrZoUHSYJ7zm3hrClh/rh1mFm/2siuMVfnUKSbFmc+sIPT79/Br9f287mn9vHnHSOcOSX8njt4IKPx0LZhLp5dzv0XTObNT87irU/NLqmQzuT4997sKL0+6h0MfmDLEHnd4qW2OA2/WMf3X+uk0mvn5ydP5FDPoiSrlM29msDCRxmKHU1ZfdA/eaFnpuqTN6y9oewj/2eNrNe/j+oPRm9weuVLW+a7wqMjldgnfIVgy4Xjx2wfzDLn15u4+vAarjtpIr0pjUk3rWVWpYeuRJFU0eTjc8r5zjF11AUc7y0hulJc82IHvSmNSp+Nj80u57MLqlDHVtywBLopxnfymMpAtwR25cAS/PD1LkIulSsXlwImx9y9ld6Uxt6vzh8/ZuavNiJL8MRF07hr/QC/3zjI9HI3r1w2832tS2LPn9F6biYc7mXP+lwin7GedCVjn5n+fbT/O7HiH4cnrL8psqP3L9VZfVO96H7hNFGIt4m3ybLGX4pzH9wh1O8uF5v7M0IIIT7+512C7ywTX3muTQxmtPHjht7x+m9SYZ8QVkGIzEoh4o8IoQ8K0fUpIQp7hRi8vvSn9QvR/Vkhip1CpF4QIv26EJYuRHH/Qad6eNuQuHfT4Pj/V3YlBd9ZJr79csf4e5phiZ5kUXwQKiY7RfeL5wpt40TR+5eq/Pqbo62rrw/X/p8Q0WuvC09XPPKqloXuqb5owD2UPoeaE5/EEZxEXrf46CO7+OEbXePH33xqIwCfenIvpiX46tIaACIulTK3jZfb4px633Ym3bSOeN44+MeMYbAykHkTuj8Nei+0nQij90HizzDya7ByUNwHVmos7qyVXhdawUzAyG9Lxyf/AvuOgeIe6Ps6pF/kw9O8XDLzgM+bLppMK3fzkze7WXTHZu7eMEDRtKjx2//uugxmNFZ3p4nldOz+OmpOeIS4/nF8ZRFny3znFJtDXrPq+sjU/2oRvernkUV2m/T0lEWuslyhClvtNQSazgMgWTAIOFVOu287r3Uk2fT5uaSKJp/+y152DefQTMHNp07iK0trOP7329g2mKXKZ2frQJYTG0NcdXgNJzeFkChA/E8QOA86zgLnTPCfDLG7oeEhSL0AnsNBDYNVBNk9JpIFiUQCgGAwiCSN3bqVA0kFKwupFyH0Ieg4DwLnlx6M1DPQsgoSj0HgHJDdvNWZ4s71/fx5xwguVabz6oV47coh18QS8M2XOrh5ZS/GmEr46tIafnJCA4oskdj7GGbf9bhdg+xclRsxNPO8Rd+IL/+vY/Ca68In2z3y/dOWuMsSyQm4W36Kt/YoAO5Y18+1L+9n0xfmYQnBjF9uJORU6UsXOXNKhF+e3siFj+xi60CW7VcexvbBLOf9qZWzp0b4+hG1peBEbh2knoPgudB+DtT+GmQnKGFwzSKdTrNm3Tp27WknnSuimwJ9TPdaFiBJuL1+ALradvPKM3/G5Xbj9frw+31UVVXRUF/H0UceztLFi/D5fFDYBsUOUKPQ+TGouw8KW8A1DzxLiecN3upMHWTQ/TVd+/J+frasm0khJx+bXc6GvgzP7RnlO8fU8aPj6wHI9q0kte1rRMr6aV2VHTHy4ooFX4/95b+GwWt/EfmE0638YuoSV3hkpJHgnF/ijExDCPjB65388I0uvntMHd87th5JgptW9PK1F9r5zIIqfntWEwA7hnLM+/VGTp8c5rELpzGY1aj02mH09wcudeR2aF4ORoyCGeH1N5exZcduskULy+amfvIcKmrrUVXbe16rZZn0dbaz8tWneeiOn6MVi3h8AarrJ9G5dyemYRCtqKRhYhNTp03l7DNO5ZSTTsQpdYOjGfYsgeAFYG8AcxQin3rP32odyjHr9o1MCjl561OzKffYEAIO/90WNg9kGPnWEtxjhl8xvpf4hs8Rje6jdVV2tJgRX1v4jdgf/tcZvO7nkbMdXuWeaUtc4cHBFsqW/B6br4aMZvKxR3fz1K4YTWEXm74wd1yMmZZg0R2baRst0Pqlw8aD+fdtHmJxrY+WqBOGbwH3wpJoxIKaWxBC8Mbyt1i+aj0Fy8akWUuoqpv0ga53dGSQoZ4uahoa2bFxFbd+70t8/bo7mTZvCStfeYqdW9bx/CO/PxAosNmYUN/I3Hnz+PQnL+ekE48rife+b4DeDRXXQvoNKPvCu0yan7zZzXde2c9DH57CR2aWjb//oYd28ucdI/R8fdFB+lvP9DG86goqylvZsSKb0ApcuuBrI0/9rxlZq68PL1Yd0l1TF7vCg4PNlB/9CDZfDbopOPruraztSfM/x9TRFs/zsUd3Y43FGRRZ4p5zW8jqJl96tm38fJfMKaNFfbpkPCUegdxaqLmJtP9H3PbrO/nWj29mx5DgsNM+weFnfOwDMxfA7fHhdLt56+WnqJnYzI0PvITb5+fhO2/E7fWzY8Oqg+04XWc4P8BTTz7KWWefwZz5i/n6N79Nxv9dqP8TZFfC6F1gxCD1NLwjr6CZJb/7nXHxzkSRZ/eM0hB0jqcnH90+woa+DDZvNeVHPcjg4BSmL/UEVYd095obQkf+MzxS/mHm/jQ8zeaSX5x2uLtsdLSR6OL7sLnLxxnoVGV+fELDWHZG4o51/WQ0k5ObSqiKCq+dVNEkrZmcNSWCYg2BmSrpOlst1P6SlDmd39x1H0++9BZTjziLptmLCUUrkDBRhI6QPnggbtfWdag2O9GKajKpBKFIOXWTJjNr4RFU1DSwceVr9HW1l+7DpeKe5MW/MITsVtBSRfo7utmyYyv33v8QO3bs5IgTvoir9vOQfgV6vwr+U0u2gWSnymvnzvUD7IsVWDLBT9togfP/1MpARueXZzQyu9LDI9uH+diju3lo2zDHNwaZEArgrDqR4d1vUN+cdo/0GWdefrzjxbteLgz+x0T02h+HJygeec3Upe6qVGoC/rl34opM+1txaC55bDcPbBni12c28bmFVeMWpixRck3aToHaW8E5G01Euf3O+xjJw/zjzsbucB50voC+i6xShyG7/6GHc6BnP11tu0knRgmXVTJ36bEADPf3kE0neeihG9nc+iahw8tRPDYQIDtlrKJJatMornov2p48w6t7qamfyEc+/BGu+/F3sVntJder8+Mw8Qlwzea36/q58pk2DOvAzv7WURP46YkNPLh1iEse28PsSg9lbhvretO8etks5lR5KMR3k9p0BT5vFztX5vp0zVq0+JrRnn87g3d8H3s+ENncssA9pahVSK7Jt+CpPvzvfq9oWBz/+22s7U3zwiUzOG5SsGSk9F0DZV+C7BoInsery7by1MvLWXTKhQRC0UOeK1zcyKhj3j9tHI4M9iFJEpHyqgO+bjLOz2/7FIlJpaSPHiuip3UKnRkQUBwoIDskFI9Kri2Np95PcX+Blskz+PY3vs6HzzsORu8F36kQ+y1UXMuuuIfHW2OM5HTOnhrh6IYAD2wZ4hOP70GWYNeX51Pts3POH1tZ35fh1ctmMrvSQ7ZvFYW9X8Gu9Ivd63Ktkic2d/5n0P+tIvrys6O/rWp0HOFwB+xy9Xfx1Z/8/rIassSZUyLsjRX4+JwK/LSBMEtWsucokhzNj274LVlnFQuOOwen6713p8vqJa/88/grt9eH23MgP/z6M4/wxH23s2ffJnJ9KeJvDuKc4MFZ6yG9JU6hO4Nkk9FHNVx1XsrPmICr2Yep63Su2cMzzz3D+s17Oe387+KQBiB2O/hOIeoWHDmplpObQzQEndy/eYjLntjDnEoPiizx3J5RLppVPuZGpZlb5aU+6MTum4Cmh5HzKyW7Q/dlh521d76Ye+bfZmSt+3nkbJdHOr+s1ubJSqeNBzHeL5V5bDz20anUuGIlkZx5HZpeY+1OG9/60Y0cdtqlNE0/rPRAWDlc5qHVjiTeGyBRnX/xA11TIZ/jfz5zHqPDgxx7xoeJVldjKBpGSkdPFElvT5DeMootaKfinHoix1XhqHQhTIFZMMm1pdBGSmnCQjbHXx57mAWHH8mrq9PQsh6KO2HvEaCV9PrO4RyXPbGHw6q9vHLZTF6/fBZDGZ2T/rAdgMc/Ou2g5Eaw+XyynE5FvcPl9EkfWndD+fn/lh289sfhCapLfmbaUk9kKDaXqiN/iyQp/H7jIEVDUPs3kgEH0fAvQXaB90jwncgd9zzC1q4UR5/18YP8V0uyUVZcRcbWePAFiyJ2K0lBqUAVebxGO0WlJMor8m9QUGooKGXv61L6utrIZNIcfsKZuDxennv4Htbse47RvYOUnzEB79QAikel0JXBUeFG6BauBi/eKQH00SL2ChdIYAs6yOw8kIWKDQ3y5LNPk8/rHHv8BWCrASUEqacoiy6mMezkR8fXE3SqhFwqZ0+NIEtw9MTAIa/TU3MsA9uXUd8Ucw33akdfcoL90XteKiT/ZQwW30ce8Lnfal7gbkilqqTwgt+huiJs7Mtw7oOtNEVcHF7nfx9nsqDvayB7MYOX8v3rfkW4ZQnNMxcc8mif0UHGNmn8tSaHCOi7yaiTsCQb5YVlxO1zEJKCz2jHYY0w4lz0/p9uxcZf7v81fV3t/O7Gb/H6048g1ysUe3NgCay8iaTIGGmDxMohzLyJbJMxkzqyXaawP4seKyKpMsKwCCwswyqaGCmdYj7PylVvsWvfAOde+D9IyYdh5A6IXM6sysB4ChMg5FJZ+jfWT5JknGVLibe9TEVtzpPsN46744X8HT/4wb+IwWecHvlCtNZ2ricUcMpV38ZbfThZzeTke7czq9LDr89sZlN/ht6URvV7Bd4HfgSJh6HhETT7Qq757k+Yfsz5lFVNAMBhjiIhsCTbOy5OQxEFdNmPV+8gr1bhNfaTsTUgCw2nOUTW1oAq8pQXltHrPvPv3ksqEaNYyLNj42r+8NsfsHrbs2x87TVyIo293IUxWsQ1yUdmexx3ox9Lt8jvS+Fq8CLZZBIrhlB8NrzTgjiq3BS6sygeFdmhYAs5cE7wEFpajpk10BNFtm/ewoo1G/jwJTegln8Shq6D7KqSBPsgotYRQNd9KMUVkrB0z76XHInfvZRf/0/r4DU/9UUUu/Sd2imOQKqwiGDzBQB8+bl2RvMG950/mZxucuEju/jB652HPomZBHs92JtIZ/Jc872fsuSsywmXVR6wspUQFcU3sFklJEa0uJqkbQo+fd9fy5Pxz2OOhSW9m3uWHvfZB/SWtgNZHDq9OjzQS3xkiHwuS4e8A1e9l7LTalE8KpIClm6iuBWiJ1bjqvdS6MqiBu2YGQMjqeGocqG4VIr9ebTBPFqsSGpDjNSmGJJNxohrWIaFd2qA0OHlBJdE2da+lVPOOIdMzgLJVfKThfGBjcJgy4dI5hYwYYrDp8jS99ff6Iv+0wxWXfY766c7ovGRSqLzfwzA7pE8920uGUCb+jN88Zk2kgWD353T/O4TJJ+C3XPBewTFwBf5n5/cyFHnfxa31/cuj63XdSrlxbewW0lMyYvP6DikmJcwMCUXlmSjKv8KQ86jsSQbEiYN2Yfw6u1Y0rslSSGXpXNvK/VNU9m+fgW5jjSpTaMMP9VNoSdH9MQaZIeKNlTA0iyQwVnrJnJMJd7pQUJLygkfVYm7xY894iC7M4mZ1VGDdiovaMBV58E7K4Tqt2OLODEyOvEVQwzu6eLN117i3A99FC10FYQugl0zIfnk+2Jse7zAHzaV1rt80Q0k4tXUz3CEsTlu/6dE9MrrIws9AeXb1Y0uT8F5Cf76U0q7x23jpKYQz+4e5fa1/Wzuz/LAh6Ywv+avmKZ3l9J2ajmW+yi+9b3rWHzmZbjcnvd0y9O2ZsqKq0jZJhMtriVrq0fGwmal0eUAdpHGbfQy6piHX9+LKXvIqA24zEHqs4/Q5zrlXT6yz+ggoLWiuRpRVJVsNsXyZU+Q1kaRfTJm1gAZRNHEHnUgTIFzgofcvhT+2WEUt4o+WiSzM4E2UiSzLY5AojiYQ1gQnB9FT2qYaZ1ibw5tuIie0HBUuFD9NmSHgpkzaN+9h/Wbt3PhRy5CJg/eo8a22aFdQtMS3LKyjw89tJMX9sb5zIJKvJ4AmZFhgu7NcnLEqLz4cMdbd7+S7/7ADBYCaWid+7XJC9wTRkZnULH0ViTpwIav9Tu4bF4lsZzOhr4M2wezHNkQGIeqgoB9R4OVhopv8f2f3cyMYy7AH4q85wNVmX8VTQmStE2jvLCcjDoJVeSxWRks2YHTGiKtTsIukhiSF4/Zzah9HtHiWvz6bjo9H8GQSyUpNitFeXElIW0rFgodhWZe+PO9LDjqJJateZK1sRcoxnPosSK2qJPwERXIDgXfrBCeZj9mWkePFbGXOUlvjZPeHMfSBGZGx1HtRh8toA0VkSQJ7/Qg2lABxW8HSUJxyrgbvCTXxZAdMtFTapDtCrn2NF19+9mzr4fzLv55KRDSdzVEP/MuYbp9MMs5D7Zyz8ZBFtb6eObi6dQFSxE9d9UShlpfpbpu1D06YBxx5wu5X31gBp/iDZ0ZrrRf5Ar4XI5JP8YRbMQS8PD2Ye7ZOMiWgSyNYRcXzymnKeLiT1uHuXP9APOqfDSHbVDYDt6jwXccd93/DIHGBeMG1dtkt0aJFtdgs7IUlQgZWyMBfTd+bReDrmMIattI21pIj1nSRSUCyOSVGsqLKxhxLKEm9xxZtZ4R5xJkdMLaRgL6buwiybBzMUnbNPJqDcnRGHde901ee+YhvDOCDMs9qH4b/jkRvNODIMAqmIy81IdZMMnvzyA0i+TGGGbGRLKXgn6STcZR4aLQk0VSZBCgxQrk92dIbxoluCiK4rUh2WWSa4bxtARo3u9jYHeKQjpLYEmUPbt2oWg2Dj/qHHBNB9kLig+Q0U3BjSt6uejR3QxndX50QgN3ndNCmcfGC3vjrOvNMLPSC2oZIvkyRkFTL1pk33r3K4V9H4jBnz/d+0TTXGddMncYkdnfQDcFZz2wg+uW97C6O80rbQl+taaPvGHxlSU1XDirjD2xPJ9dWIUn+2gJQlP2ZTbtzLB+7yCTZy9+twiSXGTVBizJTkBvxW30ImGNi+kh59GEtS3MiX+Xyek7qMs9jt2MkbE1o8sBwtomBlwnYBcpfPo+PEYPCcdsckoNbrMHm1UY94k9vgBLTziTztFdrFn1HIpLxlHpIr8/i7AEqkfFSGjYwg5ye5IoThVLt5AAq2giDIGrwYunOYDsUNCGiwjTwjnBQ749g+JR8c+PIjQLZ60bI6GT3p7A3WeyeGotK9fuLCE8J3jwLwmz4o8rWLz0DOrqZ5YknRIC1xwuf2IPv1jRyynNIV64ZAantYR5tT3BxX/ezXXLu1nWmeSrS2twBRuJ7VtGZc2AM9ZrzLvzxfzt75vBa34WOc5frl7mjXjc6oRv4Qg2c8f6gbFKgyp+fVYTC2p8rO9L8/yeOELAedOifHRWOR45DrYy8CwlY7Vw6+/+yBGnX/Q3DQFTcpJXqsmrNRSUKtxmL5pShil7OGz0GrzGfiQsZKET0PeQVeuwZBeG7MVlDpK1TUCTgzisOF69Hac1xKj9MHLqgXCmYei0blxN1FdFZ3EnIiyQbTKWLpBkGH1jEHuZE324gJnSSz6tZiFMgdAtUCQUm4wWK6L67UgShA4vx1ntRvXb0RMaqY2x8Z1fHCxZ2TYkGmqiDMVSZPMailMhtydFvGOI1es2cskln8ThnQSepSApTC4Lcni9n5+dOJFN/VkueWwPP36zC5sikSoaXDSrnLOnRsbMTTdkXqWQ1dWPHW5bc/fLhf3vMpIPaTk7xU0TJjsiifR0qhaeCsBTO2PUBRz8+swmJAkW1Pg4Z2qE2bdv5LbVfXz/uPpSZqj3yhLOaeJf+PmPb+DIsz/xd63EsLYeu3lw2YimRPBqHbjM3ne5SS6jixdTFbQNryLkDVEmrWJSdAGa772DHKpqY+HRJ7N3+ya88QApaZRiX45Cbw5hCfLdGbShPO4mP9poEW2kgKPSRXpbnJqPN6J4VPIdGfR4EUmVcFS5UP12Uhtj5NrTFLqzJXvJpaIG7aQ2xDCzBpH6MF/9+Als29vL4Gia7J4D99m6dSOf+cJVPHjfPaU0qdCY1vAoQZfKcfds4/WOBE1hF/edP5k9sTz3bhrkxnfUTgUmns5Ax93UTd0QyibMG4H5f9dNWvXTyCKXX61FsuGq+9j4+xnNpGBYB5V/lHlsnNgYJKuZJeaaKSi7Bir+hzeWLcc3Yfq7Un2HRFnY5zPsXEpercGUHEhY6LIPU3m3dbmjWMGPd2xn2+BjJLT9FOmlQx/k1b7nWdd5P5qRHz82nh2ktX85rX3LiWUHAGieMRfbeAWChGdKAAQEF5ShxYqkt8VxVLsZebGXQk+WyLGVGCmN9NY4hb4ctqgTT7MfV72P1PoRZLuMf04Y1V8K0NijDoQh0EZK9eBel4NsvkihqB+Uv/NODVB5QQMvvPQsL778KkQ+A9EvgTCIum3jBQA7v3wYsys93LC8mzvOasbvUNifKPDM7lL7EGfthYAdl1duWPGzyIK/u4NtLq6uaXZEkpmpVC48ENc+uTnEiq4UH3p4J3ed00yl185wVuf1jiRzq7wlx33v4RC+FCP8FZ599Rccc8GnP5Ajr8teMmo9sXyM7uGNFPQYy1PzKHfb6E8m8CiClTkX01qmURkqY/9gL0VdoyZaQTafJ5Xr5KVdN9BcdjwpbQe6lCKZTeGw2ehIvIBpqEwpP45sb5KBl/aDLOEod2LpForHhnd6EJvfjhq0o3pVnBM8mDkDSxOoITuKR8XKGuijRSSbXHKZdiYORoCk9IPe6x1K8Ob6vQyPpkuZsDovZafWMLpsANVnY6SQ4Fvf/h+OX7kMNXEX9H4Ze8tKXh0D0huW4PIn9nDRrHJmVLj57FP7+P3GASq8dk5pXkCw5UMMvHY/1c1bIvls/mrgI++pg1//foPT6dJvqZvq9BRsZ+OpPmr8s8W1PrYMZnlm9yi3rOrjiZ0j/PjNbmI5gz+c38KksLtkCXqP4je/f5aJC07G6fK8Az5qHuRmHbQopkZPspU98TUkjR1sH3gZS0mQ0WJo7jAZVxRX2SS2pXUkxYZuGJQFQlSGoliWxUgqjsPuQJUVPG4bGzreoDLiJ+ILEfEHEEJQHoxQHQ1jaIM8detTZNtTBOZHcTf4sDST/N4UzloPjgon+f0ZJFkmvS1Oeku8FLEayKO4FGS3iqTKpDbGSG+L46xxE1gQxcqbqD4b9ogTR5kT35wwRlyjkCpy2TlLmTOlju17+8jLJmrIgZnSUTwqelxjaGiAYs7i+ONOACVQ0sdjW/365T08sn2YKWVuPvf0PrYP5fjykmruO3/yGMZNIjeyj5BvCwPtWtk5p+d++cfnMQ/J4M+dIl1QXm8/15KijsDsm1Ds3oPyuRfOLKc54mIoo9M2WqAx7OL+CyZzXL1VApz7TiVtzeTZN9fTMmY198b38bvlV7Jz6BV6RzuZXLlwzM+26I5vZmvvk6TNrYwWWonlBgh4nVSEothVG3bVhmtMxOeKOabWNaEZGlXhcrZ07KKoazRU1JDTigjLoqhreBwuKsNlDMRHMIVJXVk1YV8An8uDy+Fk/fpNDE3IUejLkd4aJ9+ZwSpaqF4b/jlhQCK7M4GwwFnjxj87hG9mCHu5C3ejH9mhYI+Wrklxq/hmBLEF7YSWlKP6bQSXlCPZZLwxWFRTy7lHz0HTTaY3VdM1MMqu1n7kokJD5VziyV5Uvw1Xo5f2le1cdsU3sNsV6Pks+E6lJ6NwwZ92UjQFbaN5vrComkcunMrZUyO4bQqmJZAlCXtwKqm2PyMreUuM2Hff9XK+9ZAi2uZUvlJeZ/cn89OxeSoOkdWAj80uJaYPjh7mwLMYbDXcffeDHHZsKS6czI/wxp57mdHQRNDro3u4iw2dT+Nw5Oga3UVDVTnRCCgK1FRMBCGQ5bFd7vHR2tVGxBcgGg6RyKbJFQo0VTcwkhylrqyanuF+soUccxunHQCyj4Hcg14fO7vaeX3rWo6YPg+bUrrV3m39jGzoQ2gC77QgQjNLAYy8ychL/UiqhKclgKPWg5UzsEcd5Luy2EJ2rKyB4lXJtacZfrYHW9hO+JhKJEWi2JfDOWLRMGzidddScdgigs1LeOyOG5jo7uSbNz+OqsggBJmOUXZ2L0dRVaonTaZjxSZiSj8/+PF1/Px754NaAZJClddOS9TF4lof3zuunmqffbw++dEdwzyybYRnPj6dw6rL0ZhKRf2ob7Sv+BXg0XcxeMXPK8oVmzVRtcnYPce/f8VpZUulHpHPUpCaGUi9TrOntPNN00C2pbEpIZqr6+kfHeb1PX/k8hPPp6bqQBMV3TSwTBPDNNBME0tYIARTaieOMzziC46F70xqIhXktSJCWGQKOVbv2sLiKbPHmSxJEgG3j4UtM9nRtY/1e7ZTE6kg7PCT7k9R6M5i6RZq0A5CwlHpIN+RRk8beKcEkJ0y2dYE3qkBzGwpyeCq9yLbZcycQWpDjOjJ1RS6s/Tcs5eZDVVMrizH1TSF+uMvo2H6gVDpupee4PDqBC+uaMUwLSRJYs5RJ9O5ayuLTr6AbCpG9aQpTJl/OE/+6bf88HvfxlXxPzB8K0r519n4ubkl47c7zfXLu3l42zCDmQOonUe3D3NYtRdb+FhUYxWyIjevv9EXnX91euQgBtuEcX75BGcwHq8metRHPwCD85DfAsYwP7vzMZ6KP0Xnqm14XD48TicgSBWyjGaSmKaJGMsHvb3fcsUChmngcbiw2Ww4/47VrcglreJ2OJlUOYHRdIq9fft5ZdMqTpy39GAXQZaZ2dBCIVdkqG+Y/nQ/K59dg29uST+aWR3Va8c7I4SkKmT3JFmy8DBC5QFeeuR1zLyJyFloO3PE9uWRoyrOBg/Rk6oRFhhpHQ82qrw+bHM+wtEfueLdGSCfm3OOa+CZN7exdlsHqt2BZQnsDhcdrZs59RNfxOXxcduXP4Js6Vx3wy/4wVULS7DhyKcQiouGX6ylN1XKjk0vd/PZBVVcMD3KVc938OcdI1x30kRCUy5mZPnvKa/b7+vZzTmQvusgN0lxSOcHyxW7sDUhq873z+DcOmh4GHzH89autzhh6ZGctGgeRTFC3hhBEqBpGuv2bKO5pgGf08OqXZsP4KIcTvxuL4qijDPvfSMGJQmf2000EKImWsH6vdsPeVysf5T7fvQnMsksh5+5GCNWLCUXdEF6+yhmRkdSoNifY9qUJk477wSu/PYVfPaii7jw5NO54rsfZ8lx8xG9OsPP9tB/bwfZ3SmUbpX/+eUTTGxsZGD5H9my/EVM42BMnN2mIAT0DMWZO2UCerFAX9tO5hxzKl+97U84XR5u+sIFfOa8RSyeNZFnX3gRfCeVKji0DlRZYlGtH6cql8p6rjyM7x9Xz4wKD6e2hGgbLdAeLyDbXAhbI4Fy1anapQsO8oOFQBIWM5weCdn9AQrcrBz0fhniD7Nq7SqG1QRCWDy67AUM06RoaEQDIWLpFJqms7d3P+XBCNs79vyrSqKwqzaaqupoKK/BaXfw+ta1WH+F2apprOLj3/wIc4+ZzaSZDbgbfEiyhBgDpg8+1kkg7eKMz56KzWFj7+Y2GmdOZFJTPdUTK2mYWsfR5x7O0tMXUje5lp//5YcERu1k+mN0t7dy1KdupX7SJHqevp5Xf3QBr913E7H+EsLV0vPs3j+A1+lA00vGrcPt5cNf+QG7N67gxs+fz9xjT6ci4uella3s2rGVtWvXQez30HkJWGk+NCNKwbAYyGgHQZHX9qTHEasAkrMFt1dGCDHnINjs2uvC033l6uvVLf4yW8tfcJVNe3+rKwpQ7AR7HRd//dPsDnVy0bGn0zHQy/7BbvrjMZqq67AsQdDtIVcssnX/bg5rnsZxs5fw76B9fV3s7G7j+DmLcTtcY/VIFjvX7WH6oinkMwUGegZZ8co6aiZUEPD7qZ86gXBFiD29+2mqrjtIkrRt68DlcSKEYOfa3Sw6ZQFrX9qAzaEy56hZ7Hmzm5q6Y5k270iG+rrZv3MDuZ4tPPfM08xpqcDrdFBXGaC+OsLHv3UPAB//5s/p2LGR1S88xlmf/jqzjziJtj99kzfW7aarf5SPXfpJHrjnZii2g2s2Gc1kws/XEnapfGVpDTnd4o9bhtg2mOWIej/LPjkbSYLc0FbMvRfQsys5nBgyj1p6bWyXPOYDnRKqUEL5Yi2usr+9g5d3JtnUnxmrw7gEhn6CYdloHdjFBUeehG4YLN+xDptqozZahdfpRjd1tuzfw5S6ScxsmExR1/l3UVN1HacvPIa9fZ30xYbGdfH0RVNKgQavk4lT6rn4ixdg5k1MwyRSGUaSJCZW1rJ+7w56Rg6gORtnTiRaE6WQK3LE2UtxuB20zGti4vQG/GEf88+dhqN8F6teu5WBrs3MXHwCx1z6Pb7zuxdp7UpgWQbHL57K3s4hZjSVYuPbV73Gquce5ahzP87Zn/4GDpebgqaXrGxgzdo1mMINsTug8yK8doXfnNVEX1rjS8+28c2XOtg9kuOKwyp5/pIZvO1AuMtnki/WEKqyBVWnOHncyFJVzg1EbWpSm/R3sfDXvryfxrCLP5zXApFPgmRn2aplJNxZVu/aSqaQRZJk4pkUTruTpdPm8thbLzKjoRm/24sQFoOJEToGephY+W8pakeWJGZPnIJm6MQzKRw2O+5DGG8nXHjMu8T9osmzGBgdZuO+HYS8ARoqarA7bDTOnIihG1x92nc4/sJjWHr6wgOx9AkhwhNCaMUMm9fdDpoTyfIx97jzUXqWYZoW+aLG9n19JRTMm89T1dDM1AVHjUkYk+MWTualFTsA6O5oY8WqVRw169SSGgQunFnGcZOCbB3IosoSc6o8BJ0qsZzOsv1JmsIuWqIuhL2BgLfd1rdPPg+4VR4rIWlyeCQkZwmi+nbHmXeFEk3Bxr4Miyf4SoVhicfBvYhHX3yUQG2QkdQoZy06jqNmLGAgPkLI6yOTzzG5diLDyVF2dO2lJzaIJcQHNqj+Uf0c8voZiA+zqa0Vw3x/OKjKcBnzmqYT9PpYv3cH6/fuKLlylmDRKfN56s5nSY2FHgGSsRQ3f+l27v/Zn5hyRCNTjqth8gl+mo9UKBgmfq+Tc46bQ9Bfiq07XG6+9+DrbF72AoZWJDU6wnPLtpPLl3RssZDn4UcfLxlb+S2Q31p6kFwqVT47Xcki17zYwfRfbqDsutWcfv8OHtw6NKaHm3B6ZISgGUBd81NfxOZEKuYEzrJSMuLWVX38dFk3cyo9HFbj5Yi6AEdPDNCVKJLTLZZO8IOZBm0/CI09Q22cft7RFLQie3s7eX3rGlqqG8gUcvTHhphW10Tf6AhCwLGzFrG5vZXaaAX/KZpUOQHN0D/wQxXyBljQEqCga8RSCSpDUT76tQvo7xigtvFAKvKRW56g2J2idUsXLzS+wikfPwGACc017BprBBNP5ZjeWM2KTfuIVgV4/ParEMLgkVu/T3ntRPw+F7pZMsI8gRA7duws7d70K+BeDK5Z1N+4lr6xvmE+hzKe0VtU6xuH3TrC89BGLWx2SXn95mBQtSTHTG9AteXzXjzRWQDMq/Zy/rQIa3rS3Laqj9tW9Y3jd30Ohenlbih4oe4PaKab/tQAe3o6qI6UM7VuEoOJGIunzOKtHRvY1L6LVD5LXsvTUlOPx+kinc+RymcJenz/MSbb/0ZR+N8jp81O5TvqpBpnTcLmOHC+8pooc/01OJx2ms8/OGUpxhRkedhH90ApAxSI+jnxo7MonxDlmbtf4P7rfs3KB65hf+8IrX15Lrjyuzx7x3Vopgd740ugl9b/60fU4nMoLKr1MbXMfcgeYq7oLHI9HtyBolrolWbKsmxO8QQkv6aHsHtLu+qU5hD3nj+ZXV+ez8i3FvPMxdP5zjF1zKvyctykIIoMdF0OI7ezbds2DL9AN03e2rGRF9YvZ3vnHnpGBhlKjGIJk41trQzFY3QO9rJhXymqtLOrjf+LtHvjXta/snH8/3s27iMcl7jy4g/z1PKV7Fy7669xhCVXLJaif7hUjNC6djffPPu7/Pm2JzntEydRUVfGzfe/wqadXcw/fjIO50aSyWG2bN0CQzfC/g8BFnOqvAxmdOIFA906dPmO3V+NZoTwBlSfQGpWVYc83eFWlKIUPaSBFXHbOH1ymNMnh0kVTbKaWTqu4TGwVbD1lSf4yFlnsqlzBzWRCrLFPBMra9F0nfOWnkj/6DDNNfUs37GBxVPnYBgG/fERPE4nfaNDBNw+4pkUmvFuHLPT7qA6XP5XdoCBKisHxZ7/VdQ93E/UHxpPcByK3njsLTx+N5ZlIcsyD9/6OFHh4t4nn2XXznZ2XXk7n/3p5Rx+ZinZIsbUQn11hJqKIPt7Y2NhXIun736BcGWYs09dSJkQPKFtomFqPQtPOoxHb3uCN5a/wYIvfgH8ZwAyWc3k26+UQBsOVWZBjZejGgIcURfg8Hr/WGNUCSFHcbg7bTY7M2RJkqY43HKp0chfp/EswYa+DNcv7+HEP2yj7GereHFfvITM77oMzBRDo4NUlZczc+IUptU3saBlJosnz8Jht5Mt5vF7vKRymVJ8GfC63FRHyoj6w1QEInicLiL+IFXh8oP+Am7/WCrR+KvUosmOrn3sHzxQKjuSitM+0H3IP814/y7ZhLIq7KqNnZ372Ny+k7daN7zrmMWnLmDHml385LIbSQwnGe4ZYeWmbfzsjvvGj0kMJ99p0o+/nDqpVKYqyRLf/v3VqHaVB298lOGuYY6c14Qiy2STWe763n0MdA6xc/eOUmB38EeQ28Dpk8P0fmMRpzSH8NoVNFPwixW9nHb/dsI/XTUOAsAWxelWAGmaaglRZXdISFYpmJ8oGPx+4yCvtCVYtj853pwz4rZxxWGVHFHvB1sFuBeA4idv5KlxR5le1zR+Ix0DPQTcXhoqag4EvawSg1VFJeA+WPe67O8uXDvUe2+/P6P+YIB91B8i6g+9LyZueH0zrz+6nIu+/iGqJ1a+6/ORVJym2gbyxeIhd/LL97/Kzd/6Mo+9+Drt92/kD9+7llDAxzU33s6qzaVQqWpX3xk8H39ZV1nqxlPbWM2U+S34Qz7Ka6M898pGvKqMbpj86Rd/pqw2ypLTFtLb1weSrQTIG8NOV/vszKny0hEvsPJTs3lk+whXPd/OQEajI15CkUhKCJtTAkmqUrHwKzYJCqUFXdOT5qrn2wm5VD40I8rhdX7u3jBItd/O7WeOMTGfLYG2lRBF4+BRBZlCDlmWqS8/YGUWdI1JlRPwjEWW/jdIWILbv/E7hrqHqW2uwR86tIFXMWZM2dyHbg9R1VjFm9u2csnFZ7F97z5efelpnlq1kv1DB7rUevwHoEbSWKvEJ1/bjGOM8bIiI4SgmC/y2es+ye9/cD8bWjux21UcPhfHfegoevb1MjI0DGoZhD9RGi4yjkm3sz9RpPHmdXQmikwKObnj7GYunTOmziQ3qiohLBFQJXms0YVUYnDQqVLptTOQ0dgzkueExiC6ZVHmfocVmngE0s9D8Hx2D+yjb+MwsixRGS5DWIJJVQcCGLlinvaBHlpqGv5hvZkrFg4ZqPggtHXlDhafuoD5x8/9p86z6JT5KIqCa3od80+YgFbQWP61GPuHDkzcKZ/wjvLVMR1cXR7kpvteKblMQwn2bm4jm8rhC3qpqorwhQuP4SvXP0LvaBq9qKPabBQK8ZKI7vs6+E+Bqp/xqzV9XLesm6Jh4bEr3H/BZC6cWTbel7MkQvwIIZAkyS5LCFkIQCkt4KJaH/u/toC7z20hWSy1Qlrfm6ErWWTw7WB35Xdg0guAxN6BDkzLZCSdIF8ssLevkz+88iSmaVLQNZLZDDPqm/8hNyVXzDMYH6EvNsRwapSirlHU/7GenW1b2pk4vf6fD4XOmjR+HkmScLgcGO6D65EjleF37OASg6c3VjN7ci0OFVx6mo033kwk6sXutGMhiCWytPcMUz2xktlHzWT7qlaKBa1k0E56Gir+Zyz/O0LEbePe8yez9QvzuHh2+cHMBRRHCNMCJCHJIEmWIcZnCr1toV0+r4KtX5jHC5fO4KSmEM/vHaXp5rFqxZ4vQs/nxkWf1+nGY3fSPdJPXitw2vwjkWWZdD5LVbjsH15M07II+0M0VddR5g/jsNlx2Oz/0LksyyIYDfzLRb9lWeyNe6F5KdhKKmjLWwfSlvJYo7NEKkeiby9fP17m04fLDOVVLvpWCbU6IeBFUeRSWnFvLz+4+Do+/OVzKRbHHub+a6H/2wDcfW4zW74wj0vmlL9nL23Z5kaYJf6qSEimKVBc4UNCdE5uCnFyU4htg1nu3TQ0lsW+AKw8QgiQBUVTZ07jVAbiwxiWSTqfoz8xgq5rpG12ZEnG4/zg+tfn8iAsQeva3ezfuBdrOIHdEuiA4naiBNzYg148YR/eoBdv0IPdWXoAFFXB6T4g1hWbSnwoQbQ68i9lcPu2/RQGekHLgi8Mlkli6ACqUlZLO3j99g6ObZHYMSCYXikRmHMYC08qtavIDCW4d3vJ/dGKOo2zJrLgxHk8euuTJXfMexzIvvFcwCttCXx2BZsiEXSqOFQZt01mXrWX60+aiKR6sCwBEu9uNDWaNxjJ6rRESwzJ6xYum8xgRmdPbKwxt1Uo/QGWBX0jgwzFY8xoaMYhQb5QJJfP0THYS0OFSf07uth8IL355lb23vcK0/0uZjhstA0nmVoRIqPpJIcSNJcFaN/WgSrLIEusHoizvnuYnGbQVObHMAUum4IlBO2xFOnRNJdce2i0SiqfJZ3LoBsGXpcHv8uN/T2khSVKYDeAdWt7IVgBpg5OH/TvxuU78DBLaun3735yJSMjFjkNagISaQ4Yp+2xJFeetZhcQWPl5jZO+MgxmIaJJEklu0WNluqXgHOmRpgUcpI3LAq6RbJosqorRVeyiGkdAvCPQCiKhKmVfKhfre7j4e3D7LjyMD7/9D72xQq89IkZJAoGz+4eLfW2Sr8IZgopdCGqrFBXUYWm6SSzaRx2O1WRMnZ27mNGQzPVkX8s5vynX/yZnU+v4pwZE9k1xszKgBu3XWXvSJK6kJesZqDKMlv6YuwZTjKUyTO3OorfqaLIMk67imVZmBaUeV3sfXUTq+c2sfjUd7eMUGWZymAURVGwLIv2gR6i/iBBr59kNs1gYgSP041dsaGbOkFvALfDyfZBL0gxkE3o2QG+6EHul6wq5PIanX0xhICQu9QfrJAtMNIX496fPMhhFSEaJ5SxbW8vqk1l3rGz0TUDu91eYnDsrhKTvcdw0axyLipFlNk2mOVHb3TRn9H4+JxyfnBcyTYQRhZZlkAgVBBCViXMQnzcik6M9WUOOlXiBX08Dm2J0uSwYM1NYMbH/FoFGYWAx0V5MEzHYA/bk3uYWtf0DzP3tUfe5Lk/vESZ14lmGCxtqMQSAoEgkddI5DUqfRY9iSwum8qbbf3kdYOzZjTgsalopolLVfE4bby5r4+cbhB02fE6bNzzw/uZMr+FYFlgHMSnyMo4OEAzNOyqnabqugMlIh4fgfeImw8NZUB1gOqF5BrwRlDUA0kNyWajqBkEfG5UK8cJkyVWtAvy5QXeePwtJs2cSIVlEk/lSGcL1DRV4/a5ScZS4+qGuntAPoAx3zmc43uvdfJ4a4zzpkXYceVhNEcOSA1LzyHJICRhyQLJkiTALJV8BF0qiUKJwQGnSiJvjjP77UAIAz+EttMBgdvuZiAxQraYZTgZZySZYO6kqTS8ww+Op5P0jw6zvXNvSW//Dcqmcmx44BWCLgfDmQKPbulga3+MkWwBzbDIaTpLGyrQDJP6kJe/bN/PnJoICyaUsXMwwf7RNG67yki+wKbeESaXB6kP+Yi4nQymc9hNixfuf4WCVqQ/PsJIKk48U6oXimeSDCViZAq592cEmhZFU4HYfprcg3gmTARJEB86EMlSVJlQwE1jbRlRj8RruwVbegX5bIHzP38WobIgDreT3ftLpTXRMQtcK2g4HQ7AgraTYPAGAK58po2Zv9rIis4U95zbwnePqUMZmxeVG5t9YRZHUVRASEIViNIWHetpEXQq5HSL5/fE2RfLM5TVuH55D22jpQcgkTchfGmp6TYSDtVB2Otn2oQm7KqNeY1TUZQDT/Devk5kWcHjcOJ2uEpVCDY7frf3kIv26sNvoGU1Im4HUY+TfSNJ7l+/ly8fNROvw0ZbLEXY7SRZ1NBMi45YCpddRdNNDMtCM02GMgXaYylMS+C2qVhCkCzoBF1OJkYCrH1pAx/+6nlEfEHsqnpQejDkff+Wdno0jSibCLuXc8Kpi9i0p8iaeAND3WsxDZOh3hG6O/qRZk/i6AUtPPhEJ0NjYBhTNxjuG+Gw4+bQ/+dltA8nxvBapXjE6GAcp8tVgs1FvwSuklx+YucIpiXoS2tc+tjug67n8wurSsEoI42EhBBCU5FIGYYo4avesVNPu/+Aqf/NlzrGP8sbY8mG5BPgWcLkqiYWz54zbnT8NTVX1x/Sv30vWvH0avqG4khA0OVgbk2E9tE0r+zp4czp9cyfUMbuoQSZok59yMeRjVXYFZmOkTSzqiPsG07iUGSmlAfZPZRgVccASxoqKSKxbzjOrOoIw70jJIeThMqD/5AKSeWyeBzOUtJfcYEryPT5jVTWjrLmgTR9HQO0betACEGgKsLvHl/OWUfP5sFn1wCp8d1fXltyITt1E5fDPhYkLIwjQSvKy0u9LwvbwVtCn7x46UwkIG9YpIoGuilIFkqFgU2RMa9B5DB0gSRLCVUWcr+eFzOEURIrMys8PPbRqQSd6nijrrf/PcChnaVO6FaO+kjdezL3vcj9VyFLrajzxK2Po21up84SGF4X9WEvdUEve4aT2CSZhrCPmoCHVEGjO5FlKJ3HoSqc0FLDn7d0YAiThXXlWJaFXZEJuZ30p3IUTQvDFDSXB7AQtMVSVPhc7NvSzoIT393vcjgRI+gLjFdCvFNPv02DiWFsio22XYOQ8VFlixEsC5RyxFIfO7b2c9mkSjx+D5PnNfPaw2/y+R//kaF3oEBM4x0DuIoaF586n1sfeHUcKdKzr4+a6trSTOP0KxA4h/5iJUfdtYXvHlvHFxdVv6cfLIw4WsECIQZkgbW7mLdKJxozps6bFuW4SUHmVXuZGHLy0LZhjrl7K1c8uZdYTgf3Iqi5ESQ7NeU1ZBLZf9iPzGXy3HTFzex+YT0b2vrRLYuRbIGOWJq8btAQ9hL1utBNC80w6U3m6E9lOWXqBAbTeXoTWRbWlZMqGPzslY0MpfME3A72xVIokkyV381wPkfbSIpynwvNtBhM59m24t0Y6u6RAVwOJ6Zpkink0MaiZpl8lnzhgNQJegPUlVezeocG+zcydW79eAxadbvJ2iL0tQ8gSRLCEkyYXIvwOPnQmN/7TgYLS5DJ5EllCpimxXD38BiDe5kxfWbJep74GHiWYgmYGHLylefaWXLnlnHY7LvTgMMU8xYgWmWjaO0o5kwTc4S3e1BZAv7n1U6e2hVjdXeazz+9j5GczlO7YnzqL3tLir/zYhj+JbNnzGGwc+gfc4VufJRn736BRQ6Vpoif+rAXp6owpyaCXVHoTmSxKwpFw6ArnmEwkyen6QRdDn67spWox4nHbiPkKlXc220qkiyzZzBJ+0iKNV2D9Kdy1Pq9lPucbO6NsbCuDI/dxoyhBM/9/gWGug+MEpwQrcTr8uC0O/A6D/jBAY8fxzti4WX+EMIStOXKoH0tsw4/UIZTZR+F+rlsfWs7hmZw+yd/SOtNN3BCuJftWw8ABawxp3XdKxtJJ7M88MxqLCHIZfLEhxJ07+rl2COPhaEboP0sQFDjt7P2s3MJOlXW9aZZcudmLn9iz4EQcumRQbJiFHPousZ21bKUXdmkSIZr4mEtPYDdV8Uj24f5yZtd3HNuy3gdzEufmMnGvgxn/XEH/WmDqvo/gm0C08qD3PN0BmZ/MOYmYyl2b9qHp6CjSRKb+mJohklLmR9VltBNi3NnTuT6VzdjCoFhWUyrDFHtd9MRT9EYDTCaK7KqY4isYbCovpyO0Qzru4dRZIni2A5x+9zUffRYtr+wjmlloZIkME1+t3onheXbefZ3z3Pb8ptRFPnvIjXfSZuWt6LLQaRilqkLWsbfP2aGzP3pWravWs7iUxfQ19ZLqEoirwnK3tE9yjRM9u/sYtnTK+jb2kksnjlgaD7yJi6Pi2nTpoH5GfCfPg7GGMhoJAoGfzivhW2DOX61po/HW2P85IR6vrCommKqF7saZyRhpLDEHlk4tK2ZhGE4XRkKIyX03sa+DPOrfXxibsV4PrjSa2dpnR8hSoMd0fth/3kopPEq3g+8e71BL4NdQ6i5Apv6Ywgh8DntiDHjqirgxmlTWFBXxoSgZwzNYaGZFqm8QcRjZ0XHADnDYGZlCM2w8DtUDMui4h2RpFw6x/7WLi6/6bNM+fSp5EM+dNOiMFZlUOG007mz6wNde0drJ4+/HIM9K4lUhXH7DqQHp08JgqzSsaOTQq5IdxxeaBU8u0Pwxl7xDhfL5M0nVtClDRHXCwdVY/zljmdpbGpEIQU9Vx4kWZfvL9lKXckiHrvM4lofyYLBn3eUVGxhZAsud5Zs0jLzDrFdXXpVanT9LVHL4ZZIxdbjn3gyZR4bw1kdS5TmHblsMrIEd67rL4khn72Up3QdBrKTsDeCaZgHOfh6UWfTm1vRi/o4fOWgjIcic+m3L+KJHz+IKkmEfU6qAx46RtO0jaSRZIk7Vu3ksJooW/tihN0OQm4HWc1gSnmAt9oHCLnshD1Ont/ZRUPEx2C6ZIGO5oo0z2mka3cPxXyR1/+8jE1vbuGWl69nyWkLySSyxIcTCEtwzw/vZ9Vza5k0o+H9W9EiR3cuiBxby6LTDm6LUdlQgV3biRaoItY/impXMbR3w3XzmQLLX1uNLeJAUmUUj4owrFKHPQGzZ84GFFBDINlIFgzKrluNbpaY/d1XO1FkiYagg1ObQ1w8lgsuxjbid8sYRWEde1UioY7hwvYVsqJSjPU0/vCMMq59eT9nPrCDjX0ZZpSXdtBD24a5dG7FWNRkfqmTXeZNjll6HE/teJTG2RPpbesnWBZg61vbOezYOciqzEDnIA6Xg1B5EMuy6G8foKapmgUnHsYjP3iAsNtBuqCzKj7IMY1VZAIeCrpObdDHC7u60S1BU5mP/lSOfcNJol4XDWEfLlUlVdRpivppigYo6DFyms6ck+fzmZ9chqEZ7Nm0j60rd7D6uXW8+dhyjvvw0XiDHrxjUuHrv/ky37/opyw+dQGNMyf+bdCAEGQKORSvyhdPK6AdcziyIjM6GCdcERpPctSY++g49lO0b191EHNVGQJuSOXB5wBpaqCU0RFgFQ38h0VJbx7F6C7w8Y9eUsJEhy8D9yL6hnNcMqe09i0RF1PKXDSGXQfNXgQQxXYKwkJS2A1jFf6fPN4dcnmk40BWvJMuJehUmV3p4bX2BI1hJ7ed3kiF186pLWEunVMxXirBwA9Aa6Oy5VM89fTT2PwKrWt2Yugm846dzc8/fxt7N7dRPqGc5EiSPZv2ER9Kct2nbuasT52GLMusfmMLe9v7SRQ0GkI+8rqJ26agKiq7hhL0p3J4nSozKiLEcgW29Y+iyBJ2WcbtsNMU8VMd8LBq/zAD6RxT5rdw5Y2fQVZkZEWmrDbKjCXTmL5kKr+55i6Ge0eI1kQJREqYL7vDRrQqwq++dgezj5w5/v5Bbpyu0RcfJp5J0zsyQHW0nGRvgr/87jm2LNtWwlstmEzrml0YhkF1RGHNS5sYWL8KvahREywVi9VFoC4k4XFAU1QiJ2REtbcElDMtbMFSkKPGW8FPfvBTpP5rIL8BghdQ5rFx1pQIR9T7mVrmpsxjO4SbJMjuu4VCKqYnhoxbf/dSfo0C8OnjnSlLcGG4UvNYruOxecqZUubm8sMquWhW+Xh7wqBT5SBbI3AOOCYjKR7Wr9/KjtZtFPMaQkC0OsyrD7/J6PZONjy/jrxp0jCtntcefZPetn7O/dyZSJJEeW0Zq55dgxACU1iosoQsy1QHXLSNpMgUdZqiAbb0jdAeK7kFjVE/QbcDUwhaB+Msa+8no+lMXzSFq371xQMx3HdeasTP5MOaWfH0Gl584FVOuPAYVFvJ162aWMnOdbt566lV1DZVE62KHBTUKBgauq4T9Ydw2O1EvUFqm2qonljJpje3smP1Top5jRdffIM3Vq9mV1sb2Q1bkHWNLxwlU+mDzlHIaTCcgVgW9gxDNqYhuVWsvIniUFG9KrE3BjjzrDM554zTwLMQQhceBNf5my7n4BbU9N0M7s/Hshm+c88ruZgCcOfL+ZHON11fa5imeOMxH57q99nLWORg79GlRWo4jx9+58fMO24OLfOa+P5FPyPVG0MgSBU0tL5Rdr+xhcxAnIjHSUozKJ9QRt3kWmRFpnXNLqJeJ9MqwrzZ1kfrQJzMWOuh45priOeLJMZKOzTTwmdXSeSLFHSTjGZw5hWncsUPLsHueG/kSKQqzIIT57HsyZU0z24kUnUgB94yt4mn7nqeupYJB+ljh82OMgbTHc2kKA+EsY2FN8tqo8xcMo2efX289dQq0gNpJLuMWuHA0+yHjhT7RwXLu2SKNhVR7iE9pDFm32FZUOzNURzIowYdeCcHMPbk+f3vfk8Z90Pv16HsiyC9v4qM+M47CXk30L1LSy++euRbMFYfLEkIWWFbPmMh8rvevzkpe2HCbyB8Mc3NLTRPbqZ8QhmRyjD/c983MMMqUa8LSYKeeBqnTaU7nqYjlmLqghYMzWDTG1uomlhJIOqnJ5El4nEyIXjAKq8OeNBNk87RA27E5QsnI5Dw2W3ossS37vkaH/rSOQcZee9FHr+bXzz3E1rmNR30fllNlBue+iHHf+Tod8cNTJNkLoOwLHqGB9EMHSEErV1tVDdWccUPLmHqgskIwyo1RJMo9a5EoU84KDu1lopz6oieUoN3ehDpEBGozI44fX9sY+rMKUybNr0Eqqj+yfvevQCisIdc2kKS2DxuzI4v2jFuj90tn6goluqa8LGDRq//TVI8pWGR9gbiuRDf+cz3aJnXxJ9/9xT5kEnKJdB1E5EzqfR7GEyXMjXLnlzJ5je3MWFyLZMPa2aoe5iefX0MpfNU+FxMjPjoS+bI6wbbB+K8MwfVGc+Q0XTwubnk+iuY/FfM+nv0XuA/l8d5SMBf11AfLocD07KIZ5JkiznKAmF6Y4PsH+xl8qRJHHn2Uvra++ne1YMwBd4pATyNfuwVLkZe7EVxq6h+G4F5EYy0BoYotVNKH8BtS5bEl7/yZQ6fkYeB70D510vNw98PdEjPUdh/K9n4aCExaPz8rpfzmw5i8CXHyZ1mQb6irqXoSSXCuMrfL/pQAq0DfMeyYOGp/OmxB3nmDy8wmkvinRrAyOg4azzYK10MJrIY77ihbCrH5je30rOvj8NPX8T6VzZyypQJHDmpiv2jaTrjmXdV6wOkizrRphq+8KsvUNtU82+D2uqmycsb36I8GCbg8aPpOm6ni/7YEIlMiogviM/txet0I8syC06YR3w4wd4V+yh0Z/FOD+KdEsAWchB7pQ/FqeBq8GIkdewRB+56H4rfhjZcBEvQMqOZ++95AFkkSmvqP62Ei34fNNp6DwH7C+zfXohLlvalO1/Scgcx+PevarlPneg+P1Kj1uZSJt6G9zm9RbKDZwkM/ADZUc9oxsYbr7xR8uckiXxHBnuZE1mVCS4uQ/HakFUJM2cgxny64Z4RNi/fSlPYx6zqMH/cuI/Gqgi7x4q1/ppmHTGdb//+67i9/16ctSLL+NwenKqdsDdAyBcg6PFRX15NZShKwOPDabNjCAuboiJJEjMWT6VnXx99e/rQBgt4JgewBeykt4xSHCiUpqYN5sfi0CA0i0JvDkmSuPJLV3LswrLSbIvq60vTad6vb77rJuxSF8Pd+qb5VyXGO8/KB7sD1s1DXVrKZm1Hz36AUXmWVpoLZI7yza99i5ZZzZh5g9SmGM4JHhSHDBLIDgVJAt+sMNETa3A3+vBOC44luHUyHgd7PQ5OOH0RM794Nl++9fMcfkYpSKLaVBadMh+v18XU+ZMx9JJ/uXXFDlKjKZKxFPF3gN3elUjY2/sPJUWqw+VUhssOynG/jcvKFfMUDR1N14mnSxEmu9POV2/7PCd+9Fi04QJ997dhFU2cE7zIToW+B9ow0jqOChdWziDfmQEhmDRlIt+8+lugtUHmjfHC7/dDWqYfu7STwW49rWvWLQc9pO/8z8WHV7RZeuHKidOEZ3SQg1oZ/m1jyw3hj0PqRRTVTcHw8/rrr2OZFtpQAVvUiWyTsYUcJNYM458dxhYq9YQ0Ejr+uRFybSlS8Sz7O4fY3T7AG4+9RcvcRjp2dCLLMt/83VdRN7RxtjdAXW+C1/70Oh3DCTTTRJJlunb1oNgUAlE/iIP17K4VrWRv/AtbNu2j5aR59OzrJZfO432HMbd52TbWvLCexpkT35ex1j3STyKTxrIEbQPdhLwB3M4D+nL2kTNxuOxsfX072Z1J9FgBK2+CKHX3kVWZ7J4k+mgR1a5y7bXXcsS8EBhDUHPTB9q9sS03EfatpmNLITlij33uPVsZ3vtGwvj0Ke6FvrAyXcsbeCd+lPc93lDo0PNpUEIsPf4qnn/lOXo6e5HtMpIqUejJIQyB6rPhnuglty9NviODo9xJpjWBkdTxzwnjmxtGz2too0X2t3bRt3+As644jRXPrsa5d4D+XB5ZgvmhAJNjOdKb99O2uY2MKtMwaxIrn1nD7o17qWmsxtANhCXY8b0/0p3IkB1O4J5ZTyFbRCvoFAsavlApJn7fT/9E+/Jt7Fq/lxlHzjykL/3XkN79Q30osoyqqpiWiSzJGJY5DvJvmj0Jh8vOtrdaS5bzWMmnVTBxVLmxNAvVZ2PuzFnc9Zu7kUbvhJFfQ/Sz73/dEaR334hV7Cc+aDxz9JdzD7/nDgb4xLGuTr1gnVdVl3ZnslU4I9Pfpy5WIHJZ6V+ti3nzz+LRJx9Fswz0WBEsKPblcE/yYiR0EmtHKPRm0QbyaCMFFJdK6PBy9LiG4rZh89koGjp6UqO/MEL3zh5GsgW2GTnWpBOs6BpmOF8K0i/yeJkSLzD00ibyu3sZ3NXD1n09eAMeNj+0nOM0eKyjhyHDoL2jn4nTGpBtChte3UTznEY8QS+ZRBZR1Ni7s4sn73q+hEaZ21RCJ76HJV4WiNAfH8btdOO02ZFlGcM0kCWZTCGPawz1sbW1FSSptIPfNuBiBfS4htfh4eEHH6E6OACOaVD+5Q+0e+O7H8bLI3TvzMcKafH5u17J9f1NBt/9Sr73suOcF0ar5arMSAzfpAs/gP+hQu9VkFtF1dQv09a1j40rNyJMC6FZCN3CUe6i2J9H8bxjfA3gnxPGKpoobhUEOKpd5NoyyA4F52Qfmd1JMkUdQzcRuiCvG/QHoTWfYa2aZ9PeIWRJYnE0zJJQkMaURmz5DhpTRXx2G0P5Iq2jSXLDSTxlAZpmTUS1qQzsH6R8QpQp81uYftQs9mztoEZA99YOlr28gcmHNeMLet8TH20YBuXBEKZpkRxMUltdhSzJCF3QtbuH7StbaX1zJ4pTQbbLWMXS/QpTIMkSF338o3z2is+VynELW0ojdz5I2nXbd3GqPfS3a60Lrh75wSF8nHfT6uujxwYr5EcnTPFHjIrb8Dec+gHqTRIlSG1+K4bnFJYcfTjrVx6os7WF7DgqXehxDW2kgDAEjkoXxYE81R9rJL8/Q2rLKK46D5nWBO5GH57JAezlTjJbR8l1ZjHTOoq7NG1MditYeQs9XsRZ4wYhaEwqKJLEnEiIlKazP5PFFIJto0layoPEsgWKisy8cJB8eYCquZOIVkdwOO3c+9MHqXc5iXhLAL1X23o5/lOncfyFx7yn/9zW30U6lyWzP0XYF0QraPTs66V1zS4Gu4eJjcYJHBYl35Ee7zAPcNiSeax6cyW2wltgrwMlWMrSvV/mtj+DbeQqunem4qNDxXOXfiPx5vtiMMCGmyI7ph3hmRbPLKLq2Ec+mOkZvx/6vwfNy+jo0Tji2CPo6+x/x0aXx9vi5zsyqH4bZs6k4avTSCwfxMjqOOu8DD/bg39eBHu5E1e9l/TWUVR/qVm3u8mPNlwgsyOBFiuS78zgqHBS6ClZn7aIA1tRUMzq+F2lVGOmqJMt6mQ1nXKPixOqyqn1uEhpBj6biktVGMwX2JlIMZgr0J3LE/Y6CbmdUF/OFT+8dDxrBKU6aIfNjtNux+1w4bDZx2E6y/6yEpvDxt0/uh9HkxdJlKaqWQWDXHuGqvpKlr26nKYaA9pPheobIfiBBovS//oFhHzr2LE82zr/qtghdel7moufPNbZqemcEilLuopiMo5A4/v/Zed0CJwOhV2EQiHC5U28sewNivni27IN1W/HXuZEGALfjBCFnhyKWyXflQEhoQ2XdFTk2KrSKNe0jjZcLPVuDjsw0gbCsJBkieDicjzNfmRVxswY48dbCtgqXWRiebwOO5mIAgWLuoCXjKazPZ1miz3P/lyeN0aGaHF5cakKC8sizC+LcGx1OQXNYMPgCL2dQ2hrd7Pplc1odoWqiVWE/QF87lIfanXMDwbYsXon+XSefVvaGdRGEYYFkkDx2tAG8jhVBzfeeCPHL51YwsKFPgzeY0F6/9N+U50v4MzfR9+eTCKXsD511yv5tg/E4N+9XNi3/3XXZZV1UjTZ24Z34oeR3mfQG0kuJao7zgd05h5+FfH0KOvWrR8Hm5U6pNtxlLswkhracKE0UXuiD6RSY1BhCgLzoph5g1x7Gtkm451amrEw+lofklLqvO5p8mGPOjGSGpmdSVS/DVvIjrPCVXLFkhrFiIplWigBFVuZi6xNoBUNhE1itCeNUTDZ7ijw1r4BOtJZtscT5AyTImBzKjhtKh0jKY6dUEa4J8ZrD71BW+8Iw/2jRKsjByU5gmUBHrjlEfYM7AcZZKcCJmR2JJB1iS9c+TmuueqbpQKC2J1Q+f0PxFxhGcQ3fhW3s4+ePcWOhV8fveo9gzXv9cEPfgCXHu1ak0ta59c1p1yj/Rqe6iMOLSrSGpc8tpuzp0SwjSegJQieB44pEL+XE8/4Jjv37Wbnjp3jOshI6ahjo9LfDja7JvnI7UnhmRrA1eCj2J/DTOql4VQ2eWyX6oy+MUC+M4t/TpjUljhGWiezO4UkS7gbfbgavGixIpntCSRFRnEqFLpzSDaF0X0J9LSGb0YII2NgpErhU9mp4Gn2M9BdEtE7Eyl6/Rb9fWmiXhf9ySzrOwdZ2zlA1GVnkmbwh/tfxulz0zK3iUK2gGpXue9nD9FR7KfQk8PKmmjDJRUiSzIfu/Qifn3zzaXJ56GPQvAjJd37duxbt/jwwzs5ZmJgrGX/u2l4w3VE3C+xd0N2tJDmw3e/mu/9wAwGuOfVfN/lx7sOc/nkFqH3KbboKSgO/zusSMZ7aT2wZYjRvMHvNgxw4cyyA9mm7HIY/AkEP8x5513Gpu0b2be7VMLiqHSheFW0wQOVdlbWxMjoIMBV66E4kEeSJWwRJ4pXxUzoDD/fU+rxDKg+G7m2NIG5YQr704SOrBzLrAj00SKKW8FR4cJIl7q1u+u8IKDslFryPSU3TXYoqG6V4OIy7BEHtogTT0sA9yQflimQ7BJJYWBmStEzwxJ0jqZZt38QwxLUNtUQiPhJjqSwO+w8cP1DFItaqTpQkUqDtYoWp55zCg/f/wiStrdUX+1eAu4DkJ9zHmxlZVeKB7YMkdUsom4b1X7HQTl4PduPtv8HFNNxIzZgPrXo67Hb/k6m4G/Typv8YYds3zX7aE/ZUPI4qo6+50AEJacz6aZ1pIrmQd957KNTOW/aO7r2WDkYvQ+sFEb4Ks7/6Hk8++RzJRyXS8HMm4cOkDlkyk6bQOzVvpKe7s1haRbaUB7f7DCSBIpXBUVGtskUB3IYCQ3FawMLVI9KcSiPkS354q4GL0bawFXvIbcnhb3CieJWcdZ58U4LHJTGE5YACwq9WbI7kkhuhezOBPZyF/pIAT1xAKp6xuWnMOfomQgBA/sHefAPj2MLO9DjGragndzOFKecdiJPPPwX1NFbSqN2vceBegBY8NiOES54aOdB9+93KHR8bSHhdxQd9L12CeXRZWx9LTtk5IvTFl2bjv3NIOPfY/DSq1KjpiG+37WnmPQ5VpHYcyBQEnHbeOyj03DbDpzm8nkVKJLEmneCsmU3mDEwhlEVkycf+QufuOJSHE77ezIXwCpamFkdW8hBpjVBvjNDsT+HPepEaBbIEmbORBQsrLxJoTOLkTKwR53osQJG0UTx2sZTcnqsiOpTybQmcNa6cVS6iZ5cg29GEMwDWau3I2vZPUlc9V5CR1Vgj5TCrYpHxTM1gG96kPAxVZSdWos74sY0SmMI9m1tJ9+ZKQHoCgbFnWk+fOEFPPXnZ1BVCQpbobj3IOau6UmjyhKXzztQjem2yTx+0bSDmJvY/TAB9zq6dxbSlsV3/x5z3xeDARZkYr8d7dM6hZEVWvfNFBPtByCeO2PkdAu7IvHSJ2Zw97ktXP1CB79Y0XPwSSq+DVU/gz1LkYZv4q7f3M2XvvYlvAHPe4sXm0xmVxKraB60Y4qD+VK391lhhCnId2WwdAvP5ACyo7SbJVVGFEz0uDY+tMpI6+T3Z7AKJt4ZIbShPMm1JeB7ZncSPV6y8s2cgeyUSW+JU+jKllRDVkd2Ksh2CSQJZ50XyS5h6RahcACn28Hm5dtYvXwDgflRsruSuAJuvnTVlfzx9w8iDf0M2k6Guvug4tqD7vPGt3r4+osd3H1uCy9eOgO7IpHTLf6y8wD/tGQnet8vscyMNdpn7Jt/1cid7ysj9n4O+sEbiMuPcz2THDIvbpha9Azv3Yqv4TwkWeH4SUFSmsltp5fmGaqyxEdnlfGh6VHsfw0ml+QSxtezFLJvceJJl9DYPINV61eTTry7DMNV58HMGJhZA3vEgeJSMXMGtogD2a7gnuSl2Jun0JfD3eBFG8qjjRRL4nG0iOxUKPbnMNIl3emq91J5fj3CEFj5knFlCzpw1nowkjrprfHSaNmMQXLtCKpPJd+ZwVnjKamSjIGVMxECHBVOjFENS7Noqq5j7rGzefb3LxHPJdGGC9RUVvHz713P1V+8DDJvgmNiade6F77rPk9vCXPJnAo8doVav4Mzp0Rw2mR+fvJEVFlCWAaDb11GNLqXXSvzQwXTPKHu8ELiX8ZggLteyac+eYxjdypunVLfMuoa2T+Ad8JJqLLEqc1hntwZ46Q/bOezC6u48a0eVnalyOsWUY8N1ztEOO75pcRE58Vgn8iMwy7kw+d/mGWr32Sgb4B3QjdsfhtGQsMxwQMWpQXWSuLYNcFDYtUwwrDQRwp4mvykNsawNKskiv328TmDskPBNyOMo9I1nqrL7c/gafRjaSaq306xN1cKi07woI8UKHRncTV4sfIm2V1JsruSCN3CXu5CcSooLoX0jgSKTaYqUk6oPMSjtz2JntSYO3cWLzz1EkcdcRSM3gv934HK75bG7b4zSZ83eK09wZ+2DbOiK8XcKi/VN6xlSpmL7x5bP949Z2DlNygPvs6e9bl4oSh/esnXYqvfd077g0ROfvdKYc9lx7knyrKY6vX02PP58vFkhFOV8dgVTmsJ83hrjJtX9vLg1tJsn68s/SvUhRIsITLtldB+Bv6KI7n8iv9hJDVCe0cb+WweySZjL3OWAGNFC6ySVeyscaP6bWNGkKDYV4pc2StcFLqyY4ktC6tgYo84Ud0KjhpPaYiGRyW3L4W7wYuZNSh0Z7CFHRR7cyRWD+OdFsBR7iK5PoZskzESGpkdCfS4hmxTcFZ7MOJFbCE76W1xin05jJQGJjxzzwu43C4uvfwSHn/oSUK2baURuxXfLEWo7BPetZ7TbtvAr9f2s7wzxcwKD+dPLyOnm5w+OTyOZE3seRhn4W5G+7K5xIj5x4VfHf7FB+GZzAckyT1yZX+7th8zLaz+n5Pufn287PQnJzQgSzCt/EApR2eyMF7+chDZG0AOgWseyF7UxB3cfuOPePO1ZSw+chGqrJDdm0IbLmAVxlynMYSgNqphFSyCiw/Ebc2c8VcGmgkS2Ks9ZHclMbM6+mgR/9wIZs5Acau4mwOYKR1Lt7CF7GAKjLSONpAnsytJri2FpJQkgDAtXBM9uCZ6KfYX0IZLrp2ZN2nb2s7MOTN49eXX+M0vfoSS/GOpK46tttR6wTnl3Vgv3aIrecA9nFbuRpbgJyc0MLOiZJdk+1Zi9t+EMFPWQLvWlo6PfOmD8usDM3j+Z9ANTZyyZ32+1+UaJL/7WvLD2w46Zl61d1wsCwG7hvOs7Ulz6WO7xyeElGAaEaj9ValacegXkNvE9EYbq958i1tuu5mps6eAAD2hjfughZ4sV</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44754,7 +44996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -47405,8 +47647,46 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Logos + websites + social links: finish the remaining ~90 entities</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Bulk Source</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026: add logos INSIDE the ecosystem-network node circles, plus official websites and social URLs, for Organization (85), Business (34), Sponsor (9), Regional Ecosystem (4). DONE 17 Jul: the graph now renders logos clipped inside node circles (base64 data URIs -&gt; self-contained, no external calls, private); 25 entities that already had a domain got a logo+website (Google favicon sz=128, the working source -- Clearbit is dead). REMAINING: ~60 organizations + ~13 businesses have NO domain on file yet, so no logo; social-media URLs not yet added for most; the 4 Regional Ecosystems are GEOGRAPHIC (states), not companies -- they have no logo/website (use a state seal or skip).</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>NEXT: (1) find official websites for the ~73 orgs/businesses without one (web search per name), then run the same favicon-&gt;base64 pipeline (tools: fetch_logos pattern). (2) Add socialLinks (X/LinkedIn/etc) per entity. (3) For Regional Ecosystems, decide with Andy: state seal/flag image, or leave logo-less. (4) Higher-res option if favicons look weak: many orgs expose a proper og:image or /logo.svg -- can upgrade specific important nodes. Google favicon works; DuckDuckGo (icons.duckduckgo.com/ip3/DOMAIN.ico) is the fallback.</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H69"/>
+  <autoFilter ref="A1:H70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="criteria" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$N$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -739,7 +739,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>295 records</t>
+          <t>300 records</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>34 records</t>
+          <t>33 records</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>130 records</t>
+          <t>132 records</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>69 records</t>
+          <t>72 records</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>94 records</t>
+          <t>96 records</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4600,8 +4600,64 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>BUSINESS LEADER vs INFLUENCER vs BUSINESS -- three different things</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Network Definition</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Every person and company in the database</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Category discipline</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026: 'We need to distinguish business leaders from influencers.' Correct -- they were being conflated, and a person had even been filed in the companies tab. THE THREE-WAY DISTINCTION NOW ENFORCED: (1) BUSINESSES (B2B) = COMPANIES. Organisations with a logo and a website. Anduril, Oracle, Capital Factory. Never people. (2) BUSINESS LEADERS = PEOPLE whose value is COMMERCIAL -- they run/own/fund businesses, and their worth to BFT is their B2B network, capital, hiring power and industry access. Tracked in the people table with network="Business Leader" (31 entries normalised from the old 'Business' value, + Scooter Braun moved out of the companies tab where he never belonged). (3) INFLUENCERS = PEOPLE whose value is AUDIENCE -- reach, voice, content. network="Media/Influencer". WHY IT MATTERS BEYOND TIDINESS: the two gates score them DIFFERENTLY. A business leader is not judged on whether they can hold a podcast audience (Gate 2 talent = commercial standing and network, not charisma), and their loyalty cost is usually COMMERCIAL (Scooter Braun risking a fanbase boycott) rather than social. Scoring a CEO on 'would you watch them if you disagreed' is a category error. Entertainment and Political are the other two network values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>SUCCESSION WATCH: age out the elderly allies before they age out</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>All public officials; senior leaders generally</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Forward-looking coalition risk</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Generalised from Andy's Steny Hoyer note, 18 Jul 2026: Hoyer 'seems like a democrat ally of Israel but he is very old and will likely be replaced in office so it will be important to see how his replacement leans.' That is a genuinely good strategic instinct and should be a standing rule, not a one-off. THE RULE: for every elderly or retiring pro-Israel ally -- especially DEMOCRATS, where the pro-Israel bench is thinnest and most fragile -- track the SUCCESSION, not just the incumbent. A retirement is the single most predictable moment a reliable seat flips, and it is visible years in advance, which makes it one of the few things in this space that can actually be planned for rather than reacted to. OPERATIONALLY: flag incumbents by age/retirement signals; identify likely successors and primary fields early; score the successors' Israel posture BEFORE the seat turns over. This is the cheapest possible intervention point -- influencing who fills a seat is far easier than flipping someone already in it. Same logic applies to ageing megachurch pastors and org founders, where the successor inherits the whole audience.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F95"/>
+  <autoFilter ref="A1:F97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4612,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB296"/>
+  <dimension ref="A1:AB301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14309,7 +14365,7 @@
       <c r="O138" s="6" t="inlineStr"/>
       <c r="P138" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q138" s="6" t="inlineStr">
@@ -14679,7 +14735,7 @@
       <c r="O143" s="6" t="inlineStr"/>
       <c r="P143" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q143" s="6" t="inlineStr">
@@ -14753,7 +14809,7 @@
       <c r="O144" s="6" t="inlineStr"/>
       <c r="P144" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q144" s="6" t="inlineStr">
@@ -15151,7 +15207,7 @@
       <c r="O149" s="6" t="inlineStr"/>
       <c r="P149" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q149" s="6" t="inlineStr">
@@ -15229,7 +15285,7 @@
       <c r="O150" s="6" t="inlineStr"/>
       <c r="P150" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q150" s="6" t="inlineStr">
@@ -15541,7 +15597,7 @@
       <c r="O154" s="6" t="inlineStr"/>
       <c r="P154" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q154" s="6" t="inlineStr">
@@ -16345,7 +16401,7 @@
       <c r="O164" s="6" t="inlineStr"/>
       <c r="P164" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q164" s="6" t="inlineStr">
@@ -16419,7 +16475,7 @@
       <c r="O165" s="6" t="inlineStr"/>
       <c r="P165" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q165" s="6" t="inlineStr">
@@ -16501,7 +16557,7 @@
       <c r="O166" s="6" t="inlineStr"/>
       <c r="P166" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q166" s="6" t="inlineStr">
@@ -17753,7 +17809,7 @@
       <c r="O182" s="6" t="inlineStr"/>
       <c r="P182" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q182" s="6" t="inlineStr">
@@ -17827,7 +17883,7 @@
       <c r="O183" s="6" t="inlineStr"/>
       <c r="P183" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q183" s="6" t="inlineStr">
@@ -18511,7 +18567,7 @@
       <c r="O191" s="6" t="inlineStr"/>
       <c r="P191" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q191" s="6" t="inlineStr">
@@ -18589,7 +18645,7 @@
       <c r="O192" s="6" t="inlineStr"/>
       <c r="P192" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q192" s="6" t="inlineStr">
@@ -18757,7 +18813,7 @@
       <c r="O194" s="6" t="inlineStr"/>
       <c r="P194" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q194" s="6" t="inlineStr">
@@ -19007,7 +19063,7 @@
       <c r="O197" s="6" t="inlineStr"/>
       <c r="P197" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q197" s="6" t="inlineStr">
@@ -19089,7 +19145,7 @@
       <c r="O198" s="6" t="inlineStr"/>
       <c r="P198" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q198" s="6" t="inlineStr">
@@ -19167,7 +19223,7 @@
       <c r="O199" s="6" t="inlineStr"/>
       <c r="P199" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q199" s="6" t="inlineStr">
@@ -19257,7 +19313,7 @@
       <c r="O200" s="6" t="inlineStr"/>
       <c r="P200" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q200" s="6" t="inlineStr">
@@ -19347,7 +19403,7 @@
       <c r="O201" s="6" t="inlineStr"/>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q201" s="6" t="inlineStr">
@@ -20289,7 +20345,7 @@
       <c r="O212" s="6" t="inlineStr"/>
       <c r="P212" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q212" s="6" t="inlineStr">
@@ -22217,7 +22273,7 @@
       <c r="W234" s="6" t="inlineStr"/>
       <c r="X234" s="6" t="inlineStr">
         <is>
-          <t>Verify explicit Israel/antisemitism content.</t>
+          <t>ANDY 18 Jul 2026: they are MORE PRO-RUBIO THAN VANCE -- a meaningful placement under the Rubio/Vance preference criterion, and a useful marker of the establishment-vs-restraint split inside the conservative coalition. ALSO ASKED: add 'their allies' -- their frequent guests, co-hosts and amplifiers are an unmined bounded roster; sweep youtube.com/@chicksonright for recurring collaborators. Verify explicit Israel/antisemitism content.</t>
         </is>
       </c>
       <c r="Y234" s="6" t="inlineStr"/>
@@ -22439,7 +22495,7 @@
       <c r="O237" s="6" t="inlineStr"/>
       <c r="P237" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q237" s="6" t="inlineStr">
@@ -23671,7 +23727,7 @@
       </c>
       <c r="P251" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q251" s="6" t="inlineStr">
@@ -23757,7 +23813,7 @@
       </c>
       <c r="P252" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q252" s="6" t="inlineStr">
@@ -23847,7 +23903,7 @@
       </c>
       <c r="P253" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q253" s="6" t="inlineStr">
@@ -23937,7 +23993,7 @@
       </c>
       <c r="P254" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q254" s="6" t="inlineStr">
@@ -24027,7 +24083,7 @@
       </c>
       <c r="P255" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q255" s="6" t="inlineStr">
@@ -24117,7 +24173,7 @@
       </c>
       <c r="P256" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q256" s="6" t="inlineStr">
@@ -24211,7 +24267,7 @@
       </c>
       <c r="P257" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q257" s="6" t="inlineStr">
@@ -24477,7 +24533,7 @@
       </c>
       <c r="P260" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q260" s="6" t="inlineStr">
@@ -24575,7 +24631,7 @@
       </c>
       <c r="P261" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q261" s="6" t="inlineStr">
@@ -24669,7 +24725,7 @@
       </c>
       <c r="P262" s="6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Business Leader</t>
         </is>
       </c>
       <c r="Q262" s="6" t="inlineStr">
@@ -27985,8 +28041,518 @@
       <c r="AA296" s="6" t="inlineStr"/>
       <c r="AB296" s="6" t="inlineStr"/>
     </row>
+    <row r="297">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>inf-21366cf6</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>Scooter Braun</t>
+        </is>
+      </c>
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>Music/entertainment industry (HYBE America CEO; founder, Ithaca Holdings)</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
+        <is>
+          <t>Industry power, not a personal follower base</t>
+        </is>
+      </c>
+      <c r="E297" s="6" t="inlineStr">
+        <is>
+          <t>Jewish</t>
+        </is>
+      </c>
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>Entertainment executive</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="H297" s="6" t="inlineStr">
+        <is>
+          <t>MOVED 18 Jul 2026 from the Businesses (B2B) tab to the BUSINESS LEADER network, per Andy: business leaders are PEOPLE and must be distinguished from both companies and media influencers. He is a person, so he belongs with people.</t>
+        </is>
+      </c>
+      <c r="I297" s="6" t="inlineStr"/>
+      <c r="J297" s="6" t="inlineStr">
+        <is>
+          <t>Hollywood Reporter; Jerusalem Post</t>
+        </is>
+      </c>
+      <c r="K297" s="6" t="inlineStr"/>
+      <c r="L297" s="6" t="inlineStr"/>
+      <c r="M297" s="6" t="inlineStr"/>
+      <c r="N297" s="6" t="inlineStr"/>
+      <c r="O297" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P297" s="6" t="inlineStr">
+        <is>
+          <t>Business Leader</t>
+        </is>
+      </c>
+      <c r="Q297" s="6" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R297" s="6" t="inlineStr">
+        <is>
+          <t>STRONG. After his Dec 2023 Tel Aviv speech calling for the return of the Oct 7 hostages -- invoking his Auschwitz-survivor grandmother, saying he 'had to come and stand with my people' -- BTS's global fanbase mounted a sustained campaign demanding HYBE fire him, including billboard trucks sent to HYBE's Seoul HQ. He held the position under enormous commercial pressure. Career-risking, unpaid, and public.</t>
+        </is>
+      </c>
+      <c r="S297" s="6" t="inlineStr">
+        <is>
+          <t>Dec 2023 onward (post-Oct-7)</t>
+        </is>
+      </c>
+      <c r="T297" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodreporter.com/music/music-news/bts-fans-army-hybe-fire-scooter-braun-pro-israel-views-1235840387/</t>
+        </is>
+      </c>
+      <c r="U297" s="6" t="inlineStr">
+        <is>
+          <t>Built and sold Ithaca Holdings to HYBE (~$1.05B); CEO of HYBE America and a HYBE board member. Elite operator and connector in an industry where pro-Israel voices are scarce and costly.</t>
+        </is>
+      </c>
+      <c r="V297" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hollywoodreporter.com/music/music-news/bts-fans-army-hybe-fire-scooter-braun-pro-israel-views-1235840387/</t>
+        </is>
+      </c>
+      <c r="W297" s="6" t="inlineStr">
+        <is>
+          <t>HYBE America, Ithaca Holdings</t>
+        </is>
+      </c>
+      <c r="X297" s="6" t="inlineStr">
+        <is>
+          <t>Map his artist/label relationships and philanthropy as B2B edges. High-value connector into music/entertainment.</t>
+        </is>
+      </c>
+      <c r="Y297" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="Z297" s="6" t="inlineStr"/>
+      <c r="AA297" s="6" t="inlineStr"/>
+      <c r="AB297" s="6" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>inf-9e5bdf64</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>Yishai Fleisher</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>Podcast (The Yishai Fleisher Show), Arutz Sheva / Israel National News, speaking tours</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
+        <is>
+          <t>TBD -- verify</t>
+        </is>
+      </c>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>Jewish (Orthodox; rabbinic ordination)</t>
+        </is>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>Religious Zionist</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted as friendly with Christians (evidence: youtube.com/watch?v=V8b6bleSw24). International spokesperson for the Jewish Community of Hebron since 2015; born 1976 in Haifa to Soviet refuseniks, raised in the US from age eight; IDF paratrooper; Yeshiva University; Cardozo School of Law JD; rabbinic ordination. NOTABLE NETWORK EDGE: in his Hebron role he has personally toured VIPs including MIKE PENCE -- a direct link to the Pence/AAF cluster Andy is building out in this same batch.</t>
+        </is>
+      </c>
+      <c r="I298" s="6" t="inlineStr">
+        <is>
+          <t>yishaifleisher.com; facebook.com/YishaiFleisher; il.linkedin.com/in/yishaifleisher</t>
+        </is>
+      </c>
+      <c r="J298" s="6" t="inlineStr">
+        <is>
+          <t>yishaifleisher.com (own site); Israel National News; World Mizrachi</t>
+        </is>
+      </c>
+      <c r="K298" s="6" t="inlineStr"/>
+      <c r="L298" s="6" t="inlineStr"/>
+      <c r="M298" s="6" t="inlineStr"/>
+      <c r="N298" s="6" t="inlineStr"/>
+      <c r="O298" s="6" t="inlineStr">
+        <is>
+          <t>Israeli-American</t>
+        </is>
+      </c>
+      <c r="P298" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q298" s="6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R298" s="6" t="inlineStr">
+        <is>
+          <t>Not yet established as a personal COST -- advocacy is his professional role (international spokesperson for the Jewish Community of Hebron), which under the voluntary-vs-paid rule is weaker evidence than an unpaid stand. His post is genuinely high-risk in security terms, which is a different kind of cost worth weighing.</t>
+        </is>
+      </c>
+      <c r="S298" s="6" t="inlineStr"/>
+      <c r="T298" s="6" t="inlineStr"/>
+      <c r="U298" s="6" t="inlineStr">
+        <is>
+          <t>Career broadcaster: recruited to Arutz Sheva 2003, became Director of Programming for the English department and grew it through the early podcast era; hosts The Yishai Fleisher Show. Fluent English-language communicator built for long-form -- exactly the format profile leg 1 targets.</t>
+        </is>
+      </c>
+      <c r="V298" s="6" t="inlineStr">
+        <is>
+          <t>https://yishaifleisher.com/</t>
+        </is>
+      </c>
+      <c r="W298" s="6" t="inlineStr">
+        <is>
+          <t>Jewish Community of Hebron, Mike Pence, World Mizrachi, Arutz Sheva</t>
+        </is>
+      </c>
+      <c r="X298" s="6" t="inlineStr">
+        <is>
+          <t>NATIONALITY CAVEAT per Andy's own criterion: Israelis rank lower as front-line influencers to US audiences (perceived bias) -- but the charisma/actual-influence override applies, and his value here is precisely the CHRISTIAN-facing bridge. Verify the specific Christian-outreach content in the submitted video and capture his audience numbers.</t>
+        </is>
+      </c>
+      <c r="Y298" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="Z298" s="6" t="inlineStr"/>
+      <c r="AA298" s="6" t="inlineStr"/>
+      <c r="AB298" s="6" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>inf-5f8d144d</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>Tim Chapman</t>
+        </is>
+      </c>
+      <c r="C299" s="6" t="inlineStr">
+        <is>
+          <t>X (@TimChapman); Advancing American Freedom</t>
+        </is>
+      </c>
+      <c r="D299" s="6" t="inlineStr">
+        <is>
+          <t>TBD -- verify</t>
+        </is>
+      </c>
+      <c r="E299" s="6" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
+        <is>
+          <t>Conservative movement leadership</t>
+        </is>
+      </c>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="H299" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted: President of Mike Pence's organization Advancing American Freedom, which Andy assesses as clearly sharing BFT's values and mission. AAF is already tracked as an organization here, and Eugene Kontorovich is already linked to it -- so this closes a real gap at the top of that org.</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="inlineStr">
+        <is>
+          <t>x.com/TimChapman</t>
+        </is>
+      </c>
+      <c r="J299" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted</t>
+        </is>
+      </c>
+      <c r="K299" s="6" t="inlineStr"/>
+      <c r="L299" s="6" t="inlineStr"/>
+      <c r="M299" s="6" t="inlineStr"/>
+      <c r="N299" s="6" t="inlineStr"/>
+      <c r="O299" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P299" s="6" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="Q299" s="6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="R299" s="6" t="inlineStr"/>
+      <c r="S299" s="6" t="inlineStr"/>
+      <c r="T299" s="6" t="inlineStr"/>
+      <c r="U299" s="6" t="inlineStr">
+        <is>
+          <t>Movement operator rather than a content creator -- runs an organisation; value is institutional reach, not personal audience.</t>
+        </is>
+      </c>
+      <c r="V299" s="6" t="inlineStr">
+        <is>
+          <t>https://x.com/TimChapman</t>
+        </is>
+      </c>
+      <c r="W299" s="6" t="inlineStr">
+        <is>
+          <t>Advancing American Freedom (AAF), Mike Pence, Eugene Kontorovich</t>
+        </is>
+      </c>
+      <c r="X299" s="6" t="inlineStr">
+        <is>
+          <t>Verify his own Israel record (the org's alignment is not automatically his). High-value connector: AAF is a bounded, on-mission roster worth sweeping in full.</t>
+        </is>
+      </c>
+      <c r="Y299" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="Z299" s="6" t="inlineStr"/>
+      <c r="AA299" s="6" t="inlineStr"/>
+      <c r="AB299" s="6" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>inf-fabdcd8c</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>Stuart Knechtle</t>
+        </is>
+      </c>
+      <c r="C300" s="6" t="inlineStr">
+        <is>
+          <t>YouTube / campus open-air apologetics</t>
+        </is>
+      </c>
+      <c r="D300" s="6" t="inlineStr">
+        <is>
+          <t>TBD -- verify</t>
+        </is>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>Christian (evangelical apologist)</t>
+        </is>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>Christian apologetics</t>
+        </is>
+      </c>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted, WITH HIS OWN CAVEAT: he and his father (Cliffe Knechtle) have expressed 'Judeo-Christian' values -- a strong positive under the existing Judeo-Christian criterion -- BUT they are VERY PROSELYTIZING, which Andy notes 'can cause trouble in relations.'</t>
+        </is>
+      </c>
+      <c r="I300" s="6" t="inlineStr"/>
+      <c r="J300" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted</t>
+        </is>
+      </c>
+      <c r="K300" s="6" t="inlineStr"/>
+      <c r="L300" s="6" t="inlineStr"/>
+      <c r="M300" s="6" t="inlineStr"/>
+      <c r="N300" s="6" t="inlineStr"/>
+      <c r="O300" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P300" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q300" s="6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R300" s="6" t="inlineStr"/>
+      <c r="S300" s="6" t="inlineStr"/>
+      <c r="T300" s="6" t="inlineStr"/>
+      <c r="U300" s="6" t="inlineStr">
+        <is>
+          <t>Open-air campus apologetics -- proven ability to hold a hostile live crowd and take unscripted questions, which is genuine conversational range (the Gate-2 signal). Works the same campus terrain where antisemitism is currently worst.</t>
+        </is>
+      </c>
+      <c r="V300" s="6" t="inlineStr"/>
+      <c r="W300" s="6" t="inlineStr">
+        <is>
+          <t>Cliffe Knechtle</t>
+        </is>
+      </c>
+      <c r="X300" s="6" t="inlineStr">
+        <is>
+          <t>ANDY'S CAVEAT IS THE POINT AND SHOULD GOVERN. Aggressive proselytizing toward Jews is a real relationship risk for BFT: it is the single fastest way to blow up Jewish-Christian trust, and Dana's guidance (keep Jews out of the front-facing role; let the Christian effort be organic) makes a proselytizing partner especially hazardous. Recommend NOT elevating to the roster until his posture toward JEWISH audiences specifically is checked -- supportive-of-Israel is not the same as safe-to-partner-with. Stance held at neutral pending that.</t>
+        </is>
+      </c>
+      <c r="Y300" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="Z300" s="6" t="inlineStr"/>
+      <c r="AA300" s="6" t="inlineStr"/>
+      <c r="AB300" s="6" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>inf-9e9ad92d</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Day</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>The American Conservative; X (@AKDay89)</t>
+        </is>
+      </c>
+      <c r="D301" s="6" t="inlineStr">
+        <is>
+          <t>TBD -- verify</t>
+        </is>
+      </c>
+      <c r="E301" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>Restraint/paleoconservative</t>
+        </is>
+      </c>
+      <c r="G301" s="6" t="inlineStr">
+        <is>
+          <t>hostile</t>
+        </is>
+      </c>
+      <c r="H301" s="6" t="inlineStr">
+        <is>
+          <t>Andy-flagged HOSTILE: writer at The American Conservative; flagged for a friendly interview with Tucker Carlson (evidence video submitted by Andy). The American Conservative is the institutional home of the restraint/anti-interventionist wing that the Parscale/TIME reporting identifies as the drift BFT exists to counter.</t>
+        </is>
+      </c>
+      <c r="I301" s="6" t="inlineStr">
+        <is>
+          <t>x.com/AKDay89</t>
+        </is>
+      </c>
+      <c r="J301" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted; The American Conservative</t>
+        </is>
+      </c>
+      <c r="K301" s="6" t="inlineStr"/>
+      <c r="L301" s="6" t="inlineStr"/>
+      <c r="M301" s="6" t="inlineStr"/>
+      <c r="N301" s="6" t="inlineStr"/>
+      <c r="O301" s="6" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="P301" s="6" t="inlineStr">
+        <is>
+          <t>Media/Influencer</t>
+        </is>
+      </c>
+      <c r="Q301" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R301" s="6" t="inlineStr"/>
+      <c r="S301" s="6" t="inlineStr"/>
+      <c r="T301" s="6" t="inlineStr"/>
+      <c r="U301" s="6" t="inlineStr"/>
+      <c r="V301" s="6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SnsP3Upcv1c</t>
+        </is>
+      </c>
+      <c r="W301" s="6" t="inlineStr">
+        <is>
+          <t>The American Conservative, Tucker Carlson, Harrison Berger</t>
+        </is>
+      </c>
+      <c r="X301" s="6" t="inlineStr">
+        <is>
+          <t>VERIFY the specific interview content before hardening this. A friendly interview with Carlson is a real alignment signal given Carlson's tracked hostility, but 'appeared with' is weaker than 'said'. Capture his own on-record Israel statements. Also assess Harrison Berger (@BergerPosts), named by Andy in the same breath -- unclear from the message whether Berger is the interviewer/host or a separate flag; do NOT tag Berger until that is resolved.</t>
+        </is>
+      </c>
+      <c r="Y301" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="Z301" s="6" t="inlineStr"/>
+      <c r="AA301" s="6" t="inlineStr"/>
+      <c r="AB301" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB296"/>
+  <autoFilter ref="A1:AB301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32428,13 +32994,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
@@ -34473,70 +35039,8 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>biz-4ef6152a</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Scooter Braun</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Business leader (entertainment/music)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Music &amp; Entertainment (HYBE America CEO; founder, Ithaca Holdings)</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Jewish music executive; founder of Ithaca Holdings (sold to South Korea's HYBE in 2021, ~$1.05B), became CEO of HYBE America and a HYBE board member. STRONG GATE-1 COST SIGNAL: after his Dec 2023 Tel Aviv speech calling for the return of the Oct 7 hostages -- in which he invoked his Auschwitz-survivor grandmother and said he 'had to come and stand with my people' -- BTS's global fanbase mounted a sustained campaign demanding HYBE fire him, including billboard trucks sent to HYBE's Seoul HQ. He held the position under enormous commercial pressure. This is exactly the costly, career-risking loyalty the Gate-1 criterion is built to surface.</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Scooter Braun (CEO, HYBE America)</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>https://www.hollywoodreporter.com/music/music-news/bts-fans-army-hybe-fire-scooter-braun-pro-israel-views-1235840387/</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Hollywood Reporter; Jerusalem Post; Israel National News</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>Map his network as a B2B node: Ithaca/HYBE, his artist and label relationships, and his philanthropy. High-value connector into the music industry, where pro-Israel voices are scarce and costly.</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>Andy</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr"/>
-      <c r="O35" s="6" t="inlineStr"/>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>HYBE America, Ithaca Holdings</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34834,7 +35338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34851,7 +35355,7 @@
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -42329,8 +42833,146 @@
       </c>
       <c r="O131" s="6" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>pol-8d6f0a01</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Mike Pence</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Former Vice President of the United States (2017-2021); Founder, Advancing American Freedom</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Republican</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted as an ally. One of the most consistently pro-Israel figures in modern Republican politics and a leading evangelical voice -- the intersection BFT is built on. Founded Advancing American Freedom (already tracked here). NETWORK EDGE confirmed this batch: Yishai Fleisher personally toured Pence through Hebron in his role as the Jewish Community of Hebron's spokesperson.</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>https://x.com/Mike_Pence</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>Pre-VP House record (IN, 2001-2013) predates the 2015-2026 sweep window -- NOT yet measured. Flag for the pre-2015 sweep.</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr"/>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>x.com/Mike_Pence</t>
+        </is>
+      </c>
+      <c r="M132" s="6" t="inlineStr">
+        <is>
+          <t>Run his pre-2015 House voting record when the pre-2015 sweep happens -- he is exactly the case the current 2015-2026 window misses. Also note the strategic tension worth watching: Pence represents the traditional pro-Israel evangelical Republicanism that the Vance/restraint wing is displacing, so he is a barometer of that fight.</t>
+        </is>
+      </c>
+      <c r="N132" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="O132" s="6" t="inlineStr">
+        <is>
+          <t>Advancing American Freedom (AAF), Tim Chapman, Yishai Fleisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>pol-331c1898</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Steny Hoyer</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>US Representative, MD-5; former House Majority Leader</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Democrat</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted: a Democratic ally of Israel, and a valuable one precisely because he is a DEMOCRAT -- the pro-Israel Democratic bench is the thinnest and most strategically fragile part of the coalition.</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/member/steny-hoyer/H000874</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>Andy-submitted</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>Long-serving Democrat with a consistently pro-Israel record; NOT yet measured against the House roll-call sweep -- flag to score him on the 30 clean votes.</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr"/>
+      <c r="L133" s="6" t="inlineStr"/>
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>ANDY'S KEY POINT, and it is a genuinely good strategic instinct worth generalising: he is very old and will likely be replaced, so WHO REPLACES HIM MATTERS MORE THAN HE DOES. Track the MD-5 succession and the successor's Israel posture. GENERALISE THIS INTO A RULE: build a SUCCESSION WATCH for every elderly pro-Israel incumbent -- their retirement is the moment a reliable seat can flip, and it is foreseeable years ahead. Score him on the roll-call sweep.</t>
+        </is>
+      </c>
+      <c r="N133" s="6" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O131"/>
+  <autoFilter ref="A1:O133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44996,7 +45638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -47685,8 +48327,118 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Add faces / official profile photos for influencers + business leaders</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Open Design</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026: 'also add faces/official profiles for influencers/business leaders' -- the people equivalent of the company logos now rendering in the network nodes.</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>APPROACH: same base64-embed pipeline as the logos (self-contained, no external calls at render, no leak of who is being viewed). SOURCES that work without login: YouTube channel avatars (already fetchable -- the reliable one, and ~20 influencers have YouTube handles), Rumble channel avatars, and each person's own site. X/Instagram avatars are login-gated here (tested). TWO REAL CAVEATS TO SETTLE WITH ANDY BEFORE BULK-FETCHING: (1) RIGHTS -- company logos are trademarks used nominatively, which is routine; personal photographs are copyrighted works, usually owned by a photographer, not the subject. Prefer official channel avatars (posted by the person) over press/news photos. (2) OPTICS -- a private dossier of named individuals' FACES with stance ratings attached reads very differently from a list of logos if it ever leaked; for an org that 'operates under the radar' that is worth a deliberate decision, not a default. Recommend: official avatars only, allies only, and skip faces for hostiles.</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>UNIDENTIFIED: 'Moderate Case' -- who is this?</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Unverified Identity</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Needs Andy</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026: 'Did we already add Moderate Case?' ANSWER: no -- there is no entry by that name. But I could not identify who or what 'Moderate Case' refers to; a web search returned nothing matching as an account or commentator. Not guessing rather than inventing an entry.</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>ANDY: need the handle or a link. Best guess is an X account (a @ModerateCase-style handle) but that is unverified and I will not add it on a guess.</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Sweep Chicks on the Right's allies/collaborators</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Bulk Source</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026: add Chicks on the Right 'and their allies'. The entry itself already exists and is now annotated with Andy's pro-Rubio-over-Vance read.</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Bounded roster, so tractable: sweep youtube.com/@chicksonright for recurring guests, co-hosts and named collaborators; cross-check against existing entries; score each on the two gates. Their Rubio lean makes their network a good sample of the establishment-conservative side of the split.</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H70"/>
+  <autoFilter ref="A1:H73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="criteria" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AB$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'influencer'!$A$1:$AC$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'organization'!$A$1:$N$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'business'!$A$1:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ecosystem'!$A$1:$J$5</definedName>
@@ -4668,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB301"/>
+  <dimension ref="A1:AC301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4698,7 +4698,8 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="27" customWidth="1" min="27" max="27"/>
-    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="55" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4838,6 +4839,11 @@
         </is>
       </c>
       <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>audienceGeography</t>
         </is>
@@ -4912,6 +4918,7 @@
       <c r="Z2" s="6" t="inlineStr"/>
       <c r="AA2" s="6" t="inlineStr"/>
       <c r="AB2" s="6" t="inlineStr"/>
+      <c r="AC2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4994,6 +5001,7 @@
       <c r="Z3" s="6" t="inlineStr"/>
       <c r="AA3" s="6" t="inlineStr"/>
       <c r="AB3" s="6" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5064,6 +5072,7 @@
       <c r="Z4" s="6" t="inlineStr"/>
       <c r="AA4" s="6" t="inlineStr"/>
       <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5134,6 +5143,7 @@
       <c r="Z5" s="6" t="inlineStr"/>
       <c r="AA5" s="6" t="inlineStr"/>
       <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5216,6 +5226,7 @@
       <c r="Z6" s="6" t="inlineStr"/>
       <c r="AA6" s="6" t="inlineStr"/>
       <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5298,6 +5309,7 @@
       <c r="Z7" s="6" t="inlineStr"/>
       <c r="AA7" s="6" t="inlineStr"/>
       <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5380,6 +5392,7 @@
       <c r="Z8" s="6" t="inlineStr"/>
       <c r="AA8" s="6" t="inlineStr"/>
       <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5450,6 +5463,7 @@
       <c r="Z9" s="6" t="inlineStr"/>
       <c r="AA9" s="6" t="inlineStr"/>
       <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5532,6 +5546,7 @@
       <c r="Z10" s="6" t="inlineStr"/>
       <c r="AA10" s="6" t="inlineStr"/>
       <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5614,6 +5629,7 @@
       <c r="Z11" s="6" t="inlineStr"/>
       <c r="AA11" s="6" t="inlineStr"/>
       <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5684,6 +5700,7 @@
       <c r="Z12" s="6" t="inlineStr"/>
       <c r="AA12" s="6" t="inlineStr"/>
       <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5754,6 +5771,7 @@
       <c r="Z13" s="6" t="inlineStr"/>
       <c r="AA13" s="6" t="inlineStr"/>
       <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5824,6 +5842,7 @@
       <c r="Z14" s="6" t="inlineStr"/>
       <c r="AA14" s="6" t="inlineStr"/>
       <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5894,6 +5913,7 @@
       <c r="Z15" s="6" t="inlineStr"/>
       <c r="AA15" s="6" t="inlineStr"/>
       <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -5976,6 +5996,7 @@
       <c r="Z16" s="6" t="inlineStr"/>
       <c r="AA16" s="6" t="inlineStr"/>
       <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -6042,6 +6063,7 @@
       <c r="Z17" s="6" t="inlineStr"/>
       <c r="AA17" s="6" t="inlineStr"/>
       <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6108,6 +6130,7 @@
       <c r="Z18" s="6" t="inlineStr"/>
       <c r="AA18" s="6" t="inlineStr"/>
       <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -6186,6 +6209,7 @@
       <c r="Z19" s="6" t="inlineStr"/>
       <c r="AA19" s="6" t="inlineStr"/>
       <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6252,6 +6276,7 @@
       <c r="Z20" s="6" t="inlineStr"/>
       <c r="AA20" s="6" t="inlineStr"/>
       <c r="AB20" s="6" t="inlineStr"/>
+      <c r="AC20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -6318,6 +6343,7 @@
       <c r="Z21" s="6" t="inlineStr"/>
       <c r="AA21" s="6" t="inlineStr"/>
       <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6384,6 +6410,7 @@
       <c r="Z22" s="6" t="inlineStr"/>
       <c r="AA22" s="6" t="inlineStr"/>
       <c r="AB22" s="6" t="inlineStr"/>
+      <c r="AC22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6450,6 +6477,7 @@
       <c r="Z23" s="6" t="inlineStr"/>
       <c r="AA23" s="6" t="inlineStr"/>
       <c r="AB23" s="6" t="inlineStr"/>
+      <c r="AC23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6528,6 +6556,7 @@
       <c r="Z24" s="6" t="inlineStr"/>
       <c r="AA24" s="6" t="inlineStr"/>
       <c r="AB24" s="6" t="inlineStr"/>
+      <c r="AC24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6606,6 +6635,7 @@
       <c r="Z25" s="6" t="inlineStr"/>
       <c r="AA25" s="6" t="inlineStr"/>
       <c r="AB25" s="6" t="inlineStr"/>
+      <c r="AC25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6688,6 +6718,7 @@
       <c r="Z26" s="6" t="inlineStr"/>
       <c r="AA26" s="6" t="inlineStr"/>
       <c r="AB26" s="6" t="inlineStr"/>
+      <c r="AC26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6770,6 +6801,7 @@
       <c r="Z27" s="6" t="inlineStr"/>
       <c r="AA27" s="6" t="inlineStr"/>
       <c r="AB27" s="6" t="inlineStr"/>
+      <c r="AC27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6848,6 +6880,7 @@
       <c r="Z28" s="6" t="inlineStr"/>
       <c r="AA28" s="6" t="inlineStr"/>
       <c r="AB28" s="6" t="inlineStr"/>
+      <c r="AC28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6926,6 +6959,7 @@
       <c r="Z29" s="6" t="inlineStr"/>
       <c r="AA29" s="6" t="inlineStr"/>
       <c r="AB29" s="6" t="inlineStr"/>
+      <c r="AC29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7004,6 +7038,7 @@
       <c r="Z30" s="6" t="inlineStr"/>
       <c r="AA30" s="6" t="inlineStr"/>
       <c r="AB30" s="6" t="inlineStr"/>
+      <c r="AC30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -7082,6 +7117,7 @@
       <c r="Z31" s="6" t="inlineStr"/>
       <c r="AA31" s="6" t="inlineStr"/>
       <c r="AB31" s="6" t="inlineStr"/>
+      <c r="AC31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7164,6 +7200,7 @@
       <c r="Z32" s="6" t="inlineStr"/>
       <c r="AA32" s="6" t="inlineStr"/>
       <c r="AB32" s="6" t="inlineStr"/>
+      <c r="AC32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7230,6 +7267,7 @@
       <c r="Z33" s="6" t="inlineStr"/>
       <c r="AA33" s="6" t="inlineStr"/>
       <c r="AB33" s="6" t="inlineStr"/>
+      <c r="AC33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7296,6 +7334,7 @@
       <c r="Z34" s="6" t="inlineStr"/>
       <c r="AA34" s="6" t="inlineStr"/>
       <c r="AB34" s="6" t="inlineStr"/>
+      <c r="AC34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7378,6 +7417,7 @@
       <c r="Z35" s="6" t="inlineStr"/>
       <c r="AA35" s="6" t="inlineStr"/>
       <c r="AB35" s="6" t="inlineStr"/>
+      <c r="AC35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7460,6 +7500,7 @@
       <c r="Z36" s="6" t="inlineStr"/>
       <c r="AA36" s="6" t="inlineStr"/>
       <c r="AB36" s="6" t="inlineStr"/>
+      <c r="AC36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7526,6 +7567,7 @@
       <c r="Z37" s="6" t="inlineStr"/>
       <c r="AA37" s="6" t="inlineStr"/>
       <c r="AB37" s="6" t="inlineStr"/>
+      <c r="AC37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7596,6 +7638,7 @@
       <c r="Z38" s="6" t="inlineStr"/>
       <c r="AA38" s="6" t="inlineStr"/>
       <c r="AB38" s="6" t="inlineStr"/>
+      <c r="AC38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -7662,6 +7705,7 @@
       <c r="Z39" s="6" t="inlineStr"/>
       <c r="AA39" s="6" t="inlineStr"/>
       <c r="AB39" s="6" t="inlineStr"/>
+      <c r="AC39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7728,6 +7772,7 @@
       <c r="Z40" s="6" t="inlineStr"/>
       <c r="AA40" s="6" t="inlineStr"/>
       <c r="AB40" s="6" t="inlineStr"/>
+      <c r="AC40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -7794,6 +7839,7 @@
       <c r="Z41" s="6" t="inlineStr"/>
       <c r="AA41" s="6" t="inlineStr"/>
       <c r="AB41" s="6" t="inlineStr"/>
+      <c r="AC41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7860,6 +7906,7 @@
       <c r="Z42" s="6" t="inlineStr"/>
       <c r="AA42" s="6" t="inlineStr"/>
       <c r="AB42" s="6" t="inlineStr"/>
+      <c r="AC42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -7926,6 +7973,7 @@
       <c r="Z43" s="6" t="inlineStr"/>
       <c r="AA43" s="6" t="inlineStr"/>
       <c r="AB43" s="6" t="inlineStr"/>
+      <c r="AC43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -7992,6 +8040,7 @@
       <c r="Z44" s="6" t="inlineStr"/>
       <c r="AA44" s="6" t="inlineStr"/>
       <c r="AB44" s="6" t="inlineStr"/>
+      <c r="AC44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8058,6 +8107,7 @@
       <c r="Z45" s="6" t="inlineStr"/>
       <c r="AA45" s="6" t="inlineStr"/>
       <c r="AB45" s="6" t="inlineStr"/>
+      <c r="AC45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8124,6 +8174,7 @@
       <c r="Z46" s="6" t="inlineStr"/>
       <c r="AA46" s="6" t="inlineStr"/>
       <c r="AB46" s="6" t="inlineStr"/>
+      <c r="AC46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -8190,6 +8241,7 @@
       <c r="Z47" s="6" t="inlineStr"/>
       <c r="AA47" s="6" t="inlineStr"/>
       <c r="AB47" s="6" t="inlineStr"/>
+      <c r="AC47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -8256,6 +8308,7 @@
       <c r="Z48" s="6" t="inlineStr"/>
       <c r="AA48" s="6" t="inlineStr"/>
       <c r="AB48" s="6" t="inlineStr"/>
+      <c r="AC48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -8322,6 +8375,7 @@
       <c r="Z49" s="6" t="inlineStr"/>
       <c r="AA49" s="6" t="inlineStr"/>
       <c r="AB49" s="6" t="inlineStr"/>
+      <c r="AC49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -8388,6 +8442,7 @@
       <c r="Z50" s="6" t="inlineStr"/>
       <c r="AA50" s="6" t="inlineStr"/>
       <c r="AB50" s="6" t="inlineStr"/>
+      <c r="AC50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -8454,6 +8509,7 @@
       <c r="Z51" s="6" t="inlineStr"/>
       <c r="AA51" s="6" t="inlineStr"/>
       <c r="AB51" s="6" t="inlineStr"/>
+      <c r="AC51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -8520,6 +8576,7 @@
       <c r="Z52" s="6" t="inlineStr"/>
       <c r="AA52" s="6" t="inlineStr"/>
       <c r="AB52" s="6" t="inlineStr"/>
+      <c r="AC52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -8586,6 +8643,7 @@
       <c r="Z53" s="6" t="inlineStr"/>
       <c r="AA53" s="6" t="inlineStr"/>
       <c r="AB53" s="6" t="inlineStr"/>
+      <c r="AC53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -8652,6 +8710,7 @@
       <c r="Z54" s="6" t="inlineStr"/>
       <c r="AA54" s="6" t="inlineStr"/>
       <c r="AB54" s="6" t="inlineStr"/>
+      <c r="AC54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -8718,6 +8777,7 @@
       <c r="Z55" s="6" t="inlineStr"/>
       <c r="AA55" s="6" t="inlineStr"/>
       <c r="AB55" s="6" t="inlineStr"/>
+      <c r="AC55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -8796,6 +8856,7 @@
       <c r="Z56" s="6" t="inlineStr"/>
       <c r="AA56" s="6" t="inlineStr"/>
       <c r="AB56" s="6" t="inlineStr"/>
+      <c r="AC56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -8878,6 +8939,7 @@
       <c r="Z57" s="6" t="inlineStr"/>
       <c r="AA57" s="6" t="inlineStr"/>
       <c r="AB57" s="6" t="inlineStr"/>
+      <c r="AC57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -8944,6 +9006,7 @@
       <c r="Z58" s="6" t="inlineStr"/>
       <c r="AA58" s="6" t="inlineStr"/>
       <c r="AB58" s="6" t="inlineStr"/>
+      <c r="AC58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -9010,6 +9073,7 @@
       <c r="Z59" s="6" t="inlineStr"/>
       <c r="AA59" s="6" t="inlineStr"/>
       <c r="AB59" s="6" t="inlineStr"/>
+      <c r="AC59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -9076,6 +9140,7 @@
       <c r="Z60" s="6" t="inlineStr"/>
       <c r="AA60" s="6" t="inlineStr"/>
       <c r="AB60" s="6" t="inlineStr"/>
+      <c r="AC60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -9142,6 +9207,7 @@
       <c r="Z61" s="6" t="inlineStr"/>
       <c r="AA61" s="6" t="inlineStr"/>
       <c r="AB61" s="6" t="inlineStr"/>
+      <c r="AC61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -9208,6 +9274,7 @@
       <c r="Z62" s="6" t="inlineStr"/>
       <c r="AA62" s="6" t="inlineStr"/>
       <c r="AB62" s="6" t="inlineStr"/>
+      <c r="AC62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -9274,6 +9341,7 @@
       <c r="Z63" s="6" t="inlineStr"/>
       <c r="AA63" s="6" t="inlineStr"/>
       <c r="AB63" s="6" t="inlineStr"/>
+      <c r="AC63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -9340,6 +9408,7 @@
       <c r="Z64" s="6" t="inlineStr"/>
       <c r="AA64" s="6" t="inlineStr"/>
       <c r="AB64" s="6" t="inlineStr"/>
+      <c r="AC64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -9406,6 +9475,7 @@
       <c r="Z65" s="6" t="inlineStr"/>
       <c r="AA65" s="6" t="inlineStr"/>
       <c r="AB65" s="6" t="inlineStr"/>
+      <c r="AC65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -9472,6 +9542,7 @@
       <c r="Z66" s="6" t="inlineStr"/>
       <c r="AA66" s="6" t="inlineStr"/>
       <c r="AB66" s="6" t="inlineStr"/>
+      <c r="AC66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -9538,6 +9609,7 @@
       <c r="Z67" s="6" t="inlineStr"/>
       <c r="AA67" s="6" t="inlineStr"/>
       <c r="AB67" s="6" t="inlineStr"/>
+      <c r="AC67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -9620,6 +9692,7 @@
       <c r="Z68" s="6" t="inlineStr"/>
       <c r="AA68" s="6" t="inlineStr"/>
       <c r="AB68" s="6" t="inlineStr"/>
+      <c r="AC68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -9698,6 +9771,7 @@
       <c r="Z69" s="6" t="inlineStr"/>
       <c r="AA69" s="6" t="inlineStr"/>
       <c r="AB69" s="6" t="inlineStr"/>
+      <c r="AC69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -9764,6 +9838,7 @@
       <c r="Z70" s="6" t="inlineStr"/>
       <c r="AA70" s="6" t="inlineStr"/>
       <c r="AB70" s="6" t="inlineStr"/>
+      <c r="AC70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -9830,6 +9905,7 @@
       <c r="Z71" s="6" t="inlineStr"/>
       <c r="AA71" s="6" t="inlineStr"/>
       <c r="AB71" s="6" t="inlineStr"/>
+      <c r="AC71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -9896,6 +9972,7 @@
       <c r="Z72" s="6" t="inlineStr"/>
       <c r="AA72" s="6" t="inlineStr"/>
       <c r="AB72" s="6" t="inlineStr"/>
+      <c r="AC72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -9974,6 +10051,7 @@
       <c r="Z73" s="6" t="inlineStr"/>
       <c r="AA73" s="6" t="inlineStr"/>
       <c r="AB73" s="6" t="inlineStr"/>
+      <c r="AC73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -10040,6 +10118,7 @@
       <c r="Z74" s="6" t="inlineStr"/>
       <c r="AA74" s="6" t="inlineStr"/>
       <c r="AB74" s="6" t="inlineStr"/>
+      <c r="AC74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -10106,6 +10185,7 @@
       <c r="Z75" s="6" t="inlineStr"/>
       <c r="AA75" s="6" t="inlineStr"/>
       <c r="AB75" s="6" t="inlineStr"/>
+      <c r="AC75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -10172,6 +10252,7 @@
       <c r="Z76" s="6" t="inlineStr"/>
       <c r="AA76" s="6" t="inlineStr"/>
       <c r="AB76" s="6" t="inlineStr"/>
+      <c r="AC76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -10250,6 +10331,7 @@
       <c r="Z77" s="6" t="inlineStr"/>
       <c r="AA77" s="6" t="inlineStr"/>
       <c r="AB77" s="6" t="inlineStr"/>
+      <c r="AC77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -10316,6 +10398,7 @@
       <c r="Z78" s="6" t="inlineStr"/>
       <c r="AA78" s="6" t="inlineStr"/>
       <c r="AB78" s="6" t="inlineStr"/>
+      <c r="AC78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -10394,6 +10477,7 @@
       <c r="Z79" s="6" t="inlineStr"/>
       <c r="AA79" s="6" t="inlineStr"/>
       <c r="AB79" s="6" t="inlineStr"/>
+      <c r="AC79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -10460,6 +10544,7 @@
       <c r="Z80" s="6" t="inlineStr"/>
       <c r="AA80" s="6" t="inlineStr"/>
       <c r="AB80" s="6" t="inlineStr"/>
+      <c r="AC80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -10526,6 +10611,7 @@
       <c r="Z81" s="6" t="inlineStr"/>
       <c r="AA81" s="6" t="inlineStr"/>
       <c r="AB81" s="6" t="inlineStr"/>
+      <c r="AC81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -10592,6 +10678,7 @@
       <c r="Z82" s="6" t="inlineStr"/>
       <c r="AA82" s="6" t="inlineStr"/>
       <c r="AB82" s="6" t="inlineStr"/>
+      <c r="AC82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -10658,6 +10745,7 @@
       <c r="Z83" s="6" t="inlineStr"/>
       <c r="AA83" s="6" t="inlineStr"/>
       <c r="AB83" s="6" t="inlineStr"/>
+      <c r="AC83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -10736,6 +10824,7 @@
       <c r="Z84" s="6" t="inlineStr"/>
       <c r="AA84" s="6" t="inlineStr"/>
       <c r="AB84" s="6" t="inlineStr"/>
+      <c r="AC84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -10802,6 +10891,7 @@
       <c r="Z85" s="6" t="inlineStr"/>
       <c r="AA85" s="6" t="inlineStr"/>
       <c r="AB85" s="6" t="inlineStr"/>
+      <c r="AC85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -10880,6 +10970,7 @@
       <c r="Z86" s="6" t="inlineStr"/>
       <c r="AA86" s="6" t="inlineStr"/>
       <c r="AB86" s="6" t="inlineStr"/>
+      <c r="AC86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -10946,6 +11037,7 @@
       <c r="Z87" s="6" t="inlineStr"/>
       <c r="AA87" s="6" t="inlineStr"/>
       <c r="AB87" s="6" t="inlineStr"/>
+      <c r="AC87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -11012,6 +11104,7 @@
       <c r="Z88" s="6" t="inlineStr"/>
       <c r="AA88" s="6" t="inlineStr"/>
       <c r="AB88" s="6" t="inlineStr"/>
+      <c r="AC88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -11078,6 +11171,7 @@
       <c r="Z89" s="6" t="inlineStr"/>
       <c r="AA89" s="6" t="inlineStr"/>
       <c r="AB89" s="6" t="inlineStr"/>
+      <c r="AC89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -11144,6 +11238,7 @@
       <c r="Z90" s="6" t="inlineStr"/>
       <c r="AA90" s="6" t="inlineStr"/>
       <c r="AB90" s="6" t="inlineStr"/>
+      <c r="AC90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -11210,6 +11305,7 @@
       <c r="Z91" s="6" t="inlineStr"/>
       <c r="AA91" s="6" t="inlineStr"/>
       <c r="AB91" s="6" t="inlineStr"/>
+      <c r="AC91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -11276,6 +11372,7 @@
       <c r="Z92" s="6" t="inlineStr"/>
       <c r="AA92" s="6" t="inlineStr"/>
       <c r="AB92" s="6" t="inlineStr"/>
+      <c r="AC92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -11342,6 +11439,7 @@
       <c r="Z93" s="6" t="inlineStr"/>
       <c r="AA93" s="6" t="inlineStr"/>
       <c r="AB93" s="6" t="inlineStr"/>
+      <c r="AC93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -11408,6 +11506,7 @@
       <c r="Z94" s="6" t="inlineStr"/>
       <c r="AA94" s="6" t="inlineStr"/>
       <c r="AB94" s="6" t="inlineStr"/>
+      <c r="AC94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -11474,6 +11573,7 @@
       <c r="Z95" s="6" t="inlineStr"/>
       <c r="AA95" s="6" t="inlineStr"/>
       <c r="AB95" s="6" t="inlineStr"/>
+      <c r="AC95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -11540,6 +11640,7 @@
       <c r="Z96" s="6" t="inlineStr"/>
       <c r="AA96" s="6" t="inlineStr"/>
       <c r="AB96" s="6" t="inlineStr"/>
+      <c r="AC96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -11606,6 +11707,7 @@
       <c r="Z97" s="6" t="inlineStr"/>
       <c r="AA97" s="6" t="inlineStr"/>
       <c r="AB97" s="6" t="inlineStr"/>
+      <c r="AC97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -11672,6 +11774,7 @@
       <c r="Z98" s="6" t="inlineStr"/>
       <c r="AA98" s="6" t="inlineStr"/>
       <c r="AB98" s="6" t="inlineStr"/>
+      <c r="AC98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -11738,6 +11841,7 @@
       <c r="Z99" s="6" t="inlineStr"/>
       <c r="AA99" s="6" t="inlineStr"/>
       <c r="AB99" s="6" t="inlineStr"/>
+      <c r="AC99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -11804,6 +11908,7 @@
       <c r="Z100" s="6" t="inlineStr"/>
       <c r="AA100" s="6" t="inlineStr"/>
       <c r="AB100" s="6" t="inlineStr"/>
+      <c r="AC100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -11870,6 +11975,7 @@
       <c r="Z101" s="6" t="inlineStr"/>
       <c r="AA101" s="6" t="inlineStr"/>
       <c r="AB101" s="6" t="inlineStr"/>
+      <c r="AC101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -11936,6 +12042,7 @@
       <c r="Z102" s="6" t="inlineStr"/>
       <c r="AA102" s="6" t="inlineStr"/>
       <c r="AB102" s="6" t="inlineStr"/>
+      <c r="AC102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -12002,6 +12109,7 @@
       <c r="Z103" s="6" t="inlineStr"/>
       <c r="AA103" s="6" t="inlineStr"/>
       <c r="AB103" s="6" t="inlineStr"/>
+      <c r="AC103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -12068,6 +12176,7 @@
       <c r="Z104" s="6" t="inlineStr"/>
       <c r="AA104" s="6" t="inlineStr"/>
       <c r="AB104" s="6" t="inlineStr"/>
+      <c r="AC104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -12134,6 +12243,7 @@
       <c r="Z105" s="6" t="inlineStr"/>
       <c r="AA105" s="6" t="inlineStr"/>
       <c r="AB105" s="6" t="inlineStr"/>
+      <c r="AC105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -12248,6 +12358,7 @@
       <c r="Z106" s="6" t="inlineStr"/>
       <c r="AA106" s="6" t="inlineStr"/>
       <c r="AB106" s="6" t="inlineStr"/>
+      <c r="AC106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -12314,6 +12425,7 @@
       <c r="Z107" s="6" t="inlineStr"/>
       <c r="AA107" s="6" t="inlineStr"/>
       <c r="AB107" s="6" t="inlineStr"/>
+      <c r="AC107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -12380,6 +12492,7 @@
       <c r="Z108" s="6" t="inlineStr"/>
       <c r="AA108" s="6" t="inlineStr"/>
       <c r="AB108" s="6" t="inlineStr"/>
+      <c r="AC108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -12446,6 +12559,7 @@
       <c r="Z109" s="6" t="inlineStr"/>
       <c r="AA109" s="6" t="inlineStr"/>
       <c r="AB109" s="6" t="inlineStr"/>
+      <c r="AC109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -12512,6 +12626,7 @@
       <c r="Z110" s="6" t="inlineStr"/>
       <c r="AA110" s="6" t="inlineStr"/>
       <c r="AB110" s="6" t="inlineStr"/>
+      <c r="AC110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -12578,6 +12693,7 @@
       <c r="Z111" s="6" t="inlineStr"/>
       <c r="AA111" s="6" t="inlineStr"/>
       <c r="AB111" s="6" t="inlineStr"/>
+      <c r="AC111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -12644,6 +12760,7 @@
       <c r="Z112" s="6" t="inlineStr"/>
       <c r="AA112" s="6" t="inlineStr"/>
       <c r="AB112" s="6" t="inlineStr"/>
+      <c r="AC112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -12710,6 +12827,7 @@
       <c r="Z113" s="6" t="inlineStr"/>
       <c r="AA113" s="6" t="inlineStr"/>
       <c r="AB113" s="6" t="inlineStr"/>
+      <c r="AC113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -12788,6 +12906,7 @@
       <c r="Z114" s="6" t="inlineStr"/>
       <c r="AA114" s="6" t="inlineStr"/>
       <c r="AB114" s="6" t="inlineStr"/>
+      <c r="AC114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -12854,6 +12973,7 @@
       <c r="Z115" s="6" t="inlineStr"/>
       <c r="AA115" s="6" t="inlineStr"/>
       <c r="AB115" s="6" t="inlineStr"/>
+      <c r="AC115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -12920,6 +13040,7 @@
       <c r="Z116" s="6" t="inlineStr"/>
       <c r="AA116" s="6" t="inlineStr"/>
       <c r="AB116" s="6" t="inlineStr"/>
+      <c r="AC116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -12986,6 +13107,7 @@
       <c r="Z117" s="6" t="inlineStr"/>
       <c r="AA117" s="6" t="inlineStr"/>
       <c r="AB117" s="6" t="inlineStr"/>
+      <c r="AC117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -13052,6 +13174,7 @@
       <c r="Z118" s="6" t="inlineStr"/>
       <c r="AA118" s="6" t="inlineStr"/>
       <c r="AB118" s="6" t="inlineStr"/>
+      <c r="AC118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -13118,6 +13241,7 @@
       <c r="Z119" s="6" t="inlineStr"/>
       <c r="AA119" s="6" t="inlineStr"/>
       <c r="AB119" s="6" t="inlineStr"/>
+      <c r="AC119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -13184,6 +13308,7 @@
       <c r="Z120" s="6" t="inlineStr"/>
       <c r="AA120" s="6" t="inlineStr"/>
       <c r="AB120" s="6" t="inlineStr"/>
+      <c r="AC120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -13250,6 +13375,7 @@
       <c r="Z121" s="6" t="inlineStr"/>
       <c r="AA121" s="6" t="inlineStr"/>
       <c r="AB121" s="6" t="inlineStr"/>
+      <c r="AC121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -13316,6 +13442,7 @@
       <c r="Z122" s="6" t="inlineStr"/>
       <c r="AA122" s="6" t="inlineStr"/>
       <c r="AB122" s="6" t="inlineStr"/>
+      <c r="AC122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -13382,6 +13509,7 @@
       <c r="Z123" s="6" t="inlineStr"/>
       <c r="AA123" s="6" t="inlineStr"/>
       <c r="AB123" s="6" t="inlineStr"/>
+      <c r="AC123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -13448,6 +13576,7 @@
       <c r="Z124" s="6" t="inlineStr"/>
       <c r="AA124" s="6" t="inlineStr"/>
       <c r="AB124" s="6" t="inlineStr"/>
+      <c r="AC124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -13514,6 +13643,7 @@
       <c r="Z125" s="6" t="inlineStr"/>
       <c r="AA125" s="6" t="inlineStr"/>
       <c r="AB125" s="6" t="inlineStr"/>
+      <c r="AC125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -13580,6 +13710,7 @@
       <c r="Z126" s="6" t="inlineStr"/>
       <c r="AA126" s="6" t="inlineStr"/>
       <c r="AB126" s="6" t="inlineStr"/>
+      <c r="AC126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -13646,6 +13777,7 @@
       <c r="Z127" s="6" t="inlineStr"/>
       <c r="AA127" s="6" t="inlineStr"/>
       <c r="AB127" s="6" t="inlineStr"/>
+      <c r="AC127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -13712,6 +13844,7 @@
       <c r="Z128" s="6" t="inlineStr"/>
       <c r="AA128" s="6" t="inlineStr"/>
       <c r="AB128" s="6" t="inlineStr"/>
+      <c r="AC128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -13778,6 +13911,7 @@
       <c r="Z129" s="6" t="inlineStr"/>
       <c r="AA129" s="6" t="inlineStr"/>
       <c r="AB129" s="6" t="inlineStr"/>
+      <c r="AC129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -13844,6 +13978,7 @@
       <c r="Z130" s="6" t="inlineStr"/>
       <c r="AA130" s="6" t="inlineStr"/>
       <c r="AB130" s="6" t="inlineStr"/>
+      <c r="AC130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -13910,6 +14045,7 @@
       <c r="Z131" s="6" t="inlineStr"/>
       <c r="AA131" s="6" t="inlineStr"/>
       <c r="AB131" s="6" t="inlineStr"/>
+      <c r="AC131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -13976,6 +14112,7 @@
       <c r="Z132" s="6" t="inlineStr"/>
       <c r="AA132" s="6" t="inlineStr"/>
       <c r="AB132" s="6" t="inlineStr"/>
+      <c r="AC132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -14042,6 +14179,7 @@
       <c r="Z133" s="6" t="inlineStr"/>
       <c r="AA133" s="6" t="inlineStr"/>
       <c r="AB133" s="6" t="inlineStr"/>
+      <c r="AC133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -14108,6 +14246,7 @@
       <c r="Z134" s="6" t="inlineStr"/>
       <c r="AA134" s="6" t="inlineStr"/>
       <c r="AB134" s="6" t="inlineStr"/>
+      <c r="AC134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -14174,6 +14313,7 @@
       <c r="Z135" s="6" t="inlineStr"/>
       <c r="AA135" s="6" t="inlineStr"/>
       <c r="AB135" s="6" t="inlineStr"/>
+      <c r="AC135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -14240,6 +14380,7 @@
       <c r="Z136" s="6" t="inlineStr"/>
       <c r="AA136" s="6" t="inlineStr"/>
       <c r="AB136" s="6" t="inlineStr"/>
+      <c r="AC136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -14310,6 +14451,7 @@
       <c r="Z137" s="6" t="inlineStr"/>
       <c r="AA137" s="6" t="inlineStr"/>
       <c r="AB137" s="6" t="inlineStr"/>
+      <c r="AC137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -14384,6 +14526,7 @@
       <c r="Z138" s="6" t="inlineStr"/>
       <c r="AA138" s="6" t="inlineStr"/>
       <c r="AB138" s="6" t="inlineStr"/>
+      <c r="AC138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -14458,6 +14601,7 @@
       <c r="Z139" s="6" t="inlineStr"/>
       <c r="AA139" s="6" t="inlineStr"/>
       <c r="AB139" s="6" t="inlineStr"/>
+      <c r="AC139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -14532,6 +14676,7 @@
       <c r="Z140" s="6" t="inlineStr"/>
       <c r="AA140" s="6" t="inlineStr"/>
       <c r="AB140" s="6" t="inlineStr"/>
+      <c r="AC140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -14606,6 +14751,7 @@
       <c r="Z141" s="6" t="inlineStr"/>
       <c r="AA141" s="6" t="inlineStr"/>
       <c r="AB141" s="6" t="inlineStr"/>
+      <c r="AC141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -14680,6 +14826,7 @@
       <c r="Z142" s="6" t="inlineStr"/>
       <c r="AA142" s="6" t="inlineStr"/>
       <c r="AB142" s="6" t="inlineStr"/>
+      <c r="AC142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -14754,6 +14901,7 @@
       <c r="Z143" s="6" t="inlineStr"/>
       <c r="AA143" s="6" t="inlineStr"/>
       <c r="AB143" s="6" t="inlineStr"/>
+      <c r="AC143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -14828,6 +14976,7 @@
       <c r="Z144" s="6" t="inlineStr"/>
       <c r="AA144" s="6" t="inlineStr"/>
       <c r="AB144" s="6" t="inlineStr"/>
+      <c r="AC144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -14902,6 +15051,7 @@
       <c r="Z145" s="6" t="inlineStr"/>
       <c r="AA145" s="6" t="inlineStr"/>
       <c r="AB145" s="6" t="inlineStr"/>
+      <c r="AC145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -14992,6 +15142,7 @@
       <c r="Z146" s="6" t="inlineStr"/>
       <c r="AA146" s="6" t="inlineStr"/>
       <c r="AB146" s="6" t="inlineStr"/>
+      <c r="AC146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -15070,6 +15221,7 @@
       <c r="Z147" s="6" t="inlineStr"/>
       <c r="AA147" s="6" t="inlineStr"/>
       <c r="AB147" s="6" t="inlineStr"/>
+      <c r="AC147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -15152,6 +15304,7 @@
       </c>
       <c r="AA148" s="6" t="inlineStr"/>
       <c r="AB148" s="6" t="inlineStr"/>
+      <c r="AC148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -15230,6 +15383,7 @@
       <c r="Z149" s="6" t="inlineStr"/>
       <c r="AA149" s="6" t="inlineStr"/>
       <c r="AB149" s="6" t="inlineStr"/>
+      <c r="AC149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -15308,6 +15462,7 @@
       <c r="Z150" s="6" t="inlineStr"/>
       <c r="AA150" s="6" t="inlineStr"/>
       <c r="AB150" s="6" t="inlineStr"/>
+      <c r="AC150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -15386,6 +15541,7 @@
       <c r="Z151" s="6" t="inlineStr"/>
       <c r="AA151" s="6" t="inlineStr"/>
       <c r="AB151" s="6" t="inlineStr"/>
+      <c r="AC151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -15464,6 +15620,7 @@
       <c r="Z152" s="6" t="inlineStr"/>
       <c r="AA152" s="6" t="inlineStr"/>
       <c r="AB152" s="6" t="inlineStr"/>
+      <c r="AC152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -15542,6 +15699,7 @@
       <c r="Z153" s="6" t="inlineStr"/>
       <c r="AA153" s="6" t="inlineStr"/>
       <c r="AB153" s="6" t="inlineStr"/>
+      <c r="AC153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -15620,6 +15778,7 @@
       <c r="Z154" s="6" t="inlineStr"/>
       <c r="AA154" s="6" t="inlineStr"/>
       <c r="AB154" s="6" t="inlineStr"/>
+      <c r="AC154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -15698,6 +15857,7 @@
       <c r="Z155" s="6" t="inlineStr"/>
       <c r="AA155" s="6" t="inlineStr"/>
       <c r="AB155" s="6" t="inlineStr"/>
+      <c r="AC155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -15776,6 +15936,7 @@
       <c r="Z156" s="6" t="inlineStr"/>
       <c r="AA156" s="6" t="inlineStr"/>
       <c r="AB156" s="6" t="inlineStr"/>
+      <c r="AC156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -15854,6 +16015,7 @@
       <c r="Z157" s="6" t="inlineStr"/>
       <c r="AA157" s="6" t="inlineStr"/>
       <c r="AB157" s="6" t="inlineStr"/>
+      <c r="AC157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -15936,6 +16098,7 @@
       </c>
       <c r="AA158" s="6" t="inlineStr"/>
       <c r="AB158" s="6" t="inlineStr"/>
+      <c r="AC158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -16014,6 +16177,7 @@
       <c r="Z159" s="6" t="inlineStr"/>
       <c r="AA159" s="6" t="inlineStr"/>
       <c r="AB159" s="6" t="inlineStr"/>
+      <c r="AC159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
@@ -16092,6 +16256,7 @@
       <c r="Z160" s="6" t="inlineStr"/>
       <c r="AA160" s="6" t="inlineStr"/>
       <c r="AB160" s="6" t="inlineStr"/>
+      <c r="AC160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -16177,7 +16342,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB161" s="6" t="inlineStr"/>
+      <c r="AB161" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4QAqRXhpZgAASUkqAAgAAAABADEBAgAHAAAAGgAAAAAAAABQaWNhc2EAAP/bAIQAAwICCw0LCgoICxAKCgoNCAgPDgkIDQgLCggJCAgICggICgoICAoKCAoICwgICggICAsKChAICAsQCg4NDggKCAEDBAQGBQYKBgYKDw0KDg8QDQ8PDw8PDw8PEA0ODw8PDw8PDw8NDw0NDQ0QDQ0NDQ0PDQ8NDw0NDQ0ODQ0NDQ0N/8AAEQgAWABYAwERAAIRAQMRAf/EAB0AAAEFAQEBAQAAAAAAAAAAAAcCAwQGCAUJAQD/xAA5EAACAQMCBAMFBwMDBQAAAAABAgMEERIAIQUHEzEGIkEIIzJRYRRScYGRofBCsdFTYsEVM3KDwv/EABsBAAIDAQEBAAAAAAAAAAAAAAMFAAQGAgEH/8QAMBEAAQQBAwIDBwQDAQAAAAAAAQACAxEhBBIxQVEFImETcYGRocHwMrHh8SNCUhT/2gAMAwEAAhEDEQA/AMIH+fy2mKBaQza9UTZ1yoEy669UTbLrjcF6Egza43he7Uhn+WurB4XJCiyj568JoLy1FmP0/Xc/3At+OqrrcvMpmf67Afdvt+5H76r5HC8sL7FT/I3A37bH9QP7f50M88KFW8/TTtFwmidRc0kZa8UUWvqcQSTa1vqSTewAP5779v0rySVgIjBag0FXlvkG/O//AMj631XBKKWjopMi6i4STroGioQos8lvrqxYIQNqiSVe9z3O/b97f8dtDIoUF4QUzNXn0Hl+Xff7zbbt8trD0GgFi8ATMtUD3NvoSzX/ABsFX9NCLSOAva9Fec9Nl3aQRqLxNtqKcq3eAeQ8tcJJEeONImEfvrlnbFXKoo3xs28hut9u4NqE7gxXNPp3TGgQFcuL+ydVHGSGelMhCJg1SIjZUCfFhuwtbHDt67AGuJh2V52geAPMENfG/LSspGCVsGF7lWR1mRwtrsjISbC4uGVSPlrtsjXcFVZdNJF+ofFVIVI+f/GiKtxykSQ/zvorXNHJpDcaUGpX57flotg8LgG1Blb+DQiF7SlUtdfysSR8mUD9XG4H4i2gvscLw2Fcb6Yr0hIJ1F4ksdRS6Rt9mblY9RNFUAhY4JpEZgoDhVhjlZQ3co2ajH0uT8tLNa4N+Sc+HRe0dfYoocd9mvp1jT0saNHNkCZEEhW5a42ZD3wIJLdiPXZUybGVoHaQb9wCunjPl5AtI0FUA8Y94AFEZjZRfqIy2xcb+YdxcEEEg03SODrCYCBj2FruFmTk5yqmmngqmjLUd2dVKI5kCqRkEmvGRDkJQXDNeJSoZgDpo+by7Rykmj0RfIJSPKM56oWc3aSOKvqoYTdFdFUjFAZTDEZFFsUB6xe4VbA3AUDYGjssBKUeKRsZqHhnF/bK0Jyn9m+lP/RqmrY1cHEopo3jcFFirzAZ440MRV2VIo6oHqvs8Sm1yiqF7w2wOQjafQxHY92QRlCnxR7ODJDxWp6mH/Tqs0fSKZGSAtGy1BkMgx9zLG+PTa+L3IuMTN1NUD1Qn6EtbI8Ow08enPPuQbSIA/h6k7fiD5d/oTo5dYtJybV0J0zUSSdRRfGbUUpGLklzJSngmWad4FEyzExKzXSSONGDYAkC0B8/9JYd7kFZrG7iPkn3hL9riLrr9Fqrwz4/gkQfZZ+tdc8ib5i/xfBHYi4BGA2t+OkjmbFr/ah57rkcerma5f8Anpquc5RXSACkMuYvMKtp6OoahWOONVB6hGUiWJDiNCMO2LKWBF7kqbLo0RDngFLJpXxxOLMYQh9jmviPF0SrAkFVBWU3vfOTJKFmZ2LBj1HRZgWbc5G533byYbhZfSSXNbs3a1V7LvDTBRVHD5gc+F19Qis1rsqyLVJKtj8MsE3pY2kbbVOY3TvRNdIyrYehI/Pmk+0HwNFoOPOAL1IjlJFzeVaeOFdu9ysUYsO51WY/ztvurEzaifXVp+gXnEkVzYg+uw8twPvFgLfUn9NNiSOFiSK4VsL6cELoJtm1FE7FRsdwCR+Bt+vb99DLmjkqu+WNp8zgFaeXGaVUaAsOsGQiIdR8CpcMFAZbggMLq22W1rnVCaRrhQR9D4i1k7TGcXRK1LR+N6NIUAqciBf3jL1MuzXtiPoAFAGwtpLICSvox1TXDLlUZ/Gj1DgQnGMbFj3b/wAP8nXFbRlV95ecLq8zeDFqGWCIXZo3UD5tgSB+Z2/PQY3U8H1RJ2ExFo7LMPIngk32+inhTNUqIkc3/wC2JUkF5V+JVaMTYMVxZoymQNgdK+thCxMBIkaR3XpTT0lOpkl2V52jeTEbs8cUcIZv/Ska3+SDSFzu62AZmx1XA8Q+I4vPj98zG42KQxFibfRh+9u+gA+bCYR/46cegXldxni3Ud5Tu0jPKSTuTIxdiQNhcn6/jp61u0UeV83e4ukc49ST8zatJ05XNoueEuUBSCOvriscLWdUbIlYnVTBUzmNZDGkkjKqJ03ewZilw4jC+SjQ+KBuLnAN4UTxlxZGlkMVsHZnGNirKXbzqASFDEMRHsUHlsLapFgJJKC3w+ISulIsnp0H9r94A8brSpxKqRT9pWk6cMgselNNUQ0qmzXGQaVJVNvhglFje2vQ0DKtjTxtcHtFH86KF4Y8MLNS0zgC6KUY+pKSOPMe5JXE7/PVOQ06k4hbuAKNnhGiRVS1sdvh30rkOVpIXABXuSojVWndgIoVMhLdrKL2I9b9sRuew31Xa2zQVmSQNaSUGPYypCaniNYdljpoo2B/1K7iVI6C/bYU81/yt660jsMWNhNyWtIcXrCBcbDcfj/B89Z+U5WwjNrPXNfmNII6qOnieeWWKWlAhR36YmsrSuY1YrYZW7XIAB9QXSxF7r6BUNfqWxsLL8xH4Vlit4XIo96rR/7cDFiP911Fvwtf5nTjabwFiQOw+aKXLvgyLaqnClI8pFEhsl4mB6knoyh1YCN7K2LXv5Q1+WfY7alc+vbHMIdpca6dzwuL4n8Ymc5kjpoZBGiKqogcqcbKq2uqxkltzgG+I7h4TqKMNbgV6KorxhsscmKte4j2vipa49PLa+RuQATqIhwtu+xrynpqvhtctTEHWeYxydTzO9MsMRhuwIKYTfaJImjIZG84IaxHrTdhVI5g972g/pIHzAKzj4NqZaWJkWztFLVUkqOCQTHK1msCGVy3XAZbiyLcGw1UlaCUzhlLMhd/w3zHsbRwk5dl64xv3JywBCgXJJWwAJJsCdVHwX1TFmtr/VL8ZeJaisaKjpVMkk5EUUMTBBI4Bd5GLsgxCBiHlZVQLmcfNYkMIaVW1GodJjp2R95fctH4Tw14azpvW8UqqZLQsZAkFOFkVGcrGXEWNQ5KriGqlAuLsbcrqFJeJRG9gPJND89yvPjOBBFG2wzHZX2vbuQdwQdjrP6jlbaE4WeeG0DmcvTSrFKJJVDmcSLisPVjjlgCq7JUMlRCYkd5VMccoR1Mhp2cDQ1jaNH8+ywPiLYp9WZGy08YAsVjpXrnqj7wzihdFcgoxBDKTcpIDi6EjY4uGXIbNa4NraYNXYvqgdzk9k7iMfD2npujNT08aVHupSZBDT2kLFJYow5ABleMliSrCx7a42PD9zuFnNNo5YtQ7Uy7aN8E4B65Aqvj1WU+IVLSMqotnGWYWkipj6eaTpRRXNwdpSbE2FrnIzndVonysY3cSAFYeAUyMojgHnYSiR3XE4iw6Ud72L3VAR8ObMTfEGuSbs8JDO+USB8p8uC0D9z7lqv2c+YS0UzQHywVEYprn+mWMH7O7G/YsXiJ+cwYmwOuYX0/PVItDrS3Uue7/fn33j7j4rje1XyYME719GwKcQIm6Cj3n2+NDLLLTKi+8jlpxUyzJYuJHyuQ46VyaMHK30bsWgpBTVBkFLS07yVkgBaJYixswUko+0awAlerOzdNmFg+Cl5qvs0ffS0r4H5TPwikqeLVONTxHphQoJ6NLC8katFGRZpHJIaaYBcggiSwMkkxS3a1VppCxjnjJAQUreblZPVw1lXMZujnhEB0o1Dqy4qoACKGKtcKzv00DNezCkTjKyg8RcyUTP8AM4cDgD3fnvT/AIh8fzzH3r2W+yR+UWP3rG7fXI2+mhBo5QNX4xqtT5XOpv8Ay3A+PU/t6IscovGmNE9NTIpqGklViZoqQI1SkkdI7NUJFHVSo0UhgiFQTFkSUPu11aaDtsJhofaDS/4mbnEkY2gjGDnBrFfxS7vC+KslZVwO2akmpDZMSJHlkWRDmqMEC9ExqFso9TcHRAc0nrpKmETudoP1IP2V851eKRRcMmSmlaVeJsMJCFPuXgQS4siouDU8YRCFv72+5BbRJSGs55STVzex05LHE7yKN9x04obRiuufVYJHEijY90Yi2/Zh2BPqLWCnuLAH56p8hJQze31C43haT3y723LbbXtk4B9ccgDa/dRfVuT9C0+vO3Sk9aH1wiLxqqON+47H1sCNifpfY7+vfVILBRtBNFdnwz4+yqEquMdSeCmgakjPSadIHbOS4xQt1ZYllDuD1GWNSwaNZDFcZITgrZeG6skCN+egP2Pw4UTkpzvWn4k9WYWWilganKdRMwinrQGIFwps46YGaxhZXbPYKey8BNJtZFFg89grZzf9pSasjaONRTUreXANlJJY5KJnFgF2DdOMW8u7sLWrvlLkg1evkkOxopv1P8en1QRp+OBWAP8AbQ6S10RcMK1Uc4IyX9vr66CQlzgW4K6HCONTo56EvTZLH4i1nsGyEXwFhsBI98Sp2uNiNJAwmGn1UmnbbHEX24+uFfuUxPVJbc4NchcRa6AAABQFAAUKoCiwAAAAHcZLnWr/AIbO/UasyPydpz8lSec3Oeorp2nkkAT4Y4gC6wR4qCi+ZN2YZs2AZjYHZUAjnbjZQpJP/Q8OkabGALwPdj5/wEI+KcQIR8hcG1iARZrjupvYX/qDEbfhftgFplpI43PBJo9knwVKDMLKFAVwbMzeYi9/MzWsAQLfM7nRpP0q94qb0xruEQIK8G6H5Hv6j/I9dUysIWEDcEWvZr4/FSyGWYhmqWSBYnqFgRYIpoTLWOJJBHLLCXJggWJ53McgV4lZmksxEDlabwymgvPWgPh/fH7qkc96tft1TnEIhE5jEccUcYBb3lozDHH1Y5JHeaGokUyPHLHc7LiJziXH8/O/xQNY+R8xbxX5aF1ZSEXedrPYlY1PwKfLk9rXNjsDrlDDwRsYMdXd/cn+FUolXEfF++o7CBK50RvonKWhqYzZUuO+/Y68NFQvhky4opcpuSw4k7Rq5pq1GRg3xxtC0dQ8pcWJFpEixYf6pFuxHrAHYCu6OP2odGwjpV5737q731RX4FyvmoXmiq2SSZsAGiYlTCo8hsQpVyxfIFReyntax2MLeU70WjOn3bqs9u30X//Z</t>
+        </is>
+      </c>
+      <c r="AC161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -16264,6 +16434,7 @@
       </c>
       <c r="AA162" s="6" t="inlineStr"/>
       <c r="AB162" s="6" t="inlineStr"/>
+      <c r="AC162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -16346,6 +16517,7 @@
       </c>
       <c r="AA163" s="6" t="inlineStr"/>
       <c r="AB163" s="6" t="inlineStr"/>
+      <c r="AC163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -16420,6 +16592,7 @@
       <c r="Z164" s="6" t="inlineStr"/>
       <c r="AA164" s="6" t="inlineStr"/>
       <c r="AB164" s="6" t="inlineStr"/>
+      <c r="AC164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -16498,6 +16671,7 @@
       <c r="Z165" s="6" t="inlineStr"/>
       <c r="AA165" s="6" t="inlineStr"/>
       <c r="AB165" s="6" t="inlineStr"/>
+      <c r="AC165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -16576,6 +16750,7 @@
       <c r="Z166" s="6" t="inlineStr"/>
       <c r="AA166" s="6" t="inlineStr"/>
       <c r="AB166" s="6" t="inlineStr"/>
+      <c r="AC166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -16658,6 +16833,7 @@
       <c r="Z167" s="6" t="inlineStr"/>
       <c r="AA167" s="6" t="inlineStr"/>
       <c r="AB167" s="6" t="inlineStr"/>
+      <c r="AC167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -16736,6 +16912,7 @@
       <c r="Z168" s="6" t="inlineStr"/>
       <c r="AA168" s="6" t="inlineStr"/>
       <c r="AB168" s="6" t="inlineStr"/>
+      <c r="AC168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -16814,6 +16991,7 @@
       <c r="Z169" s="6" t="inlineStr"/>
       <c r="AA169" s="6" t="inlineStr"/>
       <c r="AB169" s="6" t="inlineStr"/>
+      <c r="AC169" s="6" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
@@ -16892,6 +17070,7 @@
       <c r="Z170" s="6" t="inlineStr"/>
       <c r="AA170" s="6" t="inlineStr"/>
       <c r="AB170" s="6" t="inlineStr"/>
+      <c r="AC170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -16970,6 +17149,7 @@
       <c r="Z171" s="6" t="inlineStr"/>
       <c r="AA171" s="6" t="inlineStr"/>
       <c r="AB171" s="6" t="inlineStr"/>
+      <c r="AC171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
@@ -17048,6 +17228,7 @@
       <c r="Z172" s="6" t="inlineStr"/>
       <c r="AA172" s="6" t="inlineStr"/>
       <c r="AB172" s="6" t="inlineStr"/>
+      <c r="AC172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -17130,6 +17311,7 @@
       </c>
       <c r="AA173" s="6" t="inlineStr"/>
       <c r="AB173" s="6" t="inlineStr"/>
+      <c r="AC173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
@@ -17215,7 +17397,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB174" s="6" t="inlineStr"/>
+      <c r="AB174" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAgoICwgKDQoKDgsKCggKDQ8LCw4LCggIDgoKCAgICA0ICwoICwoNCgsIDg0OCggICgoOCAoLDgoKDwsKCgoBAwQEBgUGCgYGCg8OCw4QDxIPDRAPEA0QEA8PDQ0NDw8PEA8QDQ0PDQ8PDQ0NDw8NDQ0PDQ0PDQ8NDw0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAACAgMBAQEAAAAAAAAAAAAFBwYIAwQJAgEA/8QAPxAAAgECBAMGBAMFBQkAAAAAAQIRAyEABBIxBQZBBxMiUWFxMoGR8AhC0RQjocHxcoKx0uEkM0NSYnOSk8L/xAAbAQACAwEBAQAAAAAAAAAAAAADBQIEBgEAB//EADMRAAEDAgMECQQBBQAAAAAAAAEAAhEDIQQSMQVBUYEiYXGRobHB0fATMuHxghUjM0KS/9oADAMBAAIRAxEAPwBC5jM064CoEVtT+GoIiUVbFWCyCrEa6W7SACJPsPhnAXcDw16/dWdq7XpPeIpOaATOnBo3awRv3FZMjwBUdkeC0F2JBYFf3VUJpkBgdyNQLAqQROPPzNzAyDEDqN15gZVNOpThwDszyd7REiOdx7qU8M41lSoUK5VVloA1aZBJMEGbbKIBUAWYhqtOhXF848beHJPMXtPZxLQaLiACCOjDpkETIibHcLRpIU64Fzpl8tkUyjVn/aszmi9BVp1XSvC0Lo1JXoyDBPeMjqDMadLte2i7K5oJ3CO8lYnYjPqMe5gP3EEGAQcoHFWL7M+wWnUIq16lYs4osy6lCo6imVCNSRaoAZJjvWksxLsCqpn62PvFPvW2o7Mhmar3BMriP4TeF16XdtlpAXSD3lTWovs/ea/zNfV1Pnj1PGV2HOx0IFWjhndB7BCRvM/4dqfAa1HO0aQNGkUDMq6q1GkQErGrLA1KbKFDsI03cpuxuf1J9cFlU+07uxVn7LpNbnojSN27fPHq4JAZ3nKrl3qCiq/s8uaas4VqNNiSKI0hgVSdK7QALWnFilUBAJ1CoYjAkOcKbpE6kR7r5wfmFKkAuWzBKmpCwlJWaVpoW8bAtruVXVosvhvys7NEIdOj9OZU95eMtS+Z/ifvp+vGahTdomBwWjc+x9yZAget/ZffF5oVQlUT4ZxtV8NQFgAApLHUigHwLGwv4ZBVYCkFTqSdGoB9wVfG4Z7v8boI3ag9o9rqRZbiCOqeI6k1IIGktSPwlh8M7zAG95InFs5ajYtI8tyo0BUoPJMgOE2MiYh3eAO5fcvl1VgwZgRewBHrIkW8/O+APYdyZU6jNDKfPYL3TBBv3VevUXUL0y1OjTRV3MCa/l8QxndqVS0NB+fJWm2LhmGo57b6HmbeQCudyjmwAvy+mMwHXW3q05aQmpkeJwMNGPgLIVaEuUc5ozK1AykAgggg7EbEGbEHrNsAe+8hM8NRht1QftabKcMfMgcPfMaKiAf7ZUogI41gIKVKoRoBAMlgdIIKyVGjoPa5rczRca9izOKY9lRwa42Ok8VBuVMwj5TJVVp6TmK3eEFi7KpSmyU2ZvE5VTEkeIy0DUce9yhVPu/iExeWh4qXs/8A9eX2dhPSwwXCpuNimdwTK2ewst5sqiR/vTsi+SA6juxvOGAbZUXO+fPNc5c1xDWZ0gX6bR5f0geknFRogAJlVf8AUeXxEnRSLlJ/GLSYIAiZ69PScGbCBeeiJPep/QotGzD+4P8ALg0D4VIlw1Dh/H8JmdkeRZdbgzJYwLEaSqgEDqSGI9IvvGT2w8Zw0ajXnBC1uxWOyGoTZ2m42JBTdyPbNm6JUUqOuNUg0T3Y0qC47xqqsSB1VGU7W6LqVHM0uA0608q1iC1pm/ASOZ3c06E7WagyQzfdGx06fadXrv8AQYlTJcYQqlNgvvKhPAe31s2dLUqasSy6V7zUCCA0GtSpo5UEFgpJEi53J3UIgkQq9OsIIaZAPiqn/iW5kzdHMZ0HIF6BalVSo+dWilULTRKho0yrMCHDK0wz6BAYRDnDDMGwb6RHH9LM44ZKhc4WO+eHzmsPLVHTkeEQpAIpNBOoiaKHSWChWPmQigxIVek/cqtU+7kEyOV6DF6ZO3iHWBZuom/tLdIXbFxjCSCVQe4AEJycJymkXgWldQNri9Ggsuf7VST5iMNA23zy90qLp+eZ9ly7pVb/AH/Tb9I6YVynMKVcmZ5VqIx2XUfU2gC9tyOnnjsqbBBmfngmtlOa6J8p9h/LE7HRHNWNYPzn5pq9ivGVZmAA3T5iXJ+/9cZbaoiqCdSFrNjvDqcDQH2lWWocCpOjVCAPDqJjyGFTHkaarTupt0X3gHGKD5daeumVNRkC6gTImRYwTYyBex8sWKQMSFTrhsgdSI53gtLLqWgG1jvHlvMfKMFc5xsgFrQJSn5r5xyek03GVLtVqh2qU0aolPugFhnGpQH1H4lE6SJgg6jA5WUbm6+f7Vc+piIaLAepPqq6cAeOH8GDCGFHJSCIIY0KYIIYWM9D1tB2xGNO1BqWMdScvAcr46XQx5wYg9VLVR/dSmB5Yahunz8pUXWPz8J3cvcHMeEVL79zS0E7XepmSKpPmVI84wyay1vAR53Sh9Qb45mfAWXJ/N8MppN4N7B503+G6jp/1NuJMzGQFZztPIr6PUwNOmLz/wBA+ixZHTJ8R6xaCfSPP22xaGY6JS4U26kotl+IhPM/I/ynBmg71Vc5p+2Uyux3tGFCugJgNCx5tMg+KDeQL2F+pwg2nTzmQtNsmpkarUdpHbS+Xy9KnQGqtXV9OldZChZJCgH03H0thDSFzK1tWq5wAZqUh+FjjGWfL1Aa+lXNQ/utUwfzEKXYGTC3CmYUQDhxTDYsEuq4fEjpuI71YfjPbStTJ9+1mhlZbjTUHhcCYIEnqLbYEwXVariCGQdVS7m3nJa1Sq7ZDIV2ct48ymZaqqySBTOTz2VQBZPxUn3MzjSUGDKFjMTVJeUS5R5x108pl4g5U5ejM/Gi0wqOdOjSYQ6hOn1gwJOZlIQTUzyVbvhlEjurER5d4D8PQUqKP/4knpHk8aLftI3Ov+k9uFKhp0wzUDKrapnHPlbuqwFRf7JuvXbBxE3juPmVQcXQYnkW+QuuOdXiGv8AKdyfyiSd9kt6QYtMC0ZUWX0Bwe8ySSgfFa+iqu0aV2Mjc32EH69LnBgbSqL2w6Ct+pxBjtJ9r+22JtKCWwva5t6OhmMEyRsSomAZmJJBsCNt9hitWaHK9h3Fosm12c9uVam6sxlaYKyxmBaVA3v8+knYFRWwYLejqnVDGuDpOgTA4Z2x1UrV8w1WQ1lpBjpQAAKdyJJ1bT+U4CymRDYTGriZbJdylJ3n7tsrZw1LwpLMB59Kg9IJpk79dsNqOHDddVm62JLjZek4klKnqKzCg9SLgNLHYTI64aNbCQOOZyA9nXFi+Ykn4q1M/wASBEA7T0EjzX4gR92g8CutsY6l0PySDSpA2ZhZGMnRItRNJz7Cmrm8ORIVxSu0x6+nzrSWqYcB7eqs9wrIt3NAzV0mnTv3aVUNl2aDmY/7njGxM4hn6cA9zj5H0VZ7Dkkjhq2PEeq4m8G5WdwCSyqSOksReT4iFFp2a3UC05kNJW+NcNMNn53oxU5WpodfcK7QPFWcvbeNA00evVCfU7YILWVJ7i4yVrGu7KZamotpRFChRsWGkAT0gT/hBGoJ4qI9pn7t6Z/KFRfY2Ja3lI+p+cYlGDsqF5KoyANcC5G9jcjbcyNpOxFt8BtMK2Q4AEaLLX4837wC0KF9NcFQPbTpAvuPniQaLFQLiJAQ/wDapBF5LE9bEx+nvt7YONVXcICnme4y6CloIMLBtOwF7RYifQ/xxZGllRIvdFeWebzTqBzl6TNBBJUDUv8AykNv/wCwEdIvjjm5hlOi6LGQnvyB22JqXXNJjA01DqouNtOsWWVsdRSxAFS2OU3PY7olRqsa8Q5dMOT+KU61HLMhUs9JG8DBKrAKmoqUY0cwqmxIYqpADHUCMXS/M73v+QlNSlkZ7W7xoe1cgaSxTpDqQN/UBifp7fEfXCQHVaUtutPmPNqiGWA+pn0gSd46fPHAZK6W2UCzvMiwqrTZlchS5IVVBOlidRLGBeABsb9cEGq5lspjyNy/l85mqOVq6tFWnXoCd+8ek/dy3RjcqRs+kDfBSOjIQQYMFRfs34NTNevwzMk95RrVqVNxYs1MvTI0kwbAsoF2SwI0glfi2PaPq0+YT/Z1WnU/sVuR9E2eGfgrZ2V/2kGmR4oQyxncSw0mI31e2+pR/Un/AG5YPanjdjUycwdIWbtb7CcvkctRIYh3qhKYidYXxVqrkRC7LMfE4FtWDYOvUqOLjoqG0KNOkwUwkEeYV/aK1FSCqWRh+YBV1qYlTpbWARG09JOlpzF1kagEo3la339/d/bBihotSm3kT1+/XAyV2E//AMKva1Wy1erlO8IpOBVRWJ7unXUCdMENTZlmHpvTZSlmGtpNmgSq72AmEm81zCAywhMEiZiTHsQL/c4UgWKcESQhnMXHdSN4d7b7XmLj36460XXH6KKUcwrIUKnebfYx0iDK80yIWXl3N6/3QYrVola1FoGpWVgyssyC1OoEN1PxLvpOJZst9xUC0P01C0e2Tj3e5582PC9dMpmGCG+XzS01o1VQ2PhrUWdGhTpdGAGLjB0VVJINrFWz/Dj+KbLZpaOVzBZc3VenRTTSdqeYqMVSnUBpKyUwxYBtZVUKkzpvjMY/Z7hL6f29q2+y9rsAyVjDuzX9qA/ia7VFrVqrK37qkpoUBYApcVKwg71X1MSBJASfhxcwGHytCSbQxJqPN1WPgyLr1km1wRuT1Pzkz5z0N8OykcqZ8Oz6tvqj/Hy6j7OOFy6Aiua40PDCn5/K28C2BtUyOCKcA4wUIqqSCGsdj08vuMWGncqzgtdVhj1hmn6xPzHrafnhSTeE3AstfjjSFFtz0+cnrJk/w+U28VF4Qejl9LRFiP5T5zf3/TEnGyg2xQzmHh7qBWSQ9Jg6kelmHnBBIPmCR1xNsOsVB0gyF45pjNL3okESNtIO0xM2P1nqbkzpnIcpKjUbmGcBanZhmmp1+9DMBSp1zIOko1Sk+W1AgalYLUcqQVhlUzbE64BbHFcoGHZuC0OY+YnzdTUT4RCqNgB1MfdosL46xoaIQ3OzGVl4flfp/E4kSvASpFl12t0AwGUWF+zmY2+f6dMECg66OZAwiDoBPzN74mDvQyFk5WdczWcaiCCpb0DDU0E28+hGFb+iAmbLytrmvJim0arbgkX38QIB2n02I88dYo1I3oKwA0nULC14tuNx/PBEOFtUK4YEH83hsZkxYbzG4sOtzjwtopG4Ue4bT7pnpsvhklTNlZpgHpDNqvNiY/NYzh/sEFh1aeSFcTTuKZpg+KozO/ov/DT6XPqTYTebekcx5KD+iMu/etbl7gLVLx/r63gRiTnblBrd6OjhpBvpAE7kb/Kf1xAFS3rf/Y+k/QE/WYH9PLHAplDeNLpg9I62MzcWkeXXBBohFb7cZBAVTYgSfSNh6/d8euvWX//Z</t>
+        </is>
+      </c>
+      <c r="AC174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -17294,6 +17481,7 @@
       <c r="Z175" s="6" t="inlineStr"/>
       <c r="AA175" s="6" t="inlineStr"/>
       <c r="AB175" s="6" t="inlineStr"/>
+      <c r="AC175" s="6" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -17368,6 +17556,7 @@
       <c r="Z176" s="6" t="inlineStr"/>
       <c r="AA176" s="6" t="inlineStr"/>
       <c r="AB176" s="6" t="inlineStr"/>
+      <c r="AC176" s="6" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -17449,7 +17638,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB177" s="6" t="inlineStr"/>
+      <c r="AB177" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAggHBwgHBwgICAgIBggIBwcICAgICAgICAgIBwgIBwgICAgICAgICAgICAoICAgICQkJBwgLDQoIGAgICQgBAwQEBgUGCQYGCg0NCA4PDg0NDw4NDQ4NDQ0NEA4QEA8NDg4NDg8NDRAODg8NDQ0NDQ4PDw4NDg4ODw8NDQ0QDv/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAEAAgIDAQEAAAAAAAAAAAADAgYECAABBQcJ/8QAOBAAAgIBBAECAwUCDwAAAAAAAQIDBAAFERITBgghBxQxCRUiMkEjURYZJCYzNDZCUlVhdaGxwv/EABwBAAIDAQEBAQAAAAAAAAAAAAIDAQQFAAYHCP/EAD4RAAICAQMCBAMEBgcJAAAAAAECABEDBBIhBTETQVFhBiJxMoGRsRQVQqHR4SMzNVJic/AHFhclkrPBwvH/2gAMAwEAAhEDEQA/ANU1XPCz9TBYqpg3HBYqx4NxoWIEyLjAsmI8i4e2S68i5O2c6865O2dFMm4O2RKZNwSsNkybgFYTLkxRWcSPOkhY6R4NxwWMseDccFiLHkXGBZMR4NxgWS6865O2c686522RMedcgrIMmTFlYbJhXFkQWTCiSJJEziYSrHSPAuPCxljwbjgsVY8G40LEEeRcYFnfXkXJ2zhjzrnbZBo8m4BWGyYUWRBZcKJIgOuEIgiIiZBjFEdEwCZYUTIRMG48LFVMG40LE68G40LPU1LxO1BGk1ipagikIEU01aeGKQspkURSSRqjlkBcBWJKAsNwCcNkZRbKQPcESvi1GDKxTFkRmHcK6sRzXIBJHPBsd+O88wx4Fx5WEyYVwCITrhRJEbS9BnsuY60E9hwhcx14ZZ3CAhS5SJHYICygsRsCyjf3G7FVmNKCT7C5SzZceEbsrqq9rZgov0skC/b2nnW6zIzI6sjo7JIjqUdHQlWR0YBkdWBVlYBlIIIGxyexgWGAZSCDyCDYIPYg+YI5BHeZOlaZJPLFBChklmmjhhjXbeSWV1ijRSxCgu7KoLEAE+5HucgAkgDueIbOuNGyOaVQWY+gUWT9wF8TbaD7NLWvl+xr2mixxJ+V/lJQfuU2RH+bb67Vyob2Bb8x2P1Tl23uW/Tn8/5T53/xA0AybRiy+H/e+W/+i/8A39/aUT4Q+jbVte0qLV6MtFYZ2kEMM8s6TN1TtXfnwrSRoOSOw2dyQo9hy2Wng6flz4xkUij2u74Nek9F1T4t0PS9W2jzrkLrW4qqlfmUMKtwT3APA8/Tmz+fegHW9PqNbikq3xHGXmr1e5bCqo3boSRNrPEbnirRytsAkUhYJjM3Ss2NdwIb1Au/u9ZU6d8d9N1eYYXV8VmlZ9pTn+8Qfk+vIF8kAXK74v6T5dQ8WseSJqEMccdPUJvlDWd2ZaRmQr3idVDS9JKnpIXmv5vc4hNAcmnOcMKpjVel+d+3pNfU/FePR9Yx9KbAxYviXfvAAOTafs7D23Ufm5o9ps16xdAlveNeN1K45TWtb0qCINuF5zabdiUyFVZlRSwZ2CsVUMdjttm11JC+DEq9yyj8QZ8z+DM+PTdU6hnymkTDlY1V0uTGeLIsmqAsWaFzWDzD0g6zS1GlpW1S1avxzSQrUmldIooDGsstx561fpiHYCHAflxZVDMY0kxMnT8yOuPgsbqieK9bAr/XnPpml+LunanS5tYC6YsZUNvVQWLXQQK7bm47cV3Py2RePI/s5tbgqmeGzQtTKhZ6cZmjZtgSUrzSoElff8KiVaytvuWTbY3G6RmVbBBPpz+4/wAannsP+0Lp2XL4b48iITQc7T97KOVHmdpcjyBnxz4MenjU/IrMtejGkS12C3LNnnHFWYkjrdQrSvY/C37BUBHH8bQ7hjS02lyZyQvl3J8v5+341PTdZ69pOlY1yZySWFoqUS49QboL/i8/2Q1Gbs+k/wBI+oeMavZtWbNWzWn0wwBoe2ORZhPFIA8TqV4cFfaQSk7+xRd9z6LRaF9PkJJBBFf6/wDs+NfE3xPpur6XHjx43TIr7qNEbaI4Io3dcbfvmiXqX/tPrm/+c2P+12/42zA1f9fk+s+sdC/svSf5Y/Myr+Diz8/SNBC91b9Z6UYAYtaSZJIBsxVSO1V5cmVQu5LKAWFfHu3rs+1Yr6+U2tT4P6Pl/SDWHYwc+iEEN680eKBN9gTxP1S0eha8p06SDXNN1LQbkHsk9a/1/tJUkQy05qswaVVADPDahaEGSMDv4l19gobUJWVWRvZvyIP7iK+s/OmV8PR9SMmhzYtRiPcPivgUadXXi+wZG3UD9m6lc+B/i16j4Pao6Y4k1CrJr9WlIipGHsQalfgjeNZWaNCzpugdiikgEnYnE6ZHTSlMf2xvA+oJmp1nVabVdex6jVitO/6M+QEk0jY8ZIJFE8HkgX6Ty/Qzp/kcY1H7++8Ply0Hyg1OWSWfvBlFgxGZ5JhDxEP1IiZvxR8t5WKumDUDf426uK3Hm+b967e3pL3xxk6Q50/6u8LxPm3+EoVdvy7boBd32v8AEBw3YCVbQPLa7+BeVGsVNeHUderwFCOvqszd0HWfoUaO3GVI9iGG2++IXIp0ebb2BcD7zY/OaefR5U+I+meMD4jJpWa+9ooVr9wUN/SbM6D5RUq6do/zkscZsJRrVGl/v25a28UaHYhZJFV1X3XkTxB3YKdpXVETce9AfWp80zaXPn1Op8BSdu93ryRW5J9hYv079hKV4holiLzTVp7rI4taLS+5mCgFKdeR1vQKduRMduaKaX3b+tQHdd0RK2NWGqcv5qNv0HcfibP1E29ZnxZOhaXHgBBTLk8fng5HA8NvTlFKr2+w3uT4VHyWlpWtXpa/j/lL3rMkiT2EjtWqNneTmrxSTai+nxoeIMTN0mCN+raDeSILDpjysVx5Nx79yD+Lbfp2rtxLT6bUa3Q4VyazRjAoBVSUTInFEELiGQnn5q3biN3zcGL8IrDy6b5SdIrmlqkmtao4r2DDzi1GWpA0DTdck9f8TGJyUkkiLFyST2DCwcpl8MU9twa+1Q79xE9UATU6Aax/E0wx4huXdRxB2sLYVuOQLAPbyqUP0P8Ajvlde7d+/jqHyJq8VGpWTZlNwSx8WrF5pnEfSZu1lKxsxi25bNtX6cmpVm8W9tftGzftz+M2fjDUdGzYcX6B4fjbufCTYuyjw3yrzdbfMDdflNJfUyf50a5/vNj/AM5h6v8Ar8n1/hPp3Qf7L0n+WPzMqPi3kU1G1Xu1mCT1bEc8DsodRJEwZeSN7Mu42IP1BPuPYiojFGDL3HIm9mwY9RifBlFowKtzRo+h8j6TY3VvtDvI5oWhX7tgZlK/MQVJu5NxsWj7rc0If9xaFgD+maTdVzkV8o+gN/vP/ieMw/AnSkcOfFYDnazrtPsduNTX0YfWXP4K+suno3ip08NYbWI1vyQNJA80D2LFqexC00xkHIHtVpCzBtw/5jtyfp+oJi0+znxOfKxZJI5/OZvV/hDP1Dq/6RSjRnww1MqsFVFVgq1x2IWhXbynz/zf1yeQajVem8tSrHKpSWSlBLDO6EbMglksz9YYexaJY32+jrlHL1PPkUrYH0Bv8zPTaH4I6VpMy5wruw5AyMrKD60EW69GJHqDK14zV17+C2pRVKrN4/NaWa/ZCRhleua4bpJmWYwL0QrM8UEsaCOQF4+M3FCDP+juFH9ETZP0rtz24F8Hz95ranJ0v9cafJmyf8wVduNbNENurd8pXcdzFAXUm1IBtbD4jepLVNXoVNOtPXSGjNBNWkrRPDYWWvC9eGQy9zgOqyM28aR/tOJHHbjkZtZlzIqNVCiKFGxx6yem/Dmh6dqMupwhi+QMrB2DIVYhiNu0cEiuSeLBvvPa8x9Zmv3hVL2K8EtOwJ4LVWv1z8+qSBllMkk0LxSpIxkhMIjdlQ7DgFx79RzvtsgEGwQOfT3Fe1TN0nwf0rSnJtRmV12srva1YaxSqwYEfK26wL9ZaP4xbyIR8OGlFuO3aadjmT/i2F4R7/r/AEe3+n6ZYHVs9fs/gf4zGb4A6Tuu81eniJX/AGr/AHz5J4X6i9Z0zUbOq1rm9q64e/2xRtBbILFe+BFjReHJuDQdLIGYBgGdWqYtVlxucgPJ732P3fwqei13QtBq9Nj0mTHWJOMe1iGS++1jZN1zu3A/Wq+lWftFfJTIsgOmqoRlMK05OtixQiRi1ppuaBSq8JVTaV+SOeto7360zk38v4fznlv9x+lBSv8AS3YN71sVfA+SqN82CeBRAu9dPNPK5tQu2b9nh327L2JuteCc5DuQiksVUewALMdgNy3uTnu5di7dzzPXafTppcKafHexBtF8mh6njnz7TBRsSZpAx0bAMeDGVsGOBiCTBjA0uulfGnVK+lzaLDcdNOsM5mrCOE7iT3mRJWjM0ccx95ERwCd9uPZKJLC6jIuM4g3yHy4/P3mTl6TosurTX5MQOoWqa27j7JIBolf2SR9bpapZkyvU1y0Nnwqiy0F3woktAd8KJYwHfDldjMd2wxK7GZKti5ZUxlfBjgYqyYNRoaTEmdULdOdmRUndOjJk1I3SDSZNQC0JpMKootBd8KoktAd8ICILTHkfDiGMylfAqWQYqvgxoaTEmDUMNJdmdULdOdmdUndOjJnVB3SDSZNQC0JpMKootCaTCqKLQHkwoktBd8ICILTJV8CpZDRA+RUYGkw+RULdO+zIqTunOzJqdunRkzqkFpAvk1ALQmkyaiy0Jnwqii0Jmyaii0gRkxc//9k=</t>
+        </is>
+      </c>
+      <c r="AC177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -17524,6 +17718,7 @@
       <c r="Z178" s="6" t="inlineStr"/>
       <c r="AA178" s="6" t="inlineStr"/>
       <c r="AB178" s="6" t="inlineStr"/>
+      <c r="AC178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -17602,6 +17797,7 @@
       <c r="Z179" s="6" t="inlineStr"/>
       <c r="AA179" s="6" t="inlineStr"/>
       <c r="AB179" s="6" t="inlineStr"/>
+      <c r="AC179" s="6" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -17680,6 +17876,7 @@
       <c r="Z180" s="6" t="inlineStr"/>
       <c r="AA180" s="6" t="inlineStr"/>
       <c r="AB180" s="6" t="inlineStr"/>
+      <c r="AC180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -17754,6 +17951,7 @@
       <c r="Z181" s="6" t="inlineStr"/>
       <c r="AA181" s="6" t="inlineStr"/>
       <c r="AB181" s="6" t="inlineStr"/>
+      <c r="AC181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -17828,6 +18026,7 @@
       <c r="Z182" s="6" t="inlineStr"/>
       <c r="AA182" s="6" t="inlineStr"/>
       <c r="AB182" s="6" t="inlineStr"/>
+      <c r="AC182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -17906,6 +18105,7 @@
       <c r="Z183" s="6" t="inlineStr"/>
       <c r="AA183" s="6" t="inlineStr"/>
       <c r="AB183" s="6" t="inlineStr"/>
+      <c r="AC183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -18004,6 +18204,7 @@
       </c>
       <c r="AA184" s="6" t="inlineStr"/>
       <c r="AB184" s="6" t="inlineStr"/>
+      <c r="AC184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -18086,6 +18287,7 @@
       </c>
       <c r="AA185" s="6" t="inlineStr"/>
       <c r="AB185" s="6" t="inlineStr"/>
+      <c r="AC185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
@@ -18172,6 +18374,7 @@
       <c r="Z186" s="6" t="inlineStr"/>
       <c r="AA186" s="6" t="inlineStr"/>
       <c r="AB186" s="6" t="inlineStr"/>
+      <c r="AC186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -18258,6 +18461,7 @@
       <c r="Z187" s="6" t="inlineStr"/>
       <c r="AA187" s="6" t="inlineStr"/>
       <c r="AB187" s="6" t="inlineStr"/>
+      <c r="AC187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -18347,7 +18551,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB188" s="6" t="inlineStr"/>
+      <c r="AB188" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4QAqRXhpZgAASUkqAAgAAAABADEBAgAHAAAAGgAAAAAAAABQaWNhc2EAAP/bAIQAAwICDQoICggNDgoICAgKCAgICAgKCAgICAgICAkICAoICAgICAgICAgICAgICgoICAgNCQkICA0QCggNCAgKCAEDBAQGBQYKBgYKDQ0LDg8NDQ8NDQ8PDQ0PDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDw0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0N/8AAEQgAWABYAwERAAIRAQMRAf/EABwAAAEEAwEAAAAAAAAAAAAAAAUDBgcIAAEEAv/EADgQAAIBAgMFBQYFAwUAAAAAAAECAwARBBIhBRMxQVEGByJhcQgUMoGRoSNCUrHBk8LRFUNyc4P/xAAbAQADAQEBAQEAAAAAAAAAAAADBAUCAQYAB//EAC4RAAICAQMDAgUCBwAAAAAAAAABAgMRBBIhEzFBBSIUUWFx0QbhFSNCkaGxwf/aAAwDAQACEQMRAD8As4I6ouXgjYNiKs7jWDe7rO8+UTDFXHPJraCe0faGLDRmaZ0gjGmaRgoLWJCrcjMxANgtyaDO1RWZMNXTKbwkQ1P7YuAEmQDEOl7GURqF5eIK0isVNzyvp8OoqY/UIZ4TKkfTJNcyWSY9h7cjxEQmidJ4WuFkiYMhKmzC45qQQQbEEWIBpyF8ZrMXwJT08q3tkuTuyV1zOKJm7oTsDKJ5ZaE7DagJsKy7TewMmKqG8k7TBHXN53aehHWN5vYaMVc6hpRKm+3dtFwMBD/sye9yN4QfxYtwqWci48Er6Ai9vKpOtm+F4Lnp8ViT88FS1jqSVsFs/Ya2gxXHwk3iT3SVVOuWSTfq5HTMsSA6akDjTujniUl44f8Av8E/XRzGL+6LS5afdpMUDRoUrA8YCbmgO3AeNbEHal5XB1WOj3ere8g7Tfu9Z3n2037vXN5raabD0PqGlAq77dHZqaTDYSVFaTDQPiDPkQuYnZEMcjsqkxw5UlVmYqofdAnMyXn6uTaT8FjQRj7l54/t+SmkOHJ8/IVMcyrtLbexN2WlX3nFEFcNMiRo3gtLLHK17cZLwDOpvlH435vym00+W19gOsUXCMfOc/ZfuWiMdMO0mKrIm6UCVw1CoRaOlJ34Go1Hj3ak5XjUah4GOvTdU8ntMMdZ6prYzMlY6prYwL2y7VxYPDvipmyQxWzEKzsSzBUVEQFnZmIACjzNgCRzqhI1OTwirvfP7V0OJwM+CgjxAfEWhaXEJCsYhLfikKs0j52QFVzILZiTYqAQWybi0ihRRtmpS8FZcOmU5tCPlcelgP2qNZGbzHBbi4r3Jlo/Z6788Ph8GMHOxhZZXMUm7dozHLZvxWTOwcSFxmKKoj3d2uGNM07q47WxO+vqz3RLH4XGq6LIhWSOQB0dCGR1YXVlYXDKRqCONDncCjU1wzZFJWXjcKvApHhqmW6rA/XSEcJsQtU6Wocuwd7YhRhXs3qDx/TMrnxCNKsYnfH3k+4YTfBRJPI27gRr5M1izPJlIYxxqLkKVLMUXMmbMuq7N7CRpyylfeF3h4vHtmmkZkU3SCMZIENrDJEOLngGcu/iIzWNqZU12Q7CtRQy5uzzAkHVr625HoCOIHAfXnX0pKOU+52PPIphdkHpS6tyaaCkGy7UCcxuqJL3dV3wSYNBh2TfYYFmVR4ZYi7ZnyN8LAsWbI4F2Y+NLmp9rz2G+mm8lotj41ZY0lQ5kkVXRuF1YXFwdQeRB1BuOVeeuv2vAeFWB07H2Vc0mpOcj62e1cEi9nuzF7dK9j6b6V1eWea1WrwRtv6lvUDnQM39DeoNKkrd7WGO/Gwyn4VilZf+TuA32jSqujnug39Tm3bIhfYgU+PjlK8OIDG2bzAOhHQnoL2tND+r5ANRPjajjxMq524GxIt6aW+X8UhfP3tBK1iKN4Yre1LbseQ6jkJwwrfhSttjTG4LgKYbCLS25+A8WWc7jwDgYxyVpVH9Vm/urzesl/N5HWntJx2BhBpVX06uMpLJB1U2ShsyEBBav2LRVxhUtp4+2TcuSsv+oV+HObP0noGHH1jqM10SmftJ9szJtSVPy4dY4E15BBI59TJI/wAgOle39Pqxp4v58kfUL34I22T2syA8wVOmliwDBc3PKL5rA6kCrVMtkWSprLBw7QMTe+pJJPUnU/U1PlDLyx2LOuDbbdaXcEGjLAah2kTY87UGdUZdxiFnIVwmNJ50o61Ea+paTuN7SRps5CzJGI5JUkaRlRc5cyDViBrG6fQ9K8d6lCS1HHlIrVLdWSHJ3+YeH4WbEOBcCEXS/IGRrKBfiVz2B4HhTWltlT7mhGeglc+MJfU529rCc2CJDCo4588zE35G8QUW0tkb16VJ/qfXVRUaVCK85Tl/2OP8g4fpzTvLslJ/bC/Ixm7ci4te2ua662tpl8duPG/KvvgZML8TFDV2j36wpZzLDuxYOEO8cnMyvkSN2dreDgptZr2FH/hvHKeQfxazxgqx3sbe3uNxUv6pXGnDwHJpzt4ederprVdUYfJEW2e6bYy2GVit72004E8D99POiivYLw7OJXMDe1rjha/Tr59K1KvjKOqXIrDCf40sR9Rcfek5QwwqkHMFJYD0peSwHrfIeijKsQdCpZSOjKbEfKlXHPJSQ6tlsd2vQvJ9li/zU7UV5Y9VLjgK4aep8qh6FgUixtKyrXkPG1og3anefiZkeNnAjkTduojjAKn4tctwSPCbEaHQA61+hrTwTykfn7uk+GBuzeFviIb8N5Hw6BwT14AX10HpRmZj3ENmyZsTCSMyb6IurahkEitJm8sgbNflc0O1ZXAePcGYTBWYg65B9TyPz40aEfmKyymHdjS8BYNoRl1HncEcD04+hru4+wd+JOvDLzte514X+VAsDx7CmHbUUjbHgPHvkeW1MaJHeUDKskryKpNyqyEtYngSAAOH71Pri17X4KMpZ5QT2VP+G6/pyyg9DmWJgPJhIpP/AFrQ7odmGrl4OnD4ylHAaU8HbHiqBKGA8bOCugxQ8z6cB9RrXucniAp2bxY3g62ktrzMT2+/8fPsjcHyZszSQn9MWI15DNh5EW/S7uq+rDqKBPkY7Z+wImk1P0+gH+aIuwp3OvAYsjUaVzIVIIw4i5oDeTaCED3NahHc+TalgdOHxgaNjw3Yj8F73HwFxe1gCVBWxsZB0JpC2rZIdhPcgz2elvvB1if7FW/tpWaeBis9RzUBoKmKjE0FwbDRmQFGRw6V65HlDu2TiAssbHRQ6Fj0XMM32vXGzsXhhTCOBFOeLHcRAXGis5lZvQHDon/oKF5GpPhg3Cm4I43djc+gXT6ftVbS1xcXlE6csPgV3FjWbdNHwGhPg6IhS/wqfkJ1MBPDvTUKklgx1BxdkI88xTk8cq26sylYwfSUo3kVB5VP1dWU8DVFmJLIU2WchlHSN/uVUH0JINQ3yiljY3k8x4+s7DKsR7ONrLiEVh//2Q==</t>
+        </is>
+      </c>
+      <c r="AC188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -18430,6 +18639,7 @@
       <c r="Z189" s="6" t="inlineStr"/>
       <c r="AA189" s="6" t="inlineStr"/>
       <c r="AB189" s="6" t="inlineStr"/>
+      <c r="AC189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -18512,6 +18722,7 @@
       <c r="Z190" s="6" t="inlineStr"/>
       <c r="AA190" s="6" t="inlineStr"/>
       <c r="AB190" s="6" t="inlineStr"/>
+      <c r="AC190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -18590,6 +18801,7 @@
       <c r="Z191" s="6" t="inlineStr"/>
       <c r="AA191" s="6" t="inlineStr"/>
       <c r="AB191" s="6" t="inlineStr"/>
+      <c r="AC191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
@@ -18668,6 +18880,7 @@
       <c r="Z192" s="6" t="inlineStr"/>
       <c r="AA192" s="6" t="inlineStr"/>
       <c r="AB192" s="6" t="inlineStr"/>
+      <c r="AC192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -18758,6 +18971,7 @@
       <c r="Z193" s="6" t="inlineStr"/>
       <c r="AA193" s="6" t="inlineStr"/>
       <c r="AB193" s="6" t="inlineStr"/>
+      <c r="AC193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
@@ -18836,6 +19050,7 @@
       <c r="Z194" s="6" t="inlineStr"/>
       <c r="AA194" s="6" t="inlineStr"/>
       <c r="AB194" s="6" t="inlineStr"/>
+      <c r="AC194" s="6" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -18930,6 +19145,7 @@
       <c r="Z195" s="6" t="inlineStr"/>
       <c r="AA195" s="6" t="inlineStr"/>
       <c r="AB195" s="6" t="inlineStr"/>
+      <c r="AC195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -19008,6 +19224,7 @@
       <c r="Z196" s="6" t="inlineStr"/>
       <c r="AA196" s="6" t="inlineStr"/>
       <c r="AB196" s="6" t="inlineStr"/>
+      <c r="AC196" s="6" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -19090,6 +19307,7 @@
       <c r="Z197" s="6" t="inlineStr"/>
       <c r="AA197" s="6" t="inlineStr"/>
       <c r="AB197" s="6" t="inlineStr"/>
+      <c r="AC197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
@@ -19168,6 +19386,7 @@
       <c r="Z198" s="6" t="inlineStr"/>
       <c r="AA198" s="6" t="inlineStr"/>
       <c r="AB198" s="6" t="inlineStr"/>
+      <c r="AC198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -19246,6 +19465,7 @@
       <c r="Z199" s="6" t="inlineStr"/>
       <c r="AA199" s="6" t="inlineStr"/>
       <c r="AB199" s="6" t="inlineStr"/>
+      <c r="AC199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
@@ -19336,6 +19556,7 @@
       <c r="Z200" s="6" t="inlineStr"/>
       <c r="AA200" s="6" t="inlineStr"/>
       <c r="AB200" s="6" t="inlineStr"/>
+      <c r="AC200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -19426,6 +19647,7 @@
       <c r="Z201" s="6" t="inlineStr"/>
       <c r="AA201" s="6" t="inlineStr"/>
       <c r="AB201" s="6" t="inlineStr"/>
+      <c r="AC201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
@@ -19520,6 +19742,7 @@
       <c r="Z202" s="6" t="inlineStr"/>
       <c r="AA202" s="6" t="inlineStr"/>
       <c r="AB202" s="6" t="inlineStr"/>
+      <c r="AC202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -19606,6 +19829,7 @@
       <c r="Z203" s="6" t="inlineStr"/>
       <c r="AA203" s="6" t="inlineStr"/>
       <c r="AB203" s="6" t="inlineStr"/>
+      <c r="AC203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -19696,6 +19920,7 @@
       <c r="Z204" s="6" t="inlineStr"/>
       <c r="AA204" s="6" t="inlineStr"/>
       <c r="AB204" s="6" t="inlineStr"/>
+      <c r="AC204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -19770,6 +19995,7 @@
       <c r="Z205" s="6" t="inlineStr"/>
       <c r="AA205" s="6" t="inlineStr"/>
       <c r="AB205" s="6" t="inlineStr"/>
+      <c r="AC205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
@@ -19848,6 +20074,7 @@
       <c r="Z206" s="6" t="inlineStr"/>
       <c r="AA206" s="6" t="inlineStr"/>
       <c r="AB206" s="6" t="inlineStr"/>
+      <c r="AC206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -19938,6 +20165,7 @@
       <c r="Z207" s="6" t="inlineStr"/>
       <c r="AA207" s="6" t="inlineStr"/>
       <c r="AB207" s="6" t="inlineStr"/>
+      <c r="AC207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
@@ -20028,6 +20256,7 @@
       <c r="Z208" s="6" t="inlineStr"/>
       <c r="AA208" s="6" t="inlineStr"/>
       <c r="AB208" s="6" t="inlineStr"/>
+      <c r="AC208" s="6" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -20106,6 +20335,7 @@
       </c>
       <c r="AA209" s="6" t="inlineStr"/>
       <c r="AB209" s="6" t="inlineStr"/>
+      <c r="AC209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -20192,6 +20422,7 @@
       <c r="Z210" s="6" t="inlineStr"/>
       <c r="AA210" s="6" t="inlineStr"/>
       <c r="AB210" s="6" t="inlineStr"/>
+      <c r="AC210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -20278,6 +20509,7 @@
       <c r="Z211" s="6" t="inlineStr"/>
       <c r="AA211" s="6" t="inlineStr"/>
       <c r="AB211" s="6" t="inlineStr"/>
+      <c r="AC211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
@@ -20368,6 +20600,7 @@
       <c r="Z212" s="6" t="inlineStr"/>
       <c r="AA212" s="6" t="inlineStr"/>
       <c r="AB212" s="6" t="inlineStr"/>
+      <c r="AC212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -20458,6 +20691,7 @@
       <c r="Z213" s="6" t="inlineStr"/>
       <c r="AA213" s="6" t="inlineStr"/>
       <c r="AB213" s="6" t="inlineStr"/>
+      <c r="AC213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -20552,6 +20786,7 @@
       <c r="Z214" s="6" t="inlineStr"/>
       <c r="AA214" s="6" t="inlineStr"/>
       <c r="AB214" s="6" t="inlineStr"/>
+      <c r="AC214" s="6" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -20642,6 +20877,7 @@
       <c r="Z215" s="6" t="inlineStr"/>
       <c r="AA215" s="6" t="inlineStr"/>
       <c r="AB215" s="6" t="inlineStr"/>
+      <c r="AC215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -20716,6 +20952,7 @@
       <c r="Z216" s="6" t="inlineStr"/>
       <c r="AA216" s="6" t="inlineStr"/>
       <c r="AB216" s="6" t="inlineStr"/>
+      <c r="AC216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -20802,6 +21039,7 @@
       <c r="Z217" s="6" t="inlineStr"/>
       <c r="AA217" s="6" t="inlineStr"/>
       <c r="AB217" s="6" t="inlineStr"/>
+      <c r="AC217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -20896,6 +21134,7 @@
       <c r="Z218" s="6" t="inlineStr"/>
       <c r="AA218" s="6" t="inlineStr"/>
       <c r="AB218" s="6" t="inlineStr"/>
+      <c r="AC218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -20982,6 +21221,7 @@
       <c r="Z219" s="6" t="inlineStr"/>
       <c r="AA219" s="6" t="inlineStr"/>
       <c r="AB219" s="6" t="inlineStr"/>
+      <c r="AC219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
@@ -21060,6 +21300,7 @@
       <c r="Z220" s="6" t="inlineStr"/>
       <c r="AA220" s="6" t="inlineStr"/>
       <c r="AB220" s="6" t="inlineStr"/>
+      <c r="AC220" s="6" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -21146,6 +21387,7 @@
       <c r="Z221" s="6" t="inlineStr"/>
       <c r="AA221" s="6" t="inlineStr"/>
       <c r="AB221" s="6" t="inlineStr"/>
+      <c r="AC221" s="6" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
@@ -21236,6 +21478,7 @@
       <c r="Z222" s="6" t="inlineStr"/>
       <c r="AA222" s="6" t="inlineStr"/>
       <c r="AB222" s="6" t="inlineStr"/>
+      <c r="AC222" s="6" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -21326,6 +21569,7 @@
       <c r="Z223" s="6" t="inlineStr"/>
       <c r="AA223" s="6" t="inlineStr"/>
       <c r="AB223" s="6" t="inlineStr"/>
+      <c r="AC223" s="6" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -21412,6 +21656,7 @@
       <c r="Z224" s="6" t="inlineStr"/>
       <c r="AA224" s="6" t="inlineStr"/>
       <c r="AB224" s="6" t="inlineStr"/>
+      <c r="AC224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -21502,6 +21747,7 @@
       <c r="Z225" s="6" t="inlineStr"/>
       <c r="AA225" s="6" t="inlineStr"/>
       <c r="AB225" s="6" t="inlineStr"/>
+      <c r="AC225" s="6" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
@@ -21588,6 +21834,7 @@
       <c r="Z226" s="6" t="inlineStr"/>
       <c r="AA226" s="6" t="inlineStr"/>
       <c r="AB226" s="6" t="inlineStr"/>
+      <c r="AC226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -21674,6 +21921,7 @@
       <c r="Z227" s="6" t="inlineStr"/>
       <c r="AA227" s="6" t="inlineStr"/>
       <c r="AB227" s="6" t="inlineStr"/>
+      <c r="AC227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -21764,6 +22012,7 @@
       <c r="Z228" s="6" t="inlineStr"/>
       <c r="AA228" s="6" t="inlineStr"/>
       <c r="AB228" s="6" t="inlineStr"/>
+      <c r="AC228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -21850,6 +22099,7 @@
       <c r="Z229" s="6" t="inlineStr"/>
       <c r="AA229" s="6" t="inlineStr"/>
       <c r="AB229" s="6" t="inlineStr"/>
+      <c r="AC229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -21940,6 +22190,7 @@
       <c r="Z230" s="6" t="inlineStr"/>
       <c r="AA230" s="6" t="inlineStr"/>
       <c r="AB230" s="6" t="inlineStr"/>
+      <c r="AC230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -22025,7 +22276,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB231" s="6" t="inlineStr"/>
+      <c r="AB231" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAg8CAgMLDQoKDQ8NBQgKDRAKCwoKDhELDgoLDA4KDgsKCAsLDQgJDQsIChAIDQgKDQ0NCgoNDQoKDQoNDwgBAwQEBgUGCgYGCg8NCw4SDxAPDxAPDRAPEBAQEA8PDw8PDw4ODQ8NDg0PDw8PDQ0PDw4NDQ0NDQ8NDQ0NDw0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAbAAADAQEBAQEAAAAAAAAAAAAHCAkGBQQDAv/EAEgQAAIBAgQEAgUHBgsJAAAAAAECAwQRBQYSIQAHEzEIURQiMkFhFSMzQnGBoVJ2kbG10QkWJEV1gpKywdLwNVNVhZOjpbPh/8QAGwEBAQEBAQEBAQAAAAAAAAAABQYEAwECBwD/xAA4EQABAwIEAgkCBAUFAAAAAAABAAIDBBESITFBBVETImFxgZGxwfAy4UJSodEUIzPC8QZDYnKy/9oADAMBAAIRAxEAPwAgcwstTYHiOTn9LqKhvlhQiTdILq6MrbaY19ZwhS5PZj2NiAK6B7TFeRz+tocFvpd+Vrc/0zWumcAXENDctRfmOZKPfLbHhmXMdRKoIBy7ApDAgh1qptSG49pdQuPiPPglrcNx82TRNyCvbWx652Px4rKS9gp+pyKGWNeGWhxjEKl2piWeeWVj16kXd2LsfVnAAJYnSAAL2AAHDDGDdTklFE7Mjt1O/isdmvkRSZQmoulSufmahrCSolLEKAEGqdmG7atSqSACdlViuSqAyBBtmcuzbLP9CtVHRRRkuaM9Myd++/2Q95VZHjxTMNPIYdDOKmwLTgBtfq3C1JaVWsdUMje0ACTYMJmKsbNL0ErcjkMja45Hs+yo38MZAzp4jmNc8yDzG4O9+9FHKnh0oscoUkelBYTTAkSTqDaRhfSJgu4AuNNr3tcd6OkAdH1trjcaG3w7oCrooTISG62OvPusERuX3LGn5e1OJNTwiMy9PXZpGB0F9OzuwFuo/sgXvvewt4QBe3au8cLYz1Ra9kVstn5xeAarVPU6DOY80Pl6ixuniFppcexJ1LCwSJql/njf3HfSPrbEbdz4nYXEjXO3nqfZaXi7bbIC8sOWMWPZFR3M3rVtVcLPMg+bqZ0XZZRY27/lHdrnfjVSxNMeZOZP4nDc8j/lZJScWg0Gw5LdZv5ePQ4pkoNXVT68ejiBbo3QtBOeqloB86ukgatS2Y+qfdsrqdzHRdcm7rZ2/K7PQfssNPLixZbe4Rw5Z5QORszYlF6RPMJMJEx6/SJD9cqSDFDH7Q03vq9kb8EOjIkJcbk93MJlruqANB9128STS7cV0As1Ts5uUjnM/wAQdRljNWZga5ljjxWrjW6wKAqzOqoPmbnSAFuSzG25JPEyaqrfUPZG8kXNhZuViez1X7hDwrg9Nw+GoqomAljC4lz8yWg/n1J2HgEHsR8asjYrSEzVEoUtYhYY2XUNJZG0K4exIsbA+8GwsoIKs2L5Mx3eoCiK3iHBXAspqZw/5C4HcQ51yOeQPIr2U3i8WmkN6msYBLJqVAoIYOvsR9QorgE9i4FyTYA4TTVlrB3cMu/5uvoV3C34WmNrL/U4CUnkcrkZjsIWswXn5UYjhUXSrW0b26QjAG9yt+nquL/WYt+USeDjUVMH8vEW9lh+y/RqThHB6mMSxRtkH5ruN+/rWB7LC3JMP4Tc5z5yp80GedpdDUoQMEGm4mLG6opOuydyfY2tc3S4VNLIH9K7Fa1tPYBQ3+sKGlpHQimjDLh17Ys9Lak6Z6W1TQ5d+mTj2qUjToN13Jmm5iYvmOaojldxj1bGCKmrjsgkAChYqhEAAt2UcGxxBzzmR3Eha3O6maEHJ/k3TZw5e000sTs7V+IAkVFSgslbOi+pHMqCyqo2UXIubkklGloY3sub6n8ThueRR08zmusLaDYckUOYT6sU5ffDNNN+MNQP8eEuIHE6I8n/ANrlgpm2xd3uEXMNa+f0/N9/wqV/fwJKev8AOYTTBkPnNcjO2YkyvguIzSMFSOF5HZjYBFBZmJOwAAJvxTQu6qDlbmovc6+aZ5oZ5xWq6QjWSpd44xtpRje7gGxqJd5Ha/tMRchRx0axsYOEWvmV2mqJajCJnl2EWbc3sBlYcuSxGHB8cmREW92AAAv+v9/HjnAC5XJrSTYLaZr5YS4LFD/J5t6dS3zchAa3rDUEtsbn4fdxwZURu/EPMLS+mkb+E+RXO5aZ9blXmulmEUU6dninGqN12uh2uktvZm0kod7OupG6PiZIOuAe9e09XPTEmCRzCdcJIVfOQ2LUua+XmG1dFDHFHURLIQiIhDi6tHIEJHWhbXGw1GxBsSLcfLYY4wejaBfkF5PW1FS4Gokc8jTESfK6MuWzedPt4FqVsp1lMuLZ80fnHW/3kP8Ajxji+taX/Qg14fGtyppP6UxUf+RqeGqXJlu0+pRlT9XgPQL259xNY6nJpMkR05jpGOmWN7C0guQjsQo1AaiLXIF7kcfNUDZpNtRuOR5LlE9pNm+h90Z8GnEmfKexBvl2c7b9qmH9/Abz18+3+1MgafNilw8f2ZBhXIvEYtVuvWU8Pu3UOJXTf3Okcin4E8VdGMQQdScKldVj5UZQR3nZf1n8bj9HlxrOa4aJzfBHybSvw9pnQE3727ef4n9XEhxWRzpOjByCs+ExtZF0pGZTeZsyXGMEluFCiM3LWAAt3JPu99+J4xEG4VC2bFkVLrnnl+LDc7O0BLRyKxDqjiJmVks0cpQRyBlYjXG7r6vffi44cZOjwybefjyUJxJsfSY49Dry8OaO/wDBwc6TlnPWIYVIx6dTrnp739WoRbyRjYgCaNWk7gaoiNzJwkUQqgZZ+nT7eAasJamWPoMSXBlzYzsqD+MVWbsQotaPff3d9+MUTHF+Qy57LS9zQzMpZuUHOWlyxkMRSVcKOMUxNirkg6Xrp5FOyn2lZW+/hGCeINsXtGZ1PasU7HOcLA6D0C1GNcsBBR4OfSXdZcRpYvoqUAB22kUpTjURYEBtSG9yrWFtVTTBg13toPZHRyXIRy5dZdGTMfpYQ7OGwSqctIF1XSemWw0qqqjB7lVUAlVNtuJxzTiOfh4hUIdk0W+WKSL+EnzwKjOWTqEWOiOarkF+1/m47j3Aj0ixI78WtEMLFNVRxOSS+hejvAfOpZvut+vZRx3IsvkG6ZnkJlmqzBheHCK0KXjfqQyVQlcFixN4q2nUItkHROtW1G5QLZ5moljEjw9xvysFV0sMhjYWNFtySfa1k2vNDAmzLy1oIpbEmWJZexB94I1qwuHCkMVO4B79gcbInhxuQngx0jXNGRSK+Jzk9JkDA6SpMkrBaiFLSSyy7FAjOvUZiuuQI3SBCICQuw3doatkkpawAXG3YgOIUcjIcTiTY79qBuQ86tlHPmX6lCQ0OIQzLY22VhqW9j9IupPZOzduKBTKvFy2xgY/hOGSqbh4UcEdiCLhh8G7jf38B1gzSlKsBmzI0fMlsz9czHTjlRCpimlgYIFjIUPC6OLFmNw4O/fYWIz6QZ+/6FIixYbpZ+W3JWDOWUWmd6wM2KYkp6VdWwpZK2eMWjiqUjBsouQgLG7G5Ju3SwjB4nYc0bUPwuHcPRbLlPiTTcusBjdSBFj1KIr7Xh6u1h/u421xrtbQIwNhuzxaSN0zmsNzqe/5qsENNJHEx7hYHId3dy5Jl8Me3MnAx55cxP8ACpw//NxFE9Y/OSfcM2qXPjdUy+KXNbFtQMNKEO4CoI1jaK5AvplWqe4J9sC/qi1vS/0wVMVH12S64zjPobm/1Vb+0T2/AcdXrxiop4J8fSo5ZUIuNoEt7tv9H7uPz+rYenc4r9FpHj+HY1uyL/MTHRhOB1atJCNcQtr7jcksPW7D1Qvqg6h7RvYeOZaOxFytsMbpHl0d7JOPG7n9MZ5V4dGrBtdZELg3Hqgud/6lvtPHbhEJE5cRawR3G5gIcA1JCSjB5fkvMeHm4A6yG58r77e/a4t7+wBPFkoNXE8IGJjEeU2XgAQY4hEVN7gqLA7km0ilXDXsysriwbgWuulKWy02H/S5t/OWp/uQ8D/7oSDfoKAPINr8r4v6Yxf9pVXFLTiwRVV9XgPQL1Ujaq3Cbf8AEqXsrILCVBbS3rALsOibCG3RLGSJtU9TOu77EfodO46HLZWfGx/IBP5huD+o1/7D6x1tHJgKY9LnBlkeeV8bP6KrCf8ANxxkbaTz9kAMwD83Uo/Gfjejn/nLe4Wrcj7NR2+3UCp+K+XFzSkCIKZqQelKWavqPTdX2k/f/wDO3Hy83X00WTH+Cvmw2TauvhYFo+oCLd01X3HmhN7rtYm4ve3E9xGIEgqk4bK4At2TkZgpKXMOFvN1o0NiXA0qxNvyW3Dn8oLqPBbi4CyqaauexuEHLtGinfz8z7/GzPTRKCIqdmRb33JtdyO1gNIUWuBqN/WsH+Hw4GYt3KM4nUGWXDsPdZbI+Tv48Z/wantfqvIoA1dxE7ADSQbkqLC432JtwmUOrceGTIEXLbl5gUMJlZeikhed+rIzMAdTvpUGw0ooCKqoqqFAHA9alKVdjC49dRnD85an/wBcHArv6rUiz+mUvfh/IHKqLcf7Zxn9p1XFRAOqiKn6/AegXSxrE0wzAo+lFUs3p1PJeYRi+hxpTX12OpthcgXZnd3LuzPjNNFAw4MRPb+9/wDOpzXtRxGesc3pWtAHLS/dYfYZCwAANeSqyQ58wMTJFrkwTFGQr6zRok2Hhog5W5WcyRO1tIvTx+3sUBeS5xtkOXuk2mwAO+fzzUsvHfga0/PGVQfXE1WZfa9g1LSRblQrXSdnupNi5jP0S2s6djg0Ai2in5ntLiQlmmX+UyDyc/u46OFl8BGnwq0nWxrGCN2UxEqfepJW/wBl/wBG3nxP8S2VDwy2adrE8rdbBJGEYU9O1zb9P2Dv93ALb7qhIFlP/nblpcvZrmkUuVlkO7AAXUBSV7MQRY3K2ubgkcV1ATgDXbKO4gyz8Q3WRyljzZJz5l+pQnVDXQzC3v0MGI7/AF1DIQdiCb7HhB2SOardcms8ekZewtigt0lto9y/VAB7gLptYja3bsC6mMyDJIwuDF+sVrpcTq8zSRPEQmNyxhGBCsvShkDdVbssh6hFzG4sFGlbbjh/RyBr23v5jx/e634C5l2m3oUqnKLPk2BZDZVoDKoxbFCGE8CbmunLLpc6vm3Lpq0gHSCNjwzCCW5tPmPBHSkg6jQc+SIVRVMMuU+og2qqcHSdQuJQDZiqkqfcSq3HuHGIyEjNeuY0AEcwmVpcIFTimCz6iDHRVsFtrFZnpWJJ73X0YCwP1jfjZwalbLI6Z+Ybpyv9vdZeLVBia2NpzPp91OL+FBzYKnP2UYF7wYfUTPt2NTLGFF7ecHa+wtf21vTzGwCIhF/nJItPLoLG/wBX9J/1f8eDHJAI/wDhiw8R81ssuhB6lBUBvgVZNj8CRp+N9Q3tYSrGKMtPNUFCcMjXDkqH4aVxzBJd/V0sn9YbH/pnbv7Q+G4scdin3yBwyU/PGHUxjE8MiS3zZuwA9k6WBQnzF0Om/bSbWYE01KzCCSpaueHOAGyA9FWCgxmhdt1WeNm2v6oYatvf6t9rfdxvcigrGeGuA0WQcLQ76I0UfYVDAfdew+AB9/HC2a1bIi02IiGPEI7AXl6osLXICxtfbcjTGPO1/cNhOIx4HMlHOx9knRuuHMStclJepy1/51jH7SquFIX2sO70WCVt8/mWS1tS4rck4fbSNdXQqLW0jXPGotpJGgah2JFuxPAzOsQ3mbeZsu8zgI8ewsfdMxBiPyflmaQ/VhkY2v2XUbdr32A7d/Pi9oqUU0AjGuZJ7f8ACjKqpNTPj2yAHYpw+O7IXyXVZjnkF5JcMwhla17lq6oE6Ag30xKmHDUboupF2aVdXxO0HPut55rbC43HjfyySHYq1yp92ogfYP38FvSLUwHhAtQY3UzbG94Tf6gOm0g8r3UdTsFDe9AHKq8+ql6MauVEYsNanyniTllQmFQNBuFGo3k3UDUqt5G+jfawXDTsubuSkry0WCnh4tsSjXOlNFHsVVr3vfvbU199TtuN7kBy19Qs7EDbNAVBBdkgLBVdQ6bXvZfx7ffx2usgCr/4Msx/L/IXKMpJ3ooYSWvcvBqp2JvuSzREaveLcchqtA0RGxmb0WvpT51JX+0xX8NV7fAcYuIMD6d4Owv5ZrVSuwytPh5pXOTuK+i8te/88Yt+0anggTFrgAdm+gW8RhzSTzPqihnun+ScqQN3IxfDCSQASTX092OkAXYkk2UDfYDjV/CuaWuOzmf+gjZ6gPjc0cj6JmquLo4Vby0X+wEEj77Hj9JIysoGMoO+KblCOb+RqaEfSKkrp8bRkFDsbxyN0QykHa7LaRUZODoA8lvJaWVHRjGdyorYqRU0lFYH6Je/mQB+JBP3/ZxPv0FlSN3Xf5b8z5eWk9QYhEwYbrMhdfK/quh+7VY7bbcY5IWyarVFO6L6UZsW8d+IYvgLwj0OK4A1RQuzjzsZ55U9bfvEbX2N9+P6KlZHoustZJIM7DuS74vVtX4pUOzMzFizM7FmLH6zMxLMx/KJJ8+NJFiseq++F4Z8o1lAF3ZpQth31dRQNrdjrSx8w3ltzK9VQfCvWfxV5G5bjubR4nVf9wioUf1TK23wPkePk6LsxGvFsUC00TMPZAYA9yw9k2/IBAJb3gEC524/j1mkLr9JBQA8P9J8ocrI9/51xb9oVPAb4utpsPQJBkvV8T6r/9k=</t>
+        </is>
+      </c>
+      <c r="AC231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -22104,6 +22360,7 @@
       <c r="Z232" s="6" t="inlineStr"/>
       <c r="AA232" s="6" t="inlineStr"/>
       <c r="AB232" s="6" t="inlineStr"/>
+      <c r="AC232" s="6" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -22198,6 +22455,7 @@
       <c r="Z233" s="6" t="inlineStr"/>
       <c r="AA233" s="6" t="inlineStr"/>
       <c r="AB233" s="6" t="inlineStr"/>
+      <c r="AC233" s="6" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
@@ -22280,6 +22538,7 @@
       <c r="Z234" s="6" t="inlineStr"/>
       <c r="AA234" s="6" t="inlineStr"/>
       <c r="AB234" s="6" t="inlineStr"/>
+      <c r="AC234" s="6" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -22358,6 +22617,7 @@
       <c r="Z235" s="6" t="inlineStr"/>
       <c r="AA235" s="6" t="inlineStr"/>
       <c r="AB235" s="6" t="inlineStr"/>
+      <c r="AC235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
@@ -22440,6 +22700,7 @@
       <c r="Z236" s="6" t="inlineStr"/>
       <c r="AA236" s="6" t="inlineStr"/>
       <c r="AB236" s="6" t="inlineStr"/>
+      <c r="AC236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -22518,6 +22779,7 @@
       <c r="Z237" s="6" t="inlineStr"/>
       <c r="AA237" s="6" t="inlineStr"/>
       <c r="AB237" s="6" t="inlineStr"/>
+      <c r="AC237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -22600,6 +22862,7 @@
       <c r="Z238" s="6" t="inlineStr"/>
       <c r="AA238" s="6" t="inlineStr"/>
       <c r="AB238" s="6" t="inlineStr"/>
+      <c r="AC238" s="6" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -22678,6 +22941,7 @@
       <c r="Z239" s="6" t="inlineStr"/>
       <c r="AA239" s="6" t="inlineStr"/>
       <c r="AB239" s="6" t="inlineStr"/>
+      <c r="AC239" s="6" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
@@ -22756,6 +23020,7 @@
       <c r="Z240" s="6" t="inlineStr"/>
       <c r="AA240" s="6" t="inlineStr"/>
       <c r="AB240" s="6" t="inlineStr"/>
+      <c r="AC240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -22846,6 +23111,7 @@
       <c r="Z241" s="6" t="inlineStr"/>
       <c r="AA241" s="6" t="inlineStr"/>
       <c r="AB241" s="6" t="inlineStr"/>
+      <c r="AC241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -22939,7 +23205,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB242" s="6" t="inlineStr"/>
+      <c r="AB242" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4QAqRXhpZgAASUkqAAgAAAABADEBAgAHAAAAGgAAAAAAAABQaWNhc2EAAP/bAIQAAwICCAYICAgICAsICAgNCQgIBwoKBggPCAgHCAcICAgHCAgOCAkIBggHBwgICwcRBxQKCQkHBw0NCgkNCAgVCAEDBAQGBQYKBgYKFA4IDQ0QEAoQFA4LCQ8LEQkKDQ4PDg0UCgsLDw0JCwkQFAoNCAoPCg0ICQ8KDg0ICwgKDhAI/8AAEQgAWABYAwERAAIRAQMRAf/EABsAAQEAAwEBAQAAAAAAAAAAAAAEBgcIAQUJ/8QALhAAAgEDAgUDBAAHAAAAAAAAAQIDAAQRBRITFSEyUQYHQQgUIjEjQkNTYXGj/8QAGwEBAAIDAQEAAAAAAAAAAAAAAAQFAgMGBwH/xAAzEQACAQIEBAMGBQUAAAAAAAAAAQIDEQQSITEiQXHBBRNRBjJhkaHwQnKC0eEUYoGxsv/aAAwDAQACEQMRAD8A/TvT7AMM0BXyxaAcsWgHLFoByxaAcsWgHK1oBytfFAOVr4oBytfFASahYBRmgKtK7RQF1AKAUAoBQCgFAKAUBDqvaaAaV2igLqAUAoBQCgFAKAUAoCLVO00B5pXaKAuoBQCgFAKAUAoBQCgItU7TQHmldooC6gNPe6HsTPq139zHqTWqlEj4IikfqhbL7lmiGW3Dpw+mP2fjocD4tHC0vLdJS1bvdLe2nusnUcSqccrjfX75GAfR9rbyy6jxJWcIkBy7M2BvuMn8idvb1/1Vx7SQjCFJpJay5Jco+hJxyVo2Xr2Ogm9cWocLxk2lOJxuJFswWwqh84LNhj06AL1IyufKp+N4GnW8mdaKdk7uUYrik4pJtpObafArtc0rq+hYDEOGdQe9rWd9Fe+2y9X2ducPcz2puNKtWveZtcIWQLGqSxgiZsAiTjSgqAc9mCPFer+H+JU8VUjS8pLTe6ey/Kt+pKpYhSlkcLP9v8FfpT2au7+wjvY9QbdIjyJb7JTllLhY+LxcDey438Lpu7TjrhiPFKdGu6MqSsnZvT52y8vS+vqYzxMYzy5dL/fIzn6ZfW5ureW2kYtJAd6bicmKbJwd35EpKGz4EiD4qt8cwyp1FUitJKz6x6eq+dmR8ZBKSktn2/gkf1g+r6x9pE5+3gY8TaSMx2pAlJweqyTnhbvlXWsv6dYXB+bJcclp+vb5R16maiqVHM/eff8AjXqb0rlysItU7TQHmldooC6gMRi93NMaS7h++hWSxJW6RpFj4W1Fdid+0NGoba0gJVZFkQkPG4Wwfh+JUYT8t2n7ml7625c3yTs2rO2VpvY6crJ232++3ZnNn0IXxmm1V1HQJa4zkdWe8KgnrgkL16dPFdl7VRyworneX0USdi3pG/x7G+Bod4IzZcOIF1M/3Kq/DVlKjg4bcSDJgcIjAtSYwTsJHgs/C8W6UsHHKoSlnz2btqnkak5ZouayuHDFYV+VF8Ny0WKw+ZYi7uuHLdXe/FdWtZa5lq63E1qY19XV0Y9CkZsBuJbbgMkZMqAhScErn9HH6+K9c9nVfGxXwl/yykw9lU021/0ZJ9OE2/Q9ObzGT/1kqH4wrY2qv7uyNVb331NHe6Gtv6X1eaW3G0XMcsqZ6DFyHBGcf0rteLwh+wkQOAwx02Bpx8QwkYVPwtJ/p/eHDfr6EyDVSCUuXb+NDOPo99LlbOW/cfldNw4s/wBm3LKWGeoMk/Ez8ERRmq32hr5qyoLaK16y1+kbdHc1Yqpmll9O50HXJkIh1XtNANK7RQF1Ac6+4H0N6TqVw9yktxZNIWeSKBrYo0jnc0ipPHMY3JydquI+p/CuswntLi8PTVO0ZJaLMpXSXLhlG6/Nd7a2JUMRKKtv8+zX1Nr+1ftNZ+nrb7WzRgpO+WV23vPIQFMkz4UFtqgBQgRQMKqiqLG46tjKnm1nrsuSS9F8Pq3q22aJzcndmZ1AMDDPdz2uh9Q2T2M8ssEbtHIZITCHBhcSAAzJKm1iuD/DzgnBBxiwwGNngqyr00nJJqzu1xK34XF/Xf4GynPJLMvu/Sx9D279ER6PZW9jFI8sdsvDWWXhl3G5mzJw1jTdlviMD/FasXiZYmtKtJJOTu0r2XS7bt1b6nycszbMY96PYe19SLAJ5Zrd7cybJoDbhtsygOjcZJlKFkR+3IaNeuCwaZ4d4nVwDk6aTUrXTzNaPR8Mou/LfZvS+2VOo4bd+zRm3pj07FYW0FrCCIrdEhjB6nZEoUFj/M5AyzfLEn5qurVZVpyqT96TbfVu/wBrka27u7PqVpPhDqvaaAaV2igLqAUAoBQCgFAKAUAoCHVe00A0rtFAXUAoBQCgFAKAUAoBQEOq9poBpXaKAuoBQCgFAKAUAoBQCgIdV7TQEun6gFHWgKuar5oBzVfNAOar5oBzVfNAOar5oBzVfNAOar5oBzVfNAOar5oCXUNQDDAoD//Z</t>
+        </is>
+      </c>
+      <c r="AC242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -23029,7 +23300,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB243" s="6" t="inlineStr"/>
+      <c r="AB243" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAgoOCAgLCgoKCAgICAsICggNCAgJCA0ICAgICAgKCAgICAgICAgICggICAoICAgICgoKCAgNDRYKDggICggBAwQEBgUGCgYGCg4NCg0ODQ0ODQ0NDQ0NDxANDQ0PDQ0NDw0NDQ0NDQ0NDQ4NDw0NDQ0NDQ0NDQ0NDQ0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAABBAMBAQAAAAAAAAAAAAADBQYHCAIECQEA/8QAORAAAgECAwUGAwYFBQAAAAAAAQIDABEEEiEFBjFBUQcTImFxgQgykSNCocHh8BQzQ7HRJCVSY4L/xAAbAQABBQEBAAAAAAAAAAAAAAAAAQIEBQYDB//EACwRAAIBAwICCgMBAQAAAAAAAAABAgMEESExElEFEyJBYYGhsdHhcZHwQjL/2gAMAwEAAhEDEQA/AOYFqeB6BQBiRQB9agBS2Tu+7hiLBVsLnmzEKqqObE+gHMjS7W8D4wchYxW4RFvE2qlg3dMUKqrO5DBr+AKR8puSvC9JxD+r8TV2juRIoBFpQbaKGzagkaMBxAvYEnQ8lJoUkI6bQgSREEgixBsRzBHEHpannICy0ABIoAxIpAFcxUoGIhoAxkioA9w8Qvr/AI9v3+lI2KllknbA2haDJGpctr4Rn/pNHZsoPys2YHQHTna/BtJ6k6EXJYihRwmOnCojRy5CFDEqQScqCUZjcqCiBLWUled7Cm9ZHmdVQqcmeQ71FPkivI0neF5EUIqgrmC5gAqBQIrkZu7J4sbU7iT2GcMo7oY/aLhY/wCILxMGWXxEdG4HTkCbn1vXWL0IlWOHlDQcU84gXFAA3NIAtGlAEJaAM6AF7cfAI057wXQRMTbje4trrYGxBa1wOFq41XhZJNvHilhlo+x9VQqEQBWtwA52P7HSspcTbe56NY0oxjhItLuvswNEGspvyKqdfcG1/wC1Q4uWNyxkop7CdvVuThmQiWCB7/8AUh536X0Ov1p6rVIPSTGuhTqLWKOfXxGbgphtoMkYtDIgmjXXwq11K3N9FdHtropUeZ1VlV6yCk9zz7pa3VCq4x23X4ZEbirAogRWkA15KAF8CgAE0VKAHPQA6tj7Lmjkkzq0ZCZWU8bNYgEA8x621vUWpJSjoWFGnKEu0sFkezPfjAQwxtPOdMq3EcjR5sgBuyqelj0PvWbq0JuTwjd2t1ShBZkXB3V23A+HSSNwYz98G62txzDTiQNfyqHjGhaZ4tUaO1N4MI9xHioJXXQxrNGz5uYyhiQfWmyg9x8KizjJS34t8BfLLzWNFA5eKYg+fP8Av100fRz7GPExPTqzPi8F7lYHFXJkwTnSgDVtTQFyKSlA9kpQCbFxSLPCzi8aTRs4te8ayKzi3O6gi1Nkm00t8HSm0ppy2ys/slrcLZETbS7lwWjZiLX4IqKRlJuLfacLaBemU1U1JONPKNNQpqpccD7y1W5/w/4KKMtlLwxwPcu8t8rqcyuFkEcgFroJEIjNmXKQCKiV1Jv6NVHo2nTikvd/39gUvh12XGdkYyFQ38NLiZfCHYEQu92VSpDR8WWykW1t5R6s2558Ed6FGMaeFzfuet8K0C5+6coWIcL4DHlyAG47pZlMnzlhPdXJKZFslSFXeMY9yM7OLk2m/T4z+vUb2+PZ7DLJPHKI2gwuz2aTvC+RRmJV2KPGyuqRyGN2dcrqG1KV1o1pRXZ0bl8Ea5tYTk1U1Sg9/PD/AFk56pwHoK1R5sClNAA5BSAbiSUoGxHiKAMGXX1oAfu4G0H/AIhZYzeSJYxY8D4wJNR1AFv0tVdcQ7LRe2VbFSM1vhfZbba3xE4c7MxUSSBMQEaFvBnykqys1rjNblqAfLS9ArWfEsrQ3MukaLi8S1Q0+x/tzeDDss8kUUOKxJkTLgnYd2ndllYh0VQFJXwCRszcq7VLfL7PuRbe8WF1jxlvGj2LSbL38ikQmORZgBdcpBPdk+Hhy5cON/aDhrctk4vVMqR8RXbAy4PaMKG0m1McMOSPm/gsBGgmW41Akmk7sg2Dq8g1yNe8tKPaTfcs+bMd0neYhOK3k+Hyjv6vHmyoshq8McBWgAMhpANkNQBkKUDLNQAt7p7VCToTqrEBh6EEcNeIt78+B41VlEmhLEix3ZPuXh54hligkxKEyFjGGOrFsspv4vCe7YeEggEG5saes5R7zZWCg+5Z32JpAikggjfZyAIWCN30qRjmxAWQhQ7ID/LDEqp5Co3G/wCRputjJYlBfh4x5aZI63l3ogwuNxpwSvH/AKdIRGrk/ahjLO6o5MmdvClr2AAtxFd403JLi/Jma9xGlOfV/jBTrau1mkleRibsTYa2C30ABvYak26k9avIR4UYic3OTbNORq6HMxY6UAAApACh6ACI1AGdKAfZT/aKOWpJ9ja3vauc9jtR/wC0SbuJv7JDMSPFoQNbEHQXB5NzvdbkeZzQJw4lqXlGq6ctCX92u1KV2jRLzOLKqKpaQv4jnd7WF7i5coARfXlDdJIt43k5ad5Ku5vYmbYjF4xu9xEgZlQfy0LKfCNdW5FgBpoNL3jVa/8AmOxMt7PV1J6yf6RSHH7inKGj6A5D6fdb8j+FauS10POYp8KzyGvisC6/MpXztp9Rp+NMwKasz0gGAOlABcFgmY2RS58hf6ngPcimgPHYfZxI2shyL0Fi3udVHtm9q6JC4N/bGw41WyLbW2Y6sfUm5t0H6UuBcH24O4zTzyqmjR4d5ieQVXjRmPkhlVj5Ck4eLKHQ0kmP7dDsqLMb3EiNleM8QQbOD5ggg+lUkq2NGamla8WqLSdm+4sKBQBlI42AB9/81AqVWy6pUEiTd58eFw8oQZjFBJJYWv8AZxs5PTgut+A42ANRKcXOaitcsnVKip05Sbwkjn/gIBlAtyHlyHl9P1rcvVnlcVhJGGOwAN9Ab8QeB8iOR8/1oAau0OzxDqoZb8gfyIOnkKbwoBt7R3JcXynNb7vA/wCD+FI4iEkYSALlCgBeQAAHsKcOQs44eCwOU2NjyuRppfWx8xw5UCjZm2UzfMMltLcb9MvDTza350CE2/A1sFW26yEXV8BiYyLaWYRNr1vk4mljox8NyyuJ7Be7xYkKu0bXQSIucMBoEmQEMsiCyiRA+cAXFwXeBdWXXdqDw/T6NBZ3yo9mayvVfIrYTsjczx93IRGPmDRyqw42ABjQc/vMoNVa6MrPdxXjn6LiXStCKyk2+WPsfPaJuJFDsTbDf1W2XiQZD81mw8gsNSEB6AsTzLAAC6trOFvqtZc/jkZ+6vZ3LxtHl88/7Q5i4V7W6WF9PIe9SSkPmB58uXL68/w/OgAsLj8r/vT6UCAsYunLl+JA5+opQNKXEWNv+JK/Q216Ugooy4g54iCbNmW2ltRmB9RkI/8ARpABYxuPSgCXvgRxtt5MPf76TR/WB2+vgoR0hudH441KurDTNnBvYgg8QQNPT610RKYbZ0ouTeypqTz04D1pRmBodtk/+y7Tzf1MHLm8kdclvZW+tIhXosnKuAden7/fnTCECJs1r3FvW3Xh5dfekFCB7Dh539fxpRAGNxwsPNutuHi8zyBtQB//2Q==</t>
+        </is>
+      </c>
+      <c r="AC243" s="6" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
@@ -23116,6 +23392,7 @@
       <c r="Z244" s="6" t="inlineStr"/>
       <c r="AA244" s="6" t="inlineStr"/>
       <c r="AB244" s="6" t="inlineStr"/>
+      <c r="AC244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -23206,6 +23483,7 @@
       <c r="Z245" s="6" t="inlineStr"/>
       <c r="AA245" s="6" t="inlineStr"/>
       <c r="AB245" s="6" t="inlineStr"/>
+      <c r="AC245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -23299,7 +23577,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB246" s="6" t="inlineStr"/>
+      <c r="AB246" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAgoICAgICAoICAgICAgICAcICAgHCAgICAoICAgIBwgNCAgICAgIBwgIEAoICAgICRUJCAgLDQoIDQgICQgBAwQEBgUGCgYGChAOCw0PDxAPDQ4PEA4QEA0NDhANEBEODg8QDw4NDw8OEA4PDRAQDREQDxANDg8SDQ8NDw0NDv/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAEAAAcBAQAAAAAAAAAAAAAAAQIDBAUGBwgJ/8QANBAAAgIBAwQBAQYDCQEAAAAAAgMBBAUAERIGBxMUISIIFSMxMkFRYoFCRVJVYZGSlcMk/8QAGgEBAAIDAQAAAAAAAAAAAAAAAAEDAgQFBv/EADkRAAEDAwIDBgUBBQkAAAAAAAEAAhEDITESQQQiUQUTYYGR8DJxobHRwRVCYpLxI1JUY4Ki0tPh/9oADAMBAAIRAxEAPwD5xaqWaaImiJoiaImiJoiaImiJoiaImiJoiaImiJooUN9ETRFHRE0UpoiaImiJoilktRKtayVCT1AKyNMqEnrMKkiFDnrKFXKc9ISVGC0hSpoLUQijE6xhSo6KVUrIkyEB25GQgPIgWPI5gR5GRCsB3mNzMhCI3kiGImYwc4NBJwL+ihbl172VyGMQu1dQpddpJAHqvY+8ElYUdmvv69uxIC+sszUw4ECWMkJF8a16fE0qjzTY6XDI3Hz6Tt1WbRvstHo1GPYtNcDc9xQCUrGWMawvgAWEbkUlMx8RGrXGLldWhTLyGMu44HvAGSTYC5IF10bqzsuIsvnjb1C/ToC43Om0itYWKCFTOVYyFjoN5gKH1IehkuRxICYS10h5tIPz2vjddWrwbJcGvaImWkkuGmzpAbaCDkD0gm06XxtY6wtMMMgRjZjsrlb7bDmR8F4MfQNdpCYmPpF1Rk8ZjZ7o+rW87tGjR002cM577SblvqSxn+4gCxEyT5Z9Jxkl4Hhv+vvwhZUM5TiNod0dt/NQ6nbP9TPHmf8AXlvrY/a9T/CD+Wn/ANi1O4/jPqfwlenTsFMLZ0gTNt4DzdU40S2/aDbNKqMz/MY6rf2sJBq8Hb+EAGP9Dz5Egx0UikRh587/AHCqz2o8wkxeOyEr+RJ2EyWP6nTXZAwWx1kibhCY/axkgKImPrL4icv2l2Y50PDqdrSSJv8A5gb9Dt8IkkRoqjBB+n2n3v10yOkkt39S7VaUREzWub4i0M78SEvMU4/kM/2AyRnMbzAbjMRvN4NtUA0KjXTEA8pJOwmzvI5tuCY7wj4mkfX36LF53p59VnitJdXZtygHLJUkO8jzDeIhi5mJ2YEkE7TsU60atCpSOmo0j5/ocHy6hWNe12CrKJ1rwrAqaRA2LW1nhUbABruEtlSiKBY2FxsTJWuSmAH5mY2j5nVmlwBLRJ2+arJXtvp77VWJcrJss4e3dxVa+D5eFChaTVNhjj8LGzyj1prYbGY8VBy4sZOSQ1MrNbQ5I7I4nR3jTYWuQImCQIF4cRIvaNRhzSLmVg0j3j3+F5SyHez1szkMhiF+tTuPsb45q1QhtKwfN1F9dcQpdVm5QCFERLDxwLzNUPLojhSaYFSNQETf2dp+S6FDtJ9GoXNJglpItJjxgwbnmibmZkg5bqDqjDUoy9PHxkri7iGVlXjaiugIXbTdqQuoVY7DVgVVAG9llJkBNOK6p4BGDaT3FroHnm+Vu1OI4ek2pRDnGcQAWy2dMGZgSQTcGN7Ec56X65dTIjrEoGTts061WwxcjvsVdjUtOuf1TuaCWU/TvM8R27HDufRksMT4A/cG3Ub7rzlV4flZie9uT/zPKf8AY3I/9ttbTuIruMl58jA8gIA8gteG9Asp0z3NzNtw1azshk2vghGgwTzPm4xJlxpuC0DJERmZmFTMCJTvERM62KXEcT8LHE7yYJGB8ThLRcA8wbe6x0tO3vyWZ62G5i2oHOYVCGTJGiyuueFeUDxmSpvqEmgxiDkPxCq2ZE/pON/pjWrOAhlek0gi8WJyL6SQPEQJF4Egq0NOzj9/fr+FPnO9y3o3YbMlI7B6GfQGRcInMyRVc+k6mSiAIRnw/wDxL2MojzbTBcKp2ZwcF/DOfTdawsCd7CWEAdWSfMgXB78OAPj7uuUOyu8zxjguCOVp5kYqAykuASUzO0b/ADM/MzHKd5mZ1vta4taHEmB/WBgSb2VZIGFXRa31W+nClrlcdPdPndt1qapEW27CayyPlwhjzFYSfETPjyKN+AGX8BKdone4elrcGggTOTAwTnxwPEhVPK9z3+3MUsA/A0XYjJmrK9O1X102G2Yfm7Vp5ZCcnAqrkqpB1U10itxFNWibuSSeyI79Kk1ze7pgOgAutJEPAJc1riYA5oMRzNMtaFQ54aZJibDbbYnrj06rUMN28r5G6ixUoY+eTupFUpJNSki/j6o1K2EukhkpxsPt5yzFVDWU2JI3TBrayn5NbjOCpd4S+kGgEcsF0sAl5GmTMjUJc3+zJIkEFYtqEiA6/XETj8YyPJU6PbrErluRYGOGvwZebYhDrmNBlOrWw8TTpwEvPH3ur8nbKEzELJOFiFrFX6KzwlIUw7QNVw7llupsgtvewAgNGpxN3zpVneXifzB3+/4V5092lq3ccNwqdGciPC34lU1Vaz/v4LeE6drDVGYFa4uVKVshZH6brSnffaLxwtLu2OIYLmIbYhtwXTLjqDiCJkOYBIhVl5vn1v8Ai32WT6h7QYWoz3wilONYmL1d7kMtoCriKq8KtjErg3WoynU+RqssgMCJRTfE/EFGtl3C022dTggQ4aQZkl8DZjtHw5c60Am4wDy/B+sYt53kEYH0XAezFJeW6nrm+KdfH15dbvnVqehSnF45THWpcgIjxLvV1ytknBTM2YCROZhZeZBJrcgDQ0EcvJaYBIcTlxGoE/DmACRtN8b/ADv5W9yu49N9Mpre5066Kd3I1rr81ZhdYlYzHPusoY0PutFhAruKqULDbBQVT1S2oQqLK68uLi9pVBTHdRk6oGGgidHjnwiDI1EhvoOzKTXuLp5hEf8AIeItFsnIiVhu4fRKcxVa5jE2LFZCbkvV4qnAS82Qt1RuEiLFuseK931Bmm7xzg28ZiWPU/S7OHe8SymcEwZ3G+4j+YZyMrodo0miiTYuEG0WkxE5IuY5dpMkhXQdv6zbNO0rHYxKr65qYCw6uTKtmzkXe1i1ZXFQO62VcaqxVdcbN0ZsWKluWW1r9wfbilw+ppDWkHoDDhEmARIJAJ1SNNwWAHQPIOJ6+/f9V5Byl5bbD2V1etXY9rEVfIT/AF0mZEpHmLYm+FciPkKIKePKYiZ157iCC9xGJOwG/RvL6W6WWTVeYDNPp2FW6jDRZQfkS9e3NRxExBrmYnY43niURvE7TG0xExFCsWHU03+QORBsQRi2FD2zZdA6I6WztJZzjiuVBampkjOpcSgyUS73p2PINgWRMo9+IASg+JMgw+sILdp9pPZqDT8RkyGukkgyZBmSASMGLgqt1HUQTtj0j7Kl1RiM4u3HttyM3ra5KDO97FiwvHTFqI8g2GEXqmgTUqS5eVa5WJHC41YO0Xuk6sls2bEgki0aWwSTYAXPW+JoXmBv9c+sD0Wcx2C6lrcmpsZFEmyKxtTl1L5MK2a/CZhdjefvS03kJTtFl7zLYjaWrD2xVmS6/ixhxjLT8h4QMARPc+7rAdP4XMTF5iH2l/d9WhftSNwhnwIUE401yDChp1qbOVbiX4dcGcZVwgJsPbFfVqNS5sSQ3xnI3nm/vTJkrDuARBCq9PDnaaFvqWMjUrzXgVHXyEVxirA2slCxEbIEKoGLjoVIxHOXnx5mXLEdqVRyB2OrWuxy/vNO0CcwAJgALLut1RxXajNAFw0LcI2Vvq3TC1V3eoHmVhTC9jkwJt0Gc+O8ESJ+TGfq5T+OPMQfimTAvMz8smYhWtpEQOn6LbexfRftg3qHJZLJUk412KxNazjEezkpc9JV6YQXlrjXqVaKIEnPZvK4CuEGRAE+U7X7UqOJpyC4NJl3TndAEs1OOmoTzyDzGxLm7/DzTcHtsQffW2LRGyzH2he3+Zx64yD8oT14/M3cZj2UBKmoRpcYbk0RXgKtTnYaKj+YfNiGB5GwrfWtwXaVPvhTpDSSHQZgkg3DQRzNc3na4GHNJMZWxXqVaomo4nH/AJ5jC5DHUuaFtr8fNi+4KQvfi3xdaEgJdcbkb83CSZMUw3lErkxHceUa747aYBr79oBkzraBaCS28NjlktiBAwYXNNIm0LVl4sg4wQkHIRMYMSDkBfpMYmI5AW08TjcZ2naZ21gOIa8HQQYMGCDBGQYwRuMhSG9VfgGpDiFbCrLoh+4j+e/6Y/Ofzn8vznaPn/TU6yo0rOYlFUQWLK/OYuLa8hYS4fSGF86kDGwpOSFkxZGCZ+NG0r8Aw13hCaVdEul87U9pnIS4TmyyZHF7cYxfHhsTNv7wkodtExIHyiVhUKaVUvFTInEFSVxL6rKqZtG310hDJuIl8hBNO0yVSFkk8g8c7AXOY07wppVnlwrTL/DXFfOzDEFLGGaa0eblWOJMhbJGVYoeW7YlBxyKHTwd4U0rBtxy/wDCH/GP2+I/b+ER/trWe8qdK9f9h+scXTrYm17+LqUU0LtXq3B2FObk861jLDFrCt4mIyCTAq0UmwapREv5Mjdih8zWZVc54cHF0gsInTp1kxNmsJYAHEus8B8Ahj3XCFt/ZL7aWGx1WvjX/eP3bQo4VKKqqYNXauBYZkMxacqXKCGTkprTBv8AJvVrPFAidxnPWq8PxFYgvblxJGoGwOsAy4C7wAyA7lhjwwXbIIC2LE/bjw3hrLsXcyy7QkxXm246XNyNk6txVfJW0xag11sdbyV4kY0jI9vUkCDxTA0u4OtNmOiD+8xzhnTzPf8AG3UYILtQ+J4uC1D37x7heLO/fcdWTvgyoDVY+lSpYrGqfxmxFDHqhSjs7TI+dxy0ziJmI8kBvPGSn03C03MadZlxMnGYA2AGACdtRdB0wqyucROuooU4s0RVRsaIpva0RPa0RSlY0RSS7WBCKHPVRYictR3aKHLU6EUJLVgaoUurFKaImiJoiaImiJoiaImiJoiaImiJoiaImiJoiaImiJoiaImiJoi//9k=</t>
+        </is>
+      </c>
+      <c r="AC246" s="6" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -23394,6 +23677,7 @@
       <c r="Z247" s="6" t="inlineStr"/>
       <c r="AA247" s="6" t="inlineStr"/>
       <c r="AB247" s="6" t="inlineStr"/>
+      <c r="AC247" s="6" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
@@ -23487,7 +23771,12 @@
           <t>live-verified 14 Jul 2026</t>
         </is>
       </c>
-      <c r="AB248" s="6" t="inlineStr"/>
+      <c r="AB248" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAg4KCgoICgoICw0KCwgICAoKCgoICggKCAgICwgICggICAgKCggKCA8ICAoICgoICgoJCAoLDQoIDQgICQgBAwQEBgUGCgYGCg4NCg4NDw8NDQ8NDw0NDw8ODQ0PDQ4NDQ0NDQ0NDQ0NDQ8NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAACAgIDAQAAAAAAAAAAAAAHCAUGAwQAAQIJ/8QAPhAAAgECAwYDBAcHAwUAAAAAAQIDBBEAEiEFBgcxQVETImEIMnGBFCNicpKhwUJSkaKx0fBTssIJJCUzQ//EABsBAAEFAQEAAAAAAAAAAAAAAAUBAgMEBgAH/8QAMBEAAgECBAIJBAIDAAAAAAAAAAECAxEEEiExQWEFEyJRcYGRscEyodHwFOEVI2L/2gAMAwEAAhEDEQA/ADC9VgOFTuGsxxxK0lXhEzix0Uwt/fDzhSOOnt8eE5pdlLFJlJD1coLxEqQD9HjBXOnvAVDsENgyJMjrIZoQvqMk7APf299pKpHiU7lrgM0S3jNx5kRAikgaAMCNb2JGJ+rTIXOxdOC//UFqhIorljqYmNpCiLDPH9tLFY2A/cZVuNfEWxukqWmh0J5tD6C7s7wR1UMdVA6yRyqHjcXFxyIIIBVlN1ZGAZWBUgEEYqsn2JHwsRseefCw0cdCPCHAPknwpGY0qMJcUk6GrxxwIPax4smKnGzYWs9SpepIIzJTA2Kcxbxn+rvqCiup98HEsDuYm2ztwzIjTsDl/Y6BjcjOb+twiHQkEm+V8Syq5WkOhRc9fQmd2/ZnrKplZKadVuCrzMFQ25HRFYL8FJt2wksZSit/Qsw6Mrzf028SY3m9k6soAaiONJQLs0SnMSObKhsDyuAdDbriGPSFGp2W7cyefQ9el2kk+SGl9kjfsQyR0yuxgrAXiVtDDOADlIIGW62RhYebIpAZWwyNS7ae/wC2ZBWpWSktv3TyHBePEpTRjyYZYdc8lMILcXkyY4juZo8NFNiJsKcJ5xPqjWV83XPMKZfsR0/lNuYynRvXOPlMnl1JFG+gQuH+7qzVXhKuaOlyix1BlIGhGoPhJlB1NpSwNzGDgDiaj9TZdHUElmtsOzupsD6tQRztiGEbxLtSdpmnvru/5SAvQ9MUq8cr0L2GmpLUSigJo9ryw2yojU+0Iulm8dhUL92+SUjQEyMdb4LYermpwnxvlfuvwZrpGhlqzglo1mXjqn8M+h3S/wA8GzJnLYYKdFMIKLUra4aRG1GccOO5p7At2BP8BhRUJjsKryyvUEe4kk5HQtJ4SKD6M4A6nW+Fm+H7xZbpLW5LcKOIRoYVZqmpimlzVE3h08cygSvrJKZIZms0hBBHhi7AXJNzV6rrG7RT5t2NAq3UxWabXJK/rox1+A/EueQolS6v4gzwOYWpnsEVyskbEi5jZJFIVCVbkelOpHq5LS3ndF6D62DeZPu0s/cpnGjjRJ9KWAyVgVsxgipY2j8W2S4M6hndhmQ5UKWEikg6kS0oSrK+Vcr/AAtiKvOlh5KMpStxUfl6v2Fz3q2z4m0aOdWmaOopakq0tzIVBpsoZioLWuQGa7GwzFmBZm04WhJWSakttuJDjZXnBptxcJavfhoz6Lbj7R8WkpZv9Snp5Pxwo364LcDIy0bJjLhBTjDCHC1FcNGIzRjCDiI3yrslNUSfuwzt+GNjhUchOtqoVpat+z0kV+yl0Ztfj/nLEdR9pLxClCPZbfehvODfD2nrYY2kRSyr4YI8pKEAGNiOcZ0JU3Fxe2mBUZyi2kzaTowlBSaTCNtDZixV1PAgAyglrdjGw1PPlYAnoPQDHTbloxtGEU7pFrbh7DMud4wSAVLC6nUWIuCOa+U/ZNutsQ06k1HRskqwi52aT8hXOPWzkG0qSnjVQI6TaD6CwUCSiWNQByu1yB9k4mwreSUn3r2ZQ6USUqcP+ZP7xGx4OSf+OoR2pqdfwRqv6YOQfZRhqqtN+JccKNRw4Q4WtjrhthplQ4aKVPivU5aGqPeMr+MhbfnhR8Vdi4U2yhLBUU19ZYUkT1YEAH5WHTFao+2n5BajH/W15hw9lLe0qhQ62VZFHU30Kkd1NwR6YGV45ZGtwdXPTtyCXtPiLTPV/SEqSrofrAqh0zBQupfLlNrDmR5fd53c1J8C7QoylstC+7scRo3jdElDt5i/RlHcgADL2I09cUpSlBNNFipQammxP2299L23tGS5y08NLSrfUeeZ2Yr0uXzRtyN4xfQLcgl1eHhzbZlMRV67Fz7opRXdz+/sOVwM2nm2fS+iNGfQxSuhH8RgtSfYRl68bTYSFOJSucJxwtxajho0yBsNFBp7RW0smzpvtFF/mzfphCWmtQDU20siUc/QJkktzy5XVgfQc/TL3GKktXJBinoos2uF+9D0NY51MRkL6c4xIfrM1uatIHk7qW7HSPEWmk+Ni/gpSptrhcb/AGJw3Wcipglhs4BeOWMTRtfXMozKVbvY2PbnepGpJaGpo4qVJWSuivcYN6E2VTlS2eWclEsLKMqO5vl0SFFDGx52C3LNfEMYyrVLPZEWNxtoZ3vsl5C4eyhMZotoVLe9LWItzzyxpHJHz6kFmY9yx6nBHH2WSK4R/oxuAblnk+Mv7HM4BV1qMR9Y5ZlPfzv4n9HB+eLNB9hFHFK02GeknuAcWwc9zKzYU4WbxcMEMyNhBbi/e2fvB4dHDGDrLNb4hF1/Mg+mEtdonpPdg33SXxKODsPGVj38/L5csUqjtP0DVFXh6l24N7ODsGcBtFWS+vQAE9zoGJ+3iniXpoF8DG8ncZDYO5xgBEbyBG1UAmwv0GugwLlUbNBTgogr9ofYJkgJ1JS/PUnOrKfnY4mwlTLUuyp0jSz0mkUX2WaIRx1MfL/uInsefmo6gXPc+UfDlghi55mny+TOYWGRNc/gYngpvOimaMsBco+v73mV/TkE/PFjD1ElZsH4qnKTukHbZe3ltZSGI5ga2v3tyxfU09gY6Ulq1Yl4Ki+JERNCyS1QUFiQANSToAO5J5D1x1iNb2K/tHigEX6pBKeXuuq/HPcAjtlDX7jFaWKpx0Tv+94Tp9HVZ6tWX7wFq9osz7SenZkijWnzhFUuATIVLO2bN0VQAMtrHU3sEjiodxZ/xs48TzwgivRBCbkPOD65joRy6lbfHEOI0lctYXWLQc+E24/hLG4YkysVa4B965UfAL5R6AYD1qjlc0dCioZWNBSLkjWOwawsD2xT2COW/EgtpblpJqy3uNb4ZzH3vowHU2whT186KoUSJ4gHK7gZP+Tf1xchLPHXgBcVTUJ3XEGe70xlq5KcMA13ljN7aZhmAGl7GzEc7NfS2s9TswU+BSoRzz6viMVulsZowGV2DD9oEi5+XQ+t/W+B7rzTvF2D38Om45JK/iMlwfr0rIW8QWlhYRzakZgReOWwOgcZgRp50awAtjY4CqsRTu91uefdK4X+JVyx+l6r5XkIxNVNWPkFxEDoP9S37TenVV6czryD4vFX7Mdg70b0co2nP6vYJextyVVRcDANzbNUqaSKTxa3WSOnmm08kcj/ADVSR/bFihJyko97K+IgowlLuTFh4abZMYp1A0M0yt6+anC/wJLch7tsafExTcnyXyYzCysormxu+E8RESDU5WUr6WzA/PGZqfUzaUfoQwWyHsVYqGsVYqdQbEaH0PI+mGx0adrnVVmi43tpv3GztlbszqoQMSQo5KCfdHoBp+gwypq20rC0ezFRbu0twJcUdjZZIqoD/wBbAP8AcLDN/f44bSnldmLiaXWQutxO9ubReGqFQts8TkjtdGKlPusnkb4n0xoKUYzp5HxMlOcoVFNbodPcDeNZ4Ipl5SIHA6i/NT6qbqR3GMzUg4ScXwNxSqKpBSWzRcOFW9/0XaagtaOqC00nYM7fUP8AES2ToAsrHBzoqv1VRJ7PT8ff3M903huuoOS3jqvDj9tfIDm5+zxGoOl9BgVUeZhulFRRYN497vCjPoMQxV2Pk7LUBXHHf8iglVucpSNR3zG7fyg/LBXBUb11y1BGPrpYaXPT1/oD/BvZvjVdLB2LMSPg7XPoLRk+nxwcxcssJMzmBhmqRQ+m4exwmcAWAYMo+8qsR+In8sZNyuzbpWVgqbIX0xLCRXmj1tZ7m2FqajKfeVzaGwQ4ZTyYEHqNcUnEvxnoKZxx4PNAslSoOVXY36gFVL37Ai8lzzyW/asCuErNNRfh+AHjcPGzmvH8/k2/Zk3gJDU5/wDkbgekjM3+/P8A5fHY+Cvn7ybouo3Hq3wC1vcmpNyDzBGhBGoIPQg8jgfSk90FqsU1Zn//2Q==</t>
+        </is>
+      </c>
+      <c r="AC248" s="6" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -23578,6 +23867,7 @@
       <c r="Z249" s="6" t="inlineStr"/>
       <c r="AA249" s="6" t="inlineStr"/>
       <c r="AB249" s="6" t="inlineStr"/>
+      <c r="AC249" s="6" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
@@ -23668,6 +23958,7 @@
       <c r="Z250" s="6" t="inlineStr"/>
       <c r="AA250" s="6" t="inlineStr"/>
       <c r="AB250" s="6" t="inlineStr"/>
+      <c r="AC250" s="6" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -23754,6 +24045,7 @@
       <c r="Z251" s="6" t="inlineStr"/>
       <c r="AA251" s="6" t="inlineStr"/>
       <c r="AB251" s="6" t="inlineStr"/>
+      <c r="AC251" s="6" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -23840,6 +24132,7 @@
       <c r="Z252" s="6" t="inlineStr"/>
       <c r="AA252" s="6" t="inlineStr"/>
       <c r="AB252" s="6" t="inlineStr"/>
+      <c r="AC252" s="6" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -23930,6 +24223,7 @@
       <c r="Z253" s="6" t="inlineStr"/>
       <c r="AA253" s="6" t="inlineStr"/>
       <c r="AB253" s="6" t="inlineStr"/>
+      <c r="AC253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
@@ -24024,6 +24318,7 @@
       <c r="Z254" s="6" t="inlineStr"/>
       <c r="AA254" s="6" t="inlineStr"/>
       <c r="AB254" s="6" t="inlineStr"/>
+      <c r="AC254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -24114,6 +24409,7 @@
       <c r="Z255" s="6" t="inlineStr"/>
       <c r="AA255" s="6" t="inlineStr"/>
       <c r="AB255" s="6" t="inlineStr"/>
+      <c r="AC255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -24204,6 +24500,7 @@
       <c r="Z256" s="6" t="inlineStr"/>
       <c r="AA256" s="6" t="inlineStr"/>
       <c r="AB256" s="6" t="inlineStr"/>
+      <c r="AC256" s="6" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -24298,6 +24595,7 @@
       <c r="Z257" s="6" t="inlineStr"/>
       <c r="AA257" s="6" t="inlineStr"/>
       <c r="AB257" s="6" t="inlineStr"/>
+      <c r="AC257" s="6" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
@@ -24384,6 +24682,7 @@
       <c r="Z258" s="6" t="inlineStr"/>
       <c r="AA258" s="6" t="inlineStr"/>
       <c r="AB258" s="6" t="inlineStr"/>
+      <c r="AC258" s="6" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -24470,6 +24769,7 @@
       <c r="Z259" s="6" t="inlineStr"/>
       <c r="AA259" s="6" t="inlineStr"/>
       <c r="AB259" s="6" t="inlineStr"/>
+      <c r="AC259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -24563,7 +24863,8 @@
       </c>
       <c r="Z260" s="6" t="inlineStr"/>
       <c r="AA260" s="6" t="inlineStr"/>
-      <c r="AB260" s="6" t="inlineStr">
+      <c r="AB260" s="6" t="inlineStr"/>
+      <c r="AC260" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -24661,7 +24962,8 @@
       </c>
       <c r="Z261" s="6" t="inlineStr"/>
       <c r="AA261" s="6" t="inlineStr"/>
-      <c r="AB261" s="6" t="inlineStr">
+      <c r="AB261" s="6" t="inlineStr"/>
+      <c r="AC261" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -24755,7 +25057,8 @@
       </c>
       <c r="Z262" s="6" t="inlineStr"/>
       <c r="AA262" s="6" t="inlineStr"/>
-      <c r="AB262" s="6" t="inlineStr">
+      <c r="AB262" s="6" t="inlineStr"/>
+      <c r="AC262" s="6" t="inlineStr">
         <is>
           <t>US / Austin metro</t>
         </is>
@@ -24849,7 +25152,8 @@
       </c>
       <c r="Z263" s="6" t="inlineStr"/>
       <c r="AA263" s="6" t="inlineStr"/>
-      <c r="AB263" s="6" t="inlineStr">
+      <c r="AB263" s="6" t="inlineStr"/>
+      <c r="AC263" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -24943,7 +25247,8 @@
       </c>
       <c r="Z264" s="6" t="inlineStr"/>
       <c r="AA264" s="6" t="inlineStr"/>
-      <c r="AB264" s="6" t="inlineStr">
+      <c r="AB264" s="6" t="inlineStr"/>
+      <c r="AC264" s="6" t="inlineStr">
         <is>
           <t>US + global</t>
         </is>
@@ -25037,7 +25342,8 @@
       </c>
       <c r="Z265" s="6" t="inlineStr"/>
       <c r="AA265" s="6" t="inlineStr"/>
-      <c r="AB265" s="6" t="inlineStr">
+      <c r="AB265" s="6" t="inlineStr"/>
+      <c r="AC265" s="6" t="inlineStr">
         <is>
           <t>US Latino evangelical + Latin America</t>
         </is>
@@ -25131,7 +25437,8 @@
       </c>
       <c r="Z266" s="6" t="inlineStr"/>
       <c r="AA266" s="6" t="inlineStr"/>
-      <c r="AB266" s="6" t="inlineStr">
+      <c r="AB266" s="6" t="inlineStr"/>
+      <c r="AC266" s="6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
@@ -25229,7 +25536,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB267" s="6" t="inlineStr"/>
+      <c r="AB267" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAgMCAg4NDQ4NCgkNDQ4PEQ0KDgoLCw0LEhAKDgsKDQkLCg4LCg4LDQoMCg4NDQoKCg0KCgoNDQsNDwoKCgoBAwQEBgUGCgYGChANCw4QEBASEBAQDw8QDhAQDxIPDxAPEBAPDxASEA0QEg8PDw4NDw8QDw8QDQ8PDw8NDw8ND//AABEIAFgAWAMBEQACEQEDEQH/xAAdAAABBQEBAQEAAAAAAAAAAAAIBAUGBwkDCgIB/8QAQxAAAgECBAMFBAcFBAsAAAAAAQIDBBEFBhIhAAcTCCIxQVEUMmGBCSNCkaGx8FJicdHhJHKi8RUWFzM0Q4KDksHC/8QAGwEAAQUBAQAAAAAAAAAAAAAABwECAwQFAAb/xAA1EQABAwICCAUCBQUBAAAAAAABAAIRAyEEMQUSQVFhcZHwEyKBobHB0QYUMlLxI0JiguE0/9oADAMBAAIRAxEAPwC45c3Yss3v/wCFPD/x4EZMbUZxVdCTrnfFjFfVvcj3U/l+r+HHSQUviuXT/XLGYyO94/BPytxwJSGo45rnhWO4nj+ZUTUWAlj22He1Kbd1SfPbxt4gXHG5oqk92IpuaCQCCeAlZGkq/wDRc1xzFkFnas7JHOOLnLU4lDT66fqrKjpJTPIWSON3YUpkMjFGUgxmMuWsAjC54Jtek5ziRlbv+ENix0yEJnM3Hs25ize71nVFSzMxWZWjKaiW0pCwAiQX7qKqoq2CgAAcVDO1ROmbqK8NTVdPLjscc3OZyho6V4YSbdWr/s8fhcEdQB5B8Y0k3IHEraT3ZBPDSURGUfosMQmpb1NaiNvdKaJpBb160zxC3/b3O1xxZbhHHM/X7JwYNpUmr/oqMDxVQIK+SNx4ieGOUFrDYNHNHpAJt4Pe48CGAccIZz9kpYFUHM/6Mjm5kSlZ4eliEQJsKdmWfSBcsaeVVuR4aY5JmJtpB3tC7DPamFhRxVT6LDz/AEOArCL4uvi3Soh8D4/0+H8eOzKculU424cAmk3VLZiizxnfET7HrJicsAuxYraz/wC7s+zAohkiswuXNypK+HYzCUW027rneUPa5q4yq5zRP2RH5U5ycx8y5d6NTTyPNo0shMUUJNu64cqZQxBJ1dW6siaUJBdpvzzQcrqVmi6ztiqfmB2eMu9oPO9OleJaRYIpCkccqOJLNEZVaqKs7JuukaI5SusBozpJu03NxEbFnYqg6kdV+asnKOReX/KkhKKkhpyoC9YIDM217tM4aZ7XudcrWB2+FxrGNMAKqGlRvmh2kMi8s0IqKlBIN+kpMkpv5GOMM9j4gvZfEBhY8SOe1n6imkgDNDpnL6SXLeH09qWnnmPheoZIEAuW2EfUZ/EKQen7oNztxXdimgQ2T7JhcNiY8D+lJxPDpO/QxuB+xO6d30uYH3tsSAAf2fVBjSP7fdJrq7uXvb75ZcxMcC9WbDZRaxq9Agc/aBlR2RQtjYyCIbqASduJ/wAyx5iSOac0hWXW00YI9Rv/AC4AYKLgSKZlejG21/5bePz4c2ZK66USMgUeH6vwoO1NUd5b1b8usKlsjTDWSuiwZlZjpj1BSQsZupZgRcMSQAW4IDK3jU2OduusXC0jhnVCBN7cj3ClUPMfOOZ8rGRESnkuLByZbA6rEhdAJutrave2O2/CQA/etoOqVKOs1sHjdM+fcWzNl/lRNWP02r6emmkF7sgsl21RqI1NyBYhVbuqfUcXcPXcKkDLsZLC0hhw7Dl1UeYA9YncN27ass86c/8AmNzCP19XPIpBXQHMcRBDBrwxaYjqV2ViUuykqSRtxsOqvdmUPi4lM2Acs815owp5YoJZIY43laQIwjWJAxdzKQE7uhtgxYlWABII4hlcGk3SrPPK3Fsg4HTTO0UkNXD1Y3gcSAeGuGTYFJYtSiRLEKWA1EhgHQuLSIKlVP2a8xYzmSGGCWkq3qFmMfQqIipaJQ7wszFVWVlZdKXPvgkhQzhoun+GZgEFV9nLJmOcvczPT1EbQVMZAeOQWZSQGHwIZWDKQSrKwYEgg8OIjNRkRYrYCqnQx38/P9fPgNhGFJFZPYQPPw+P2bm17efDxmVy7Va2Qf0/Hjgc0kL8wJ0SncDuuu913LJc6kt52J1W/eNt739To5+uws2i6rvrCk4OOWX1+6acx8yXpsS0xazdbODFKQNLWAjlC9NbWIZi1h432222sjmp24h9Z39Jth7/APOJgJRi1fWcyeV1fCI3WZ6GpVY+6zm8MjIQQ2gkkAEFh53I8RcwdMOqi+dp73Lz+lcS51JzXgAwcr8uqzI5R5Kyi2bi2JNPFh8cbSXpI2kepYaSlNHLbpwmW5PVeyKFKsUJ1LqOpuabheBbG1TbFMwZu5C41HR1TVJwaWGVlgVhE7UlSsimRomUD2iBmMgjmXSlVEQLI/UdospDLTByVN1mbPa8gxU2gDpTzzdS5ueqlGhj02sAnsga9ySXsAtjrSbQoptCW47nCkzdivfXowtVTTN0bMyJKYdUccbFFPSWKyAsgNwCVAB4QpxMq96nNmO84MpV4hj9qnxWsgWOBFWappaWnYCGSaVB9SpDQUkfVkRXCVEhsLO7y4X9AFJJcDG1G1UVZF/S/AchFoBKIem1IPUX/wDn7vD9W4bkbLikuZsy4VlfCdcrrEg828SbHZVA1Of3VBJ9OL2EwdbFv1KLS4+w5nIeqqV8RSw7deq6B88hmeQQ5Z07XSYRiuqCMhFYMzyEa3iDDWqRDuqXQEKWc7sCVBFgQ8F+H/ywFSq+XRk3LLadvKI4rxuL034nlptgbzn04o2M78jaPK+XhKEWppS6ukiiA++V6dhMQYybr4MV89fkLzcCaroY0uOcASYzyG5NbpE02gFwA4xHVXfl7l0MByVNMyiOd4HFhpYohVju4JVmN7kg6bWA+0TawrGsc0kKnicQasiZ471hXlfEmjy0tm02Ub30+Q/D8ONugfIOQWGTeyVRY21HFtfSd9vA/G33fdxMXTndNmE4YPzOxjKlJKsDCDrLZ2iSFZGG4X64J1lsSTdJYz47943jimDOoJ5djqEoe4DNTjl9zFydzDwEUNagqYWqATJI0cFXh1KFVSuHGKnYVI0orGBYwJ5FASgUyPUcYpLZLXDps77lXB5hbvvsKsuaWQMY5B48KihqJpMJqhItNXwM9OamAaetA6qVkjeNj0pYpUj1MmsR6Cp4hewtuMlHktEKyMwQ/DgPSZRfnYoJz05nVnLjJiGPSZZJdGprkIugszBftG+lQCSo1XINrH0mgNG0sbXd406rRMZSSYEndmVg6Yxz8JTaaebjHKyEvGsz1+Z64vIzSOfNjc29B6AeQFgPIcF2jTp0mCnSAa0bBl3xzQ8qVX1H69QkneVFMWy7j+J5fllSKaWCMMHmjilaKM2uBJMiGOMhSrd5l2IawDDirWdmOBTGzmFuLzzwanxDLNJ3iIGbR0lBsxdLpJ3d16QjKA+5pmYMLWI2dAVS2q9zc9XPhI+fooNJgBgO45eisetw6jw/lm4jGiLoPZR7oGg7BfBQPQWHHnqpPjHWzlaVPV1QRuXnqy/BfBl8PdXx/gPl+B4u0h5BO5USLr7ppzVQX9SfuubfhxICmJkxKsGHysfOw/NrcROICTbZNuM0FZiFIr31SgbhRY2uSG2/Z89r2sfI8UsRTJhwVhjtiJnlfjY7RPJOaiqp5pJenI1HAqtJbFIIuojCUXKjEKfqxOk1xJUJJKjgqqxRUx4jC0xbrw748lObie7IwsTIFGf4/wDvgLNuYRaCFHtl5oiTEqeAHvJHJMw/vGNYjfwv9TIPn8RwRfwvT1aVWrvIA9AZ+QvD/iKrNRlPcCeth8FUzRN7TKqgFnchVVQWd3OyoiKCzsx2CqCzE2APHvA7bsXlBnYItsN5m5w5EdnWOGagqYtEbm0lNVJEQ7u2qSpAEKmXqa5UlBlS8ismypxUp1mveWh1s+fL4Vx7HsZJaelu+aNOqzC+fuVGFygsA9HTTGzMptJHExDaQSfdsQSFNyGNrq2/oBsUnu3kDoP+rE0m+4GyCeqtrHK/Em5CO0SpJN7I1lldokJ0G95FikZbC5Fo2uwA2uWGDjGBuLeD+4/K0sMZoMP+I+F5/wDCZDTYID5BARff7IPjYcTU5AhROO5fNNIlNTgeQHCtKbEKLVlQcQxkgeen7he5/G338QF0vI4D6rtid6fF6bBqoFr3A2Cjcna3n/Th5cGEF2SVqufsSV2Mwc+IBSrH7Q9XTOEqRH/w4M6VXTElu/DHUdUdMiYQpKVuqyoaYAa8kg3y5zKstMhGlLLKYTf0/lbgJDOyLqDTtbPG3MkAkauhH+cvdJ9bd622zX8+Cp+Ho/Jf7u+iHWnv/X/qPqiP+i/yjh5yhVVso0yMqwxSNZGVEGqd4pChYCR3WNyl1JgsblbB+Mrh7gychfmT9h7qbRmHOqasbbW2BcO3Li+DZQ5dMYJ5keVliIhraiqhlDhurDNBOdEAaFZGXoIoZhaQ99Qy4Fo1xYKzpSq5tI+YybW28FaXLLmZTVvZ4wjSysVoaddwSCYnqIGUMvg6vFosdgRv4Hgofh6gHYWXbahHs3Yh5jzNS37B8lGFh9fo7Oxc7f2JmPw+qYkfLcceU0o2MdUaP3ke618HfDs5D4Xn+MjJgSjzKIP8Kk/hfhFE5Ip5iY/1+f8AnwwgqM5qITTmnxK49fHig92rUBVholqcPa2MtzIAP3e81vkNj/EjiUvEyXQNwumBu4KSYBnOmy5iyzqx9pQq0ZcMAjKyslwrEnvKGJuL+m5Bm8VgGtN4+U4C/exaaVlR00YmyoBv8ABct8hv/DgEsaXODW5lGIuDRJyWcuf88RZ3zLLObsjyHSrhbdO/cGnc91dK3Jvfytbg3YZjaVBtJuTWgczF+plCWvU8Wq6qdrifTZ7Qiw5YdqOoyPyZijiSTVDAhLqlo9KrefUzBQV1oZdQJ1ys6a9QIHnjQc+u7eT2eC3cPjhRojkhW5/8+67n9nMMY4ooUZ1j0RRxSFGK2MzITrfuL9plUlgpNyTt4dgpny5Zd+uSxsViHVrkCyOjsSx1eYez5Sow+rilnRSL7jrTSG5DDYNI58xpB7pvsRtCubTwk7dcnvvcvL41x17ftRnc04azJ3ZFrmQgKmH1h7xOw6c/uodrqd1s8Ya+ki9n48fj6utjnPdvB9gtrCCMO0cFhdKLygegv8zsPyJ+fDFH6pDWy6Bvt8eOlN5KG1l+vxlV/wBStsyTtieS8WwXLsE7KOhU9TpsCrXMbaJFKg6lZSVOlgLq6MLhuIWi6eRaU6YVNRUtP3kKX/5jWJJ8yASCR8FuR6HjUaQ3MEcTCgzWoeK0rVmBPYA3Uj903BADEeF7233sfiDwHKmj8Tg6jXV2FoBF8xnvFvQorNxNHENIpuBsbem7NZO65sPrtD6k0kqwI7y7nUuk+BvtY+B8fDgptq2EIXlt4KtrIPN7FMS5fy4dHTmoqJw8VPKGPUhhllgmqIOnpKypI1MrKxaMQGWqe5ErAdTf5jAzkdU+SRq7Ekw3sycx5oyBApf0FRQ6r/3PadRPwCni6Kb6TdV7TzULm6xstJeyXlqXl52eKRKoJT1C1UzlJmAZLzSKHGkkEFHsGJ0WYA+9dd/RuKayk4OIEzmRz29/BycVh3udLQcoV+5y5iYdmTKstK5R8PkjkikUEBHhcFZFEyMGXUHK3WRHBbukEC1V9PD1HFxMuOd+CsMdVa0BrYHJUNhvZw7L2LSFfZ4Q9xdfa68S3uAo2rOoLkqux3LAfa4Q0KWcm/E/dTy45tHRP+B9mXsnYdVXNPTlvSeqrJl23vonqmQfNfDx2vxE/BTlJ9Snh8bEFX0h3JrL3+2GE4RBCaL2NNf+jwjRCoEtTqDdMkBzH0Sb94rpPGbWwlRp8rT0KnDgVaGeq/LVF9GlS0SwrPiKtEyxJaWqgnM8k1TLJDbrQB4xLFqAKlZo02EkYNalSrB0ljs84N1ZeWGmG2nmg4rOX2c3kGqnqVDLqCtBK6lbkA7RalBKkKdFtjuR464a52QWaW3Rs4jmfHMZzjGdLrGWZFjCyFI1ZowLEjUSW0O7ndkUiwVFVaWkaIxGHewm5HuL/wALaw2I8Ks14yBjrZQ/mF2S8uczcVaYrNTzt7xiA0u37Txsh7225Vkublrk34GFHSWJww8It1gN4Pz/ACvX4jRuGxB8QOgncRf0T9TZBoey7y8IokklnlHTkn0MJpA3ebvKuuGJGRAiKVBO8uvURx7vRmKbWqDgJkiJOUXyHuvJ4vCeBTO8nfkPRV5k3LGK4/XvGVq+oySdJomq0dai31asOssPSO5ZuizhL3ba43HAa36oG2/fRY8x2UgyhlXOud640vtFXAYeoUkHtPRcXHWuqKXnvIoEZSUuYnMiRvoMUkIYLu1pm3039+qXW2RkoPj+UuY+SMYKulRrA2eLrSKyG1mjmjBEiOCD3W3B3UG68I+9i6RzXSnigzVzEr6YhmrG1IqMZFm6hRdOkdVo+ovuLcqwZiO+WubprwbFIPN3C/IMMzgE96pFvMCb8iLj5G3DC+TmluklTQ5zQ+9Un/on/lvx2s47V0wnjI2Rc+Z1xhU6lTTxswBkcSgKPtS9LUmsRrd2vJGoVTdxxOGuP9ybrbbrliFdnbN2YRHDLiPQivEj1ZnjaSFSWV2WONQm7yW2aUqVBa6hV6kxge7zWnf8c+C5znQAv//Z</t>
+        </is>
+      </c>
+      <c r="AC267" s="6" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
@@ -25323,7 +25635,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB268" s="6" t="inlineStr"/>
+      <c r="AB268" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAgoICgoICAgLCggICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAoICAgICQkKCAgNDQoIDggICQgBAwQEBgUGCgYGChANCg4PDQ0NDQ0NDg0NDQ0PDQ8NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAABBAMBAQAAAAAAAAAAAAAFAAECBgMECQcI/8QAQBAAAgEDAgMEAwoOAwAAAAAAAQIRAAMEEiEFBjETIkFRYYHBBzJUcXSRk6PR0hQWIyRCUmJjkqGxs7TwCDM0/8QAHAEAAQUBAQEAAAAAAAAAAAAAAAECAwQFBgcI/8QALhEAAgEDBAAFAgUFAAAAAAAAAAECAwQRBRIhMRMiMkFRBnEjYYGRoRVCQ1Ji/9oADAMBAAIRAxEAPwD44tpVUtNpLLM626kIXKPeUTFqosMcpR+SYt0pIICmbGTDlahn0SQMJFZ5YTyNSNCipQEaRLAGG+sj1U5dgE+Vr9gZGOch1GOMiwcgwtwjHF1DeItGRcPZ6oQqwY7FWnSelpwal5ujjL67j4E405Ldj5PrrC565TKKTiWC5tpqA4fdE3Ah1bWrekKzbAAwGI2AAI6CNS0a5R4fN6qpNeNxn+Afa4rwC/nYCY/D7b2royLOSgs3rFm3evXMUY126bwtK62ra31MbAuWiSrUubRzSiuDRp3OowtKrnV80eY49yk/8hOXcJ3xxwXFbSn4UmQLGFloD3rP4OTcupF3YXgHQmepmUY597Sjn8NHefS97V2Sd1PPp7f5HlNr3Osw9MHJI9GJfI/lbrPVtUfSPRKdWE+mAc+yyFldSrIxV1YEMrKYKsDBBBBBB3BrOqxaeGTp4NMmsyRZiNTBwqRMBppQIPTX2B2btcl2h0WPiW2vzaUFerSUZdpHyN4VSfLnL92T/FCyNyDA3JLQABuSTtAFUnb030TRtn7yl+5u4/J1rqFP8Tew0KjCDykXqVh4jwsv9Tf/ABdtdGE+jW/3oqRf8o6iz02uvSmjSzuA42loRdQViAWJMgE7Ak9CKmhOawn0dNa2tzCpFtvGeTj57oTTlZR88vIP171xt+l40vueoRWIorNYciZLAqYKKgCE0AYMy5AJpV2NbOyPEHUlnUWmQhXOpb7Fuvgm36JAKqdXvTHU+kSy+j5mt6XO0FXuYrCKSz4weVuKox7ykuvfYlS0zE6TJGqdXUipKdKT9jrLPQ6tVpJcP3NPnn3TMR0UXrd0uoZlSyCxKzbVpIiQQRIiQJiCVnThp885fR6La/SkreaeeH2eO8U5tx+6Bis1q2e2CRtubdnQZu94RZUdnGgrOx1AHbpWVJR47O9paNShFcZLn7nXNuNeuXbtnEuWr123cL3LoXfrOkh3KhmYkCEL94wYeIqts9qb6XP5lWenRzg50c7vORk/Kb5+uevKtRadaWPllGcecFfrBkSNipmMiio2tdgQJoA0OLPC+v2GnRXuMkdoM4uqmTkKQAZ7bFBnTJUbtuDtDCCfGAK9KgnN4R4Vp9m6k0sHgXPepbjNZuXpuGWD37BKuCVhWGx1SWZYMd2IBKp0NKjtj52fQGi2E4005L+AhZuMDpVtKgSTAYufTPsPzVqT3Sktr49z0KlRilygHxBS0ntJ7zA7AbqxB8B5Hf5prNlKUamzfy/YstU1Ho0+WM9lyECEsG1q0TCrpnUY2ABA3PxeO+xSt6kVKVSWV7GDeVIP0I+I+cv/AEZM/Cb49YvPXjOoJePP7s4ifqbAVYbWRWKo08CiobyAxWkYA3jPvadTGSOsPP8AxxQztaW0O0IIBwr2svIKl2AGpg7MdwsFmJPdYt7XY2uPM0YWgaOoYlI8H4pxgAQShuMZlMV93MMWiZ6+nw8TNPm5t5a4PW6clBKKXBcMC49xRo9/3YEHy8hO39KfCUpdGxF+XJnXlnIe4Ec21thZMkm5GwVSoed/1pG07HYVbjaxk/El2Up1FykX+1gKgbQiiLbAQo2GnoPGNvX4zVis3s7MG44TZzS5yufnOT8ryv79yvFr5/jSz8nJt5bK/NZArHmosD8ipAGJpAAPNuf2aaj5gARPX7BuPTUtFZeCOZ1f5j5kVnmJEkxrtD0fpXInx8tq+iKFFqB09rSjSp4PMOaOSkYtdtsRq73Ztkd4MN5Qi4RB8i2xnaIlk7RzlwW1WgvcuXIN1LFldVxe1be4Sw2P6u56KDB8zJ8YEitXHjBbVzHGHIsA4lYBntEkmSdSyT89KoNcYGqrSX9wQx+LWirAXU1FGAGsbyp9PnWZdtxg8nO6leU4we15OZXOqfnOT8ryv8h68aupbqks/JztF5WQBWeWWNFAYHFQNZHIiaVIcB+ZeHLcSGmAynb0SOnlvvU0eOUI1k9Xuc/5fwu99Nc+9XS/1i7/ANyHxZ9ZMY5zyj1ybp8vyr/bSS126j/kaK86ko8tsJcOyc27ut28R4k3Ln21k1/q6rSe2VZ5+5iV9YoU+HLkF8R5hyFMHIugj96/sarVL6guauGqjZft7lVo7os0V5pv/Cbv01z71Nr6jXn3ItuKfYIz7kyzGSTJJMkkmSSTuST1J3NZTk28sfDj0g0rSFpIeo9w8YmmgMBQBqcQuQCfASakiGSwa6bGq/giUF7mexnuu6mD5io6sFUXJHUoxmsMLJz5lgaRk3AvkGj2VnPS7ZvLismTLRrST3ShlgbinFbjyXct8e5q9Rowp+ng0KdpTprEFgF9satZJ9qGa4aa2PS+CNOyh6FUQ4VAEWFAAfmf/qc/sn/fbUtPljJFuAqIfkegMCoEwiNxJoFBz24p7XwRsjTB0RUDhUAPFDAiabEABza/5JlHViqgeZZgAPWTFWKXqGSLgKhEyZRQSCJoAQNR5YGjlCpssMGCmhgVACoAVACJpOgK1zzlFLauvvlvWmHiJVtQ28d16VYt+8kTZ//Z</t>
+        </is>
+      </c>
+      <c r="AC268" s="6" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
@@ -25414,6 +25731,7 @@
       <c r="Z269" s="6" t="inlineStr"/>
       <c r="AA269" s="6" t="inlineStr"/>
       <c r="AB269" s="6" t="inlineStr"/>
+      <c r="AC269" s="6" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
@@ -25528,6 +25846,11 @@
         </is>
       </c>
       <c r="AB270" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAgsNDQgKCw0LCAgPCgoICAgKCA4ICAgICAoICAgKCAgICAgICggICAgICAoICAgICgoKCAgNDQoIDQgICQgBAwQEBgUGCgYGCg8OCw0ODQ0ODQ8NDQ0NDQ0NDw0NDg8NDQ0NDQ0NDQ0PDQ0NDg0NDQ0NDQ0NDQ0NDQ0NDQ0NDv/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAACAgMBAQEAAAAAAAAAAAAGBwUIAwQJAgoB/8QANRAAAgEBBQcCBQMDBQAAAAAAAQIRAwAEBhIhBQciMUFRYROhCDJxgZEUQlKCwuEjQ2Jysf/EABsBAQACAwEBAAAAAAAAAAAAAAAEBQECBgMH/8QALhEAAgEEAAMHAwQDAAAAAAAAAAECAwQRIRIxQQUTUWFxgZEUIqEysdHhI1Jy/9oADAMBAAIRAxEAPwDqg9SwGhe9pgWAEtuYzVZ197AKDGm+NVni97AVu3ifEPGaG97AVmx3v6ZphvewCRxFvFZp1P5sAFXvbBbrYDQkmwG5ddlE2AMsP7v2cjT2sB9B22MTBZ1sAqcZ71lUNr72ArbvH+IEDNDe9gKv4434O7ZEJdicqqurMToAAOZNsNpLLMpZ0jzct3wgVL7UIYmUoBxTpsdYVq1RcjMTplRhBEHNMGmq3reqfz/BbUrNLdT4InG+1qEBEuqUKf7jkonUcM5iqyNJ4oJPKdLQ48cnlzfyyZJQSwor4Qsrxu4pVyy0iKNYAupKFaTBQSwYLmp6AZppOWABJp6jNOhczp7ltcvNEKpbwn+nT/AvNoYMq03anUUq4+4IPJlYaMrDUEWtYTU1lFXKLi8MI9gbvnYjQ/i25qOnA24pmjh9rAWV3efDv8sr7WAbW8ffqFzcXvYCp+8rf+TmhvewFccXbz2cnU/mwDQ+FXD/AKor13p+qxq/pqLMsnKUGY0ZViXFUhOAGYZSQPUK0XaVZxain0y15l32dRUk5NbzhFmDuGvQp1qVTLUu7Syeo8sj8MLIIinAhkB8qRrNC6rzk6RWqaxkRd83DXw1Cq0hRSYLpSWmoHX/AFWLuZjXK7T72k/UrGWeP0Ms6J6ruACCS7q0CcjwO/y/KT0kifyZ843TfQ2lZRQCXrA59anSqRUQuBTrkBWDVng03YmGJqHOAgAALnuBeWldP3OdvLdx5Fj8AfD0Bllfa10UxYTCG6FEjQWAaWycPInawHG3H2+FnLa+9gE5tjEzNOtgIE1ybAdFvgJutEXO73moMooi9MzH9tR61SipCqdWdTUgkFieXJZ5e/1Wft+x1PZu6a8v5HFt7f3RLikKd4eZhkpSoHeSVUx1CFj4tWOg2s5XyXsbmKfCk/XBnvl8ARnM5cuYaQx0mIMa+LRuHeCe6ixkR23t8V2FRqbepTPKXpMEP0cAr4EkT9xaYraWMrBWzvKbljfwDe9S4iot0rUSMy5jTqAZlD56ToSORyshMHoGHW0q3bg2irvIqaTRfXC21aRpUKvy56aVIPMZ1DEHyCYt1kXlJnJSWG0bF+3h016i2xqBGIN+aLPEPzYDiredoE2AxULuTYAi2RhZm6Gww3hZOnfwuYE/TXRqDQwy0qivlOV2JruSoYK2VajMoJA+WdNLcfe1VOfEjvrOynbZpT5rHpvZIYv2Fe3qU8tSjkgj0qaMW9TPwsajMBlSno3+moZpICAZT5PuuDlsmRjVdTeOHHLG8+v9Gnvj2i4ShSB4gpBYACSD18xaJFJyLGdDFPIG0bxWNNMou7Ush9RCjC8NUlYBqZzTVAuYk+gxY5RCQWM9qlw9c/gqXCqpvGOHHvkHsZ3WKNHKuprpmUCJ0qEiBI6Dv8vPSbYpPL2QrmDSwl1JjavxBhUVJghQh8FOFh9mUjTTTQkQbdZRmpwTicndW87eq6dRb0/Z7QqsT/EUTPF729iIKvEO+9zPEfzYBHXDZJJsAxMLYALRpYBw7Nw3Qu6GtXZaNIRLsep5BQJZmPIKoJPQWGGXB+HTHtO90EvNElrsQbupPCVqUHrK4NNtVDAq66A5W4gCVniryk6VVrp09D6tQuo3VvTqr9XKXqsL88/cMb7RyvIgddeQ/iNATJPgwNfBgYedFjBxaFVvTvNQlIRGaFzEOwVTrmAJUk85BIWeoFpMUjSo9YBrZdBonkO0yLePU81jBhxPfQKfaD6hIOUKqSWZiSOELMgTIMQZNpUE3hIh0+DvXKXJFGcabyzVq1nThps7GmOXAWJUkQCC05iDqC0dLdhRp93BR+fU+edoXf1dxKt0eo/8rS+efvgEL3ttj1t7leaNS9E2AcuGsMqIJsAxtm7QpoOlgFjv422K3oD9q5grdmPP8rE8p07CBgJPgN3gVKG07tdTUqC61lvFNqAqsLubx6JqU6po5vTNU+gKIfJn4lExas7RpKdFtLawy77IrShcRhl8LzrOs48PE6OYmujs2ZXekoQiUCk5nMlpqpUEgDKIEjuLcrTPplHC5rPkJTEmzKpLD1q2hmSFOaORaV4j9o8W9+KPgTatam1hRPGzpVWzHM0wTAXp2GnSSfPi0afPRR1NPRUn4rd4VcXhbpTqMl3/AEy+tTRsud6r1cwqEakektPh00ZpkNFuo7NoxcONredM4jte4mqjpRl9uNrxz4iFoKCcvWNPr/m1y1g53JmS4G2psZRcbAMCtjOOVgIW/Y1Y9bATu0thZ6JEyQAxYc8x5lfAMDxpPzCfXGiPxfcCG6a6ONobMX5XW/XapPLSlWSqSD3yoY82h13ilL0ZYWibrwS/2X7nYG94qAVS44YmQMwPfUTH0IHibcNCazg+nd8o8+YnMXY5oE1I5kiOekTp3gzaTwdTWV0gRq4rWOHjboBy/qPIR97ebjsiSr8XIo9v6B/W3ljqWFOoT/QE0+gSPtbsLB/4UvU4XtFNV5Z64YCXJ4ItPfIrQ5uagor+SD4MK390fY9reZsiJv17sMkU14JsB7uV1LFVmJYLPbMQJ+0zYYYy9rXx6Tkpqg0KnUMOsjrI58re2SOopohqVZRVu17p6ZKquR1UA6qfETB6gHzaNWjxRa8UTLefd1Iy8GmdLd2+NVqUqTSGBUETr+f/AC3ze4puE2j6lFxqwUkRW8CvSkk01LHlwiR9ZFpFFyZrUpxUc4FTfb+IcxA5Dp+PvaakV+sMqhvqw471KlddcqKrr/wUscy9yuYyOo5aiG6O0morgfU5O/puUnNdBb3u65V10J6dR9fNrMpgnwvdibvWnSQGQnujVT/aR4DDxbLNeoK+oTbB6BXszBTnpYA2wxu2TPT9UhKZYBixyr1IDE8gxEHlpPLmAJ/eFhg0yC4HpMQEqrxICdFDETAP8uQnWAJt6ZyeTj4Cj2tdHouZBjlUQiDBAbVTqJUhoI5EHtbTkbD7+Hfe/wCmVu7NNI60idcsc1PlfcfQzQdoWal98Tqeyr9wfdy9h/4rxDnHDB05zaghT4WdXVrKS0BP6JoIOpiT4m0rqV0tLBX3ePiCDVpodM0VG7lY4AewPzeRHRgekt6WEpP2OPu6+W4R9xUps/1GImFAzO3OF5COmZjooPk6hTawRWBBW2e5TJSGgEZAZbJwg5fqAskkSonmxJ1yZRq7EwozGIMzER182ybFjdtVaNM+nQAZpCeqRoWJ/wBsdgATnPbQcjYAAxJf9So1WSM3ciJn6GY7T0sMEXccSVKSUlgV7vULI9B9aZzVqin+WUqk6ARwHQakbZB+3nY1GosITIQBKZA/UU1BJhiWC16IkwdKqQeJ5ATDMC8r0nu9RTyWcyMJgMsEETB0MZkIBEwRDCdWk1hmYycXlcy0m7TepdnWmatWnR0AZalQKUfqOKJWdQY1Ecpgc1cW04tqKbOxtL6k0nNpevQk95m9m606VY3etSvF4Yekgo1BV9KZDOxTMqmmJKq3N8ggjNGbO0qOSdSLSXj1F/f0owapSTk9a6eZUza2ZjHIdyYGvcn/ADbpTjDRF9Cj0011DVHj5mMwBOuVRynuTALQoyiS2VfCsd9TP15/mw2GPg7Haq6GooqrImdKmX/v1IHLPMRGlsA//9k=</t>
+        </is>
+      </c>
+      <c r="AC270" s="6" t="inlineStr">
         <is>
           <t>US-dominant</t>
         </is>
@@ -25625,7 +25948,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB271" s="6" t="inlineStr"/>
+      <c r="AB271" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4QAqRXhpZgAASUkqAAgAAAABADEBAgAHAAAAGgAAAAAAAABQaWNhc2EAAP/bAIQAAwICCw0KDQ4PCg0KCg0KDQoICggKCwoJCA4KCg8OCA0KDQ0KDQoICAgLCggICggICAgKCwsIDQ4QCggNCg0KCgEDBAQGBQYKBgYKEg0LDg8QExAPDw0PDw0PEBAPEA8PEA4QDQ8PDw8PDw8QDg8QEA8PDQ8ODw4OEA0PDQ0ODw8N/8AAEQgAWABYAwERAAIRAQMRAf/EABwAAAIDAQEBAQAAAAAAAAAAAAcIBQYJBAMCAP/EAD4QAAIBAgMFBQUFBwMFAAAAAAECAwQRABIhBQYHMVEIEyJBYRRCcYGRIzIzUoIVYqHR4fDxQ3LBCUSSorH/xAAbAQACAwEBAQAAAAAAAAAAAAAEBQIDBgABB//EADQRAAEDAgUBBQcEAwEBAAAAAAEAAgMRIQQSMUFREwUiYXHwgZGhscHR4RQjMkJSYvEzBv/aAAwDAQACEQMRAD8AzCgoicCueAnLIS7dTFDu164DfiEazB+KsNFuseuAX4iuyJEBGhU2uw2HnpgTqgqDgQiPwu7N4q5O+luYVsETl3hH5j5ryAW4BtqSDYlMxDo46M1JSyVoe4Ztk526HCOOnj8Eaq6iwAW0cXoq+8U5MWvmN0CoDmYWV79SVZG0E6KubY4eVLvmWpnbmIkzBIgAfG4RQqXcgogICA65VXXArQ51yES5wbYL62hvOkAjjrIo6h5fuRBM1Q8Y8JlJuCqaFI832k2QkIbFVsBeNq+fCm0B/wB1QuKPCOFZVlp8xo5kDQFxqpGkiG4v9npbl4SNBiuYhru7p6qFZG0mx1VcptxG6/wwGZEQIl+qOFh/MPpjhMudGAkhjit542znBJ2ggLvjLD3sDmhtRFtc4br2XbMo5NiPSj3C9dLIBZfdDtepkkSNWOZ3VF+LGw+Qvc+gxa3Cxa0S+Sd+61d4MbiLFDGtvw0DNfmzco79TmIc/wC31wLkDakbIQEuN90VpNh3GXqyoOpOmvrbMBfyIvfoue3MQ1M2HKKqRoI4gWNgFVSWP5UQfw0BW3n0wcMrW12+yHAc51B6JQ6fcmKWR6llBlkYMc1jkVRaJOgWJAqC1uRPMnCiRxec1VtcPAyJuSisfGLZkb7LkkVVVlUmRLC0brGckqflJsVYDQ6DkxwXI1krGnxAPgdiPkkE7HQvcPCoP0KzQh7StYD+EhHqLX/hp8Dgc4OIjVUjEPXSe1PVn/QT1/u2O/RRj+y967jslxiY35Y0TgEK1xOylYYz0wKSEWCeFM0OzCfdGuBXyDlSJPCKfZx4aZ69HIFo/EPRjovzFycEwzF3kEpxYoACNVpNugguoHm3I87ILD5WB+eIOdYDkqtjboh0xs9/yRs56Zn0QfHW/wCjyxU0d8nhFOPdA5Qq4h70pDDZnCd9MIbsQAFjGaY/BmIQ288DYh5DMo3+n5TLs+IPmzHQX+yrzcftlxWRqqzmygGKbLryu3d5Av7xa3rgYNIFStC6dpdlBVh2zxSpFhamkks9Uhjo8qli0hH2fLkrEgEnroDyxbh3AgtP/Cgu0WHKHb8cj8JHl4Mm9slracrW9PlywJ1hqlggPC86vgobfdtjhON1xw5CUuHaBHu41xjB0KXsc4DRSEO8lvcxQcNXdFNnPClqTe0j3MCuwo5VheTeibvsk02ZBIRzzOdOdhp9LWv/ADxzWiNpCT4hxdIKpxdyGPeC/lGWHzN/ra5wLnurWt2RD2enhYkfvv6m3gUdcoN7X5sRi5go269calAPezdWKvnaHv2janDRq8WXwyynPUFcwKnKxVNVOqEW54VOk/cpx9bla/BYUjD9T/L5Cw+qoe6fYVjjlaSafvssbBXu4kLNe7OzOwJN0ayZQGjGURqShYTYkvaG0oBsNEHBgWxSl4JJJ1OyJ+0+AFLWNTVDAO1EpYKS4DyQESUx8Miqt5EysZFdNQCp0I8wkpY0tbvr69/v5XnaeGEjg9wvS31HnobXoEqe8HaPVZ5AKd2USuoNtWyOVvy962bXXXCx+F7x7yDZi7C2yjqjtIof+2f6YgMKeVZ+rHCVBKQH/GNOXkIUZV2Q7NX+xioyFW9zlSNPshbf0xQ6Ur3M2lk9HZ92WEijQC32eXTkTazn9TE26/HHZjlSN4q6qZDcWEmVhb/TUH0/z/xgJpq4ooaALp498V12fQPJoZLZKdWOkkjfhg9fEc5AucqE2OU2LzZW1V0MPWlDPVEoHByuqIrMc0jOxkkfzdna7s37zMSxI8zjPSnM7MF9NgeGtyEWp7tk0NdvrHJTlZahaVShCvKyqAQNCczKCqfeYFhp5jni4EuFCUF0xn7janhVDgttZzJUqu1oKohHkipqRQAyCJu9YnMwtG2QZRckyXLtyxfE07G/HNjVQ7Uilw8XUmiIadCdjagQVn4eIxJygknXTn/U+eA+qVjxEOFxV3D1V9z/ANceiVcY28JU6fbMObmPph06KSiGAHKnYtu0/VcD9KXcKWUaKX2XJDJKirYlmAsBf4/H4YjkeNVF1GiqbPdjbQiqIlUWXIyqv5u7AZj+rxf/ADBOfvUHCC6Zy1TQcKqFXJYHwt4yeigafC5uf0nFmGjzGuyjI+ioHal4brtHZs2QWlpnNRSA3zMYPxdLj8eN3QA3sWU2JW+PeoJGuLdq25ojsE8wytzaHX2/ZKnwn4xLGFSQZSNASNP8+mET2Uu24X0RpBFEze628VLOn34ySNGIUsh6rfVfiLY6NxboVTVzXZm6hE3hFu0wkcNV+1AoRCljaMZSGLeIh2YMFzWBsD1w4wji9+VzqpB27inSRAFgF9QKE+vYlsk4x0KMVMyAhirA2uCDYg9CDcEeWERw8nCVjEMtdfVbxb2edfaI/wCGICN3CsMjNys7RsdSeWNcZSEOIKiq9/2SvTEOo5cIUQuD+zAKqM2sBfXpodeXlpoNfF6YFleVXKwNF0dYtskVcRvoJLDW+mYmf9IGdWHQX054ojYSaoZzwG5Snp4QQE0aKpszHM3UIrWT4ZyrH4E4KbUR5RqfkPuh7F1TsrlFssd7Lb7gkKsB/tVbf+Wb6Y9jb3jTSvr4qRdYV1WZ+/e5K95KFGglYLblYMbWwl/ibL6G28YJ1IHyVg4TcLbuA6kqyqy2LLoQTplIPi0+uB5JDVDmQgWKbbs6bA9nmA90voSSbggX1Op5+Z5DF3Z0jhOC7ySXtMh8SS7jTwii/alZcAH2yY+V7NKxUHrlBCg87AdND8RO8SOFdz80nhiGQHwVUfhLBby5YHEzuVd0RyhDT7oDMPFcH1wwdiCRorWxuOhU+u4aEgXNzYc+ZPIfM2GBxiHHRWZKC5V425UwbNhBcH2th9hAdXjLAhJJ1zAxxrZ8kTMjyMvJQpbDrAYB+Ldezdzz4BIsZigyzbn5IU7J4gtLNUSvcldnyQ0+oQIZTHAGvayMe+eRnYWDG+ioAu0/QiNgZGN/l81nzITdxWqXZ9imi2c8rNmkJRUUrb2dVjHdqw+88oTLO4ZUH2wt3t7thMfC6EktH29idYSQPFHIh0m8h9llZfxCsjJbndswhPS66ydCefLC/DykMJ3v8dPumRYHSAbVH5+yz32rPIofwkOiOZAQcwKA3v63Fvj1wrFqAr6JlqCWpxuHe6yGOFrWvEqg9LICp+eg+eIGOpWYdIQCEQZdjrAVbPbPMCin98a26AEG46t5YYxQ9O9dSPXrlK5ZOptoEvm/+xKaStndspLSEsb8/wCo5fLAmLees6nKIwzB0xVQ7bqUvkq/UYDzlXmJutUgtNso5gO8N9Lf3fGiLwf6oQOdRMvsmsg2VQPUune1jIGiLnxRBzliAOuRpW80CtYGxUKz4JwkIkeGgXO/gk+Kmde9h7kmabXqKyruR389RMkYTlneRssKpqO7sTlU3sq3vmBIbeYWMNAZGPW5NK21J1oAUhdyUxG5HZ0psnKarZu7hIVj7MZamQ+zxVDKsEez6mCOJq0n9qVkMgKLfxgS7duBjaAZX8nZtm6lv8nODict2tIoTSxosMrtQB6+W/KcTsr7+Q0+wYWnqO9SSvnihkW6iVp6xoo2vchFBzKHDEKNEdvDm+bdrsbLintjIcModbjLU63J+O5ps4wx6cbail6evmj9wxjWeiQ5VjzQp9nGLJFpYBQdQqagXJPh88YpjA6oC0LX5aFBXjLuIqLJLaxeNo6gAaLIg+96CUMrHl4j55sAYqLL3h7fP8rb9lYnP+2drjy49h+HkiLwwrlfZ0EqG6mGGZfVWjGb6C/LUEcjax9Iyg+H/Ehks+jvEK5b60qPAG5mJ0qEI6IfGOuVl1IvbMqnUAgs4JGkFp4sk87XC40rcLLWr3cnd2bvpPExbVj5m/zsCBhV1amtEVkIFKr4m3LqRymkIt5PjuoNwvcjuUM9x0JqYww0zAn1A/mbD54bua06Kh0rgKLt7R1TUyCnY5nSdZqgIgLZfZJJI2JAuQKeOOVybBVRiTyJD7s1gazqHU19wNPykuLzNfkIpYH3ioPuXP2XN2VaSWaRT7JGaeKrfKjwZZauLPHOCVkijlRWbv43QfYmNhKszJjVQ4iPBRHEv1BytpqCRd1dO7Ua+y9FRhcDLj5v08FM2VzqE6hoJoNyTSgHvsDR102msez5EeRI9pbGqo5Y5ZmVJa2mRbUzStYNKvs4Fo8xYpAgJXvbHF4ubEYtrjIayxPzWFAQTWoDaAVGw48V9cwLcDgJ4nRgNwuNhyOqf4OplIq4k2d/Y2GYkfxsqfEHi29LPS04Aamg2fDC8Ny0b96qvUh/zEyKkkUiZZI2jV1ZWvfU4CFsjDI4ULiaeza/h771XxnGRhsjo2OzBpIBtcc2tfwtpRaB9kXiqlQgKvmjkKtHr4gMuV1b96OUSgkc8nkSQPnc0RwuMdEdDp5LRwO6sAI1GvmiBx5pwIZb2ymJi2nIlQfq2Sy+pY30tjsX/wCZHh6+SedkO/eZ5j18UCeyXxdCxvSPb7GRooSfOOQlqYdLA99B52IiHvYX9WjQ7kJp2jhP3HOHNfv9/eiHBvyJaLaMSOe/pUmhe4sfFFmgkTncZZFV7e/GWyoGGDmx0exzDUOGYDjWo94PqqyzpMzXteKFppXnj4EIIUO4QItnt8sZ8yJ0BsVJT8Ohb8TyxIOUSkq3D22WlsItRG5vcD7q9TooJtck2F8alsBzd01PCVSvaW3sLezn4VVf3o7Rkk1J3AhETd/UNHMj+JKesOaaly5NYywQmTPqEAye9jUQQhuUDQHTa+o8eUonxplBqASWhpJFXUaatI/xIFGmmoHKq25vGWrpqWop4pAkNUuWpBUMzDl4SbiNsuZM6AMA51BClZluapJsdRt505VLMS5kYY0AEOzB4qHg0pQEHTQ6WOhFTWqvIT4iczE5iW8RJvck3vmued73w5yB8YJ4S/Qq8cZKotV94RYS01LOhtoQ9JHmt5Hu5Fkia1/EhHMYjh3UYBt+dfMHXlpCgEyn/Tq4l93VmnJtnfv4ddPu5ZraWHiWP3tSSQNCcZn/AOjgHcnGoN/b+R8apv2a7vOZyPl+FodxjAakmmzDJ7FKJATbVfHSkeupiI6Sjnyxl5zVjnf6n7haXs9wbMxv+7fsUiG4e7c5qZZELBbIqlSb5rhiNPyggkeuEsr/ANoAaraYktEhzetk2o2K1PTtP3ZeSeNzOqi7PeGxAUAl3ZY44AiqSSw8zi2Fry5r+BQe0/klZGYtoYm7nw+vkAkLPHnaFgcqXI1t18/L6HzGDBh4jv8AD8oTrvXjUcfNo9FH1/liQw8I3UDK5f/Z</t>
+        </is>
+      </c>
+      <c r="AC271" s="6" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
@@ -25719,7 +26047,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB272" s="6" t="inlineStr"/>
+      <c r="AB272" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAgMCAgkDAwwKAwMECg4NDQ8LEBANDwsNDQ8OEAsQEBEQCwoNDw4LDxAQDQsNEA4JCgoNDRAODgsREA0NDQsBAwQEBgUGCgYGChAOCw4QEBATExATEREQEhAQEBIQExAVEw8QEA8QEhAQDxISEBAQExMVEBASERASEBAQEhAVDv/AABEIAFgAWAMBEQACEQEDEQH/xAAbAAABBQEBAAAAAAAAAAAAAAAHBAUGCAkAA//EAEAQAAIBAwMDAgQCBgYKAwAAAAECAwQFEQYHEggTIQAiFDEyQSNRFjNCYXGBFUNSU6HBCRdjkZKToqSz0xgZYv/EABwBAAIDAQEBAQAAAAAAAAAAAAUGAwQHAAIBCP/EAEARAAECBAQCBggEBQMFAQAAAAECEQADBCEFEjFBUWEGEyJxgZEUMkJSobHB0RUzYvAjcoKislOS0hY0c+HxJP/aAAwDAQACEQMRAD8A1T9dHR3ro6Bvuxv7pTaFFp7kzXC+VGOEEPvlfkcL4yAoJ+RYjlghAxHH0w4XgVViLqljLLGq1WSG57+Gm7CAOJ41TYeAJhJWWZCbrLltPv4OYHNO2/W8Y74MW0mn5fkCO7UEEfcEDH/ZyLjHH7lhUMDw3s9qpmDnllv4a/3A8YBIONYiM3ZpkHS2aZpu7Af2kcIWwdGmnLmRLq2quGsakf30p45/MDBcf8beoFdL6iXakkypQ/Sm/wBvhEo6KU0z/u5s2b/Oos/G33hy/wDhhtLwx8O+fz703/tx/h6g/wCsMV/1R/tR/wAYl/6Qwn/R/uV/yhrn6ONO212fSFXcNHVX+xlPHP2JHhz/AMxcj1YT0uqFsKuTKmj9Sb/b4RCeilPLf0SbNlfyKLPxY3+MJJ6jfnZtTNN2t2tPxfPiO1UKAPsADn+AFXI2fsPlKlOB4l2Rmpph49qW/jp/aBEalY1hwKjlqUDgMkzTgHB+JMEnajfnSm70RitLmkvEGecEvslTBw3tyeQB8FlLBSQGwfHpexTA6rDSDNDoOik3SX57dx8HEH8NxmlxBxKLLGqVWWG5fUfOCL6X4OR3ro6O9dHQD9696rtRagXbrbtRc9f149x+aUaEfW/gjlg8lUghQQzKeUccrpg2DSlSjiGIHLTp23WfdG7PYkcwCGJSoYti01M0UFAM1Qrylj3lfQdxY2CnnZ3p7s+2Dm8VxOpNaVfmWolyzFj9QTJJUfYnJkf9pscVWni+PTq9pKB1chPqoTYNzbU/AbDV7eFYHKoXmqJXOV6y1XJ7n0H7J0gm3S6Udktz3C4MtFQ0ylmZzhVUeSST4AA+Z9LcuWuasS5YJUSwAuSTtDCtaZaStZYC5J0AipG5XXRUyXxrJt1CLoZCESWQMTI7EAduIBWOfkmTydiPw8DD6th3QhIlidiEzLuUhrADdRsObaDfhlWJdN/4vUYdLzksAovck7JFzyvrs2p80HrDUVr2ejvm4SfA3+BD3FXBaQ8isQCqSO5P7QsY8mRwoUE8QiV1JTzK9UmgU8smxLsAzm5vlTd1HYO+8PtFUz0USZtcnLMAuBdy7BgN1WYDcsIiWnr7eLYzV9Q6tca6Voh5zGaj6q2UkcQYLbHH8NCWELMad1ZuU0bEnUSJK2QkHKlIV+rJohLHRc5Ss6mcALBAZJEVZM2Yl1EhycvLN7anHsywMqXCS6SCXUDBe0xezqOwx3TiaSOrHJQ2QeBJ7ZIIUqzphmQgNGSVPkZKtUSepmKlu7WLaPvo4IBcAjXWD8mZ1iAtme/htqxFtRtpA43i6ebTuTML7amOmNb0Z5R1EXtJYDwJMYLD7cv1iD5Nx5IzDhGPzaEGRNHWSFWKFXDcn0PwPexADFcDlVpE6WTLnJ0WnXuPEft2cFt2R3rul3vj7fbgKLVuBbR/BKtB/WJjC8se5lGFYZdAAHSGxjWDSpcsV9Ac1OrzQfdO7bAnuOxVVwfFpq5hoK8ZahI8Fp94bd48QNQk2+k2G+B1vzusm0O3sl2iHxN4qCIqdMZ5zPnh4HkhfLsBgsF4g5YemDA8LOJVSZRLIHaUeCRr56Dg76QDxnEvw+lVNAdZ7KRq6zoPqeUNfTzs9Jtpptrlez8drW+nu1MjeTybzwB/JCfdjw7kn5cVWzj+LCunCXJDSJfZQBowtm7z8Aw1d62B4WaKUVzjmnTDmWeZ27h83Omks3D3W0ptVbhWanmW2rL9K+Wd8YzxRQzkDI5EDiuRyI9C8PwuqxBZRTIKm1OgHeSwHLjtBKvxOloEZ6mYEg6cT3AXOt20iF0++1g3Ns70lho6/WtprVZHKRKkTBgQ6l55aaM/cMAzEff0XVgk+hmBU+fLlLSQQ6iVOLgtLC1DiHEDpeLyK6W0iUuahQILJZLaEPMKQeBZ4FW8nTBarFtNHqLQsEmntS2A98gt3JWUYZwzB5FLw4DpxZ1HEqoPPPpowfpLNm1yqeumBcqZ2NGS+gIDAgKdi4GoJ0hVxbo3Kl0SZ9BL6ubLOcDVR3IJcgkai50Yaw67hb92fWPS2msC7W+/iRFQRNho61PP35AoozNxYHMRB8OVIq0GBTqbGjR5QqWxJzCxlHyufVce1yeLlZj0mfg3poUUrsABqJo23tux9m+rQs2r0lrXWdqpIdXU6W+1S0sallI4/CjDPAUZjKs9a4jNZyDQPTx8MrJkeocTqqKmXNNJNKlBai136zQLcdkplgq6tu0Fl7pizhsisqES/S5YSChL6Nk1KGPaCllusd05A1lQd9d60t23ekJ9SXbIoLcnI8ccm+yquSo5OxCoCVBYgZ9JNDRzK2einlesotfTvLOWAueUNlZVy6OQuomlkpDn7X3JsOcDXS/WBtZqhoofiDaa2q/ZnR04H8mfi0A/j3Sv7/TFVdEsTp8x6rMkbpIL9wfOf9sL1L0rwyoygTcqjsoEN3lsvxhV1FbQT7haeS96eJodc6fPcp3TAZivkxknwQ/7GfCvjJ4s4aLo/iyaOaZNReRM7KwdL2zeG7bc2afHcMVVyhOkFp8vtIIZ3929mVz35O79sZurBvBt5FfABT3FMxzp/dzLjmMeSA3h0ByQrAHzn1SxvC1YbVKkap1SeKTp9jzB2i7g+JDEKVM5mVoocFDUfUciIGFwT/XF1crQyjvaf28hDkeMGpl4lPv9vBXwOLwHz58sMtX4dghWm0ypU3Pq02PncHiFQAmD8QxoIUP4dOl9m6xTN5C44EdznLWc19isZTTgiFylIXnMfZCp+qRgMF+A+mMFebYBdV5OqZSCSZj1D5Rdk6k7JGwfc7C7EsC41BmZP4TZuJ0HPm3Dc2cC4F1g6cNBakt01fepDuFebkpSSolcOwJHkRBfw4eGcxhRyjBA5YAHplndIa6SpCJKepQkuEJDD+p7qfd9eELsvAKKalSp/wDGWoEFSi5v7uyGe2XSB70tXy4bRbl1mzGo25lGMtKx8BxjLBck+JExKFGQjLKCxPo70llS8RpJWL042yrHDYP3GznUFNmhf6NLXhtVNwieXbtIPEbgOeF2GhCrxa8gEYPkesxjSozgslp0RXdVQsoZv9XrV7CNf6ppQPCD9ntmXEYwG5RcQfDch+gJ1RWJwXrmHpHVhz7WV9eL5XPJTnUNGCyqekVjfUufR+sLD2CttODZrbuGGhjSD1+f43qKq9WOpK3czWdHsxpk866tkWSpI8iJR5QN5HhFzO65ViFj45LgetL6LyEUMibi9QLJBCOZ0Ld57IPNT6Rm/SecuunS8Ipz2lEFbeykXv8A5NyHEQv3y2j2p2x2QSnvNPK6UgWNZ6eMNOJCDh5GzEpDN5YSMsTMQqgEoBDg2LYpW4iVSZodTqKVKORh7IFzYaZQ4FzZ4sYxhWF0eHATpRypAAUkDO+mYmw1uXLE7O0FHp83Jte522cVbau8YrfiBjMoVmeNE5N7XkUhsg5DHySD5B9LWOYfMoatSJuV1dsZS4AUTa4Bt3QyYNiEqupUzZWZh2e0GLgC+pF+Rgd2BDs91ay2aP8AC09r+EzIPstTHyMgHnxyAdm8DkZUGfbj0enq/EcETNP5lOrKeORVh5WA4MeMA5I9AxlUofl1Ccw/8idfMXPEkR6dGaLfLRddZN7ptQ3OVg33aNcFP5KzuFH2+3qDpSrq109LtLlJDfqOvmAHifo0kLRPqv8AUmqIPFIsPAXaJj1Vasj0fsFcKljwlq4uyv2JMxEZx/BWLH74Un7ehfR2nM/EZKeCs3+3tfRoIdIKgU+Hzl8UlPirs/V4qZ02bDa13A0E990nc30nA8zI0cTSr7kC+X4SRjkQQQMMeJBz5wNMx7G6SlqRJqaUTDlBBUE6F9HBs/xeM06P4HVVVL1sirVLBUbJfUcWUL/Roku8fTJuNpSwNuHUXF9T33T6BhhWWRI0JLFZDKxxEC0hXHkcseThh+F9IaGdMFCKYIlzC2rgkhg4y7sA/dBLFuj9dJQa/wBJK5ksOLMWFzd9rljziIXrVW4Me3VvuNpu9TqK7axbtJTKCHVvolBcyEjhIRGpxHz5c1IAJBGVIoTVTkTaNKEye0VkuG1FgLuLtdtDeKM6orzSSVyqxS1zuyE5QC+iru4Y2e3EQQa3oW1jFoD+hqevjnhp2M6wiHipqOHH9Z3OXkYTmVwFAPDwAA6OmVManrlU5BIylWZzkd/VZubcd4KL6H1ApeoTU2BzgZQO23vO/J+G0Qmyat17fdoKzWFwvVTZ6zTzmOSnZCJO4TiFciRG/FPtyU9jK/IYjY+ic2nopVbLpUUSVCYHC3tl1JZiLC9jcM2oihJqa6ZQzKqZWqSqW4KcocK0A434ta/AxJ9oel7cbVNoTcMXGTS+oL6hY+1nkaNyCpdxMn6wBXC4PEcc+RhaWJ9I6GSo0PowmS0FtQA41YZTo5D738bWF9Ha6aBXqqVImzBezljo5zbgAttYQj3/ANkNw9C7c1F91LeJr7a04KYmaULKzOoVeJlZDg+7ypxx5eMZEmC4zQ1FUiTIo0oVftAJcMCXfKDy15RHjeDVsilmTp1apSWHZLgG4DNmI+EFj/R/3WKv2Ulp18SUdZIp/mkbA/44/kfS300QU14VxQD8SPpDF0LmBWHZfdUofI/WF3WCi2N7JrBMpPZbpECR9o5PdID+5u2qn884+/qDowrOKqlOi5SrfqGniMxMWukacppagaonJv8ApVr4FgD5R7dCMiSdOsBX6hPNn+PcP+WPVfpWXxFfcn/ERJ0VDYbL/q/yMF7cK2rftMyWqKOlvNxmQskVWOUcvArkMMOQPIUuFk7RZWKn6WXaSZ1U1MwqUkA3Uj1g/DTycPo4hkqECYgoISX2Vof38IH+idztJaHukOjqmhl2xuV0l4xx9lRDNIR80lg7kDEgY9zJL8uSDK5LVVHUVCVVInCcEi5zHMBzStlb7AjnrA2nqZEhQkdUZRUbBhlJZ7FLp23Y200grX+72+wWOW5XZlprZSRs8hb5Kiglif3Y/wB/oDKlrmLSiWHUSAG4mC8xaUJKllgA57ozt6Vbhp2y9RsN8uED2iwaiaoW3mT6UcycUXPyZlXNP4JxI4GDyBGy9IOum4aqShYUuXk6xtSGcnuJ7XcH2jIMAEqViXXrQUomZ+rJ01072t/9jSL1isbHGae/Vz0NV9UctYFll0LT1UK15j/VtP7+4fAI8gOGHiWRknMZ93L1tuEelJwtKXHXFKurfUJs2vg2wBQ8Yzi5pTiuYg9SFJ6xvVz34P47ntNGk9M8MtMr0+Hp2A48fkR9sY8Yx8seMesTLvfWNlHKKq1m5d1ve8FXY9UxCur7XN2kpwqus0MuWgWCN3xLNVBedZVyiOC300bKoTuSyB7TRy5dJLmyFMFDMVOQQoWJUQOylLshCXMxRBLskQpGsWupXKmpcpLZfeCvVCQSyipiVKUwQAQ1yRZHRVp01a7CraTSmorPU+9fhlRY3z+0OACsD9mGeQ+/pOqZs9cw+kKUVC3aJJHK9/CGSmlyUSx1ASEG4ys197WvAS69WVen5wfMjVMIH8eR/wAs+mfomWxBJ/Sr5Qt9Kk5sOWN3T/kIRdFNStiF80I/4c+nLrLxU+OMMniIj/8ALGNmX8wc/Ij146RfxfR6n35aXP6hr5OAYlwJpYn0+mSYphoyTceGrfaJFuhetO6s10uktVtNt9qC2yrNbqtWCiYlAJO27KYi4JaKoo5A/ej4uAwYGOpRpmyJJnyWmIUCmYgh2vZwLtoUrDMbW3u1JROm9VNdCkkFCg17XY6PqFJOov3AbcfUm9+ut0otK6c+C17XaEkSp7tOFjUu6ssRmElR21kA5ERI2TnkM49rNRy8NkUyp03PLE0FLFzYEE5SEuRpcjl3rdbNxOZUJlSAhfVspxa5BABdTA6lgeBiGbl7h797y6iOzV0Sn/pibDyR05TwEHMCWQTSRqo9rlSysW4D5sFYjRU2F0KPxBBVlFgVPqbWDAncefCwmvqcUrV/hykpCixOXYcy5A4+XGJPr3ZbqB1htxS6YqqO30lv02FaA078Zk7a4wrGobJf5t4y8gDZBAPqnS4lhcioXPEyYSt82YApLncZdvlaL9Xh2JzqdEnJLAQxTlJzDKLMSfnEZqOuDeK5aNBg+AWevkalURo/xXc4r7lj7x93uXi3baMyHiFyCotp6O4cmcxzsBnuRkZ9Hbkd3a7xTV0gxBUnMEozElDB8+ZtWf73iQWPp33209tRUaBgo7bU2i9NzlZ35Tc/bxPLvKoaLiOGFZAQT7izFq83GMNm1SaszJgUiwAACW4MzsXvd+60WZOEYjKpF0gRLIW5JJU7nfg42aEez27vUFaax9ptOx0lZd9KKVKVGBII0bAwWniV0TKiMqCO2UOSCD69YhRYUsCumqWEzC7p0c/0libu+7x4w6txVD0SEoKpdu04LbbhxwPBo89zbfv7DfDuJr2gRrVaado6j4eWKLvUpYM8btHPNN2yfr4qSqF84UsfXqjXhfV+iUs45lKBTmBLL0BAKUpfg+7bgR9qRinWCqqZIypBCgkgEp1bUlrP3ONzFpen/cAXSnW2TObhHXoZYH4sneRPbK8UPHFNQxEpBQhyJagK0h5ljNMkYnT5TmAZrEasdgVe2s3UtrJdreql4o54XYaEODe/EgeynQJ43LbmKdZFR+kF909oaHMtTebrHIQP7qHxKT+5RLyx9+Jx8vRDAP4SKmpOiZRH9StPk0C8a/iLppA1MwHwTc/OGrW1WdhOs6m1NN+DpPciIU0p88Uqo+KxMfBA5ARqvlQQ8zn6CfXyR/8AtwxUn25JzD+Q6j5k+A3j7OJpMQTNbsTQEnX1xptuLeZ2izOo9MWfWFqa2X2KK822X5pMqup/kwI8fY4yPStKmrlKC5aik8QWPwhjXLTMGVYBHO8Zoaw6xKrbbduYbQR0lj0Rb+cSRLGBDUsSOdQyxtEWdyoED88rEqjx3JFbUpGDJqaYenKUqYWLv2kjZPae17hte4RmFVjhpqo+iJAlhw2xPvdnXQMeHBzBi/0dTaXu9ZX6ouFQlx3NvEj842IWRYiweR1XALCaRg0rrmNSqLhSDyC9JlTQJclKCJKQGOxLMB4AMAb6neDfRpMpYXUKU85ZL6OA/wBd9tOEXQvd/t2nLVLcrm60NDQRmSRmOAiKCWY/kAAfP7vSKhClqCUhySw74dlKCQSdBGWmlNyrQnUpHvPcqT4HbutuboCfpilKAhzhsd1Oa1UgwylufbyyArrc6Qv0A0CZjzQgHvD6d1so8HYGMqkTkKxAYgZbSirK/BTa2Njv5teNWY5FlQOnvRvII+/rIY1eM/OsHVtHp7cGh3m29lipbzSTyU75Khqkw5TuLHy5SQeJaWWXCcgq8CUKSetGwRBmSZlBUglJAUP0vdn2OigO97uIQMcX1M2XX05AUklJf2ttNxqCfK0WH6Zepy1dTlrraCsiW23CicgxE8xJTSZEbHIAJ+ccwGQCAfAkUBZxTCl4cpBCnBGvBQ1H1H/oww4XiiMQQuzEFm5HQ/eGnZbpovO3ms6mgr3R9BUNQktNxLGep4jNOlQxZiYbd5+HiHFHlPeYZGGnr8VRUS0qSD1pBCtMofUpA3X7R4dnTT5R4cqRMUCRkdxq/IEkmyPZSLPfWGfbioG/PWLW60j/ABtLbfxGkgPni9Q3ITMv7OVBkViM8kML5wR6nqT6FhqKf25pzq/lGg8bEcC4iGQBVYguf7MsZBq2Y6nhbTy5QY+oXZa3797WT6UrCKeqk98LkZ7My57bfng5KSAYZo3ZQRnIBYfWqo56ZyfEcRuPtzYwXraRFXJMpfhyPGA7sxvhqPdDaa6ba3Ym175aZpJoWV/a0rhCsE6/ZgWKd1lymWWQARzRZK1lHLkT5dQkPIWQbbB7p+beWoLUaaomzZK5K7Tkgj7K3tz4xlvSxVVRcRaoEklupftiIKxl7gODH2wvc7gYcTHx7gYceOfHrUjNAGYkNq7hm4vo3PSMoNFO63qspzO3j+940u6WNh6LpM2yrN0dyStFfBTs8gHu+Ep1AdoxjPKaQgGQKWBYJGmcFpM2xXEFYlORTU90uw/Uo2e+g4PzJ4DTcHwoUEsrX65F+XIfWIZrvZap3yvdPQ3kyWXePWKNV1TB3aO1WseKemkjEiJJl1RVU8GlqhUTCQLGUNqnrxSJJQxkoOVNg65m6gWcWe+ycqSHLx9q8P8ASgynC1akGyU+61nB7tbmCDtJs/R7xdDw0U0UVvVu8KaVSxWeSKV+xWAlQ4jqnHdAGQ9O+E9jqooVVaqmxL0h30JFrAgOjvSLclDjFiXh6VUXopAZiN9fevfW7baQF+nTd/cjeayxdPccn6PzW8OKmqVh3o6CApG8MXEFe9yYQpUBn4RkMFLLzJfEKamplHEGzAsyfZKy5zF7tZ8u5tYQJwyqnzh6EqxRYqHAWAGz8+EGvrM6TbfrXaeGv0RClHf9HwhIkjH62ljHmAAeSYx76ce48uSKAZmYCcGxdcmeROUSlZck7KPtePteewi9jWGCrkugdtOnEjhFHuj286vp+oKgm0Khude7gSgZ4GlYgVBkYeFjVfcrHIEoj4q78Ed1xjqVUixPLDbjmGjc/o+gchJwNE9FWOrH821t/L5xoV1ab8V2kKWHbXQp+N3T1f8AhwqvzgjbIeZsfTgBu2xwF4vKcrC49Z9hdEmYTUT/AMpFzzPu89n8BYkRouIVK0JEqTeYqw5DdR5CCRsHs5bdiNrqfSNvxNJTLylcDHdmbHcfHkgE+1ASxSNVTJ4+qFfWKrJ6pyt9BwGw/epvFqjpU00oSk7a8zufGCH6Hxciv3Ut001W5dbDrrQcv6K7r2HzBMPAlAz+HL4bKnJUErIoVmR0ZGZfRmgr+oBkzRmlK1H1HP8AdixAysouuImIOWYnQ/Q8RDFsF1W2TWOpv0R3JgTbneWn9jxyqEFQR4Bhc5yJPmkfOQsMmGSZFMpkrcOMtPWyFZ5XEbciOXFu8A2j1IqkrV1axlWNuPMHcRYnUelrXq2kSlu6CvpIJUlCt9JeJg8RI+R7bhZFByA6q2MqPQVC1ILpLWI8DY+YtBAh9YBustkb9cDVWqmcyXPcWt5V9SoKdi2wDCU0RySGeLFMvuVu5UVNWiqRwBWVWJTlJFpYOUcVn2j3G/MJSk2iuZeo975cP2/lpONf7N1u4kAsE9VLp7QUSIvYoh2JJQuQyST8nYQMOK9qFKV8AhpmV+K1ZFSJJzhIK73VcDm2j8y/c8e1y84yuw5Q87e7KaC2nGdIUdNp+YxrGXiRRI6L8g8mDI/5kuzsx8sSfPrxPq50/wDNWVb3NvAaDwj5KkS5QZCQP35mJt6qRPFTt0+pDSu0l4m272MpINU7rXd2cxUcaiOOVj75ahk7as6k5kUupT+vliVlcsNPRTKgCfVrKZQs5N2Gwd/C3cCzQMm1KZSskpOZZO3k6iNPsOUTHpk6ZZtqZptaa2l/SzdjUHmonPkRg4zFF7VwgwoJCxhwiqsaRpHGkGIYh6Q0qUMspOg+p5+bObkkkyU1L1RK1F1q1P0HADYRYD0Fi/Heujo710dA13t6ddA9Qli/o3WkC17xAhJF9ssWcE8HHkAkAsh5QyYHONgMertLWTqVWaUpvkfD9ttEE2SiaGWPuOY4GAHFtJ1MdPA4bdVsO7mk4fpp7l7ahFBzxSXmgZiMgM80EEWFC02AR6Jmoo6n85BQrij1e8jYDk5N7xW6udL9RWYcFa+fLmPGFaddGsNIn4bcHTl6tFanzNGgq4iPz7hFPFn81Dvx/tH14/DZa7yp6G/V2T5XMexUKD50EfH5XhZ/9j2guzkUN7NV/Y+GXl/5+P8A1eovwxbtnR35rRF6clvUV5Qik65daavPw23mnL1d6x/ka1BSRgfn3MTxE/kpkjz/AGhj1L+GykXmz0Afp7R8rHxiU1Ci2RBPfb53hJJs51KdRHs3MrotqNJTD3U1s8zuDn2yS8pArKMBis1TTy+4NT4I9exUUdN+SjOrivTwG782ItePHVzpn5iso4J+/PkB3xYLZbp90H0/2D+itFQJbRIAHc+6WXGcc3PuIBJ4J7Yo8kIijx6F1NXOqVZpqn+Xl+33izKkolBkD7nv4wRfVOJ4710dH//Z</t>
+        </is>
+      </c>
+      <c r="AC272" s="6" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
@@ -25814,6 +26147,7 @@
       <c r="Z273" s="6" t="inlineStr"/>
       <c r="AA273" s="6" t="inlineStr"/>
       <c r="AB273" s="6" t="inlineStr"/>
+      <c r="AC273" s="6" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
@@ -25912,6 +26246,7 @@
       </c>
       <c r="AA274" s="6" t="inlineStr"/>
       <c r="AB274" s="6" t="inlineStr"/>
+      <c r="AC274" s="6" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -26002,6 +26337,7 @@
       </c>
       <c r="AA275" s="6" t="inlineStr"/>
       <c r="AB275" s="6" t="inlineStr"/>
+      <c r="AC275" s="6" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
@@ -26096,6 +26432,7 @@
       </c>
       <c r="AA276" s="6" t="inlineStr"/>
       <c r="AB276" s="6" t="inlineStr"/>
+      <c r="AC276" s="6" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -26190,6 +26527,7 @@
       </c>
       <c r="AA277" s="6" t="inlineStr"/>
       <c r="AB277" s="6" t="inlineStr"/>
+      <c r="AC277" s="6" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
@@ -26280,6 +26618,7 @@
       <c r="Z278" s="6" t="inlineStr"/>
       <c r="AA278" s="6" t="inlineStr"/>
       <c r="AB278" s="6" t="inlineStr"/>
+      <c r="AC278" s="6" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -26373,7 +26712,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB279" s="6" t="inlineStr"/>
+      <c r="AB279" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAgoNCg0KCg0KCgoLCAoIDQ0KCg0NCAgKCwoICg4OCgoICQgIDQgLCAgKCAsKCA8ICgkKCAgNDQoKDQoNCggBAwQEBgUGCgYGCg8OCw4QDw8PDQ4NDQ0NDQ0PDQ8NDQ0NDQ8NDQ8NDw0PDQ8NDQ0PDQ0NDw0NDQ0NDQ0NDQ4NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAAABgMBAAAAAAAAAAAAAAABAgMEBwgABQYJ/8QAOhAAAgEBBQQHBgUDBQAAAAAAAQIDEQAEEiExBSJBcQYHE1FhkbEIMkKB0fAUI2KhwVKCsgkVcpLx/8QAGwEAAQUBAQAAAAAAAAAAAAAAAQACAwQFBgf/xAAuEQACAQIEBAYCAgMBAAAAAAAAAQIDEQQSITFBUWGBBRNxkdHwocEisRUjMhT/2gAMAwEAAhEDEQA/APLkWhL4INkEAGyECRZCFYLqx0H3992dg3Ya2Lf7Y+uFvLXlXXThZt0HMhqTZ44ywCDYBMNiJg2AQoWxGrkABYjTKWAjadHOj7zSLFGCzMeHAcTwFBW0dSapxzMkhFzajHctX1Yeyp2oq7KqmgIA3sq5DjRsRqTSppwAtztfxJrZHRYfwfPrJk4XT2JrodS9SOCrQHPhnx7iMgNOOb/kavA1V4NQtqyvXtU+ywLsDe7szsoGKVGGdAM3QjuAxOh+EFhoQdvw/H+b/rnvw+DD8R8M/wDMvMhrHj06lVwLbphhlWwClcArZCaBAsgoLGLFjYhytgOaCAWI0m32doUSRnbJmQgHupmPliFbZGNbehoYGynfiXp6lo1wLlvYitPGtf8AqfDh5W5esnc7rDSSgT80dBXCakd3P6WZl6Avd7kV9afRZ5YmxpSMqwOKgoCG7/A0Ph32fRvCaklxFXyVKMoNrVHkTfLgUdo295HaM80JU/utu+b4nm8NhFRZD0Y38WAmDSyFYyNfSxFFW3DEWA5oL2fqLG43KSx1cXwKFPxFSoByzBIHyp504gWy8TrcsYbSZaPqJkvqlO1a8o07Hso7vFEXMe7vvNfJEuiKFkDYXxSuI37ONsLWzMtOT3Wm7bNuLrRjpe72SS97vQmrpN1p3jZ0sSXme83tJpBCxmMP5VXADg3S7XZMNSBmAcGIkgg1q1HmbycOXH3bL+Hhka8zW/HTT8L0Ful3Va16vIvKMrIImrHeJL0yFsNFCJDfIbvgpmcSSk1OamxoYiEYtTTv0t+1d+43GYGr5ikmkr8m7rpaSS7pnnl7T/VXJc9oPiCiK8MZ48JJwikZdDUVrG74Qd7GuE4q1A6LB1lUpJ8VoznsZh5UZ67Su1/TT6/K7RIq/fna4U0rbgFfSyBbTsC0dlcOUKD6WIwNWwH+g82TfVWRHdcSLNG7KNXRXViKHIllBFDka2DV1YKlZptbNP1Sd2WH6z1DJHJGzSXZMEkTkE5TyzxGNJcNXWOOKF3Ds7K840UgDApxcW093dNeiTv95HS+I5ZNVIu6Si0+jbVk+ltuqLOezn03MqRoScYjoe6i0XIeXhmMrZtanldzWwdWNSKT3sI+2VNCUhgEsRLLLI5Eh7UzLgEUZIimRIMRZ5WzYGJFphLGzsLGMW5a8Pbj3Bi5Zo2bSWttbO6tbno+L9Od1JnQPr7uUa3e73h0R5LrGHzEkQnAXSWKqBippRahV7Oue6rJxV7pXJViYzX8pWfBdvYqX/qTKPxt0aMhonuUkqFcw2J0qQRqCgSnI23fDWvLl6/o5nxSTlVguj/vX9FQh/NtUyQtcvl9LEbw7Bi3f4ff/lgOu+IEcPpZXAoGGP742NxOJjp6iyuBxO46LdJZ3u73LF+VvXlKjfWVAlArVIwMFCsKE0AAIGVqdWMYyVS2vzoWoznKm6Sejv66apLp8krdAOstxd1RX7PtAI2dD+bGHjCtRlGKu+hBGdaHPIirVw6c7tbfkZRxco07Re/4Jnv3Q26BYZS/aRtE0j1iUzRFRvHG9YcJAw1pUGuEkVtk+a22mvTU6SlRoU4xqTvK+6v907nZ9Wl02Xe5+wRLzGwqCXaID3X0WOJRiWpq+bEhdciYK8strpa+pehiKFdOEaSj1V/llWPam6RRzC7YTXslMSAjSMpG5zOYAkbBhz93hTe3fD4uMX2OVxUlOppw0/JACR+v1tq3Kijcxosvl9LK41xaQZo/QWFx+VC0K/42BJFf0Cy62AWtzOzH7iyFZHV9Vuz8d5UaAkoSOGI0HmAxHfhtWxLtAlw6zVEvuuxtunvQue5uSBijLiQEZgYSGAoAHGedQRrrqCKFaNVKMtyli8JOhNuOx0/RrrZeYLFJuLGlWAJGJCysQwYA4VY1yxAqorUuBZTwcVdrd/gjj4hU0jLZfkkHZPXUiOkt3ULJEEnyyxCEFZnbMjsgUYHCRgUFSpNKU3gru0tvti8vEW/+N/jcrf0r28ZZSxYsBugmoUmlWZUYkqrvVsJzAoCcraqSSsiGmnq5b31NPEvqf5sSWK++4Drl/Z9PGyA1p2BaP0HrYBsOEj7/AOj7/awuTJWWvIM0OvIWFxzjvboFijFcNdGBP6R9T8K6t4AEiaEHIo168aSstXy+Tour3p3+GlOJMcMjKWBoHxI4dXjNRhdDpiISVC8chXEHhkr4ZVI24rZ/JmYbGyo1HN6p7r9r0L1XHofdr5DHOmGaCUChGhGakMCKh1YFHVsLKwZWAIIHMZZU24y0Z2MqlOvFTi7pmjvXsy7Mjcs8KuSCQDkDTgQpAoanyPK0ka9TZNlGphqd7tI0nWnsm7Js29/hIYrsn4R0pEoXHhQsxLJmwCpQAkjzNrNDNKrHM29SKtlpUp5EtuRSShw4siK1yyOfnbfeHXBmDT8QltKPtoFhvq8cjnqOfO1eVGSNGljaUrX09UOEoRkQdw6HlaJpp6l2LhOP8WnpzDPDryX1s25Jk37CmH/CzRz1v6CBnLNhWoWhBYCtCAaAAVqcWEZZ92W8LVOlxkZOLxtm4U+7+Pn2Fk2XlvboUjAGJDHXNju1bES2ZIUs4GWRupGE3cftclYU3csstDzpXPlZyI2dt1Qddd72bIexKyQO6tJBLXspKUzUjejmwKEWZMWQXHHKqKq16+GhWWu/MmoYmdF6bci3fRH2i9m33Cgl/CzMcJhvTBDiagAjmyhkqclVWWVqisS6WxKuDqU+F1zR0VHHU6qs3Z8mR/1u9duzmhvFzgWd5muk92BMYWBJZNwlmZw1BGGZTGrg0pUcbWGw8pNT4JlfGYmEV5fFrtyKedn7yn/mOXEfI+W9bbOdRqZLhmB40HL6jXlYNDgx2aQww6moHMAnyIBrZsop6MfCpKDzRepvFaoDUyZVbztmVKeRnWYXEqvHXdb/ACMNtX3CoUe8y05Dv/jz7rKjDM7sjx9fyoZY7teyHXR250FPGvz+xbSRy51F32eD31/VWh50Ir/bnpYoQvDswA5r861Bp3aV0JoxY8TSlbEaxTaOwlK1Gh0poK6HPOnDgK68LOGM54bArVD7w0rWjD1568joXIbYfdEtkt2rKqsxZMlVauGSpbdUEkhGxVFapnWgsFuG1kaq/wANMTcYpC3ONmJ8qFv2sgjbpBdd3EPhIYcta5eFgxwe8wVKMOK1HMqR62Qh5eoaIij4aD5DL1paGrG8GXcHU8usnz0fc5C/v+dnwoOQoNLQ0V/FE2ObdaV/uh1+zFtasZ501wAOX3/H7WNgGzhqMjTPT9XGlf6uPGg4E5kjR2l3yNNDVgP1CuJTwz8NGxHI2QGM7xcQyhhwowPdwz8Roe8U+RGiSbMbGrpixkdnRK4mLZALh3ixY4QBmwJFDkLGwTS7e2OyXkxOpRnheNlYUKslDp5EEVBUggkGpDEuZqrhdcUQB1GOA80JH+NPKwCL9ErjWNSfgxqfAqSPWwWwWJlNwueO6o4sW3RlrTPXjVjoAQJbMfB2kn1R/9k=</t>
+        </is>
+      </c>
+      <c r="AC279" s="6" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
@@ -26480,6 +26824,7 @@
       <c r="Z280" s="6" t="inlineStr"/>
       <c r="AA280" s="6" t="inlineStr"/>
       <c r="AB280" s="6" t="inlineStr"/>
+      <c r="AC280" s="6" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -26573,7 +26918,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB281" s="6" t="inlineStr"/>
+      <c r="AB281" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAMCAgsNCAkPDQoNDQoQDQoLCAsKDQ4KDw0LCAoICg0KDgsICggJCg4NCwgKCAoLCAgKDgoKCAoNDQsIDwgICgkBAwQEBgUGCgYGChAOCw0QDQ0PEA4PDw0PDg0NDw8NDxAPEA0NDQ8PDw0ODQ0NDQ0ODQ0PDQ0NDg0NDQ0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAACAgMBAQEAAAAAAAAAAAAGBwUIAgMEAQkA/8QAQBAAAgIABAMGAgcFBQkAAAAAAQIDEQAEEiEFMUEGBxMiUWEIMhQjUnGBkaFCgpLR8BZUYrHhFTM0RFNjcsHU/8QAGwEAAgMBAQEAAAAAAAAAAAAAAwQAAQIFBgf/xAAvEQABAwEGBAUEAwEAAAAAAAABAAIRAwQSITFBURNhgfAicZGhsRTR4fEyQsEF/9oADAMBAAIRAxEAPwBODLx+i/phS6zYIku5rZ4Sei/pi7rNgqlyzWFfQfpi4ZsFJcs4cmCQAoLEgKALJLEAAAbkkkAAcycaus2CkuVquxPwLgxK2anZXIBMWXVRpv8AZMkqyBj0OmIAG6ZxRxRDdgoCShjve+EFsvGZMsWmRRcsbhTIAObKY1RZAOZQIrACx4l0Laxp0ChJGqrz4CkchX3DFFrNgqly8+iJ9kfkMVcZsFd5269+jL9kfkMXdbsFV4rx8uv2R+QxRa3YKSV4Msv2R+QxV1uyuXKtZzgFeU4VhOys2z49MSApKsT8PHwfZziMcc0jnK5Ei0lYapZl2poY2pVRrJWaY0aBSKdX1DLiG4aqxirwd2vwj8LyRjeOAvmFIZcxmHaWQOBXiLZWKFqJ/wCHij5mgMLmTr6YLc44DvqmRxfj0cSks9e5b/XAnPDdfdEa0uwASj7V/E6I2qJ9R9H8wP5nV/Cw+/GRXe3IpoWRrh4wqld4fYvK5nOTTDxIGkbXJFlpFSPxD80ipLFM0ZdvrHUSFS7MwC6jjRtBOYHRX9K0YSh5e57Lf9fNfhLH/wDLWK452U+lbupDLdzHD1R3nzWfSNQWeWOfLgIB1McmRt/QAToWJAG5GDU64Jgt79kGpZoF4O9VXObtH5m0ySFbbQWtWKgnSWVXdVYrRZVkcKxIDOAGLV0JIlaJOOn7b/mf54kKpXNNOemNKKwHwc9wC8R4jrnTVksuFkzKkeWaRy3hZc7UynQ0swvdEVGBE+MuddHNV5r6g/TlUegHIDagOmEyYR0rO9Dv5WFSqeaTp7e5wBzynKVC9iVUTvC73Z5ZCCzSSncRodIUHkWO+kemxJ6CgSBDc5J8N/qwYpXcbymZA1SFUQkDeTwRZIFWxMknzAUWIs7AXgjXNP8AH4lW+m5mLo6mP2v3EeDvFCsisATyt9K/iWIQg/4vwI5iU3BzoKlejcYHAJg8KH1Jd3CIq65XbYKoFkk8v8/a7GKgkwEtOElI3vL702zLBI7XKqbjU7NIw28aQdP+3GfkG58xITospCmOa5lWsahwyQEowVAXsoxAojiPuwnvknvbjG7jljiNX0H+CTsr9G7PrYAklnzMsxU3emQwJv7RZdBtVG+pOFquBRmeLFFXeX24Ko1HzdP6/XCLjK6VGmM1UTvM7YsoAXzZiQkR3vXq59lsdRZoWNV4tjLxxyTNR9wQMymD3Dd2KPApIJck62O7F73Yn358qrYAAADj2mqb91egstNraIdCaHaL4Z18CQl+YuRpNJsLZC+ZdlWyQAQASTzJOIx9QZHBWDRebrhie9Ur/wDZWWiy6hoHeI2DQGkpy1l5miGknZfDErHooBBwWneL5Bx72TdRtNjAwiWnPLAbmSkn3yZB5hCsckcOSI1RRsxBZ4zR12Bfh+UIg2UnUSxKeH6Kg0ROuq8J/wBA3HgD+JxHfJK+Pu6r/mof4sHLeYXLD+S1t2AX++Q/n/riXRurv8l6vYSP++w/1+9iro3UvHZDEpN9cDRV9FPhK7UD+zOTF7q2bRv3c3mCL9yjKfx9xhargYTVFt5RPeTx2y2+FgJXSBuiAtXdP2bjnyssigSzqwjeLmAzuVAdRZbVG4dCVpQvlIIc45tpDmu+O/NensJpVaAGE43vc49IhMvs/wAKXKTSIi6VDIQG5hXW9JBuippee4A58yhUkmSraBdgZIy7acVEuUl8O3k8J/CQmgzhCQNwQb9wd+h5YI2LwkpctcyYhLQ91oGX152cFyFKJApIHMizMJNddKVdh1HLpUXUw7XpH5WCXFv9eZdJHsR/qpn8RHZ10gyDMyN9ZnlTwwdJR/obK/n3B8jBlN0bAJC3jvUwIJGsLyVrJvBs4CY6/pJcSbYshJLnKjG1SyiGKUXSMx7jF3VUp6fDP3yiDxcvI1JI3iQMTsJtKoyEk0NaohTYDWjCyZVGF6tIkSE5Z6oaYKZPartNerC4bCac9L7sJ2nkg4pFJHK8TMGjZkNA6606gfKwDDYOCLb3xmsJpnlii2N92sNjgec5KwGXkndZGklklkeyzsRY00KoBRVCgqAbHbrjjtdTOBEL1NajUaJZ6Iu7v+OmOYBwxQfKWINE6KYgtYN61A3vfppGI6iCZalOM66Q8QiHvI77cpHE3iKGuxpKhtxsKXY+hBI2G/OgWKdCTglDaeGMVQ34nO9CPMzZRIxpWJZjIo5a5nSlIH7SJCLsCvEqlOtR6FghgC8zaXh9QuCS5kxqEtKwdsWoskm5YqFcrYEb7P8ARxMFSO+zvczmJI1ZtMSnVpWQN4h0mr8PSoAPNS0gJFEAhhbLaDnNnJZLgMEUR8OzUYpp0kjA31KfEFA7AE71Q+eQk77DSLXdQGqKKpyWKTkeG2rynS9adLLpogMTqB8ytutV5edi64TQpxXCPX0VrO7LiHjwAqRf7Q9xsa6jlYHPoaIx5C1UTRddPTmvptitLbTTD29RsVL9q+PQRxsWJZ1GycrI5Ak7DffbkBhaleJgKq4DRJVNe9DvIld20ynYt4jKFFWCAi7aufmDdCgF7kY9xYbMAJeF86t9pkww+iXiZK2IVhexGoUKJO+oauW12N9XtRfqWWD4T+ly2V72YUn/AGIzFClRj0VWAJrqA4QH8Dv0vAzZKmkHyP3hFFVq1dlcmxzQRo1LfWIVfYBgjc61bgjbb+eFYgwc0Q5Sonh+rWooDoT99jGDELYzTr7reyqRwrOwUzNZyoNDw0Fr4tMNOtiG0FiNMekq1vs9ZqcDiHPTy36/CzUP9Qu3jfFOo+U/OORu/ShvexIC2T5huTIZztkOAuHMKHthuATrF7ijzN8x1u9r5dSE4qohQkAYoQTyJ39joo/cCBt/LAgFklQ/DO2M2WmlkiLagiQgKSdLeJ4xGkOFvkh1ofK8gG5sVUpsqC68SEWlWqUnX6biDy7x8k/pu1xz2Tg0j5hrlDAFgy7sh6bFSt3yIPpjxwomz1i074dcl9CNoFroBzdRj0zCrD2q4zJLM/iG5AkcaihYigdmC+VUutWi2BJBHmYace9bgV8yIwXb2e4IbIPtz59Rz5/sjb9N8bc5RrUZQuAD6ilu/S2P3cunXFtetXVP5eZJGiLIC6ElJAKcGiNANrqWjTK9qp+XSQCpnXaw8Qx31/SoS3LJKLj3CTHmZFYaWD3XPYnUCCNiCpBBB5HHn6jSxxacwug2CAVYLjeXCGtTFVAVb0yUFAA8oWOYbblkkcnnpa7x2nCMPz+UDmhbjeTDIxUi6b5eTCuXqDtsGVTYGxO+AkKIb4fn2VtQFjr7jrz5+h/94CCopqPKqOn1bDyGrAvav3SN75gA9RjSq6uTKKoZ1cAScpKNFh0ksEH5WBDAjZfc4wtpm92WZGWg4gDJD4phily0jSI6p9LIiGtoQ+gI7RtIrKzKS9hiBfFtll4too7TBjYeL4ld7/n2zgWauNQAW+bvD8x1Kr92f4aTJXzPr+tbmNMTMoogAkEguDQ1arocsehe6ZXmGNyCM9AAkYcvlUn7Z5gfcL/E+2K0RIjEKFy8hLhBz+Zidqrck/ddfiNjjOSmaN8lkTpARSOmqQDpvshmjeutOAd7N2bZZOnfusuChe3nYOeSPxBpdkHmCKUbw1s/KGkSTSSzeRwwXbQ4AKjtVndUbxBmPj8LVJ8G7v8AKaPFuFylbJYCrA8I7Dn1VWH3kH3J3OGXNd08loEZID4xwCUKWAatyxUalI9SFUFD6GMH3Q3YTJG60WOjIqD4UTJ5Y0MpAUVEviMCQpqk8WtmDAqOR+7A3EDNW1pdkJTg7re4jiE08KHKSxQu6+JLKjIEWiWepaJOkeUaRqbSDXNQ8dolNNs7zEiArd8K+DvhK6S8BmdQVMmYkYgjewY4jHE4s7KY69t8J8dzsck/9Mxuk+6JOFcL4VP9Iy65aH6sKuYhky4iIRvlYJLGjFCU8joCpZNjYGIS5sP9DPcHlmiCMWa6jlp5j29Ep+0nwO5FWY5cyZdmOrykzLYrmszFwNtgkqj2w22sTmlXWZmJbgk92j+DLOBwI3gdAdjrZDvzPhlTv1/32/qOhuKNkqbI7Q/I+67+PfCBHChZZ5fH0rUjoPBZ/KGVkhM2ZhXUfEDBpzojCU7sqyDNdk+IEc/utfRPAvAg8tY/1Q0Pw08R28kZXlaSA1Wx2cIwo3drYII02Dg/1ABgof0j3CQR30R1wj4Z51WzJ5/RJWT9AAp/iIOGadtYDiD31WX2F0YEd9ExuCcYy6tWrxJNy8laiNPRA3kUEg6Qi2FYEknc8GraqlQ3n4DLPBdmhZ2tY4MI8InmZIHWPhN7Jdm4gn1hVm3u96v9kaieXL3rfHJqWhk4JmkKi7ci0KilVV/8QF/yrARaUxwXFZ8X4tpSwQBRLG6of0euN8UkGCrpUhexC7mzUaxFifKo267gbn1J6D8ed4aDmgXtkG7Uc66NUB8WyGXimOezIVMwsTRRh30iPLllk+sAIjLakD26t4XyoQWctttSG+LXGEQ0g50U8hILt/wlxwj4zeHyzGMSMBZVHdHQO3+FnVQR7g79MbNoLc24LQsYd/F2O2XvkeiNZ+8fLgAoxvnsb2rnvsPUnoMMMtDHBAdZqoMOQ52m738uYnuQFaJe9wRpog3sQeRwnVtAIICYpWcsMnJYcE7eCONUJNqAGss1GhYuRm2BJ06GKaa8MldOLrWgsIGsD1QLNQD2TpJjyldbd7cZ6i8BFtRXWTZf/9k=</t>
+        </is>
+      </c>
+      <c r="AC281" s="6" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
@@ -26664,6 +27014,7 @@
       <c r="Z282" s="6" t="inlineStr"/>
       <c r="AA282" s="6" t="inlineStr"/>
       <c r="AB282" s="6" t="inlineStr"/>
+      <c r="AC282" s="6" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
@@ -26757,7 +27108,12 @@
           <t>live-verified 15 Jul 2026</t>
         </is>
       </c>
-      <c r="AB283" s="6" t="inlineStr"/>
+      <c r="AB283" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAgoNAgoLDwoLCwgIDg0NCgoOCwsKDgsKCg0NCgsKCwsNCwoKCwoKDQoIDw0KDQgICgoKCAoLDQ4ODggKCwoBAwQEBgUGCgYGCg8NCg4QEBAQDw8QDQ8NEA8QDw8PEA4NDxANDQ0QDg8PEBAQDQ8PDQ0PDw0NDw8PDQ0NDQ0NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAACAgIDAQAAAAAAAAAAAAAHCAUGAwQAAQkC/8QARhAAAQMBBQQGBgYGCgMAAAAAAQIDEQQABRIhMQYHQVEIEyJhcYEUMkKRofAJI1KxwdEVFiVTcpIkJikzQ2KistLhGBkn/8QAHAEAAgIDAQEAAAAAAAAAAAAABAUCAwAGBwEI/8QANREAAQMCAwUHAwMEAwAAAAAAAQACEQMhBBIxBUFRcbETImGBocHwFDKRUtHhBiOi8WKCsv/aAAwDAQACEQMRAD8AN4vc+igmcJ0PC3RVwUrVqb6GGMUEgka5wCqPgeVsWKX3e32DfLI5qIPnP52g8S0hWUzDgUkf0hN6Yb3u37SG6kDxKmAT49nlxnVIsl2ke83kfZbv/TTZZV5t6OSYuanif+OBUe8K+dURW8DguegktnQDMaxquB5DPh+Fsheys6aEY+MYjyzgfHMWjCkuNKThTkOOpj599oqS6ZfGJAkamM/n8PwtixZqZ4YUic5Vx4Gf++AnyNvVi+qdY7OY7JOvLMjQR88LYsXqNe20mG69chmkgyDKpgGB9oZRlpwtvq4QVgotr2hhCwpYWlRIySeyCFpQQcSSBPakZKGWs4shTG7y90o21QhJVgD0DEQVYSrIkgAHySPxOLEj3TgvVxfSBeQT2aVPVoGcAFbjhPIFQWmTlOFP2U21naBmtyA/ddK/p9gbhJ3lxPQBAktgJBJk5E65Zie/Qn78rLua2XVRNXfXD2hHDQpUVEc4PzzFJerg1aJqVKe4xJ5mJ/K1JfwVzWXvZXLZDdv17kBefeoJ+GthHPqbkfTo0t5KJlL0X5Z/vEz4q++w5fV/UPwmAwtA7iuf+Livtp1+0r4ZcbZ2lUbwvThKPAqvbSbgltMlWPIZ5LBjnkRP32m2rVHBDPwtHcSmYvvbiKVYkQcoyJwlkuZGJEkA+yeHEi3UZXzjlJHzxVipr0xV7ClKhpbWEwRj7QWhSkyIySSRkoKISgSZj0KJCmrg2nDe1bqxDvo4W40TI+sxDCowoEpSVAxi7eGDrAxRSudKK8A5v5q3YMlFOtSciApymZeITkDhBcMAlRyOZyA1nGGazvCOgXUNjDLgqfjJ/wAiPZL3eV8S6MgRxSZznMg5gwZ4EKEa2UPetkYxXjdru261PWL9Tifn4nWyupVzHwTqjRDddURl0V3tsEFvFGp010JMHCDGSlFtJ4E2iw59Fe/Ky7lBh5kq6xDcNJiVpWlYSVEhOIpK0ZkH/ESZyiSBaNWnUYJnoehKso1KNQ2HoR1ARk3ZLUtyCSUjgbCjMdUeIBsi5tLsx+wpHZUBM/Pzlb0kohzYEpbtsm1F0JwqdccnCjSQnMnwA8PKZtEMquMAodxYBJCPFPtCyjZQUziEvBJJjCMKkqECVlRVJSRmGkqThIxQQT2AgGy+Wg4i4+X+eaFd87RN+mrKDhS2QEQtRLYgZBZOPhElRJ4zaOYfheljpFtVati6k/osxnNOYGpiEmRHAQeXPnHoMiVEiCQgB0l74H69ufaLVJj4HF6HT5HSTGvGBHC2r49wFV3zcF1HYbD9HSngf/TlUdym6tVZtASZDLUYzxJOiR+J4T321+qZW5YZg+5Odd+6pCbmS2lOFAyy+ePPWwpg2TNgIMqKd3TYG3EpbStt710zhM8FYoJxA+1kbTDg1pA0VjmNqfcuXNuzi7i11SUtrIKgFlSlkaAqhMAZ+rGpOpJNfaEDK0ABTbRYy4JJVyuXZBKHU4UgRA8AMszqfEmcrDkq+m0k2RlvTZEfqqk8TGXdxsGKsuTF1MxCFu1W65BKXEpGNGhEggdxBGXdY5jzuKWlkWIshZv8lq+VriErCSCTCVKyxQcIzHGQTJmIOfVnuytJXzFRZ2lQN4/yhVe9ar9S0hTWEuLxhRSPagJkySCQePaAREQTYR7jlkiJTSkwCpDXSAI/Hz+UWt3GyS13UoKcSylhnCVqSpaSsBXZTGZMNlRAlQTCsOYsY3utAKVP77yRoT7pUekRdakbynJOLGE9rOCWx1CoJgnNqcwDChItqe0m5axPGD6R7LqH9P1M+Da3e0uaeck+6NPRGYSi5HMwStQV70hMeRSba7UdK3rDsDSRyTbXbXpDcWGJTVjV1UUyVaWrLiieyCxJu2GybQzLOzAX1s/ThVUeSfvHyLRcTFlbSAm6MlPSA3CEz6osBBlHzCpbyAKxSNIzA7j+Rn3WKa6LFClt1g3B7fbOfoJFLeFI09epqcKesolPkF5SQwOtKFITJEjtDCQVczbpWObiO0LqZOUDjG69pXz/ALEfg20Q2s0doS4fbJIJIAJjSDFzvhHffXsnsjd1FTpq7rokt1JX1KRd6Xk4mgnESEtqCCA4mCYkE8jZTSOIr91riY8f3K2mu7B4I9q9oaTaQ258JAnyUbsLsHcV3bpKm+nW0PUtctVW0osYg3SVLijQU9PTKlLZQzUNJKiEqKlrKihsBDZL8RiKrxRaYIsYMSQLkmb6Jc3Z+AwrHYl7AQTIkB0SYAaIsL8LTEwFq7WdH7Z+9tmLtvZmiYLbVSh0oLKW0PNOvJp6xupYwltSgMS8WAlblOjtlC8RGqF4caVcyQOZBiRB4Hf0lHYfsXU218GAASAbZQRmgyI1F4PrBQz6Qu56gpOlVcNNTUVPTU96dl1plpDSHPR6lgKKkISlKiWqlYJIkoQBoBCio2Y5rZqNSJJN49reyKfTC3cUlNsCw6zTNMqL4QstoSglKmnVwYAylsedqa7AGggI3AVXOeQ4k238wuukRsbS02xdAlunbbedP1i0oSlSw22ArERBMqUkmTrBtDENDWiAiMBWe97sziR/KXy+K7+jmNbLHJ+g5tjvxVSLQ0hlbi1E4ggDF2iTihRAIGXEDnabSCcvgqH5mjMBN1MXT0kXjUEJSsqSkkpASMUeynEQkKJgZqAHHKTasCXZVZ2ttFZdgN4z9VdAdcYLLrKiFCcUA5kFUJCuGYSBn32rdqRwKIaLBB5rePj3n3amB9bX0kqIMk9aiBPsiBkDrhHhbr2McBTPn0K+Ydi0nVMRbQX/AMhom5+lrvApoLmz7JXV4u8Btk590ge6yDZz8rzyW57eoipRba4NvRTW/muP/qjol8Td91EwOKkU3jAz8haqg8/UFzhB73Qo3aFIfS9mNAWa+DmpZtzvTyqKTdI1dgpmFMIJxPlaw4EuKFQspHqFaQtYQPaKUjU2Oq4YVnl+a5i3kEhwm0DhaTaJZ3QTf/s7d4c083SS2RLnSq2PexQlp+vQUxOJRpPSUk5gDAKRwg5nOIhSiEzACx0nSCOnv+OZW4ukPaQOMneBbTzi1uM2ANk6T+Go3OrH7urZa8FKfFL7/rh5mwFYS3zHVM8K7LUnwPSVQOnHeX7doEfZQ8r+dTQH+w2HxR0TDZlg48vdLvRqR1cqUAO8x38dbKTJKfZwNUKd6u0tP6fASFOx6wjICIHOTOnD3ixNN2VB13A2ahfcW2uG/MMAFIMkCZUOCj7+J58rElw1hAAumJTE7r981Ou68CxhUMlECADyUOGUc5J8rLqjZNk0o1wBdK9suAd4NzrCsSV1tGZBnNNWlHkIw+c+A6bj3TRkHf8AwuC7EZkxWUiDB6Snb+mbqim5riI/f1M5TIwMkjz99kOHcWutxC3XGsa+mQ7gfZXjflV/2UVAomcV33RJPHEilBnxnnxtfhn5sQXcc3qCqdo0x9MWgaFvo4JTd3XQuaf6Ez9/GsdQ8wzVu+ihtBQo0PWU4QVk4wHBTpKuzKVLMTGdoxLmVA0DeOgVI2cxzQ6TMdXF3vHJep9HdqKumuKtgK6n+kIVrHpNC81iB7w9E8ld9lSd8EGuj5tOq8thL6bOfoe0LzY72aavpqtB46IyPMoJ42rLZEK4PgyOEekKg9N3aD/7YhucmqVryUt18k+YCPdYDE3d5JvgSAw8/wBkku8rbxxV/FtAUUNjRMEknUxz4TrmdDYJze6i85c6FXk1z5RCKJQmO25GZHdOXuVnnxtNlEngFezKdVJ0lz1qllXojIcVEuGNP5TzOiBOhtcaR0Lh88kUGM4KUqNj64UBhinJ+0FqbOXghU6ngJ58h3Mb+pUvb4KrbvbhaTtfdqS9hRSVLLilqgQ2mqbeJV6ohIHaVkEgzHC3TquFBpGmCSYJHHivnvCbSIxQruaACQDewtlmb2334a70yP0tm+e7qy6boRSVtJWuMO1PWoZfbfU3iS0ElQQolMlKgJgEgjhlq1MFroi66PXLXU5LoHHdH7In9Gzf3s/fHRAZuOurEUb9I0zSONuPJo1q9EKRTPUzrmFtbkMtFbI60tuBSHEKbWhTvoDmOzMn1/B8tV6XNqMh8CRxG/Qjz0PoonpUb+bhunogLuC7qtureqUqpgG3k1habqHSusfqnkK6tLrgcfCESkh11OFvqmlBOAOzhxnUKTntazuxoY8vl4Rw6K/S1uJvozXO07fF3s1FPRUzTrK6thC21sMpaUhaFLCkqGDQgG1EIgFBf6NzpC0LOxd6O1lXTUaqupbqCXnkMhTlQykOBJWUglJbSDGY7MjtAknFEBzRpLQl2zgTTedQKj/ITPug/wBK/fIxV9IqtdYqGnqVHUNMPNuJcbdSmnbcWpC0kpOF1x9BhRhTagcxFk1YEuWzUC0MF7oX7HXWk324o9pwxPdOndn5HOeNhHiEfSgkq13pTuhrsg90WpJKLiFUqTZu8VXnkheHxPwzga8zmkaWhNtFgzE/circd1VCWAlSFlQ5kfGLVgq4JWaC9v61Kk+wCB35Ax4jWLdbbUHbGeHyF831aB+lGX9Rn11VfWtxO0C+raErWpSickqClE6yY1mcjM5ayF32VD2bd55Jx/aq0B29SwaAANQQOHwRv0WLa2l6ypKBjacVI0SAv+I8UwIBxxnBzgWjiR2hyiWnrz/2pbPf9O3tDD2i+8lvIcZ1ETw4qa2Y2GQ3RwtRc/yknCn+H2vDNI7pzsXh8GGCHmfDcOSWY7ar6z81Fob47zz3dearG127JwPqcaMo1KMkFIiDAACVJiZACVGdFTZficA9pL6WnDSPZPdnbbpPApYkQ7jczwkmSDw1HiFsbm9q/wCsLlM8cTFckJInJLiPUKeAyxA5ZnDytrmKLrPJuFvuBaxs02ix6rDt3s+9SX3IP1ZMpz4cvAaePxg1wqBWVKZpHwV43Mb2kfpchZCVKg90nM/f+OuVq6tKRZXYevBgpjKffNSdcEyDPGfIfPI2XmiYkpoMQ0mylkbzGw76wA8R4j8vmbVFqKFQBYb76RlOmiKYBX36Qde8nXnmeJEWlTw5cqKmLDUllLfI/TpVnmiO/IjOLdAbVHaT4LjtTDHsAz/lPhvWWnv1Qr9ZSTpnlw8j4Ejn3etrEO8FB+FYaekGFPXzev7NVn8yLG1andKUYWh/dHzcom7trcJ7RhABmfZgT45xpnnkLC08Tl+7RMa+zu0+wd7r84qtXrvIccqSlPYa/wBSvE8B3DzJE2Cq411QwLN9U9wmxqWHAe/vP9ByHufwqvVVJTWocT6yCCD3gyPLKyus2QtjouIMpmqa8EVGyyCRIcTl3SMx3EeVkglphbPAqNlBXandWtFVLZkDONDPIQI8PjYttbiltTCx9qi66+HUwMC04e6csuIkcFyRnJBA4C7MxyFyPbuWRnb6owDJRzyyJGHWPEfHytDKwKzPU4FbFBdtW/WgJQsg+0cgAQDMmPVJmZ4Rb0vY1RFN79y//9k=</t>
+        </is>
+      </c>
+      <c r="AC283" s="6" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
@@ -26848,6 +27204,7 @@
       <c r="Z284" s="6" t="inlineStr"/>
       <c r="AA284" s="6" t="inlineStr"/>
       <c r="AB284" s="6" t="inlineStr"/>
+      <c r="AC284" s="6" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
@@ -26942,6 +27299,7 @@
       <c r="Z285" s="6" t="inlineStr"/>
       <c r="AA285" s="6" t="inlineStr"/>
       <c r="AB285" s="6" t="inlineStr"/>
+      <c r="AC285" s="6" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
@@ -27032,6 +27390,7 @@
       <c r="Z286" s="6" t="inlineStr"/>
       <c r="AA286" s="6" t="inlineStr"/>
       <c r="AB286" s="6" t="inlineStr"/>
+      <c r="AC286" s="6" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
@@ -27125,7 +27484,8 @@
         </is>
       </c>
       <c r="AA287" s="6" t="inlineStr"/>
-      <c r="AB287" s="6" t="inlineStr">
+      <c r="AB287" s="6" t="inlineStr"/>
+      <c r="AC287" s="6" t="inlineStr">
         <is>
           <t>US (country music heartland)</t>
         </is>
@@ -27216,6 +27576,7 @@
       <c r="Z288" s="6" t="inlineStr"/>
       <c r="AA288" s="6" t="inlineStr"/>
       <c r="AB288" s="6" t="inlineStr"/>
+      <c r="AC288" s="6" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
@@ -27322,6 +27683,7 @@
       <c r="Z289" s="6" t="inlineStr"/>
       <c r="AA289" s="6" t="inlineStr"/>
       <c r="AB289" s="6" t="inlineStr"/>
+      <c r="AC289" s="6" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
@@ -27428,6 +27790,7 @@
       <c r="Z290" s="6" t="inlineStr"/>
       <c r="AA290" s="6" t="inlineStr"/>
       <c r="AB290" s="6" t="inlineStr"/>
+      <c r="AC290" s="6" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
@@ -27530,6 +27893,7 @@
       <c r="Z291" s="6" t="inlineStr"/>
       <c r="AA291" s="6" t="inlineStr"/>
       <c r="AB291" s="6" t="inlineStr"/>
+      <c r="AC291" s="6" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
@@ -27636,6 +28000,7 @@
       <c r="Z292" s="6" t="inlineStr"/>
       <c r="AA292" s="6" t="inlineStr"/>
       <c r="AB292" s="6" t="inlineStr"/>
+      <c r="AC292" s="6" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
@@ -27737,7 +28102,12 @@
       </c>
       <c r="Z293" s="6" t="inlineStr"/>
       <c r="AA293" s="6" t="inlineStr"/>
-      <c r="AB293" s="6" t="inlineStr"/>
+      <c r="AB293" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/4gv4SUNDX1BST0ZJTEUAAQEAAAvoAAAAAAIAAABtbnRyUkdCIFhZWiAH2QADABsAFQAkAB9hY3NwAAAAAAAAAAAAAAAAAAAAAAAAAAEAAAAAAAAAAAAA9tYAAQAAAADTLQAAAAAp+D3er/JVrnhC+uTKgzkNAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABBkZXNjAAABRAAAAHliWFlaAAABwAAAABRiVFJDAAAB1AAACAxkbWRkAAAJ4AAAAIhnWFlaAAAKaAAAABRnVFJDAAAB1AAACAxsdW1pAAAKfAAAABRtZWFzAAAKkAAAACRia3B0AAAKtAAAABRyWFlaAAAKyAAAABRyVFJDAAAB1AAACAx0ZWNoAAAK3AAAAAx2dWVkAAAK6AAAAId3dHB0AAALcAAAABRjcHJ0AAALhAAAADdjaGFkAAALvAAAACxkZXNjAAAAAAAAAB9zUkdCIElFQzYxOTY2LTItMSBibGFjayBzY2FsZWQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAWFlaIAAAAAAAACSgAAAPhAAAts9jdXJ2AAAAAAAABAAAAAAFAAoADwAUABkAHgAjACgALQAyADcAOwBAAEUASgBPAFQAWQBeAGMAaABtAHIAdwB8AIEAhgCLAJAAlQCaAJ8ApACpAK4AsgC3ALwAwQDGAMsA0ADVANsA4ADlAOsA8AD2APsBAQEHAQ0BEwEZAR8BJQErATIBOAE+AUUBTAFSAVkBYAFnAW4BdQF8AYMBiwGSAZoBoQGpAbEBuQHBAckB0QHZAeEB6QHyAfoCAwIMAhQCHQImAi8COAJBAksCVAJdAmcCcQJ6AoQCjgKYAqICrAK2AsECywLVAuAC6wL1AwADCwMWAyEDLQM4A0MDTwNaA2YDcgN+A4oDlgOiA64DugPHA9MD4APsA/kEBgQTBCAELQQ7BEgEVQRjBHEEfgSMBJoEqAS2BMQE0wThBPAE/gUNBRwFKwU6BUkFWAVnBXcFhgWWBaYFtQXFBdUF5QX2BgYGFgYnBjcGSAZZBmoGewaMBp0GrwbABtEG4wb1BwcHGQcrBz0HTwdhB3QHhgeZB6wHvwfSB+UH+AgLCB8IMghGCFoIbgiCCJYIqgi+CNII5wj7CRAJJQk6CU8JZAl5CY8JpAm6Cc8J5Qn7ChEKJwo9ClQKagqBCpgKrgrFCtwK8wsLCyILOQtRC2kLgAuYC7ALyAvhC/kMEgwqDEMMXAx1DI4MpwzADNkM8w0NDSYNQA1aDXQNjg2pDcMN3g34DhMOLg5JDmQOfw6bDrYO0g7uDwkPJQ9BD14Peg+WD7MPzw/sEAkQJhBDEGEQfhCbELkQ1xD1ERMRMRFPEW0RjBGqEckR6BIHEiYSRRJkEoQSoxLDEuMTAxMjE0MTYxODE6QTxRPlFAYUJxRJFGoUixStFM4U8BUSFTQVVhV4FZsVvRXgFgMWJhZJFmwWjxayFtYW+hcdF0EXZReJF64X0hf3GBsYQBhlGIoYrxjVGPoZIBlFGWsZkRm3Gd0aBBoqGlEadxqeGsUa7BsUGzsbYxuKG7Ib2hwCHCocUhx7HKMczBz1HR4dRx1wHZkdwx3sHhYeQB5qHpQevh7pHxMfPh9pH5Qfvx/qIBUgQSBsIJggxCDwIRwhSCF1IaEhziH7IiciVSKCIq8i3SMKIzgjZiOUI8Ij8CQfJE0kfCSrJNolCSU4JWgllyXHJfcmJyZXJocmtyboJxgnSSd6J6sn3CgNKD8ocSiiKNQpBik4KWspnSnQKgIqNSpoKpsqzysCKzYraSudK9EsBSw5LG4soizXLQwtQS12Last4S4WLkwugi63Lu4vJC9aL5Evxy/+MDUwbDCkMNsxEjFKMYIxujHyMioyYzKbMtQzDTNGM38zuDPxNCs0ZTSeNNg1EzVNNYc1wjX9Njc2cjauNuk3JDdgN5w31zgUOFA4jDjIOQU5Qjl/Obw5+To2OnQ6sjrvOy07azuqO+g8JzxlPKQ84z0iPWE9oT3gPiA+YD6gPuA/IT9hP6I/4kAjQGRApkDnQSlBakGsQe5CMEJyQrVC90M6Q31DwEQDREdEikTORRJFVUWaRd5GIkZnRqtG8Ec1R3tHwEgFSEtIkUjXSR1JY0mpSfBKN0p9SsRLDEtTS5pL4kwqTHJMuk0CTUpNk03cTiVObk63TwBPSU+TT91QJ1BxULtRBlFQUZtR5lIxUnxSx1MTU19TqlP2VEJUj1TbVShVdVXCVg9WXFapVvdXRFeSV+BYL1h9WMtZGllpWbhaB1pWWqZa9VtFW5Vb5Vw1XIZc1l0nXXhdyV4aXmxevV8PX2Ffs2AFYFdgqmD8YU9homH1YklinGLwY0Njl2PrZEBklGTpZT1lkmXnZj1mkmboZz1nk2fpaD9olmjsaUNpmmnxakhqn2r3a09rp2v/bFdsr20IbWBtuW4SbmtuxG8eb3hv0XArcIZw4HE6cZVx8HJLcqZzAXNdc7h0FHRwdMx1KHWFdeF2Pnabdvh3VnezeBF4bnjMeSp5iXnnekZ6pXsEe2N7wnwhfIF84X1BfaF+AX5ifsJ/I3+Ef+WAR4CogQqBa4HNgjCCkoL0g1eDuoQdhICE44VHhauGDoZyhteHO4efiASIaYjOiTOJmYn+imSKyoswi5aL/IxjjMqNMY2Yjf+OZo7OjzaPnpAGkG6Q1pE/kaiSEZJ6kuOTTZO2lCCUipT0lV+VyZY0lp+XCpd1l+CYTJi4mSSZkJn8mmia1ZtCm6+cHJyJnPedZJ3SnkCerp8dn4uf+qBpoNihR6G2oiailqMGo3aj5qRWpMelOKWpphqmi6b9p26n4KhSqMSpN6mpqhyqj6sCq3Wr6axcrNCtRK24ri2uoa8Wr4uwALB1sOqxYLHWskuywrM4s660JbSctRO1irYBtnm28Ldot+C4WbjRuUq5wro7urW7LrunvCG8m70VvY++Cr6Evv+/er/1wHDA7MFnwePCX8Lbw1jD1MRRxM7FS8XIxkbGw8dBx7/IPci8yTrJuco4yrfLNsu2zDXMtc01zbXONs62zzfPuNA50LrRPNG+0j/SwdNE08bUSdTL1U7V0dZV1tjXXNfg2GTY6Nls2fHadtr724DcBdyK3RDdlt4c3qLfKd+v4DbgveFE4cziU+Lb42Pj6+Rz5PzlhOYN5pbnH+ep6DLovOlG6dDqW+rl63Dr++yG7RHtnO4o7rTvQO/M8Fjw5fFy8f/yjPMZ86f0NPTC9VD13vZt9vv3ivgZ+Kj5OPnH+lf65/t3/Af8mP0p/br+S/7c/23//2Rlc2MAAAAAAAAALklFQyA2MTk2Ni0yLTEgRGVmYXVsdCBSR0IgQ29sb3VyIFNwYWNlIC0gc1JHQgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAAYpkAALeFAAAY2lhZWiAAAAAAAAAAAABQAAAAAAAAbWVhcwAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAACWFlaIAAAAAAAAAMWAAADMwAAAqRYWVogAAAAAAAAb6IAADj1AAADkHNpZyAAAAAAQ1JUIGRlc2MAAAAAAAAALVJlZmVyZW5jZSBWaWV3aW5nIENvbmRpdGlvbiBpbiBJRUMgNjE5NjYtMi0xAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABYWVogAAAAAAAA9tYAAQAAAADTLXRleHQAAAAAQ29weXJpZ2h0IEludGVybmF0aW9uYWwgQ29sb3IgQ29uc29ydGl1bSwgMjAwOQAAc2YzMgAAAAAAAQxEAAAF3///8yYAAAeUAAD9j///+6H///2iAAAD2wAAwHX/2wCEAAMCAggICAgICQ8ICA0ICAgICAgICQoICAgICAgICAgICAoICAgICAgICAgKCAoICggICQoKCAgQDQoIDQgICQgBAwQEBgUGCgYGChANCg4QDRAPDQ4OEA0ODg0PDg8ODhANDw0PDhAODw4PEA8RDQ0NDQ8PEA0NEA0NDQ0ODw8NDf/AABEIAFgAWAMBEQACEQEDEQH/xAAdAAABBAMBAQAAAAAAAAAAAAAABQYHCAECBAMJ/8QAPRAAAgECAwQGBwUHBQAAAAAAAQIDABEEEiEFBhMxByJBUWGSCBRCUnGB0hUjMkORU2KxwcLR0wkzcqGy/8QAHAEBAAICAwEAAAAAAAAAAAAAAAcIAQYCAwQF/8QAOREAAQMBAwgJAwMEAwAAAAAAAQACEQMEEiEFBhMUIjFBUQdSU2FxkZKh0TKBsRXB4UJysvBDgvH/2gAMAwEAAhEDEQA/APKrYKp6KIiiIoiKIsXrEiY4rIBIkDBZrKwiiIoiKIiiIoiKIiiIoiZPS1vZLhcMvBvxJ5BEjAA8O4Zmex0vlXKuhszA2IBFaTnblipk2xjQmKjzdaergSSO+Bh3meC3rM/I1PKdtOmE06YvFvWMw0HunE8wI4pB3Y6A8Pi8NFiMQ0xmkvnLG7AAkA52uzE89f1qstWq6o8ufLid5cSSfEmSVbKyZPpaEAbI6oEAfYYeyeO6vRQNmf7cuImRxlEUrFkjI1BQEkLoMtgANf0lro/ttR9rfQfUddFMlrJlshzRuO4gHCIw3zAiGukvJdKzWSlXp023jUAc+AHQWuOJG+SBMz3Jx1OyrwiiIoiKIiiIoiKIiiJN2vu7Hicqv7LKVNwCrG9yL89FsV7jf2RUPdI4eKVmcPpvVJ8YbHteU39Frab69rY76rtIjwl97yN2fFZ3xzKgEcq4a1rD8N7dlwbn/sVB7AScQrGPgAAOhe+zsY8nEfipMmWLIi2JVuTMSCfxG+lviTpaScw8MqY8ab/y1RN0lAnJMgyBUp/uPyV1VYhVdRREURFERREURFEWk8yqCzEKBqWYgADxJ0FcHvawXnkAcyYHuubGOqG6wEnkBJ9lwbp7eix8mJiwbLinw2DbFOYSJFCiaKPKrKSHfKzNlTMQEN7ZlDQ9nnl2yWqzix2ciobwcXNMtbHAHi4zwwAmd4U2Zh5BtdktpttoBpgNc0NcIc69BkjgBHHeYjcUz96MSJGRnC2Q6EjMLm3MDmCBqDpUStZhgpwfUBO0lrcsQKZkjKZwUMqKRmQMgkj6nNEdHV1sLEHtqVswrG01qtqc4XgLgbO1jBLiOWAAPHHkoW6R7e7RUrIxpuk33OjZwkNaDzkknlA5p0VNCglFERREURFERRFBPTr0nY6CRocLmjSJU486JmZZH1yFyGWNQrx9awbM4GYEgGH86c4rVRtTrHZX3GtDbxAF4uImJMwAC04AGePBTDmtm7Za1kbbLUy+5xddBOyGgxMCJJIO8xHBV42ntaWc3meWa2oM0jykHw4jNaowq1KlY3qr3PPNzi78kqUaTG0RdotDByYA0eTQFZr/AE+t6PV9tTCxbPs+YBQQCcksBABNhzI7zbsNq4Bsle2zOhxUtT458VvM0Rw2BkSMmabDoZUTh5VJaRjJw2lLuv5Ajct1ojqa2DUqTbNppxXA2l7q2jhQr6bhy7cbEIGhaWKNlynI6cJRCtjGeqcigXVuVhyAr4U3SHtMOG4gwR4EYhLRjLXYg7wRIPiDgfumFuV6QGOw2VJT60g7JiTKB+7Lq1+28gl+XZtuT87LfY4a92lZ1X/VHc/f6g7lgtHyjmpYLbLmt0T+syA2e9m703VZrdXeWPGYeLExXyygkBrBlKsUZWsSLqylTYkac6nHJ9up2+zstNKbrpwO8EGCD4EFQZlGwVLBaH2arF5vEbiCJBExgQQlavor5yKIiiJo9Km+fqOClmXWRvusOtr5pnBynL7QjUNMw9yNq17L2Uv06xPrD69zP7ju8sSe4LYs38mfqNtZRcNgbT/7Bvx4XsGjvKqxtzpYxE2Fkw8l880l8SWAzgIwZEBCrlLNd5VyhbkAKoRbVyq1X16jqtU3nkySd5P+/wAKxtJlOjTbSpNDWtwAG4D/AH+Uz1NdS5qZ/RC3hGH3gwV7gTriMMWAvbiQtIo+LyRKg59ZhpWV6KJh4U17G3m4G9TzX0faHqzDsZGy4bKe8B8rDxRe6t+NnDsmxGIE+8r5IqkW2ZwmPZR96c2KvtZB3YYHzSvc/qLfKtClfYtH1KuivofCsryFWo9GfHl9mBCCvBnmQMeT5yJ8w7rGbIR3rftqc8yqxfk+5H0PcJ5zD/a9H2UG57UrmUA+ZvsYY5RLPe7P3Ur1vq0BFERRFWD0hd/uJi2gTMRhAqIwJCiZxmnbQ9bq8OEGwK2xAv8AeaQRnjlLWbZq7TsUsPF5xcfsIA75U8Zn5O1Wxadw26uPgwYNH3Mk8xd5KA9q7WzF8xJZmZnJvqzHMzE21JJuT3mtDW8rMe247C57NdD/AGrKJf3M3/TCYvCYpWZThsTBNdQcxWKVWdRp7aBk+DVyBhZDoMqSsd044BtonFBpMvrgxAbhPqBPxL2y3vYZrEdvxrdWZUoCz6MnG7G48l800XaW/wAJlJnpE9MeF2rtR8TAzGMQwwxlkZCcpd2bKyhlu8pGoH4fhWlL6tR94yo8mnCrf5fOi6lYH0U9v64vCk8xHiI1PadYpmHgBwQe7TvqU8xbVD69mJwN14Hf9Lj5XFFufVlmnQtIGILmE931NB+9+FYapdUQooi4Nv7XXDwTTtyhiklPwjQtb52tXktdoFmoVK7tzWud5CV7LHZjaq9Og3e9zW+ZhUC29vBNNmkc3ZmYsVCgXdmkY6C5LO7MSbsSTqaq0+o6o41H/U4knxJk+6tIGNYAxn0gAAcgBA9kz55tT237+dcFkiF43osIoiL0RZVqInXtnZM7YcYpReKOfgyODqkpRXXOOYV1ayvyLAg2OXN6xZ6homuBsA3SeRiRI5HgeYhec2imKooE7ZF4DmJgweY4jkZ8JK9GveER7TgB5TpLh7+6zKJF8zRKvxIrZs07QKOU6c7nBzPMSPdo81reddnNbJdSP6S1/kYPs4n7K5lWCVe0URMPp2x5i2RjH5BkSIseQE0iRkX5AlXIGvM1p+dtZ1PJdUMO0662OMOeA6B4StvzTo6TKdIkYNvOnhLWkiT4wqzdF25HFmVsTE7wskhVmR+EXHUXMUta3XtcgZlHhVcLQ9zW7O9WPs1IF21uTE6Ytj4fDY94IFMKpHFmUyNJd2XOWBks4DKy6EWNiV6rrXbQc5zAXb1012hryG7kyuIPCvRC86OIKxiiM48KzBRBkFIKKacbsgtuw86G4O10aYC+UBMOYUW4uCczq5vb8Q90X2xtAfoheDtabEcYDbo8cTP/AItWdXJy0KZBgUCAeEl94zywwH8qPt19t+rSwzgj7qWOW19G4Lq9hrz6ta3RqOo1GVWjFrmu9JB/ZbJVptrMfSducHNP/YEfuvo9lNgbEA6gkEXHPS/hVpmVGvxaQfAyqsPpuYYcCPER+ViuxdaS9uyoBHmsetLa/wDxgqrvTBOvWMjs6v8Am1WY6IgDZLXPaM/wSWMXH4fqf71A193NT3cbyXhOsDG7LGx7yAf41yFV43EriaTDvAXO2Ew37OHyj6a5aap1j5rGhZ1Qtfs7Cn8qDyj6aaep1j5poafVCx9lYX9lB5R9NZ09XrHzWNBT6o8lsNmYQflweQH+mmsVesfNY0FPqjyXRE8CiwVFHcoyj9BYV1Fzi6+d/Pj5rsDGgQBgueaPCtzWI+LKrf8Aq5rtFaqNziuBo0zvaPJOHduVCsmWwsYuVrcpe6p96HG3a1vgRs0PzVVf+l76LF41vwxK9WZVcE2d/wCCVeD1ZOc3suOyDsy1WTpapurWqyOpAuhjxsi9/UN8SrM9EzhRstrFU3SajIvbM7HCYlM5zMfYk+QcfwUVA+q1h/xu9B+FO2s0eu31D5Xojze7J5H/AJisarX7N3pPwms0eu31D5WTLN7snkb6aapX7N3pd8LGsUe0b6h8rRpJ/dk8rf4zWdUrdm70OTWaPXb6h8rTjT+7L5T/AI6zqlbs3ehyazR67fUPlbcSX3ZvI380rGqV+zd6Sms0eu31D5W3Gm92XyN9FNUr9m70u+FnWaPaN9Q+VkzS+7L5G+mmqV+zd6XfCxrNHtG+ofKd/R9h5WE/VlOsPsMeyb92rA9EdN1GpbTVBbIoxeF2YNTdMTvVf+lkisyxiltQas3dqMGb4mE7Ps2X3ZPI301Y3S0+sPMKvGgq9R3pPwv/2Q==</t>
+        </is>
+      </c>
+      <c r="AC293" s="6" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
@@ -27836,6 +28206,7 @@
       <c r="Z294" s="6" t="inlineStr"/>
       <c r="AA294" s="6" t="inlineStr"/>
       <c r="AB294" s="6" t="inlineStr"/>
+      <c r="AC294" s="6" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
@@ -27938,6 +28309,7 @@
       <c r="Z295" s="6" t="inlineStr"/>
       <c r="AA295" s="6" t="inlineStr"/>
       <c r="AB295" s="6" t="inlineStr"/>
+      <c r="AC295" s="6" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
@@ -28040,6 +28412,7 @@
       <c r="Z296" s="6" t="inlineStr"/>
       <c r="AA296" s="6" t="inlineStr"/>
       <c r="AB296" s="6" t="inlineStr"/>
+      <c r="AC296" s="6" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
@@ -28150,6 +28523,7 @@
       <c r="Z297" s="6" t="inlineStr"/>
       <c r="AA297" s="6" t="inlineStr"/>
       <c r="AB297" s="6" t="inlineStr"/>
+      <c r="AC297" s="6" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
@@ -28256,6 +28630,7 @@
       <c r="Z298" s="6" t="inlineStr"/>
       <c r="AA298" s="6" t="inlineStr"/>
       <c r="AB298" s="6" t="inlineStr"/>
+      <c r="AC298" s="6" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
@@ -28358,6 +28733,7 @@
       <c r="Z299" s="6" t="inlineStr"/>
       <c r="AA299" s="6" t="inlineStr"/>
       <c r="AB299" s="6" t="inlineStr"/>
+      <c r="AC299" s="6" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
@@ -28452,6 +28828,7 @@
       <c r="Z300" s="6" t="inlineStr"/>
       <c r="AA300" s="6" t="inlineStr"/>
       <c r="AB300" s="6" t="inlineStr"/>
+      <c r="AC300" s="6" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
@@ -28550,9 +28927,10 @@
       <c r="Z301" s="6" t="inlineStr"/>
       <c r="AA301" s="6" t="inlineStr"/>
       <c r="AB301" s="6" t="inlineStr"/>
+      <c r="AC301" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB301"/>
+  <autoFilter ref="A1:AC301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/BFT_Living_Database.xlsx
+++ b/export/BFT_Living_Database.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'political'!$A$1:$O$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sponsor'!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'israeli_tech'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'backlog'!$A$1:$H$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'nurture'!$A$1:$R$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'criteria'!$A$1:$F$97</definedName>
   </definedNames>
@@ -823,7 +823,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>72 records</t>
+          <t>74 records</t>
         </is>
       </c>
     </row>
@@ -28951,7 +28951,7 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -29164,8 +29164,16 @@
           <t>CUFI.org</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>https://cufi.org</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAATQUlEQVRoge2aaZBc13Xff/e+rfdlunt2zIIdIERxgUgqsikyjmWJFmU7ImxLKUnWElOk4lSceKnkgzKKrbJdKsUVW6QV0UopVtGm4EppISmKcZUB2rKqQtIkARAkSIDAYPaZ3pfX/dZ786HHECESFGTan+zzrbv6vnv+Z/2f8xr+WS6Xh//nnamjR48Y2x/F0aNH7H/M+8SbfcDR/34kmUpat67Kl/7yHcWdYrFu/FchjdNPrT/40E2jv3CTEvIuLXuffu/dDw8evf+D83KuuXrHHY/5/xDKw98TwCP3f7CoZTxjp+xzQT+8RWjxJ1qIr+tYPSuE/D0htCfQnwfxCQ0TSulfF4bMCPSnIhXfm9/aOt4c2zGS7uH+1K9/1X0zAMyr/eHRo0fsvJew3vWhr/YfuV/9hNDid8J+dExASRpW2XJSHzNMpycNc0QIAyHEb+s4TsQqUHEU/Fbo9/MqDm1DyA8PxiZusIn+VZDRfwR8/c0AuGoPPPqFX7xZGfym0uK7UutrhBQfSaQLQaYwpZzUiGXajhWFPioORRwFAEjDxHIy2jAdVOTH/W5V9Frrnu/WDa21KYX4vK34kifim6TkqTvu/torPyqAN/TA0aNHDGs1zIba8pVkl0D8hG3Z70ukR8JceTay7JQT+K7s1C8QRwGmlSDwemRLM3Rqiximg9ZaKBWSyU+YdiJDeepgOgq9uFO7KPxB62OD0P+EQAi0+CXgFa0RYmhWfTUA3tADj953ZFxL878BoZTGZCpXeVe6MGVJaUqlIgMgDn3c9gaZ4hS50gzV5ZPMv/WnGXRrdKrncTubZEszgGBr8WmENEhkSqTz4xqltNtep9da9xTqPqHVM7GWZsI1v361ufGGHlASQwj+hZTm/tLkwTCVG7Mb62dk6PeY2vvjREGfQa9OcXw3IxMHqS49h99v0W9vEgYuGk2/s4WTLjA6eyObi0/jJHNki1NIwxbd+kVRHN+n08VJu7p08pNx5GPAK7rofRu4KgCv64FvfeH910jDuhm0Y1rJ3yhNHRxPZkad5uZZ4fdbeG4DJ1VgdOY6es1V7GQeIQ1A09o8h2kn0BpUFCCkwcjEPnrNNdrV82RLO5jeeyvLZ44z6FZJpEvkKrOgiatLz8rAH5wNtfrZhG12Y9Vp3Hn3w/0f2QOmZU4pJR6wElldnjgYI4TldjbF6Mx1GKbN4vOPI6WFnczh+C5evwVaobXGctJorRBoTDuFYZh0GyuAJluawU7maFfPkyvPUhzfh+1kWHz+cYrje43ixAHdWH9xRgT9/6MiFcko/THg6R8JgF5YkI/oFzcN03LLkwdtrbFVHAoAjSb0XUYmDtBrreG2N3HbG0ThgDgKCL3u9lMkWscIaaCVQkiJYdiYTopEqkCnvgRCUNlxLW57HdNOghAYpi0q029xNi8+d0DFflPZYvGNlIcfCKFv3Xfkx6Q0PyuEmCmM7p5MFyat2vJJMTp3A4bpUFs+iemkh1CUottYJlOcIo58Rsb30qpeQABaK0wriTBMBr06ppVAqxitFYNujWxpBiEEUpporajseCvt2gXc1ga58gyDblU3Ns4to+JPxyI+1+45z334CkktL0NjmjVgOpUdnUoXp41+Z0soFQGCOPKJVYQQEr/fxu1sIA0TrSKkNOk21zCtBEpFQ8sDKg6x7CSGYWM5aQzTxnJSdKoXGHRrxHFIFPq0a+cxTAcnlScOfZzUiEhmCjtA/7GB8cVSUkxdyQOXABxbuM3UkcpaTnq1suNa5febRnF8D6Oz19NYf5Fea41CZSfd5jKDXo0de28lV56l11of1v3qBZqbZ+k11/DcJnEU0Gus0Kkv0do6R3PjZbr1ZUYmr8FO5vDcBv3OJol0kW5jFTuZZe7Qu3BSBZSKyJXnEYZhaM0zUbK1fiUABsC3H/g300Eq86AUciFXnp+2E2m7unRCJDNlsiMz1FZOYVpJOrWLBF4HtGZk4gD9bo1Bt0qmMEkc+ZR3vJVMYZzQ75POVZg+cBt+v0WmOIVpJUjlxyhU5ug0loiC/tCroUe6MAFKU109RXPtDG5rjWxhUiCECgcdX0ZW8IF3Xdvdd8v7W8ePH7+swQ09MGhUtdLnpGk5iVyZxvrLMgo9Vs9+l8VTj5FIFVFxSBwHZEd2YDlpus1lcqVpMoUJwsBFGCZSSnLleexkFidVIA48DMMiU5jEtFMUx/cSeD2EMC4p4PWb9NsbuO11eo1V/EGbKPTpNJbJFqcNadq3KMEXsfjwO995/LKQh+0qNOrsUGuq+1eWnfyYQCTDwKU0uZ9+p4rnNslXdtKunmffTUcYm72RTmOZpdN/wcBtYCUytDbOonVM0O9grJ4mDAa47Q0MwyYM+vR7NaJgQL+zhWFa+IP20HrSxEkX8PsdVBwR+j0sJ00qN47bWqUwuntoiM7mRWWED9x++/HoNSH07f/10Uo3dH9fCPnpXHnOicKBmclPkMyWSaRHAIXpZNhz+F8TDLq4nS0K5Vkmd9/C+PxNTOx6O5adGsZ9HKDiCK1iomBAFHmgNXHoIYBcaQcajWk6OMk8pelr2Hv4Lgpju+lUzxOHHtP7b2PPDT9Dr72OP2hjOSk8t9GSsVj+hXcf2tp/813uq8PI7IW9ICWMQKCNRLqgu41VQq+HNG08t0mmOEWndhGAiV23EHgd6hsv4fXqOMk8hp2gMLab0vQh4tAjjgK6jWVeee4RpDSQhoWKQ6Rhkq/sQusYy8kMQzIKqK+9QK40y8F3fJhTT3yZ6vIJVBzSrV1ESJN8ZR4hjHmF+kNp8Ls3jdQ/B1waiOTP3/3nHbT8smEllkw7Q+B16TZX2LzwNL3GMoWx3Rx65ycoTR4kkS7iJAtEwYA4DrCcNOn8BP3uFqsvf5fVs39Dc/MsoeeiouCS8mzTy/r6i6g4xLQcpDTJjkyhooB29TxCSMrTb2HQ2WL5zDECr0sUDBDSRBoWCM5bSnz9Pb/yh8FlOfDN+z/wFtCfs5zMnJTSjMKh20EzOncD5alD2E4GIQRKRVSXniWTH8dO5oYMtDzLyPhe9B5N6Pdo1xZ5/ok/JgoHIMByMggEWmtU6BP4LnSqJDMlQr9PvjLPoNektvI8xfF9bC09i99vAQy7OWBaDmHQPx1YZvczn1kQsPD9EJKxPoQpDhqW7UehZ6EVqdwoEztvZnTuBvx+i25zFRWHJNIllFKEQZ9kpkS2tAMhhoVBCIGdyKKiAM9tAhBHAU7SIDuyg1R+HCkNtFYYhk0cBQghht1bCJLpEsGgRWXmemrLJ/D6zSForZDSQsL7lQoz11XO3Assf78K2e43BJkpIe3/pFWc0VrhpPJ0Gyv4XpeJ+ZsYm70ev98mCj36bdi8+AyZwiRaxRTH9mLaCWDIPpdfeoJEpgR6SB0mdr8dISRua2O7Hzi4rXXCwMW0UzipAvnKPLWVUzTWX8JO5CiM7qbTuIjXqw+jQQg0IpRCPJchbF4WQjoojCkzulmgEkJItNa0ts4jpYGTKrBx/kkm5t/G2PxhlIqZ2P12iuN7iUKPXnOFM08+RKGyk+L4XgAsK4VpJwl9lzAYsHnhaUpT1zA+fyPNjbO47XUyxSky1hR+v83Si8dIr56mU79IdmQH/qBFc2OTOPKRhnkpfwQ8EXn6C7f/hz/vXVZGP/C+gx81hPhly0nLRKZsB4M2hdFdpPMTaK0JBm3atfPUVk6xceFp4tBDGtZwCitMUJo4gIoDtpZO0No6R3X5BFoItIqRhkUiVQDA77cIAxevV6e2fIJea43G+hnCQYfQ7xGFHpn8JFJISlMH0UoRhwPS+XF8t0UUuGMYWn/op976tw8+dupSFTI9Ff9ZUhgVFUX/zrASxFFAp7a4zSgTSNMmjnyCbaq8eOpxpHlsWE3sJJnCJPtv+SBzh36S1bPfQxgmcegRBYPh2dAHrek2lvHcxjA/tCbwepcYahQMAHBSedz2OobpkB2ZHnpBGigVoSElhNhry751eSeuUKXBM4Hf9SQiJaRhhF6HfGUXppOm3954Fc8HpSJUMGyIwSCkMejwzOO/z/T+W6mvn2F09nqEFridTYJBm05jmU5jCWlYxKF36Tk6Vq/WA2lYGJbDoFcn3B6SBAybYugp0A+EicR/ee9H/6x1GYB0S+7SWvzHKPBKvtfRTjJHrjTD6Mz1LJ85RiJVoN/d2i6try9ev8m5Z7+FlBZuc41kdhTTcui11y8pHav4iucBEukRBr0adjLH9N4fp772Ip3aBZSKUXEo0WLedjt54DIAUnjmhhA8APq05zaElcgQhR6dxhJTe34MpWKSmfIbXg5gGDZjczeSyo8z6FWpr71A6PV+6DkYluBMcZJg0GXnW+4ADd36RRKZElHooVUMQrxDSfs9xxZuu2yKNB587JS/9/BdJyfTdSOOw3dnR6ZobZ4VxbE9DHo12rVFssVpvF4drdWVdEBKg5GJ/VhOCh2H5Mqz5Cs7yZZm6HeraPUaHnZJ7ESWdGESaVhsLj5Jv7tFHHrkKzvpt9e03++cEJpPplOJb9z+q9+4rBNLgJtHT+9Rgn8bBX05bD55Wluv0GuuUJ48gNbxkLOLK6+RtNa4nc3tKgTbWzq6jeVhIl/Z/IxM7EdFPsWx3YzO3oBSEYaVBGDgtgRCd0VVfu/2j37F+8HjEsAThi9Qj2oVveS7rTg7MkO7ep5EagQnXQQhSGbK2E728rulQXn6ELnSLCqOqK+exu+36VQXaW2eZWvpOdzmGqBJZitUpq99jf4j4/uxnAz19TOsvvxdosDb9sgEXq+uo6APcFM8Hr/n9fBLgJ+756HFO+/52n8mUh/pdzbrppPSudIsvfYafr9NvjSL215nfOdh7ETm+1ZXMclMBSEETjKPaSWGhC9dwHLSQx5kGCQzJQzTIT+681WGF+RKsxTH9tCpX2R8/jAqjujULxIMOpiWQ3PrXKjRj2j4QELE33k9AJevVQzeHQb9cnPjJcpTh2jXFnGSBZZe+EsKY7txWxuMzb+N5vrLuO01tNbDvYaQVHZcS6xCiqO7qK29gGHY21R8uCMddKtcWoIISXFsL5mRabaWT1AY3YUQgvL0NfRaG1iJEZqbZ9FxoITgifTGxsO3L7x2mBmqvC0LCwtyKl2bFFL0Q9/Nmlai4KQKorpyknx5jkR6hNrKSQa9BqOz12E5KQbdOqaVBAFaRfj9NlorOrVFpGkjgF5rHSGNIcMUEr/fYubAv8RKpOnWlzDtFEqFRMGA+voZ0rlRQq9Ht7mC1trQmrbMJb/z1UdeeN1Eek1Wao149Iu/eJ9hJu4ZmztM6Pe2v1fUVp/HTmQpTR7EcjLYiQxbyyfwusORUen4Nf1CCIE0LEwrRaY4SXn6EJ36EtXlkxRGd1GaOkjo91k5c5x8ZR7DSlBbPkUU9v9IavE1hVhOb60tXckDr9nMPfKlO5Mg5+LQd+urzxujczc6fr8lOluLoCFTmCJfmaexdoZObZF8aZZCZScqjoijgDjyLw0xhmEPhxfTQQiJYZh06hdxUkVGJvZTXXqOwOtiOWly5TlMJ0199TRROEALqe6450+feD2lXy2vmfInmAiFUr8tBe8LBu0/WH/l/wW2k2Zk8iCWnUSpiEG3Rq4yRxyHqHhomDjysZzU9nJ/uOSPo2A4WfkugdfBcjK4rXUsJ0O7en57U1fFSRVIpIvUV57HH3SeBY6jdfIHm9ZVATh895fC937qoe89ubnvuNCsRIGrN84/HSFEPLXvVsJBl+bGy6y89FdM7Xk7vtdBK4Xb3iSZKdPeOk+vtUYyXcJOZrGTeQw7SXvrPJmRaYQ0qK+cQghJujDB+NxhtIrZXPzbIWFU6vNPb67/pBG27r194fgb8w9elcQ/KPfeW5F2X45rQUfF8V/3e1tjKg5HcqUZhDSECn1C3yUOPZobL2PaSfx+k25jGSktihP70CrCba2Tr8zTa60y6FTRGkK/R6Y4TSJdpNdap7l+ph1H/mmtQWj9nV/+jUdPPvjYuR+qPPyQNzTf/oNfcXrRhswnE9mI8Csa+R7TToTp/JiZKUyjtRKB16XbWBmy1O0ckIaFkyqSSBfp1C8O1zNKkcyN4qTyaD1cDPc7W39Ht78X29FHhGc6wutt3vlrD9euRvkfCuDv5PHPfSgdpMNflUKkkfqU1uJ/SCFL6cKkShcmpZ1ICxVFRJE/3FiEw2nKtJKYdnJYiUyHKOjTbSzTa62ilWqDPg5in9A8+dTW+scXrlBp3jQArRFf+cwvOReZC64dO1G2SfyJhlEh9FMgjximXTTNhG85acuwklIIiZBoNCIK+9of9HQcejKO/A5CP4USNwqhz5hYP+NHXtqw7cxP3/3gqR9V+asG8Go5dmzB9F8+d20Q+E1DMlDSekCg34bmdxH64yAOgXgBtAAOCMQpJM9prY+g+b+a6F6hjeuEkJU7Pvmn/1uIq3sb+Q8G4NWiFxbkI+Nnbg8DXYvG1fOpmvVxhL5LSnUPkTyoDT4rtf73kXSflHHmU0rop+6856Hjb+bOfwy5ZIRvfvl92UfvOzIOcOzYbeY373//tXphQcLw/cOxhYWr/mfAPxn5/0We01e51FguAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
@@ -29208,8 +29216,16 @@
           <t>CUFI.org</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>https://cufi.org</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAATQUlEQVRoge2aaZBc13Xff/e+rfdlunt2zIIdIERxgUgqsikyjmWJFmU7ImxLKUnWElOk4lSceKnkgzKKrbJdKsUVW6QV0UopVtGm4EppISmKcZUB2rKqQtIkARAkSIDAYPaZ3pfX/dZ786HHECESFGTan+zzrbv6vnv+Z/2f8xr+WS6Xh//nnamjR48Y2x/F0aNH7H/M+8SbfcDR/34kmUpat67Kl/7yHcWdYrFu/FchjdNPrT/40E2jv3CTEvIuLXuffu/dDw8evf+D83KuuXrHHY/5/xDKw98TwCP3f7CoZTxjp+xzQT+8RWjxJ1qIr+tYPSuE/D0htCfQnwfxCQ0TSulfF4bMCPSnIhXfm9/aOt4c2zGS7uH+1K9/1X0zAMyr/eHRo0fsvJew3vWhr/YfuV/9hNDid8J+dExASRpW2XJSHzNMpycNc0QIAyHEb+s4TsQqUHEU/Fbo9/MqDm1DyA8PxiZusIn+VZDRfwR8/c0AuGoPPPqFX7xZGfym0uK7UutrhBQfSaQLQaYwpZzUiGXajhWFPioORRwFAEjDxHIy2jAdVOTH/W5V9Frrnu/WDa21KYX4vK34kifim6TkqTvu/torPyqAN/TA0aNHDGs1zIba8pVkl0D8hG3Z70ukR8JceTay7JQT+K7s1C8QRwGmlSDwemRLM3Rqiximg9ZaKBWSyU+YdiJDeepgOgq9uFO7KPxB62OD0P+EQAi0+CXgFa0RYmhWfTUA3tADj953ZFxL878BoZTGZCpXeVe6MGVJaUqlIgMgDn3c9gaZ4hS50gzV5ZPMv/WnGXRrdKrncTubZEszgGBr8WmENEhkSqTz4xqltNtep9da9xTqPqHVM7GWZsI1v361ufGGHlASQwj+hZTm/tLkwTCVG7Mb62dk6PeY2vvjREGfQa9OcXw3IxMHqS49h99v0W9vEgYuGk2/s4WTLjA6eyObi0/jJHNki1NIwxbd+kVRHN+n08VJu7p08pNx5GPAK7rofRu4KgCv64FvfeH910jDuhm0Y1rJ3yhNHRxPZkad5uZZ4fdbeG4DJ1VgdOY6es1V7GQeIQ1A09o8h2kn0BpUFCCkwcjEPnrNNdrV82RLO5jeeyvLZ44z6FZJpEvkKrOgiatLz8rAH5wNtfrZhG12Y9Vp3Hn3w/0f2QOmZU4pJR6wElldnjgYI4TldjbF6Mx1GKbN4vOPI6WFnczh+C5evwVaobXGctJorRBoTDuFYZh0GyuAJluawU7maFfPkyvPUhzfh+1kWHz+cYrje43ixAHdWH9xRgT9/6MiFcko/THg6R8JgF5YkI/oFzcN03LLkwdtrbFVHAoAjSb0XUYmDtBrreG2N3HbG0ThgDgKCL3u9lMkWscIaaCVQkiJYdiYTopEqkCnvgRCUNlxLW57HdNOghAYpi0q029xNi8+d0DFflPZYvGNlIcfCKFv3Xfkx6Q0PyuEmCmM7p5MFyat2vJJMTp3A4bpUFs+iemkh1CUottYJlOcIo58Rsb30qpeQABaK0wriTBMBr06ppVAqxitFYNujWxpBiEEUpporajseCvt2gXc1ga58gyDblU3Ns4to+JPxyI+1+45z334CkktL0NjmjVgOpUdnUoXp41+Z0soFQGCOPKJVYQQEr/fxu1sIA0TrSKkNOk21zCtBEpFQ8sDKg6x7CSGYWM5aQzTxnJSdKoXGHRrxHFIFPq0a+cxTAcnlScOfZzUiEhmCjtA/7GB8cVSUkxdyQOXABxbuM3UkcpaTnq1suNa5febRnF8D6Oz19NYf5Fea41CZSfd5jKDXo0de28lV56l11of1v3qBZqbZ+k11/DcJnEU0Gus0Kkv0do6R3PjZbr1ZUYmr8FO5vDcBv3OJol0kW5jFTuZZe7Qu3BSBZSKyJXnEYZhaM0zUbK1fiUABsC3H/g300Eq86AUciFXnp+2E2m7unRCJDNlsiMz1FZOYVpJOrWLBF4HtGZk4gD9bo1Bt0qmMEkc+ZR3vJVMYZzQ75POVZg+cBt+v0WmOIVpJUjlxyhU5ug0loiC/tCroUe6MAFKU109RXPtDG5rjWxhUiCECgcdX0ZW8IF3Xdvdd8v7W8ePH7+swQ09MGhUtdLnpGk5iVyZxvrLMgo9Vs9+l8VTj5FIFVFxSBwHZEd2YDlpus1lcqVpMoUJwsBFGCZSSnLleexkFidVIA48DMMiU5jEtFMUx/cSeD2EMC4p4PWb9NsbuO11eo1V/EGbKPTpNJbJFqcNadq3KMEXsfjwO995/LKQh+0qNOrsUGuq+1eWnfyYQCTDwKU0uZ9+p4rnNslXdtKunmffTUcYm72RTmOZpdN/wcBtYCUytDbOonVM0O9grJ4mDAa47Q0MwyYM+vR7NaJgQL+zhWFa+IP20HrSxEkX8PsdVBwR+j0sJ00qN47bWqUwuntoiM7mRWWED9x++/HoNSH07f/10Uo3dH9fCPnpXHnOicKBmclPkMyWSaRHAIXpZNhz+F8TDLq4nS0K5Vkmd9/C+PxNTOx6O5adGsZ9HKDiCK1iomBAFHmgNXHoIYBcaQcajWk6OMk8pelr2Hv4Lgpju+lUzxOHHtP7b2PPDT9Dr72OP2hjOSk8t9GSsVj+hXcf2tp/813uq8PI7IW9ICWMQKCNRLqgu41VQq+HNG08t0mmOEWndhGAiV23EHgd6hsv4fXqOMk8hp2gMLab0vQh4tAjjgK6jWVeee4RpDSQhoWKQ6Rhkq/sQusYy8kMQzIKqK+9QK40y8F3fJhTT3yZ6vIJVBzSrV1ESJN8ZR4hjHmF+kNp8Ls3jdQ/B1waiOTP3/3nHbT8smEllkw7Q+B16TZX2LzwNL3GMoWx3Rx65ycoTR4kkS7iJAtEwYA4DrCcNOn8BP3uFqsvf5fVs39Dc/MsoeeiouCS8mzTy/r6i6g4xLQcpDTJjkyhooB29TxCSMrTb2HQ2WL5zDECr0sUDBDSRBoWCM5bSnz9Pb/yh8FlOfDN+z/wFtCfs5zMnJTSjMKh20EzOncD5alD2E4GIQRKRVSXniWTH8dO5oYMtDzLyPhe9B5N6Pdo1xZ5/ok/JgoHIMByMggEWmtU6BP4LnSqJDMlQr9PvjLPoNektvI8xfF9bC09i99vAQy7OWBaDmHQPx1YZvczn1kQsPD9EJKxPoQpDhqW7UehZ6EVqdwoEztvZnTuBvx+i25zFRWHJNIllFKEQZ9kpkS2tAMhhoVBCIGdyKKiAM9tAhBHAU7SIDuyg1R+HCkNtFYYhk0cBQghht1bCJLpEsGgRWXmemrLJ/D6zSForZDSQsL7lQoz11XO3Assf78K2e43BJkpIe3/pFWc0VrhpPJ0Gyv4XpeJ+ZsYm70ev98mCj36bdi8+AyZwiRaxRTH9mLaCWDIPpdfeoJEpgR6SB0mdr8dISRua2O7Hzi4rXXCwMW0UzipAvnKPLWVUzTWX8JO5CiM7qbTuIjXqw+jQQg0IpRCPJchbF4WQjoojCkzulmgEkJItNa0ts4jpYGTKrBx/kkm5t/G2PxhlIqZ2P12iuN7iUKPXnOFM08+RKGyk+L4XgAsK4VpJwl9lzAYsHnhaUpT1zA+fyPNjbO47XUyxSky1hR+v83Si8dIr56mU79IdmQH/qBFc2OTOPKRhnkpfwQ8EXn6C7f/hz/vXVZGP/C+gx81hPhly0nLRKZsB4M2hdFdpPMTaK0JBm3atfPUVk6xceFp4tBDGtZwCitMUJo4gIoDtpZO0No6R3X5BFoItIqRhkUiVQDA77cIAxevV6e2fIJea43G+hnCQYfQ7xGFHpn8JFJISlMH0UoRhwPS+XF8t0UUuGMYWn/op976tw8+dupSFTI9Ff9ZUhgVFUX/zrASxFFAp7a4zSgTSNMmjnyCbaq8eOpxpHlsWE3sJJnCJPtv+SBzh36S1bPfQxgmcegRBYPh2dAHrek2lvHcxjA/tCbwepcYahQMAHBSedz2OobpkB2ZHnpBGigVoSElhNhry751eSeuUKXBM4Hf9SQiJaRhhF6HfGUXppOm3954Fc8HpSJUMGyIwSCkMejwzOO/z/T+W6mvn2F09nqEFridTYJBm05jmU5jCWlYxKF36Tk6Vq/WA2lYGJbDoFcn3B6SBAybYugp0A+EicR/ee9H/6x1GYB0S+7SWvzHKPBKvtfRTjJHrjTD6Mz1LJ85RiJVoN/d2i6try9ev8m5Z7+FlBZuc41kdhTTcui11y8pHav4iucBEukRBr0adjLH9N4fp772Ip3aBZSKUXEo0WLedjt54DIAUnjmhhA8APq05zaElcgQhR6dxhJTe34MpWKSmfIbXg5gGDZjczeSyo8z6FWpr71A6PV+6DkYluBMcZJg0GXnW+4ADd36RRKZElHooVUMQrxDSfs9xxZuu2yKNB587JS/9/BdJyfTdSOOw3dnR6ZobZ4VxbE9DHo12rVFssVpvF4drdWVdEBKg5GJ/VhOCh2H5Mqz5Cs7yZZm6HeraPUaHnZJ7ESWdGESaVhsLj5Jv7tFHHrkKzvpt9e03++cEJpPplOJb9z+q9+4rBNLgJtHT+9Rgn8bBX05bD55Wluv0GuuUJ48gNbxkLOLK6+RtNa4nc3tKgTbWzq6jeVhIl/Z/IxM7EdFPsWx3YzO3oBSEYaVBGDgtgRCd0VVfu/2j37F+8HjEsAThi9Qj2oVveS7rTg7MkO7ep5EagQnXQQhSGbK2E728rulQXn6ELnSLCqOqK+exu+36VQXaW2eZWvpOdzmGqBJZitUpq99jf4j4/uxnAz19TOsvvxdosDb9sgEXq+uo6APcFM8Hr/n9fBLgJ+756HFO+/52n8mUh/pdzbrppPSudIsvfYafr9NvjSL215nfOdh7ETm+1ZXMclMBSEETjKPaSWGhC9dwHLSQx5kGCQzJQzTIT+681WGF+RKsxTH9tCpX2R8/jAqjujULxIMOpiWQ3PrXKjRj2j4QELE33k9AJevVQzeHQb9cnPjJcpTh2jXFnGSBZZe+EsKY7txWxuMzb+N5vrLuO01tNbDvYaQVHZcS6xCiqO7qK29gGHY21R8uCMddKtcWoIISXFsL5mRabaWT1AY3YUQgvL0NfRaG1iJEZqbZ9FxoITgifTGxsO3L7x2mBmqvC0LCwtyKl2bFFL0Q9/Nmlai4KQKorpyknx5jkR6hNrKSQa9BqOz12E5KQbdOqaVBAFaRfj9NlorOrVFpGkjgF5rHSGNIcMUEr/fYubAv8RKpOnWlzDtFEqFRMGA+voZ0rlRQq9Ht7mC1trQmrbMJb/z1UdeeN1Eek1Wao149Iu/eJ9hJu4ZmztM6Pe2v1fUVp/HTmQpTR7EcjLYiQxbyyfwusORUen4Nf1CCIE0LEwrRaY4SXn6EJ36EtXlkxRGd1GaOkjo91k5c5x8ZR7DSlBbPkUU9v9IavE1hVhOb60tXckDr9nMPfKlO5Mg5+LQd+urzxujczc6fr8lOluLoCFTmCJfmaexdoZObZF8aZZCZScqjoijgDjyLw0xhmEPhxfTQQiJYZh06hdxUkVGJvZTXXqOwOtiOWly5TlMJ0199TRROEALqe6450+feD2lXy2vmfInmAiFUr8tBe8LBu0/WH/l/wW2k2Zk8iCWnUSpiEG3Rq4yRxyHqHhomDjysZzU9nJ/uOSPo2A4WfkugdfBcjK4rXUsJ0O7en57U1fFSRVIpIvUV57HH3SeBY6jdfIHm9ZVATh895fC937qoe89ubnvuNCsRIGrN84/HSFEPLXvVsJBl+bGy6y89FdM7Xk7vtdBK4Xb3iSZKdPeOk+vtUYyXcJOZrGTeQw7SXvrPJmRaYQ0qK+cQghJujDB+NxhtIrZXPzbIWFU6vNPb67/pBG27r194fgb8w9elcQ/KPfeW5F2X45rQUfF8V/3e1tjKg5HcqUZhDSECn1C3yUOPZobL2PaSfx+k25jGSktihP70CrCba2Tr8zTa60y6FTRGkK/R6Y4TSJdpNdap7l+ph1H/mmtQWj9nV/+jUdPPvjYuR+qPPyQNzTf/oNfcXrRhswnE9mI8Csa+R7TToTp/JiZKUyjtRKB16XbWBmy1O0ckIaFkyqSSBfp1C8O1zNKkcyN4qTyaD1cDPc7W39Ht78X29FHhGc6wutt3vlrD9euRvkfCuDv5PHPfSgdpMNflUKkkfqU1uJ/SCFL6cKkShcmpZ1ICxVFRJE/3FiEw2nKtJKYdnJYiUyHKOjTbSzTa62ilWqDPg5in9A8+dTW+scXrlBp3jQArRFf+cwvOReZC64dO1G2SfyJhlEh9FMgjximXTTNhG85acuwklIIiZBoNCIK+9of9HQcejKO/A5CP4USNwqhz5hYP+NHXtqw7cxP3/3gqR9V+asG8Go5dmzB9F8+d20Q+E1DMlDSekCg34bmdxH64yAOgXgBtAAOCMQpJM9prY+g+b+a6F6hjeuEkJU7Pvmn/1uIq3sb+Q8G4NWiFxbkI+Nnbg8DXYvG1fOpmvVxhL5LSnUPkTyoDT4rtf73kXSflHHmU0rop+6856Hjb+bOfwy5ZIRvfvl92UfvOzIOcOzYbeY373//tXphQcLw/cOxhYWr/mfAPxn5/0We01e51FguAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
@@ -29252,8 +29268,16 @@
           <t>ICEJ.org</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>https://icej.org</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAKlBMVEVHcEwZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2gZN2huN/T+AAAADXRSTlMA8dAO4LohSnY0YY+mWp8LSgAABntJREFUeJztWYuO6ygMLWCDef3/7+6xgaTtndnbSacrrcTRaNImBBtjH9v0dtvY2NjY2NjY2NjY2NjY2Nj4nyHJ/BBCOO+eXyR9Vn5xrPKisCfyrUBuKE0/s2RVonX52xxvINTeK6zQXDdQMaX8+OYYq9cR4W/zXJbfIKbcZIrvNY77sc4bTm4JD/lDGkTuOrlMaS2fj/KyiZiSHD+igE7tUhmifHlYZig8bFAyqQafkF9sfoHDwfvSH1YOSX2RqBbV4AOeGNXVuErOOX6zxyHimVS1BeWvh7wB23ovpTLX/KUGIeuzMoLiV00QRUKwaT2N8PuSbfIIRxojYyj1l8wQW3Upr9j7Vj74wZ9jesqV/C9EQ1Tvd3D+c2r+dmGxnaNEw4Ftgrfkcww60Tn1XfzFVKRWKekQEsphBFZGcCF8r+5LEHgTw6dr942ZWz2EIQXQ3BZH7dAqpGoDuVeYwGOC+o58uJ6P0pADWhIu54Mo1F2T4W/SqJPc2TpxSxU5oVVMQO9sQlHuqzWDdz2mOoyfYRVkv+K8w5+EDH38YeuA9fvcepamvlu+nvsVBOUURL6HGXSpR9J3EKrqcfYEZRD0Qcgdsa+vSfS+Nc1N/npustgrkM3i3Uy+Kr97DcToKEdPMXqniwcNLA0S9oeUEasq4K7XKGLpB/+dR1gvXhFnnh3YlZsqgBRs6S/y0gBjU4LKQ4HrrBhG/mMqORZ2czOTG0vSABkKLFeH2x9DuMRcvE9Kne3qHpgLeNGFar4fvKacjFosZqLbUuCGTYjIhn26vCYu19Q0FieXncAUYN9uto5pydpFYA3nOpeUEsE8CcUAvjuWFfXGmzBU8/yWAroF1GcNMgqtTLiGXJSfT941dTRHNjccpY0KLTnq75RoVuv5OuTHeWv4tHRduVTnlItzmUtP8xpHgVSNqa5zofnwWOgsdQP5cfXDrtMH4AUz87GbA4fa9u96GAZ+zkB5Lie7udKlwGmZJe5IzhddQJTcrcZASCWZk8iTnEOBZ82QrJKG7qjOUJz8VAskYd11bAKnUGitok15zcVHBSLxvDEr4uBdQaGKOtY84scpKVoVAAXAIuhElgLHVs8bhwJwinFdT5AQ1BgV3KQe6a4ogMjX95WQj2VRNbh5bc618YncvK6c2WwCDQtj9J/WJaaABxOMTmNt7H3V9w1WITjEJrCA1ek/rgosALCHZSSEpYBX+jMCtGtZH5KneV1bYDHMSNn24eehYH1ARbdNd6s69p7prz5g1iLpTU4e/wnGHrTeHhLqoto6r2cUuDZfa2us9XIo5q7tgJ5FaLnZTY/z5ky463ookKaS6W6tJrlr6equlARHH37f6J180x4VqD0/XG0QrRkunlmU1YjF04B+BDTKoThkDO0CjZS3coV9jqtZu1oSZUtmPqd2dhcybY/MX7QDAEehW5A6LV/OHcio400Df7VHjEweFU3SKhsGX26PiIhoSrQIIG1EPZGWBmhO8l1QYDO88yE5dA3tYrOuZWVNUABSGqqyONfITasfBlPHoGV5iGjc1BaurTOygMHgD4ICRZy/2BpEIwBsbtU4PIwL30ZJGKJ5w1hyIMKN0o6coYNFfY/JDjYu7gF43aPWKRlRpD3WCv3BiyjGw1BACVvvZHcMUeoSh5cFNqKLQZA8l8KVWEMrnQlBefhmh4YyFCij8E60GFsDGEmwV3a1lcT+Wk0UNYCsrqGR21aeQ5GsBQqMUlQBOJp+E3dmjJE/7dWkwXxxC3SCljHBnOyottAO6qkoSKB4Qj5K2hD3Y525D22tg20PTPozWHXPGcFcwmN5G6v2PgFGV5RQtC442EqGAgkUMg42rhJRsLKcSpxJ+f78MVc0oDzOBywC76w8xhZn1utvtGarum+ZiZ8UgAqFJ9cTy8Mmj7GIoIeO4hLCOBqieRT8fAKrJ5NfnFvO86Q29GtvyNd6+shoOtdrL92dlXUnl+0/kcW71Qa+2GPNPI7XvPzKWWWEpZM22i/ySdYMmLA3v3tqj1h4jdHAXe/t+7dAkebLX6YOYCT3xrnYvwOTP/9S8af4F+10DRYU/J0KEO/Avh/7zcoQlVy8fLERUbQFrJ/Z/XukcXT1JCiO46gP/2w5McjJ1zqTjNRxFHOp+r+ExA/ENImH/5vlG7T6kLJ+Ogq5CLrzzzrfM9KTuT/9o/WfCP/6dWNjY2NjY2NjY2NjY2NjY+N1/APY41EXgR5gDQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
@@ -29296,8 +29320,16 @@
           <t>Arab Center DC, Dec 2025</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>https://fozmuseum.com</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxAHBg0PEQ0RFREUFRYSExAWFQ8WGRkWIB0WIiAdHR8kHTQsICYmJxkUIj0hMTU3Ny46FyY/RDM4ODQtLisBCgoKDg0OGxAQFy0mICUtLS0tLS0tListLS0rKy0tLSstLS0tLSstLS0tLS0tLS0tLS0tKy0tLS0tLS0tLS0tK//AABEIAFQAVQMBEQACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAABAYDBQcBAv/EAD0QAAEDAwEEBQcJCQAAAAAAAAEAAgMEBRESBiExYQcTQVGBFCIyM0JxsRVTYnKCkaHD8CMkJZKTwdHS0//EABoBAQADAQEBAAAAAAAAAAAAAAADBAUCAQb/xAAuEQACAgECAwYGAgMAAAAAAAAAAQIRAwQSEyFBMVFhcYGhBSKxwdHwFGIjMpH/2gAMAwEAAhEDEQA/AIOV9cfAUMoKGUFDKChlBQygoZQUe5Q9oZQUeZQUMoeUY8ryzqhlBQygoZQUMoKGUFDKChlBQ1IBlBQygoxalyd0NSChqSxQ1JYoaksUNSWKGpLFDUlij3Ugo81IKGpBRi1LyyTayRb6WS4VscMYy950gfrsHHPYuMk444uT6EmLDLJNQj1LDW3CLZqtdTwQQyPjw2WolYXlzxxDRnDQDu8OKpwxyzx3zk0n2JfvMvzyQ0s9mOKbXa3z5+HcbC47R0F62el66BrKsDzNDeLuwh3Y3vB/E4UMNPmxZVtdomy6rBmwvfGpdPPwZRta1TGoa0FDUh5Q1oe0NSHlDUgoakFGDWubJaL70SUYnutROR6pgaORcTv+5rh4rN+Izaio9/2Nb4XjTnKfd9yl3KoM9yneeLpHuPi4q9jVQS8EZ2X5skn4sja1JZFQ1pYoa0sUNaWKGtLFDUlihrSxQ1pYoj6lzZLtOwdFkdLHSVPk80kjz1fW6mBgG52NIyfpdqxta8jkty8jd0Ecai9jfS7KXVMs3lUmZq/Oo582Djkq7GWopcl7lCUNNufOXsfdBb7TcatkMT7i6RxwGhlP+t3HPYvJ5c8FclFL1PYYdPOW2Ll/xEq+2S0WOq6qSrq3SD0mRiF2n35AHgucWfPkVqKr1O8un0+J05P0oxM2OivFvdPbqvrS30oJGhkgPd3b9/I969/lyxy25Y14o8/hRnHdhlfgynSAxSFrgQ5pwWnIII7CrqaatFBxadMt9dsrR2+KDr7o2KV0bXviMT5HNcQD7J3eKpQ1WSbe2Fq+26L2TSY4Jbp0+6rPq0bH0l6qHR092D3huojyeVuG5A7XcwmTVzxq5Qr1Qx6PHkdQyX6M0m1NoZYbl5O2pErmjLyGaQ0n2fSO/GDyz71PgzPLHc1SINRgjiltTvvNNrU9laiPrXNktHU+hF2plx98P5qy/iHbH1NX4cqUvQ5rcX/v8313/ErSi/lRmzXzM6h0VULaDZ2puDm5edYB3erYMnHvIOfqhZetm5ZFDovuamhgoY3Pv+iOV1FU6pqHyPcS97i5xPaTklaiSikl0MqTcm2yydGtzNDtbTjPmy5icO/PD8dKr6uClib7uZa0U3DKl38jb9LtvbQX6Goa0DrmkuHYXtIyfEFii0M3KDi+n3JdfDbkU11+xSblcpLnXyTyOy97tTj/AGHIcMK5CKhFRXQpTcpycmdRtLG7A7EPqZGjyqfBDSDnUQdLfsjLj48ll5G9Rl2rsX7ZqY4rTYXJ9r/UjlE9Q6eZz3uLnOJc5x4kneStWKSVLsMh3J2zHrXVnlEfWubJtp1foMOqO5e+H81Zuv7Y+ppaBUpehzC4vzXzfXf8StGP+qM6S+ZnYeiiqZdNjZqUnzmOfG4dul+SD+Lx9lZWsi45dxq6RqWLacbqonUtS+J4IexxY5p7CCQVqxkpJNdTLcHFtM3nR/CavbKha32ZA8+5uXH4KHUyrFIl00W8kSx9NN0bUXunp2kHqWEv5Ofg4+4NPiq+gg1FyLGulclEhdFmzny1eevkb+wgIcc8HSey3w9I+Heu9Zm2R2rtf0I9Jg3T3Pp9SL0k7TfL19LWOzBDlkeDucfad4kYHIBdaTDw4W+1jV5OJKl2IrsVDJLbZakYEcbmRkk8XOzgDv3NJPcp3kSko9WV1jbi5ETWuzije/wT5y5/yUf+6r3n/r7lusPj7Fm2P2ytWykc7YmV7+tLS4vZTbsZxjD+ZUGbT5MrV0q8/wAE+LLjxp0nz8ioX2W3Ssc6lNZ1rn5LZW04YGnOd7XE54KzjWVcpVXhZXmsb5xv1owbObQT7O3Js8Dt/BzDnS9vc7f48l7lxRyxpnmOcoStFi2iv1p2kl6+SCrgqT6wxNhkY7mcvbv5/FQ48ebEqTTXjZNknjm7ad+FEzZbae0bMxSmJlcah7Szyh0dMS0fRb1mOODjtxxXGbDmy1bXLpz/AAdYsmLH2J+fI0VRLaqqofI+puTnuJc5xipcknifWqWKzRVJR9yN8Nu237Fwt231ptuz5oYoK5sZa5hkApw8l2cu1a/S59m7kq0tLllPe2vcnjnxxjtSdFaE+zwdnqroeWaX/KsNajvj7kP+HufsT7xtDZq+0QUkcddBDG4yaGMp3a3kAanEyZJxkZ58guIYs0ZOTabfn+Duc8coqKTpeRosWb525f0qT/opbz/19yKsPj7FayprJeCMpZ7wRlLHBGUs84QylnvCGUscIJY4QSxwgljhBLHCCWOEYsrku7Ue5Q8oZQUMoKPMoKGUFDKChlBQygo9ygoZQUf/2Q==</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
@@ -29340,8 +29372,16 @@
           <t>Ynet News, Sep 2025</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>https://eagleswings.org</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAJFBMVEVHcEwIK3QIK3QIK3QIK3QIK3QIK3QIK3QIK3QIK3QIK3QIK3SxMqhCAAAAC3RSTlMAyhI/sJR1J1rf8Sc6QEAAAASiSURBVHicxVzpmusgCK0al9j3f98bTdtsyqIw9/ydfoGwHEDJvF5DiC4FvyzGrKsxy+JDcNGOPYovO3iT3w1kswSnLNympSn7rEVQs0QMKyz8p0SICuKToUnfYZKsHaxHLN8wg5dTIS5c6TsWmZC0g+KrCgLB4MfFF/hJ8Ynt+wfChHjLivwezLAfkoT4gsFgnAi+G4ZMEIm0R0AekS9m/g1mQH4QlD+SipPJfwM/BuXCr4ItXyT7D6z/WT47BITtzw4B2fjbkHl9gWj+VfBYQJJ/PmBVwygvn1cI5Pj/B1YSiifAm5eECgHA8oDVkM/xgIYDODmg4gCOB+b73wYYLCROwRWJLF8lAjndoI4B6CSgwcEb6IVQxwALWb5OBDBaER0DMHJQhQMYOahDgqgBjhCV7oN3YBEQf4VKJwTROmh+hUK+ES3ADBAOnlJoxPAIKNT3ZWoN+agBatztPlDJAYwEd+bZ2xWVTgipAm7/1e4nDRZCOjH7lVn01CiEWB/wIx6nFAJIBB55718qhQiJQHf7pTgPIQO5PQXdTpcDtwEgkCp4qTwfXa2kHxAHXEUdc4OYIxAH3OScrCXlCNgB7vbrK2EEARXgTvxR+e8/T7OVEe4C7OPxz4Bxc6UBHkafrVeraseJlIADoPFunbaBd0t5AA6A1outr07SOOySuAW4C2omen6ZXuW01Kvi08MgtIvepgDAXJFFDRkMwE7RLQq8V6B6MpICrMG9op/3zICCxxIjEkyAOwH+sH5SI8MtBEEHsAnryt/i9psbC1LEE+wLMAGBputQ4J2xYRbSAZTff/9CxafshILx+yzfdAbYAoBNp7/+GfFDRXwusoDy4UYj3O1DO1qN4WwIUD5SWNKjQmfq6e6mRP5YcVx+qZ4PslvpRyubO1ZQPkpjtnk8wlABxLP/uKOUj6aRRFRweCUp9bNXJWZ2PyooM1/xX3c4nVxFIvVVlXkAQ82sIjkX/GLWDPqhviIYqevscpy1dffQl93DZ8LVn2C+EtrI+ukTo/tib2HwY8LVa+znHaD0fqvKjuAHxLlUTwf6KdHqncrCJmcMyUZhcZV1TjXNkC3Q2//x1bgrbExnoiWPoxKvH11YSitx7mOINwb9js0lfLN6o8TgzZHzF1tS5p9+iXZ7FJctb+9DSjvLVcJLKYW6BP7g4eskS8jErvXd2Cx/SybMBF3rj54r3Ud52AS93OeNzxc8nggkQm9mGj1HKWi08r13aceenTzMani0TYdN8fiWP4ZmRBP78+tUNIb2aeKDjR6hZzcOmxZe0InpS1+Qr11QZTER4W+AUo7XM9X2pYGrX7M828kZ9I9z8VFKAtB5vtIqyRXg1KezSXABUtF1ljlOQBdbVC5yDxD2SnTWKT4gbfcpakDcLlTTYKUOFUoaMLYrVSKRteH89zfad4jfaLM/s3CydWHg1E3mK6cd5PC/QswNwwNdFDEC4RZA1Qiz8+wkJVBuIBCMfm9ZIHSaMjqDCB7mjHz2KfG551kF3k3y9AlvC+RROOsdrP7uifrCVY9UC8p41p5T8roEnXPMhhaxzEvl4/+c6z8A8CENfv7/D7vqjm+O4bplAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
@@ -29428,8 +29468,16 @@
           <t>Word &amp; Way, Jan 2026</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>https://philosproject.org</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAY1BMVEX////+/v65libl2LO4lB/z7tv+/fq3khT9/Pe7mS+7mSr28ubu5s3LsWW1kAW/nzrGqlbby5vXxIzQunj59u3n3Lzq4cXf0KTayJXDpUrPt3DJr17VwYXBokO/nzXi1KzQuX2tMcNBAAAMhklEQVR4nLVb2YKqOBANIewgKIuCgv3/XzmVDbKLc7vjw8zFltQ5tWdB6PuRV8n0vvVNt65FUbTt3C2v61gnQ/o/XgYjYh/9X8fHHEl8W+YWEzrKgg7+/6Rcu59rnTtfEvpYMxl/oHydJuOyZWy2be2Wn9vMBHjdfvpmbkv6PMu6RzLAS04PLyOagGz6uF8p2Kx8PijfOaoLvK0Y31KUDlVS318toeJtz2vylQIEUimRk6ahXgjBpOx+4v3lcYnLGjWYNLvu8+narCDDZb5X0TkadswBAVE6NgWFfpu4nbG/r2H+GKGqIQQ42BWVJ/fnBWSdb9UpY0AStV/C6l5m8MKfRNUQejP8dFAOcqQiGt5PsIisSdLPLFhaN0cadxhn67XSfQzwFzH/LeMgR9o7hvoJmmj7zyx88Lt8ajOMFz6VIjbgL2rxBKXcDgxc1Ytaw0/1wSWElm1vZGPoC0D/zk1ahP6FWNIOjDenyQK20MVhCZDUv0OC/Aqa7O7IfIPQvzqXbgcHCwsAaJKQCAEGqh4ALJVlFYf+d8W4OYDn+VgS3I4BCbwMpCM4fucQ3sLPX2PbAX8ONAIJg1cCLwM3IO/lgK/j3+WTvuCYIG4J8avBw0DVZHgelQlU/IWJn33h8AVJArWE0RNr3AwMHSarC75q/xoDfjuglnC94OLq5sCGCGOCdPuQvqfFCBH/1GxpcODQAvxumkGhTkNwotwwC+/2mHT9m0PmBcdINlL2np+ZEkGWw6PydQg/Mn7r4yBCA6TTxcGBAz/M8nZKaunfw4EVONkYOoKXzwygcZNZzmBA2L+ZOww8Pl+gpvhDSG/RY0EA/f9v/DsHbjvIZ1LewgygBKquyfjar3/GAMx5vR7KDdsBvtwtu9HGE/zPh99n/4+ZXO7nOAB+28l6qmjpRcjV+tqvf/rNtBJcZLGaGz15QTKcmJXDMeKCzE7R/fqfClzg8qr/KuAL4wUv5jeHeBfc2fE3iH+E+YvNrHpCvnDDpNfM7hj5gjNbQUH8aQvzu6KG3w6GBme1/kiK8iL4atZkdPjsH+Z/EejMXMne7wto2PCqmMExT0Loq5z4ffYPJgV9iMu1Q3bwJljPCkKwhtunA79b//CXd9JONG45dO33BcrbZVLihpgzxk4owfi3QKWTkdHzrdcOqgw3GjcUzVDiJ9Olhb80TEYZLbklmWlSx0i1vlF9qxbuIsFmNhq12dH/uSlGqCTXkABeDoYnLlQKImZOT2T6ZRh/WtUZiUEF98Rlu3xwX7AG/PKggGG+4VLahYa/cOKn08c/XVtQAYqibV6TO+55fWHGsxLywAIu+BWZDAj7d43hAQ0zxCAuAG3dydVZw/rsoC7IS2GAWsBean/UP3z1JGxxRgjw7Dfav7uFddsBRN1SeVjN5IkOeiV+j/7TOxTZdHGqFALgJhl76OFf7hzstAOwApnCYU6IAeMRGTT9O5qtW4m3jjadMWECYOj+EvSGUurhLLLdHLRqLFjJEc8/4Y8Af3MvWd90YV4wvZmyaDPzcv4EuewgpmbP34jgJVdtlUrBb9WQdYu3ZGEZLWUCwP+9C7wNKOloMPdyYGihWsmeER4kU2u6oP3nNJfFpKQK3AVAE6t3q9Kdzty+cKOzsgFxaVYLs93+XZ3HO8vuqMMdSKwIAFmBSvwgpbOgcNrBlGUii0C/pbhbOP5VHQhbCQtWBKhm3LHeo/P80OELJem5SA+yHt373v+5e6+RCjuxSTUGBKE3Qjwh0WEHPRHRsGWSnMFPqQbyH4SkBgOClXqn1cOBqoWp5Jl84IQ69W8wgNBGfijOjYUPVQD6TUqf3O2ZPRxA+GMVyEiyRAgQtH+B843SXmhaE2AhUE8Am55QwP5e5wDe09L/AqEy4jnw6wzAdBPKe9Kw0kUT4Mo02lGGwhwcElwJAZnzhuYBnpPC+kfMdRJIJCCAxUBMIB5TAYLbJpovcIsBTTyO9e/NxK/3EFyAnqcuXYARCwFC8wMHyuJLTpjhlnhCIv6V3gLzkLmmVe1mM8AFWEM2wH6zFocdrJSvkVHH8JcY04VR/woEtYFRWo3FwAbvIZ7meh9jUeLdFxaqjweBfpDrv11KsrkLGyk/657HjPmNLsCbhjPwkvAaxgNS9+ELd7oW2BPWrTL7z28ZSydeBnjQYs5oREJ4NXhBTC7B7aIJ5p8OXxgJsMbNRto/9K4/YQRc08yUNQGe8Az8Yw39OmlxSxmWvlAXkLxaqjWe/+kSxYJJ5WWABYq7EMNgoATzS1pPoyjGS3RZMibC34+oAFc41n/RQGSOcg5eTEIX0RkMMJ9uGD/eUV2kfDQmdjkNAXcQIObxT2BcWETzrkTGNHOkkPsmZGbDHApNT13Kx50HfcnBK4f0/UAFXjZl/R9IDgcD6KpGlLe4mFQBIE3fgJfSl4w5e0q1wDioFtAbq6+PgkSJjO6VyLqghgQTtjXaBchXvNadb4VRop5VCwEO8NLhngrA7F9OsEd63xgzugcDDkV6LAQYV1z0ML8/FdNRtzq3DfRWTIBW3ZjgkV5fhzDGjeDtjeIWfk8FwK8ebLhdcRbOQ9zplDEsQoDyFSkrIzLZHnZnjRh6kXKcmpV3Rlj0SUH+qQCbLkA9F1yAglzRsU0P6dm9pq2MaYbWdF2esjmFF2W0UXGt4xwf8Hol16KKUogXEGAtibJolKygyjADMN5NSfbeENA3J5axwemUeaYWOFvgCeB/QorZ979Hmp4/j3x6zNwGinJ+sOWBMP6IlmDbvvYNUZlcge0XDURph7NeQp3Jc/jMABtaKD4xYrLXzHRXakQ8EAHjSQccsB08qHk+ZXSHAJ+wC9Q5YevEEj/ioZgloxycmKWAZKbLR9HfMIDuon/m+EUy4ukYOMhApPT5KZr8AwMR7ULpxBXHH/HI0LMlXcpB1tdcFdFfMYCGrSQPiR/xcpCXZBHloGw9C4u/xQDfEpP4I16SMSlYDO6wCEl/xwBw0ELgk77AilJelkecA3vD5pcZALsrJf6Il+Us/XKkwhf+koFD/0g2JhCNePJBkfSFP2PgsH/2L9HMs25fIGW+gP4sDmj4ZXNKA2SyZ0NmB2cd4dtImKj4o7095wsUEqllB7/HgIH/KNFaPiNSOPgDBnT9049couGLVAdSg4PfYsDEj9CPXKRiy3THKjnzBfeq7/9nwMavLNMNTzIfDESR7gu/w4CNX1moFEu1u2TorC+cZsC0f/aM9lJyvkwxu0jkBWkHv8GAA7+yWB2J5XqFAXTOF04yYOuffvhyfcQliBUBZX9COUDoNxhw4Vc3LHg/+NQZEDVS2A5OMeDSf7Rv2QgG+KaVyoD0haA3nmLAjV/dtKKTDRf8IzqDY3z0hRMMuPFDNbjR8jSSDIiNS42Bwxf+hQE3fn3jkldDdOvWYOCjL3xkwG3/0b51ezAQ8c1rnYHDFwICTCTzryz68Oub13wqvn2PTKOTPZNz5CAACJ5+qX9AWx6rMIIBiAUlz85GRcg48EhA10V7yCNf4jcPMIiZxBEO668DvkB9mRUV3+EXRzgMBiAa8UMsRlsQ8oUrKZ7YtzLoxW8dYtlnehHsbIx9tTIEE2gyXqkLpc/+IySO8TgYEAeZLAb2Wtkcd5gfu49+BfDbB5mOmdxHuZDHDqYS5m/dJ5y8+qd77yzJuRiQh9ksBpDDDtKFHqJa3Qbgx+86zLbP5DnOd3CgzXEpcLYk3+l/P87nY0AcaLQZsDmo2m3xgAzgdx5oVBhwHuk8ONBq5cRzpSiEHwyQHukMMSAOtdoMoA954Qx+z6FWjQHHsV6VA0dMPGv/bBU663PrFwYD8mCzzYDLF77B7z3YbDBgHe02OQgwEIh/8mi34xuDAbonwQ+3Wwx8tIMA/sDhdosB43i/yYFRK5+Lf+x4v6V/DwM0N8/sgoPFgDcvhPHLCw6nGVCveDg40HzhBH55xcPpG04G2IEtfsnFrlA8vuDHLy+5fMWAcs3HzYHBgLf+Pa75eD4eBui/vRedHL7gw79fdAoMDwOUhP2ql81BJmtlv/4RvepViqte3zPAHvkuuxm1sht/tF92Cw8/A0i/7mdwIHzBs/6hXvcL4A8zwJ56LjwqvuDCr154/CcGGBT9yufBAa+VDftn04srn7WzYv6KAf6cXXrFx6XXgwMbv37p9cz4yADDVC/0TrF27Teh+420hDqCgnrt9wT60wzwl1sXn/OugGBVAP5/ufh8jgE2rKvfC902Xh+Oq9/n0H/HgCReufyO+elm+/L7V+M8A3J4r/9HXyCXn/8ASFy9Pv99OSoAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
@@ -29516,8 +29564,16 @@
           <t>YAF.org</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>https://yaf.org</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAOVBMVEVHcEzXHSgAVqQAVqQAVqQAVqQAVqQAVqQAVqQAVqTXHSgAVqQAVqTXHSjXHSjXHSjXHSjXHSjXHSgY7X1UAAAAEnRSTlMAEiXPPniT/hDp3rJanLwrckrv2/5IAAAF6klEQVR4nO1YiZKkKhBULkFQ2/3/j90sLi+wj9k3HS+CnEMaoSrrhJmua2hoaGhoaGhoaGhoaGhoaPifYlkfwLr031DeL495/OMxzutva1/WKSqPmNdf9ALZ/ueCx28x6M/GJ0w3DPp+Wf9RqtTU3zFYHtM8juM8Lz9Wv9TVVxlgT9o0/9AH/eNOfZnBkfL0I/VrIfWeMFjOlO8S5QnuvR8xHhT012oZPy2Wp97PJi7blpLHPmRwk/skdJymxzRNXuG8EoVdn7ww+MfmjzMdBr1Xuk6ezgwu9R3j2337JvnGYO9La4OvqB+8F4T+URU3PwqdZaovnwLb9/RXTRor509fYVBk+xSXOs7qp+rxV2TwmfpuqZlfUx+S8cJg/Ex9t9bML6rHMTnP8wRdZwbTZ+prwSy2kv0hjeTYRW78UH0t+4ryzqkyL9SHfMldnU/tAq6anzSkSvaVzC9ckNBs6ApSuIPgbpAk3zGoFX/B/Lda/oHrTUtcyuEvSV1rLf8FrtXLdKX6CjequzP6vLzgqsodrVx9BfOrbaqwo3ygjSUGZf1Xd71wRUAN9AT8BVVpaYWDqcz0EtF+rZ46dP/d/miaptvD+XxHK5s1X9xfDf444XoArI9XrnAXBhX9l0jVzkjy+eajJ5dY6lP42beDcve9mN9XjDsf0DdXCTpOl5Aeu01LMfyX7KucUaWqrhR05Xwo6b8urdReufX1pZZWO55KbK9iK01yqja1c7jG2lLU1RVXqo/4ZqavjLvL/sFjNzepri/g6aoloK5+74RxXyS/Cv+/pC/9K+l1aMHSiN0uvO5k+hN9502Oc+EHQsn3RAnuPiAg1ZGBZs5YmmJWscRRxweLNjIaaOGc2G1mdpBHg/xG+hW34hdjXsW2kRFrLcTe287ABdo6aJBSio5JS6/xUNbT1c5K5pSU8XMyhasO03kKq/AJq5RTVkorsE+ROMxYEqkl65yCOJK0Y6AhqJOO4RtkuQQj/9ZxIQfvZW2FlKRHyExAKGY5XqlBxAkDQ7BbM6kVSeSaWYd19J50d9Lgo+4chOhDILBUSFqc1NpoEZzAQ3icDWHJvBnkKkMEjApmWMuZ9vkktJXkWCbgBRv4ISJM0XQXZg4Jj2ySQtkYbw7X+xGc6wR5B1bYc4JKSRZp+ER5jhrRs4zxwJN4wAvehOxoxcgxFOyTLOjkkpk4jWSM2Y1J5AXJcipWSgb8xJgcGEIn/E6nNEzANOUXNiGf8FLBnLzFddIbaTmCfZCmrRHCsMQmaeOOQTR5BlYed4AlLEb4tRI+hZARCLyW3MGZoIeEpEDDrkQAucCkF4NQ8KNBCJ92Rqd4qDBkYOVCtatAAO6OSYgnlZpB5HSHGGjlIEXh29clLCXeSIVMQPv6iHrhV3skoFLmI5aomeAysCLnSmSlr1SkYAyOUzHUKDxKf18jUKfje8gj3yN3vXtiAFIToI/yQMAvjlThqfCSwalSBP9IFuSIkNLxAUXGlzPn1MMgJcSR+RbpOKP8CV7vhArVRKnrd+6TGu6HAQgf+paATgFJwqHMQgnDOWgNmGOpQ9nYRbQdOLU45TsZlqHQSQQe5BBLHsfDQVrIfEaNzGKNk/s2AJOl7w/SOUpPTf0MA3QsFyqMCkHSa+8R9EQ/jy5oFW2gVOl8GyUJlJ1+FkHHOoaYUnOkLo0pKg0Z9m8R0OFcw+84H8+5eCh08UM8GHRapz3SAjoC4pTu8vsoLe5gXsb1FNXfwE6/NF+A2hFQQwA3Jo4Gsw35kMfcDGlodou3BQbTecFO1m4yDQsEDBpUfItzxZo0O/A8rXhSYCQaZuaYTDBcbgvSALJsWiizAFsioBI9BCWLV0O2iqs8a+SQxQ5KZm/IbHeaAzuTCW4Cih7IJsGOIgEIKBDguLjUCRhleHqNUTKyRMBuKcD55l++I5AjC8du00PWMOTBJm0nwGwCjiEwQ0gvc/3yL0xe4dMz5+JlRfx4lnYYhufeA0x8AW/+CdDQ0NDQ0NDQ0NDQ0NDQ0NDwX+EvsnLBcYo7v1oAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
@@ -29560,8 +29616,16 @@
           <t>FDD.org</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>https://fdd.org</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAJ1BMVEVHcEwcVaEcVaEbVKIcVaEcVaHKyMjJyMjKyMjKyMjKyckdVqLKycnpRCN5AAAAC3RSTlMAz5oXPGnXaheiPy0hYHgAAAPwSURBVHicxVvbtp0gDJSbgPr/31sF0XDRjadJyEMfuro6QzITIFumCSG0Cn9i/Fd/Cyn0pKVUwwiYdRXrKofhT3o9wowjYMYSUBF/r8EgERhxEhiVA6X1wUFqPc4GkxzpgSO0GNiGQgz0YB1uGU3AusEE/OAUuNmOJuA54ZTZHagNaEJum1lFIFaZ96Fl21hFIMNGBP7CbhtrDSoCnpWAkuVe7OZtm/lqkDZjcTXjZSfAKoLjQGLU7YJdAswiUEJAE87sBCYD98Jl4yeQhQ8ExjXjmADeTgTDxQRw9OLjCKqqY6jd2CSwXwiNKE9i0QI8EgjXkfIoGgvAI4EWgeVMwMyFv+an8YTPUQEljz1AiOw+kgrAsxUpXaz/wmdrg4UHbMLfJchzT8ovo8sGEmD476n3+g8PSvarop1hAiZJdllu9t9s/cEC2QkBNaQ0jZs4wI89QFQ9Eo1Ao/86iB/3QUE1rtGiHgUtfisKMKm9R5HgxzP4Q/8FTVjv/4hGBGqnkHncweVfPbBVKKzQ0GDOZstPByHVKBRegPUv+fKvTSgohX5sVmQfbIJRKdTduFz+fQpQ8bZG240z7+f451mFdnBbpR/gnwkgFUHu/Rw/JYCoFYWwb/gpAYQElgoezuVSAtaVyga1/OAhVF/4VDZ4x08TGzob1PgeXkQBPg2BWn/ZJQQUgMaHrsTP7yBaEBMo8ecs/bcDTx/i26Dof8VYHgqQhkAuwHIoX+LjE8gL4IspTIVfXh3/P/zL8hv46ATsy/IL/dO0wvkrPjIBkIBqAGKa+LgEbgXW5TdNeGQC9hm/lh8FgZSAcv7zDI9LYHmo/0P1Q6Da0Dfx9cvycTPQHMGqt+UjZyDNoKH/36ofCSDuBY0h/I/l4xI4KwAN8OR9SAANv/4d6Gf6j0A8EdmiAF34mAR87oA+fMRTcZDAXQD1U34x8FzoMgV2rh/zarbABHTjI5rAwgT04iOb4EpAh//PQLyZ+TsB7bNXMxB3An/1gF4DrLiN2F89oFsAuDfDOVVA/8a9AlECboYjWP4K3J9m9TsAtwLuPIh+SQDqeMSBIfyICkwuVuBTAlCnIy5K8IsCSD4xHZaAM770AJIZ5RcJUiTgUxOiSMCoJnTFhwqQ/Fr0pQIkM+IPHqD5qaZfAkSfufdLgOhnim4JEP1Y161BqncmvRok+6WskwDdO4s+ExC+8+giQPnOpMeFpO9cOgjQvrP6TYD4nddPAtTPfH4QoH/m9E6A4ZndG4Hq215mAjyfDj42Iq5Hbg8EBNunm83NiA++SUCyvvCrDiSS+30nJCA4c5/i9qFgX3wIk3Q36mnt8ZGmNANftiqqpf8DJFuMvTNeln0AAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
@@ -29604,8 +29668,16 @@
           <t>Hudson.org, Wikipedia</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>https://hudson.org</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAABAAAAAQCAYAAAAf8/9hAAAAUUlEQVQ4jWNkyIz7z0AumL6IkYlszVAw8AawYIhMX8QIZ2fG/cfgE3QBTBEumqABJALcBkxfxIjifBwAMwxggMj0QQMvwJyNi0YDjKNJmXIAALrqHFuiVz8zAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
@@ -29648,8 +29720,16 @@
           <t>NationalReview.com</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>https://nationalreview.com</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAY1BMVEUAAAD///8nJyfR0dHv7+/o6OhFRUWMjIyVlZXa2trj4+OcnJw6OjpRUVHOzs7r6+ssLCy3t7eoqKgLCwsdHR0iIiK+vr729vYYGBjIyMivr69gYGBtbW1mZmYxMTE/Pz99fX0hbDC/AAAD5UlEQVR4nO2Z4XayMAyG2wEiKCigIAjC/V/lp2zSpJQ2dfv35T1n+7GV9CFtkzQIwWKxWCwWi8VisVgsFovFwprih3NMdX08Hrunxsfjpv/zMut8uXwIEMni7ITMgyBIXgqS+Odv131dty/ls4LnT13GmT9AKGVxdYzZPQe99QaoarlWEyb10R9AFl+OQYGaY3nHuDEQvBT0lS+ArFcri9Uq88sL9uEGwPOFfFbi20xph1bubhaA+2kTQKZ3XwBZWlehMABk0TaATAdfgKa07cTOF0Am5FVYVrK0HGQFkC5Rww4gW9fGXgHIbvuRgz9AE29a2wKQxeZZiO0AUd7WbZ7gYxGM3gCy24qJDoD5DN2OfY1Cw+QPsBmVFUCyjAAAh58/XWNorabFI+y3wrwTFUCwbBQDAA6PIS09afGsNvqADCBghqBlBT2g1r8DuAMX0ILRKqKXBh/QAW7gcE6fAZh2Ih0A5q1PAQz1gQeACpqfA6zrAw8Albd+ASBrzQceALmyQsvJ5rJC8wEd4AjsfXYM3wRoJ9IBQCT6LBCZfUAGOIPq0TsUl+Bhic+CCWBMDQAHEIeI+VgB9FWCCDqVnU0AxzXADaaCZOcLEIsME6hKlQRQDR1Mx3tica4A9s9Inkqo8u0DB0Cd7bJ+X6AyOadeUBCA6HGt/SZwADRpmob4nhL2xPk1ADEhM7IkARhErQhXAGLAhr5X0huAPv8KQMSo2m1mAk+A1GP+NYDoseW9L0DYeV3S1wAawcsHPgBt79eqMABoF99w8gKYvKY3A4gM+3TwAYg8OxRGANGjU31SWcIIkOxBGUK/FdoA9IhkBzigUtDVbKABbBFsAdzBtqFHQRvARgtmC6A6gEGpzzbYBNCjsh1AnEExKIs/AUDdOScA7hl5LIIFwNSDsNQDMRgWEqsRB4BeH9gBYEUuW2f7lQQgBv0s2IrSEQ48GKyZdLMDoNuuCwAtwonYqPtyAIgz9oEV4AYDIrFR5wQQGdoH9nsBqmpp9wI3gLgnZADcwZ7+CADVBw6AK2zRhJRG3ZkAIO4RFUDs4JbJCQC7hgAgxtMaYACXOtDh7AGA7P4KQDxSG0AHizCYmBubTS+AZX8DgJMZAC1C5DyLmQIorQOHRAMA6bpGNRAMR7J1VaiDAijs53aIMMCkAHDg/0Kfs+yvJcReDc0dgSM7IQBw5AP86RFfsh2ZGdCGri+YYwQBQNhttOQ7wXDUWHtVVZEoOTfMMx7kb4BLOT+Tzr/17H8AVpPO5tlq/iL7I8e3uxdBOb0HVdfj85Esmz/orqYYgdnRq0hmsVgsFovFYrFYLBaLxfoP9A83QzWBtqTBCgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
@@ -29692,8 +29772,16 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>https://salemmedia.com</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAaVBMVEUaPa7///8XO634+fz8/P3f5PMbP6/y9PoTOazO1e0iRLCLnNTs7/hZcsNSa8Dn6/bW3PEwT7W2weQ1VLecqtqAktDDzOl1is1nfsgoSbOFltFieMS8xuZAXbusueFLZb2VpNilst5vg8lkHmWwAAAGtklEQVR4nO2b6bKkKBCFLWRxV0TBHfX9H3IAq+uuKlZpT0xMZUT/6NtVN78GhJMn0XHe8Y53vOMd/80Aa3F11vsfx8EYBz8CY/WhD7pzk6tfq3LWtO+TuK1mIcqybJrwTzSN+rsQc9XGiewZrYM/MGck17lrJtu5DIuh436GEErTKCIfEZEoSlP18yzjXT4VYTm3iWRUcbw6GCp7wBIxDp1KnBIXwtt2QOi6JEpR5ndD0cxJXwcO8J6EAJ6HaVwOPor2M/8AgWpkUNYVZZuwAD8xEOo/T+MwR+Rg6u8DEiG/m8qW4aPpAykG5L6S/SNckoX00BAAzOYcuadkN0GKQwAgSMbsxPS3WzTWRwaAii46M/3tlja1/QgA2mTnzP0ngDKwB6BjenJ6BSCsAQANz89/QzO2BAB1ic7Pf8sqxw4A4JifPf8GoLWdgL44ef2bgH5iOQCBQFcMAOTSEkDmp+4/D4CutwIAWFyxAhVAzuwGgE7kEgB3oFYAnvSvWAEKYLI7Cjyx/wi4SvKQ1CgwZNSZ0meEqJ/C2zo8Ga02QhCMm0sQKnHBh2IMG61A76ElahOOxbQIxjRyf/kdJLTaCD3WbWX3CxH3tMYYeF9qA7XHKbmjRDNjvYyrMpxybgTkx5ej0goASH995FGR1Fom/pT9DxL1jwpNoTAZi3DqlJgki5hMhR1AvPoQwqxkwG47B0vtoinmcOJZpKYknW2+C5x59RxMR3ZI15oR0RTJHA4c+VZHAQiatV0A+rHtcfqFQi8PDSF6q8/X4dpD4FruZL9S6KGwEuWAFmsApDgg6X6DsPsYnS4CsAxAh7W9jIx/ByD/dwG8dQB3OlZZPRdqCtbWgFY01xNsLMIbUsXl5QQbj+HN9cv+mSL/GEC9cRq7aBKSBsYvusoS29iK9TIgiE9NtZhQ2hO7+2YnoihJui2IINF2h1IkTTlXsTQs2MHmGPZ+O6gPE6wfx58oIHRJFBlLjGtLrBFVnCia3oyM8xJGn+0DfIG53U0xlPl3g060iVZNjqV4+DYCLD8G8JVGq9UIZTw3/hzFx41KEBQnqHI1Q6mmEAkLDg4DABay3J7CVw9u7R1i8DZU6TMQqV+09AgBqIuTSzMXDS2zRwC4Ot2ecrMpDuyHgJ09BLqi4cJ6HgBu+fkGAcxC62m4yKNSp7n9JFxhEajCylpSqWVwgU0FM2GrKgHui/R8m8LlsfUk4D7Mzp+GyL60AM7JzQITMEs82zFQp5IseXTyPJDxQH0LHIWQn9WxuQe3KpEfCACzquCInAdhaZN8IHi47ttw4Fl6DsXBvpGZCODUTFZNkXPtfxH3JRCYH5qDO4NmDmiftHM5FlPecR8hYwzC4zC+9VbwHcLYTtqH62USV7Mow2IaFIzpI0fGpbShQQcXwU+Me+juvaa54zThOA3cNHi3AaLwUO9uD8XUIrocMZ19bQ2OufHkVoNMTztNFkAeCGrWjt3GOeI+swqPgeA6GddbLpDLSwEMg8PG1dPcunP0EoKTrEv77Mnn8BgBXS+vsvZvOE1BuSom/g6AM68ugv8JABYbnvvel9V28jJAEK4C8GTny1Sy4FWjx6PT2lMAu70GbsWHppW0fuECFHDi1X3AHbYbuACXEYzM3aOeBs5TFADQ9Z1wTxLdfUJIUj9XEJLVRy+DaSFZrhf4abPdvvxo2UCX6PtPY1klTI3F/djdMOCMZel5Th0XGwbD3j0OUH/2irUdmGpfciznWPaUBg8XcPElP8KIFKUJ5Fz4G9UE9HcOwxW7Hmoj0OfdMGmLtNRN27Zt40e01SLSlHzeLujcgW3PJmCrDQvtSZqudZTe+9bZI4wujCyUuxvuVIeAddc07++RVnuatOdX5lel2U5+sCElTgg33LlDAHB80Ks+FtmeHgO4uuYGyxL7vU+A5wsB9Em4C3DRHR6TH5W7Do0+iy4DiIr9mgTg5jIAksv9ulRJmasA3DyxqIs3tNRrAaNBWl0huQjARUVvd4fmEgCYdsLSKr9iDUDih4mtKwFwO/jpS1fJv6eP/CKm9rYMwFRW4cT1/afXkyt5OwhZH2qaabGF6z4Wo7F89OsEz5AsV+qnMqH4iTpHy87gfg0r53623NWzIlm6yinKuiGsTNfy2QJHvx7i4ID2sp2FtsAUiX61w7zX8c2Sg3Bp2eqXKnyeT2MjtKBfXjJ5KRZ8bcjpW3pJq1iacbEHFc4jOO9yI1dF1eo3XEwtcc7rLQvFoxzQZtxiDkqZfArduGeqenh07i+rwD9dG/xZFlz+ntM73vGOd7zjmvgHjQF8fXLaOkUAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
@@ -29736,8 +29824,16 @@
           <t>Company reporting</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>https://dailywire.com</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAZlBMVEUFBQX///8AAAAaGhqjo6M6Ojrc3Nzm5uZlZWX8/Pz19fXQ0NDJycnT09Pt7e2rq6t+fn4UFBRAQEBqamq6urqMjIyzs7MlJSUgICA0NDSZmZlycnJeXl54eHjDw8NVVVUsLCxISEgpm2UTAAAD+klEQVR4nO1Y17KrOgwFhRJK6C2EhPD/P3nkBiZAZrbJ3LkPWi97o4C1rG5bFoFAIBAIBAKBQCAQCAQCgUAgEP63gC22v3x+c7iGAYH87hbTNA5XjnF0O7kQtONVCi+rhcHqPvR38uvr++8MoGjiKLp5ns/h3eIqrQe+m7cjZH56XxOY0mktuL/4e8mrMCDgvuwPBGHipy4yePpCEK30QZsGVb6SFJ74sO8MCLTNJwGOsCkABrGwP6zUlb4dlivJI9l57yQB204cF9yYk6m1sIN3haJYl0Aa8C+quwmBi3NAALWM8L7xlZfgAshCZu2HTimyNzz/TiDwYkTkJeHC4DYI93rjQqAQ2rxlt7MHriZZOBPwSxcxDc8+TmYGGH5PfAofKsPByiRBZ6kXqZC82lMEcEsCeZFVgWLwYjGP2lTUq4BHwsoq0Io8ChwT/RoBVy2IFaCf/VDzVFAGB5gjJmhkzu3nygkCTE2uDG0n0DloAuleuC8R4otUBKsWsvjyMwKMQi+9EGSQYRRUkoCWs4HIOng3/NWwN+oEBwSwvN9ULnYuxn0gdjtoKWKHGVMJo3gzGY30HxHA3FKWHvi2WZWHPBa6fGGeCIVgPUXSvMw8cExAhTvukwUBC3FWhBmqLFHuAQwR8X9t5oFjAp3MbvQti7IoR12i5IZ1Lv3zwtQV1XrJyp8RsGoZa6nFNp5gi74Ko8QFZMIHrEDJsIgMDXBIwFJKgia/+tzEuTIAqGCwmwtInrWh/i8EnqFOwK5yWXBYUYIykKFvSSoGk8DfLGB7RS+eeThaoiVhjZbOMNV/HAPKtqHDKxGOB8IAN95zoVQ9SfzJfk9gzoIaeGcIpEeeoiR1cpKTBph+T0DVgeSh2q0wgOy5c6HiMOvE3wmUSmNx0cZWaQDWlmKNgNEs9JUAtJVcu1mpiufBQGUJt5LRLPSNAIDssWz401vgMg3r83zs/pzApMayBMt9Ns9oWsfB4UyJA8e4CuwSQJXDrJI1PFeNYaE+9Ij5nJMszfVvCLCp8F7PM2EP2txvp6tgV83x4+RkTEAOpe2UxXN4iQMBlHLuLlcdB0CaIM1/QcCvH2X5yOrGm7cfyMMmuLzwhs5HtsOVEwvNy6BOgK2kD1z4WBXzLMxIeZ8tX+bHKQ8sJXcDv58P29wHQbq9qBi53LwKWfywva/fK9vl7NN6uzMPWGiC5HlG/8HpOLxlhb5fPI+E/c5GWb2ITlQhtoQbb7Wn12593wMj9oQ9PcjsVA6wruc01StCePx+xslGN99eN4G3b2g8mp+pQnwJ7Ybr+K4L8oOhEwvlSQKf93SHbx39cFI9gUAgEAgEAoFAIBAIBAKBQCAQCP8V/gFMNjCD7FJFzgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
@@ -29780,8 +29876,16 @@
           <t>2024 content deal reporting</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>https://tbn.org</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAACAAAAAgCAYAAABzenr0AAAB5ElEQVRYhe3UO2tUURAH8N/efekGRYOCqEEQtVHXJpLGzsbOQr+EhV9AECwELbQWH61+ANEmIBIbCy0WI3ZqIYJgfBDUaJLdtTiz5HpzFxTscv9wuPfMzPnP48wZKlSoUGGjo4YTqCPDcIxdH1+wFa0xNoM438ciJoN3GLpB2OV99Wth3MOHCKiIOqYxj8PxXSrYdnAQe/ENz7ALr8PuGKawguf4iM04Dss4G4atwmpiG55gLpzvD3kLjfjvoItH+IHHuBjBN3E6nP7EqfC1D/NZZNDEpiBcjjUMWTtKJmQrsdpRkd1RkRe4EzrSVfRjfx+Xw241xzPMIspLkeG1IIaTmMUDHA2yPLq4F8SdkE3mgs1jiFu4rdBnjSjHodh/zxHswEzoy5qzJ13dYpybwflIqAxLuFoMsCzav0UDW6Ssm1LDPbR2BSPUpWq18RkL/yuALu7ihtT9C7ip/DWdk6q1Do3CftwcKEMPZ6TSvgvZhPVzYojtuII3eJpXFiuQWev6YnCsPdUmfuEV3obsCC5gZzitx2rFuSlcx4HgbqFWkwbHiPyTNChWpbJ2c1nMhZOXkXUeE0FcNogyaRDtCZ4e3kuDaHo0ivMZ1uM78OfT++rfR3GW05WO4jFcFSpUqLCB8Bv7AXX3fpjPygAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
@@ -29824,8 +29928,16 @@
           <t>allisrael.com</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>https://allisrael.com</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADkAAAA5CAMAAAC7xnO3AAAAYFBMVEUNHzUql88NHTMYT3INIDYOIjkpksgSNFAqlc0PKEAni78WRWYUPFomiLwOIzsoj8UlgbMfaJIQLEYcXoYid6YaVnwXSGogbJgUOlghc6Eje6sSMU0eY40VQWAbWoEkf7CZxVP+AAABXklEQVRIie2VyYKDIBBEwyjummiCcc///+UEVLpHRZbrWEfwQVNd4O126ZJOfuxK9mXluOWTTG5kk5A8dAGLNyGkpA5kHXzJ+2gPxh3hetn7ywRIIs8WDPOZJI/eDqQlWTXYmZTeJZk0NuBij4NHLJKgXV/6HLa0ygIdABT5831DMgN7COMDY2YGFi2AHb9nVdcWRmQaSDCo+QAjQWoCxi/Y8s334nEyag3qSM5DIG5bxPRgiDoyQfH6O44CS3Ie9jVO2r6O0JG5QmaYJWyPcAWK15jkgT2iE6j48zveP1BH6ObYZ3f8+8JKLdcSWz2o45slqCPLZxNaTBlfHNjP+mOoPjCojC+2p5ajKMYqkypsD6wu0ndq0oE9sxp0+ueRScoP/ix5EF+qLgof4+D1xYHdGuGdPYUx6sguoXiy3U56wcmyuKBgU5A/elL1vt+0hulxa+8PaAfqZi/9a/0C76wP6oTgE3kAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
@@ -29868,8 +29980,16 @@
           <t>GYE.org</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>https://guardyoureyes.com</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAF7klEQVRoge2Y229cVxXGf2uf69xsx3aJHTtpLk1MLlUgrVtoUXngIiHUhwJPUNQ/pH8NqngBIYGKUCT6gERoCFHaxkRNk5g4rhvT4NiJx+O5nNviYR/P+DJObECaVswnbY/P3vusvb691vr2npG3b/9dVOR14DyQ8uWAA1wHfdfNO34C/LyHDv0neAd41/Tai/8WfQK9Rp9Ar9En0Gv0CfQafQK9Rp9Ar7E/ApK3J40/7f3/MdynzjACmaKtBE3s1wXxHMR322MAGqeQZmDEjm2DthJQBddBXGPnq+66rHguqKJRsqvNJxMQQeOE6JN/0rzxGemDVbJmDAIm9HEPDhCcmcD/6iE0Sqj+6grpcg1TDqm88QLu2JB10Aitm4usX5xB45Tg9CH804eoXZyBOAXZHhYFhcI3nkPTjMblO5hSSOXHL+J+ZXAH6e4EBLQZsfb7j2j8dRZtxWyPfzT7OY2rc4TTxyh/7xxZrUl07yEi4E4eoPL61607UUL90i1adx4A4E+NkTxYJfpkcYfNNoU0wxkugxGiu0uY0CNbbcDBQdgWtF1qQKhfnqV+6RYa5bvkGqQUIEUfHGMjlKQ03p+lef1TCt88ifgOiNC6vkC6vI44hnh+mejOA8QIznCJwvQJxBgwxqagsbY3N/Ecu5bvIvm4ON1d3RkBgWy9SfPaHKQKAs5IhfL3z+FODoMq8cIK6+/dIF2ugUJzZoGhN1/FOzJCfHeJZKlK68YCzrdP07w2h9YjAMLnJ3EPDRHPLeVbrZiBApUffg1TDtE8PUQEd3KY+p9u5j7lJPdGQEhX1q1zIiBQfG2K4qun2gv4R59BmzFrv70GqmSP6+AaCi+dIJ5fhjSj8cE87sQwrY/v21BXws7ub17OdwnOTOAcKLXtI2KTK991MfuJAKD1yKoEVnG8iWFrPFObOijhhaOI66BJihksYEoB4fOHqf/lNsnCCsn9FdZ+d410tQFAcHoC78hIx8nc0azWpPqbqx2VUUVCn9J3znT6jNiU2zMB1U6xGJuTIGgzon7pNulKHh0jdkHPsVMHCxSmj7N2/xEap8TzDwFBij6Fl0/YNNhWhNpKaH54b2u/EfyTB21N5c/i7Hx3VwLdIAaSR+vU3rtBVm1Yo0bQDNzRMsG5SZyRMuH5IzQuz5J8/tiSzJRgahzv2KiNoNmmPALiex1BUht1U/DJXCsK4hhwuitWVwJipGMwy9AktZI+UKDw8gmy1Trp8jrxwjIiNq3Io+YMlwkvHKX2h4+srcCl8NJxmw7Z9u1XzECRgTdewJTD9g6L7+AdHiFZqqJZZjv3k0JSDBDPQaMUjVOSxUcEU+OYSsjAj6ZBoHZxhvjThztfNoI7PmQLMM2Q0MMZrXQNv3XWxT85ZnV/oz7UprH37CiF6eM4I2VM0e96cnc58xVnsIgZKpHVWgCs//kWphziThwAIFl8TPPqXHentP1nT9BWTHNmAVMKNrECb3IY7/AIgz97xSqXI3usAQVTDgjPTlD7bMXK6r+qrP7yfaTg2ykNq1KmFOQFv3eHt0CEbK1J9dd/23ooZ0rxtSmCU+PUL9/BGSxS/sF5zEBhx1rdE0uE4remCM5OtHNb45Ss2iCrNtAoQXyX0nfPEpwaQ9NsxyaQaadtsU1HkjdamkHSaRqnaD2i9fF9mh/M07jyD9KHa11vHt1VSBUzVGTwp6/QuHqX1s1F0sfrdgHH4I5WCF88RuHCURof3kOVXLOts86BktX8KMEdG8KUwvYYqrjPVOz4xu11Q5I3/e9PjaNJivfsCKZSwFTCrikk+c/rv6Dbr9P5TVGjxKZNkiKOgxR9JLDXXVJF49Q+b9qArBG3z4gdV2FVskZkHcpPe8k/7bPYsyXLyBox4hgk9LZ79w7oW08+BzbuJp6D+MWt/RupYWSr8zlxU/LzuV3simwt2rbdbc/GYMrB7nbYx0G270J92vS9mnvKvP+z78RfQPQJ9Bp9Ar1Gn0Cv0SfQa/QJ9BpfegIbt9E/AlUge8LcLxIMcAXg3zzvbWD6jzfGAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr"/>
@@ -29912,8 +30032,16 @@
           <t>User-provided; general public record</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>https://fedsoc.org</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAYAAADDPmHLAAAQI0lEQVR4nO2de3BdxX3Hv7/dPeeee69sSbasp43AlYVswDB2oICpQ1JMsbBNGRiKSeg0JDNMh5KWppmWNAlNQ0NSOiUJmXSmj1CgdEKgZXiYRw3lEWMSaExwQRhsoxjJsmRLsp73cc7Z/fUP+TKG2NQPnbPnXukz1sj/SL/v1X7Pb3d/u2cXmGVGQ7YFRM9toqnj1XlDe9+orWs5a6F0nSZjTA1CTkGQAgAITILk4MTQaK9Scp+sUoP7uzaPWxYeCxVrgHkLzs5SKr3Mq224AKF/Thjk2p1MVR1BZGA4DcAFSQZrAuBDUF4X/XEG+oXj7oDWr4UTB3/GWX/3/h2/CGx/nqioKAM0daytC/LFi7yqdCeBOklRCx36iEK6YA7AhkEggAAGT/3goW9CCjADRmsQEdgwjDbbQzaPgWhT/7h4DT1PaEsfLxIqwgCNHZ0XGoQ3pBz3ciFlIzDVyMzAB617AhDRlEkYAAhBIf/z0PfvVTLzL327nvSnSb5VytYA9R0rHZcbNrCiW6QQq6SUMGwii8dgSCkBEELf7ylOTt6B1Pg/l3v3UJYGaFp2+ZWS8FWp5AoiAvOJP+UnAomp7kGHeluo+eb+HU9ujVXANFJWBpi/8Pxzs3X1fw+Di4SIv+E/CgmCCQ2CYvAPWuk/L8eZQ3kYYNE6uXAu/6Ug+rqQUoIYltv+A4gAMCEMw23B2PBnBnpe2WFb0/GQeANUL/5UezqVut/zvPPAbP2pPyoEGGMm/Hzh6oGdzz5jW86xIm0L+DgWLV93XUq5j7opZzGbhDb8YQghXCnkxnTt4p0TQ7vetK3nWEisARoWX3SHl629i8ikkvrQHwmSQkghrqqa37ZnfHDnL23r+f9IZBfQ1L72Pm9O5nod+qBkSvx4CGAD+PniFf07n3nMtpyPQ9gW8FHql3z6h5maqut1GJRn4wMAT80QHM+7r2bhhStsy/k4EtUFtCzr/HI6m/2KDoJybfoPIaT0lHIv4MLkQ74/nret50gkxgDz29as8rzM/WCTuKx0wjBDKdngNXQ0j/Ztf8S2nCORCAO0tp7rqUz1vwpJp/FJ1O6TCAMQTMsN++8UJ4cTNzNIxNNWcKq+oLzU6sTO8U8S5iJqFpz+zaaOtXW2tXwU6wZIz1/U7GbnfI11Ra2yfghmhlCyjQl/bFvLR7FugLnVrTe7bqaeI1zJSwLMgCPlF1vaPrnQtpbDsWoAd07zknRt0w2hn7MpIyYY0pFzjfESlQWsGmDuglM3Eof1NjXECTPgzMluaGi9uNa2lhLWDNDUsbauqrrxRq1DWxLihxmO67bncj3rbUspYc0AAriSWTeXbbXvBNFBDvOalq+1raOENQMw688TzazGBwBmAptgffNZ606zrQWwZIDGpZ2rZSp1TqWP/I8Mg6TIsuZzbCsBLBlAOc55RJSqsKLfcSFhVtvWAFgyAAfB4AzM/h9ARACJmWuAwmT+RROawZk4BihBoIb6ZWvm2NZhxQBD7z/fHWq9baa2PzODiGodo9pta7E3DSR61lTo4s8xIShjhDjFugxbgbUOThEzNQUcgsPAekXQigHmt61Z5Sj38zM5AQCAVGq+bQ0q9oiL1slslfi2IEqXw1bvKNHM1jfkxJ4BFsj8nwrQRTO98QFAKtf6MmisGaBxWef5bsq5fbbxp1ChPmhbQ5wZgATzdwTIjTFmYmHDYQC9z7aO2DLAwjMu/5pSajWbmVj/PxKcM4L22lYRSwaY37ZmFSn6Omg29QOHSsHg0XBsZI9tLZFngOa2Tld66u8EIGf6tO9w2ODgYM9W64PA6DNAxrldKXF+5HHKCGYGpEnEOQKRGiA779RPp5T75Urd739SML1rWwIQYRfQ0HpxrVdTcxcbH5X2ts90ILVIhAEiywDsir8hIZfPPv2/DhFhZHRst20dQEQGqG9ddZWXzv4heAbt+D0OmBnw5KBtHUAEXUDLWVd8UQp5k4BO7nk+NiHAhLonrZyxUdtaEEEGkELeJMi0G8wWfI4O7Qs9SkL7T78BgsLoj0PD+6RyZwd/R4GB/sHtzyTiwIhpN8C+d567bbh3+zU6CHcRKczkfX9HhsBaD9lWUSKSQWBuuHtLcXT0PB34t+lQJ2KwkxQIAAs5bFtHicimgQN7XjjY+9amv86PDrcWJsdvZsPWlz6TAAEwbCZs6ygReSl4sGdrDgE/YLTpme0OAKEE8iO5Mds6SsSyHCwyc35LKMwWhQCAUtDF7oJtGSViWQ4Wwnxu9uk/BDOUm7Z+MkuJyIU0L113ipB0SdRxyoUwyCOz4HTr7wOUiNwARucbCUjNsGMAjgqBIGGu9TxvkW0tQAznBGYa2sagabWUsjXqWOWCELLazTZfmK5p7k4vWtqfG9gdAlPX4KSbl6dyA581wIuxDJhieS4b2y9tdLzUy4JocRzxygEiAcOsjQ7fAdALAEyiRhBSMJTP5/bvUrL6oagPm47HAKdfttFLp/59dhbwUaj0D1NnitKhF0cBIVPQoQ8T6pf2vf+rz4Tjb/ZGoSCW0SibcNiwSejh9DZhlG5BYcYHq6fMgA6LABjKS62ub256AJlMYxQKYjHAwM5nnwGlrpEyFUe4ioMZbW4oaqL43bG9mzba39XlePX7XS91+WwmODaIAGNYB/ncrWND7z4dRYxYX06cHPnV/7g1rYtc5a44mRs9Zwo61JtMGF7dv/PZJ6OKEXtFSmj+voEoxh233DDA/sLYwWv2vv1UpEfMx26A/p2bt5vC5FMkElMNTSSCUO9laiI/UNJKK+T9/OzK4LGgcEfU5wrHf0AEAKNSRLM1gaPCYCjpwTApSrmRTp2sZICMmzpzRh8QdTRo6sp7MmJycqT/34zvb+h/97/6owwZewZoWbr2TAk6b3bD6K9jjJ5gY75rtPingd0/fT+OmLEbQIPmSUIm7riJhySKI0N/sH/Py/8RZ9j4p4FK9DA40rRWbhARtNab4258wIIB+v73iW4T6L89nh6g4mcMBOhiYOWhsDIL2LvjqbuaO37nl0LJjWBqhsBQqLlbEAI2JiuJ0iCRBVCjjamWgk6TjlpSycMG6QjPRtyyebSaOi57KOWlrq7EJWUiQAfmpZ63nrgYMdfIy6ccR+JHpmIvmCCA+LTmpeti3yZWNgbQ/rhPEGWUs44dZoBIVBkKY18vLxsDjA/unKccryIXEYUk6CB4pb/r6Z2xx4474IkipDfEmNouVc4caQgT+EGX1vrW+NWUWUJtXLr2m65SXyVJZZkJmAHD2AwOfw6mgIkHWfO7/sToVltHxpWVAQCgcVnnX7lK3lZ+tQGC1mFX75ufOAv4RmJGs2XTBZQQPr7Fml8qO+sSQKD6lqWvLrMt5XDKzgB9u570GTxQdjeOMkNKWQeh7k3CZVElyuavWN+x0pGicZ004e8L19lAZbqlSBChmM+95KfEZUk4JqYsDNDSsXYlpPieVHKVIIFyv3FUCIJf0FsZ2Nj39hOxLPsejcQboKn9kotUKrNZCFiplUcFESH0gz3jhfylo+89b+3U0EQboLH90kblqJek4yw54gS6zCECdGgGQ6Ov29f11GYbGhLdj0ohNyq3MhsfmCplCCXqHCU3NS1dv8GGhsQaoL5jpSOUvLai7xfiqS8i4TgOP7Jo+brr4paQWAM4qjlDwBm2dcQFCSGI6IGWMzqvjzNuYg0AACDybUuIDZ46PUQpdV/T0s7IXwgpkVgD7H3z8VFjzMPlV/I9OYgA5YiftHSsXRlHvMQaAABC1ncabQ6Wac3nhGAGBIkq6bo/ziy84Deijpfov2x/19M7c2OTNxA5ENL6LauxIpVom5vOfi/yOFEHOFlyo907QM4WpbxzpHIaynId+ARgZqTSVe0knW35sYHICkWJzgAlRvreeE5ODv3mcM+uc0HqVqPNYLJLWNMDCQk/Px7pTCjxGaDE6GhfWMzv7xvtf3tL1YL2BiXFhbY1RQ4B7JvncmO9W6IKURYZ4HCaOtbWCcnrKr0rIBJgAwiv6vUo41h5MeREqV+2Zo4wfK+S6vREVwhL3ROX/k+Htv7iqL4tzXYNM5STBrPGxP69tx7o+dkzUUotGwO0tp7rhVo87GbTlxqtbcs5IiQIAEH7YQHAECQVoY1DoHkQlBXCBUgDbD5Y3ijVOYw2ACNHQnZNjPS95efG7x/pe+O5yDVHHWA6aG7rdEmZR9xMujMxjU9TjccMcKg1hNqSHxvf5OcmX6+aX9vPkGNG+76QrksUVmkjavyJvfOlN69BOl6dkpQFgFDzpAT1G+K9ArxXTQ69t2fPa7EdJ594A9R3rHSkWvig54ork9L4RARBBL/o7zFa32ck3W9jT/90kPgugILMj9JZ98qpkzPtQ0QIgmC3r8Pv6qGBe4YPvDFpW9PJkGgDNJ6+5u7MnNrPhn7e+iviQhC0gQ7yhW+F0tx5YMfmcauCponEGmDh8iv+zFHOH4WB3cZnMJTyUCwUtmm/8Ln+nZu3WxMTAYkcAzQtXb/BcfCo7aceAEg4mBjpuVuk9Jf27/hFYFvPdJO4DFCz8MIVSon7iOzO80kQdGBCacRNg92v/qNVMRGSKANUVTXVVc2de49UopqNvRE/CQHjhwe1Dq7q2fH489aExECiDDB/8fl3C8HLjcXGF1IiDMOe8dHh3x3p3brNmpCYSIwBFrR96gsk9LWG7fT7zAzpuAj8sGv44OCGXO8ru60IiRn7oyxMHR4plLtFCFTbWOQpjfT9IPdOf/eeS6K6niWJJCMDSHm3lKi2dQCUEArFQu7l4ff++9own58xjQ8kwACLzt5wCzEuttX4RIDR/GLA/vp8Pl8RxZ3jwep+AHfOiiVSpf5CCEv9PoAw0JsK4eT6/V2VUdk7XqwaYH5T/S3EQX3cT3+pwKT94J7etz6xYaY2PmBxEOjOWbGkaXFrF6Bj7YZKS7i+X7xj39tPfyXO2EnE2hig7pTmG+Nu/CkkJidyNw7ufrpiq3vHgxUDNLd1uopwxdTTGEP6L93OSapv/57Xfy833B3ZJstyw8oYQHrykwBOi6vvJ5IIQvOCX/AvmG38D2MlAwQ6XJlOuTLqa2OmxnoC+dED3x54b4uVgxiTjpUMUPALp0a51MtgSJVCaGhfsaivmG38o2MlA1RlvNqodnUTAQQH48N9D0on+ydRX7pU7tiZBRhBkNN70hcJmtqvVwx6WfCXDnS//JNpDVChWDFAmC+MOqm54Gna5SsEISwGOjDmB5wvfGNgzwsHp+UXzwCsGEC6btfJzgCmxhAMw6QLAR7Lj43cPhPW76cbK5XAeQvOzmbqGrcoL30Om2PvChgMISRISOigaAI//E82wZ397z73aoRyKxprpeDG9t8+z0lnH5dC1H+sCWhqs4YQEswE4xcOFIPiw1TIf3+g55Ud8SmuTKxuCGlcsma5UupB6TodH3qh8jAIBCPg+xOTm6VyHw5zuUdn+/jpw/qOoJYz11dD6ytJ0NVEWA5QNQDfML1PwrwZFoMXocRPy/XVq6Tzf4hgSoqODhpiAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
@@ -29956,8 +30084,16 @@
           <t>alexanderhamiltonsociety.org</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>https://alexanderhamiltonsociety.org</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBIgACEQEDEQH/xAAaAAACAwEBAAAAAAAAAAAAAAAEBQABAwIG/8QANxAAAgEDAgQEAwYGAgMAAAAAAQIDAAQREiEFMUFREyJhcTJCgRQjUpGhsWLB0eHw8TNDBhUk/8QAGAEBAQEBAQAAAAAAAAAAAAAAAgEAAwT/xAAcEQEBAQEAAwEBAAAAAAAAAAAAARECITFBURL/2gAMAwEAAhEDEQA/APBDlUqVK9jzJVqpYgKCSeQG+aoZOw69KZRD7DaeMV1TybKCPhrZrayThly27BV75blWoSzhOhY3upOoHKmFrYJdRajM0jEbktj6Yoq34WI5tY8gC6dI6Cuk5c70UtHbbNJYzR46AZFVHc3FyWW3MUKLsEbnXp3kiQBSwx+9CTx2cx1FNL9GQYIpfymlsXDi2GjkkS4H4m/wVctvdqcT20MpG+sMBTIwJ4flm1d6XyP4beRo9fQs5P6VLMTaBktkvI2aGLw7iNsMmdjS+WKSFtMiFW7GmywJCstxM8mDsCDpLt6CqlWO4U21xMFlQjQ5G7A96NmnL8J6sVpPBJbymOQbis+maBpUqVKzOanPGBmoKaW0K2caSMgeeX4F7VZNS3HNlAbWOS6mT4VJQH+laR2l7erHOsis+dSoeVVJaNcLrnueZ26L+tb2ltcWwElldrIincZyBTkC3RcMuh//AKrSZJOrIucUUGRhs8gB6ldzWcN5NLs/hDuVOc0R9oQsI4MNIdtuS+ppwUWFWbyq2euoYFdi2znXjHcVrCmMnxCx/F0rQ/4KqBWtV5rn0X+9cfY354UnuTyo0c9ufer+mB271mKbnhnjZkkQmT5Sd80nuGDTNbTrliPjYHy9vWvYfv8AtQl9w+K7Q6hplHwyDmKN5/FledkeNljiv4mBAwsynIagby2NtMUO4O4PcUzltpFtJ4pxnQM5/Cw61leJ49oH5SW40uO9Cw5Sqr+lQe1SgblMahk4GedM75il+jEHwQi6sb7Z3/alftTO4fVY21w3lkU6R/EKXI9LvWthAs8b6rjI35j+lG8O4pD4amSNlYc8Kd/yoQ2stwuGAVT1Z9WPYd62jW2t9MNtLM0vZTkH3HKnNDwbIba8k3tdXq68q1lAhhZI1VQdgFFZQyPoAZsbbgDc11cSKzKgIOOYzyppgmFQsajpjlWn71ymdIxzxV7Y35dqor7dq6HM1W+R3qxyPv8ArWZDV1RYAZJ2HXtUU6hkcv3rKD4pEklsysdPieQmkSHL8QyCFAwAfTavT3MQlt2jbkRt715m2dnuvvN2kQo/qy0O4UpRUq3XQ7J+EkfltVCuDqzphxLBtLQr8GCDS+mMQEnCSsgyfE0xj1pQeghvJinhjSu2AUXB/Oj7cwpKWjcBWUAqE8w9BXEtu1pF5WCnq55n2/pVW0rkgG8CuN91BBpehOY1mkUtJ90h2UA+aokIt8hAQW3JJyT65q7DwdTStObhwMEjkPYVy7q1wAhJSTOMnqOdMR1pMDiNs/w0SzBFLMwGBkk8sUHZ4DsWIyB1oHjcplaOFTpt8lnfv6UrcTBUvG7CLbxS+Oirml03Gr15WlghYQquNx+uaHeVIFQ2tmqITjxpULfpWMUl/daj4raSdO4wN9uVC2lJhrw7ijXcDxOgRl547VtxLivgxrDbqWnYYA/DXXDeHQ2mlCDlhn3oWSwMV+0eoBZcsJSTy6j/ADFW7jfQS8Q4zDl2ZyDsS6CuobjxoEm0nxIpGdlHzZO4oaR7+zc4klCg4BJyDvRUT3D3cn3WhXfJyPhOKC/AvFIgswnjOpJRqB6UH7UyutJ4XHgeXxm0e2TS2h17Pn0zpv4Wm1t4Q2P+x3AzjHb9KUdDT0SorWzNjw3TSDnrtilynTGWNZPPOrHfCoWyxPvyFAGD7O8Uso1RFt8bj+9MhbyIZBM7MCCF0IScE5JrPiLBrARDGVbUw/D2HvVoi1mafWYFlEBA0tHhfpvitrOIi5TxV0FRhEzk46k0ii4hKkSRFQVQ554J/tTrghe4kFxNgADCfxE8zV5ujTTwCrgxt92djWZ4XbPp1KThtQUmtJHeByQuVPTtVC8GPgPvmulxGz20TAAjArJbNzc6mYKmPLGoxk9zWkdyHcDSRmtzyOfzrKFvBhkYHbka6nhF1BgHDjdG7NXEsq3Ewt4+Y8xNbIEgBDyDfvtW8MHtreC5iWRk+8Hxg/Keo/zvQHE4G/8AahI5WRJYsvj5sdKNklW3v/u2BWQFmUfv9aDvZxJxSVh8MMOknsTRuY2E1/cLMyxxZEUYwo/nQlTnk881K4+3aM6YWEizRmymOzfAexpfVqxVgy7EHNWXGs1t40tvK0UpdlXYqGxmquLtpYxGqCOMdBRqvbcRZVmBjnPzLS2aMxSsh+U496vn45/XVvD40hQMBgauXOtwbizlj1FtKNlR0oRHaNw6HDDke1NRLc8YiaPCgRLkkDdj0rRq9UCs0a53VhnPfagpYijNgcumN654BP43D0Rjl4yUI7Y5UReDcEb56119gytl1zKM+pNGTv5dC/G2wHesrJMJrxz2Aq7meK1zJISWOwA3P0FWTwoaXh04m8S1uBGGUB8j9jQ9/wAMjhRJdeqTUApdsZP86Kl4rEmMRTFvwhCKGvprq5iw9p5cgrpfzA0bii7a1VUKn/mzl270indksZnPxTTMGP1NMbS6umncTRxjQMuwbOaV8QbTaQJj48uR2z/ujcxp7LgKn1qh75q65OrOpUqVWWjNGwdTgqcimF0sV3ZteaSsq7HsTS7rR8nk4Mo/E9LkeoXU4/8AG7uO3uXjk28UAKfWk9F8Ot4p5GjkYq2PIRWnsb6eguIn4ZeteQgtBIMSqvT1o8ut3a+JAQykbClcdzdWKBZ1N1bctQGWHvWOPO0/Crkpk5Mfy/WumjmvQwjTGg9KpolaXWenQ0mj460R03tsUx8y8jTG24pZ3A8twuezHGKUsqWYKlYpHlRkjl6UsktLi8l1vKwix8IOM00R1ZchgR6b5roADl9K1krQiuoVsrKVI1Kl2AO/Q86VcaJ+1hflVAF9ad8cJbTCuDJIwGAd8dTSLi0iyXZCnZAFFcu/DpyDFSqqxvQNxUqVrDbyzHEaMR1NZmVH3mU4Zaqeu9WtlDbjXdzDI5Ip3ND312LkqqJojTkKU8DboWpnG42I3BqVKiH/AA6e7kiDoyS7bjOGHpW/2aK4YvJbyW8o+dRj/deftbmS1k1xE46jvXqeG8QF7H5HUuNij8xXTm6NByw38akYhu1PLv8AlXn5IpI2IljKnsRXtrqCF0GtW26o2CKAkt+ZS6nzyAYKf5VrEleaiuJoSDFI6Hpg1seJXpBH2mT86ZTcMhcAyXBG/mdyAMdcUuuoUZ8WkUhjXYud9XrRsp6q0nl+1LIr5kO3mPMdqJv7dJUN1bjA38Rfwmlg2ORTS1uSFWZ90+CYd+zflgfnUlYu96lE39v9nuCoPkYZU+lDCjTnmP/Z</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
@@ -30000,8 +30136,16 @@
           <t>User-provided; general public record</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>https://washingtoninstitute.org</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAABAAAAAQCAMAAAAoLQ9TAAAAmVBMVEX//f///v/////+///5///u///7//////v8///+//3w///+//n8//3r///j///o//8CWIQYYIwSUXpDco4AXIWu1Od/m6kXWHQOU3So1/F9udQJU3qQs8kHU3VYlq/W9v8JTnXQ/f+IyOREconI3+fA+P8FVYa64fAhY4Rho8M8dZA1dZe08P8UUW4XYooOWnSv5v++0N66zdPC4ORIAAAA00lEQVQYlRWP21bDIBBFD2RggJBmmqaGSvFSNU2rser/f5z0Za/ztNc+8NCsnWM4y6qJhAjtobjhNmpWmtF4S1pp7VAZXQMTAlkyxpC+M0C2g7G7UWSvHqaUDpDHbI5DLk/PwQQiQOTlNZXT4W2/lt27AsZTycPHOssgks/eQpZyuYzzvJWcr8SE8vm1jt/pltaSOugWx1uRZbPZ9IZCTWVIXn5+Q5Gy/nkHy7ie14ko5TJ10d5voOtDJNP3AVDaRcDDtex1XQ376iBWCopAqiqr9B9idQ57tlsWqwAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
@@ -30044,8 +30188,16 @@
           <t>User-provided; general public record</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>https://jinsa.org</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAEAAAABACAYAAACqaXHeAAAH1UlEQVR4nO2af4xURx3APzP77nbvQKhCo1ZRsa2Va4u312rrDxpiTPxDhFpuu7R4kLQqaTW1iD+htywLNdDYWisEQdPm7hBZHgimbSoaE6kVjT9uD+ttaVCIxRasQNMCx97e2zf+8XY2b/f27b29Wy5NfJ9kk/t+Z9585ztv5jsz33cQEBAQEBAQEBAQEBDwf4jQf0Q6lq8AmhvUrgT+DezP9fcU3AVHaRcjQiwB3gFYDbLnFwG83qYyPVphuAp/1GBjX650HuBqBtQLRC9T8EiD7fnlv0BpAGRFQaN4xrKs0oDe9p2d06/41MoZWp6jMluBpxtorx7OuAXpVWsCFIDV1t9+amtFU1PTlvnz5m2qqLcaOHcJ7NfFpRiA7bn+ngEtxBPmNcBnC4XCHbHk3natN4T1PIjHL4H9sVBuodEDcMq27Y1aWJra14TzpqcBrdK2k7rsA/bzKqQKD+MEy8mk1S0YHpVO4URov7uC3k2+mx/oe0krLcu6GYi76i2KJ8xPp1OxAwDXcPjEINFNAtbiLJ2xUFS8wToJ4fg2quNEOpa/ClxeFHuB+yoNKqUYGRmp1rBojUQ4PzR0jmxaAcQTpgSeBT5eUfcvlmHM35v43AWtGBQd0yMqZ4couLsEKCwMhkUYMSG/yyi0qcyQFrxmwGJgW66/55DfVs+PVi0HPlal6o2GZS0DtmrFtar/9ZqNN8z30XjFgCnA9yIdy8cVI+IJcwbwdcpfp5s1S7p3z/Aom1S8ZgDAR4G7gR9rxR3Jva22bd9SFG13ZSkltl1SLQDaarT9LiXE9+MJsxeQI4aBUSggVNmrFoBhS/lbM7m4tFyyInolcBX+YkYlEnijTWX+qBW1BgBgZTi67KnhTO9JAMMwZD6fXwXMp+IYW3Ree9DiozNdOEtNNllVT8Qh4Ahwk1Yc4UPNNuwE5lLxAnwicYLgbLeiFnOEEPdooe+BReeFEDpiR6r8WvDnvKbVo50IgFDqq2Zy8UVd2RbyPuAjxfLWcfwiVM5cH528P9Kx/P1a2LWu8xBQ7wFmP7C3zmd6h5ubn9XCi2LuLGBlnW1UI+8W/AzAW4D1ze1dpYAmhEgBr9VhdD3wWKXxGpy2pdi0r/vW0jq3ML4BXFGHTV/4jfKLpJSf1MKudZ2ngA0+n/09kAV+Bzzn85nNZrLzqBayInqDQH3F57NjURb3/A7AFKA7HF0WLrViGD8B+qvUPY9z43oZ+AOQSqdiuXQqpoB1OAPyEnCa6peho0qIH2rhH1zbijOD8sBQA34htzGvk6AXd+X6e57QQjxh3sbotb0DZ61eTKdiF6hCPGG2AFNxBuQeV1EBuCudivVqRVZEpwI34uww44n8biRwvk1l/qoV9Q7ACaXU/OFM7zGtiCfMHcBSV53TQDKdim2p1VA8Ya4AkjiZIc3PgaXpVCw3Rj8axljngEqmUNyiXFQeY2cCm+MJ83Jse2N6Q7zMmXjCDOPcMx6q0v4FYLjOPk2Iegdg03CmN6uFeML8BPAlj7prEeIJ4F8V+vcAqzye6QRM4EmtyIroFJyZOcLEbwUCsNpU5j9aUc8AHFZKlS4wS1P7mi3LerBGG8cQotpW+SpwHHh7lbIWoPv2tXt+vXtdZw6gWeUjedH8OHA9jbkWnQBu0ILfARgBHhzO9JaitmVZdwK3eD/Cn9Op2BvxhPk2nItRAdiaTsVeiSfMY8DNHs99WCh1N7AF4CoGz2SJbgN2+ezrWJRdXP0GwWds216UH+gbAViyds90pdQA8L4ahtYA/8RJdswp6o4X5fcCKbxviydsKW4yk50ntWJQdDwpUAtq2PPLkTaV0f3xNQMsYI12HkAp9U1qO6+ArwGVV97ZOMmW0zhbWojqzJK2WoUzcwAIUUjYyHnAdB999o2fg9D2XH9PRgtL1u65jvK9uxqC0c67mYm385ovLunePVcLTWrkMK58/gSQnkIVXlZKPayFrg2/CCulNgJvbUBHxmKaEmJ7LLk3DHAlWVsotQnnFDkRLnMLYy2Bze5Dj2VZYSHEfinlfqokJGzbRjlJjUXFXy0OAD8rhEJSiaqhQIYKBQPbbqF4NpjDwCtZop8HPsj4PqtJ4Kxb4RkEhRAvRMLh9tcObfN7gysRT5izgYPALI8q54RSbbvW3z7ZKfFR1FoC3xqP8wDpVOw4sLlGlYfeDM6D9xLYoZT6TTi6LCxc01MpRcG2MULV41euv8d9jH0MJzNcmRs8YhlG2YfYrIiGK+qgELSoiygkucanxUvLx2sJ/B1nq2rF3+lL4Gxrj+b6e9JaGU+YC3GyQe5F3pVOxXZoYVBEFwp4gInf9Gqhv2+EgJNtKnOrLvCaAdeN09D65vaug/mBvlMA4XD4V5ZlPW3b9oJicHzOlnKnrvwic6cWnMTK9eO0Nx7Kvgw1+tvg1VLKe7XQu2Zh7szZs+sty7oohBi2pVxtJheX3nRBhO5lcp2Hil3gUnwdXulOoh74wRf+NDQ0dDAk5S8vRiKllFhWdMwC7r8E9seizGf3EmhUlJmKM63vLClaW1eMKNX01Lc/47KhuoF3NshmPZTFGncQHKZx/yMEsDTX37OzWkFWRKul0iaLM20qM1ML7hnwKM59fKIzQQFhYFpze5fMD/RVi+7vxvk4OqnZH4r/JDXJNgMCAgICAgICAgICAt58/A9mLaTINdxv7QAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
@@ -30088,8 +30240,16 @@
           <t>User-provided strategic note</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>https://newsnationnow.com</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAHlBMVEVHcEwbO1gZO1cbO1cbOlgcO1gbOlgbO1gbO1gcO1h90I2AAAAACXRSTlMAuhRQQMpq3Jab70VbAAACe0lEQVR4nO3bYVODMAwG4FKg0P//h3W62aTJmrD0vJ2+OT+tR/Y0JDhxpIRAIPKFmJ8xp3P3x+l7/+VSyqX6Y3eVIB8XUi4AAHAHlM0VnvdPyZerMMDqSz0zVgAAAAAAAAAAAAAAAAAAgDcG5MfPk5Dr148YAaw7Im39kaq9ov712NaLC1BblD4XX7+/UNorh1aFtk535AJULd8I8JlwLkDb0RCgFS0CqEobjAFVtkEIoAyoAajigBhAngQLIIoWA9TjKkC0QRAg8pmAfnaigF5gA7rTFgZ0bWUDujaIAxa2IweAz04cwHfkAbCTMAHAri4eAJudGQC6IxeAdu4MQN219RGACKYASD4noM3O64CV5lvluniDhd57/7m3/jognSTfoawLALtVX8T6ZUCi+RZlvQekjRzwmJ0IgOUrDgAvWg4DEmuDzQLcZoW1QRzA8n1fkscVSJmSSxyQdypwAJKYnRiAt8HqAIjZCQL4dWYzeyCJ2YkCctdWZgX62YkC+MX5dAB40XIcwNvKAUi0c/c4wPh1I3rg6X9PXwYkPd/zCvA2mADQdzQAsFmcANBPwgjA2mACQN2RAJDPTfySPAGgnYRhBbSiRQDajsYApWghgJLPAMjZiQGkQAB2fsDWC4IAcRKsCog2CALE1cUE9N9QiQL6k2ADutkJA7qriwDs4gBetDiAt5Vdga5ocQDfkQfABBMArK1cADo7MwBU4ALQjzNTAFmsj5rwFu0k+ADmFyjFunWEuvzO/zEBAAAAAAAAAAAAAAAAAP4loPz+s2b8IZfDFer3mpS9+bIxgC+cgCf31tUAAIDF+WDYV6zeMbyQ0/n4GgLxl+MDvI2rWAD1FZEAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
@@ -30132,8 +30292,16 @@
           <t>User-provided strategic note</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>https://thefp.com</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHIAAAByCAMAAAC4A3VPAAAAdVBMVEX17ugkICH07+jh2tUoJCSMhoPp4t3x6+WWkY5GQUHFwLtVT1BoZGMkHyJJQkMqJSenoZ6gmpfSzch0bmy+uLR6dnQ7ODh/eXcvKiw4MzWyq6ialZKSi4rZ0s5BOzzk3thdV1ZNSEdkYF9VUE+4sa3Nx8SFf36A1vu/AAAELUlEQVRoge2aC5OiMAyAy/EoKKy8VAqioOL//4nXpC2g3qArj7nZbXbmNoFOv+sjaVKWkKXlD//RSI3USI3UyF+ALOxHSQlxhUZ7DUAvH1qWnyGPxoMENiE71CzaNUA9fWiaTojsYYjX6asZkRKDDb6WRG6WQhqzI8OIiyu6qEGPmlfISyTF/AyJYoq+fGUPI7dDXWmkRv4qZANyfEL6McqgV36I7Mtz9AleDFYjfzsyA3lGZgzlNgMS/fLPjw8FGqmRGvkZMimlOIshW3F/AvJl5TUB8qzsN+vLMcjyASmqaKNXRRv/qqJHjfKyBmlPQB/NNe30C+iNaNZKOAJJnU5ag6q3vZf00foYWfZm66QM67iN8e2xP5W01zQfgTT7SDNodauAt10mFHCkNS/SMK5PyM3cSG9WJEtRKCJZk56xW3VzEOLLUiAt0fQ0FrlTRiAMitsmkkh1eSaQg3v1cyTZw9PbosgDPN3+dGQCT+05kVnBJeyQJpOOAMgg2XMpFRKM/WBS8L5fehKZFTYeJ9ap75cp6fvlcOX+baSShCyN9E7zIi0uX3dIC3tF5NHjspLIAAxvPHJHQSRyc8bNs2qRSzgJxp7DosgcflWLIsX8OksiBSldFInx7rYoMoSH9aJIzPTagLdDuclQIKxoaqTI2fO7u67kLvc5TIpkRC7mdiYkziFThkJGGOjuUufpkI7LJXo0TFBcSiK3lSuhneGuxiBDkBzrgRT11Ol0bsHgbd+XH0mdMDlvr0Mdvkaqw6tu5AryM5pnIMSXz3kVGOGEbqDYisVM+8Oe8u55yUyFxJXqkKq03MTEUWtrj0WyNYzjRhK+ey47/k/mINKr63pPLjAHNW4g2FWs4tVQNqbYM9EbGguiDSAdWgVQAnFkgIsK9daR0hpcCf4fK8w4P/x+2UMS3mMmkCTnT4oOCQ0qntke12dacf1ESlZXEyAriJ4CCWvn3o8yk1UPjHKwZP/mKC05SojpUYfEtbwItYD9PDjA95HmBjI8uZa4VID0k8SWx4qHbunADb/1cpxvIL2EIRiQNaiMKieBEwyrTYbxBlOUFy7yvl9yt0tUTpmTPtKBcfNaFpq70CRIJkEyHsUUEnrsJpbvIIwRGc5tjqGoGIusb3YO+wOQVz6xXxLZFTtY/Il7vgZmPhtbuKuLXdw+MKPmIxL3qiXsOMMtPSEyEr7XhYK8sB3hKmkeHVKBH7x+/i4yFovZIiEYXcXtwTXDV43Ru0ydAkkZ5gOIhErFtCASOBDXmwo+GRPbEBnnZEhyDiCPVIdXDbHQwK98jEJUsLBImiDGCqQBSFcFPIlsVMoTEnqRajXU5TtI5dk+HhQrXKoOSVIcVwab9IRRIfBH3RXQ3jd7k+sUn5Sox6jxNlf3kEtKUxyieBD4n/1RnEZqpEZqpEaORy4vfwHIJ1g0XqtWNAAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
@@ -30220,8 +30388,16 @@
           <t>jwpf.org, influencewatch.org, causeiq.com</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>https://jwpf.org</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAGFBMVEVHcEzHJDfGJDfHJDfHJDfGIzfGIzbHJDcWov4lAAAAB3RSTlMA4hy+lm1C50ri7wAAAoFJREFUeJztmNuioyAMRZsQ6P//8STRSqioOOr0YfY6L21PZYdcoa8XAAAAAAAAAAAAAAAAgP8b5p/Kl5zKL+WF3vQrD3CR9FbkF9pcsu7doX8ZAVZKyVnSrK76+UE9k8oBEUmJFu2n9dkSzEXeNL9a8WQF5NSVbOTzpwDKSCWcqpZyKJ8k7F70beatluSJo3lD1eIjeTmWt5xYlisWIbIPSylcsYx16SVnZMBZRfoBD0wrprqW1P9QUiQ5tF5J3bCbODwg/1kqVAAf+ixavxOKcXltgXGVMxaYEakbipLG5Vv911S2p9BYNEtw3l+AjLCDTviafDvAv0iSixeP9faBZ6bMsgLYiGGJXXp3KdEC8a9qRliHHfYedfdenTjmgWkNm6cjX/9adG/8Hvcvl68O5JEnrLJDJ9nRnztSfLazxfYEk0dMtjh5W2n6bz8KiyJ5Z+yURruFb5O/hMNrLbuhTm6J6Jm6lVrCsf54NwbB9ycm7zSVmugmqe90zdAL+x0s1Lu7fsD3HVcswVB/LCe4eUvVhG4SxJaT2SfcaX3bnG9WQnOg8HI2oZ8E+tj8+XfHPWeCR6O2WGlzksyEdRJMu9cu6UeIC/ILPmPIuh81GlNqr5Mg2eHTpO+7denBpPDHFDtNLSlKvSGwdW7R3nnVI1zmSVKHZz8HVllv80qtvvEYftCFKZdwsvs0lVvvQUeHGKrU9Lj3Jrrbh7s23X0ROXmMeuIiOjbBXZ0u9aRNBp1gp7cn5F9e3BHrQjJdLBoD9POch+6Af23I54+nFs6rOwo9+2tA16gvG57JggMbdJSHyfET2A9Z6fIcuGQDP5p/AAAAAAAAAAAAAAAAAC7yB+fUMzRDXHw/AAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J28" s="6" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
@@ -30264,8 +30440,16 @@
           <t>jns.org/about-jns, Wikipedia</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>https://jns.org</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAACAAAAAgCAMAAABEpIrGAAAAbFBMVEX//////v68AAD++/v+/Py6AADefX3DExPturrnoaG3AADQRkb34ODopKTmm5v89PT56enGHh7IJSXhh4fSTk7JLi7229vkk5PpqanwxcXLNjb77+/kkJDdd3fYY2PZaGjss7PyzMztt7fPQEB4gaOLAAABQElEQVQ4jb1Ta5OCMAxMUkMrr0JFlIfC6f//jxdaq6cjfrm56wy00yzbzXYB+K+h1G8JyoMFXC1vYGQ+ybT6PSQpn0EJBW4iTFZ3SoRhOlcyhSpieOJbjvA9oLUIuemGICY3pooK5to5PYLTxURE9U6I2kZWOmsXYRvYpsxpApoolW3mBIY9S53YA4R3Tog9oDFfo1Sqjqhv8/lwb9MEQC864UxkBJAtUjC2efEAzhbLS6IjOqLr0UZrIoMAUMGWqICuZiZ3vFG8AWCV1MS0DYg3ALWYR7RXawxWTldO+nnu4gE4NZeu1K8MaQAwF1Z7y6j0GmTTA7L9Se4QLn1v1K7XpK+PLgqiEZ5Sh1U73IxCm8/ii/mZKPRZwODT4FguqHlNEcYwQJUy6WlYj6TdHeb8QyBv17Ee6eWn+Vj++/EN2u4N6fT02d4AAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
@@ -30308,8 +30492,16 @@
           <t>Genesis Prize Foundation; user-provided bios</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>https://genesisprize.org</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAUVBMVEVVneH///9PmuC/2fPI3vRLmODw9/1rqORboeKSv+vd6/m21PH1+f1+s+jE3PSexu3m8fvV5vevz/ByreaMu+qozO+Et+lipeOZw+3P4/dAlN8n1T6QAAAGMElEQVR4nO1Za3erKhB1RlEEFATxkf//Q+/wMDVpknadZvWscxf7Sw0OsJk3tqoKCgoKCgoKCgoKCgoKCgoKCgr+OWDCuv6l/XsprZTS9Rb/DoHZazFq3emaYaQQ1PGbBBAvY8+Q6XGRmtPWi7XD7yqDjRtWTLe13msiIrwV868yyAREdanEUhnHLs50f4HAiBXus4N935t2+U0VZAJ1ItDOC4H/4v43BHoUmrHevnP9lGdeCYw97R0JND1bxDSJN4YBVm7WehvWF0uuQeF8TU9YDQN/vb+fvq0hZMvYAqEVlrPvTvrq+A1M3/QR5DJsbiZBLNrtXXqtofmmJK8BxOaIbrcJgP5NDNzivifIPIBdo0ap2o3wEd03jpkFbj31znXx/Bsv+FDoHugUyKvhsRphT6bDdfZS6uMYwzbgGoricnU+8kRNEkN17OQ2G38fE+IgD8vY+anLogTTnV52c8ovOAuIjlmnqSOpKY6oMccKuuy6TZcO4Ns0Q8YZNdRBaJjiIIjliXt3BvwNuawtC2BqbXeaGvmRUxu1WxkG4ga4KNrb+0aBClZDC6rR81YraHgiQDljVSBs31sB6nHawEE9eoMzAJ0UWdWbtF5DR1sqxlAr8PH8BsQQDDwIMA4rHk4SQFNDnUwEPIiVWgi2Tk+CAntoc5vFD9BzkE+qxyUFRgOqj0qkk8YyKOO2mYpE7BS4pGW5fxAYoU6zll0+TAu4gckvdpOx0CmUclkvF3JLFgjseYZTijZYDfTZqmyDliNvgYwfjcPwMAGLNMNoGnxJIDkdhAMzOuWawTW00QQyr0C67knxAO5QmaNnrEI68S5YKYolDbjgSvP6bPtgbNXmIFi7AFL+jKyGMxT5fQP2RICR6W4QlB6jQE12+CBAqo9RYMb+SZ1B10JurZJBmcgE2g+YtXpE4CQRjEJr6VEoGrfXKAh5oJdTYDa5xwz4DuPJO3ANpyHTie6E6jMB8k13kuC5UeZO05Etu2ogDnYLBad43MHRUdR8yhF1IEChpI7slP/cEag60lyeljLHOrikQqyhPQhwN/AowWb1tMpQGHfHUoyiPJikM4fPIW+mGT8ToNQ45fSKlko/9ip7MylHISYCq7iWVwFPCm0I49avQVmVq8EEHwh6ARv11+0USA80EKbtXZDglAIDZ5VnUHIXhwbImeh0YXBQ8LSNXwwFkPTaNwbMMCVB6hF2Pc/a0OqPTBA5GjvPW7B51AMlz965nozoDwIhPQk9uMUbmJ7eK7GjfJ6wu8uUbZVLC5hUnj8RoAg2SaL1aVznVZTPUVCdihGIJ1EQGaCzzTQ1dqFHXafagF0YG7ccv1s9H+JWZgm+jTTLHysz55uP333dRyF6mKZJ9tXz/aMYlYLszqcW5DpWnZvA09ONBD3x0288C73e/p8AXvHo1S8Q6IYD3Z06uRTvamRf4aM8Gdnd7Menu57qAfDre8TXBOjiQJjMfUTxRn11mVj9WP/0Kl2DvrAIN4G5fffVDYg3lvLVD+1EBI7wokKxYHQ9ZJwfTnjnpVSUOE99CPbW23r+7kXpSwKhk6dKpcXGhqalJyuoidvEgSmUXXRSKGViykI/22bsmp994jsT8CHNS/BUYpUNWZpaNK0SILZn1daCEtSdqC3kbOsX29c/2v+GgA0akDCa1g9rIlCtLoJ6dCo61OiBdOvqJPXSNE1Kt00//Jxw8gEeKzatbRxLd5Yej3vjmO4xLRXE2ApTzxs0v0n/ohZ9l0COAnpseazXmVJz7XWYBqCDUksi8q0CI9mQB362fSCwextQt9CGNantyOF3JRDaO82Sl3bJJJ3MN5Mf49SoT0vqWOpru5gI4NCCzSPq2i/D/p48XUOjI7b8cUheO5RMIPhGuj1hA625Qr6LQPaBI6nLawXIBHhztKkYyGWw9xjgJgwfE6Bd2xxp1NWLLIVr96bPmV8RQA1quORUzExQQZUu393bTPCKQPhccXg+D5cESkRUBXUL7/oXx/iZwI0TUlrIybillIMpFVNj/firwB/A37c9VIzyQCxG+lSMghFcLehW28zv8sEqfTl5OBCfOD9/YQm5L95q//1muKCgoKCgoKCgoKCgoKCgoKDg/4r/ALfJS8jSebWTAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
@@ -30352,8 +30544,16 @@
           <t>advancingamericanfreedom.com, Free Beacon</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>https://advancingamericanfreedom.com</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAwFBMVEX///+9TExNgqQrRWO7Rka8SUm7REQlQWAiP1/8/P0dPFy6QUHv8fPm6e3u09Pr7fD57+/CWlr9+PjU2d/Jb2/qyMg+ep8YOFpJXXV2hplZbILg4+fHzdXFY2PHaWnMeHiPnKtic4i6wcqpsr40TWoALlPOf39AV3L25+fy3Nzfq6vR3uflu7vUkZG4OTmdqLXan5+CkKC4zNp6mrJci6mIprues8W6iI5oco2PY3LeztJrlbG7maB5bIFhgJwAH0utwWucAAAIsUlEQVR4nO1bi5aiuBaVipLwEhEpSEDlpaithfR098zcvvfO///VnESrWlTAB1atWVN7rbarUph9kpxXkkOn84lP/NOhf7QA4QfzB575sQIUyP4wbt03DJu5uWH4hvIujPkRTUFmLkbqbJbF5T/4j5kV0zvqV7E9jBBSqX/0ZJI/RAAbn/TrE4QIPW5VsrR1ch2Qu5GpmyW7t12C1KhEbup64LoBPN+mXigB81iKUs/zSooQumHASnbgU3gGo8zzThbmPtiMLzcpq5tC4VelKK9MgeBJjIq2DcOkBOEjNVT83WeJS0lShNKkdcPUIxWR9BL7SgghatI2f8dOvThyL+gXJA1DwloPUklkdPQwan7Q9kAx4qxtX6QEYlGD5qW1RXQyWhDgbBe36ZZ+y4Io1LiJ7ByS4IYvGV57Ht0Lb/hSgGlbtuzP0JVrYCdJQtUsT5L4XiF83hVRQ/jvitxJD2cQZrA6825ZvHJXCZlBzFRn5AILOoAI9SS8l57DjyCKIHpt7lioBJN2AloMPaXXTqXCCM0u8bwXdEVdxtzwym8FWaLY7ALP2wwfFx2detd5FUW4DjNvI+mPuSXpycel75/4xD8Md/v+RtSboxE9+sTDrw/y+UWJ9z3Is9oAQ9247s/3Q6GkikEPKaUp9uDzTBby9bevvnlncqLnbwxncwOfzlTY1blufkYPvjw/ffv5/cfXL/foCDAQzoCTil4SSBwwO6sF+tMbvv38fTqfjibWfHDwwHAwWDjOerXdzOfrShESUsnAYaSYqOe1VPntlwRPf0hyF6Bthpx5OFgC8XwkSRK0abKsjQbnuhDjcBE5PdF4Q+ymFFUE7h/PBxL82esB3XgqBjydWJIMvF0Z/kG7NR47lTMwSylJK3WJRjbs6s5raXDA//T8n8VA9DLXgLPXlTXJmsw329V6OawcXofbAOww46wq0VJE/mGf39p/+XYowff9M8O5pmm98cbpLxeDWm4BU2hfBUPTd38eCvD0dci1buls5yun3/81bt7a7ztOpRbcDOV7SYCn/4q173VHwN/vL+ABrovb+cgC7ZC0TesCdH6UBfijB4sPkLkEQhm5Lsq7RjCRfusCxM9lCf4HJgeqN92sRpImDAAsoMfV0RqPpqNV6wKY8fdvzwf4/++rNVe9znCrATPMhfYij7ZroY+A1gUQ0H3/C8AunU4rWzEV2/XiMaRNGA6c0WrtOB9BD9yrzXRsjdfcFMSsD4cLMIYNRITWDWEIrmbYUYACfMBiCbq/sV5euCuUehaXwFn2ne1Ie9GETnZfKh3yjVhOpzAsjjn4gLHV02QeESTuil8mK3ABY7BD0SRa5fmVimg3JKSLiYiBAtzYdzyybI3mW2e4luR9E7fFLhijNa7yBfr5YBBXh0mB4bwrHYAPXO5am3V/IRzxShgjTL402gj3vFxWzYCfnQ0GdNawF95ovb2fA2aIuvPt+pBj05OsEW8aNsWa4CTz1A3AzE1Mw6gRwhmNAZPRlAfeY6sDg5jCwJtsUTEN0yhcapolJpN6zMM4Yx6rUQRlsOAYcGM4wgIyIkuYQoMESuIxhlDKGCvPQpjybI1E158KQRDcSi8az0uEO4BF4UbqrNfb7WZ1qgaxR/hN1/H5mxJnGJHi2px36GymVu/V9kRsXq+5a5J6O29wxhf4DENiejLSAMavXnHPAqkoRH+IwN034+uN5ytIB7q7wLhrnJx+U2cEk+xY1xRQjDBN61dAGb56QWc9t7ryGzmwS5PNGuZ789a0wxl3GGOWsBM7MNJc6QQVCekrFuADwQuOxlZX+0XEc9Lxaq99g6m88xEgHqSL2sv8WGGVgpqwRSmOmm2xWdDrneHAkvdu8Jc7kiWY+APVH0xkrQfOcbPLDBYnafKe46ZzgGNf2NVepO3eEb6hP13xlOQx19kr+WDepcl8dW4b0Jyd3w4HJp/nXj0+784jmSqwtHjw28DqXrALeQg+iPYT/yo8viqonkEJH16QU38dGmTt3deeR1x/sV+Qy4IEJJEHP5v7JoGGnIaiKgYlADC1gE+7cR2i7C2lMpnncdI88zgqD4B4HAyC2KtmSFJRGOXOqs/xXhG4WKX7oYYqFndyoYuJ67qzmjXOXxmOS6L28EWlDA4bLUHhBS37GgmTEUSYKQTxQkDdGu5qcdRKBiNFkJg20fN6EpxBN+LnhKAU4ZgLUHMC+QrdrWWwMUHuBTcGMNicYVeMwyNZnhGmvM5AfWIdzAhSWXXHOPSrtfQNBsHMzFWXr3bgkghWBHLMUOUH3e5ftXZcoNymuFLHKOcOGy+MYaxRkKuYGVwbSGEX/PwXWjPY79RWWOqUc+dhxZ8VY/fZYIQ6w5gQgjGsvJ1h/gtGmc91wATUfVu/jKEBCcZeFEUsxZ4O8874z0gtYBou0N8WoDPXTXRd9+H/HKspr9wLUjdjqttsBW3Ap7QQM5lQDnG9Ii5jKG2/gOxfjhYrIm8r7yzay46CW65DTdaeTkW3VIXZqDWr0mfnz+UqoQRJkhSEl3Kdu8S8CrwqrFBV6Cq5ItvTI9cV9VcNJxaXdBVifiGrztBVV1V6kvLi3DZKCpUgw7XXpRXg0bWtUi6M8PWlXJEKSU8rd/lK4aape60dgA34STt2YKjMDrJr63xFhb7fSn12wHdbJr1SB3Z5RSsV8rtObiqsLUO52I78dgvrX3HyhkUlHvWGBbq0X5a1za3wm4zcjXzYfB6tw9GvfIsazGZB8y71OgSeB0loCln3sSIcuQpjd/UBH1G7G32bEfGGxTG/f2zfOhVvWGDadkmWGUG/2YlDPS2MUnJexXv8TtL9UKiKSfk+gZeKUuGuS2wJbFTII96wYEn5DQu9gC0J7JPh87D0So9QGKJ3ecPCKHhhFHJxSTHs7B3fsIhFpC9rgS+0v403LC6AoWJVfZ8N2XkkrhemJxdg7whKTfBRH7cl1GOu6/7dL0F84hMfir8BQDfBSBmhsKEAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
@@ -30576,8 +30776,16 @@
           <t>Public record</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>https://babylonbee.com</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAPFBMVEVHcEwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAD7sDr6rzr/tDx2UhudbSQVDwQ/LA7loTXKjS9Q8JaqAAAACnRSTlMANeCUX8eu9Bd1EynQTQAABfhJREFUeJztWw2ToyAMLQqILWq1//+/HvIlAgGq4t3c9O1unWlX80xCeET6ePzwwxdgmF30T0dBSfbijNKKBBghuX8hBNWzX8CANhXvX4KkosBIU9m89IH2MUO4bwV6jDQnVpAjFzCgFK3We9I9NTrSrxyE/arxN0CCAWqtdc2hxUgyuwPiTptngKZy/jtAZDP7fjsUbiKAzO3P02cR+EyzYYDvtD8unL8U+DLqTLjBB0zZn5dheFkMwzLfxUDFf+TS/OoD6QY+8FFmQ/VChGXmjfwVgE+SQV/XvgrAuLxU/Dk3eSCOKhEqB6HV8ReO1xT0r3gZFIO2pn22ZsB7Ct2vXj9z7WqAOxMA5Xx9MEe+uqCrmQUyAtPAzS3bCCgvDDIP6TW2xGSLex+NzgAIsho0wWnYTtilxnEbmW108Z/1+N/XAXUcRui0Z0NxaXIg2Locg7ADUgRWDm0JhYx5UYSGbfzv6sBKYEqeK1RDlgIm6UusOajzz68DNgtTIJkJs0/f/kYgVgdKCGRGad/lzlcEgDpQQiBZKkvsrwSgOsCLCMAM8M5+J0Seh8Z4ABwFkkDkxG53aSAKyIm/GLWR0iEZ6hC8tOv17aujJBCLMsPUvXo0Exndbh7Q1w6BnV2bhyCBx358R9evOEPQ84CpAyYZsgR2QzzmJJK1vxEISpEeBmkCjp6PLGFx3r5LIJGEiZG+pVlohCa8ExBw64D0vz7mCDx6e5vBR/AnIYFdHXDnxiyBhw2CHwMM+ybigaMhEEGAHN2aDxInZwkMeQIPU5F83USA90MCI19A8DwBc6d+qBvAMwGB9zwmsEqyNAGcIZCcrtVk8RZr8jjUYj1NwCRB52WhIZBULLhktjxIwFy6wAN1CHwRgosIeO+bUZBc2elhmEB+FJha6CchNDpiBA7ogfBO/fFuK2EqC0/pAQVm7Pj/ZD9IVaKTemBFC96oycIukYZn9YBIQZPGfg46E2Wi3Xt6MtpUT5jszA4x+IHDWT3AbABiqWZdADM4qQcc+7HRzjbRCqmycyFwZH/8qYZb58Sy4Np1AUOb6ofmXMdDay62fY/XH+eFFnlAsPdO7Pt2t+hugRgzlySE97hm3CJ/zUG/I1C0NoTb+qiEQVKQJDskWfuFDN7qZ3/QPyftP5zlQS1kHmsVdQjOoUiypgAJQi0L8zjbIRlhVb4sZR2SZKU1iDRIjndISLO7dFmHBDEfykOTfVaipgMzD7ilODgV7Xqv8WcKbocE6CdGZ0P3mO6QbF6IDgW3QwIEaZuMdkKsVA/gzQmx2e6bDomchLiWZM7xTIfErpsTmux0f8AqsogLLLmSDskhPSCvYF0QfGTzAz7bELAKzB5f+niiQ4Jg38Q94KdhoSwH7VzSISlZGZmRcLxDokMQRQEBc6d+qIs7JGlBUt4h8VcmFy3P/4MOyV8jUB6C95zAFyHw3i/vkIyfBKYsgSs6JKdaNFd1SL7XAwoXdUiO6YEVF3VIDuqByzokx58XFHVIYAZnJyNHdkZsOB0SKBFP6gHHfqZDQgBVekoPMOepXXyji1Nou/h2B1y6LgitM+yocoiiuzLsCG2DvSC0qA48aXBi2xJ3GoG6YEGHpPMg38xWQuC8DYkOSXb7xFMLEvvi/mlBkkOqQ8FKGJxEZqdVSYfgFLLbnHBTpDoOoinY58X2GRsgK0hAdARsTeyBeprgMKcECZyEXUP78n12ctc2DSFlObyXbOBSlpPwRGf/dzmCNgeThWKWlSiqBwbpARI58aot57JHM4J6YKi+pVK2kebPENcDygF1dzfLYj0u8RSQGyqT6/vzUJJqkrO/pwf0TJSSdFdAbav98EgaqjF40YZOEEq2zFNgX22pvWFvt95DMMm93UYHiAqgt9hX3li9QmvH8cMHMxqG10c/qai6q9lj8B6nlcMw8GUyOqCw1l/EwM5Ldgbq77G/U07OE4J7vl+hwMKtt81N7jdArftNGzHT3/UNmw1C6VNCuo4IAV/zG35pEogSdNlcewht7dL7I/Aj8M8TQDfW3x/+U/wBAXQQPD9x5MQAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J36" s="6" t="inlineStr"/>
       <c r="K36" s="6" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
@@ -30620,8 +30828,16 @@
           <t>buckleyinstitute.com</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>https://buckleyinstitute.com</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAb1BMVEUANWvAeyjX6f8ANGzCfCemcTInQGLa7P8AMmmbs9IAN24AMGmrxeLN4voSRnrD2PAAK2YvXIttjbK60uwAQHWHo8RggKa1zOff8P8AJmJ5l7pzkraRrc2BnsAvV4UAPHJOcJk+ZZEiTX5VeaKku9jjppkLAAADoklEQVR4nO2aa5eaMBCGKbRNYAjhDiqKKP//NxbWlkTXXWe3r2XPad6Pwjl5zFwymcH7trI8B+AAHIADcAAOYHWA7yvL+7GyvJ8rywtWlufk5OTk5PTlFRBHabrZbFKSEr++VgxpXcThPj8eSkIjkBI+Q2KWr4pxNxCWgRRnfcPhq7hOkAgfA7hAxOceRzCZ4LK9r3f8WvZTFZaEAoi6MAzHsdH2+jq81vxc2QxtM8D24KVyLJOhMrYQ4U1hGZVJVlfaQhBNBtuDWVISVcIARPL2uSR5yguLIE7AASlP1g5Ed99ID6PlCNXdl/4CINLifYDJY5OxNZ44QI0wEcQPATwqG8tQKXT9gBgAHtXGV1WJ9QIWgCzHZQvaM9QGvB3wKDc2qLA2YAJkJg5G7M2TByB7EywNNhXwADxa4kAUpzUANvEXAljFBBZAg00ETIDU+MCIzcUfjoJ2lTwghyUPtODTiAUQ0HZ5S99WDf8CQJ6MC4AtwAKYNmBJxAW2KOMBpJkpXnfwO9JjABrMQdDhL2mPAGR6LkwOQNekDwCmqtjLqj/3SOF3+PWvANIbBeWh7pQ5BHYBfn0LwG92ua3tPoz17+WFaFWXPWN9G0C011ruhsLXcZ5swPH3GuAtqTHP+vQZ/54LEFfnrJTwAGQDzNd2Fe+P0VNs8I4PWF4w+4EKh/QJCFYYjtmNjvWui7W/vCDCg4RPg+w8cNO7k5SmVA5bbfaoGcBn4eNULIlOlUlG+ojeg8eHUSApt9Ih+nrOOY5nAmOFVSoiuVtisq1WAJiqYlOTaWxNxL0XnE1aqqBuyASQybMuh0yAQC51qe8fkTZgAnh0XAKh3SOzERdAnkxlOqZAL2ADlFaLAtms5AJ4gXlRI2tTNgCZTp1ChsEndmAdACsX+moNE8jEREEBnN3w88BgHYirJKJ8SYSiQyYiTrt+Vh+awqwGAjCb1R4dTGWooOcx9zjurJFFD1yf2y0/WhOLGjs5Y01MBmtmM0I7pbIvHgJIGqzJHXhqRYkJ77daNFQbB5zbdMCzWFJQtRbAncGld6iL1rq/VqCq/NKC6bOr0e1Nh4aiZMi7wrf+vkB1iYJwnBQXV1N8Pb78uigutPLt4bVQe5QDcsf310+LM+xrkk98wNCq7QHn/x8EmDsku2QD/YTjztcS99XOPbL9OcF2qYJGM1Q08Rhu6+HU4ztUCUNlGQU0hePkefjPdCVL8GWdnJycnJycnJyc/iP9AkqjZLUIGk/OAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
@@ -30664,8 +30880,16 @@
           <t>Public record</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>https://tpusa.com</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAJ1BMVEVHcEzFFDnFFDnFFDnFFDnFFDnFFDnFFDnFFDnFFDnFFDnFFDnFFDmyQEUVAAAADHRSTlMALPRO0xgJvG/lpYypaZTyAAAEdUlEQVR4nO1ay7aDIAwUEBDo/3/v5WElAbwVWuLGLHuqE5LJJIDL8thjjz322GOPPfbYY49NMcVudoBpcbMD68vJmx14aaHudeC1bvcFITrw4vY2LiYHXvw2Lu4OeBduSsPhwF1pyA54Lt6RBujAizv6ICAH7pCEwgEvCcQelA6Qp6FyIEgCZRBqB3waKNtTy4GXIZSEpgMEkiAZE5tzVrfxgy7OSoOSAVprc4J8mJ0QhAiuV8M/gac0/Lg9KQ9u9UXwaOaXksCE6wKP9jNJkCPoKQi/SAPb7Bh6DMLXksC2dRg92lfDmhLuY7l9DsKwMkthz+E5N6u27p9/5L/aIS7K09UnaCGYVOpEigsbkATJ2vDcaLsF6P1/1xzwktDpgadeC31F4B0OdPJACt1gvrEbBl+CPM5IQSv6XG8CoavYD629UqOdgtiIvrECLkExD+170jWB6JwSma1esG75Db4hbrZLmtau5StRTbk6w6vYkjrAu6VYltkH8APovc1IsYJSAN5Hvhu9tx2rsvhWx/bnvSoOtCRzPH/JZMF+fjBfjvXjzuJXRfqP7MmB2AfrbMPS4ccP8rKWKH623rGcafT4e4+ralW4Zr0bE4zP95FeMfeP0nMTunJzHujemmH89zTdbkk7eGjKoTE2N6ed3V9h/PfjJwOBdzBNBLvvP9ieF/jp8UoUDnSHJoIfHFBg/D39ZwOJR8fL+/6IRmH85H6pyXtst1rZCgf6x08F6+w9OAlclMm0aFGrOKbrnz2h/uyTo9oaA9HZZhs6MLATVBsINU/pk64K/z/E/u6oVgmwVuN2/EbuzyN7ODB0GgDHH77jV/T7f5f/1XE9KsCU/5r+be4VDowdRcBk782rwv/45m+ubCDZE4Eq/M8TrXdgcO+JCyjiV/m/cNDF1tHdN1TA1L1L/l96Mxs+jdtAoqMAqALfXFJ1NXr4ACpwX+mG42/mHrZK0AISAQXW38mHvVDuE1QxFM6+BgRwfAs/SFvgz71zgBJkEwERAfo2tAMGGLg2CDCZfyjeKQHFVDwbHzbh2ALwBJB8mmkgALECignIzb7zUuJYb5oBcAL09BsvEIDYg3AFEFxAgwBEtUcVYKYTYFnKACAJIrhyZCAAAZ8hAsy/cAQLjnSTkIHTFcAbMygAqAnz6RW4wDlkrQKwEtz4AsAUAFACnOLbg1xzJiwXdWECBsK5z2F/fAAovoHJo3gkPJqD52vwAlcc4dDmniIAOeVJhGANaooPP3LfixUH2+D8KSBYzkAcRCAFKUoANN5Y8nArxB0BPqBA7Pqs2h3OtjwMVxmY9skJtEz6JLowAyQUzDlPKgQzQPLhUUaMlGcgAzTfXjFMgeqAYLoJTAHQCGkykJccKaBAHyCpATANJh0GZ3QUoxjiYFQBQAGar2Fl5mBYMOAgEQUO4Uu6DzhIMorAIihliIYCRRGAYYhGh4H0x5SDTkTEwQULcd4jpwGdwI6Y60KIiYpgQVWogAMk05i3I+mB9Iq+CpdcdQt2wNJU4R9eFKUY5RCKeAAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
           <t>GROYPER FILTER REQUIRED: vet individual TPUSA-affiliated figures one at a time (per the Dustin Tropp pipeline-filtering model) rather than treating affiliation alone as an ally signal.</t>
@@ -30712,8 +30936,16 @@
           <t>Variety, Status News, public record</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>https://cbsnews.com</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAZlBMVEUhISH///8AAAAeHh4XFxcbGxsUFBQZGRkRERELCwujo6Pc3NwHBwfh4eGampr09PRDQ0O2trYzMzPV1dUsLCzp6elYWFjMzMysrKyOjo5MTEx+fn5mZmZzc3M7Oztubm6GhobDw8O39aNqAAAG2klEQVR4nO1bWbezKgylICpOaB1ah2r9/3/yqlXL6FR7vnXX6n44D8dKQgjJDkQAfvjhhx9++D8CYcMmkINnGxj9kXQDgrB6BtHNp5cB1I0jp2xCAM2v62ARaFdRPIlmQf04ehBIrC+KN60sj2XRLNw8M+3vSMcENq1i5pIlbg/o4fPlkzpP16WPcGpyrnREoLNdfAffgd6JDmmAHbOfrZCYJ4lHsLjtFt8hzuAprmAkwRHxPe71CUaAtXtU/uWShvBD8Qjmx8X3cOBHvvix/E4D8IEjWGAl7m2BCw4HZytpP5d/udyuB13RuO7f/GoUhzQwrod2vwr+EQ2s0+bf47rbDzA4bf49bsnOvYDIB+FHBdfYFw+gc678PiKdLz9Nfd91fT+lG3jKLg3McG209v4sm6wIw+s1DIusKvP7bU2L7ZkJ1wsbIHWjBvQ03DYsjDFC3R+rY+kehKCM3AUt0nqrI8K7dpA4yJKJfHfFgU16TCUBMuG1CvTR+75xEcxMM4AfJB3rfkm3PCvsDB90yJ9VATxj+DfqeHuoZW/VJr6MEvUc4kc9pVbLg8WdKQ5oGkcVHHUAGIalWoU42bIXPRUBonExlz0IZo5qqYNqomDYhpUyjgTeBgNAxYt+hYz5eXLXeBqNZhsBM3morLAhHNlyCEgf76IPLzNEZ069yDYCWdFotV7AoaT4vXgbjoCVEM2wwG6ppB+nxdpW9EQD+BVDruFzPeYF781mwVz8/epWFD0grpmtA5+r4jvkjAwv8/mHdEUBuxQHY0y2EKC0szSBYNJ82QtMjgXQJ6vvdobM2gAJiS1ezAhWxa4Zrdlt6wnGWQKX+WDIDZotkSPCTtIv2MhpJVty7gTuVdKwry6uAWRcJoYG8wTtq9DSkN1uNqu8u+CGCDHz55Mn3Fmh8tvNzhgNkD4amo/3FPjSGq9SFBEZaz/OBg+9G8Jo+hGtTM2TrWj51Mv4QaRdA5TM6xzynmJUezxQOVFYTQ9ioFsDXEx5QCSQyhS9AnGicxjzQ10+MCYzSUZSpehVCM6G7HZ80OicwB5DPRVtZOhI2iKeAgHDV82Dt6FfQZNK1G2/C/a4icOQcZMFulA0ymkN4f/o2DmFexUMiaxXptFuAzjIodKpzts5d4FW0kzs4UGsVcBXG+jIJuxRSmv92k3aYAx7ObF872Bv4iEy5LTzijRaUjJstofsouTgUZkjk/DXUEsK+IqH5OBRqYr/wXRFAXndjivQqiaT/2MFBtK5pMDt20vgryigqmDt85zQHoLhogKKZCly9a1QbcM+1qVaBVL1a4cDkZT1XhRdr8DARxShOPSXJalBK5GAj6FYHwlfySiSiDv+o2SkTcfexpqMRyv6IGleDxTO+cLkbFRMB/s5cQ+R+OBkfJDrCIk5aqigZEe8UBgE4XbSTEzTs4paUnokFGlJqf6QgmE+IW8lK9ttApGOMLR8oTBp59cz4fXdbigYgClMHP1pIRPyhNIMJUopC+DJv8mUZhJTY8SA9wAxX5ySneE44AxgsKzSXjiq48tzVgO07wbFrVkpJuHG1cvnvT2u2ZCI9mxFWrNmJlwu0UaBwVQNO4wP2N/azXYNSjbW8Uc06eIRjVCC0AdrLm9zgcYfUvFs4qZ3wcFa/K9pyabGrcdkLBOyxJeeK4e1Yh3csn0QcFM8Ys/2zFBIpGsHlXLEiTPGCN66H7Bnixg2YlGnzYTzO3Id6FzfvmjCld3ogreJvUKKn2m2em9E5FLcr94ndggsRqRgviFFJlTcGOjPh2YgQzHuLbPngYkdaIplek/m5TJQpeJx2uMhBspLS9omzJVNobiKuFBn9pZu9kWs8pZNl5e6S6u2ScgoABNYO+yllR/fQ+iNEQZ59UM9hMQS1TAr5dsX6j4xJCNdw54VZuVzuLYrq9Aau8f6a7sk15FoVd2nXAR98m/zDMDx5glb5nBxadsGniyfZAsXlxs8cLTw4tVt7DSkv7o1+atbCCFoInfpTe35oLwItX6YAfTmdIZ/X143ZX5vV965hDv6OKSrK6UW8/X9pjOsbzQQ7MFmB3gBGYfKQT3SLSGIBT6viafHgUae89qYehxpJDq1kelQo+1pNqDHWrn+fTNb3853QjuTm3zQa43tw/2kExzjo85WtPe+UJL/WUsn6JtaP3DFtP60qRX0m+FwWD6lrXdoxTh0ShZX5zQ2dzDxAU8ITmvtBj3Ng86u7JRGpza39yD1dlegTkFOFg96Ggqb1Za9Xvqt/MoHDj1MI8tXYqObZ8aXPvEY0LFu8vh3H7kM6Mg3CJvy/ZkPpe4tCsomRH/wmc+og/yhE/m7D51++OGHH344Gf8BQCJiNQ08PekAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
@@ -30756,8 +30988,16 @@
           <t>Public record</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>https://foxnews.com</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAkFBMVEUAM2b////CABcAMGQWKlm2Bh4ALmMAKWAALGL7/P0AJ2HCztr3+funuMlheZh+k6zk6u82VHykssPR2uMDPW+NorgsTXiAmbG6x9SGmK9EYYZziKLv8/YAIl3Z4uq0wM5OcJOarsJxjaobSHZqgZ03XYUZQXBMaIsAGFhacZEcT3xXeZsoV4Jff55Da5EAHVuxjhAfAAANt0lEQVR4nO1bCXPqOBI2q11JvrBBtjHGB8YHQyC8///vVrdkY5LMCzuvtipdUzMBbOlTq4+vWxrHeRTYkZUtcQ/Nj/hSTn5clRFeGONbgot6MoWfGQAgaabzr/IEvBxAH9szBCk0U6BjMJ0/Hl6uAAfuJ5PUZzMF8OYKOKGXzw+crftMx+juTufPwcs3wAFdPjGyg1kjwDMFxMXrN4Da4MQJ6jdjgnMLcHevXz8FsLZt0E0rBCEETNUPCsgt/3iRAABRZHu6exqGYZN145g4+DqNAbZ5vmRqCJ0kK86NbWhBHMd1TWo/D9vUn5hgsHdetgMAQ2fcXA7pNif1ZJ/b67rvoyhtw9yfhIfVqnnVBkAMxqJPG58Q4odpa88TdB7iggHophYQ9x56AQKIYLZO6bpJvo3WRed4FxuA7+kn8WUaocs8XXfw2xi6PiQxydv+nCUQM3OP7C04aQAgaScW4O9Cijp87zD6liXEZR0ezplDTRDIeWw1D3qB8DxRQHmEdN9aUtbbY4K+4Q3hNXMwNAEVZHYcbHQYBk462YAUM7cB47Gt3Xr39uu31VDNNhFOcnGPl79fESheA6hK7mEZ5NcRvCYtwLUVbOpCowMTBQRHY5wAobeIlH5UOPAFEEBkzbMd1YgwmySIdobaS/o8Juk5wd+HEFqGdtDDVbvJBjywEICSy7Ym2wv4nk84YPStefQOgMS2gPKw9CZOzi2ptwX8VmTANysMmR1Ava2AsFtcJcBOkdZ1mn1HCehqL9QowLYAcn62RgCdcxuTQ/L7PM3ea6KjkNdbQbDcf7BABiEP/KH6XSX8MmHI3apsC0dbAU3y8SZjfK2DdPw9fwCOMYG4V4rEBys2xOfP9AtQl5b++hOcy4LfjK6JSvewszwj2H0h7kPv7Mft5jdCo2WD7lbFNaEAN2Di+uOXFkaVUPv9+LcBVCbgllepakFE3HDP5as0EDrrMB3+NgBslE3UUiGv1Nyj51VMPEQ5Ev+HcaWJkimhZdxJ5nUwZglSIp8DaP7NDPZoAl4qlwpGHpzdY3JIH8XEZIA85+1+fT8OI/Y4dlhEOylRJ755i7QsBjN012wouMsdgIKJuffMX7lzWZ0qOb0Hj1tSBq4blHF+6ir6NhyIemO1+8UV3OoX88UdQJF2Ah9OFCAAPMpOAMDJaZIty/BGXQAZ93VvFJFVV5Rvi7aEwvnIlInFHwFo2WOARr/5D/Guo1nJfJ1TC7GKzrRamt8K+e5NIWxXHwEIK6akQ/34ixsWEBVGBScETMlF3hadGQ86Dio6jov4QwB5RS03jRd+Wbl5AT3j1mQz6OUFh+UQhQwdiySAqlXDLQPwadaJzPxl3hhluPkGGbcKwlZbeLOczx2kWyOldC84KkjucRFA7cG1mTI+ZOPZTmdj1Ru/0quL18vzA0eXpYqOezo7B8UigBjbNL5NILQLqKDHSfjwjts+6WtZ7bkTlArQg+XORgPIr0cld3AyIweMwUAbERnR+cFAnlb1WNc+sSSDSNtQ+eYZAFvHUwHVyywHCA54BoAFqv1s/ueNRXRQYENBBuFNj55W0AKQACF0j96toRcAEGy9J/XXPWV0qTQYRcdNv45yAxuASbOVXbI/bsFqdUPgMNmEeP2M0IBRDSbpONwomyh76FgASJu2XKLRmTQTHjWwovGnC+2yevu0rYL1DHIHwF45DuPhE1XKjEI2N3uyJQ2EnmVbTAG3p4RC+4+k42bGmvHwh71kqsiOnwHwMWUGqWk57Lxn8ztQhWoiuo9Q5bIgZVpbBmDb4OIWEFqxYhMDV+1TAMBJ5VaFPE6YgUS3/EsAHjVAKFOxK/uyeGqDqgdVHrgCwEHClvR8GcDwGQAfwWkwfMpqoerQCjquO8aqPlkG0E16igtb0FZw1v1/1t6Fsjvmbjmd142KWuWlJQAbZDOBJQ28V5sZWSHPGtyyO1a+M40DpTf3JB+3AJSxlGbzq/1YA0EHotkZT2CK7okJqO4Y4ZES3eVr+rTAApCvpZxH72jtwQKAphqmB1Cr2RmUAZBJG2y5yamTkUAbrR2KHYS5QBo+rencwzxeuFdkq0gtYKnHCzdiN4MjmxHfpAsYt50mI/0e7q2+Zjgi6Nnd/twxrNAQkiBa0AC+iIEIH9yTuInB+gSAou1iwe2bc7VUHp//0goKWnMUZToPlgYkseB0HA8CbfBuDPYJgJl3uLbFBZGVrUk3mswZLmQksWZOxwHYKpWCTwFQ3T2YmVpzYjobwcmzjmLK6zwiq+4Yp+NY0qj6aHnsUwAArxcRlG1nsfKGLssx7W4yb1/AjdAd2wF1bhekT1Q9BUBLnnMz83WGPhq9wiyZhTN4M0h3s5QgOxP8OXVs5m9slM8BUB1kezI9UCzDCy0YDRMR3oQO2g7nJ66yO5bTTVfp23Tp5gDCB1oNQbH3TRlWb/sRAmBqUyLWQom/hjg7c65EE4DRcZmV3Gam6PGkmgLXxJkLgM7mErWN7+dh+l6MgE14PKlmwFE+hodUtQxO0+oI8zAUU+oDJBV9PJVWPacn2QxA4CTjmCRA9kjEQRwXK24Azagd+1aASKvM7eDAVe1GiwX0JwK+fmgAu7Y1SkCc2wUR+0JkRf91Z4LPEETE1IiiBmR0HGYh8X3/adL+ltAtYSlMVh2dbwIdztUOgL6l25gkyDzJfhcC7DaXaXdh8Ydq6iz0xQSngsnmfFlfio6bqIOpCtQ7CYsYJd0B0PmtlxVCBlUBJWdRimawWD9IkZzlH+Lh7MI/ydpi4B8GtvrsEPqkjmuSpwNbG1OBWuAQrARX8t6DFKa1FHkwQVFxAlQfvDZ+kHQMxR+hKPoO4hNP69S9+YcTtc2DCRRlvadcgqqglqDRyZXxxfPdFG9n8QO/Ca7gRt5Ctb9VqYvbjWZWItYKzliusZNOonXQUieEXS1VwGkLK5vRnWYAbK5wpGLzPgZQSdYXr7F17tjwYqLjLlVv/trNX2PMy9sFQsUOc31ywwD6UwAuV+QnADxZ+wXsJEOfL/JWr0wxzXh/eC+gbBd2sXAIdlDE+D+7ojEBIMLBZwBUZ4UlKaguOvHrJTIf7x2VR9xApyNWcKFU7ADrYJY9Akm+mgHg13Q+BLDaIkdmPUY2FbPil1+AaH6X/SCnDZp92sgcHfe0bn0TTsCiP6XjiFEW6gU2gPoGFwDEjZEDVN01XkW3SsUtVzH/vjipsnP0UNKz0WKyPQOZVwBfwRbDhHXJyn4CYNVSD34A4HeJEaFBvlJo0XSab2XzOx8lqoB1RyDY09n7wcR6TscoHce8OAuT6UWm+IrhWzwDkCcQmLymAe6oE+hajdygJ5rfrXJUN3XYVYyMBi87Q/LLazUlaWzi+IbmN6k6tABgwgpVU3o7Wg3/+IIgf7w0plPm7zfgITw95eaX11JPdFJOaH6Vi76/AEA06jwxEJKtBT+rTvZ7ovldX6rUOHbpp3enmjBCRsHcG0qYnvLq4S4ZtaEHAIEK1jEvZZGsEOPiLx1FqX/K5jeFNbuBFYd3K9vzQpggfkUjHpABUMbiv247zAEY4ZdMpLWv3PeK+Z0rpvPHnhsnO+mcl/Zlmpm7EYxt7qoklXfDNACiLvTU0fM4wAGwCMpl57ApY58jIANnt8GeBpzjA29vNOdm3bGy8BgVzbMJgLui1aT8GIA+7gt5y8bf8efjnnNgniLQ6aFlrM/gWTfMH+FOtdENgEE3mt1PAKgDT8LvX4R3/l7ZEjEMZIOu8/ldTEn7eXcswtR/A9FGNwAKVSQrGE8BYJH1qPLZv1th/W7NFZHzKgyATTSrnxrJWbqG0vFfFLoviLgNoJscBhkAtWL3qSi0AZRWwt4sJzhZSBaadrJjmlsYVD+S2mAzerWuhCwAeNIMX46EYvTKmrK+/NoZRy55lw9A5FU0CibDe6O2ghsH747RgU+M2TwAgE41Kf4NgHmfybPOLchQWZ0j1hwGIMmKU9vTPyiO3kqH3Abd+uwQxkecBw2YZtVcAzMAVgim+lSxmwljFMddyC4J+hs2hW6K1xfsCA7XJL0b6OsKEw2Y9DoDgFXVJdVmrIUyGwhMHb6lsV3FzzZjdYFqiou7KNQGg6jzrabJFAC0rrhaRrg30ovXdN3LuKWnI7JLF6ZvYARNdFlH6l5mzgMB2JC6OATxzVzammrAMdf7LDcMjIgqGmjWyWzLmETJTMCchpV1rPY0EIwXH8vmLbfb+BMbYF6iKcYyJRP2ANf6eIfGWKyb2DXTLD65j+/JVhk8lYe+zK0W9lwD5sznQwC6J+/TwAMTfdjCc8XC6aH2+ja+N+XFKkXnAKBur30EQHf73S17y1NKl5Eyeeh076TRjX7zHqd2VT8H4OgDhw8BqAuPJT921mfO8p4AZRuTVFBe1VWnDYnCfDMlWHapxb6A8sznIwA0nsh0wGsZxYxioG6igPc8DvjK3CAOB21zRxL5/aQXAJzI5xKqjA0325zLGu38fCp+nkpuXYTsN19kWTz4/FOqhwY4Oe7DnH7d7AtoZtw17bzrxjo9TEwrCjiSgINkQfRrk4/yk723mJY+dFiA7WteYRs+NEMAtPMM/0Z9IX9SqQjaj/HPmu/K3+dDP3znt4f/RTPm6+Kniwco/5ykz49S/xnxXv6/KPzIj/y/yb//sDj/+cPi/OsPyw+AHwA/AH4A/AD4AfAD4I8D+C8KmDr7ETMVUgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J40" s="6" t="inlineStr"/>
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
@@ -30800,8 +31040,16 @@
           <t>Andy-identified partner institution; public record</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>https://reaganfoundation.org</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAX8UlEQVRogbWaeZBeV3mnn7t899u33je1epXU2peWN9mSZeMFvAEBxoQKCQM1U4QCJpVJZpiqBJkZSIaaqrCkSAKZBAoYEttx2Gxsg2zJlmRbi7VYS0utbnW3eu/+vv727y5nmT9aMGMwUGEmp+pW3X9u1fM7931/5z3nPQb/D0M//l7ryHIoJXTQWCzVt2BYw9IwtmusfqV0SyBlUkqJkrocCH8p8L0x33NP16u1k5aqnZe+WO4Pbi6974kn5G/KYPwmH41+6eNh0VjaXKrIu1Y88/ZQqn1nNN3RGs22hSKJJiLJBkLhOHbIAUCKAN+tUi3nKOfnWFm8HuTmxhcWp6+8XivOHtG+eiHTaJz/xJevev+qAjQYY4//fr8fiP80X1L3hruGW7uHbgtnmjtxInHsUAgDg4WKS9qxODI+z3BXI7lSlf6OZiquh2NZGFri1aus5Oa5fPZl7+zLTyzU81PPG6b6/J98fXz0/7sArbVRPfRYa65U+GBVOH9cjQ02Dux+iGS2GdM0mS7VOfLGVXqbkgx1t/H7/3iUzzwwzBeefoU1bU28Z2s3vR3NfOXZ41yeXuBj99/CUrHMhs5m0okY1UqREy8+yaVjT+Ur+dk/D1Tlm5/++4kFw0D/Ojbr18MfMMWrh/ctlYLP1+MbPpwceiDZt/1uYokUh8aX8BQ8ee46bek4gZBU6x5+qcToSo39fc2cm5ynMRVnbXOGf3j1Im1Rm6Z0gs89+SK1apX2hhSXZ3Ps2rWHvs17ooYV3lcp5LYd/JY9ve/d+alDh361iF8pQL94wJa50IfmCuovZced29Zsv9/2Iw0cPH+NtkycM+NzfOfsFOszDi9eXcB2a3j1Ovs39xAKPNrTCe7fsY6GeAQlJGcvjvHoHds5Pj6HWy7TmEqQr9Y5fOINstEIPWvX0rN+l9XQPtA3O3nxPjmtinuzhXOHJlD/YgH65IFY3TQ/NlOw/kz3PNTYOrjbKAmDb58Y45prsr4hSlCvEfJX4/0D27vZPdDOzv4OEmGLjoYY8YgF0idkSmxTs3drP+lUAlmt0p5NUKl7PH/yIoNNSfq72/nb7x+mIRZhw9AWo2fz3uT89Nh+19Du3t322UOnysFbcb5lDugXD9h1x/jkYtDwqdjg2xud7BqeuTzP0ekiH9nRyVePjLCtwWF7dzPr2huJhzQrS5Ncvj7L5HKOlZUlSsUVarUqQkps2yYajZFKNbKmpYX1XZ10rBkgXxGcvTyBkoJwJMLTxy/w6N4dCA2b+teg3SKHv/vl3MTZH3/O7774pQMHED/Pav8CvD5gylf5vfmi9enE5rcnm9r7KNU8zs4WKOdX+NyLZd7Tn+GOdZ00JcMsTZzh8RNnGMtXqFYrTPgxJmliRTXhSo2SAkfUSAQFmvyrtOoTREJh1jRledeem7lr+E4qbsCx05eoForUhOLY6xfJxKN0tjWy950fb6xXVw7MjNRLBw5c+7sDB94cTsab4bXhHnls31JFflv1v6ejuWcjy3VBQ9RmZqnIZw9f4T/saGNobSt+LceJ4wf5weVlCsriuOzhqrMGoQHfxQpclAwg8DClhwwESB8rqNPsLdAvJokQsK+viXc99Nt0dQ+yXKjw2f/5FI/sG+apQye4fVMfj9yzB1Ev8s9/9cm5/OzIB/70G2OH/m93elMO/NGdtbaVuvX5oOPO7c0Dw8bRiSUOXlng1bky961r5aaWGIOdDUxNnOO5Vw7zT5OaV8wBDoe2sRhqIkuVeFDBki4PJ6+TqwoaLJe74gtMVgzShkdY+SyJKDM6S11azC7luXruZQxRZ2jdEBv7ujn+xhV2buglX6mTjEXobG+nsX0gvjB1qfVH3xYHD50pVN5SwCcfvf2j1djgR7q23mcX6gFfPT7B9u4mEsKlvzlFazbBtUsv8P3XL/JkrpkX7C0s2o1YKEJBlQ9lrtKrFrhQjdGrc0zULEzp0ywKXKs7vL9lkW6jwJVKCFsJKoFNTsQo1SULY2eoL49z6y37aMykeOX1C5gGzC8XKBbLbNq82fDc2trlyQv5n5xaPPYLAorP/9FgSUS+Hh28P6HizSSjYTZnw3zxpRH2rkmzoS3J+PkX+Jtjo7zodvGytQHfDLHGKvOFtuO8PGdzthjhYsWhJEwu1SPUAigHmtFaGCkVYznJeNWhxfb4g7VznF22qAUGRRHGF5r569fwl65w22372LlliCOnLnBpZJzmhhQ9a9ppbFtrXR85sXP3WvHUoXMr+Z8J0M98PJwL9GdzkaE9PZv38cML1/nh6DIhy+Dm1ih3buxmYuw03ztxnkNeF0fMQTKO4p7YDONFzVRBMuVHKEgbV2oQAcgApA+BD1KAELhK4wYa/IDliqLoGQynqyxVFPkgjFaK8uIEjnJZv34LueUCG/o66e5s4cLoFIP9vYQiidjUxZdim9qzzx+/mpcmwJQnNs/kxb09O9+OGQpx7/oOdjc6vDYyxaY1bbjlRY6eOckzpRaOWYNo06JR5LmDUfDqvFxtoiwtCLwbwD6Inz6r8MhgVZgIKATweiFCCMHWeJG04WMqwbSbYKSc5PmDz3F15DT37NtNLBrm+uwizx46jpSawW130dqz496OFr0ZwNKPv9daVLHf9hp3PrR20x77qTem+dxLV5mqBNw32MKWzgzHj36fJyc1B+2trIu5fLBhnJPlJD9caqAkrRuQ7g1wcQM8uPEegAogEBhSYAqBJQVIScXXnFt2CFuSB9oL5CuKJc/B8KtUZ85x2x330N7exlPPH2WgqxUtFR3trdjhSGTy0rGJf9+/7zXr375zXybnm59Ys+tdmyKpZhpsiJWX2NQQYXd/B+7CRb7+yiWOGv1M2y14SvNQcoq7ozPM1CzyHoifAsvgzTMvxSq8CDBvwBty9UEKwggG4zV+qyuP6wnOLDsEUoPSiMoyzTFJz7pt+G7A7u1DzCws05BNkUln7IXJ8/XpwvEfmVXqTcRbdiYb21nKFzl++Rr1eIbGVIzGuMUzx09R1DYjZhcoRbku+B8TnYyWbd6TneH22CIx6f5i2MjgZ2FjCIEhBKb8qQBJjIDtsSJ7G4qMLBk8MxUjCDSGlORcB18Z/OSlY9RLeTpam/jqt3/Ad556jitXJ4jG0zR2DuwMZxKNZqEabA4nW1udcJyTixX+7mKO8+PTDHY0U1yaYjxf5ZjXRWBYENTpMkv81eBFsobLhRWTBmrcFsvRQA3jRsIaMiCBT4vtkiQgJFfhkQJTCbKmy9ZoiSQ+V3MGLVHB7w7kSFoeWki0VIyXEywvL3PtylmymST7bt7Kf/zoB6hVa1ihMNnmta2WndhiKm0NO8mWkGWHsL06v7O+gX+zo5fmdJzR6zO4tQqXQ90QuOC7TFc0XxxrRipFNTDIUGeqrHl34zKD4QqIgHWxOp9at8yfrlvi05ty3JwuY6oApGAg5nJbushi3SBq+LhK4wWS565FKbsGhlJoJch5Nn7gc+XqKG3NWQzT4CcvHefshVGEVKSaOkNOND5sSqwddryRguvz+JkJ/vHCHEY0hlaC68vLjFcdAsME34XARwUBUTOg16khfZ9aPSAmatyaqbAzXgYRUK4GXFrSbM163NteZWemjiUFppJsTLlsTHs4KqAWgBSK5qiPpSXcgFdKoqVkuR5idnoS4dewgL23bOP977kPyzaJZ1pwHGeHDUZ/OJZheqnAH9y9FVMrqnUXEfgUC8tc1Y3geyA8ED5aery2bNOvQrSZVfI1TYMlsWXAtaIFIiAfaKIOxG2JVpKIaYCUIBSzZRiKKKIECKHJhgJGli2mShZSrsIbajWMlms25fwCnlujq6OFV0+c46Vjp3nfu+8hGctgh8J9plRGs+3E6MgmefrsOD84M05DMk4QBFTKBfIyvOrvwgfhYQifFtMlrl0KNUHC8AmrgJW65lLRxpCCrSmPh9pLXFiQHL1uECUgxmpiX12BmoCQqQjbkoqniVqKqBWglVwNIalAKaqegVuvEgQBIcdhYnqBVCqOEwoRcmLYltNiBkIkLTtEwRMseYqiL6lLjVSSeq1GTeifzT7CR4uAuifoj/l0hAXFukS7Lit1SW/Ex5aCiHB5YsTEUyauMjizaBHDw1KSzojPSk1joKm5mmxY0BwJ8IVC3wgdlMJQCiU1Sip838OyTFLJOPFYlMmpeQzTIhRykraQAgyDS9dmSNSKlOs+KcdCKYUIbni5vCFABnRaNa6XNZ8808ijLcuEkAgheG1G82hHgVqryW3tPi2RAFMFCCHY0aCZLsGRCUHUkByfAa0k0ZCi5Js8Ox4jEIqUIfANjdIKX2iwNIZpoNFopQh8n/n5JRoyadBgWRa2UqosRZBtTidobMzSaoCBgWkaWLaFI2oQBFgqoMup8eHOPH87YlFQBrOuxZqwIq4lcyXJy9ehP+UzlQ9YNCU1T+MHmrCpqLiKQlUyUjEJGYJERGAhWagoLA1pRxAzAlyhcRX42sA2FFEnjOOEiYRjPPT2fQz29wAg/DomumwLESwKr5bdPbCR3QOdPyut3WoRJxwjJYrMWo0YyudjgytYXp07G+A7U1EOzocYCIXY3mDQl6xQDjQBJj+4atKXkCxWDSquQXfCYHLFxNYBDRFF3BZMrijmSgb5ukU2tPqnfaHRShNIQGtSYYjHE4RCDql0mnQyhWGs7sFE4GKaasn2fW+sXl1Zb1kWc2WPw+MLPLS+DTvkkExlafMvMmJ3oYTPqUVolwGua9DleEyVNJdqNnNFifAjOIZif6ePEAqtNVJppFQorRBKU3FhJGfiCwukQV0ooobEMiVCaWxDApqsI/E8k66MQ7qhFceJoDS8eOIC3S1ZBnu7COpFQpYxZrqee6aysoBSipChyRgCA41lO3Q0NdNqlLC8GqYMsGRANiS5rdHl0fYSzYaHKQUlX1OTUPQ0F5c0nlCrXn7DDrWU1F3JZAHKnqYeaOpi1W3ChkRIiaUlWim0UpTqBkpCf4tDa1sXthMFDUnHwjYNtNaI6go2xmnTq1dOlnLXAyECGmIO92xaSyAVvlQMdncRdsK01WeQgeDogkkiYjJe0LTEFEOxGgkjuFEmSNKWoFTyKXr8DF7dgFqoKjQQNiXcsMsQEktJTK1ASWwtMbXECzTtaYt4JEz/wACGYVN3PXZvH6KnuwOtFUF1KUCLk7YpvTfy85MLXr3aVTTCPH+twPcuzfLhjQ3cunY9HQ0Z1hUnmRcpFnxFEEhao5pTM4qNWclA1OWNFZOCCw90uyyUJKfmNDNFMLQEKZlaUWgJw20+YUNydNIgbksaQwGTKwZl1yBqQSUwKNZNtIY96xOkMhla1qznzPnLnLtwhc1DA/T1dJJJOMjq0kKY4Lzpu0EuN3vl9VJ+Hi+QzM3N80CLSblaw44keHjvHsIqoNVfxJSCZycNlBSEEEzkFWNFg5ghGUrWeW1KcnFJUalLRhYVsyXNbEkzmoOKr7i8qLm0AH2pAEtJ5stgI0k4q+GzUjWRUtPTFCYdC3HT7h1EUs2cH7nK9ZlFnn7uJVzXRXg1RHXxdTMUXrZ+t3dfULCnOkOp9r1Dm4ft3qYk3zq/wOTiCj2ZKBsGNrAw+hozi8ssiATTFYORPLRHBBHpUfSgNy15esxgprw669uzHnFLMlVY9fPetKQlphjPa2ZKEPgKW0sMLYnYCkNJqj7UfQjbBns2pLllqIXh+z7I+NQSK/ki73pwPwO9XbS3NRMUJz3/+ivfuDlTP2Q9cfGivn844y0vzj+44aYH0mO5Kg2m4O4tPUwsl+hraaCzrZOxsy9RrAasyDAVTzG6oqkGmpaQR8IxyFcEVU/zcJ9Pc1iQdBSODmiLK1pjkmw4IBMSTOQMkBrHEAgBEXs1/qeLFgaaHX0p7t/Vxs69D5JtH+C1U+c4dPQUc/NL7Ng2RDqZoDb67KxRW/zztg/8rxkL4B23ZvJepbweJ71zw9B2cmWXw6NzzBUqJCxYt3YNlvKZv3oaL1CURRgtFaW65HrJoOgqVCCpuJIrixptaHrSAsdURC1FKix5ddLg9IyJEhrHVBgoqh7MFU3yVQPQ7OpL8Y7d7WzevoN1u+5mMVekVCzx7gf3k0jE6GhvxSxfQ82/8oSTjXz9y98+Li2AHx3Py/3bWy5Vi/Mf6Nt0R2xwTRczuRK5QpnebBzbthlatx5Zmmbq2iiGVhQDG1NKlJJU6pKqt5qwUirqnmQ8pxjuWrXQH41ArqxxfY3WqyFT9zV+AEIqMFbh9wxluWl7P0O3PoIrTP7iK99i66ZBypUqu3duIWIJ9NSP83i5Dw088pXFN50LHTy9tLJvUxSsyL6edTutXL7Ito4GvHqNk+OzDHa1s237LZilKQrz4whfUBUWSHVjF7ZaBislqfqSsqtYLitGFlYdyQ9WaxytFVIolNAopQiHDHb2Jnn7cCs3bx9gaO+jeNrhO08+w007NnLw8HHSqQTrB9bC8hu+Ux79zJqHv/CDtzyZu2dzbKxcLmzNtPb1b9qwyahUq4DB1w6fY7AxTiqRYPOWnaQccJdGwKuAVni+ccPv5Y2SeHUNyFc1lbpe3ahodaPKlBhSY6Lpb4tyx8Ys9w+3sXn7Lob2PIIgwpFjp7g2MUM8HuXR37qfLRvXYfs5FSu8/uOIXvmvn/vGsbc+Wnz+dKH6wuPmzMzEyP39W/YlM5kstmXxvdfOs2NtG08cPcuWni42btzKxnXrUStX8UuLtEdquAKq/v9ZwFAKQ64uYmgNNxYrS2u6GkI8fFMjG7ti3L6lnR13PMjAjv2UXc3Tzx1mcSnH7zz6IOfOX2Hjhn7iYZN47sW5mFz8w8jtn73w2GOP8ZYCHnsM7ng4PyVmKSzMjO3v23hLOBJNsLGjkePjc2xf28bhs1fYtq6HTGMbwzfvo681SbGYozlUoT9ZIxWSOIYmxGqyxmxNIqzpSpvsWhvh/u1pdvZn6Ght5G133cG2/e8n3drLlbHr/PXfP8m2jf0s5QrYlsU7H7ybeBhi+SPllJj9lHmT+q5h7H9Ty+ktGxwHDmBHZrZ8Yu2Wu//LHY98rFFaCV44eYFCtU7NC2jLJhjq6cAwDHo7W5BuhZmJEUZHR5mfm6JaWMKtVvADH8swiEUjxGIJEukmGlva6evrJ9vehxPPslKscObcCIbWTM3MU627vONtt5NKJWjORIkUTuVS7uifmeX6F439B36hwfFLu5QH/l1HLKwaPtrev+vTb3v/nySdeIb55RWOvn6RC5Pz3HfLFq5cm6Zc93jbLdsY7O7ENDTCrxP4dYIgQCqJRmOZFrZtY9sRLDuMwmR6doFiqUy1WuNr3/wubc0NfOwj7+PMuRHuvvNWQpYktvxSOSVmDpi4f20MH6i9Fecv7ZEdOlUO7kgtnqgGpYWp8dPDzR2D8Y6ubqO1KcvSSpEtg2t5+pWz3L51HV/7px+TjoW5MjGDUJpoPIlhhwlHEiRSGdwAai7MzOUQSvP5v/wGWir+4Z+fJ2RbPHjPHlKJOAN93WzdNEgoyKv4wsH5tLj+n42q+Btjz4Ff2gD/lV3KQxOove8qnBGz6tTC1Eib79XXtnX2WVvWD+C6PrWqS09HK3MLy1Rcj2wyxlPPHcWvu7x8/A2iTohMOsGT3zvI9559ibFrU9y5Z5gXXz7JbTdtpbujGaUUN+3cTG/PGlIxE3PlvB9dOfVjJ1j8Q/tW47tG74FfeQ3h1/aJDx1C/+RUfvLFbwYHl2Yu52auntoViSaja3qG2DTYi2Pb9HQ0YaEZn5ylqSFJV1sTI+NT9Pd0Eo/FeO3UecbGp9i8oZ+bd20hCDxMw2R4x0a2bVlPJOIQqk0SWjiUi1Sv/jc7cD8T23vgws8n7FuNf/Fdic//3tCgFbX+uLV3171DN7+ztalzfTgST2NaIWqehxN2eOP8KOGIQ3NDA+lUkiOvnWF6Zp53vG0P2Wz6htX66KCGqM57xvLZBbs+9bztq//e/MhfjBn8+g79bywA4EsfHwj7wt4ci6Tuamxfd3u2fWBnqnlNayLbHoqmWghFU9ihCIax2gRVSiADD+VVkO4Kqp4PdD23YLi5161g6UjEki9UTX1+8B1f/te97PHz4/H3vtdabhpJmaFYUzST2hyLJIZtx9lhW1a/HYo0O3Y4aVk2piHLtsWibZrjlqlPW4Y8mXCCN0KBk+sOLZeM9/3m123+N7TJLjdmrnI8AAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
           <t>Process public leadership/scholar roster and add named people per the ally-org rule.</t>
@@ -30848,8 +31096,16 @@
           <t>Cited in existing criteria; public record</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>https://tikvahfund.org</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAV1BMVEVHcEwxZJGLqsMtYo8gXpBdg6cmXYwhWIUqYI6+0+BzlrM4Z5EkYJNVfJ9mjKxAb5dFcpo+bZdPeqBLdZskWIczY403a5kaWZEZXpMaW4sVW5kYVYoTYJ6k1AjmAAAAF3RSTlMArwvA9yTe/tAEEofqMRxoWng+S+2fliSPH9IAABC/SURBVHicvVvnYjI5DGSrtxe2uL7/c96MvPlySSgJgejHHV+AtawyGsnmdDqd6qGANCdKypdDfN3I6/TL6zsijyj+94ji/4+ov7w+ncasgmQL/l23fFklPR+0yeutwOsikddtc3/94vgaP9ofX+PfF1mlGvnktxXjN5rMe6196KbTaSgtXmpTQYNeeWcgCTYwKXwmGNXeXb/elLXOuRxPGDKltXa6gzJLaZUJIWR42rwarGjNFk2QJh5v4DtVcUozfhmyp6em9HwVVijWr4afMOVwT4F+VQYLuWo41bPSzkGBrD41CXTBwwIWxUe8tdaY9vDBsmKfUNVjf6My/KDuzqfTTv3xTtJgX5qfcGG8Z4CW6+OzeFZR4QtaKYUvTblxDs/rFrhWeQ0FbNm/fWtWxnGtfMK71uA9bbLmVGRay5/xgL5zcTN3TNBXHgpYC2ueWvoCCmADRWmpgFJtDbvQ/tbmy79vpZmjgbXOilNfBkMduOqYc32rYMJ0h5tgpHW5sfqJX2HY+HyG1UuY2RmLr9StFbtYOOZccoNWh71+/1pfaTG83fkIy2dYxGGa8K/QAKueOyqg/VZfX51bMSIwQD1jfT4Knl5K+auDLmliRXTywZZTJ/Gi8YlmoxexLJQ5r/AiLMIo2Pk+nFjcUuAsBjBqZgRwfaupSxLVoi6jseLk9wAQQexoOsFCr760MLcxWKredXw58dmOIelvhuHuZSFqOee0tMmhyxLz2SCA+gqPgwr558c0CRWAtVtGrKxqtxTbCBSLkDwl8CGfcgOMitKJ/5gCJVPNGhhvyA61znCA0eLg/YsnlxLJi3dWfsoFfogBNzoq4BmxU0cF3K0wRAgi7kKJHB6NpJrhM7AmHo0MkL3hyb664MhR006W/j4zE6z12GxaAVWM9oDDJrGyva/Kv5tRKWQe43uo+CwYQMyCBDYWKVbI02SXXwUhDz2dlvxzor6SVCSuSfpNuedeLmkf5dxZKBAIYmOOJa2iLVrP6GXaE6Xo0PwyoguGGO2YfxkVUBZR0zCCHdIPJqgsHQi4uiKzbFonwICMn7QKiN6X2vFhyN9ljQokV9CMcAkQtfgo9kLxM19CAWdkW0oem1zxAc2OROkWMYCzwZaoLpsPVAB2Q9WjD8OnDHyXejPMRIJBujOHYhJvokDYJbUBjHa94oOFiG40IqfOgNo6WKTguXRUQLxptaTAfM2CdVFRAWsQLkPGpbTfWQaoQcCy8CHVUpefkO6SbPTQwmDRAcB7SgRhGcQCt5DtBq2ZVom+CAaigCzrGZ0WWdSXin+8XJH6StyGN9NYOxnOZ8ttS9hvWqC0uuYAscEudYrLAjKAoyirXJahZcUdCiXVdxehYPSSu7MgONFeQtgL9OIpQGkooNTVEBYZKsk/xnxfMiU0E2lGeqM+yqMVXGr2S8pnxHgNylJvTAZvJ5qUiRV9CoKF4ny7mBHuuA0poXNw9B9RZYUCXhGXMkVkrC64sVjlm7ugMF/iQyRbUICqjLn3oCc3HUBJ21iM6cmKxdh3YgK4RqyHKCF9u+CDkQbwgjxSbxiMkxdQBxzCnh75eB1D/snA8gNQZtqAugCCYAJgFBVAKIMlkbx8heMm46qetadiVWOkNhmLOdMaZZKEzt1zgOwkFwUqiSBhAGe6gyaQV6yaF+CYeAXomyIImWiAjuZiHJ87AYa7DqAgh0hHvHyNfF0hIodSghMbL1b68ks5r9tIo2LNgjdAv4eMCEZ2JMUeeXnfAZQe1StSFmQlUvGoKDriKZDFg7B89oGUDAEQmsIbiZcceSx5CVOQ0Sbf6GsoI1AHYQ/ILwhexidCsZmVpDcdq/JnPF9W/FF41kbgYSyklfWEVanp2L+7WgM+S5OEoMCaJPzJcVd8szUIYlfRsIpk75MPUGgBVuRQyEHjaYAFYasU25rJssblV2vAF1k6RyQRNkWSz/pYVOifjF+oFAvVx5KIPVolPp5ZBggZjAUogB6RNAQOvFaEL0g9M/z9KtsQeGMUkNVYgUhFqvEhD8iGpUbQPhBBDFGgl1pitLrIgq7JUIoGLKzYGsKHLFMAnqG5efspoqXx0Ay3GAtVQ2JJjrsxfFDMNF/9QCas5r2NMYcU6hAFO9s827LuAxjV/0N6QA+gHXm85CCTdCG1Zndz2tkg3SByF0WaWSnocCVzWKgFFSgboWb6Q2cBLcEZmDYrkyXSGGBQLOFkyl+A456c2ZsHQ0q2cmTA1n33pPrLW2n43yNbZiZblpkdvRC5lQqQku2Kb34XAv73TAVA1AcHiCzonLPKkTGWBJjk32fritgnrI/WkmVJz6PdSA1+FIFRipLPUpEDHEQHxN0SglgkUPj+baogMtDcy0oKsUvxiy3qaVOAI329l7guKLwkoIMwQaBBnDIczRuBWf2ryTMcb/M+DhdMJ7CF1oY+6ckk9A8jMAoKCNFIrMh+JqsJS1gXyTl03nLYED+ZJkcdKtgOcabUsM+zEjd8iB4fMABdzuipiCSoPhGZmdCxvEOT6oA22Btctj3aIQKEdJS02bKSiWffGu99FXgafI4YxGJmdm7RBa92OiP2DyIjGxoiVEb9aKCMnAExAp8gBbvvVeELJiAt1dznBl7niMc7p04V4V0r7WKLh1ViqUUDAQW4b5ITSYHOP5SCh5BkwIISBViPeNznQYwMfAc6xFFBUSLlDhAAeRgIh87KlGZjsJY/T8E3KWgCDpaAQWjK+CJjeKMiLSRLnYDhAt5BrAYnQWQyB1dOtmYOBD2Q4zs88JrMbyboOyBzJHxBussGNNVYAUPAoCUMAwTe+nEwGmoLGqW/UJcfifS7LmOvAThmgyeljcDeYnMya00rj7olf4ECwoqReESLvsyhdfsLA3DSZOJ6C8KeJR3OR4olLIleqDNrhfUohKk0VZEKGs99t0q5+53IHRNk3E1Vc7wnc06OTAM75YYkUSiQ4sZRIDSYpBABH5vBpuRI9KdV8LNMbDfUWeYzynMCnekQ9CSMmeMwwq8Xn8jw6yStrHTDE3vb7vs87LKkFSsR5zMZ+nLPMES7RLiVZE8aEj5fMSqBfbGNszKFIxrpHxDRazLmByfkfEMIOpiCKYtI1MseegQHfTjKtdK+sjKd47TxsSr0QWphmYzpodOeg1owDG3AV9GEGzDDGetHFDKRN60MTjbGbKPnX6XAuwmEA++oqy4WGMOOdQE4mo3T6TwOoIhGCA17zPfjqcXvBWmtlAx+sDcteY7/ky12HIkxEiomB0ci6ZtjyBGcjGyfICMbHDw73bBwd44YxNltwum1i6Ph2VjmhnAW9rU8LTHlryOAUhdMBMkrnuZEbijlf3ZxCM4ZaBJpOeqmCes5nnWY34Hguwbgp4IsA2lixoyEAhkDXzQg88Fb3iT8COfpxC2Ol34Hgu/CYas0FujOQi4YC17UywAELuD8AEgtaDSpSM/PpAaPMNGLgsh2jk5H/AdiK/omlsa61SiNhhSkBUYIYUFqSgiCxurHecBn6cF+bEKeir4jYYeOyrRFMAxkwegH4iClAjXBxlMWxOxp6wP/UfyJ6rNyLk5OQI4HmQUE8iI46eBiwa1yvGPsj5uxWzKuYERTjAYpzlqoBwofLCAc1WmZYrh4ZNrG0dDzBDTEmo34apyYuvNyHjpTgYmud76qJSrJVFGHjHkGCv+Tmn0Ag2tEzHFUnXllNxYo6wxiLTsaMnKFRSYsYpAnSt8pcSqnFOxQRjTKZcrW35nxNKxAoeOEC5SE1EBfO9V4UNLMymk7J9LmIPx5UYP8cOsoS4ITm5OIAHXWt48XH5CZoznmAbqvRA7FrJmIew4lqI0UhZyEVavPzROIwCcB0ZICBN5BReqdx//8B5uyBAApZgliiBH49DQUfBOQUmMlwIMoMgJzs9HynK0b0TFKCCjHgwY4Jtw5lnhEZMUGKR6siacopssM09BkAH72IWjEuHBROv0UJvJR+tXI6GEJcrjaCBOKZ+L838a4iGfryxrMb9qxK0IMYiI2XRwJk4XzNETOx7QRquYtKjGPR/2daw4PyYiSyBO3JEg/MsWTlZzEQ2sW6dl73kIBWzDdow35LelRCenaOQgH42kiG4MKrbHhURXn+BwboV6Y5P7jfi48DY2JGDlPRtOrmVdtDC92NKVM9SQJn41CUQHADYk/ElEarh3u9+vCoaU0QD3HJCnPC+T4/AWyrI5jgHoPWgvthAJlwTGUcOURMQk9GnCSh2cyt4VMex3kQCUO7wKoKXpDtMDHcJhoxMH97xvCi5LuOjC/UHQ5qpA7EltNinz8Uw6rZx/y13jgVE9WjuBAO+Ta2aa5V1AFfZwX81SQU9zqNR4QMJTB2O54k6Xexel166X2jqvoAT/5nx1N/EBACgy594T4nzkUY9GT0829RnnkuSYP6L55OviItFavo4zhwL15xmsYhMiCJG3QxQsZkondq2TKNeeATWV81vRlcKC+9L3OBjJ05ijQ6tZNp18KL0pVKUcTuuNoxJn1PLImlP2CBnaWKYZ7Ukt6SRo05LzBQvSb0P/y0pFURQKilKizsy/gIu/SOmdlVIEgaHlNRO8JLZCPSbyHOjv7nKHAFVlASeNdTZ8lXN9lpVwN2ivNoXiaoId88HDgW4Ig8JyVJGjPOT02OsidRcOhLOcipbXPGctcEawc4gBIKSv3TQ9xTnOGuKApfQUZepdWC/OfjKUCq9zsyjuObiIpsuH2jctfC+9G0tQ5FVjbjgfa6867r05mg/rh86FvSrG6wGArqUA5gX0hHFEG2BrJLaQnTeauSopKyDxLqEDVsyv2yZln7U5ub3z3msjjskdi2HpezJVC5NsBnMTLaZ163mTsmnD+N8erbnqTy5J2SrODlYGg3rt5/WuBlY+LURaKTLwCej6hNrAZ42jqBS3RRynACarjXGjiXWPOY1s0rjxPWu3dy++/Fh6QdL0cF4Ma81wP1RcV0cvNCvsqOvgu9eyt4YzSEnmGSiYTk5we1TMy83Vc4E0m7zk3xmJ6kSvDtICJvwzwPnt1CPAg2wOKwEgZhLxvjrZwNzzmZ418MQxR0sr7quDZnN1BT0GK+pT0tOUB89NHU5ck8SBiaE29zdKZP2BY2JOgPQVEPHBV5Ocye6NGmZJVAy/y2hGtkglJ2upXTGa+yqS0bQteDurOCS3QkichGxOtX8qG3qTvvM7Oq+HhWEYFEs4ObcWJ+R/EIGsuuj+5rpu3Ja+vZjtZQbmsN669P1P4K5W1lQFZJlc1Sp7U2W62l3828HzhzbmMXNSJFjqX/+X400sZ+buMx3jQvjFSzR+z8Bbfi+nYm5zjfIy/kJOfThht5MareS0jfxdJQQMu7Hmax+3rTi662r/AQdRDmdKabs+9c/nO0ySf8TjhD2rxocEmvdDMm3P5yCucfk8YBS9uCd5FLlEDCnjVc6mowLzxTunLZkOfZRIM4BU2V/Y8w/FLq59/THRdznnAanJzvBrYnvueP6a6+LOHl8gAZmy2lOe4WcOC2DW8O/TUo9KbklZyf6CVg+SZv72q2RZf/uXJK6ROLLuTEQpsxEWdcXj/+ReEr5Td8IYUOmU0hDw23sEU5VchfyUz+oDp1FsqADYCawyl/CzzrwS7BuoNq3Mz73GgRWoqueTxV7J0HIempYMj+jKgXeb1/hcN6S8J2BdLf+XcxG6A95cSr/4sCZCHc9Wi9I9VMvD13sjrvwsB/sK/+fTfunhw/f8AH3yjQIr8NbsAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
           <t>Process fellows/faculty/board rosters -- a high-yield source of young Jewish/Zionist intellectual allies.</t>
@@ -30896,8 +31152,16 @@
           <t>Cited in existing criteria; public record</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>https://hertogfoundation.org</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAIVBMVEVHcEwAhmkAhmkAhmkAhmkAhmkAhmkAhmkAhmkAhmkAhmmq+l7RAAAACnRSTlMAXvPaHTTmSgueJtSzVwAAAdtJREFUeJztm9uOgzAMRElMEof//+DlVtTdLWOX0KJWM299sDkxNpXA03UURV2uEo6q9EsGbUgxRtd4VJIWgF4Op6jaqQxHlTeAwylkBKgyKcenLj3HbBVYUzyTIS4pxgqs0lSquCCkhqR630Xd/Es1heqCiFJL+p1hO4kdXBNoaE3VPoSEfn8iLIIc8Eh1GowiRCkoPmGCaF3fJhBUwakGMLo+unN/VWEK8wioBLh6N8GpzE38db977gFgCjM8oGjPHcBnsJsINEG08ScpOkMbgB09K4Bngd1FCUT7ABQARGMIR/X7Y3xCBbLdxmCITgAQAhCAAAQgAAEIQAACEIAABCAAAQhAgM8GMF8Uryqvq0By6WUVOEEEIMCnA8TsEnjb3PgcqMUl8OXs45+EPoDv/TMiAAEIQAACEIAABCAAAQhAAAIQgAAEIMCbAK5e6QRLrScAOJZa0XJ5+1atY60Xbla7AOBmdRNAfMtq9+XL7cieYJkTFiGbRhQrGrWAb71escHBaALT4mESwBkYrComTD+9sbcILJPLIGU3RR8cn2ugzadz2HyiPEyhvdfolP8bnZYMk9FJBkeOOHultrirrV4NZjc5yex2od1vnuvjbsXbRLQZHimKulo/O/IBNqZksywAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
           <t>Process fellowship alumni/board rosters.</t>
@@ -30992,8 +31256,16 @@
           <t>israelallies.org</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>https://israelallies.org</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAilBMVEVHcEwWMUgXMUgVMEdOtOFu0vVdweodi8gtboxFpNBSuOIVMEYWMUcWMUgWMUhtz/IWMUgXisgYi8olj8wkj8xt0vRu0vRt0vQfjctt0fRu0PMabZ4WiMYXMUdszvAQhsVSntP9//84lc0qkMpt0PJco9VEmtDq9PqbyeZlrtrR5vR8u+C32O0XUHSf3ajjAAAAHHRSTlMAue8lI+U3/gQKFBNG2HBYlVDjl7+kzrlzdYz+JyNBcgAADR1JREFUeJztW4l2ozoSjW1AAi943xoHwmaInf//vVFpLQlsk550z5lzut55bhabuqrlVkkob2//5J/8/wkNIy5hSP+67tCL49N5tzuA7HbnUxxE4d9RTaMgPu32vl8yeZfCjvz94XwKvD+NIgqY8nejGQkA8g/n+A9ioMHp4PeoVupL+PT3uzj6I+q9eOd3hw4XfH+/58Gw3wvX7E/Bj5shig9+VzuM9xTHQeBJCYJYRMgu+FH13mn/XrpDB4f3RR2NvCA+737QCmF8cNRDuJ2Cp65mIJ5/YbgEZ8f45fv+HEQvySf8GWaITq56H8L8r3Gfd/ad0X9XPZ1Of189jff28P1Db5LTkAvtBTaZLSa/iSE82fpL/+S5qiNvtTpupBxXK68bHNPFcjn7HQgd9+8C6+GURfpmu16TvCqSLE/YP2S93p7jlZOc4WQ5H30fgne2h78/4ceG3mqzrZjmJCFVngKApM7YGcORbTc2BjpdzC/fhRDtbOY5YGIJAzb0rMpBYZLV8MGOScYvkLqqCcNgQZjNL+Pl7Dvj31nj988o+KLVdp0UWUZSMeJEAkgKbpEkhXvJenv0kMsmy/FlvJj85vj9k9ZPQ1DP1IrhgwM0gFQ4AYyQMSgMgoFNp8vLZTyaDUvhyPa/H2tzhqsNU59wBVykTml9CIdE2AUurLEjpswGl/liSCREJ2v8+1jf8Y5r4WUi9RfySADQp3DEr6w3xg/TBUNwGU1eGyHG9Ff6sf7FasufDy6Wts7qFAMQEakQ8FvblW0Dlg4v1NPA0m/GH/HhM6WZUpLkCooCIONQHAowxESCQDB+4QbvgAPAjN/j3gevEw1A6TUHtTQJsgHZaAKFSHwVCOHZpj9PlFXqCfNb+rUBDIAC3S5UqmxVg0QnI0AwXj5BENsE5EPbxUhotXV1auaxADAT6PvGISYQGCM994LtAB4F0IHEQn+KfGyN1gDAJkhkuqTpWjeJPBUYgge5EJ77mn7WBwjFaMzw+Fz7G123v6ICdq1twAPxcln0N0zBg86/LFtAkCH74ohHWlPsJMhTeVnHgQiDy7iXFMNdrwGEIwr72WZ09rAJ9pJBmW5lLtCZMMG8jw/iR1MfkDa3Hk0ydIbtjsMQolaZZiP5gPJcBE7s6I8eGkAgsJ5cIANYAIhlJxM266NUIzLhcukm41MDsEi0AGSGcmwAaWYD1XZTgUhFJvSkwnMDvJe3KtNStegka9oM38qwmC+qMJBx2AmDRylgJMu1sIbISPV5r80Za4nQPXNa15tQmuDS5wR6em4AJlWqhZG+lqT5uLboNMtTdJaYryonKBPYTog6JOi6oGxRHSqQ0z8/Pu6FCYkch4dFjtoE455MeB6CHMF70fPQhDQfTG4p0phYYhJzvRJDnsyVExCAfha2RZFvipI9ra4A4NMQs0URCW6Ukq0gg6nkgsvcmMDbv9avAVjce2famRNuxiY2F8G31e9UFEg6RJWZvs4BBACNMb1dP6439vFZaRPkjg/yTN1KtyIKpqOOCV7nAAKAQqBgg2+ympmhMc2QRYZQH/S5KszKB+OF1P+4DmFR4861jckN3F/nNcOhTeAGAfaYTATlg8tc+iDaDwCg0jDVrR9PwVvKWoMGp6JxujKJPpR0qKiA1eWhNMjSsOqMiNx5/DOFzATXm6apXHCQ8YEyiSIjnQeKDuPX+lkIwJAbJvd7I+TOUvCT/cMOmSk+b1KaBj576zU5UouLZBgO4OF3ToQw0oHSIAAmaFJJBaooyzAcFINi8tten+u98v+YOTLkA5QXMg90EAgfvCwETFr5BOb2a3NTDrgbl3yKG+CCK87KxCLDxA0C7gPEg+WDcGxljAP1yuLX8AhkkhfwCRnR8BvAS1ZFwp3ixq7JIg8wgNO5q122xRxAAnoZmrQGDky4agjPFKoS6E1zyIgEC0GJKZjAAOAVKTArUmUQnbtrwy0qvzXP/bSA1Lem5zmYgHAguDyDoEmjZIKZARBiAKUfwAqhA0EuyEgENx5iLXcFApDCDXYJymNr68dpIKNQcyEnQwzAg7no2RevIfirmTa3n1bBSKEK3qVdpAXA9h93Xh5rF4DhQklFuifgUYhcsBcWWtVte3u/vbdtViXO02qogHeUaYpneI7CjZtTkDEZdwDALAlZ4CCIYrVOSFEUhHQaHIioRlCNumKm53dxw+0IMBGQo0ME0BoiADsOgK6A9oDP0x4ABedD3QSlKsZT0R595rkDIMUVWpCxAXBZ2gBEvTzqH+ROdQcAQAHXmym/Rh/Ypklr9zeFrtCEdAFMGQ/oGBAAaFxpaStH2AWwQJPpC+Yr4IM7vtB9SAfAaIqJSFtACbMAloIUWX7jrJ8l8lpWq7stv9HW9m/Yr7JCH/YBiA7vtgt4DCjrgeES9cEXyj5lELpZIIPwLn1ifkWexQCbHphqKIMQsgADsCQDzr0ZHjJZwDtU9n/zJAvkNNmkIQCgZycNqQaQui2mbIQh3O65tVDJSbqBG9fKoY4iS9NfIGqCRh0AsQagiEhbgHSyQKjOPnUiKACiGola4YD+9fXFlX19/Vo5VMxnaKYn9AUADwGwe1xeBGCEN025EkAGRQC+4LQj5NfXBcl8CQvGphhxACYNfFErplv9exsAnwo1QFKFKH66CYUIvMM5tKqNMVv662LLGBaMFwgAq0ahbolKsTocbvQDaqsW8VrYFjDj53EIRxWsHBQ8NIqcETgqlEy+Lh0ZL6YOADM3lQAMFabWTItXvOunkA9zyISzsD68qx/06IcF46U54V2h6svL8ixappXWmVc4CpuBTbE0Qcf+ygZjBIDipkwVAxSFlbUaccUCmrqHXESOPtBv+4NajbnIQxrpKLTSIGc8395a+GQfN7B1ld1Y0wBtgLjIv8AOiocOcACIVVO9QuKLIKCmHqJVYd6DplmhJmE3TjrsC6ZXhi65VlOzAQZQ08NAJ+LpzaGiPHNbIoaI9wq8D72zc3IXjWjKMZrJ6wADqJWicKeDQFQDT/ugqBwuRD1uy4tfDolnYOrETQfov4zkynmgyTiQPtAKM6crxQ0P+J73B2YqZIJmkAfUSpVZIpBMECAf2ABQfeLE3DTWVMjcHuIBvUiiw7DcvTlkaK/B23kBpel6taZCGi8ZAsAsE2kqkOUAhWHt+AD5RE7Y8VRI98TDYtAs2OpXpifqhKHbmOK2G1IRUz9+szOEBdB6rapI5cFzTGBeCwvBTQqvgqj44ZsDAOA1c6oKguKiEJnAsoBFjiwOrfKPlgUHZMEIL5nrdyaSCrQJUtYUYBOkFjmS5mZmbykmztcATA7wIUs6LKUJWCIUUrKswFJbpxU+y6tcH7/2wdx+dRTKxSrFhiwOe1+ROKfWifXG5JUJxss3W9RikTKBnh+kThRYa5H220o0NSevAHTf3snuVCdCuNHTEYsLrAJl3bJbyBcIOq/OKJV8WMqa+OYpPiyGvTe0LVVkT6Og7/WlmqPs1cvWQOVibT36wZvTpMLWYGZ7aoJl3wtcb2fHoc5FYj0b12gEoOi8332CoPf9rX6H7ysnaAS2E/rfnltrI9wdzrQEycO3+AEvzKWqSW+hSgXr9TFyNlqLxg2s2tqUfo17AfS8PlYIhA0Oet+BskH9cgcFioxCXV4fZ8t5F8P4yYYaYQPNyGayjPbQIBOY9we4UVALN+tV+BZOZsvRyAIx7o1AxwZn/Z1gS6ynWiZAu2i6+rfiZSGVW5kGOIB/Xexn880uPk8wEqnMmmdnHxGLALNwJW+aXTyLOdb/IAOMiGz0zUauqdrJZN5YZe4CBdpkJQ7XG+3FmaXfroK9EsZ87c5sZaMBNwIxe7mUCfReMr0WJ1ASvXXkjS4c/QO2/dIYAgHZ4G0idrNleu1aWkMtUKgtK3If1/qoze/o79k+0St8X6+Pd3NGmzVB+/nkmAUAHRJqN5/ZSjex42+ofr6xuyz9s9lOSynfVJarwYpU5AAUU5OaoSLrDdoFOlk6+gfvrQQjMErY4Q29oXfckkIGgkhF/iFTEHqnZHvEm1BnI0v9iwTsCGwv35tQZEag09VmC5tXlRMAgLAFG/56u1nh/ddTx/3j74xfDJlBsPa1AgpvddywoRK+YYylI+ydIySvNkdnY/HMMf9w/2N1wemwi93ECb0A9lVvpcDe6s6fHEyc4Q/cVtojXnyOvT7yhj848rwogr83cu7T6WzkDH8+cGNtjx4aBd/8o4Vpx/qwo/Rv/W0AnSyc2P8vzG/JdMDGXEb8C9f4MPwf+asL9uzFZPoEBPP8YjR3tV9GPzJ8Lsy4o8Vs0jccOoXGo6udWX+I4YYK+Hc+Hy0Xs9lkMpUymcxmC6a8r/2bL347+B8gAAhie+p8JGTeq5l/ZTR8W/13hCVZj6m7g1/OftL4SCh94/5+NHBYj2ZemvzRxGeueOD3MQ+R3kD9cRAhj74lhAGX0WjJw/NZqv4RIFSmQ/8fHP0tEP873f/kn/x38h/MrD8go0GiLQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
           <t>TO-DO / MANUAL INVESTIGATION: systematically process IAF 'Top 50 Christian Allies' lists for 2024, 2023, 2022, 2021, and the original/undated edition (2025 done). Dedup against existing entries; add net-new allies. See criteria 'Bulk-source manual-investigation queue.'</t>
@@ -31044,8 +31316,16 @@
           <t>israelallies.org, public record</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>https://israelallies.org</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAilBMVEVHcEwWMUgXMUgVMEdOtOFu0vVdweodi8gtboxFpNBSuOIVMEYWMUcWMUgWMUhtz/IWMUgXisgYi8olj8wkj8xt0vRu0vRt0vQfjctt0fRu0PMabZ4WiMYXMUdszvAQhsVSntP9//84lc0qkMpt0PJco9VEmtDq9PqbyeZlrtrR5vR8u+C32O0XUHSf3ajjAAAAHHRSTlMAue8lI+U3/gQKFBNG2HBYlVDjl7+kzrlzdYz+JyNBcgAADR1JREFUeJztW4l2ozoSjW1AAi943xoHwmaInf//vVFpLQlsk550z5lzut55bhabuqrlVkkob2//5J/8/wkNIy5hSP+67tCL49N5tzuA7HbnUxxE4d9RTaMgPu32vl8yeZfCjvz94XwKvD+NIgqY8nejGQkA8g/n+A9ioMHp4PeoVupL+PT3uzj6I+q9eOd3hw4XfH+/58Gw3wvX7E/Bj5shig9+VzuM9xTHQeBJCYJYRMgu+FH13mn/XrpDB4f3RR2NvCA+737QCmF8cNRDuJ2Cp65mIJ5/YbgEZ8f45fv+HEQvySf8GWaITq56H8L8r3Gfd/ad0X9XPZ1Of189jff28P1Db5LTkAvtBTaZLSa/iSE82fpL/+S5qiNvtTpupBxXK68bHNPFcjn7HQgd9+8C6+GURfpmu16TvCqSLE/YP2S93p7jlZOc4WQ5H30fgne2h78/4ceG3mqzrZjmJCFVngKApM7YGcORbTc2BjpdzC/fhRDtbOY5YGIJAzb0rMpBYZLV8MGOScYvkLqqCcNgQZjNL+Pl7Dvj31nj988o+KLVdp0UWUZSMeJEAkgKbpEkhXvJenv0kMsmy/FlvJj85vj9k9ZPQ1DP1IrhgwM0gFQ4AYyQMSgMgoFNp8vLZTyaDUvhyPa/H2tzhqsNU59wBVykTml9CIdE2AUurLEjpswGl/liSCREJ2v8+1jf8Y5r4WUi9RfySADQp3DEr6w3xg/TBUNwGU1eGyHG9Ff6sf7FasufDy6Wts7qFAMQEakQ8FvblW0Dlg4v1NPA0m/GH/HhM6WZUpLkCooCIONQHAowxESCQDB+4QbvgAPAjN/j3gevEw1A6TUHtTQJsgHZaAKFSHwVCOHZpj9PlFXqCfNb+rUBDIAC3S5UqmxVg0QnI0AwXj5BENsE5EPbxUhotXV1auaxADAT6PvGISYQGCM994LtAB4F0IHEQn+KfGyN1gDAJkhkuqTpWjeJPBUYgge5EJ77mn7WBwjFaMzw+Fz7G123v6ICdq1twAPxcln0N0zBg86/LFtAkCH74ohHWlPsJMhTeVnHgQiDy7iXFMNdrwGEIwr72WZ09rAJ9pJBmW5lLtCZMMG8jw/iR1MfkDa3Hk0ydIbtjsMQolaZZiP5gPJcBE7s6I8eGkAgsJ5cIANYAIhlJxM266NUIzLhcukm41MDsEi0AGSGcmwAaWYD1XZTgUhFJvSkwnMDvJe3KtNStegka9oM38qwmC+qMJBx2AmDRylgJMu1sIbISPV5r80Za4nQPXNa15tQmuDS5wR6em4AJlWqhZG+lqT5uLboNMtTdJaYryonKBPYTog6JOi6oGxRHSqQ0z8/Pu6FCYkch4dFjtoE455MeB6CHMF70fPQhDQfTG4p0phYYhJzvRJDnsyVExCAfha2RZFvipI9ra4A4NMQs0URCW6Ukq0gg6nkgsvcmMDbv9avAVjce2famRNuxiY2F8G31e9UFEg6RJWZvs4BBACNMb1dP6439vFZaRPkjg/yTN1KtyIKpqOOCV7nAAKAQqBgg2+ympmhMc2QRYZQH/S5KszKB+OF1P+4DmFR4861jckN3F/nNcOhTeAGAfaYTATlg8tc+iDaDwCg0jDVrR9PwVvKWoMGp6JxujKJPpR0qKiA1eWhNMjSsOqMiNx5/DOFzATXm6apXHCQ8YEyiSIjnQeKDuPX+lkIwJAbJvd7I+TOUvCT/cMOmSk+b1KaBj576zU5UouLZBgO4OF3ToQw0oHSIAAmaFJJBaooyzAcFINi8tten+u98v+YOTLkA5QXMg90EAgfvCwETFr5BOb2a3NTDrgbl3yKG+CCK87KxCLDxA0C7gPEg+WDcGxljAP1yuLX8AhkkhfwCRnR8BvAS1ZFwp3ixq7JIg8wgNO5q122xRxAAnoZmrQGDky4agjPFKoS6E1zyIgEC0GJKZjAAOAVKTArUmUQnbtrwy0qvzXP/bSA1Lem5zmYgHAguDyDoEmjZIKZARBiAKUfwAqhA0EuyEgENx5iLXcFApDCDXYJymNr68dpIKNQcyEnQwzAg7no2RevIfirmTa3n1bBSKEK3qVdpAXA9h93Xh5rF4DhQklFuifgUYhcsBcWWtVte3u/vbdtViXO02qogHeUaYpneI7CjZtTkDEZdwDALAlZ4CCIYrVOSFEUhHQaHIioRlCNumKm53dxw+0IMBGQo0ME0BoiADsOgK6A9oDP0x4ABedD3QSlKsZT0R595rkDIMUVWpCxAXBZ2gBEvTzqH+ROdQcAQAHXmym/Rh/Ypklr9zeFrtCEdAFMGQ/oGBAAaFxpaStH2AWwQJPpC+Yr4IM7vtB9SAfAaIqJSFtACbMAloIUWX7jrJ8l8lpWq7stv9HW9m/Yr7JCH/YBiA7vtgt4DCjrgeES9cEXyj5lELpZIIPwLn1ifkWexQCbHphqKIMQsgADsCQDzr0ZHjJZwDtU9n/zJAvkNNmkIQCgZycNqQaQui2mbIQh3O65tVDJSbqBG9fKoY4iS9NfIGqCRh0AsQagiEhbgHSyQKjOPnUiKACiGola4YD+9fXFlX19/Vo5VMxnaKYn9AUADwGwe1xeBGCEN025EkAGRQC+4LQj5NfXBcl8CQvGphhxACYNfFErplv9exsAnwo1QFKFKH66CYUIvMM5tKqNMVv662LLGBaMFwgAq0ahbolKsTocbvQDaqsW8VrYFjDj53EIRxWsHBQ8NIqcETgqlEy+Lh0ZL6YOADM3lQAMFabWTItXvOunkA9zyISzsD68qx/06IcF46U54V2h6svL8ixappXWmVc4CpuBTbE0Qcf+ygZjBIDipkwVAxSFlbUaccUCmrqHXESOPtBv+4NajbnIQxrpKLTSIGc8395a+GQfN7B1ld1Y0wBtgLjIv8AOiocOcACIVVO9QuKLIKCmHqJVYd6DplmhJmE3TjrsC6ZXhi65VlOzAQZQ08NAJ+LpzaGiPHNbIoaI9wq8D72zc3IXjWjKMZrJ6wADqJWicKeDQFQDT/ugqBwuRD1uy4tfDolnYOrETQfov4zkynmgyTiQPtAKM6crxQ0P+J73B2YqZIJmkAfUSpVZIpBMECAf2ABQfeLE3DTWVMjcHuIBvUiiw7DcvTlkaK/B23kBpel6taZCGi8ZAsAsE2kqkOUAhWHt+AD5RE7Y8VRI98TDYtAs2OpXpifqhKHbmOK2G1IRUz9+szOEBdB6rapI5cFzTGBeCwvBTQqvgqj44ZsDAOA1c6oKguKiEJnAsoBFjiwOrfKPlgUHZMEIL5nrdyaSCrQJUtYUYBOkFjmS5mZmbykmztcATA7wIUs6LKUJWCIUUrKswFJbpxU+y6tcH7/2wdx+dRTKxSrFhiwOe1+ROKfWifXG5JUJxss3W9RikTKBnh+kThRYa5H220o0NSevAHTf3snuVCdCuNHTEYsLrAJl3bJbyBcIOq/OKJV8WMqa+OYpPiyGvTe0LVVkT6Og7/WlmqPs1cvWQOVibT36wZvTpMLWYGZ7aoJl3wtcb2fHoc5FYj0b12gEoOi8332CoPf9rX6H7ysnaAS2E/rfnltrI9wdzrQEycO3+AEvzKWqSW+hSgXr9TFyNlqLxg2s2tqUfo17AfS8PlYIhA0Oet+BskH9cgcFioxCXV4fZ8t5F8P4yYYaYQPNyGayjPbQIBOY9we4UVALN+tV+BZOZsvRyAIx7o1AxwZn/Z1gS6ynWiZAu2i6+rfiZSGVW5kGOIB/Xexn880uPk8wEqnMmmdnHxGLALNwJW+aXTyLOdb/IAOMiGz0zUauqdrJZN5YZe4CBdpkJQ7XG+3FmaXfroK9EsZ87c5sZaMBNwIxe7mUCfReMr0WJ1ASvXXkjS4c/QO2/dIYAgHZ4G0idrNleu1aWkMtUKgtK3If1/qoze/o79k+0St8X6+Pd3NGmzVB+/nkmAUAHRJqN5/ZSjex42+ofr6xuyz9s9lOSynfVJarwYpU5AAUU5OaoSLrDdoFOlk6+gfvrQQjMErY4Q29oXfckkIGgkhF/iFTEHqnZHvEm1BnI0v9iwTsCGwv35tQZEag09VmC5tXlRMAgLAFG/56u1nh/ddTx/3j74xfDJlBsPa1AgpvddywoRK+YYylI+ydIySvNkdnY/HMMf9w/2N1wemwi93ECb0A9lVvpcDe6s6fHEyc4Q/cVtojXnyOvT7yhj848rwogr83cu7T6WzkDH8+cGNtjx4aBd/8o4Vpx/qwo/Rv/W0AnSyc2P8vzG/JdMDGXEb8C9f4MPwf+asL9uzFZPoEBPP8YjR3tV9GPzJ8Lsy4o8Vs0jccOoXGo6udWX+I4YYK+Hc+Hy0Xs9lkMpUymcxmC6a8r/2bL347+B8gAAhie+p8JGTeq5l/ZTR8W/13hCVZj6m7g1/OftL4SCh94/5+NHBYj2ZemvzRxGeueOD3MQ+R3kD9cRAhj74lhAGX0WjJw/NZqv4RIFSmQ/8fHP0tEP873f/kn/x38h/MrD8go0GiLQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr">
         <is>
@@ -31092,8 +31372,16 @@
           <t>IAF Top 50 2025; public record</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>https://newsmax.com</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAEHklEQVRogc2Y7YsVVRzHP3fv7rauoqYsLJE2oihiMmpMLJhgYfiioDFUUHCPIhQlK+VTf0NZSZEkFuhAUUHFoTcW+UaF9cVZX/gAvbAXlgh3U0M0apXdvb44M8vsdR7Ombl27wcuO/fO+Z5zv/s7Z+73nAohnh/sAo6Hb+vk0wHcBF5XUpw3aJ+J5wfPAr8CfcBkzri3gA1KiisdsRudsVeXwasK9AN7PT/oLWsg/GJRv3njdoXt6UjqyZLXgE1N6GcSs8pPoxkGZgAHPD9YWLKfOi0yALAK2OP5QZn+WlaBiF3AuhL6llYA9NPjkOcHcwrqW24A4GVge0Fty6cQ6MfbO54fLCugbYsKACwF3vX8oMtS1zYGALYBGy01bWVgNnpB91lo2mINxFkL7LZo31YViPp+2/ODNYbt62SHuNRBHicL0DFjhkHbtqtAhB++8ihtYMJCdx34x7BtFPYW5LQrbUABfxjqfgF+tBhnDXo9ZFW8nAElxWXgKGYLaQz4CHPDoJ9IL2TcnzQcexqN/5ETwFkDXZeS4hLwmcWgfcBBzw9mp9wvv4iVFLeA94E7Obpq+PckcMZivI2kh71yBmqOWwWYpHIa+DpHV4Upwx+QbzgiCntLE+6V/h0YqDnukgtycBz4BPgtQ1eNXZ8GvrIYcxnaRFLYKzWFVgBDN59Z2amkuAocAR6k6Tw/qAAoKcaBT8k23Mh29N4hTlMW8eBEpePF8Ppb4OcUXbwCGBhuZA7JYa9UBerAXOC9muPOU1LcQ8/v0QRdFag0fJZlOIl16H10fPymRIn1gAC409k7DHyZoptmIMdw2th7PD9YHb5vWpirAkM1x1159fstdeBzYCShTRJphtNYCOz3/KCHJu8HFgH7Rx33CSXFDeAw8G/sftIUQkmRZjiLTejTvaYs4jib6/BqeP0T8EOD7hEDACmGs+gFDqCjt02gnPoiacwEDtUc9yklRWP2SaxAjEbDeTwHvEX61Ewlbz/wPPBmvf/pipLiIjr7QI6BBMN5VICdwHLD9lOYbGjeGO2ZPxBenwTOoY/gM4kZNp0Ws9BVt8LEQD9wsOa4sxqyj4nWNN0WxnRL+QqwFaCuw943JlolxW3swp41pga6gX01x108IgfH0Iv0P0OtbdizwmZTvwLYW3PcTiXFAyWF0TM7DHt56bYwtqcSO4CXbAdRUvwOfIx52DPG1sCT6N+GeQXG+g44VUCXSZFzofXoSlgRhr3DmIc9I4oYqAJroy2oJcPAFwV0qZQ5mbNOjmHYO4Y+g2oKRQ1Yp8aIMOx9iHnYy+R/NxBiG/ZSKWPAegpFxMLetaJ9RLSqAlHYO0qBPUCcogYm+q9dLFyBGCewO9l7hHgsvgv8aaj5q8ygEUqK254fHEHvjbsNZRXgb+A+wENwpj0uJzuTxgAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
@@ -31136,8 +31424,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>https://daystar.com</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAGFBMVEVHcEwAbpYAbpYAbpYAbpYAbpYAbpYAbpa5YKdEAAAAB3RSTlMAO2jbGo60G3P71AAAA1pJREFUeJzVm9uS7CAIReMt/v8fn0nSScRgIohQh7epqZHLEtza08vy/5t3xgGEZBxAzrb+fc62DELOpgxizrYM0haAJYOwBbDa+d8JWDJIRwB2DA7/dgzcLwAzBukMwBsFcPq3YnARsGKw3gHYMLj952DhvyCQczQIYC0DsGBQ+rdg4EEABgxWGIC+LIH+9RlUBPQZhDoAZQax9q89jh8EtGXJg4AyA4SALoOEBaDJACGgKktQApoMUAKaDHD/egxcIwA1Bg0CerIElL1sCCUGgIAD5dAJAEgRGI4Og2rjlz9yZUl0BAMHoau2JGUh5y4RgxyunbY0x2KHlcCanfVu+7ZHD4Zvq3GxquD4wSP7lRHCsYMY7gOuYT2xmj8RRGfQbldHWszxStdInxHC+Tc0/5/isTuEayVK2d7TP0NYvxfKxWWIwKBXO8eOEIpG7vZPuMAVISSPWqHA0N/z0z9DGHoHRGQTXTNeIZCVBoKQeXM6Q6DdvkWvjomMIT7bckysedoayOE0fGPw/csgm09Eq/pODMj8kLowbUfll+ZDNp+kVN8Oibd0kM0nrZP/Qmi3M7L5JtxUXGhhmJ/+hz0K0HXwClotDfUf0INl+psZXFOhAQZar4ax7LSSgdLr+T74r9kE5qDKHvBVubUZ+Dpd0Afz/adHvvXTwVyDB+/R95oM0I9M4PORrv+9CGoMGk8Cvn7AmmXNt9qgw6Dpv7JZDLrvwpMYEN6kpvjvezo4bIYmqdsvvm2ICQwq//u0e6mJtPu6/X/bvF0E6VtBs8CtIsjKksq/f/ndFAaw/R+qFy+CIIP0tTA6n+QYgAQboh97r5SShsB/U2qMv8y1DOT2csY8L+gyDMoVP6bbjH9uAePn84itizDOoGzxruFeHZej/suadnZ17N0yPVakQ9hPzyuDgH/SUCuLMOL/bn/yg8Md+gCDOw1GHa/Ny5cldxV5zXzWj+k+jqR/mBthcLf/SB+tbAZX+w8KS8dk4CXSP2zlyBL2Z0WYOfoy5/aVElTUIRLIo1fWgmz6VIvM0Stlzjb9n3+z9H/tb/ftsTRw8kjYapv+0X6G31wLUqOXZ9E4fWeb/u7fbPYse/ubnTybJdv0/9rfbvRu9vaBuI5/0/SjcfpLtP3i9j+EI1VO1gw+ZwAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr"/>
       <c r="L48" s="6" t="inlineStr"/>
@@ -31180,8 +31476,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>https://nrb.org</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAFVBMVEVHcEwJTHIJTHMJTXMJTHMJTHIJTHPsruKLAAAABnRSTlMAIoq93UtPXWOjAAADFUlEQVR4nO2aiZaDIAxFm4T4/588IGFTWqGGaju8zpxKRXIJixF8PKampk4IkKwQrgOgxYomwASYABPgQgBGK74OYGrqCtmOT2SefGxsMHhIsFkOZXiceTo2PxABsM2805AorbH6XnSx/QEE0f+IoSMS+04Rvq0Mpny69kP3x+gK4vxuCCZWXBB0e6K3ZCtoUcQSPIrbseRYuMyhJe8AZ18M+dLzeCA7wfouwNixpHBfuyIgkVbgOGAVe4Eve61SUXYZEaVT4jC9NuA0snw1oQYA3jnukIIzVAHWaicjOwCBc0eoDICxBSD5Yg9A0TsZ8RCAUPIGABOAGQCwXA5gnNJRTC2V1Igm6NcE+DkAtyImd0USmX0qy6Y+D4CVlAyrfCBiQCTD0J34yXng8plwAsw+MAE+2QcgKQdwU9ziTeYzIbEkaZMNq4W1iG1IQes/ZgDPAxJaE2Q22fzFFHO3B6np7mc26S4JwCbdB0D/HkChCcwm3SImDJ8MgBAxPKbbY/cnAYlPyMrFel1mMBZFHU9KYAfPI42bMBGlgGQ9n+aBNX+cB2AzD8Aj5HhX/28mrAJc7gEtgHe6wj08MPvABFjYafEm2UuW77xCQGKlvVC4DUhqayJltDIEoFsT4OcAXEAi3RFFZp9aMMYtvzYPXA7gF799Y9QBvOPdkfZidc9yvdkQqyhbpC+2IkoA3uRS3DSCVGDHlo3mtpmMQwjOEBcUABx3c0B7FMbCG7ftZLJQ3bnEOLfJtqQflAlAEN3PKa+iwtas4bCLbzB/MgqTNULYR1bctFslFXcTcnjaNDL5UtrPXjA+C1caAHYHPeq8IeUNAO/aPEGgvHnv1fIGi9eo91gA2xAGvufLaA4YjBn9mjEzvhAfvch0m1f/bgMydVKda9D69ufr/RNgAnwjgCrtV3qgvfCGn08AtF7zOt9LACi/oXKqS7WLuj2g3VjPAKBy1FXuQTp5946j4JAGqod6AB/VeIBK0cVw2gAoPhO05X3tgVdcJ50WR8HTmPCUgf3Fire7T3fYOz+B3ZltuE5UXt9vf6XlRfZNdPgbAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
@@ -31224,8 +31528,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>https://frc.org</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAATeUlEQVRogb2aaWxd2X3Yf+fe+zby7eR7XB/3TRRJSRS1azSbxzPJBLYzgBs0huPsSGEEKNDCcVsXqPOhRr+4SRs4aZulaBsETuIFHc94xp7OqCONNKKohZQoieIi7nx8+77ee08/PJJDbZ5x7PQAF/fi3fvO/f/+2znnf4/gH6eJR85y3z3Jz7GJj3/kE/Wx/1AAdees7DwjARMwds5y3/lnAvpZAPaEbe5WHM99digQ6u3rtNn83VLWtetV1WcYig2BUBSzpKnVFBQ2ioX48oP78ysXXp+PxjdlEdD3gf1/ARCAiorln3x5uGVwdPxktdL4QixmmYhsmx2ZtHTlcoZWrUiEEFQqOhaLQn29FatV6l6fkm0IsOb3l68pSvT87ampK2/8j4VNTMo7IMY/FsCuxi2/9gfjHV0DE5+JbXs+v7Rgjm5sVBzlsmR8pJdCscTV6QX6u1s4PT7IX3//fTraAjxzfJgHa9tcmLyL2+nA67Xj9ctidw+zXn/iu3dvfPj69//rnRWgTM0qn8gi6k8hvHby1YDvN7/6+dd0ffTfT17WvnjzRjHUG+q2qIpKNl/itVdOkEjlWNuK8eKZUYb7Q4SjSQINHg4d6MQwTGKJDC89cwi/183M7W3L/ful1kza/Wx3/8CpF1/rrCTia5uxjXKFTxgfnwRAASy//e9O9o0e+8WvTV9zf2VxTul2WF1KKpPn9NFBQq2NbG0nCDR4sGgq0USGckXn0rV7GIakWKwQS2bYiiSwWTWc9XYuTN6lquucO3GQhcW4srZqtlYrvhfOfvpgc3NXaenu1e0MHwX6PxhAAaz/8j+/elzTJr753o/1zy3M52yfe/kEDV4nKxsxookMbU0NLK5sc3N2mfVwjKpRplTNo1oMUKqUykXWwwnCkTSJVL4Gqqr4PE5OjQ/Q193MdjTFzGzUmozZDx0c6x8dO2Nfun7+QYRaTDwV4ifFgAJYv/qtXz6TTg588+qH1bHeUBsbkQSNPhfPnjjIlZvzXLk+j92h0tRsZWQkwMBAM63NQTxuN+WyjhACq1UlncmwFY4ydz/MrVsRVlZyeJwu3C47E2O9fPetK+i6ga6b+Hx2nn2uflYRM//qT7/29vtAgVpcPAbyNAABWL7yJ6+eyGZG/uSdtzNjE6P9jB7oRNcNvvPmZRr9HiLxJL399XzqxQHGDh6gwRvCqroRWFAVlfMXb7DwYJ1f/9VXEUIiqVIxMsRTa8zM3uXH78xx904aw4BiqYyqKhw52IOr3sHc0hpHTyizpn71X/y3r5+/vA/iofYkFxKA9jtfP9mvase++e6PCscz2TLZfInRwU7mljbZCCcwRZF/+oVhvvArLzPSfxqXI4SCA6SClCAEbG3HuXrjLmdOjCKEAKmgijpcdS30dvYzcayNhqDOykqCVKpMqLWR0cEOtiJJrFYr07eSwaGDnT0tXZmpe9cjySe505MA1GMvO71jxz/ztYvvyV9OJEpIJIVSmYXlLVbWo/QP1fP7v/88ZyY+jdPWDlJ5zLpCwI/enWR+cY1nTo3hcNj33ZWASp0tSH9PL4PDNqKxBNtbRTraGrk1t0osmcWqWYhsm6GjJzvsWxszk8ltvcgj48SjAAKw/s6/+dXXblx1fSUSNq3HDvWyvBZBEYJiscrJU0G+/Huv0B86XdP4E+JLCMGbP7rM/37zAq0tjSRTWTpDzdjttkeelCjYCPo7OXCwnrXNDS5dWUFTVT51dozeziayWZ140ug7+1LzyuW3Z+eAKvvGCOWRHtUv/evDHbFI8J8tLZSdE2M9HBvrY6i3HcOQHDsW4Hd/6yU6gsdAak8UHsAwDG7euo/FoqLrBulsnnyh9JSAkyA1OoLH+N3feomBIScIgRCCpdUIodYGbt/O1hcLHb/58hf6ugAr+2J3vwUEYPvcb3z2i5OXtC+ub2SVSDzN3fl1TNPE51f58pefoz90GqT6VOEBNE2lWtVZXg1jmpIDg11MHB76mHFfweNspq3T5OrUEvmCQUvQx/XbS0gTSmU1OH68YevSW9M3gQo7VtgPoP7KPz/QLuXYv713R+8Y6G6hXKnS0uRjeSPCr31pjDMTLz3VbaDm94oiyOdLfHh1lkKxxNjBXjpDzXjc9VgsGoryqNH3N5UGXwDFFuWNH95lazvF2YkhnE479+YjSqjD56lzr723ci+TYicWdnsTgDowcvTE0qI5lskWsVot/OIL46iKyqFDfs6dPoEmPE8VXhGCUrnKlWt3+Iv/+To3b89jSvilV87S1hogGkuxsRUlly8g5dOsJ9GEh3OnT3D4cAOdbUFUTaVaNWgJ+HmwJIcPn5o4Dth2Zd8DqGvAUa00vri1WXFMjPUA8OZ717m3uMpLnxrE7+xByifPr4QQbIRj/N33/g9//e23uXZzjmw2Tz5fRFVVFKHgdtejKArrm1GSqWwtrT4JQZr4nT18+qUhNrajpNI5FCGIxtNsrJftmqX1WUsd9ex4zx7AZ780HIhHrUeTqTLzy1soisBVX0d7qJ6xkWEE9ie+UAjB6nqY//Xtt7ly7Q7Vqk6g0ctAXwdHDg1gtWg4HDZsVgsOu406u41sNk+xVH6qJQR2xkaGaQxqTE4vYrGovPYLJ1GElVTKdujMKx1NOwBC2/1PqLuv895do6O/q4UzE4PcmV9nbTPGL32miwZP+xNfJoQgkczwvdffp1yu8MqLJ+nubKGxwYumqQghyOYKKIpAU1UcDhtOp4NCoYSuG7WsYbM+wQqSBk87IyNBwpsbtAR9OOts6LpBPKa19wz1dp5ndX4/gGK1+bvTSdOtlyu0NvmZurWIqsJgfzNW1Y00nwwwM7tAMODlubNHKFUqbGxFWVreRAgQioLYEcgwTBRF4HDYCQZ8tDY3oqk1yMeVI7GqbgYHmnnrhyt4PU4yuSJuVx3JZMnV2RnoBLRdAAGoUta15wumNn4gtKMdgdWm0NISQGBBPjbSCiqVKlJKnPV1xJMZWpoa6Gxvxma1YEqJlBKLRSOXK+Jx15PJFTAMg/B2nCtTs9Q57Bw80E0w4MN8REECCy0tAWw2wd/+4AMafS4isRR+v0XVNGfrDoCyZwFdV33lsskb717jwuRdHHYrznoNt9OFlIL92WfXNa7duIfFotHd1Uqw0cvyahgh4NrNORr8HoqlMk0BH3fnVhg/PMjs3SVOHR/BYrFw6vgo8USaazfnaGlqYGyk7xE3EridLhx1GkNdvTT6nbUsN30Xw9S8uxZQdiygGIZiMw1JR2uAX3j+CG3NDWgWgc368PAvBBSKJS5dmaFUruCsd/CDH15kZS3M5LVZ0pk88UQa0zRRFAVFUaivdyClpFgqs7EZ5fadJd6/dJNCocTBA91EYkmuT889lplsVht2m4qmKbxzcYZSuYoiFExTte3IvRcDIBGqqnDq6AAjgx3M3F3hSUlCURQuXp4hEk3ictWxvhHBarNgGCaD/Z143E5efvEkXo8Ti0XDZrMwNtKHIgQ9Xa1UKjqtLQHCkQSJVIat7TgHBru4MjVLT1crPq/7oZgwpeTKjXl0w+Di5F1sdgXxUQmH3QmNVFWzJIG/e+MS124toQiBrkvKlfJDAKYpuTEzRyKRwemsQwg4cXSYYqmM3WZlKxyjXKlSKleolKsYponVomG323C56vB5XPj9bg6P9qOqCtlcgWKxhNdTTyyexu/z7AGUK2UqFZOejib6u5pZ2YixuL6OUIwyO8vNXQuYqqanHHYbDZ0tWC0qc0ub1NWpZHLZ2mJE1qYJiWSW7UiSqZv3QEJLcwPlSpVMJk8ylSWTLaDrOoViGU1TsdkspNM5XK46pATTMPH73Pi8Lvp62jlyaIADA10MD3ajqiqGYSCEQAhJJpulVDSJmGnC0SSZXBGPV0MR1dSjAAYyv+6os+v9oRZt7EAH3XNrnL98i62tKIcGqiiKle1InP/4rW9zY+Z+zX4CItEkxWIJu93GVjiO3WZlYnyIK1OzBBu99PW08ePzUwz1d5DJFlh8sEl3VyuXJ2+xur7NO+evEgj4eP6ZcY4dGQIkwYAfic7mVgRnXT0vnT1MMp3j1r1VpJYzqtXsFjtLzF0XMovF+LLXF8xOzSz6VjYiROMZcvkK9+fDvHg2i15x8md/+X0uXp5BCEFHe5BKVWczHCPY6KOzo4mtcBxVVfB53TtaFFgsGsha5tK02tzR465HU1X6etoJRxJYNJUfvPUBV6ZmeeHcUU4fHyPQrHB/PkyppPPOxWnWt+IIoTB+1JXNJCKrOwDmrgXkyv2F1WDL8Oq1qZRvK5pAEQIp4fbtKMnsBndmdN7/4CaqqmAYJh2hJvL5Ihub0Z2Q+iiDiB3zSClr1zv3FKHs+bcQAlNKNFXB43YihEKlovP9Ny6g6ybnnm9kdjbGdiyFUEQtVQpJQ4PcvHdtaZWd5eXuXMh882/mor6GynWvx4ayoz0ELC/nuHHrNpM3blCuVD9KWj+hWiNE7YW1wU/sPa8oO1BIhCIwTRNVrS16aiD1+Lxu5hbmuT59i+XlHDueipQSj8eKy12YmXx3PbLrQnvV41KaoiK232sP2YtS1hYlwQYPlYrJO+/cJ5pe3BPm49ouPLI2zd5tu2sBIWq/S1OiqkptzFAVJNDgc+P2l3j33XkMHdqa/ahqrVDQ3m4rlYsbF6pFcjsAD5W/9VtTVye7e8Vtm1Xj+KE+vvEHX2Cgp4Xp6Tj19QKP7+maf6ijaq36oRsGpXIFARiGidyZXiiKglAUTGmiabXMowgBUmCrq2Kx6Ny6lWR8tJv/8NUvMjrYidWq0dkl712/MDVFrX762IqM+ZvJ8qc/f8CdTjqfy+elYrdauD23SjyZQxoWBodtbKyXMQ3o7GiiWtXZ2k5gsWiUKzrxZAZMyXY0SalcoVgqE95OYBgGuVyRZDpLtaqjKIJYIo3LWQey5k4WTcViFQSac1y9kiAWK2Kzahim5OadFYJB1ejoiPzld/7s0rvwkQUerUrIxvZSvHdw6MTNm6nWy9fvk8uXUBRBOl3B666jrUMQ3qoiJaTSOYrFMoVimVg8U3MLoFSu1DqTkmrV2Jv4VSpVhBBEYykMU5LLFUilc4CgqlcYPKiwcD/D3FwaRRGkMgVu3HmAaRqcPG2dmf7wrf+0OpfeAEo7xn68LnRvKlZ44bWuCrLx+a3NknXXhYWAaLRMS5OL1pBg4X6KbLYGt3v/oRiAh37fTat714Bhmui6SbFcoGfAJJ0wmJ5OPaJSwaFDnrzPt/jHf/+tDy8AWfZV6B6zAEAssrB57uWxlnjMfjidLu+9WAJbmyUa/PX0D1lJpSqUijw2CfukzTQlbi9MnHBRyFiZmUk/PA8yJaF2F0cmCt/9+//yt3+RTRox9mn/SQAAMr6pV5q7y0vDY/0jm5uio1SqmV4RgkMjfeSygmS8zOiYE3udQTZjUK0CCD6ORcqaa9ns0D9kZWjQw9oDQXhLp1Tapywp8fscnD2nTt6efPsbMxejS9Tqoz+xMscOnbxzdTtz6Kx9qau7c3xzQwZLZZ3mJj8TR4aoVKssPYgRjUh8XjsDB+y4PBLDMKhWJYYJ0twVdidzCbBYwOcX9A7YGBx0US5amL6Ro701xDOnD7G6FqZcri2SXC4755513EtsX/rD1/9q5gY116k+KuzTvg9IwLx2/kHk2AvOha6e0Nh2WAb9Xh+tzQ3MzC4yPNRJqVQllxUsL+Vx2G2EQnV0dNloa7cQaNYIBFWaWjXaQla6um10ddXh8zhIJwTzcxUCvjb8XjeLD9YJBvw0NflZWNzA73Nw7lnHvXx68ut/80cfXATS1IpZjyXxn/SBQwLG1LuLm4fPWu4MDXf0rCwX26/fXBIWi0qg0UsmW+Bzr56lVKqysZkjGpGU8na2w2X0soapa5SKCtm0IBVXWHlQplyqo6WpnWyuwImJYbo6Wlha2SSXL7K2HsXnV+XZc9rVePjSH+4Tfi/v/zQAexDX/+9yuLkzO3X0VMgBdX2RSMW6vBymrbURRQj6etpZXQtzbHwIVVVJJPIcHj2IwMbc/TDJZJHBvm58PjcBv4fRg70YusFWJIHVorG8EiYaS9LXZy2MHy1+79aVt7/xg/8+c+PjhP8kAHsQc9cjye2te5OnXwyshEINLXrVElhdTSmb4TixWIpSpUJz0M+duRUMw+DMiRG2wjE2wzGgljLb24LcvvuA5qCf5dUwt+88YGMzQjCoGKfO2G55vYt/9J0//+6fz1zcXqLm83s10J8FgJ1OjES4Urz89p05f1P0/fETDeG2do/HNIUvHM5oqVSRStXAomlkMnl8Xhe5fJHtSBIpJeWKTqlYIZ7IsLYRoVIp0N9fXzp0RL0dCm3/1fSlH/3xd/70wwvZRDVGLdtU+QRfKX/aBC52oK0I6s59pqPt8OmjJzRLy7l02nE4GpFtqZTpKuSlWq3WVnGGYaKoAptVoa5eGH6/lvP5zQ2PpzBTLmxcvHbh2tXJdzbXkeSp5fiH6v8/b4BHQSyAzeUT9ePPhpp6hns7XZ5Ap6Y5W01T8+5WD4RilBVRTVUr2a1MMrK6MLu0Ov3BRiSfljlqPl7ho4/bP9XeiZ91s8f+zR0qtSLB/mO3emDuHDof7Y3Yvd699w8W4OfVHt2xslf64KOv7j+3XSq77f8BoQsoZh55INEAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J50" s="6" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
@@ -31268,8 +31580,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>https://passagesisrael.org</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAP1BMVEVHcEzR0dGxsbGlpaX///8AAAD19fXt7e319fX19fVJSUmRkZH6+vpzc3NbW1vCwsKEhITg4OAyMjIfHx/v7+/I1eMBAAAACnRSTlMA////////96NRV/rZWQAABS1JREFUeJztm4uyoyAMhitUbUUuAu//rEsSsGoLrR237s7AzLmpNV8u/ATPeLnguN/67qejv90vj3H343j98RjHbka4db+2TqO7nWs/EdxPsx8IIAsn2r9efQjAz8tvOcb75XYuwO3Sn2n/eu3PLYFQhhWgAlSAClABKkAFqAAVoAJUgApQAf4LgKnRYTSnAPRMto9hjocoAvQiGnYuIbjpdwDNABYVj173mmJxcBCyAGjesdWxEZGOfaKRARjB2+HZWQWHfwCgs7GGE38fwAQr/PX14ugqeAUAmc4VO/sBwFBKMw8Ah2rnM0DRPpy1R9p/BjBr+9M63l2+Og4CgPpfPjrdpNwcPQm2AN2m/vR62k3hr7U2HQ0QPDTLv9065PZoGdoCdJsIN+sAyE1+jgcIk0wsz8pVAECE/F4DWu8BUBsLqwCYL+xPb2VjDbDJAMjeHJEA5/ba921BVF8B9Hw17e3DZ3BFfWZ1fNxRvp80pY7IP4wWlqenoeKVTLAkIg3nyYzmbD3xCwCg+1hCoAY224cwIajQJM7hcLG8UvqibFMfgyjU4y3rsgRgqSSwN8pF0lOfxmO+Q8QcfggsGUslFY4YDr/CJdao1n0G0GMJMtdu5iYwGdcqP/uJNsM3FipFIawmxRqATGEdhmoKKuMaCNSHAHBzaMFakS7pKX3UrYJR8FNOUCHwpUk4wOsYfBayofFEQIOrKTbLcBYAohm+PALsUJCtDKZ8Q6lF/X5kXmP1TAQwhEQq/Cj8BpandTVnABqOvrcyTssR7ueRZiCocB6KZIqlYkhwdArAEIM4eLxmANKQfPbUTb0CGG3ahsTLO4V6IsCIoMZckdfgjGxtFwMAABzjTVGWLUzFiVMZTXjPTTm/AoDIWi5nWexiysGvjtYjhT7G6qSiw7nl8CxLm4dwVC4S2Qu7mYSZFKAe2ugUxk8EKAv0jLLLMLEWd05wiSHYhmLPI7qmNIUbBR4/wJWj2whqvgjnaDF0lFN9p3tjcjxtGT2gDDEA8BkVLwJjtjVTcuOK0KuGo7A1m9cx8mokXYYqU2KOYsNSMgyhQnxYTB7OBRnrcaDY8+3ilAXgqQTSR9rZu3a1LnNIOyZ5pCBNUW1Jk4MjqmkElTTo5kbUsgAqNWcxunAAuyEt0gZxwFmioeIc3BeFgwUgE+zI1N5H4pbTj62oZgFSCcxTalgoqAGYgWobdTjIK+gjqYdMVokdxNxyElD51BzkAOb2OFXdSBFphI9ex1VvWKxEUKtKQBWAWjrJ9ftNVA6gSSUwxJ0Qx0g0s1VU9knEbFwn6VSULQ3uizet4FsAltQ0lYKLaxp8x4WftS+TCkhix3OcHIBIhqOI0Y4JZ0QT+wQMs1j3KbzQOuwDUPFGY/yJMyxk2hkQH0uz8KlJGnCdHOa1xErxvPx8BuCSZhMAKnqaUE9TKY2pfTlsqZvMASx0UNKWGbwTIze8UF6ac6ab6bF78iiVpWcaBQD6xeAqFHC8kTsfjQTrPObDZS/KAPTzZ/xWej+zzYxdJiEftVxH9NgGe+mKSXzxYTFbDmLEmqIaZQD03AzsHQ/rhn0iB3mAr57EsPhQWbL3IlwEYF8BROfNpzJcBtj9KIbMqz3W8wCdNK8OvzVvdj/JPuhfNk1RIX8AAHK3N2aHAhjaq54H4L9+gP1//NuuAlSAClABKkAFqAAVoAJUgApQASrA3wU4/XW/0194PP2Vz8uXTxaOGd2/8NrviS8+jye/ep1e/YYsnPHyu1+9f3/a6/9/AKQTGf1tdiGwAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
@@ -31312,8 +31632,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>https://hayovel.com</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAArlBMVEUFWaQAeNUAY7AAf+ACQnYAUpMBWaRHcEwCSoMAgeMAdM4CRogAa78AfNoARXgAT4sAQ3UARXoAdtMAS4UAcsgAX6b//v7///8AguUBe9YDV5cAZbIEUY0DabgBXKLv9frR4/P6/P3m8Pj1+fzc6fQBdc0Jf9y10u2XvOHG2e13suo9leQEb8Eii+JZouYAPW2dx+4MYqcneL6zyN5Jg7uRrs54osxUks0+b55tjrCmv/4PAAAAFnRSTlMBkU/a+RoNAP71bAYmtqeGzmE9OOvP0AN9dAAAEnlJREFUeJztW2djo7oS3RQHp7eNFdtgakwxJmCa/f//2DsjUSRwyrb76WnvjbGQNGf6SIYfP/7ffq9po/Yf0/5xMbm5eUI7pT83k4sf/xEKonJxc3p1cnt7hnZ5eXl2ic/b25Or0xuB4t8Sv74B7bPL17b1V6/Acnv1dPGvJEGcT55OJNpH2uXr5dmJkMRfJ/9jcipR3242SRRFQUotiKIk2Wy3LYqzk6ub678KgUv+tqW+TaLUtzzHtW3GZmxmo5meFQLIpgFxKXTx9+j35DdRankuKKPNusa/Mtex/CBpMJydPP0lKRD5RvabyPdMWyEtN7oBEGnSauLpL5gjTO/qTPCU+J8Ql0DYrhUJMVye3PwhApA/vRWKj6yvqfcgzFSo4uxq8icQtOunk0sheyL/LeotBkdAuLyFNf42/Ub628ByvyZvWSqEmeMnwhonv4dA0yaC/SQ0vybPnMSHRyp9thc0QvgdNWjaE3e9berMvhY+s9PEm6WWOpK5IRfC7emPX0agXZ9y8SdQ/nGSzJb4tcNtOvM3FlPBwhqFEK5+1RCgfsG+eZQ8OZsVJX4LgTmbjedsI/Ds2YORFhfCLxqCdsHVv/GPsg/78qx087retCJn6WtqB1uP2X40sFebORFXw80vIGjMLwmPGh9z/WSz4dEhcPkAZm4Sx9pEYHeTzsyhEByuhl9A0NCPvGPSnzEvavPe68YTCNNX34wgADNKHDtI7cEME+KCM3wXQSP/yDnKPvOSPv9vuQ5gAYnpwwpn/tZn1jYcToRmfkEGLX33A/FvJPopH8SCV8tJEofRHzdJxjMZC7+NQLu++pi+HUY9eR6faXVof5ZuQ2hi65M2jiIPCfjt176gaZ/QZ862p594dmOB0cZxNpHJvG1kepvkmOfAbwnB5cn1Vwi0p7MP9U/WLgFoXMQm7QfkkdE2dIPXkQU0c7kdXF59ERO1m1vO3EclR7TuDUCAhOI3nreFQ1rbyIY23ONTYT4pEJx9nhdggKRc64M14IKkgyTlmggEAG/zGiEOMht+CG1YHyYO6OorQxQGuPlAiDMRWCk8ppIPcsbgAtAE/W9/NJcSQ/RFUBYGkH6W/ZjpULXBY4GwVHgmEEQ+3I/74sdzKWB8agaIgCTgow4gWGBtNczduhEV3JAbRcpSRQDjCs5m/qdK4B54RIktYdt0PM+y3FadrxHPlXbaFq0bxXpNzxl6JHO5Ej7yxYlQwIi863kOlfzY/2ADxIkIrhF3OgFQeqJg1Is7wObJY+oOggfyy6ejADTtpGNKJk8FLnZikPl6TR5gcT8TbEPlDK7PPQdZN5U4hldSN23d5JKOR4PboyLQni5HHkjkN43rb7EpwlKNhTZ2CJLcHJCEUCXIU91GMa9rqmq7W0J5V0cAaNckgFSxQCp72rgT+Y5iVtyeXreeK6yBxKJMdaSkKYdWrrFjOYG7oGqBqO370GsNbJq5whXD5u5MbSx8VZrfz4uOuqKIgYGsxIb9Ztudjklw2XOI0TB0IC7yWZsoEjz0zi1EMHJFIQDJixDhuKFHoeBlMwwxjfXxe6PcIWI2TMM1PW4Mm864mR0cEYGwgECib/LlI+RcEXjB5ZBIp2Z/FH8Zn72OuNlQIt72+HlSH1nBzZk6yETew4aU5ovo0YR+ubURaOi6XeEgFuRVnLQ2z6mXpwoA7QeC4DqSQEZrCL+xiKYMjEZxTfRvwtmw2cH6VcpqSGFygGcWhUN1q3JxC3/tWAT/88TvwwdPN+tRkCaYiE7j6gF2tm7iJJeA6/ip1y/H7GT9eqaYoXZztl5vekMNt4klGTZRQguGacrfUvfWV3vJBai/8X1kSzrDSiK/L1VS3FZ0oF3R+v0STqjuSIGIKKkiIDtBdF7PRzYAAWC00AwsCHPn+NdLED6yXp9IpZGm3arLtxmklZrgaUgpfF3zpV9VERCwOclLfLWj+ZwEMu+dlVS8PpOMQJv8nM8TZXXKQZCa2X61tnOsI1fczEzQtaX+QRmSrtHXkWOEgCbLBHwMkXSgnYKPVKkmWUirzAO7LQYCLEEg+5byAbTUPJW6USQSy1KXQx3zteRFsNL5/EQCcAJW1ErQDjjsTeqHYWhZlscJzVOLrlEeoEDYcj4dLgeLerBnpgbx4kbIr60w9P2UA5hHfbiCVc/nt50OtItbSWSNfAXq9Zbahhppey4uNwmVJjSAYj2nl/CuZiA3OdH4fN4hA6BAMf/ZOSKccD4wMOZxhtv2Jj7W8pe5MmIwcnDNh8oAUD/Pe0eECZC2VRM4tvpxOt9tCgBhBC2CK8h2sKVMRyTIk7qrdXcx+NKPGAlI3m9yF2qNAJmQzEgNMgkHsI2CALVohI805cYEn8OVH3FPwwU13r+NuksMocs0oMl0lL/lQlP8nHyzLQq0CWywVm3QFnNQadm2aZrieFw4OIwFpQDd5jsYkmtKKuHFjJcQJYtODHkhb7uY7XBu3pRoAbd+O2uqY2xIR2HI4/TfUhEOWVeIohOy4mGp5wjyfBP9HNharuxFHODiVJIZg1v/bKxQe/759hapNpi+oc3jSDUM5gMUxGIndFdaz8L3GIHG2uAiGaYG/403NY6G27cOwCkABPIM5tRE4e1tq8ZYxjhln68YyMtFHJFLH+vhcam9EYspjgYhvv286gHMlZqTWbUAPR9slJm1Ru92iz9KjYj0BhEkXEDJsHr2EYn4YnI65zOawpBLQC16bSuo6rpOAm/ITUDCjrGasg+H8onEdowZteU8DYOoSqJUPvbjQm42idrVz7fd8GTJxj50vLkE8DrmsqkGyvFIZrGwhAGyGoybjmOqpbtZv8WfARhsKntg3Dzj3bAKslMu5liNJ8xOd1vPzK3RYswkCVz0AIbKDvMPTsnh1GB0VAQxsyL6c7VC92CVvp0MVx8DiEcAojgyZ0dEwHUQjwHARXe4MQg2cVyEbhSPtvwcQBx/AmAW7uIk99yh6KDTmNpIBcypRv0sMOLKAiuulzvD8UMA/tDccwyoAx+VhmLuAAYniOOhEULZ/IYsAuYV8a6Oa8eqi1FJ/wUA2poGdWzs6rqSY5SZxKLNc3U7ZtXNDSUOp+ioPXjIqKKHG8ZG6wWnP2M1DvANGXM9H4MgVmnHRivGNTFbK9qGooVk4p28wQWVOMWfwHTy4Y8IRRzfNyclABDL+1I35ecU9ENsCI6Nzj6YWRiQipUDljyDkgHG1WQfhpw/bB+9RRy4Xl3Yg8ABAH0oNuJSZqc0KqcRhVMbRqseZpeGYcSpbdf02bPKXN5hmeJDrjsq9FS2VRtDI7N2RpcLbl5okDQg3C1rsTWDcRtG98uQv4MAqHIId4YyJTX495nP+2U7DAtjGYS1UdpeKNf9sGajy4YTAKhNWQfgtOa/lsLtjbjdDHjE4C6noytiDK7bNKvAVxi66Icd9nsCtyQlAJRVV7IhsjzuAVzcGoZaERHfRUn74xxMB74fUr1VxVi+DrEBMBtWTd4cTjagb7y/COk8E1uC0M8DPqlyEL98JaQEsfHSlmQ/TmhSZ2mM57Dd0thVeUC8xTvRaCljVxTIkzVdx3XT+BfeXfBLjEHbFe2cwvLqZWCbfUhhNkC/dKckV8ZylzcAbJ9UyGZOuVsuDfxn4E/TaLGl0V0vlRtGd0FjjGUzkL7uqmJZQoNlfwDg1Evjrj2v1E4xuGx+gLF3RTjjTuhxCMZSLGiIq45kA2fZfyq3+jHiS2V7heF3GRlms1x2x5WwQoxorNCussIX5/B2bijLCmJNxIsFjd2u/YS4+b+joAqEQ6M03TYlwLaWy35ndA0AbbRmoZEVeYMAo3Z1VZZlQNJYLusgyNsWUMcuCPiNkgxO6l9W2BNgXllRM5ZFXi9LxyvLzs+Wy5f+kEa7X2ZxEylQde2yXcmPuS3ID8btuq7tg062C227czG3zsCpn4Paqu637Sh10L8K+NM9Lm0LTK/KlnEGn6mWeVvgVwDQH1lrz9ky6yzEDYvVsqjAS5FlCPkiBCzlIa2ollmxA7mlUnD7S8JqSScGvpFlhgeu6+akCnEwW95Lh0QXL+CiDWCM8K1WWZatsqL5XajKsuVKLRoQmNGZEbtqiDGrFforKbKZGLnzyqzwZiE/qrJzTHyWz4jusZC0vOtXBULKrrIsjzO7I1KVWgYhn2QkFwCbKf18tJH3RShsPlvuVoU1C+BtDcYX+aDw+hTsyvmIzTwYlQXVI7Iz4gB0coU+8WFwBENgkDXGF2GfgO0AONGRC1sfaYDyEQaovxWQtXnFKisdwIBCVtWoEPVq6i+GJ6VgmPcjundnreipXMR1UbIFuK+eE17cQ+nDuhDxcrVaLQ8VZq9WxfhXeVgrWjE+KS0xHiK1w64SygGo2mW81mYu5r0MTqtPV6tFNQSQr6Q2VADXJLUsGB0iBxm/EVZZ63d2tUCPCLcsxO37we9GkxdM8IZG1pNf1OMa3c/ErUHFSccEYuYu68XjZItF0TgawLw8q/S160cSgbrfqyT+F+UQAPAtmpuqG7p5YIZZO7GNHVDLTtSFzCIBjJ7ruYEI9gor/l7WAHyYqWGAC3WfrYbWk+9hrmU7b9+aqJM3x/808eV0SF+7vl8sVlKoQzRacA7bv0XQPR3DSwY/W5BgCMbiIM3z9vsQUlgt+D/ca5ynO2cJ94vV3fhnM+35ZbGQRYBxvK3av8hRAoEdIlM4BXVnnseHdRZKgqny8tBMppmq9UKz6BwJgEdDWQSIJi3t/lMcccDG96VX8s7KtQO635oXY8FiHwYrPkn8W+zV4ydi7O7Yk12oCsBRt7cTnK066quF3iSGcK+3vZAYcw4cmyiiXdAOmHdY9G2ll7KJ8uHPR+gDweNioR9aVsLVYtAyLgB4/yJrBcwFlmcEhQIv6Gc6AioL9/JESbEocrDu3Qc/n1+80JpNVAn0AX29qffzvV7mgkXu5NxaFxQMsPpeJ49gs1JXZvZKsAr9IwFQbYjBjUvZ5QBAqwDvoMPm+ToLAYmB7ELXEQzogjOAPZw0Xc/ajSFzD+i//+gRCmQEIiTssMKiyr9QKLnkEAmArmeHkCuFVgUV0G/FNAtX1Nf+62JloOuLIy7YIbh50XWdxzxIgFbQiQ4tMa1YE8Z1KB4w9n4g2KYgp1PLVrreRl5miz6xBtYUScADxGMu2LfTB4zgKStvFhAfWSk80CymZFIwEHh3vpiWwi4PUzFw34dE56D3K4h+BO+prg+zkCqC63sa7tsoSPd63/ZNwmPBFMGAWaspxbd8kbWPsQicC6kKQiDrp3MbYBzTJwrgCCZ3uj4llZllN3+6bx9cdPbTg8fsw3Tv0xHDtDFvxiACGifnEkSyVgZ8OuoqdDx85AG9GUAJRGUGc+erTqeHsM1oAUwNWYDrnpXTNtFwHQwBCIYxv6GPkIlBz18+4as9P4AwSdgJ9jR9T3sEsSR0CAsE53t0QexCMYxcc0pNDboza48+/cAfTIXCMnx7/Pr5Xk175FxTBW9ii22ZXb0DARToDvRpzohpkeco/BAhfboYFk2wmEPOtwLY59Oqnxpgh+AHIThHTG7zSy9T4twrzum8Bx6dc868iuRUel44foyLfjJvQHL633u6GNXRA8nAGjwYwpySjD5f6CE5yfmBjlDMvDif7g/5B8++NzyYAcn//tvPFl8/TrntjZ5qYySGaUkZabqAobo5tL8vw8+ffQfyxS/RR0wmBOf7fLwuCykFId2dI8lCDtND/tWj942N/gJ9rgVCoASWZrWcBOOW7zAHCCIMjx5pyxPId76v/w7Bj2fYwTkFhOHy9DCdtQe2bzVUh/tzrPT4HftXITzfCTWMNmQz8q/yg58TBmNt7wA2pg+/83y/Nrk/Pz9/16uhN6CV5fGn7gfkmQn20e6ef50+2vXF48P59Px9nztDPTjfom+HB/0d9O9/90UX7fr5jguhCWfy4l+Tn1nV/hz0Hx7/4C0XbQIhnL8DQviFsQ+Fz7wS5EH//ua3xN9DgBDesdJ7kX/lcBJ1G/H5ncjfPf/p+16agEANEc/58mUn3De9/DDl5En6f/66mYa42EDQD8FnGPghnZVX+/eG/B+9ZaVAmDzePbwLMRzK3DLlR4xn/cmhF2JTOBXk7x7/TPkjCM/3D0IM70h+VZmHnmOKY8uZ7dLrhrQj1ZshD3ePk7/81qWmXfdiIBT6fr8vDqLhEummvQXmny/+wXun9C7r5PSulcPxdt7w/o9eveXv/D5DEA8Unwakzx8e7u6f/yH1BgN///X59PHx/u7u7gFYHvB5d3//ePo8uf6P3sBuyFxMunZx/V+//i3h0P6rl77/UfsfNbYTSKBfI4YAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
@@ -31356,8 +31684,16 @@
           <t>IAF Top 50 2025; public record</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>https://pjtn.org</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBIgACEQEDEQH/xAAcAAABBQEBAQAAAAAAAAAAAAAAAQIEBgcFAwj/xABDEAABAwMBBQMHCAcJAQAAAAABAgMEAAURBhIhMUFRE3GBBxQVImGhwSMkQlJUkrHRFjIzYnKR4TVTVWNzgpOU8Bf/xAAaAQABBQEAAAAAAAAAAAAAAAAFAAIDBAYB/8QAKxEAAQMDAwMDBAMBAAAAAAAAAQACAwQREgUTIRQxQSJRgXGRwdFhseEV/9oADAMBAAIRAxEAPwDcaKKKSSKKKaVYGTSuknUVypl7ZjrKEILihxwd1LCvLUlYbUgtrPDPA1T6+m3NvPlS7EmOVuF1KjyH0MAFW8qUEgdSa9ds+FV2ZM84uzKEH1G1gd5zxrlZVtp2A+SbBKKPcK7MCYzMbW41u2FlChzBBqXWfWO7ej9RSmXThh99STnkra3H4Vf0ncN9TU8wlb9E+ppzC4A9in0VXLxq6JbnlR221PvJOCEnCR40206viTn0sPNmO6o4TtKyk+NLqYsscuV3pJ8M8TZWWimg5xTqnVZFFFFJJFFFNUd+KSSU1HmqUmK6pH6wScV6+2g4UMcqjk9TSAkDYqj5z49aUEpUCncQa68yyOJWVRdkozkJJwRSw7OppQemlIQj1sA5z31iRplSJrEfPhGupjwuFMuk1TEJAB+VdTj2jqa4MIYlsn98U6fKMqSXPo8Ej2U+1sqemN7I3JO0SegqSpqH1NW0N7DgftNjjEUJv5VOuX9oyT/nK/Gr3p+8KnWF3JzKjtkEZ47jg1TNQwnIN3kNufTUXEnqCaLBcTbLi28f2SvVdT1TzotDKYZiDxdEJ4G1FM1w5I7fpc9R2lFSslR3knrzpM43g4xvyKtl10k666ZNpUhbTvrdmpWCM9OopbRo18yEOXPZS2k/s0qyVd9N6WYvsB8/lSf9Cn2rk/Hn6K5W1a3IUdbudtTaSrPXFS680ADh+FOrQN7LKHk3TqKZnlThTlxLXA1XPftsZErsVPRUnDyUEpWkclJPwNd+o8yO3KYWy8kKbcSUqB5g01zchZNflj6TyqlGlC4Ml+2TVPoG9SNv10d4pPOJHN5z75qj3SHK07enWWXFtKaO004k4JQeH5eFdu26qYlANXpAQ5yltDH3k/Gs7V6Y83MLiD7XUdFrseW1UixHld3zl/8AvnPvGkL7qgQpxZB4gqO+uiixurQFIkNlJGQRneKd+j7/APfN++hfQah7H7o+Kin9wuOeNWizRDHi7SxhxzeaixLGtqQhbziVJSc4A413ANwovpGmPhcZZhY+FVq6gPGLeyr2sbT5/bu2aTl9j1hjiU8xWccvfW0KSTVLuWinnpzrsWQ020s5CFA5T1q7W0jpDkwK3pteyJpjkPHhVNE2W2lKESXkpSMBKXCAKX0hN+2SP+Q1Yv0Gm/a2PummO6LlNNqccmsJQkZUSk7hzNUumqfYoiKyiJ4I+3+LgC4TeAlyO7tFfnU1Tr0BgSb1c34rRGUNdoS67/CnPvNcadqeHb0lqwtF1/gZz44fwJ4DvNcqw26XqjULbTzjjqlHbkOrJJCBx/Id9TxQEGzjc+ykfGHMLyA1o8+Vreipj1wt6pfYqZiLViOl1ZU4oDipRPXkB0qzCvCIy1GjtsMJCG20hKUjgAK9xRhoxFlk5HBzyQgndUaRNjR/277Tf8agKh6kuarVZpEtABcSMIB4bR3CsXlPvS3lvSnFOuqPrKWcmuOeGoXW14p7NAuVpuurQi8Wrz2HsuPxhtJKN+2jmPb1rLRjaFd/R95ftt1YZ21KivqCHWycjfzHQ5xS60s3oe7K7IfNpGXG/wB080+HxqJ9nDIIPVkVLN9ot4Ktnk5vfncNVtfVl6OMoJ4lH9Pyq7DjWE2qc7bZ7Mxj9ZpWSPrDmPGtstsxqfEZlR1bTbqNpJqSN1xyiumVO7Hie4UuiiipEURRRRSSTSaz3yq6h81gptMZw9vIAU8U/Rb6eP4Zq7Xeexa7e/Okqw0ygqO/j0HjXz7d7i/dbk/Nkn5R1ecfVHIDuFV534iyMaPR70244elqh8D+dbJ5PbM3YrGJk7ZakywFrK8DYT9FOffVD8n2n/Td5DjyfmkXDjmRuUeSfia8dcX6Reb1IQXFCIw4W2WQfVAG7PfkVXjIY3I/CMVodWSdKw2A5d+FtsadFk5EaSy6Rx7NYNSxxr5qhSpEGQiRDeWy8g5SpBxX0BpW6m82SLOUkBTiMLA+sNx99Wopc+PKBahprqSzgbgo1NbTdrLIiIIDihlGeG0N4rGJMd2I+piU2pp1PFKxv/rW+Go8mFFkEGRHacxw20g09zMlm62gFTZwNiFkuj7M9crsw92ahFjrC3HSMDdvAHtzRrO8+l7soNKzGYyhvHBR5q8aueursi0WrzKJsofkgpSEYGwjmfhWWjd3VG70jEIPVhtOzYab+6l2uC9c57MNges4rBP1RzPhW222G1b4jMVgYbaTspFVLyd2TzSIbm8n5eQMN5G9Lefj8BV2FSRtsEV0yl2o83dynUUUU9FEUUUUklAu8Bi6W5+FKTtNPJ2T7Ohr59u1uftVwfhSUkONKIz9YciO8V9HEZFZ95VdPmTERd4reXo6dl4J4qbzx8DUFRHkLhGNHrNmbB3Y/wBqn+T2/iy3oNvLxEl4bcHJKvoq/EeNeOt7BJs95fcLSjDkLLjLoGRv3kHoQTVd7t9bL5PL23frJ5lO2XZMUBDgWAdtP0VY8MeFV4wHjAoxWl1JJ1UYuOzvwsggxJFwkojwmVvPLIAQkZrftKWz0NY4kBRBcbRlZHAqO84qZGgRIuTHjMtE8ShAGf5VKSkA7hVmKIMQKv1J1XZtrAJ1R5khuMyt55QS02gqUo8gKkVXNZR3JkJEdTq2oijl7skFTi8cEpA69TU1ieyESuLGEhZrdZkrUF7ceabccW4cMtJGSEDgKmN2iFbQFXdwPyPsTCtw/jXy8KmrVLYaMW0Wx+KydylhtRdcH7yse4VzTb5+/wCZyO/szV+m05h9czvhZCWRwcXBpcffx8KxJ11MQkJRCjpSBgAE4Apf08m/ZI/3jVc9HTvsUnwaNNcgy20lTkR9KBxUpsgCinS0n8fdN6+uHk/ZW+162dkTmmZcdpttw7JWkn1Ty99XZKgQMdKxPdwH860zR139JW4IeV84Y9VX7w5H/wB0qhX0jYwHsHCLaTqD5nGOU3PhWBXWszvnlPei3WTHt0KO/HaXsJdWtWVkcTu5Zru+UjURs9mMdhYTMl5QgjihP0lfDxrEuVB3uI4C0AC0P/6xcv8ADIn31Ux3ypT3kKQ7aoakqBBSVKwR0qmNWm5PNodZt0tbaxtJUlhRBHLfinehbt/hc3/rr/KmZOXV2PRNsvYLmnnixKxk22Svf/sXwPcai2C4y9L6gbefacaKDsSGlpIJQeO73ioQst3BBFsnZHD5Bf5VYI0q6yWEQ9RWOdPjJ3Ie7BYfa7lY39xqLbubjgovBqjsNqf1NPH8raIshqTHafYUFtOJCkqHAg8K9hVX0Mw7DtxjJdddhoPzcvtqbdQDxQtJHLqOtWgVaaSe6EvADiAeEtNUM8qdRTkxMxjgKY4QhJUrcBzr2qFeG3HbZJba/XU0oJxzOK6BcgJj/S0keFSrtrSSp9bdtCENJOA4pOSr2+wU60auckOiHd0NuNPep2gGMZ6jpVPPv55pzaFLWlKASpRAAHM1o+igEdrfKxg1GpMtyfhdC/W1VruTrG/s87TR6pPCvTTMxyHeYy2+Dig2sdUn+v4VcdTWdVwsjSwnMqMgEDmrdvFUWzf2vC/10/jTIphPTkO7gKWendTVbS3sTcLga1uT101LOcfO5lxTDaeSUpJH5nxpNH2NV/vbMYj5uj15CuiB7ep4VD1Bk3+5gDJ88dwOvrmtb0dpty0aTfTs7NxmMqUvdvSSk7KfDP8AMmsxa7lsgeFW9ReUeRHkKhaebabjsHsw8tG1tY3eqOAG6k055TZnnSGL6ltbLhx27aNlSPaRwIrO1IU2pSFpKVJOyoHjkcaaQSMAEnkAMk1zI3XbL6dCgQMEHPMUpqHaGnGLXDaf/aoZQlefrBIzU2pk1Jj2UUtFdSRRRRSSRSFII30tFJJVa8aPhzpCnmHFRnFHKglOUnwr0smk4lufS+6tUh5O9JUAEpPUDrVkIoAxU/UzYYZcKp0NPubmIuk2BjhWe3i0+jdUxHGk4jvvpUnHBKs7xWiVDn29qalAdG9DgWlXMEHNcgmMRNuxSq6YTtHuDdZbpTT3pjW1zmSG8w4cxxRyMhbm2dkfH+XWtcAGN1Q7VbWbWy41HSPlXVvLVzUpRJJqdVcCytql6k8n1tvUpUtl1cOSve4ptIUlZ6lPXupNOeTu22eWmVIdcmvoOWytIShB646+NXWiliL3XbpBwpaKKcuIooopJL//2Q==</t>
+        </is>
+      </c>
       <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
@@ -31400,8 +31736,16 @@
           <t>IAF Top 50 2025</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>https://conservative.org</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAARVBMVEVHcEz////////////++/v//////////v7////////////wAeT////wAADlAQL95OTkQ0Tvhof3ycrwpabiJynmXmDodHX4/9KrAAAAC3RSTlMAD7G49CWF/tRPkZiZXXMAAAgKSURBVHictVuLeqsgDK4WRfvhpdb2/R91BFAJCiTq2Nl2tin5yZ0EHo8To6rati6fTSOElEI0zbOs27YqzszFJ65JN0IqJfXQX5WCL/A/0WgY1b8SL9pa094oS4sCvikHSTR1+0+cKNpXIzdaysCwwxFfvjWvf8BQ1Y1dt1Qr3f1Y/iSb+lZZFG2pLK+zw0oFRnkfG9qnmzNP36Gw49neQ75ZNI1K30kKtOE6hKrMUI+yxupkeVEXauEMPU4/yQilRH2BvOV+mvlSCRGBYU31ghxeQmVFryl8PikWAcLXKfKVczvpoR8Y36nHjAI1JzShFYpAH56ZxyHtnfQsgi2GmkLdjKnvh4yWAAaeLhZPmt+DZ95d/8mANYt5Mhyjpk9cv17ar+vG3NNGEegItPoR3Z6mP/Rd16u8n9YPNEQEdPqwtAkATPkXACHNGIqGHnb0gz8NoPuRJKZjA4EHRaNk0rEEAIB+9xUUgyUhKEpG4NNUBwMAZEBKFlSZQ1Bywq4m+u4MgA8xWdEI0vRrXtiX6msAdF+i3ujpkx6pJfqfZTY1zBZAL2jvgX9JeOVKMPIumE5OvQNAUwKDQMSNkWGAlr56OwBEQzQvySZG/8USgFmMkwDBG3tvyUh+oAMwa6xGCGOe6M4jFpwb6iJWAPKzAuhyEREhOBRCzSNvk6GVfvfj7BvUgS1WBG8ajmHeAMzprCSAfmAJJZsBSnkSoBuiRbBziC3LAOwkzg9zDdHurUM9fHIB6OeH0Qcwczig86OQAWwNsMnQJgKGGRgLQiyAIMymj1Sgg9SY5UZRYG7JSbgPYPYlQMlJvLeDoFRyNdDg9RnQkTIChMAzhIptAiDEyQfAcMXrBJsvqM+ooPr5DCAHIw/A6g6Lhu8EtTP7+iqY3KBGZlgz1JZT/1leV1NoA9wJNjV8nWAA9sPdfGYJS16gJcClDxJEEmB5oRWBk0HLfxcAIAlwItEGwMkgSMW3UmNqYBUYhxOLWNOCJtAfCv3ACN9MJ7AAaI4yEaJTGrEETgGweUkYCPWP7987N35IBU7RX0JirUIAahr7vkt/+KNn5CKIktmnHUZi8cUk0uOUDVgEOibvvIBtSHwYCObhFHmgpT1BtdtWmkqCmOgI+HFgoQRaeOCGbIli8nPuMTHYkdgn1EbSYUA1jCsTxmlIDH46tQJQLRjBMTaddG62Nn+SDuoUeWV9YRmtteux7r61qQ0Kdcr8R0/rIGxQohsC89vNGPpxIlWvmQiej0RVMlDF/iMUpYLPAaCjQRiKED4oAWxO34nhpMrHAKSqS7bQvnnF3kSdGxFIJZIAnNA3VdTJp7iXBeKRr/SjQkg/Djci0DM9MrNZmfuVCJP/XbD9EIDIFvrhn+cVrRjuQqB1gNBqwF5xcQk3CAKUkJCTmyeErwjGJVwmb3ZHKT/gPQcoUEXoe4c1mKrpkypNHKC1SzB6cA2DVE9qg8DuBUafCT9F6FVl6OtgRK1PGlrST4aNLl7kgM5KW0aN1y+PGwjsPfFuxpa1Mwy84j0A9klp8g20J6Q2auLT6aSUtznXu6bAKV8DoNPy4slqUgxeWQDS4WvDFAsZjbIDCVzhgGuhMaq0QXX09IZknc5sThmNAtyi4BZn99Mp2zag98qWVrEDgOnHkvYUgGYpU1Lp+9XRnQ1w05S1i0ruVeDCDN6Uy+VEIQtAyyuUYhX4osIUABAfJoSlVPoiH1jxA7JXmJLm8zP338HygbSctVBJDQfYCL3ClE0M4G/9PJGVUW6lWuKhDWlOzKxucFuo9LJWm7HSlGo7TkGzA79T6zfJgN5mHUYMBHuQ/tmmisYB3w9vXijMU8A+KcvxGxaPkpCVLCdmnASEx4BvWLbLbxxwy4akhqhL5TUoYAcdInAbhyR91LQq8qmpRH1CfHRJ7qp6/UdmmIDbdgRvCEa4EYDy+PqCDDYNVgxDyhzl7ihJ9vgW9sM/X2lsyj5jBJCuRAHAGUdMP8sC3CoOi7O+J9geSgLYHaLING9xiyIsjxsehAXmVM68b9/nsmO0JTgujwebhkRDf8lE8AjL9jsAnhEeHd8LNw3xrD12nKpJeCPg8Db58SlWGTjrWDtX/+r4JFGbKJbgSPg7tDAZqmJk3xA/Y/uKG65cj63ZiaMFZqSK72OcsYNMKWfgFyz7dyznMImJpwj9waHvAxfgW0IEgW+EtkoW4xQKmgeJe/owm92kHHPXrauf03VC5BX3PfXMcT57kuBIb6SwEiDUKW2B2cINTxVImT1iXUZY4M6OfvMJl1mBq+rNWAaw/syRzuPAvBihDrI2Ac4MeODd7wwRoGcPtZp6QYjBGWFPrU+aZwxkTwlMvk45WFztjvVJ64dnRstkUcVx2OhLRaK/3GzAC5p6o36Mnbz+1JnaFjUAO/WeQ9FgSiYS/lj0XXn3uygBmf8OQRkAEONbEZRvh0ADd0Ij6Z+H4Ol3p7Rdf/gFeteDdjdFJON6gRk1RnCmKCuXDzMV+7pRK9Z9rq3Scuk74Hb5/EsugTGcrAUtyz9zzecBF52uF+QBwcmLTg971Yu82T5eP1Sirly5s5fdTgPQn5cuuz22634nyBsFuHrd77HIgRSE0OIB+A0XHg2EUjKLgPb58h7yD3Pp1QEglZLMlzsvvcKAa7/KQkjtnxzv7772awZcfFbuyIjELTv3K+Vy0n+5+OwwmKvfyjlo56PXNA2o/+PVbzfc5XfpgpWDYPz9/19+d6Mo3PV/Ya//iyvX//8Ag2lMF0Aj7LMAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
@@ -31444,8 +31788,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>https://manhattan.institute</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAIVBMVEVHcEwsSNwsSNwsSNwsSNwsSNwsSNwsSNwsSNwsSNwsSNy5XGudAAAACnRSTlMAK0aF7PW9yxJjeSehKgAAAidJREFUeJztmlFvgzAMhElIStL//4NXBGwTPTuZtLu++NQ3g/NJXJNz6bKEQqFQKBQKhUKhTytBtaPYcHWiOLtQWh4FaT1uWlGtPo5ihncWgyDBi1+9tifSBQCLF0BFxWoAdNiqrjIA3KpmGQBepzQVQCu4lQwAX7yvIwLAHnx2GcADdipZBdAwwJZUABkuU18eFAF0/CXYl9EAwEa1dBWAYwENQMKr7BbQAGTDAjKAjvfB3QISgIb77NuQCMDxoATA86AEwPLgogIw0lBXAbgelADgNbamAsAWuNK9AMBOQyIA3OWZZQBmIhcBGIl8c/H+EyDBJtcSAgDfgwIAcyoUAbhHoQIgmVOhCMCeCkUA7lGoADAskFUAVhpKKgAvkUsAjET+7UE6gJGGugpgtA3RAdxErgBwE7kAoGEP/mxDdAA3kQsA0tCDbIDBUUgHMCzwy4NkAD+RCwCMH0iTCsCfCgUA2IPXVCgAGCRyPsCEB7kAhgebCsB+TyMCGCVyOoBhgS4DmNiGqADWNiQDMI7CtakAhomcDTCaCtkA40ROBhhOhWyA4VTIBsDvCu8W4AFMJHIuwEQiJwMMp0IygPO6WAMwtw3xAGY9SAOwPHi3AA/AiGP39WkAc0chEWAmkVMBpuIYEcDYht49yAKYSuRMgJmp8HxWf/5DYzkB8F8Uz6e8Vlh89+CScwef68sMi2eXhm89nnLuSPndAqFQKBQKhUKh0Mf1BQcSGEF9do50AAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J55" s="6" t="inlineStr"/>
       <c r="K55" s="6" t="inlineStr">
         <is>
@@ -31504,8 +31856,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>https://city-journal.org</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAKlBMVEVHcEwAr88Ar88Ar88Ar88Ar88Ar88Ar88Ar88Ar88Ar88Ar88Ar88Ar89UYvUaAAAADXRSTlMA+j3YHFK3MAya6HbJe7RNewAABDJJREFUeJztm+uW8yoIhqvRqDnc/+3utJNIDgi0q2+/tfYKnR8zE4pPlKggeTxuueWWW2655f8gOXgfo08hG/XTS3xK6hdyiqv4poofS98Ni0x9Gb2FwU/dn/RJUw1lGLrXpzSaj6Ub5nl2y2d2buhKk3QH4NYvdKpy6uZVeIAwDvNJulHthCfAn64KEDf7LrLtl3PzT9USvgcwblYHbrTY9hcCrQ/sALm2MHF3de3/lZbtrk8AwlRdgLmp0PPt89ofAaR6iyNzNVIHLI9gPzn6UzZsB4ibJueDND5zF0POYQfE8X4CsDXhOsYHcx2f7aqvBP2XAOog94wP1vFx2/1Sn3SiE5gBcm2C86pqhka8DsIgTgVmgFRdgPXB7epUx8dvE6cTJ3krQI7kZBIAjc82c7vvADxoGuLsMQDf7oHqg+zsLvTAlwDIHDu54wGUpRAPMMp6cABlKcQD0GLHL25wgPpMNZYWOADNq/z+Ag2Qqw+y2zE8AG34Jn5pgwPQdoxXQE/Fmg+yPVCmVb4AUF3ANbQYgEdeRWreCEDTUGtzwQHYxAawTUNuamiAAZLmg2gAf9ly/hiAosKWEhhAWQrhABR19K1nCgsgR4U/ABCjwl8AVB9s62ABxKjwBwCZklPNeR0KIEeFPwCoUaGQ7oECkA+2F3YkQDb4IBQg1K2VkO9CAtCOXMg2IQFoRy6kHJEA5Zp9+SkARYXNpRALQPFFazsGBlAyE3gALSpEA2iZCTjALjMhmcEBqFEhGoDS7uLJBwwgU0ggWoYBqJkJOIAaFYIBvB4SYAEoJFAyuSgAOneRDaMAsmkpBAIEcoF/A1CvikshEEDPTIAB5IMiPABlJrQyABDA7jxUSTeCAKpZrQgABWDITEABaDummjUChComALlmQgW4NvYYt6IhMigB6AlSCSBNwyr0CI/XO5IATFFhG4A5sKgWTQB0UCRkJpAAwZKZQALoSXowwBs+iAEgH9SL4hAA2bodQwHsfFBtHwKQbFEhDsAYFeIA6LBSnYYgAJlqxwy1qQAAa1QIAzAcFH0O4CjOYYrAThe0kKBlhju+H6+cdYU+LziWJD2JsZouXtXqdHfe9LyxFD4OMdz6H7aeMF1qAn1r421K0u/UqaLSnzrA7SZSCjRcSflZ+Vlnu/Omx3JQtBeqKZ1iCiGN1fLBievALqR9KRNVnp5Ly7eDIqdvx443LFfVJvr/vPuVCX3MUeEqx7rive3jEPL110wztWbCGmkYK6tpm3WQy7MexBJWTnJxrOVz11Lq9aB1NkfPtc0Hn8wcwXCNalN/1nPdtRF7VLgjuIyCY98vCGM/7BiGiXkPIpdue/HijWDz+YaFZvklKZb+L0h7vgnCvVySk19Ff/Xk+L1Y/gqoFsNR+G4O6dWE9C5Mfv28Lcv0tsxDIWgVVLfccsstt9zCyX8KZ6vMOXxcKwAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J56" s="6" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr">
         <is>
@@ -31564,8 +31924,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>https://heritage.org</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAEwAAABMCAMAAADwSaEZAAAAbFBMVEUAQnf///9Bcppgiavm7fIFRnr7/P3x9fgnX4wgWojY4uoISHvp7/MdV4bt8vYVUoJTgKPO2+WIp8C2ydjd5u0vZZCov9Get8zH1uFtk7JLep90mbWPrMS+z902apQQToCCo7ykvM9Id55xlrRngZr1AAACeklEQVRYhe3Y25KjIBAGYEYU4xmNMRqNMZn3f8ftNhNzwEDD5mJra/6rqRryidACyr4+GPaL/TOY32fMPgUvV7CQBw4WxKtV7Jy4WYz1Kta5WuyQKxh3xjz//8ACzAewIBvltG+2zb7qvM3pb7BCDm24tBDxudu5YlH3IP149eAp9UjATrwUiyGWP7/84bV3Zmxsrr0K423VyYPkU1OmMylKnlhhAY+vozTI7DaPQXGZ2pnLq8ICS7p0pvrNS0VEfObEPiNjSY9PWz5sXocaUvS4SIjmoW96jKMV8zfLiHdEbbjXnBa74D9Lb52CbLY4MfdVRodleOX4vQUatqhHCtbDEKdSY0Hd4FyfbzeqwXbYsDIs4RyKML9dUINNOGBr8/iYUwOtmpMJi2CzEZPBYkxi1zwTxmHEYlPHoGst/GQwYMEZGxE2PdySykKPRTD84mC22AhCftBjOBaEu4THCit30mPTwyzpUy0tVzHYNYpmuZ4p8z14WRRlMlWwcgs55g/FqM8GVg/h1xBfKNiSem3TUJO0yi9XsJI0ZCzYU7CGeLTqKdhAs5gUBIx6tvIIGKn+MTvfjIWj2ZkTKdOpYqSHCXPamrEj9cyt1oaKnWllxlZqQ8UqqnU/GL/FBP3UvatNWEqtDJiB0oTV1MmEGXidTgU7WryoVCaM+mRiuNBjwuZ1YMz1mE9bGa/JWj1G20xuqbRYaPdud0l1WGv3Mpw0Giy0fRt77toztrcaMUhQiXdYbDOV10THN5hP232fc6lXsdTt84H0V7D82+3zQcBTBfM7x88aoL2egmrpaoEm62fs25nC8PAJc/92gPk57v1i7thH8ovZ5w9ieSFyCqIqtAAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J57" s="6" t="inlineStr"/>
       <c r="K57" s="6" t="inlineStr">
         <is>
@@ -31624,8 +31992,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>https://liberty.edu</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAkFBMVEUKFzP///8AACPm5+nc3uIAABgAACgAABYFFDFpcIAAEjAAACYACSwAACEAAB0ADS74+fpXX3Hv8PIAACuxtbzS1Nh0eoiNkJm7vcJobHgADTKFiZUaJT7MztIiLkeUl5+lqLA1PlMKHTwAFTdKUGESHjk+RlkuNEgAAC9UWWcAAA59gIman6kAAABdY3EtOVETf/rlAAADZUlEQVR4nO2YbXeiMBCFFTDGJIAgChZfsK221Fb//79bRVtvRGnPZsnunjPPRzg6l2FyZ5hOhyAIgiAIgiAIgiAI4h9H9ms43Gb83K2RzCwqcObdGomyF18s3LqApbQngM+iYjzU48eRxQx0uHIeJp4mwF0IiwKOGuRKU+D5duMfcCYooHCsCxCPKGDArAvgAQqwXQJHAU94CIRNIzyhIhCQ2TyEZ5x3tKGRfQE++vHEfg1qfuw+h9YFqDK+CBj/hUMgc6xB+zbUGRVYg6dWKJ0ap+Jk9RumKePrDAScWmEwrs8plUWHRe16vDFUIF5wJng92pDuzWfyQ244j2vX4xdDAeEG/s3tHy+pwQ0B00NuxKp+fb42tE6GvbCoerHYT7LrUck9ZprPBsn1jcLUOn2swbMNCRbsC31SmlejKmfBYqnfSE2dq4ePVH49TjjKtTjJp0ULqY0P8c4wA2IND+StLgXF37RBKf0aVTnDY+OZOpeKQECGBeWkEGcIoyrD3IxNZ2itFRb4b1p1xk8cboDmd1Pr1PKZowDNor0AfrKFG6ZDvFhAL461VugnEAcflOG7eTB0gfAZezFDPvB4YK0zeGvxm1n8DptCFHc3QOBOF/yWC3hrWdDw5z9BYjrv48EXs1hDQ8hND0GQ3Y8KJDAraw1hamrE/Xp7u8US/JbBuzGe4LRPgvsMcVTF0zE3XWZonwT30R5UgkVnpp3IKe5HBcZw2sXmT9agvLGiuQGOqmjEw9KwBMTCawh7AUuAQdKwQ/wWavezQ7AHG8IZ1uuZxT+k0/uOKhDYnViBQ5svM1ivmf5H9aD9yy/UDjKza/1D8jSgo+Fr3r1p90NSMMkqAXMQ0IOyNR7HmmGzbVFUrudeeq72FZG0uk1hkft14B8/n5RLnFKMJ/Im1AAGv0SdFThbuOq2WQLa1NEdLgOpQsX6mm+M20wAn+ke6W3L53KgDw+tbhT5utYlrpba3Vi2WYI8TK4FXJO2u9bXhv9btL1N+rZRRm3bMGselvL2t/pB08T+bmGlzMPJ3WkhFTbWidxZZddn71R/U9/SSj3slPXT6OYLewttrpzXKPHcuMrEMHa9YuMzu9tcrvyH1W6Sp2k+Lfcj3/4y+9iZFJNSMhba32QTBEEQBEEQBEEQBEH8//wC0dAw6CwLtFkAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J58" s="6" t="inlineStr"/>
       <c r="K58" s="6" t="inlineStr">
         <is>
@@ -31684,8 +32060,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>https://yu.edu</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBIgACEQEDEQH/xAAbAAACAwEBAQAAAAAAAAAAAAAABQQGBwMCAf/EAEkQAAEDAwEEBQgGBgYLAAAAAAECAwQABRESBiExQRMUIlFhBxUyQnGBkaEjNFJiscEXJDNUgpIWU3Ky0eE1VWNkk5SiwtLi8P/EABkBAAMBAQEAAAAAAAAAAAAAAAACAwEEBf/EACIRAAICAwACAgMBAAAAAAAAAAABAhEDEiExQSJRBGFxE//aAAwDAQACEQMRAD8Aq9FFFeweYFFHw9lTolmuk3Bi26U4nvDRA+PCsbS8gukGinn9GZDIzcZ1ugj7L0kFXwTk186ps9G+sXSVMUPUix9A/mUfypd0bqxJX1IKjhAKj3DfVkjqiFKXLZss6+kkJS/KdW4nJOBwwnj402aj7Ul7qyFwLP2NfRtJbQdOSNXZyrAxv37s1jyUMoFEIIVpIIV3Eb6KuIm3F5TLbk+23NtyOXv1uOnjnToyQDkncDmody6jDf6G9bNuwniMhUaSpII7wFZBFG/6BxK1RTswbBIP6veH4qj6k2MTj+JJP4Uf0Zlu5NvkwZ2PVjyUlX8qsGm3QurElFTJdquEP63Bks+K2iB8ah0xlMKKKKAHMG2W42lNxuUx9CFPlkNMNBSiQAeJOBur6bhY4/1WyuSFD15kk7/4UAD50Q/p9k7k0eMaSzIHsIUg/iKS4NTStuxm6ou0coiXmau2NNxjLtIkxQhAPRqCAo6c+xVQ2WXrzHjuSb7OkuSULSlpKVEIdSAdJycYIPEV2t76Eu7LTnVJDeh2G6oncACRv9y/lXOGyqzxnGDtFCiZd16oqlOuAYxjsjG8Y58qkUJa2LVbdLcSAqSzIdbYeblyMJJUkLQvIG4DtVyuUuwq2aejxugakrWvRhrUohCzpB7iUn0vDBpc21YnnAls3q6vYHZbSlAOPbqNOodnuroT5s2OiMD+snkuH/qI/Cji6w6+ITWy6ra2f6rEW+5M6VbYYQpSk6FaVFRTzOQQKbQ3NoETOvRbIhohx5bTkshAbDhBI7RHcfiafMbLbWSEBMi8x4DX9XCb04+AFSWfJpAWrXc7lPmr++5gfmfnSyyQHUJGcztn730i5LtucIWsrJjgLTvOd2kmuEmSJDluizlPMNx0dG4pYJUMqKlHB9vDwrTXfJrDaUV2u7XCEvlpcyB8MH51Fk7L7WMI0tXSHcmxwbmthRP8wP40yzxYrxS+hMxOYvk1tWi0yAhxxBRLAaUWSoBGDuyoBJPvqLb7PZbst9LEeW2qMVBwx1a8dtWkgEb+yOXhXabZrg3nzpscy4ObtvWUH4AqHypWg2mE8roZl7sz5GFBaQoew6dJPwrV44wdrye5q5VnYU5adoJLoRIDBZKiN+nOcZKSAcip1wDB2gu8mZFYkJt8BALa04St0hIycY35UeHdSy3WGI7PjLj3u3PMJdQXAtSml6QRncoVMDhmR7rJS2p7zndW2UoT6S0pJWQPdih0Kuizruz8n6zaZERX2ocjUP5Vj8653W2Qo9uj3C3zHXmX3VNhDzOhSSkAngTniKlXfZeXFS7MZQERAjpi284kOsj7Kk8c8q4Xv6Gz2KJ/uypCva4s/kkU6q1TMa+0Gy46Z25Q/wB5gugD7yQFj+7UmyW+0tpjTp09pxxSC43CVlGpYOAFr4JG6luzkoQr9AfPopeSFf2TuPyNeJ1skM3OXEZYdcLL6m+wgq5nHDwFDXaMXgc3BpXmO6svNoQuHPRIDbatSQh1OMAjiOG+tOsuy2zqIceTGtkdXSNpWFLBWd48c1mNntk2MqRb7hHdY85wXAylwYJU3hadx/s/OtL8nM7ruyUMk9pkFlQ7tP8AliufNaXGXxdfUWNpptlIQ0hKEjkkYFIZl2dibYRIDzyExJEVSglQA+kB7/ZTqcXxEeMRCFv6D0aVqwCrG7J5Vi097Epzrz1rRISopWXEuSVhQPDtZFSxQ3spknqjbkKSsakqCgeBBzXqsx2d2vi2G3J69KkTWn1K6BDEVDSWgncoAAjvBpr+lCy/u80/wJ/xrHhnfEassa6y815cWhAytSUjvJxVH/SjZP3eb/w0/wCNJtqNqY99htvRJjsSKhzo1syIaHUuLxqB58APnRHDO+ox5Y1wuVjuz1x2ivUcPIXEiFtDQSB6RB1b6eusNPo0vtIcT3LSCKxmzOu+cGRaXLW7LWoaA10kZSyN+MDA+VbOyVlpBdSErKRqAOQDzrcsNGGOWyKptbs3s+1ZZ05y2MIcZZUpKm8o7WN3DHPFZ043MYslmbgnQ+229NWoKCdAUrSDk+A+daB5VJamdnExW/2kyQhoDvG8/kPjVHul4TarvcIrLSHVNMMxGtbYWgBAGoKB7zmrYdnEllqyqBTi1qIUouOblHO9WTwPfvpxtepIvi46DlMRpuOMfcSAfnmpdrlR7zerWyLbGiKRILr62ElIWlI1cOXomkM6QqZOkylek88tZ95JrpTuRB+Dhkjhxq4TrqYc1ya2++wi7QmXg5HOFBxO5Q9hIIPtqn0+CUXDZeP0iiDb5fRuEcQ07vz7lA/Gsml7CLfo9J2j6S6Q5So4b6KYZCvpFL3KwFAE8BgVe/J0sW+8XyyKV2UPdOz4pPd7tNVSRY7XboakTxoVIcdDTr7vaS0hPZWkJ3EqURy4fGu9quoiXGw38q+jcb6jMOeCk7sn+EpPuqORKUaRWDp2zYawLbaP1bay5tYwC9rH8QB/Ot9HCsY8q0fodqi6B+3YQo+0bvyqP4r+ZX8hfErpHSbPj7TMs/BaB+aKdvSrIxIjJNttz2p0svKQ6sJCex2+Pir4UkhYXabm2TvAadHuVp/7qsb+0kFuZFDAjusBhQkrMJIBXp3AAjOMjPvNdcl2jnRzjeYegStyPDUHFJYIL6gpPaWC5jPcEn30hkdiyQUZ9N51w+ONKQfkafP3q2dBFSkx3FlpTT36nhQT0eN5xvJWEnI4UgumW2Lcx9iKlRHisqV+BFEE7CTHXk0jB/bCISMhlK3D/KQPma28Vk3kejhd4nSMfsmAkfxH/KtWdcQ0hTjiglCRqUo8ABXH+S7mdODkDPttJDczbW2xHCCxb2lS3u4Y7W/+UfGqM3dra+2U3S1rfcW6t1Uhp/Q5lRzwxg48aYzbj1mJeb66Faro+IjA4ENDBXj3BI99SHDs9ML6m223vo1KW5jq/V0BJwEp4uLzxO+uiK1SRGTt2L4HUovnq4W7perMRAywp70tbuEn3+lVbp3M/UtlYMY7nJzypLnghPZSP7xpJVoe2SkFONmHWzMdt8hWli4tGOpR4JUd6Fe5WKT0AkHKdx7+6mkrVGJ0NYOz9ynSHWGWUp6Fzo33HFhCWyCeOeHOnESDHQp+wplJkMTEhAe0lKW5aOW8cDw9hFeX5EaW0xepLKpEZ4Bm5MIWUnp0jsLOPtcfjSu8bQz7sejd6NpjWFpZaQEhKuRzxKvHO+pfKRTiNW8nt8Vc7P1WXlM6F9E8lXHA4H8vaKrflXYjSLjBzOisOoaUFpdUdWCcg4APjSxi5SYE1vaNpsplsKEe7RsYJ5a8eOPcoeNaLJt9v2kiRp0d4oCwCl9lKNSh9kkg1zNf5z29Fk94amR2mHEDrjKZMqR1losnq0NSgM4wcqI4EA8Ktn6Jz/rcf8v/AO1NtiLahcy5KmvyZEmBOU02XHVaQkAYOkHBO+rxRkzSTpMIYotdMvd8lRbbUvztnAJwmNvPs7VVK6R4cmUp3rMiL2UICJcVSMBKQkb0lXdW+GqJtLZ2v6TWiJBflRhNU6uQG3lEEJAO4HIG/wDGjHnlfyYTxJLhH8krLEZq4pTMjPvLUg4ZUSQkZ45A5k1O8pF0e6uzYbd2p1wISRn0W878+3HwzTZaLbsjaZE11WrSO04oJDjh5JyAM76zxlc+bJVcHP8ATN3yiIn93Y5r8N24e80R+c9wl8YanRi0w7zKTEQXHoEDERhEdxKVrUTlx7ed6c93hSB/Z7RcIsBqc1JkSHtASyFYQjPpEkDx3DuNeZtmehPdLBU6lKG1PJDh6N9tKTgkp4jvHhU/r8pu2P3qc8pc+a31SISe0hAGFr/LPeTXQrXhkePyhXtJMbmXZ3q31VhIjsAfYQMA+/effSuiirJUqJt2wooorTBpYZ7MR9yPOybfLT0clI9UcljxScH41PLiNmS811Nty6pcyzKX20dERlK0p4ZPfVcqwW1ab7CRaJCwJzH1B5R9Ic2lH8KnJex4vlHOyzbm7cZU4IXO0skzUOHPSs5AOf8A7lVo2avSdl5baOlU9s7PVqjvHiyrmD3EHcfjVbizLdAsLkB9MwTHn8yUNJSjsp3JRqOcDmd1cYd5jNvyGHoem0yiOljJXqLRA9NBPBQ+fCklHa+cGjLVrpvLIZ3uMpRhztFaAO14+NdqzDZvaF3Zp1iFcX+s2WQMw5w3hI7j3eI5eytLbcS42lbagpCgClQ3giuGcHFnXCSkjpUeUuPHQqVJKEJZSVFxXqjnvr1KkNRWFvyHEttNjUpajgAVl+0F8XtUp1RdXD2ciq+ldxhchXJIHM9w5cTRCDk/0E5qJxvd3G0sxVwmhaLDBXoZZHpS3DwAHju9gqt3lUiYjzt06umW4WXm2wUdWI9BA8MZHuNSrw9cAzb7rHbRHgtkphtNkKDAHDV985zk14Rf7ldW3Lc5FizHpmEBYZCXSrOQcpxvz313RVLng5JO2doE+Zf2+oynEBDadcqepI6RMdO/SVcSM8O/dSm93HzlNLjSOiitpDcZrk22OA9vM+2pl4fZt0PzJAcDgCguZIRwecHqj7ifmaR08V7Ek/QUUUVQUKKKKACjJGCCd3caKKALGrRtO0FDAvjSe0DuExA7v9oO7nU20+Z49tuM5m3rUqI2AhyYQsl1QwE6fVwrJzg5xyqotrW24lxtRStBylQOCD31YkuNbSoKekRHvKgAo50tzccM8gvd76lKNfwomhdabqYSHI0prrNveOXo5ODn7ST6qh31bbFfJOzLIeiuKuezy1cv2kYn1VD1T8jyqlMWyfImqhMxHlSknCmtJBT7e6n0GRG2XWsNyETbi4nQppC/1ZoHjrPrn5VmSMXw2MpJ2Mr5dn7+hM++rXCsaTmPEQfpZKh3f+XAcq5eablektqk28twS2UQm47qSiMT6yk5yo8M899QLhEdkz3YlzeEi4SWkORJgV9GrdkISOGDwB76W2V6Q50ltTFXLL29plJKS279oEbx4/OlSpcBu306252fYrm/b3oheLmWXoSxqDyt+nd7d4IqRKeb2eYdixloVd30kSX2vRjJPFtH3u8+6vsma3YkLZiSBLu6k6HZurUGBzQ2eZ5FXwquHecnieJ76olt1it1w9IQVqCU8fbXt5hbONeDyyDXlpeheSMgjBGcbq6ypHTJIAOSd5Pv5e+nEI9FFFaAUUUUAFFFFABQDjeCQfCiigCzw9ojOty7Vd5TrKVYCZzQyrdwDgG9afmKTXO0yrWtAfSlTK97T7Zy24O8Hn7Kg0xtl5lW9C2MNyIjnpxZCdTavHHI+IqeuvYjbXxjSwPXORBShIjNw4iipE6Uj6rnjoPM8wBnfUWVdo8OMuDYQtDTg0vTF7nZA7vup8B76h3O7SrmpAfUlDDe5qO0nS22PBP51AoUPbBy+goooqgoUUUUAFFFFAH/2Q==</t>
+        </is>
+      </c>
       <c r="J59" s="6" t="inlineStr"/>
       <c r="K59" s="6" t="inlineStr">
         <is>
@@ -31744,8 +32128,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>https://nationalconservatism.org</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAXVBMVEVHcEwNHUENHUHUYysNHUENHUENHUENHUENHUENHUEEGEENHkUCEDwAAi9XMjk0K0EdHji+XDEAAA/Aw8nW2NyqrbWcTzRBQ1VYWWZ2QDiYmqJnanN/gIdzdn6KjJXBMNFhAAAACnRSTlMAs///kcpHJmzp6Ta52wAACOBJREFUeJzVW4mWqjoQHHFGMYuJAQTX///MV9UJq86dTeW8PkfBbF2p7nQW4e3tfyrr9WqV5+8ieb5ardcv1L3KFx+bjdZZho+O183mY5Gvno9ivXr/gMLPRH+8PxPEOl9s/qE9yWaRPwUDtH+pu5PHY1i/b76vPtrikRCo/mvuJ7J5GITVD7gfy2L1APU/Jf/RLOR/UC8Q8j+pX338TT3l4w92+Gv3o/yahPUDuh/l41eekD9MPxD8goTH0N+K/imC9fsj1VN+NiDXv449n8viBwge535D+b4rPmL03xH93YjwnP4Lgm9x8DT930TwDP/rEXzDEx8+/sby/pX+/Ln6s+yLiPTY+HdH1L+npic6YCf/dMQX6AeCGR0gyqdGWD3bAZJsPouILzEA5RMjvMgAlLtGWL/IAJTNvZHw5BA4ljsB8VUeGOWOHz5zDrojixsPeK3+LJt6wUs9gDLxglcOgSiTgfByAiYUvJ6ACQUvDIKt6NFm6cVjMMpgJL58DEZZz2kBSj6vBQY2uDMG5AS4P5rjcbB86dvTuq9SWOf+GV83Dla6LdpfVNKl22RpR4CoeEiNq9aplCSlY2tU7ZG0LUuRG2lnpD4KqdTGoGKW+TavRTfG2x2Z9ymDvIhC3aegjUWTpZiQL1V04j39VHLRA/vE/ERQax/VpQ67cQ9CWpqt+zzRBdGeGIQ1/jZKqI/CdHwilJgkarNYLqb1eZoUtoUmoqMTrAbqlXZbCEzhcfG8SoKT30mcYhqa1cZvD4fD1hkolAKsIRevVarIlqXNOwhWt1FAHZbL3XKr1BZXh5743RJyUH6/bGVv9pKpzEEyl7uDgb5YTrECtGmzj2XRMbOLNzeST6OAEgAorXQCQCBM0PcAsOwuAVRbuUGVCEBF5EuaJQK44wWLWx+MANCgAAB4/N7veAuyiYGUJwDEtnNeNG8jA+xoBCAVJUN/DuDjNgyJCaDQRwa0RV0SjS4atrl06FIEIN8wlgDZk4Gd6E4MIHebqP8UgISiWwB71N27yDIvogn1hR2A0okB6mUVkr2zhEHUEYB2vByExi8ArPQNALIpAKSve2k7i6zSyImBTDqeACwtuysOGAFsqdMvozk+A6BXEwCxl9JlMbx41G4vtlctA1liwEQGlO4ZoOH2AkCKSEU4dA9A3wEwGIWMMATAJnedn0XZmd4EKgJgxzHOow8Ycu5VHCtbbfqKXkUAKSyNJJ+EAS0A9j6OBQA4SD/YKbrbofXqfZuJsqI5jQIEoAgggtoLBVujpP72cBuN8vGCWEeagZnUc4gRehb9/KAnJlCZdHcYB3wss4wDVcXEveno2E0A6PebFXkEEOPazm2j8TMfqRwyQPKzLhKmiOVS5Ny6OAA1+770ZtfbcSxjADKBIII7Rk+J7C6FdwnmmcwHMh9LOu3ptvs95gJOgF6KZDIFOC9TRubjrKH6WeTfDMh0q4w1MqfhyilOJvM4nTEYcd7BxRq5GH5MdO84UUoqJU2SljdKPDBr2/qMAfFCa+tTbdF6cKc6oG3lrGQwoISmUSbzNQXtNCyhXFx+aM4c8B6NPIePZ3+saRrLNmSC1sap0bLuxgd0Fq5FURWVVQ7fRVGbLJQXi1jSVJlxzKvtpSxw4wx/lc5ej0Roj1dr6rK2J2SyQMOECxuxqi4bLinspXBqtEKcDkNlqsqHEKyx5RnXU1mbUBY1YklTGVU0yNL2fERWUL6oQ2hK40py6wA2HMuTscgrWaC6hrpwKKgA7IpOZAE9GnmBGgPQGSAGkoT+VDADLyEU18qSAdsUgeABwHL95YtG6VCebHHCcqApvALqikVCCaptdbUn/OTYritU1cBR1eNYlI9CMcYX2oquUwZypjz6UmZlY8mAA8EYEmSAngcARgXkXa9WLAD20XdoBACjCaAuvOWQao7gBynnqlGjlf1kLlA1KUIJ05TSWfSlDqVtSk8fgPHPxmpzrk6XS2NoAnuurDkVBkzUBlSE4gJ2QukjA74qThgv5lQBG6zkqsYMJwSZCwbTMZyFAMAyystKN8DsZRaqo20qn+GrbAJwVFV1tqYsi/LoETqAz4GyugiWV90xoHxTlpkBTGCyl8pWp1Eomq4HIgNZxwD74kKJtWfZNBXn4cAxQSe0VpOBGqrY18CeXspjdS1l4HApAwCscSkNBgpc0lYXAaAnAAZLMkWzyo0SH1DsGBhQcM66EkrYjbOMOylMqmBi2h44jpfLhWo7BqgsFGcOiFPlC2ePYwAfk0WpttdCYo+xVRXggxYDgADQyrFCckZzCgDGXgAARZaeAldQVGAsR0NIvFiDeEntMFhdADoBDH1wMVmWQ2NR1db6BqP/6K09I3AQgMZvjIIGWcWZABhZhS6MAnwd8U1u0IbEg9YENRprYEUYyB7ppsezHQLIxxsTDhhzRBArjghqFcMdBk8ouGUkFzWzrlmMhEVjCYBN0mUAFFoYfI8XGwFgYDIqIjm0xuKI1YN96upmawYreO88V76WV86oXipwdmEWI5qnoIjMS3GHREaieXnPKkjEvXNMRhL6xgHmh5v1tDUbbwx03MbpNG1NNtZpUmxL6jQPyU6xKyfBLw73tAxLO3pJGcSB9n+D4YqgbSLrd7lpR5x1hwXt7negsj/D6E8FukQ9bb2t1m7P+1io+m21HEiotke6PR7RNy2NTxP0cF8+PDC4s0vX7QHFaGui9bTizV1XrlN87xRmvAq/c6f7o8q5D6nmP6ab/aBy9qPaeWwwPKye47h+/Cf23H9YzP+Xzex/Ws3/t93sf1zO/9ft7H9ez//3/ewPMMz/CMf8D7HM/hjP/A8yzf8o1/MfZvvyOetnu4H68gHjuR9ofO4jnd96uPiZjjj3Y7XffbT5SQ82/+BVh6dw8M3HmhOCmR9un//x/rdHx8TfvGcy9yse87/k8jb7az5v87/o9AAS/viq19v8L7u9zf66H+VXLDzuhcffQNCPVS8Q5n3ptcXw9Wu/+lmv/SYMs7743IHoXv3uFL/s1e8eRf/ye/7ql98fK/8BHSPmbNdI4McAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr">
         <is>
@@ -31804,8 +32196,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>https://cufiactionfund.org</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBEQACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAABQYBAwQCB//EADkQAAEEAgADBQYDBQkAAAAAAAEAAgMEBREGEiETMUGRoRQiUWFxgQcVMiM1QuHwJDNDUlNyc6Oy/8QAGQEBAAMBAQAAAAAAAAAAAAAAAAECAwQF/8QAKhEBAAICAAYBAgYDAAAAAAAAAAECAxEEEiExMkETBRQiQlFhcZEkM4H/2gAMAwEAAhEDEQA/APuKAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgxtQCkNqAUgoBA2pDajY5571audWLEMR+D3gK0VtPaNqTkrHedMw3K85/YzxSf7HgpNZjvBF6z7b9qvVc2gypGEBEG0Sh81lH1Z6lCm1r71wkRh591jR+p7teA9VpSm4m09oY3ycsxWPbYzGWCzcuUtmXxc3laPs3WlEXj9E/HOu6r8T5LP4ulf5rXIasTZYLUbG/tgXhpa5pBGxvw+K6MNKWtHRyZsmSkd10oMeynE2SV8z+UEvfrZ8ly27u2njG0Tl2W25rFtgyE0UFiR7ZYWtYQQ1hcNEjY7vVaU5eS3Rlki3yV1KMx35na4ozOPfmbTa9NsTo+Vke/fbvqeX5La/JGGtuXrLGnyWzWrzdIdtqnlasGQl/OLD4RX54XFkfMx42T/AA9R3LKLUtMRppamSsTO0bVt5q/w3j4qdp0mRvx9pLaka0CuzxOgPsB9fgtrVx0yzMx0hlW2S+KIrPWzzX/DXE6Lr1m1and1dKX8uz/XzVp+oZPyxqFY+nY/zzt5m/DHEnrVs24H+Dg4HXopj6jknvBP03H6nTDeFeJ8b+6eJXPaO6OwzY9dp9xgv50R9rxFPC703K8bY/XtmEr32jvfBIGny/ko+Lhr+NtJjLxVY/FXbezjeZnu3OHMpC74Nj5x56CrPCRPjkheOLtHljl1Q8U2rZ1S4dyTz8ZQ2Mebis7cPWvlaF44mbdqpOszK2wHXHRU2/6UB53fd5AHkFlPJHi2rz28kjFCyJumN18euyfuqNNKpak7L8SaYm/TNQeyLfi4HZ9F11jfCzr1LitbXFRv2t4XI7lZ/Edu+DMlyjZ5Wf8Atq6OE/2w5OM18MrDUIdWiI6gsGvJYW8pdFPGEZlv31hP+aU/9TlenhZS/nVA04Ls3HHEPsVxlYhlfn5oe05vdOvEa8V03msYKbjfdy1raeIvyzrslG1r9bFZoZGyLD3te5kgbygt7Mfw76aOwsItWb1mI03mtq0tudqvh7+RpVsXKySOGrBAKXZzEhkkztHZI/yk6+oPd3qua1bZ7Wmem3bgwzXhIrWu7zG/4hZRw7kLZ58vnbbyf8KrqFjfLqfNX+atfGHD8FreVnl/B8DR/Z8ploXeDva3O9Cr/dWnvWFftI10tLmgp8Q14+2xnEUV+tsjls1wT0Oj7zep7ionLgtHWuv4W+DPS0RFv7b6OZ4htQR2IsHFNBK0OY42Oxfr5scDo/cqla4bRvm1/wAaZfnx3mvLE6/dLVZsvMR7TSrVh4n2gyHyDQPVUtFI7Sms3nvCRHd1+6o1egFAypENxBgo8xFC4Sur267+evYYNmN308QfgtcWWccz+ksM2GMkRPuCGTORRBktalNIBrtWzuYHfPl5TrzUaxTO4lMTliOzXHhp7XtbszYZOLMXZCGNvKyJniAe8k9OvyCmckVmOSOyvxTbfNLTj6mdxVdtRj6t+CMcsb5XuikDfAHQIP16Kb2x3netbRSuWka7xDspULTrwvZKSIytYWRQxA8kQP6uveSdDr0VJtEV5atK1nm3ZwYvFZSrxJkMnMKrorwY1zGyO5owwaHh19FpfJScUVj0xpivXLN59pPP2/ZcZK5jBLLJqKKM9z3u6AfTr1+W1zWnp0ehipz3iJ7e1YyWBzVrhh2GMNAjl2JBM/m7QHm5v09/N1Wc1tNdO3BxGDHnjJEy9M4lmvcOYd0T3QW79ltSV+veicCQ/wC/unX12nPusb9luEiua/6RG0xY4eq8/bwz24tMcJWNsP1K0tI67PQjodjqrzSOjlpnnpCv8C4uJ/A9a4ya1HOYJdOZYcGtO3DYbvl9Fnjr+Dbt47L/AJU1nWujxwHemzEFSjZmkdHWoMmk987mfI53Unv0A31UYrc2olP1DDGK03r7nX9M8XusYe4ytTtWYqt+tO7kZIdxSRt5gWk9QCNgju6Kck8vSFeDrXLWbWiN1mP6b/yczcGQ5AXrjL8dMSxzid3ukN3rl3oj6hTrVNqzliOKmmo5d6Wrh64/IYWjcl1zzwNe7XxIWlJ3WJcWekUyWrHaEirMhBjSjQaUhpA0gIILKY3I28xRtw2q7a9RznCF8ZJe4t1snfhs66eKpaJ22xZKVpMT3lN66b8ldh3Uh/BNuZl+KxkIGw27AsxiGEtdXlHXbSSd+GwVjOKZepHH1jlmK9o1P7wm6NHOlrI8llK8kbf1Or1+R0n1JJA+w8lfVtacuTJh3zY6ubCYPJYnEflUNyq6swPETzC7m04kgHrrpvw+CitZiNQnNxFMmT5JhyYThK5hjTmrXYDYrQ+zk9kQ2ePZIDhvoQT0IUVx8vZtn42M24mO87eMhF+d2JhJKxloNfTgPJzRxF2w863sk8veQFNqczHFnjFqIjp7ILrIeGJsTNcjMsVdsTJBA4bYRret9T9D4hTyzy6RfPT5vl103tMcHtkrYqLHzyB0lRjY/wC6LDy66bGz4fAqaxMRqVOIvXJkm9faeVmIgICAgIMICAgaRAiTSAg4n4uq6ExdmWgyGTmY8tcHbJ2COveT5oNEmAx0kQjfWDmggjb3bBDeXv3vu80NuulRhp83Yh3vnbnPeXOd00Nk9e4IOpAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEBAQEH//2Q==</t>
+        </is>
+      </c>
       <c r="J61" s="6" t="inlineStr"/>
       <c r="K61" s="6" t="inlineStr">
         <is>
@@ -31864,8 +32264,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>https://leadershipinstitute.org</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAYFBMVEU3R3f6+fgzRHVhbZJLWoR+h6TAxNExQnQ8THu0ucnt7fAuP3Ly8vOHj6v9/Po/TnyepLqjqb2Mla9qdZdRX4jm5+tGVYLh4uisssTHyta7v85zfp7V2OBbaI7R092Um7QDMTCtAAACgElEQVR4nO2b0ZaiMAyGoYAFplQEBQQX3/8tp85w5ozaMAEzYfds/gtvmtrvJCVNsAZxsKVUFAiAAAiAAAjA3wuwnxELQHkG1dfKPyelBNhZUCbR3in7KvIPrAQIIeV+AD2cdgt9QAqggt75BggOB0BQmNBe6kVBoATQf8bbjGzJ+qQA6mBuY2ZYEgRCAB3lHxPseFxAQAeg9tlkb0r8+pQAlZkG7WnA70MyAHUcv0btbo8OAh1A+W3YVNj16QDq0zdr26KTARGA24H3BlmADAIRgK7yBwtsRqYBUM3lwRadDIg8cH02PaQoAhIAVbfPpjkuGVAAqDTzmNhzg3EBCcBXDnwMAg+AOj7uwMkFqGRA4YGr3wEuGbAAqPgM2bXxz7vgdQB9l4TvhXgQXgd4A7agk0UUBgQAB9DKdj8/BxQAoJmrC/4LgBK0shlLCAp4EyIKI4rH0HMSTUKkQoJE1PSQA1pEbUqRisEYHHjOAhWP/sPoEiHOYwoP6OHkW98UXPVAkJbGY9qzFSSuKH9Ox6aP2UqyD4L7I9GaDnEU0wG4snAYTTjZWxteKmx3SNaa6abYtZ8vKNpzFWtsd0rYngdNXZRdV1Z1jO3LSAHcd2mtlXKfvK9olH4DxZEJVZzAihgAdAIa8ZRkKoGtbMfgATXrAQEQAAEQAAEQAAEQAAEQABaAzati+KIHT18Q9RmkPuF4UTlzcYbpJ5vXtBZggFtiv6CWfSWA6YqFghrllQChWai8BFywFmChbLgxQGgEQAAEQAAEQAAEQAAEQAAEYGuAf7MvqMDGf4UGYJE5gJRUKwBYJAACIAACcANY9u+0XwC4Xf7ZTDoKqpl7OAy6vgOx7FWg5iqXvwAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J62" s="6" t="inlineStr"/>
       <c r="K62" s="6" t="inlineStr">
         <is>
@@ -31924,8 +32332,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>https://johnlocke.org</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAkFBMVEX///8KHGEAF1/3+PsAAFYAAFgsPHjp6vAQJmsAD1wAEl0AAFoAFV4GGmAACVv8/P4ABVqpq7yPlrPY2uTf4uyorcNocpvw8vZ6gKFdZpHN0N2vtMfBxdUYKm0vPXaAh6hMVoUqNW1BS30iL2tla5Gepb03Rn1VYI9vdpoAAFEAHmmIjqsAAEgiNHW4vc+WmrIQ9n8/AAAD5ElEQVR4nO1aW5uiMAylxYqltDgCIqiIOjIXVuf//7tty8XizPpG+u0u58HLU86XJidpUseZMGHChAkT/gHkrlXz4eEQhhbtRyW7WTTvxAU7xhbt5wUNSov2vZNANLNI4J0hRNf27CeUI+Tb84B3ChBCwckagRWR9hE/R7YILLAigPzEkv2ddoAKgtQOgYNoCCALUqi0381oSyA4QttPcvkRnzDqXHCAtR/tVdxHR94R4AvQQ3DLQpWf/NwTQMHeAySQiPmDB6Qel3CZkGb+QhEwYkAeAq3BmpKIcbaV3+ErRQYDdoEicCFtAVwtkckAQ/Ula4q4UCceM5OA7AuAwkCVQLLSVAYuQALoECoZe7hS/o4W2CSAEYwLdBNANirodUNyB9uAEHjz9YkrNXazwSFgmP641kb9Svk7LQIzEWCiYMe036k+hPxshkEAoofeVdvkgVIjJ/kwXeBDdGdhLVrt0yfetyUKsy0AASffc0N50jdDkQVMY7BqJJAva/Uv2t9zEeiWFLbZx9lO/a1JT8B/AyHgeGXj9iYXvbsLwK5p8bnJf6Frwlcfh6QGIuDssM5FXKhWLO9dQHZQBJxtoI2SL/k7Lf1WiwvA1nCjQw/P1e932kox2AlIpHMdBkQJcitG+Ah6Tb0hdQgfyulNfUIMRAd7uLop1QQaDxCYduAOdTvmn4pKpoKQ1eDzyj1umqCo4ChYwl0Meqwp1tORi+DiaGNaeSFCDUfiBTsfIO+GPW6/dFeUzdaRnWFxoqt/Ulua0MjgU5ZDu7P6/xKh+wSjB2N8ZWT2BISNXJGTmZTfJ5DFYdyexGOD6+h3NKODEZHR5wTE2CVxR5+7gOcjE0gz/5l9+j66Ll3EMwJi/KYo3Qd/tu8Xo9uXmcgo/hmB8EG6gt26KuY/oKjWY0fgBAOu9wDgnijdXPcLA/vrCrYxiQUfKCKHXVlIAv6DInNgAsZUpAGugAmcHvQQenvpvj6UZbEBfUgShvVwV4CWX4DmFeR9cBCDPuxsQM2IhkkAu7qU2A3TgJ+h69BgbQk8H9NIq8EZ+CWwfccpB72hhbc864EQjN6Nf8dQCAjY4rZHQkwCM7ghcYd8ZmYhgX/Q5pmbY/4JPydxPw0hwHN4AqH5fsHP4MdkoZmHS+BnNBorIwjgnk8YeDEIUPgslPXwrsV8YeNOZrwjwoWNF31x1adBUNqYVXv3ekhfbcxrjXdEFmqhwn1xv1xZIXDpCzLwuqzDrRcCYmcyEnUdASdWFjZO2o1tuW/FvuN0BRlfLREoWiWCejfxDd3gmtgoxgpb0oDZqIUK7vZF4zYtziZMmDBhwl+N3xejOFHMpo+PAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J63" s="6" t="inlineStr"/>
       <c r="K63" s="6" t="inlineStr">
         <is>
@@ -31984,8 +32400,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>https://carolinajournal.com</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAflBMVEX///80KUTY1ttYTmY+MlDj4eWmo6z6+vrEwsc+Mk4hDTcqHT2sqLIwJEFTS1/m5Oj19PU5LEp4cYKcl6ORjJiEfY7Rz9RbUmggEDXr6u2WkZ4lEzpRR2BJP1e0sLh+dogjFTdvaHsaBDBAN09mYHFdVmiJhJG+usMbADMSACwlnh8ZAAACS0lEQVR4nO3abW+qMBgGYOjG26BarRRw400Rtv//Bw+gmRRrFpLS5Sz3/Y0Wnl6i1KTFshAEQRAEQRBEGeZrj1gEIO+7QGdeg/BjGeDVWXT+z3FfAAAAAAAA+DsAJiLOI8GuR969w5tmNYDDN+/5oSh4ybP+UHT3nrjeX1PGZTEX6AJEm7C6jH1ZVBPL4vy7i5E4DYdU3CHZ/EI9ABafKE22tyPREJG7035O7T5hpLhUC8BrhwHuN91P8jcJQHK6KoCHtk1rNqmaphJgu1kVQOy+fDWtzpKTQYDXhkN1IpU1CSDnvjrNpefLORsEROMNqKU21hgE7EfAQW5sDQI+xuJcbnSl41UBXqAqHpkDsJ1qlttK5/0CYMYBAAAAAAAAAAAAAAAAAAAAAAAAzAOEbw7w2yskVqJaI+IGAfG4StbOGg2uknUjoJHa2MUgYKxOAzZtE9TkYjWv+uqVtFbM5bVi5wooVgJkQ/nqOB0wOCn2C2zVyxJa9gu6HbVpMtmNiWf7BX7QD0/PD/s1ugBWZPeC+5BR3ciAgj6uZ2sFWN05pMFt8vN47Mmr5bcdhU51pa5dM1GnaT4KRHzMZhMRG+aqMGGqC/VtXPrtJXiJ4307/tSc6UMxzBTfN2g1QP80ECHEVtFR94D0+LBpqh3wLP7wAyiVX4ARgHOhNDw8Gd8AgDVhunPV9399gEfcgCb82cdfH+CUJfdVE6ApgPX4woBhwI8BAID/D6D6szEK6IjeHJJlgM83zfnKFwHkt6L0ZBkAQRAEQRAEMZZ/lnk/gn6YQUIAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J64" s="6" t="inlineStr"/>
       <c r="K64" s="6" t="inlineStr">
         <is>
@@ -32044,8 +32468,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>https://niskanencenter.org</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAXVBMVEX3+/0BSFIARVClv8Tw9/l8oKUJUltchYyrxMjd6OtrlJoATFb7/v/r8vXW4+a3zNB1m6Bgi5LN3OCTsbdSgIhKfIMuZm8gX2iIqa/C1Ng/c3wRV2Catrwya3MdWWOLD0nmAAAC9klEQVR4nO2Z27KjIBBFkeAFCd6NJpr8/2ce1AmiwdSZUdp56PVmFSXb3jSNDSEIgiAIgiAIgiAIgiD/P2zFL4d9Hfw33P0VqfWt6XrYSMmve+eXvreivtuGxeth09hitwCe0+U7qfDZ51t5RS3z05DvnZ/w8OOtXf9pQlLbAiB8uVuATP26Ed7i+6rPwMqozR+doFQPDJoq64vd8w/v5kUZP17C+LDY8mFM8nuf1c04osnbqOD7P3/iqlIsueRGCLp0axwvg2FAJtnwfCgXIwS02oxtNAig/hEbwBcBnsg2ljcDEuA10aYACiJAbTFbAmAioFLcagKcAO922RDg1gIxy3gktmFjBDx3Am7POQbWfTYdLchcCaBVf3tvtrSxmeBaQFj4wbdMcL0GVH0tKi0g+DTBdRYMBT7Vy4A20XoigAioM9KcCWGyqjgQEbjy6q2Aing1E4QAles6E7zXqjBDWKCOKK02gebL7QgmAiTZzAQgASRq5pqwMAFKgGw7rWBxOoJZA2RpQmuYABWBhQlP43QEJ0C2Rk2YzyZgFhBi1ARRahPgIqB+m7UJ9KZNgBTA5sIsqvd2BGgBuRbzf6vOBMgIqNPPzdiO2AkCzMKcT4UZ0gJlAs+1gmCaEzYCi8J8u58hQJamCQTaAgWfWzPdkAnQERhMWBRmeAGy1IWZhskJAkgyb0cvZQL0GlDM/wneMz0hAubpSFT8BAEkmZupQXnpHAuwNQUKozDHowCHf8c2Acw4HTXCsQBbZ+iamF1M+DVAhkyg5wowj6inCDAL8ykCFoXZsYCNHjjrA3cC1JyMt1OXrGDM3oc3TTg4DSUvLlk1bTavyi/TxHoVYWbCkRGQaZsv7mxE8Kzj8rNDJ/vOiYD0sWoSjwSWiyseUhcCSmG7kBO2+wJdmI9chKy1BcDr7paVyP6cjuihWRDFNuy3BTynlAavZ21t5f8j9kvpjRu5og4zlSXSwT70O1jCT5t74uC7QgRBEARBEARBEARBAPgBHs8nwFOoI10AAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J65" s="6" t="inlineStr"/>
       <c r="K65" s="6" t="inlineStr">
         <is>
@@ -32104,8 +32536,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>https://okeefemediagroup.com</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAZlBMVEX///8AAADt7e2oqKhZWVnY2Nh0dHQvLy+UlJTR0dHz8/MWFhb7+/v4+Pg8PDzf3996enoiIiInJye/v7/FxcXm5uZJSUlkZGS1tbWgoKCOjo5CQkKampo2NjYODg5qamqDg4NQUFCDyMIVAAAFvUlEQVR4nO2b6dKyOgyAG1yQyqqgqLjd/01+uCBJN4q0njkzb/4JXR7bNG2TwNif/Mn/TfiiXta6l9m1KavEY+9JdNxvANJM8/4IAKflrPIGMIOX5OrX0fv1PvANAAvV23j/fjv3D3BVvd2CLwA+awQAmMmlqpMAkN2UAzVeoissRYCd/CcPIAAsIDzw6d1XedukBAArqRzIAACb7dRVOUtBCVCISzFXArRVdWvWSqrbq0kZAG4xKRkVGgBIt9/3X4agBbiUuCSfgw6grf2tJsw+/0oBADtctAYDAOy/Wg7JtW9SBQBoSwhC/EICgOKLaahQ/2qAU2/zG/JCBoC1wnAM9L/DTSoBoOkKR2QAVAAAh3H9ZydSWw0A0bv0nj5WAsBqjEWo7rSyBuD9OBIeqwFk22XoPxTqagDgqVtkCRoA7GehElvUAsy58qkGQLWFqSTZSzV1AI8mq7M1wMVqNSZHqaIeADi7Sc+0AHCxsUi1XM8A0CwK6ZkewOasUiqqGQAKaQKMAHCNDX0/JLiPA1CJCWBIEWOFArgF2ESG7tuD5do3AOyNm3OqrqQAKC6kxBr9NAMYJ0FeUlqAG7EWxQqhDwAY1uJCNMEGgIYslyWuOgAAN13/sW4AVAArhg12NgLgrB0BagLwAlcCLDafH0c2AFD0ZVP9MsBnoPZSMQTAPku2vS4PAMw/Z6ZQ3z8dgBne5dUAQad4WzYI0O3ZZ/01IUFXC4B7PAzQ/T6xYYD3qcUw/izaoApQMguA19963hAGAdgSTPrH0Iw+e4xtAFj52Arz2AqgLdH/fy7vijG2AUXErADi5ausDQA79vqX5EcJgBwDHj4YGwAWdIdzC4D+X/MrhNKOsMQAkS0AuxWBLcBH+MPgiaezLBWL2wEE72EdAcCf/1W4XdMZ2NoDdGIPwF/LfUedeWQbeF36PAHwztxQixDgGXhpqB8AflU3QHau0h8A70ea+BdI02HsDYDj/Y5cVvGLtxfSAwAn2w1WggSrwMwXAO2f3FUrfL3JfAEQW0f9vRE606aBJ4CAnqNhjpQAt3xNfAEIdw7kY2Ir9Lzz/HgHwHckbAc775t3AOQtSJaKx94BkKMRe3k+A+MfoL+j4Tv559jqH6A3BNgr+UOAvokKGcK0+hnA8Q9AqQOeAdbKJn6nhHds8vpVECA7EHa3Jx8ApwpHFnoAjtwthT9DBLuMGP3eEBFT7G0v4LsFie7hmA++mHZczgHiQBhrFHfDM9O17OVUjNUdb8f4XrT3dSB5NoqcEPhAgo9kZ19Hsods0bM9uh3+5lDKqLLhPIwYB8kajwA4GEhCSPjEvPcHEKBH9HaKtbDg3gCIE4A4CDL8ZusNAA/0ndTneHJuvgAq2QnwEayerw3RAwAJeAguSzI7tR+AhMyAkG9V4YV49wNAvCCSo1C6ursHIOEIKYhKAyA+ADJ8HEvl0BXW0MdO6RyADEDDJME35EeA0zUADUgpwgYZCcLWzgFIPCZXRHBpyGqXOAYgOrYumUIWxIXSuAWgaRZzdT4JcSJtsE5MByAaBsoBEJNRcARnMkBB4kF3phGaj+QSgIhaAx6SjQjdTgDI9RlFB00VpwCFIXSW3H8AYEwnKi/KOi4B5ubsQvUkOAQwxI6fIuVluQYYzOdSJjG4A1gO9d/enhRq4AxgZ5FjGyvMkTMAu+RSOZPDEUChNYFUAimdzhGAdUKhtBTcAIxIKxVTGp0AyBF7EwFJqnUCcByX5s6JHkwHWI9M6201Ea+FyQCX0YnNrRx7izQVILRcf4LUoSOA75LbH02kTgDy7z/04M1lMsCUDxxa2Wo+8bAGmPaJRyvJajMBIP1O+4S2828BNgc3nzzF20P8BUCWO/rQqZdxAB7kPweo11YAV28APGrmQwBhXvv74LGVJKuX50IB0C7WdXhflcFQ9roLqcrDTbBv1XFVLxx8W/e9/OKP/8mf+JB/G8hX6XR/hcMAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J66" s="6" t="inlineStr"/>
       <c r="K66" s="6" t="inlineStr">
         <is>
@@ -32164,8 +32604,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>https://rairfoundation.com</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAABoVBMVEVHcEwCAgL9/PsICAgDAwMGBQUCAQF2cXANDAyVlZUEBAQDAwMEBAT7+/v///8GBgf9/Pvz8fD5+PYFBAMICAg+Pz/7+/sDAwMHBwcFBQUCAgJHRUQxMTD5+fn8/PzEwL38+/sYGBhhYmFBQEDJXFRRUVAmJiVLSkklJSUSEhJYWFenpKBBQUAWFhbLy8vKyMQvLi6pn5R3dXB4d3RjYV2xMSvWyKp6b2qro45OTUqLhoGZcm+uGBbIWUgBCBcEBQUBAQEICAgYFxff1LcSERIMDAwgHx8nJycvLzDYzbBUd4XMvp3Pxqu3ExNEborr483k28E0VGiDnKQlSmhdfopVfZc4ODhdhZx2kpupEBBqipYbPllIaXqtooeZCwxeYF6+NzOdsrm+spS0qpC+HR2Rp6xVVlUhN0Y3XHlRcHxjg4/GKyqjmYEyR1KKg3AWLDtJTU6HCwxVFRS3KSV1lqiYjnk9ZILBuaKsHx1JdZVljKPFTkhFX2osVHfFQz2USUN0cWWiKifObmNiKiiLJCLSgXTUlYXIoomxbFy2jm93hH/BfqWFAAAAPnRSTlMAHgvBCz8UAgUBS2L9KUTxWwUSKoP+NVV6bjb/w0wghBmS9av+/abF0+3caOTeSWXsm0CDo2mYwPJlmRmXnMyxFnwAABMtSURBVHic7ZtpXxrZtoejUQGTaDvgBBptRzKnk9unh9s/ZoQCkRnCoAjK5ABRBEScorlJ51Pf/9oFWAyexNLz6vSCoAGp9dSa9tp7Vz148I/8I/8ILzKJlKRLWhcJL9X/dXV19XT1MOkQCr3RRX8su5t+ibSLjjw0VDtu/Qf/2xBkYmKiG9LbIN3dExP0pZ6uLuldIKTSno6hCRy8u7e7VXp7R/EcfcRknJcxPCB4Y3QUfwKKOzHAAB1D3XUlTcIUkgzzMoMH+zE8jLfGxoAx2ltlkMhEMQCA9JMuXgu9QmFdJymdJVlcXHx2LYuLs7MzM1WI3t6JIUKQiACQSHu6lUtLS0qSxVl61KWq8meS9flEYj43n8spcgr8TCTW6d1ni7MEMQ478AgiACRdEw9Vqv5+lcls9inm2XEFsr6eSOQUcp95edmk0+kMEKNBZ1pe9skV84yCIMgOvcwTt44FSWfn4C/v3s8ql16qjAaT2ZfL4exIElCNk1b4lk0Go1ataRS11qhbNssV+FtiWJgZZgjIzFtaQdI5OPXkVd/r18/fvVe+NGqJQS5X4EHiw5nrtNCnxUmbfT6fYlehUNC7BgaBv5bnGAOZYXy0G0a4ZUIwgJG+vknI63dKlVpt1JlgYYgJojNo1UZoSYQ9wUDAtbW1hX+uQJCr7PIMsIOPZwACjNANN0hvQwAXTIOgivB8VqUm69ZEC9Mbd9NB0rxBYtvY2ihu4GVr61tYbiJnMKMpwJBYJCMwN9zKBAMDnYPTgIAdJvtevVdp1A2iMaRdvPYqQ/3XLde3BENQG2AGBVJjXjlDbrglwQOZTAYI5oqRvpGFfk0LAGTL5cq76MThAfyaz2/lXa6NjfOkjkcwkSfmE4sLY49uT/CAfEaGgBmm3r1ssQBUBcqZTLCcZ/73+/N5f7lcznuCLpcnZ0KQwlE65oj5F+IIeIwBhMPU1EyjCQCQCQaCXg/H4acrAJAjb9nv9fs9Bbu3HEznskRAwUtpmQMBeeG22cgEGTE4OP37yyaASpjLeI+8XJo7QiYEA2WvN1/22o+8Jyn7EZdOV7IanoClsOLFAuIA2ShmZJDADYNDD5tcEK6kM3aOw5NzbQEg7/WXj+yFQuHE7T4p4NOKmSdAPpARXiw8Gh0SSTAA+XOmvwmAC2bCTmchzXGeQCboysMcAEiFC6GQO2UPezzcsppZjVVHn/zFDMKgQ8zAIENOPugZa8hEuIALfuNSqbCds3soEstePwDshXTqBJIq4N2KSVMjIDcox5gTRBFIZF3jTQBpT8aThna714sYgP4jiP/opHAStqfcIEinU0kj/x1GYPYpx3snOkRlAgGMvmwB4MJhhLzfjxIQ8HvtBfuR31uwFzhP2I1ASKVSTqSCgODNAssEEVGAtkba21AJyAUerz0MnX5WB8pbLjtSwA8M+MHtdiMQnCmnqUqtNRABbwIxqYgWqbfRAjp43+vloDKYp0KY39hABBwhDLlCAS44QSo4U+HdmgmQC0iGhdGJjh5RjSIBNFogBQNwXoQA6pBrKx+0OfIIATJByo4gCCEMnCl7SlczAWtYlsYoEcT4QNrV/VLbYIEwh6Dn7OEjf2Brw+XN6x1bGcTDUeoEdigkQ/ACwrFgrtlNywb0hV6RmQiAhkqkMdk9/iO7N8N5y2UMgeUNx6oN1ZhC4MhfPoEBQsmChysk646jMDA9fERBcHsTtAPg/EccxgLKgo28y7K6qncdwf0nlBiFE7s7GwpzlZNk/SvkBN3LsQlR1bANQJoLejHqoAZj/HUVV1cdjg2MRvZUIewpF1JH7mzag1jIXgMwghlqTW7vAwbwWAiQtXswGOY3bJBVvc1BABabrUgNSSBwcoJRwcvZC86QUSMwgcH4sPe+ADjOjxMO2BwOKGfi0OsdepvNeri+GwpVwmlP6sTtdGY1AhMYtUujHfcCoM3aqQaiCm3YagCregvEGll3urPZShhlCIOCUxCFINCqxu8HQJ2FfvQ/VAct1/rhg8M0NGeTqTDVgtRJ6hoAPgDC2H0BoB8Jkgn8AdiAjOBgp/8tjALghO5w2Onexa9CALTT6vsB0Giy4TA6AXgBrYBrQw8EhIC+eO6E8hBe3JWK0xlyh5I6IQD+DYsakdu5AK0QDX/UEm7Z9FUALrRLp03mdwLD6RYCMIjhjttNUW4A0GQLfj8sgLEI8wOrRa/nn1sVZ4W5IBlysuEw9B8CUGcLR/4MWiE6/yLO3VIsWmADqwcDcSiUxT8YoWoBrWAU0Y6JmCvfUAc8waAHc8OgC5ptcZcrbrPoLQEKgiQPgFgIZY187NXk8Zio4bgNAJpOjz+Y8QYJwLbl93opFlbj9kIY9Q8hAFM4nbvNAMbxLjFLaG0KEcWg159HGsahP4NRkPN4vsWsnlT4iIoQFUH8SBqp/l1/UfVIIrsPADUA0mF7GOXYtVHccmXgEcySKhVXII0K4AynEIVZd9hpYtPpa/Clbtn9WCBJABUnVy7TDNUV9HjRJXNhpz0YxCucn8w6s6EKAAwGgQsePxwa6By4F4BwOp3GrCSDKXEg4ArSrDCTARTAYIOTEJPdXZOhEWDmz87B+wAwMoAwThr9QIDyIRgMIi0zeDOd5tLuZDKEWpDMmnQ6g1EQAuOYaN4LgBmTU/gd0zKaHLPFAUxRMxk7643DoSwyMZvNLptMOqPQA78M3pMFzDhRnDBKkeebixZHaGkCWXlkRzNyEsqiK91l+tliWjV31YaZwenBgfsJQsw+AYCOLBjgl2byZABPBm1YqgDruxEASVrUuvaARrP0fGpajAHaxUAa5s940BSgJySAfDmAKLBjtuA+8aZpHM4md31moQc0htlf7gsAaUiLI56MP+8q0ypRoAwLBL0pbybtPuE4N04/m5TTcmY9BzSah6+gv1PM8nUbC8D+8H+GVoa8ZVc+SLXAH6TpcjgcruwmSb/cvKwz1gA0atXvU1NTALi9/taGxAgLUN5TXwg3ACBYLns9QX/YWUlXcnT6SYUCHqgbQKNRzT558mS6c0CE/iYAHFObrIQraS7M+TP+QJ5WyTwgQR1yhpyVyi4SwKdQ8AaoqtdoZ5+PkH5Rk+MmAKNRl83lKpVKyp7xeAK0YBdMo0VKQ3USD3kyuZujBW1a063q7yf9cIAo/S0AOpMvtwtxV+Dv9LeM5xuHVojOnXyflCsSiflG/arZ530jovU3Axh0y/IcI9jdTew619PrCbSgzt1dcr7Zl0vQboKvZn8yP9NPDhC5idRigWWfYp7UMIbKegI4Cva7gjYW8IEcFaCmXmNceve67w4OaMkCtuTDluP5PYx12roh4d+Yz8l9KEDq6naGVrX4fPJu+lvSkGZZxKCoQUDOqzi0lSNQr+nH6ZP+6Tvob9MRVU+OVkF94FDk5klyOdpHEqjvf7n49vVPfX0jpP4OG5mtpdhgMqhr+0RqzPtpx8psZptY/OhD2t8o3//x+qfa6d9lN7e1FO/PnZ0pMNhf71ex+T9tn7HYM6qWSDupR/qJrT83A2guP336/PnrGShyCn6zSiOcAj1WzTx/NTnJ1N/N+zcDfP4/XorF+M7e+XpCrhOsBKj7h/8cfDIyMoLqjw7krvpbs0B9eTr3+TMxfNHzqyOWWKJuA+TI45ejPX/+OU0d4F238ttaQLt/cHp8zBjYAoljVa/fEawJIiyVvWxBTNzm9XcBNJdRkk9znwBQm5uvG+rLokiKNzNsq+zO1m8PoL6MHpQODqKnx5/1OHmHg2bnOz7N9eL4snlpXOz+wI8A7B9cHGxHT2EEPU5/FQAOvfVc17A4vvBI7P7A9wG0+6Xo6enx3OnmJwsswFygt0TqJmAl8s2w6J2yHwCA9SHbAHAUraQeJrDs6QRRYDYrx3rFLQ23A/h9ydhogYPo9sHm5sqc1QIAi4Ux2OY1107AKEFOuOW29Q8DfFhhsjnHtOPpsFgcjrihHocGmGBpZlTc0mwbgGYXfCABASxgsVltRavNZgNEvRqxzTp+k0bcZuH3ANaYfFg7ixWtxVg8EonHY8Wi7XC5MQ6rmXBXgjYAHz+urdHzDKrx3NnZiexEYsX4uVEj3CmTD4/eB0FbACZrZ4eHO4c7O/S6dxiJx3auTVB3AnLxjtXgRoC1tbO9w72agCISOTM0OMGspCs47mqCmy3w8ewwAsXQfs4Qdg7P9tVCJ/hqYXCnVGgHgABECHw8g+/hgEMGcbgHgEtdgxN8S8MsF+9kg7ZpuLLyAQxniMF4hGKQYmAnvnN2cVUjoIsHls20ay1up+jfAmxCQPDhLB6LxwAQoVQsIg3motFLTYMT5CwQ7+SE9gAwwcoKA4hDrBbawNIXj6On9TisXTuwwNeje5wXoCMiE2xvlj7ZbDhv1EFURItD77AB4Piq3h/yY8KLmUd3I2gHsM3LZ8eqhYYii9VGg8Gq7RhtwrHACWzuohxjl0+IJmg3HEerAHrWC+ihn34DwEE0enxl0l7vWlNBVI7dqUGTtHZE0egp1EdPGQCGoyIZQG+BC0oX0bnj60zgA5FdRSO+O5FKe1ossE0mOJ77QruFVqs1hhFRzwCiV2fHc3OX6sbWgK6iEd8itgdgJvhsZWKLFPUYjh0AuPp4dnr8ae5Se12Sq4EonoABCD1AXTGawlO0ZNZiPBaDBWx8W1SMfrxCEMzNne3XTaBlF5URgdhUkHY1A+wfUBpECcAaQyWIFeEJm8Ua/xItlQ62T4lAJyRg1/GITsZGAEx/NftrqMWbKAafyAEx2MBGhSi+8yW6eYAJAwCOr9SCQYERDIskQBb2CK4hofm37opaslIVAB1JkSqhNR6rApAJjikMNDUCDAqiCQDwy7tljdACulJpkwkBoBRHdqzoDK2x4t80ZdqOUtc+d3ZdDVggyhXwArui7JYEMknPL/8y1QHUBHBBMbC5vc0A0IccxlGSMST8fbH2oQRhRmgIxDrB7XNBCgs0Ami1VzQ1BAEAbNbI4c7eTozGw51DAkC3WmJZcmloSgUFvMDXxFu0BxQCDQC0C/7xQwlBuLLytUhZwJpC5EIscnjxYQV9yloJBRFuaCQw+xQgqF5h+uNGkEkA8MykqW2B0k/txxJOcvvg4Cua8SIagkj8MIJiGNu7oC7hI/ND9Pj4a07TTLDIrnG9zcgkkfZ0dD8zqRsBLkpUCqJfYzYqxbE4UoHmJ4cEULpCll6RF/4+NF8vnLCrKxXzizO1gvBjbiADDP3+Qqc11gHw2/5FFACbm1+tbFpKOWjFDKUYuUCfRvrX4KTSxdfIuamVYGFsnL/i+4cISP/E7290RgGAQbd/QQZAEFr0dAmPg5+gW2xfogCgGrH2YQW58DUeFxKwSFTMv1hgF53/2PXWGIo7JnqHVTpDffcFKaXbvyIfbFI/wBaJHA42FlhiUcxYS2zeSjJnsxTPdUICdrlzQjlD+YhI+C6CpIv0jyppBbS2/UQApv2PV1SNP1nYRUx0HROJ/svBymZ14oyuEQCoz+uGRgKzPFc1QhXhxnCUUQaS/rGlZcEOJFsDYlOTtRIAmKyukgv0FgDUhNrWOeoYI/Ma4RIeW+aefwEj8AjsvpyW1TQZ3dND99oMdY8+GleahRtwfL+/v08zVNQBGgZZBGA8iv1dA9hkz+MijVO0dtNI4MvNJ57NDjOE6t0oDTkB3Uz5UDepH1uQMwC1EMBHBPs0NaNZQRF9OcZklOIDNOv04OU0HoMTLIJkrBfFXOJn5QK7HaXKICBA5tN9PuxmnvGxGaXcJ9gAZKXQiJMwX4JAgTnh+fkeGFCIgfL3AVs2wD+CWDvFZAmVqri33LCYXL0TY/6Zku7CGB9tvg2Deb67qn5B+WZZJ1yfqQaiybx8SQAkBEALBTsRDEbXQrP3PXyGSr1ualjP1vBLeXLFC7LCI7aI0NUAgPMn9cMLS7x6TYuQIZcvFesEAD/Q/ChmRQzQ0g1bwKEovapN3PcSutZDGCkl3iwtLcyMd3c0WWBoFOf+kLQbtK3frB+AjXCJ9fO9OEph0aq3fTmObpc2oT56Gr2g2TtGKX7enjC0O4Sa1pX7VapxpIIwBjAPYLf56PpJHuPRJI/7a++pdCaTyXxIIwKGhdjnz3PoSUolaokuPpz9Bjnf++03q/W3nx8/bjkMfwRVv2qsU7isLhnopBudlIuz79//8ccfb5++fdokeOPt27d//AuyuKhULj18/9NPr5/++uuvb//666//hfxPVZ5D3uEf++ztr83Hefr09VN8+upV46Yi3WUz9erVq8nJyZ++L5OT+D4dgIlUKh1gtwfKBqQP+PsDZVJpJ921c+P3J/ltnUYAus2H3WRTlb6Wx2Ttta9vhB3g+vuypquVZAOD0/yNQ00PEravMzXYBDD9hHZcqvKEnk+uZYR/GRH8ReMBWos63bUzNfXkBpkCv3Bjid1UAS9MT+M5SBsvg4Odg530ZC900wee+IhkCn+Iz//9zpAMxxzovFEGmjaWaCTA3w/Q+xIJfYizk7A7DfBKZyqT8R9BeOd/v8GSVb+Fv6XvytjRcDAJf0fPjV/6R/6R/y75f6SGzq/BVxyAAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J67" s="6" t="inlineStr"/>
       <c r="K67" s="6" t="inlineStr">
         <is>
@@ -32344,8 +32792,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr"/>
-      <c r="I70" s="6" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>https://israelallies.org</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAilBMVEVHcEwWMUgXMUgVMEdOtOFu0vVdweodi8gtboxFpNBSuOIVMEYWMUcWMUgWMUhtz/IWMUgXisgYi8olj8wkj8xt0vRu0vRt0vQfjctt0fRu0PMabZ4WiMYXMUdszvAQhsVSntP9//84lc0qkMpt0PJco9VEmtDq9PqbyeZlrtrR5vR8u+C32O0XUHSf3ajjAAAAHHRSTlMAue8lI+U3/gQKFBNG2HBYlVDjl7+kzrlzdYz+JyNBcgAADR1JREFUeJztW4l2ozoSjW1AAi943xoHwmaInf//vVFpLQlsk550z5lzut55bhabuqrlVkkob2//5J/8/wkNIy5hSP+67tCL49N5tzuA7HbnUxxE4d9RTaMgPu32vl8yeZfCjvz94XwKvD+NIgqY8nejGQkA8g/n+A9ioMHp4PeoVupL+PT3uzj6I+q9eOd3hw4XfH+/58Gw3wvX7E/Bj5shig9+VzuM9xTHQeBJCYJYRMgu+FH13mn/XrpDB4f3RR2NvCA+737QCmF8cNRDuJ2Cp65mIJ5/YbgEZ8f45fv+HEQvySf8GWaITq56H8L8r3Gfd/ad0X9XPZ1Of189jff28P1Db5LTkAvtBTaZLSa/iSE82fpL/+S5qiNvtTpupBxXK68bHNPFcjn7HQgd9+8C6+GURfpmu16TvCqSLE/YP2S93p7jlZOc4WQ5H30fgne2h78/4ceG3mqzrZjmJCFVngKApM7YGcORbTc2BjpdzC/fhRDtbOY5YGIJAzb0rMpBYZLV8MGOScYvkLqqCcNgQZjNL+Pl7Dvj31nj988o+KLVdp0UWUZSMeJEAkgKbpEkhXvJenv0kMsmy/FlvJj85vj9k9ZPQ1DP1IrhgwM0gFQ4AYyQMSgMgoFNp8vLZTyaDUvhyPa/H2tzhqsNU59wBVykTml9CIdE2AUurLEjpswGl/liSCREJ2v8+1jf8Y5r4WUi9RfySADQp3DEr6w3xg/TBUNwGU1eGyHG9Ff6sf7FasufDy6Wts7qFAMQEakQ8FvblW0Dlg4v1NPA0m/GH/HhM6WZUpLkCooCIONQHAowxESCQDB+4QbvgAPAjN/j3gevEw1A6TUHtTQJsgHZaAKFSHwVCOHZpj9PlFXqCfNb+rUBDIAC3S5UqmxVg0QnI0AwXj5BENsE5EPbxUhotXV1auaxADAT6PvGISYQGCM994LtAB4F0IHEQn+KfGyN1gDAJkhkuqTpWjeJPBUYgge5EJ77mn7WBwjFaMzw+Fz7G123v6ICdq1twAPxcln0N0zBg86/LFtAkCH74ohHWlPsJMhTeVnHgQiDy7iXFMNdrwGEIwr72WZ09rAJ9pJBmW5lLtCZMMG8jw/iR1MfkDa3Hk0ydIbtjsMQolaZZiP5gPJcBE7s6I8eGkAgsJ5cIANYAIhlJxM266NUIzLhcukm41MDsEi0AGSGcmwAaWYD1XZTgUhFJvSkwnMDvJe3KtNStegka9oM38qwmC+qMJBx2AmDRylgJMu1sIbISPV5r80Za4nQPXNa15tQmuDS5wR6em4AJlWqhZG+lqT5uLboNMtTdJaYryonKBPYTog6JOi6oGxRHSqQ0z8/Pu6FCYkch4dFjtoE455MeB6CHMF70fPQhDQfTG4p0phYYhJzvRJDnsyVExCAfha2RZFvipI9ra4A4NMQs0URCW6Ukq0gg6nkgsvcmMDbv9avAVjce2famRNuxiY2F8G31e9UFEg6RJWZvs4BBACNMb1dP6439vFZaRPkjg/yTN1KtyIKpqOOCV7nAAKAQqBgg2+ympmhMc2QRYZQH/S5KszKB+OF1P+4DmFR4861jckN3F/nNcOhTeAGAfaYTATlg8tc+iDaDwCg0jDVrR9PwVvKWoMGp6JxujKJPpR0qKiA1eWhNMjSsOqMiNx5/DOFzATXm6apXHCQ8YEyiSIjnQeKDuPX+lkIwJAbJvd7I+TOUvCT/cMOmSk+b1KaBj576zU5UouLZBgO4OF3ToQw0oHSIAAmaFJJBaooyzAcFINi8tten+u98v+YOTLkA5QXMg90EAgfvCwETFr5BOb2a3NTDrgbl3yKG+CCK87KxCLDxA0C7gPEg+WDcGxljAP1yuLX8AhkkhfwCRnR8BvAS1ZFwp3ixq7JIg8wgNO5q122xRxAAnoZmrQGDky4agjPFKoS6E1zyIgEC0GJKZjAAOAVKTArUmUQnbtrwy0qvzXP/bSA1Lem5zmYgHAguDyDoEmjZIKZARBiAKUfwAqhA0EuyEgENx5iLXcFApDCDXYJymNr68dpIKNQcyEnQwzAg7no2RevIfirmTa3n1bBSKEK3qVdpAXA9h93Xh5rF4DhQklFuifgUYhcsBcWWtVte3u/vbdtViXO02qogHeUaYpneI7CjZtTkDEZdwDALAlZ4CCIYrVOSFEUhHQaHIioRlCNumKm53dxw+0IMBGQo0ME0BoiADsOgK6A9oDP0x4ABedD3QSlKsZT0R595rkDIMUVWpCxAXBZ2gBEvTzqH+ROdQcAQAHXmym/Rh/Ypklr9zeFrtCEdAFMGQ/oGBAAaFxpaStH2AWwQJPpC+Yr4IM7vtB9SAfAaIqJSFtACbMAloIUWX7jrJ8l8lpWq7stv9HW9m/Yr7JCH/YBiA7vtgt4DCjrgeES9cEXyj5lELpZIIPwLn1ifkWexQCbHphqKIMQsgADsCQDzr0ZHjJZwDtU9n/zJAvkNNmkIQCgZycNqQaQui2mbIQh3O65tVDJSbqBG9fKoY4iS9NfIGqCRh0AsQagiEhbgHSyQKjOPnUiKACiGola4YD+9fXFlX19/Vo5VMxnaKYn9AUADwGwe1xeBGCEN025EkAGRQC+4LQj5NfXBcl8CQvGphhxACYNfFErplv9exsAnwo1QFKFKH66CYUIvMM5tKqNMVv662LLGBaMFwgAq0ahbolKsTocbvQDaqsW8VrYFjDj53EIRxWsHBQ8NIqcETgqlEy+Lh0ZL6YOADM3lQAMFabWTItXvOunkA9zyISzsD68qx/06IcF46U54V2h6svL8ixappXWmVc4CpuBTbE0Qcf+ygZjBIDipkwVAxSFlbUaccUCmrqHXESOPtBv+4NajbnIQxrpKLTSIGc8395a+GQfN7B1ld1Y0wBtgLjIv8AOiocOcACIVVO9QuKLIKCmHqJVYd6DplmhJmE3TjrsC6ZXhi65VlOzAQZQ08NAJ+LpzaGiPHNbIoaI9wq8D72zc3IXjWjKMZrJ6wADqJWicKeDQFQDT/ugqBwuRD1uy4tfDolnYOrETQfov4zkynmgyTiQPtAKM6crxQ0P+J73B2YqZIJmkAfUSpVZIpBMECAf2ABQfeLE3DTWVMjcHuIBvUiiw7DcvTlkaK/B23kBpel6taZCGi8ZAsAsE2kqkOUAhWHt+AD5RE7Y8VRI98TDYtAs2OpXpifqhKHbmOK2G1IRUz9+szOEBdB6rapI5cFzTGBeCwvBTQqvgqj44ZsDAOA1c6oKguKiEJnAsoBFjiwOrfKPlgUHZMEIL5nrdyaSCrQJUtYUYBOkFjmS5mZmbykmztcATA7wIUs6LKUJWCIUUrKswFJbpxU+y6tcH7/2wdx+dRTKxSrFhiwOe1+ROKfWifXG5JUJxss3W9RikTKBnh+kThRYa5H220o0NSevAHTf3snuVCdCuNHTEYsLrAJl3bJbyBcIOq/OKJV8WMqa+OYpPiyGvTe0LVVkT6Og7/WlmqPs1cvWQOVibT36wZvTpMLWYGZ7aoJl3wtcb2fHoc5FYj0b12gEoOi8332CoPf9rX6H7ysnaAS2E/rfnltrI9wdzrQEycO3+AEvzKWqSW+hSgXr9TFyNlqLxg2s2tqUfo17AfS8PlYIhA0Oet+BskH9cgcFioxCXV4fZ8t5F8P4yYYaYQPNyGayjPbQIBOY9we4UVALN+tV+BZOZsvRyAIx7o1AxwZn/Z1gS6ynWiZAu2i6+rfiZSGVW5kGOIB/Xexn880uPk8wEqnMmmdnHxGLALNwJW+aXTyLOdb/IAOMiGz0zUauqdrJZN5YZe4CBdpkJQ7XG+3FmaXfroK9EsZ87c5sZaMBNwIxe7mUCfReMr0WJ1ASvXXkjS4c/QO2/dIYAgHZ4G0idrNleu1aWkMtUKgtK3If1/qoze/o79k+0St8X6+Pd3NGmzVB+/nkmAUAHRJqN5/ZSjex42+ofr6xuyz9s9lOSynfVJarwYpU5AAUU5OaoSLrDdoFOlk6+gfvrQQjMErY4Q29oXfckkIGgkhF/iFTEHqnZHvEm1BnI0v9iwTsCGwv35tQZEag09VmC5tXlRMAgLAFG/56u1nh/ddTx/3j74xfDJlBsPa1AgpvddywoRK+YYylI+ydIySvNkdnY/HMMf9w/2N1wemwi93ECb0A9lVvpcDe6s6fHEyc4Q/cVtojXnyOvT7yhj848rwogr83cu7T6WzkDH8+cGNtjx4aBd/8o4Vpx/qwo/Rv/W0AnSyc2P8vzG/JdMDGXEb8C9f4MPwf+asL9uzFZPoEBPP8YjR3tV9GPzJ8Lsy4o8Vs0jccOoXGo6udWX+I4YYK+Hc+Hy0Xs9lkMpUymcxmC6a8r/2bL347+B8gAAhie+p8JGTeq5l/ZTR8W/13hCVZj6m7g1/OftL4SCh94/5+NHBYj2ZemvzRxGeueOD3MQ+R3kD9cRAhj74lhAGX0WjJw/NZqv4RIFSmQ/8fHP0tEP873f/kn/x38h/MrD8go0GiLQAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J70" s="6" t="inlineStr"/>
       <c r="K70" s="6" t="inlineStr">
         <is>
@@ -32524,8 +32980,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>https://petersonacademy.com</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAAQlBMVEVHcEwAAAbv7+/29vUHFSAGFSDo6OgHFSAHFSAHFSAACxrX2NnExsigpKeztrgkMDk7RExSWWBmbHGSlpp1e3+DiIwZzrrZAAAACnRSTlMA////Xf//0pspdOmoQgAAEftJREFUeJzFW4dy5CAWPMDCNjnp/3/1ulFCYez11q1PtVvjCYLmhX4B9J//PFyfbx8f7//j6+Pj7fNprvv19j79s+vj7bvZPz/+3ewrhv/v9F9DePuN6Xm9MIZ/qPvr9SSEz9+bHtf7/3n+O4Lfnv+G4NfnvyD4xv6MwPWz4XmH+fongyV+7f5CxOZD/RECUUOY0zcQdm98ZQCmzymyU1Kq9M16Lrdm3uPyMsKrW79RgMjWAERQtmlVfqqCWdnZKi8mE+304uaPLwUgitRiEk7VrNX8w/lxu1c6exWEiUrHFzL4SgAmSa0Fhmmzkj9df0dQcd9M6FraFwA+vhKAxSWSqkG59BfzU4Ra+So5kgwvRnjtAqKpoqsIWsOS/mp+us+stazCW6/yswzeXnIQYGcVo/STSOmVEX0zf8wJLiSnrPIrEXw8aYDeB8uZQ4guNSvhTz+3wcUGpHSlOGF9kP2j+68ekgAzAS00kFRxVeJerV5p8BsEQWobtG0hy9x14O7jfN5NAPcZOJGrwTqfZyfl36y/jzRLaVt2uJqeBcjpTqdvNycURckE+vHW2TlIJUP8y/lpBV4r6Zu1LnghmpQ3QngAAKVnAHBSwX9Di9/FlK8uI0wJVkKKtgpR5c0WzcfVCSAApwhA+RzN9yHtW3SMo6kE2LHw0t5E8H4DEGRVWUSZhTHL7OblJPhB/AKi2SBgIc1CAmq++dMdgHZVJREaF5+LYUyK/PsyTU8RMlTs5vggp+Xr2P9sEKgRfoZn3fngBmCS3kvRghDFadUYzJSyYe4ohiuWCiuxc4GXWt/ydPp2Ss1byVi4RKUANrURvqjtNwA6AdlJi2QlbFDwfp0rsCilrYMx+xCCw+BA1SZOJRKh8Nv1y/4tCKQhDnTJaBCyi5MVqjn9FYCFAZurIEAVvIQ7gogpBiwq5dkH16/ga0mUwmznhOXBU7DkGvrXIfi5gLxjK0J3gYss9exUa8GB1cTZqEYAolAEsmjvZ5UxP4IwrNExJXG1jUqIELHTYNo52TgjYoGzWsk5pVwK8jdLD5ZxZR4oX85NzQ4IIFSTh+zqBEBDZ8LOMEObHNIJvEtQGhITzckkXhmj7fYGnwJAB5QhACwfjAMZ1Ll78GyRFnnaJyhIhaSr1YE077x4AgCmZAYE9BAqboBG4DhOpD7Vdp3eINamblXGnE20CxlDYe2ORCr6gjh0E8x0HiUgutC5XusUzNaQFOuy/leXrHkwa8j2ZGJAEJPt6aRhakvNQDRVDhnWCABf02jAl/PCvyCliITuSwBpAIDgcyI6M4HSvOwah4imFpYsc2TkA4CBuUHhUETq1BU7JosB/hxAkKeAi4gGZl9S89gHzQra0jCVJwBJBacRBCq9rvXfwCkrBLPMNQDZ/+xGeCwY1DEoAcrGR0sEBsEWKjXMIkIV0jwAyHB9FY2GQRVQSesOVNXU+nQWXi4dbuW0u1ROACgsGQ4L51r8Sjw0MOS2Bj+HbyImPQOYFZyaqTjGXm+Eay5zdfOcRSYY4R5UAB12Qe1mYDDNso7lSwlpCJsLMq1HAFAB0lCbUIo4u93IJYQ+cC9U8HFihrS5xghgtRa55b+QIwx++BajBkSZotKjCiajbcJ3LIXm3ZgAK5cDALgVvIjI8iCBLhYEjR1A9cId5g6fbkgyhC5qkk9GSPeIKCRmlGKDHIWeu2j1AoBRHejgcDcbgL3YjNCw34mQLtthohBdBnhXdVJPbshyMsNWkQnhlwdwLKLPZToAx7yG8J6MsDoUQ/mQSI5jTd2TTeSZzs1DmbID4CeyWutdlmMpjORwAdAlQDOiF4jFMM4AJiYP4JtNBTbBpgZi4gBJzxrRfP/RBgDZB7zfWwSbpo5FrADsZgMQvukOYMwSIQYbEG6JUXLLvXsGMo0XQptszjoGhGmtmDcAlWrhTFZ6c2azAUBFDuYCFy4WTzwZ4cJYciOCmwQooi44y6lWP9sAQLFN9DUieIkpHvesNrBIgJ0S24cwWV5UsArFHTZQTjYANgbHZWb93ZDqCYCTlGvs4RtkcxgJ6joxuKFc5YGwaW9G6JZvdtm1aSyKkR8ksryTPSJfAUD2oGnyBvxskBzcMA0A9Crp1RMvwcgOAug8oIcsnF7Qk1xNE3arqjYAQTawA0frRHx4b1yJCHcRdhEL4VGM9gZgsIDFsO2Q+3DZLAsMRocC1FkCXhWrYgHRNWXHZRRl+oy2tIL1tXmuCwe1xthzdkOnh0KWSw1jeKYtkUXthJS3XowQyRs+qhVa0HUoYkXVa+TpWeCeDG7vr/mAHJWup1mfPFoCvBEuBcSj1T5XAKB8Oylkw2T6sYDbvPDFJed8zojkUCwKMnM8USHibRWhWB3lCm1jQvgl6vgAx0G0cqNdVfFFSnRRwVJKHODhBuWkAzqxqFUi4oQLADBRsy6jmNGj7xhV8lcAzkkp5DjORzcYWxLMkRFdUaREu2ZqQzBCwqpdsr6ODRkMmdofSwB2d+Z+O8bjVc6W/YqyI90BAB1KvCLzmLSzovgyK90Kk+cLJaY/FaPwRFtss9XuUt6MsNtoYPWkSFeHFOEESr68kDsolkq8bP/HP/b3TChHFdAOq4Yhdj8bvYAKYW8GSScLsl1udIIYU8Q1xZT6H+v79ZrGt+MX/TKgkUM/jHfgTwQk9rBFt9cFgJAoxIxBQOjzuz2KCtRyrbRWePGltfWl9Q9bMts3xzW8SYMfIuv1vf9nSZdict3ZVgDItpEzY2aW4v6gExqRckvd3V/4b734EYz8tX6gIT8d8RCL78MH1kUIeAtrrwBCXzvCjeiUvadyIHNQ9+vLV/HSQGmj3gwAyOHsFkAoPbtqAwBoRuooou2lmx0A1Gln03u78FsA1Ryk0usWhPuEFZFb5GADcHdnEQ2FFqggrN/5i6X8CsAkf+uaDwC2KDFEixsABRkgk4FdI69YQ+4WjKwsTBFsZFgKarQBuQ6AOrlcpLADkK6llCte55xKPWhitIGqZhLgjHJBurpWyHtOKF1W0rh2jkY9J17fsHzX562TDUAKohe/ya0dnLDUDbIMXgAO8D0WtaJ03FKnnYhg+aAHVIaokOWhdjCZXdfQdSj92BLcAEyekczV5FL3k6muAJDMDDygLEsSGx07UNdoSPVYCWJFRDqigWiaFfX6jo0naYfetfBL6RpD7+qm6GJvqEW/ApjqKWNDpHNCJuWT3Oz8iAVWuknNOlrv4a5mszwV2xadGcz84KODBEL0gcE8TOwUztGvNf0QjMySdjnWZkLvxedRGUErfrZhRqRg3RG28ryaXYrsYFc55H2UTpeAz4ktGKig8HWVAKz6QIuaBksnPJ3h6ZO5AGDZoioqswBvYQm8aJ5G4DYdGITxuXchNpn4JV2ZQNg+1AjYBa+bCmRsG6kLtqkFqiJvawjKXkuz/hsYB1t01rJwWidheZ43m2Qxggp3z+kPG/BljlP2MeQaI147AAxhd/WRZhiNPRSjBkseG5VspYFEsPZeAqy2j5ixNxZBlVgWAoe7AAgiznPBEviaxQoglo0FeoMksUOHm09bMIMKBMuW6GQvU+WWMlAEB6F3Do27DjYAk2/w7hqiy3x1HQBMZReAabJn7BAE4+50cOoGwGQdaD+m1xIgA78XuUGz6brBJOvtfkoAcpHAQUQcnV7ARu1OaF76HgRBbJh+mp28AOjpCCwecUL3MrltqwRHDa0WDIr119URdjd0lT3kMMXCVzcDgEzx2B5hoO+ipR6M10ercsgJqTXNohP/UQjtyTkotDA7337HbpeVZxWEjIQJ2RGG5es8N9yzWYrpy0u9s4P/Re+h8GwD7E6wuwAR9H3bof0FUR4ResIC1r3gHUDfX5V2zr1LATPDF04vvmbiQoJYtEDaE5S0hyOf2nRYmec2i6u4OSqCXUDwbdwadzATr9bqfuOBo1xbwyBG8WvmD4YDTwMA1uYdG8UoTPQjD8xKzqWnUZOXkYC3GgHSMWlHAM7yS6NtA3DPhDBY2To1uLF34HKSWL9OdWxCnTYskAz6CWTXbFSpd6LWoxvG8CiB3KscgxqWSnyREeGHdTNANud7TytLwRMVDn+OO7jnPSPI1jFkuNm2pQmylilmsjZOOuwMBs4SrwBgxX4XV+zMLWbtq0fZWSd7mv+ya8byVrOZq73V5AQZ1mVDBjKBy/eUCCWm2I3wfGUIejdZJ5kFg8TtbIsscM9zUnPZtkMuIxlzERGX/LRtiQNz9gIlHX1IuNsDAOYLbtcxy9WFgVAoeY2U7LoXfts3FNwE47616yn87I7FkBwzJLKqwUwPAGC1CSna4cHSdyGS5+A7rl73wu87p33DGoym8Beq+HZ0C5iQ0BiOPYmrDVC8/NHxA60iDRnFANJWpk3XPd4HAP0S3PJiDJuGapnbqchq1S6ECwDkVOy1D9V9ZhqoAQgllFhG/gaAiTnnntiRNahNN/QrjGHDPe5COKlA6sbtjFOfF3lu5R26LTvKuaR4nvAmAc1iXFtfELzJf24+CGjqasAUiFRGXAAwznoVLn1eBYuA4SBVaKi8eb7ssn1+l8CyK6QUCJ1uo+bzwQ/4ieKuBTu7gwqo/TLmq8uPLaosMF/O3N7uA3+7fc8i3YbSuGHuMjs2Q++x/4DpEoSNeLUXp5KtINc3W88AkH41h2GUdrU1b5W//OLRCxhruCWe5irmjFznOuzkYVtYsEuVsaBzLT7K92MMvpZSRIUDtMA4eR3qCUCnWVsTfCC3uc4tp+l6RIJbwVjuzDRLkload7Iuguqb7KXNSBa58Z6qfTqP8wSA8xVwsVybQwjgSLVPhzpNP6iGcNkMRgVp+JP0ufFa/LaDIRezzo/HQh8A8PAG5+ahAMc2Lc1S8pzCkEv2g2rc2wDHWBXSCRxXC6PrY3CIpUzrBzluB17uADgg1lwLu54FeTjdSIcuEOatBy2xr++xejeeHSWXcwAN5usnl2Je9hH6COF27Od+iibzABoPpaKAzvBG7hQ4lZgrYGA9kjmlwNUP3VmBuoXyRqXJigI8MKOy6SG5lwr2+3NEAOrZoWYVGlmIWZOTMvgYZonR5TgjzxGN0zPcWfgxm07cGgEA1La9OZTWPZ7veGDJjiVvAoCAgQJqdhKeWzfz+2HZg52PO03VJJsIGTYqME2ZyXkfKvs6dQDXw7kPNtAtJrNXNvMIkaxMy7ljzH0OeJ0PajmXcUUOY0NFBFJgLJdQoGY9ViuPRIja62hpvyeiviXJUUisaaqkUktzmmYCQOnIrOVKKb3LqWOZmcnga25OcMmSzdrGPkHpWzx/wIRdB7oL2/U2MP0oc8MYOcWEuI7EDBHmeiiMvhoMXU8m2C6MNuS+wYeyGEW5XOzifjz3gYqX7T/CpS+rTgmsyCeU3sixEw+68jq3wVVHzf4U5d0mu+2jKrkQgva0n9t5wgciWs4hIHx4cGjOiEthGc1VT+36RAQXYS6Ks96jIpO+1F4gOYSCzCHmhRX17STZMxXzEJknt/UkZjkXlKtdOpAxqeVczXDCrjeoVrrjVjfX7Oa0nijiEChJM6PR/VDpx+1EpUESUrpHD7/mIJEY4JTZLxuGrq6Hu5BBett3hWWOMEbMQ9Ye2BEKco20dT8d+3E71GoSfppofZfDyCzdHVOaTmk09eVs19Ke9Z1nLFssPl2DJ4/XusbTXTcAbw/HeqNfk5ybxRiRwrJfGG414dqz1fV+mp/b3h1duR++/LwfbEYm2S3GP50X7U0cUsR1K0tmv56TebqLzKF70Xb96ulotym+0oTuA+HiSR4Swm03M4B3wxTD3dCnfli71BDuh/TfHw+3i2sGdAzEU3FNVDvdq3KDmoHV7YuDtss+2vV6++kTPj5OFYXywxk7hJ2m7WzKj86B//QRLyyRPir2o1QDABSOjEgPx7dfX8szHj95xq0/8bIeKbsiwMc/PQj++fOn3AybfFrJK4LOCqGYHx0E3540+uFjfiTe5t3KQEvO60It8THt/er6wwedHq41QkTupqa4Hmr+8SH44fnPn9664XisuP/0Gh82+/2H7a6P2/3a057HdXnu89cR3J47/WUED8+9/qYd3B85/Ttv/Nvr5fPX//Kp7+N6/+oZ9H8P4cvpuyn8S0W8f/zRE/ifbx//e0G8vz8///9fbLuaMd/wCb4AAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J73" s="6" t="inlineStr"/>
       <c r="K73" s="6" t="inlineStr">
         <is>
@@ -32584,8 +33048,16 @@
           <t>Gap sweep of existing evidence text (Claude-identified, Jul 2026)</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
-      <c r="I74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>https://freechapel.org</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAARVBMVEVHcEz///8DAAEfGxz///////8jHyD39/f///////8aFRY6NzgRCgzl5eW8u7zQz9CmpaVST1BlY2OYl5d3dXaHhoZHcEwCo99jAAAAF3RSTlMA////mw///tVJ////////////////AOmrS7wAAAaaSURBVHic7ZvpkuQmDIDXMAPd2OD7/V81djvmlEDYs+MfiapSm61tow8hiUv8+fO/BPL9/nrJ5q+JfH29vzPq36+/p9vJ6/2oehzh67fU7/KV6v+17h/yelh/QvDr+iOCXx3/Uzw/eD+hv2neTw7ALq97BtC9McO8yWBMry818b5oANkPS9uxXbpNjv9pl6GvTeL/muC76iM9jJtKxbkIhHO1UUxDnSm+a0dAD+2uXCCyQ7Q1DO+6GOwnxlDlFoKxqae2+FXjAqZlqqT9EMVaQ2vzcAKS62zqi533zUBDkB8Awg/1WKP+QBgpvkAEWDHj80OQgVh/CKAXXapZfYJftJuITyZIY4N3ouiNFIA1sf6mXEyD0dZ5pN5Sk0ghOJtvA8iRJdqRdKPN1EVjtXlC3sWLAJqrSP04ZJqUZmJdYAbFs75YAuhD83dsKY6qXrvAZTjLfVIAMIF+xRZSlpUz6wKCTErIAxgWtEMK7ANhCcgzBFmAQL9SxOx6SN8yEkEOoA+amDDX09uqZF3X2UQ/CKIX9YMMgPYa4GyAf7QH3rEq2f6MEp/xQpIzZPhwAOklWIV0wIgg9bAl6kLrfJFz2II4wOjwlYDxkxSZdHN0BGqsA1idA6gWhp+jFAn52uR+A09NGEBf1q8T/QLwFJ8AGkcMQFjjcoG4/5TO0JCrulHggg6wuq8w95WpAeBwby1oBwwCDKALdtvFpABKQT904Qx1BgZwEYDF/+aC4SJlX5+0sLGcPwGRAAK4zqkJ0x+6AGdLZnfmIiodIxCgtTZT+NQ/+gDZGddvsKUAmAww0CjiXb70eIsQgG0aSV4pQMEAXlQlJgAAPNzc/C98gNLWRtplWswKAFjv6qK55QZAM5y9it06BdA0A/gAOV89xc6tUaspgJ1iVNYAAQAv6nfNRpklBWix0Yrk0yWuPpuirgxgM3fkhgmAHQGeC4EDgLNumk2/SRmgWU7XCscgARgQU/mMu8p+1//vFoW0ve/hhhMAm+AQz5ar+JxJsW3k646DTqcJs0sMYAMWSUI9QyJaz1P7kXFGuGwy6vyuxQCIoay4NWgY0OZzbqb2/zpkR+ya9sljAOcCYD+8RUCQ1XW4EYKdEuxbDHD6KgfXFs6VI8IhWJ0gk/jpXkGCiQHOLFBoYwdAwASy+HNLmCATxADWUeBx9ACC5BMuUDmcmM7xC/45ArBpCFkJ0CwgYAtoyL8igD7vg6gPzBQfkFAYRADWy5E0RIoC9EjknBH9T1EAuIlGWBOE3ey3GUkdwtAkfnq4/4MI4AwndILVwu65w35Ks0zjOI3Tgh+Wn67a4QBgpIQyjMdcwHlHPhOPAbwQQwAUDtDsx5Jay5ZzttZNRwsdIGOBU/YB7Vi7zMMmPw6Qt4AF2LeDnyUR7a6IMATWCeFUkgIcv4YnDhSAEAVoGN4COD/JREEpEd0DEOVEVErFtwAoqbg0Gd0CoExG8pyO8TXxdQDKdFxakNwCIC1I3Hz78wATZUlWWJTeAiAtSkvL8hsAtGW525iUnKAa4NyY8OzGpLg1uw5wfsCzWzPPCQqZoBaAujm12SJ7QnUBwG4NC9tz74AiHweVANa5SgcU5COaSgA7tNGW5/ohVSWAQAybPabLnn/WAVQc0/kntTkT1AE4A5QPKr2j2lwyqgKwjkU5qvVNkFn51wB4fkU5rPZO17H7okoAm15px/WeCTLHxRUAA26A8pUNmpDpAPVXNv6tIRoJZADpTpUBn4IBmsW77EPcgAzgmZN8beedrqO7NCrA5PoC7fkxAP/qFp4WiQDLxatb//K6AwloAL7+qsvr8Poeur4mAUylbuQKGLzSBKiAgAAgxzsFDFEJR5IPygC9VwN1oYQjvJ7myQgWAeagiAVLaDmA8IKctaETFwB0UIJ2rYwnOgRXbPGHMQsg56Co7WohU1zK1bHZIeQABh6WYF0u5YoJOOssAgogBxF9lNthlAAaraKT+LNmFwHol6jyV6lb5XxgQSNfjIQAZL+2UTWhuF3Q2AD1Sns96ej/nTdSm3lksXYgeq8AbBkFKGoN/7rf36ZlPR3/kaLWZp9T8jXVYF2vimvLbgDs5YH1hc2U0/QPwOOl3Y8Xt5PL+w21vJ9c/XmU99c8cJj3Bw65vrMWu72G5HjgcO2JR9Lz/YnHeOmJx5VHLlP6yGW6/Mjl2jMfqXszHM98BtPrWt0fsS+dnn7o9PxTr8cfuz3/3O/5B4/PP/l8/tHr889+fw0BVb/Lw0+//5PyD0/loojoIXqOAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J74" s="6" t="inlineStr"/>
       <c r="K74" s="6" t="inlineStr">
         <is>
@@ -32708,8 +33180,16 @@
           <t>Batch 9, Jul 2026</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr"/>
-      <c r="I76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>https://adl.org</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAD80lEQVRoge3XW4hVVRjA8d8658zMcS6OYmpUhmk3hcrQweogCmooPUQXhB5CeuhVPFD01EOBL0EcKAh6KKQoooLCkiAKSjndE8TKlNA0dfJCNDM6c2acObuHvafZM841owvsPyz2un7r+9blW98mIyMjIyMjIyMjIyPjf0qYtLVUbsMKNKRqD6lWTo7p14Tb0TyOlDp60YlfVSsXU+NaknGNiS5HVStHZmJAYYr2dXg1mQDyeA6Pj+k3Fy/ipkThNBEu4iw+Vyq/jL2qlSEsxmtYgBx24OmZGJCbsKVUDtiEdsxKUiM2KJXnj+kdUERTqu9wak5kXI+H8SYeGTOumMhuMEMmNoCFWDNO/Q3ibZ+MLhxO0k84J94JmI+nlMorXbpbM2YyA1aJlYUa+pN8CzZOIfc98fEbThvxihGFr8KDU8w/LSa7AxvEWwufJvm1SXmdUvkK1cq5CcZeUK10psonlcpPogPLk7pVeOevqT3C+CtQKi9MKUu8oh+mystw2wznOo20h5krviPR+N2nx0RbuAI3Jvmz2INPxGebKGpRr2+Y4Vx1sTdKzz25G58GEx2hu9EsioiiA4YGjyg0NMnlDssXOjQ2Mrt9sxe++15r2zw/HNhvz0d14bL1mTGXGnDX9nlyubUKBYqzWHDlaes332No6GadJ+cIgeZmis23amraKYoGtc/ZJor+RQN2Hm1HhxCW6ule6dyZ5ZpbaGmlOOsB9foWIeRdvUi865Ekk8fgP651iuEd6MDboqhdaxtt7Ul1RBQ1/tk7iuK6oSEGBhioDWidvVet75Qw5fIXjA41BjH0dxnQgKIQCCFWtF6HPiH8hjM4JoTD9n+72qkTa13ooa+vXz6/Q612UAj5KeZaZsSFEsdGvS7zIg8b0C+EI3q6m5zuXKK7i56ufnPnPWHVnbv117rQbevii+7Y9pAQSkIooE0Ia3BwjNxrlMrDj10Oi/Bo8h1mD/rGjFuiVF4vPppjGcQ+9IjDjppqJYoNCOErDQ0bvfvGY2q17ep1ougXUX2XZ+8/NkpMPv81TuHapGa9OL5J+/NNSf0wjUa77H14C21jlNyC+4y/Kz1Je1H8kn+GH2OhWxef9/wzvfr6Voui+Bjlcl/IF06MI+g4vkmVb0lSOq7JGwnSiinl6/gS21Qrx136FhTEj1txgtQqDgqXYpFSOYy40Vxu2MUcFK/mB0nIO5pqZUCp/L74TCe32nXioC0YP5yu4Wd8jF2p/4kaDhkd7E3EBfFd7EW3+N8hSr8Dh3BvatLuSYS9jt2pcj9eMv7DGInP7/lRPzMxR8VHZjpBXYTfxZ6roFoZmMaYjIyMjIyMjIyM/zJ/AKPdGnMBuVvzAAAAAElFTkSuQmCC</t>
+        </is>
+      </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
           <t>Position carefully -- an asset with center-left/institutional audiences, a liability with parts of the evangelical/New Right coalition. Not a neutral partner choice.</t>
@@ -32964,8 +33444,16 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr"/>
-      <c r="I80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>https://pepperdine.edu</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAI/0lEQVRogcWaf0xb1xXHP2nSNMX1G9WAybUb3HRLH8ZS6Fp7kac1aZ1VhEoNKBRL1UTapItKgpqIZkvIFNbwB7QSjayWJO0SJYU/OvGjg0wT5Q8YuErcxLA0SLbxlEgxiR1acFViAw2Q5O0P/yhp8MMG032lJ+v53Xfu+d57zz33nPOWsQRQiZaNcR5dGvY0jaWyr2ULfVElWvKAPGBd5FcbuQAwGXPvaW93uGbfeiPXJWCAMLFLC9EjYQIq0aIFNgJbgI2CUpFuMurQ52jRidkIyjRMRl1CsuwON8HQJG7PEM5Bb+R+YgzoBc4AvcOeJu+iCahESzpQCGwDNuabDZiMOvLNBjTqDAB8/gDX/COc7xtkLDiB2zMk26FOzCZdULDekMNqddY9cuwON53dfXR29xEh0wC0yy27uARUoqUQOG0y5qaXFG4gf9MzCEoFTs8Q5x1u7JErGJqQVXg+CEoFJqMOk1HHeqMOvZhNMDRBZ9d/aG63YXe4xoDXhz1N7QkTUImWPEGp+MpaW0a++Vl8/gB/a+ygs7sPn380IcX0opaK8mI6u/vQi1qqahsSek+jziTfbGBnaQEadQad3f3srTxOMDTx9Fx2snwuIcoM/d//8var2pKiDWwvf5/9h09yceAywdBkwsq3Nh7iZ8pH0Kgz2VJg4nF1VnRpyCIYmuTiwGVONHbg8gzxdnkxqx5aSc/ZAXE84LpvFB6II2djSdFzHDn6WUKdzoZGnUlr4yEEpYLmdhvF26oBKCl6jjdKC5KS1dndx5Gjn1FS9ByEN5D7EI8AglKB3eFOqkOA1eosBKVizmeJ7lKzYXe448oDGQILRXRXmQuCMi3V3aWewGp1VqpFymLFUgiN+oZr/hEgsgyE+MtgMVgSAs3tNurqW2L3xduqMRlzqdi9NeV9LQmBksINrDfk0Nxuo7nNRmtDFYKgIBhcnNObC0tCQKPOQKPO4HzfIPDD7uOc55ixEKTciOV2Gr2YneruUk9AtwRKyiHlBH5qLIqARp2JyZgr6ymXGgs24n3lr1CxeytOzxB6MZvmti9obrelUreEkDQBjToTa00ZgqDgxaIDOD1eNOpMdpYWcKq+IunZyDcbeKN0M83tNjq7+pOOL5JaQvlmA11t7+LzBygurcbp8QLg849SVduAaNxBc9sXsjKisbKgVHCqfh/W2jc53zfIG6UFOLo/wFqzC406M2GdEpoBQamgunIb+ZueYW/lR7JHbEGQP7Bp1BmYjLmcqq/A7hjEaH6LYGiCuvoW9KI2TKTrQ+wONycbP583BpmXgF7Ucqp+H9f8I2wqOjBvRDbfiXPf7lcQhIepq/+Mk40d9zxzerzsPXiMqtoGdm4roLpyG4Lw8MIJlBRuIBrYzD7bLAbGTeUISoXsWo/OSF19CyVFG7DWlMVtK2sDJqOOF4sOpEz52QomiuY2+Z1NdgY2Fe1fdNZhqSE7A0uhfDI7TCL4ySOyVEdssgQWMlpyMfFCMJ8O8WzAa3e4tXpRm1AiS6POZLU6676TaDSw+fF/JqOOa/4RfP4AzkGv7FLVi9podsSbDIFet2fotXyzYU6nZTLmhlOBhpxYsHJ39AZ3AzeY7u/lzpAHgJ9Hru+v/+CdX04TWPHCWiCbFTnPAuEY2unxxnKjswct32yIBka9cykaL7VYqFFntnW1vRvzlCZjLtEcqXK5xIy7nxl3P9PeQaacZ+OMw/xY8QstK7U6VuoMPKh7luXZa/H5A5GzUR+tjYeiDrRorvyoXHL3qrVml1YQ0tCLWtSPrmKm/9/c6uth8kLYg65cs45laUrujPq4/Y13TjkPKB7lwSfC5x85olFZ0mSIB7UiaZv/wPLstTS3fcHeg8e8w56mJ+YcAJnBOVx3tOW0o+tDpMlxJls/IvSvEwCk/aaAR0r/hPvbmVigvv6JdKb7exnvaOD2N14eUDxK+usHufW0GedgOBZeveM9soad3LKdiQ2C4gULj5T+Gde1b++RdTdwA4C6oy0Ah2X0jA+VaOk5VNMgSZIkNf3DJn339dfSlO2MdGfEL0mSJH3e1Sc9ZdguqUSL9JRhu7Sn8ph07oJLuu39rzRlOyNJkiSdu+CS9lQek1SiRVKJFun3hfulEw0dMVl3J0LSdd+o9HlXX6yNwVwuSZIkHappkFSipUdOxzmz01EoM/S2iwOXX3tcnbVKENJ4saQKx8hd/GNT3IxUWHrOhjPeU9MzuDxDNLfbaOlx4vl+FT5/gIceWsk/O75kJBCuUYwExug5O8DRTzrDskaDSIDbMxTLxVprd3Fx4Ao1Rz4dAzaPB1zJFzhmzUKeoFR81dpYhXtwiL0Hj833yqJgrdmFLieb4tJqgqGJ54c9Tb1y7WVnAGA84Pp6pbB26EzHl4W7d25hS4GJzu5+pqZn7murF7W8XGDi1+t+xfTUTGzUZ0NQKnj+d3kUvvRbYBk3g5NMTc8gKBUcP7KHJ9c8FlU+blUmKQIREpeiJJ5Zt5bjR97i8ciR4MrVsLG1NlTxyzVqLg5cxncjwJNrHmPzJiM6UctIYIxgaJJ8s4HT9fu4fPUGFweuAFD4kol8s4GK8mJ8/gBlb38QVf6TRHRLqswaKa327Ct/Jb1i91bsDjduzxA6MTvm0KpqG+8JVKIlI72ojdXZgqEJROMOIOyorLVvcrKxk7r6ljHg+WRKrknXiSPl1jaTMTfPWlMWjqIqjyMIaaQrFbE4OR5Mxlycg+E21toyTMYctpcfwe5wXQKKEi2vRpHQEpqN8YBrbDzg+nhsKiu9qc223mTM5b3DO7hy9QY9Zwfmff+6f5QtL5n49MQBXIPXePWP73Llqt867Gkqkttt4mHBlXqIfVJw2mTM1VpryhgLTfBObeOPq/IxRFPsq9VZ7D14HLvD5SVcQu1djB6Lhkq0vKMSLd/tqTwm3QyOS+cuuKStpdUxx7S1tFo6d8El3QyOR53adyrR8s7/VekfQyVatCrRcvopw3bp/fpW6bpvVIrium9Uer++Neq1T0fsKCVY1BKaCxHl/gq8phe1AFHD/gQ4nKyRzoeUE4gi8p1FXuQ25Z/ZRPE/eCX8O/paofwAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
           <t>Leg-3 anchor. Its Middle East Studies students/faculty are a bounded pipeline; the planned Center for Jewish-Christian Relations is arguably the single most on-mission institution in the database.</t>
@@ -33028,8 +33516,16 @@
           <t>Interview transcripts (primary source): Johnnie Moore Fri 19 Jun 2026; Dana Gibber ~Tue 23 Jun 2026; Paulina Mon 13 Jul 2026</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr"/>
-      <c r="I81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>https://tamidgroup.org</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAABAAAAAQCAMAAAAoLQ9TAAAAZlBMVEX///8+tehXV1m1tbY8PD5YWFoVpeNjw+weqeRQvOp/zvBewezDw8SUlJU3NzlFuOkzseeDz/AIoOJxye6k3PSS1fInrOWZmZvKysrk5OTR0dFBQUQXFxqBgYPb2dkwMDJQT1J3d3mY0EM5AAAAiElEQVQYlVXM7RKCIBCF4QOyJSsBSmlGft3/TSaloc+fM/POzsKJEw/hfLkSTqTxAsJrDoGdd8yB9XpR1lhdL1WaukTbhEPgBtrfD+HRYrOFLAfTPf+hf5kC8T2kUDUOfVTRQqpbCqFljJOaJegXvsZ+UKcAdBY0L6bYmSWCaLZqZ9MPIpmR/ACjVgcLZ6yNzAAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
           <t>MODEL + PARTNER: closest existing analogue to the BFT internship pipeline. Study their campus model; their chapter network is a bounded roster.</t>
@@ -33212,8 +33708,16 @@
           <t>theisraelguys.com/team; theisraelguys.com/volunteer</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr"/>
-      <c r="I84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>https://theisraelguys.com</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAMAAAD04JH5AAAArlBMVEUFWaQAeNUAY7AAf+ACQnYAUpMBWaRHcEwCSoMAgeMAdM4CRogAa78AfNoARXgAT4sAQ3UARXoAdtMAS4UAcsgAX6b//v7///8AguUBe9YDV5cAZbIEUY0DabgBXKLv9frR4/P6/P3m8Pj1+fzc6fQBdc0Jf9y10u2XvOHG2e13suo9leQEb8Eii+JZouYAPW2dx+4MYqcneL6zyN5Jg7uRrs54osxUks0+b55tjrCmv/4PAAAAFnRSTlMBkU/a+RoNAP71bAYmtqeGzmE9OOvP0AN9dAAAEnlJREFUeJztW2djo7oS3RQHp7eNFdtgakwxJmCa/f//2DsjUSRwyrb76WnvjbGQNGf6SIYfP/7ffq9po/Yf0/5xMbm5eUI7pT83k4sf/xEKonJxc3p1cnt7hnZ5eXl2ic/b25Or0xuB4t8Sv74B7bPL17b1V6/Acnv1dPGvJEGcT55OJNpH2uXr5dmJkMRfJ/9jcipR3242SRRFQUotiKIk2Wy3LYqzk6ub678KgUv+tqW+TaLUtzzHtW3GZmxmo5meFQLIpgFxKXTx9+j35DdRankuKKPNusa/Mtex/CBpMJydPP0lKRD5RvabyPdMWyEtN7oBEGnSauLpL5gjTO/qTPCU+J8Ql0DYrhUJMVye3PwhApA/vRWKj6yvqfcgzFSo4uxq8icQtOunk0sheyL/LeotBkdAuLyFNf42/Ub628ByvyZvWSqEmeMnwhonv4dA0yaC/SQ0vybPnMSHRyp9thc0QvgdNWjaE3e9berMvhY+s9PEm6WWOpK5IRfC7emPX0agXZ9y8SdQ/nGSzJb4tcNtOvM3FlPBwhqFEK5+1RCgfsG+eZQ8OZsVJX4LgTmbjedsI/Ds2YORFhfCLxqCdsHVv/GPsg/78qx087retCJn6WtqB1uP2X40sFebORFXw80vIGjMLwmPGh9z/WSz4dEhcPkAZm4Sx9pEYHeTzsyhEByuhl9A0NCPvGPSnzEvavPe68YTCNNX34wgADNKHDtI7cEME+KCM3wXQSP/yDnKPvOSPv9vuQ5gAYnpwwpn/tZn1jYcToRmfkEGLX33A/FvJPopH8SCV8tJEofRHzdJxjMZC7+NQLu++pi+HUY9eR6faXVof5ZuQ2hi65M2jiIPCfjt176gaZ/QZ862p594dmOB0cZxNpHJvG1kepvkmOfAbwnB5cn1Vwi0p7MP9U/WLgFoXMQm7QfkkdE2dIPXkQU0c7kdXF59ERO1m1vO3EclR7TuDUCAhOI3nreFQ1rbyIY23ONTYT4pEJx9nhdggKRc64M14IKkgyTlmggEAG/zGiEOMht+CG1YHyYO6OorQxQGuPlAiDMRWCk8ppIPcsbgAtAE/W9/NJcSQ/RFUBYGkH6W/ZjpULXBY4GwVHgmEEQ+3I/74sdzKWB8agaIgCTgow4gWGBtNczduhEV3JAbRcpSRQDjCs5m/qdK4B54RIktYdt0PM+y3FadrxHPlXbaFq0bxXpNzxl6JHO5Ej7yxYlQwIi863kOlfzY/2ADxIkIrhF3OgFQeqJg1Is7wObJY+oOggfyy6ejADTtpGNKJk8FLnZikPl6TR5gcT8TbEPlDK7PPQdZN5U4hldSN23d5JKOR4PboyLQni5HHkjkN43rb7EpwlKNhTZ2CJLcHJCEUCXIU91GMa9rqmq7W0J5V0cAaNckgFSxQCp72rgT+Y5iVtyeXreeK6yBxKJMdaSkKYdWrrFjOYG7oGqBqO370GsNbJq5whXD5u5MbSx8VZrfz4uOuqKIgYGsxIb9Ztudjklw2XOI0TB0IC7yWZsoEjz0zi1EMHJFIQDJixDhuKFHoeBlMwwxjfXxe6PcIWI2TMM1PW4Mm864mR0cEYGwgECib/LlI+RcEXjB5ZBIp2Z/FH8Zn72OuNlQIt72+HlSH1nBzZk6yETew4aU5ovo0YR+ubURaOi6XeEgFuRVnLQ2z6mXpwoA7QeC4DqSQEZrCL+xiKYMjEZxTfRvwtmw2cH6VcpqSGFygGcWhUN1q3JxC3/tWAT/88TvwwdPN+tRkCaYiE7j6gF2tm7iJJeA6/ip1y/H7GT9eqaYoXZztl5vekMNt4klGTZRQguGacrfUvfWV3vJBai/8X1kSzrDSiK/L1VS3FZ0oF3R+v0STqjuSIGIKKkiIDtBdF7PRzYAAWC00AwsCHPn+NdLED6yXp9IpZGm3arLtxmklZrgaUgpfF3zpV9VERCwOclLfLWj+ZwEMu+dlVS8PpOMQJv8nM8TZXXKQZCa2X61tnOsI1fczEzQtaX+QRmSrtHXkWOEgCbLBHwMkXSgnYKPVKkmWUirzAO7LQYCLEEg+5byAbTUPJW6USQSy1KXQx3zteRFsNL5/EQCcAJW1ErQDjjsTeqHYWhZlscJzVOLrlEeoEDYcj4dLgeLerBnpgbx4kbIr60w9P2UA5hHfbiCVc/nt50OtItbSWSNfAXq9Zbahhppey4uNwmVJjSAYj2nl/CuZiA3OdH4fN4hA6BAMf/ZOSKccD4wMOZxhtv2Jj7W8pe5MmIwcnDNh8oAUD/Pe0eECZC2VRM4tvpxOt9tCgBhBC2CK8h2sKVMRyTIk7qrdXcx+NKPGAlI3m9yF2qNAJmQzEgNMgkHsI2CALVohI805cYEn8OVH3FPwwU13r+NuksMocs0oMl0lL/lQlP8nHyzLQq0CWywVm3QFnNQadm2aZrieFw4OIwFpQDd5jsYkmtKKuHFjJcQJYtODHkhb7uY7XBu3pRoAbd+O2uqY2xIR2HI4/TfUhEOWVeIohOy4mGp5wjyfBP9HNharuxFHODiVJIZg1v/bKxQe/759hapNpi+oc3jSDUM5gMUxGIndFdaz8L3GIHG2uAiGaYG/403NY6G27cOwCkABPIM5tRE4e1tq8ZYxjhln68YyMtFHJFLH+vhcam9EYspjgYhvv286gHMlZqTWbUAPR9slJm1Ru92iz9KjYj0BhEkXEDJsHr2EYn4YnI65zOawpBLQC16bSuo6rpOAm/ITUDCjrGasg+H8onEdowZteU8DYOoSqJUPvbjQm42idrVz7fd8GTJxj50vLkE8DrmsqkGyvFIZrGwhAGyGoybjmOqpbtZv8WfARhsKntg3Dzj3bAKslMu5liNJ8xOd1vPzK3RYswkCVz0AIbKDvMPTsnh1GB0VAQxsyL6c7VC92CVvp0MVx8DiEcAojgyZ0dEwHUQjwHARXe4MQg2cVyEbhSPtvwcQBx/AmAW7uIk99yh6KDTmNpIBcypRv0sMOLKAiuulzvD8UMA/tDccwyoAx+VhmLuAAYniOOhEULZ/IYsAuYV8a6Oa8eqi1FJ/wUA2poGdWzs6rqSY5SZxKLNc3U7ZtXNDSUOp+ioPXjIqKKHG8ZG6wWnP2M1DvANGXM9H4MgVmnHRivGNTFbK9qGooVk4p28wQWVOMWfwHTy4Y8IRRzfNyclABDL+1I35ecU9ENsCI6Nzj6YWRiQipUDljyDkgHG1WQfhpw/bB+9RRy4Xl3Yg8ABAH0oNuJSZqc0KqcRhVMbRqseZpeGYcSpbdf02bPKXN5hmeJDrjsq9FS2VRtDI7N2RpcLbl5okDQg3C1rsTWDcRtG98uQv4MAqHIId4YyJTX495nP+2U7DAtjGYS1UdpeKNf9sGajy4YTAKhNWQfgtOa/lsLtjbjdDHjE4C6noytiDK7bNKvAVxi66Icd9nsCtyQlAJRVV7IhsjzuAVzcGoZaERHfRUn74xxMB74fUr1VxVi+DrEBMBtWTd4cTjagb7y/COk8E1uC0M8DPqlyEL98JaQEsfHSlmQ/TmhSZ2mM57Dd0thVeUC8xTvRaCljVxTIkzVdx3XT+BfeXfBLjEHbFe2cwvLqZWCbfUhhNkC/dKckV8ZylzcAbJ9UyGZOuVsuDfxn4E/TaLGl0V0vlRtGd0FjjGUzkL7uqmJZQoNlfwDg1Evjrj2v1E4xuGx+gLF3RTjjTuhxCMZSLGiIq45kA2fZfyq3+jHiS2V7heF3GRlms1x2x5WwQoxorNCussIX5/B2bijLCmJNxIsFjd2u/YS4+b+joAqEQ6M03TYlwLaWy35ndA0AbbRmoZEVeYMAo3Z1VZZlQNJYLusgyNsWUMcuCPiNkgxO6l9W2BNgXllRM5ZFXi9LxyvLzs+Wy5f+kEa7X2ZxEylQde2yXcmPuS3ID8btuq7tg062C227czG3zsCpn4Paqu637Sh10L8K+NM9Lm0LTK/KlnEGn6mWeVvgVwDQH1lrz9ky6yzEDYvVsqjAS5FlCPkiBCzlIa2ollmxA7mlUnD7S8JqSScGvpFlhgeu6+akCnEwW95Lh0QXL+CiDWCM8K1WWZatsqL5XajKsuVKLRoQmNGZEbtqiDGrFforKbKZGLnzyqzwZiE/qrJzTHyWz4jusZC0vOtXBULKrrIsjzO7I1KVWgYhn2QkFwCbKf18tJH3RShsPlvuVoU1C+BtDcYX+aDw+hTsyvmIzTwYlQXVI7Iz4gB0coU+8WFwBENgkDXGF2GfgO0AONGRC1sfaYDyEQaovxWQtXnFKisdwIBCVtWoEPVq6i+GJ6VgmPcjundnreipXMR1UbIFuK+eE17cQ+nDuhDxcrVaLQ8VZq9WxfhXeVgrWjE+KS0xHiK1w64SygGo2mW81mYu5r0MTqtPV6tFNQSQr6Q2VADXJLUsGB0iBxm/EVZZ63d2tUCPCLcsxO37we9GkxdM8IZG1pNf1OMa3c/ErUHFSccEYuYu68XjZItF0TgawLw8q/S160cSgbrfqyT+F+UQAPAtmpuqG7p5YIZZO7GNHVDLTtSFzCIBjJ7ruYEI9gor/l7WAHyYqWGAC3WfrYbWk+9hrmU7b9+aqJM3x/808eV0SF+7vl8sVlKoQzRacA7bv0XQPR3DSwY/W5BgCMbiIM3z9vsQUlgt+D/ca5ynO2cJ94vV3fhnM+35ZbGQRYBxvK3av8hRAoEdIlM4BXVnnseHdRZKgqny8tBMppmq9UKz6BwJgEdDWQSIJi3t/lMcccDG96VX8s7KtQO635oXY8FiHwYrPkn8W+zV4ydi7O7Yk12oCsBRt7cTnK066quF3iSGcK+3vZAYcw4cmyiiXdAOmHdY9G2ll7KJ8uHPR+gDweNioR9aVsLVYtAyLgB4/yJrBcwFlmcEhQIv6Gc6AioL9/JESbEocrDu3Qc/n1+80JpNVAn0AX29qffzvV7mgkXu5NxaFxQMsPpeJ49gs1JXZvZKsAr9IwFQbYjBjUvZ5QBAqwDvoMPm+ToLAYmB7ELXEQzogjOAPZw0Xc/ajSFzD+i//+gRCmQEIiTssMKiyr9QKLnkEAmArmeHkCuFVgUV0G/FNAtX1Nf+62JloOuLIy7YIbh50XWdxzxIgFbQiQ4tMa1YE8Z1KB4w9n4g2KYgp1PLVrreRl5miz6xBtYUScADxGMu2LfTB4zgKStvFhAfWSk80CymZFIwEHh3vpiWwi4PUzFw34dE56D3K4h+BO+prg+zkCqC63sa7tsoSPd63/ZNwmPBFMGAWaspxbd8kbWPsQicC6kKQiDrp3MbYBzTJwrgCCZ3uj4llZllN3+6bx9cdPbTg8fsw3Tv0xHDtDFvxiACGifnEkSyVgZ8OuoqdDx85AG9GUAJRGUGc+erTqeHsM1oAUwNWYDrnpXTNtFwHQwBCIYxv6GPkIlBz18+4as9P4AwSdgJ9jR9T3sEsSR0CAsE53t0QexCMYxcc0pNDboza48+/cAfTIXCMnx7/Pr5Xk175FxTBW9ii22ZXb0DARToDvRpzohpkeco/BAhfboYFk2wmEPOtwLY59Oqnxpgh+AHIThHTG7zSy9T4twrzum8Bx6dc868iuRUel44foyLfjJvQHL633u6GNXRA8nAGjwYwpySjD5f6CE5yfmBjlDMvDif7g/5B8++NzyYAcn//tvPFl8/TrntjZ5qYySGaUkZabqAobo5tL8vw8+ffQfyxS/RR0wmBOf7fLwuCykFId2dI8lCDtND/tWj942N/gJ9rgVCoASWZrWcBOOW7zAHCCIMjx5pyxPId76v/w7Bj2fYwTkFhOHy9DCdtQe2bzVUh/tzrPT4HftXITzfCTWMNmQz8q/yg58TBmNt7wA2pg+/83y/Nrk/Pz9/16uhN6CV5fGn7gfkmQn20e6ef50+2vXF48P59Px9nztDPTjfom+HB/0d9O9/90UX7fr5jguhCWfy4l+Tn1nV/hz0Hx7/4C0XbQIhnL8DQviFsQ+Fz7wS5EH//ua3xN9DgBDesdJ7kX/lcBJ1G/H5ncjfPf/p+16agEANEc/58mUn3De9/DDl5En6f/66mYa42EDQD8FnGPghnZVX+/eG/B+9ZaVAmDzePbwLMRzK3DLlR4xn/cmhF2JTOBXk7x7/TPkjCM/3D0IM70h+VZmHnmOKY8uZ7dLrhrQj1ZshD3ePk7/81qWmXfdiIBT6fr8vDqLhEummvQXmny/+wXun9C7r5PSulcPxdt7w/o9eveXv/D5DEA8Unwakzx8e7u6f/yH1BgN///X59PHx/u7u7gFYHvB5d3//ePo8uf6P3sBuyFxMunZx/V+//i3h0P6rl77/UfsfNbYTSKBfI4YAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
           <t>HIGHEST-PRIORITY PARTNER/MODEL: do not rebuild what they run -- study or partner. Process the full theisraelguys.com/team roster (Andy asked for the whole team, esp. the influencers). Warm path exists via Joshua Waller (already an IAF Top-50 tracked ally).</t>
@@ -33276,8 +33780,16 @@
           <t>outreachjudaism.org</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr"/>
-      <c r="I85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>https://outreachjudaism.org</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAIAAgAMBIgACEQEDEQH/xAAcAAACAgMBAQAAAAAAAAAAAAAABwUGAQQIAwL/xABIEAABAwMBBQMIBgUJCQAAAAABAgMEAAUGEQcSITFBE1GBFSIyQmFxkdEUI5OhscEWF1VicyRDUnJ0krLS4QgzNVNUZIKU8f/EABkBAAMBAQEAAAAAAAAAAAAAAAACAwQBBf/EACQRAAICAgEDBAMAAAAAAAAAAAABAgMREiETMVEEIjNhIzJB/9oADAMBAAIRAxEAPwB40UUUAFFFFABRRRQAVD5Re2cfs0i4OpCyjg2j+ms8hUvrSR2q5Gq6XkW+M5/JIRIOnJbnU+HL41WmvqSwRus6cM/0bWNXlm+2ePcWBuhxPno19BQ5ipWkhsqyXyZeBa5K9Ik06I15Id6fHl8KdwNFteksHabN45M0UUVIqFFFFABRRRQAUVjWtJy8W1p1bTs6OhxB0UlTgBBoSbOZSN6io/y3av2jE+1TWPLtp/aUT7ZNd1fgNl5JGsGoteSWRs6LusMH+KK9Yd6tk9SkQ58d9SU7yg24DoO+jVnNl5InP8gFhsa1sqH0t/6tgdx6q8BSfxPHncmvaYqlKSyB2kh0HikfM1t55elX7IHFNFSozKuyjpHXjxPiaaeA46LBY0JdRpMkfWP68weifCtnwVfbMPN930hJ5jY3sZvrsMqWWhouO6eBUnoeHUU59nOSjIrCgvOBU2N9W+O/uV4j79a+dpGMDI7EpUdAM+Nq4wequHFPj+OlJnCsgdxnIGJJ1SwpQbkoP9Anj4jnSt9av7Q+OjZ9M6VoqJueSWa1KZFyuMeMXk77YcXpvp7xWs3meNODVF7gkcuLoFZcM2bIn6Kg/wBL8c/bUH7YV8OZnjLad5d8ggfxhRhhsvJP0VAxMyxuZKaixbzEdfdVuobSvUqPdU9XMYBPJg0s9qViLbiLzGb1SvREjToeivy+FM2tedEanRHoshIU06goUPYapVY65ZQltashqc5hLr7qWo7S3HF+ihCdST7q9F2i7gEm0zdB/wBsv5VvXeHLxfIFNpUUvRnd9lzT0h6pp14zeWr7Z2JzWgUobriQfRWOYr0LfUOCUorg8ymhTk4yeGc+GBcP2fM/9dXyq4rUrEsOQ1u9ldruklze4Kaa7tOn+ppzgitGfHtbig7cGopUkcFvhOoHvNZpeqc2srg1R9Jqm0+RVbLMfFyuRuklGsaIRuDTgtzTh8OdMPPLhLtuKXJ+2PIbnoZJY3iNdfYDzOmtb8a52ZsBiLOgJ05IbeQPuBpN3/H8hnZFPlXSzQpafpC+wk3GbuMqb18xKEhQ5A/GklN2zyy1daqhhDXwi4SbljNufuTzTk9TAL+4Rrr7QOR5UpdrmNeSL55QiIP0SeSohI9Bz1h48/jX1Bxe/N3CHLslktkF1DyA5NtdyKktp11JWgqII06U3nsjx0O/R37zbO1B9BclvXX3a0qeksoacVOOGKO1B7OcMdsjiFeVrSjtYLigfrWxwKD7dOHwqi+QL91stx1/sjnyrqeI7EeQFw1sOJPrNEEHxFbGtHVw+EL0U1yzldrEMlf07KwXA68RrHKfxqJnRZECU7EmMqYfaOi21jQpPtrqPMMhYxqwyLi+RvpG6ygn03D6Irm6zW+fmGTIjbynJMx0rfd09Ea6qUfd8qpCblyyc61Hhdxh7DcW7Z5zI5rfmt6twwrqfWX+Q8adIrVtVvj2q3R4EJAQxHbCEJHcK26zyls8mmEdVgKKKKUYom1PHzcLWLnFQTJiDVYA4qb6/Dn8ap+yvIDbb35OfXpGm8BqfRc6Hx5fCnStCVoUlaQUqGhB6iufs6sLmNX1aGioRniXYzg6ceWveK10y3i62Y74aSVkS4ZNkV2i5JlrEeU8ymLbGVRk+qhSlAb4HfxNbJwfGLdGbm5hdH5z744uz5R3VK010SkH51GXa4NZLgUu9MIbTdmGkxZxHNTYWD8iPEUw7um6KgRhZxDD3DeclpJCBpzAHWpPMeC0GpclPXZdmkoIaat7RKyEpUxHe5/1gOFQm1WzxbVHsUOL2pYYZeQhLrhWQNUnmffV/ZgZApwKfyRhI1H1bUNGh7xxOtU/bUtIk2lvXzuzdP8AhpqXmxCeo+Jlf2JwGbjKyKHJ3+wejNtrShZTqCT1HKrQbdsyglcV+yhBbUUKU7b5CuI67279+tQewL/i18/hNf4lVcLgMn+mPohZVaNAs6MONpCkDoDzrlvyMap/jRAXfG8bZxy45Fg9yftz0Fpbu9CfVuFSRruqQakMRuNwuueIkPSXVx/0ejOKb3iEdos6lW7yBOhqRuzV2Ts4vycgfivyFRHyFxh5u7ucOg661Xrte/0KwS1zoAR5ZuEWM2C8N4BKEDXh3afeanyymcFL2v5Qq+ZI5CYc/kNvUW0AHgpz1lfl4UxNi2LeSbGbtMa3Zs8Ap3hxQ10Hs15/CoRGFQs1yK2ZNbwhNomDtZ7IIBS8nmnT948/HvpxNoShAShISkDQAdBTSliOqFhHMtmfQoooqRUKKKKAMHkaWeQ3a35vKuONNbiHmRvQZJVwW6n0h7unxqb2mZJ5Dsio8d0JmywUNnXihPrK/L3mlrs3sD14yJl8FaGIag644Dx1HJOvea01V4i5vgyXW5kq4k6zYncV2V3x6YkJuUtjV1sni2knRIP31eL9FjzLLCVLg26ZolJAuD3ZoTqniddDx8KoOYLf8vZ4y84VpNoZW3r6iQoaAfE0x5yHV2qEGru3bUhpJW4ptCiRujlv8B8DU5tyeWXgklhfwqDFrtrE2IWrRhbay4CN19W+njzT5nE/Co/bYdLnaf7O7/iTVuYMdUlCE5x2zoIPZkxTr7NAnh4VUtua0ocs69RqUPDX2ebT0v8AIiXqFmppGhsB43W+fwmvxVV1usZp+Q8FYCmX5x1dX2A7T289ePtqj/7PzifKd910/wBy0dSf3lVfXXYEa4On9NktSHHCexcfaIA/o7p7qW392UqXsRrXKK1C2b5AiPZE2ZJivq+jpUlQ13PS83hVVz+yJvmE2ebBWHLja4DK3mAdVditI46e9P3GrplQ12eX5KJkeSTCeIdZSEg6pPQEiqvhjjo2jRo44sOYvG7RJ66bun4n40seORmsrBUNkGXeQr4mBLd0t88hPHk256qvHkfCuhgda5g2j40cYyd6Oykphv8A10UjokninXvB/KnNslys5Hj4jy3N64QQG3tea0+qrxA+IprFn3ISt4erL1RWByrNRLBXhNktQ4rsqQsIZZQVrUegHGvYmlZthyXdQixRF8VaLlFPQdE/nT1wc5YRO2xQjllFyS8SMnv7skJUrtFhuOyOOidfNA/GndhVhRjtkbinQyF/WPqA5rPy5UgLNdHrNc48+M2y46wreQl5JUnXTToR31a17W8jHJm3fYq/zVturk0ox7GGiyCk5y7lpyO1zXszyBzybKkW+XY0NOOsKSFBQUeCQfSVoOX+lVmLCsitDKw7K7mtA9OWpR4dOGoFELa7fBLZM1iCY2+O1Dbagrd66edz0qzZ3m97sMiJJtqYT1rmthbDq21KOunEEhXtqChNNI09WDTZq2myYzd5bcJzZ5NgJcB/lDqN0I4a66g6/wD2oSTkrMhzyLYMKVf4lrcW0h+cVOqB14jik6eJ8KuGzfPXcmckQrolhuagb7fZApS4jrwJPEfnXhtWsdwTaJl7td9mQEQ2C4qHHO4hwjmrVOh1Pt15UmcSxIpHEllFUOSMxkuWq+YKuxxLoUsPyYKS2rifN9Ua8+WtSV0sths8ty3R9mku4sshITMQd4OjQHXXn1qY2TW26v2aHe7lkE6czKZJ+hyPPSlW9z1Vqen319bT9ob2KvRrfaUx3ZyxvvdsCoNo6cARxNGcywkd7RyykzrNaHWylvEMttaHODjcRe8hQ/qkmrNg4kS9pcm4N2q4Qrei1IjMmW0U6bhSANfCtvB88ulxsl1vuSJiM2yGAG1MtqSpa+o4k68wPeaqDu2y/lxfZW62pb1O6laXCQOmvnc6MSfAu0VzkZm0rFEZTjrjTaR9OjauxV9d4D0fcflSCwrInsUyNidooNBXZymddCUE+cPeOfvFW79dmQ/9Ba/7jn+al/fLku8XaTcnI7DDkhe+ptgEIB66Ak+/xpoRaWGJOcW8o62hymZkRqVGcDjDyAttaeSknlXvSi2FZSJENzHZjn1zGrkXX1m+qfA/cabtQksPBeMsrJiqTP2ZWW4TX5ciRPLzyytZ7Ucz4Vd6K7GUo/qEoRl+wv8A9UlgP8/P+1T8q+Tshx4/z8/7UfKmFRTdWfkXow8C7/U/jv8Az7h9qPlUtMwaC7iC8fbefW2jVcZbygVNL5jiBy11+NW6g1zqS8nenHwcqxpM7Gb+l3QtToD5CknvHAj3Ea/Gujoci35hjCVqR2kOexuuN68RqNFJPcRS/wBtmJBcf9JIKPrGgEzEpHpJ6L8OR9nuqJ2I5OIlwdsMpejMslyPryDgHED3gfdVZ/kjsu5CvNc9X2GlLetuEYmVJSUQrexutoJ1UrTgE+0k1zgkXHMMn57824yOPcnX8kj8KuO2nLBdrsmyQ3dYcJWrpSeC3v8AQffVo2I4n9CgHIJrf8olJ3YwUPQb15/+X4VyPsjsx5e+WqLHc9nsG4YtAx/6XIjRYgB+p0+tVpzVqOPHU1X07EbJujfuU8nvG4Pypp0VLeSK6R8Ct/UhYf2jcPin5UfqQsX7RuH95PyppUUby8hpHwLe07ILTabnGuMO53FL8dwLQd5PTmOXIjUeNMcVmiuNt9zqSXYKKKK4dCiiigAooooA8pLDUlhxh9tLjbiSlaFclA8CK5gzjH5GH5O5FaccS3r20R5JIO4SdNCOo5V1JVJ2qYkcnx8qiNg3GIS5H7196PH8aeEsMnZHZCS2fY07leSNRVhRitntpa/3NeWveeXxrp9lptlpDTKAhtCQlKU8gB0qs7OsVbxXHmo6kgzXtHJK/wB4+r7hyq1UWS2YVw1QUUUUhQKKKKACiiigD//Z</t>
+        </is>
+      </c>
       <c r="J85" s="6" t="inlineStr"/>
       <c r="K85" s="6" t="inlineStr">
         <is>
@@ -33332,8 +33844,16 @@
           <t>ffoz.org</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr"/>
-      <c r="I86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>https://ffoz.org</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAADAAAAAwCAYAAABXAvmHAAAGH0lEQVRogcWZW2wUVRjHf9/MloKCSBHbBVrp7hoSFTVi9MVEa1RivRQqVo2XiPGWoDGRxBijBh98URNjog+aKCRqIlW7bSRGjZdiBO83Al63raLttqKogEDtzvl82AvT7cy0M1PD/+mc73znf/7/nd35zjkLMTDS01w/mE1dE4fjiGOoK/XyYFfmoSO1vhWXQNFnBH1wsCt103QICotpMMBvAIJcGV9OeMQ2YImVKDXP0aeX18TlC71+XALB2KXm7JHj/l4ely8sYhswytxK26IlLl9YTMMTsJZUOmrOi8sXFvENKBkX3Zlx+cIi/ltIZIWrVzfUmWqKyxkGsQwUxeqp7phYnBI0Z1fP0oVx1qxGLANiy1pAxgVtTgiak3DGLs+/kjk5zrpuRDbw8+ameSrcXh1XQ2PQPClYr6qtr+/sPHlG1LXdiGxgxmjNHcAxEwZE5gVOrHGaUZrmJg4uibq2G5EMDL956tEq3OkzbPvEATDGbgWwjTUtVTuSAfPPgVuBBV5jqgQKEzFtAI4tR8bAj69nakHXBRDu9xsbyqaXg5wOYBvnyBiYfUivBhb5jSv8FTD9rnJDbDt2DYIIBgzcEJyhf3hF89nms1CuOxxxDoRd2wuhDAx2pxsFzgvKUbEGqmO7e5bOUbU24KoZqmZfEM9IT3P9VDSFMmAZuXyyOZYh5+6rImNOYSNwkju8vzaRD+IxjrVisKd56WSaEpMljBMjejYamDJ2aF+hzx3IZ9P3Ae1VeSMntuZGg4gMLMNYxwDfB+WF+w0Y0oHjwo7mNT8dKneHspmLAK8D/5dBNMPdqWUCd4mYryeTFM6AMD9w3OgX5eZINpNGdRMehU1VPvGjGNiwZKYx1vOAGf1TP51MUigDosFVFqwtRYGIo/oscKwnj5i3veKqyMy5iadATwM+cz9N3xUnSxi3ABpkQO2E8xZAvjt9C3CuT97uZKH/wwmTFcln048relOxL54mqxHqR4zIP/5jfFXfNjCi67HyRu9FxDtN2SQdOO7YL52L64a7ZmxEuKwcs5SXpyIpnAHwLFIAGH0DYHhZ6mJEmv3SRHja3R/KppejdCqkXOEdydW5nVMRFLYS+xoQsd4EUEuu8stReLehvW9HuT/4avpOlG2MF48onVMVFK4OQJ/3F4PdDfMWb4UcKOf7zRflSQDtxM4n0k/CxAMRcMBKmGemqinkE9BvfYRtkpbewkg2k8Z/o/dDsq7xNYB8TXoD3uJReKq+bWBkqopCvoWs77zigrwI4GBOD5h8r7T0FvJdmbUo1/tkDc8q6MNhNIUy4Mz418tAf3177mMANdYyz4nKtmR7X/dQZ6pJ0cd86FWR2+s6+v8OoymUgRMu3fUnMFwVfkmkvENSzxsJhXtEUBJyPzDTk1zkiUXtuZ4weiDCeUDhm3EBo9kKmXjdSOgLi67o21r6fdzow/lR8re594TVAhEMSPG1V8a+5I7+yv5HmWDgdylYdwM4qg/AxPOywJAU9Cq57fOxsFogyqFe5YPDbf1G1mNco4urxK1LduR2l27jrp1IJnsEVizs6N8VWkcJoQ3UHsWHUNoKiOwpx3/e3DQPOMqV2tuwqu95gIRTWMPEmrPfsqTVXdiiILSB+a25vQjbAQQqb4yaUdt9yWVQWSeC6nos4OYqmn2CXNqw8sePI6l2IdLNgEDpayQHKzG1Z7tSNi28IvcFQP6UzIXAEtfsPSLmgmR7bkuUtasRyYAa3gNQzJyKrIRUDIhIZSsgtq5xTf3dMU5LctWA74EmLCIZqJ0l7wBjYFX+XsKYowFQHWhYWfx0f+lcPEuVS0oZezF6cePqge3xJI9HJAPzW3N7ga2gdeWYGp0JIJZsLhc2u6Z2BTAbGBORtoWr+z+bBs3jEPl2TNE3cG/cbFEAVe09nCSrS40Hk6tyvfwPiH69Z2s3QPmeX7X4qScKZhsUt8ygl4C+n9ze/8g0aPVEZAOL2ga+dwqjqZMWLCgWMhEDsuf4jp+GAYbt1BnAHAtZW1XsphVhj5Tj0Njx60H4tUg0VrvNqTlUubU2lrSI8lzcQjUZYhlw4/iOnfuBjeW+qNY7hkeni98P/wEDAwf46Lu9igAAAABJRU5ErkJggg==</t>
+        </is>
+      </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
           <t>Verify Jacob Franczak's role here; process their contributor roster.</t>
@@ -46016,7 +46536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48815,8 +49335,80 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Organization websites/logos: 66 of 85 done; 19 need Andy or manual check</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Bulk Source</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>18 Jul 2026: proposed a domain for every org, then VERIFIED each by fetching it and matching the page content -- 57 confirmed outright. Added 9 more whose domain is unambiguous but bot-blocked to fetch (heritage.org, nationalreview.com, newsmax.com, tikvahfund.org, nationalconservatism.org, reaganfoundation.org, pjtn.org, hayovel.com, cufi.org) -- a 403 from Cloudflare says nothing about whether the domain is right. Logos fetched for 66. Total visual assets across the database went 30 -&gt; 113.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>STILL UNVERIFIED, deliberately NOT guessed: ACTS 17 Collective (acts17collective.com did not resolve), National Jewish Advocacy Center, J-TV: The Global Jewish Channel, Passage Press (401), Institute for Black Solidarity with Israel, Bay Area Center for Faith Work &amp; Tech, Echoes Media, New Beginnings Church / Larry Huch Ministries, Vine and Fig Tree, Stanify, Evangelical Foundation, Congress of Christian Leaders, plus a few smaller ones. ANDY CAN ANSWER TWO OF THESE FASTER THAN ANY SEARCH: (1) BUILDERS FOR TOMORROW's own domain -- buildersfortomorrow.org returned an empty page and I will not guess your own org's URL; (2) the Evangelical Foundation / Congress of Christian Leaders -- Johnnie Moore owns evangelicals.com and .org per the interview notes, so confirm which is live. Also: Stanify and Vine and Fig Tree came from Andy's own ideas and may not have public sites at all.</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Andy, 18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>NOTYET (effort only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>DUPLICATE: 'The Genesis Prize Foundation' appears twice in Organizations</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Unverified Identity</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Found 18 Jul 2026 while sweeping org websites: two separate organization records share the exact name 'The Genesis Prize Foundation'. Duplicates inflate counts, split the network graph's edges across two nodes, and mean an edit to one silently misses the other.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Merge them: keep the record with the richer evidence/bftId, fold in any unique fields from the other, delete the loser, and re-point any 'related' references. Then add a duplicate-name check to the validator so this is caught automatically rather than by eye -- there may be others.</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Claude, 18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H73"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>